--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -1238,7 +1238,7 @@
       <row>41</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1257300" cy="542925"/>
+    <ext cx="1257300" cy="428625"/>
     <pic>
       <nvPicPr>
         <cNvPr id="36" name="Image 36" descr="Picture"/>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$M$94</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$95</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +21,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00 &quot;€&quot;"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -65,6 +65,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="006B7280"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
@@ -99,7 +104,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -118,6 +123,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00C8102E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
@@ -128,12 +138,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E4E4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FAFAFA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C8102E"/>
+        <fgColor rgb="00D6E3F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00595959"/>
       </patternFill>
     </fill>
   </fills>
@@ -182,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,70 +217,117 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -268,6 +335,15 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="00E8F0E4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -2071,7 +2147,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>75</row>
+      <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
@@ -2096,7 +2172,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>76</row>
+      <row>77</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
@@ -2121,7 +2197,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>77</row>
+      <row>78</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
@@ -2146,7 +2222,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>78</row>
+      <row>79</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
@@ -2171,7 +2247,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>79</row>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
@@ -2196,7 +2272,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>80</row>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
@@ -2221,7 +2297,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>81</row>
+      <row>82</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
@@ -2246,7 +2322,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>82</row>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
@@ -2271,7 +2347,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>83</row>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
@@ -2296,7 +2372,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>84</row>
+      <row>85</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="619125"/>
@@ -2321,7 +2397,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>85</row>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
@@ -2346,7 +2422,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>86</row>
+      <row>87</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
@@ -2371,7 +2447,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>87</row>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
@@ -2396,7 +2472,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>89</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
@@ -2421,7 +2497,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>89</row>
+      <row>90</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="885825" cy="942975"/>
@@ -2446,7 +2522,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>90</row>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
@@ -2471,7 +2547,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>91</row>
+      <row>92</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
@@ -2496,7 +2572,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>92</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
@@ -2521,7 +2597,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>93</row>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
@@ -2834,22 +2910,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M112"/>
+  <dimension ref="A1:Q119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="7" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="7" customWidth="1" min="12" max="12"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="42" customHeight="1">
@@ -2870,6 +2950,10 @@
       <c r="K1" s="1" t="n"/>
       <c r="L1" s="1" t="n"/>
       <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
     </row>
     <row r="2" ht="17" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
@@ -2923,7 +3007,7 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>netto zzgl. 19 % USt</t>
+          <t>netto und brutto (inkl. 19 % USt)</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -2940,7 +3024,7 @@
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>So geht's:  Diese Liste ist Ihre Übersicht zum Blättern und Weitergeben. Reserviert wird über unseren Onlinekatalog unter https://www.kikripp.de/katalog (Passwort haben Sie von uns per E-Mail erhalten). Dort sehen Sie die tagesaktuelle Verfügbarkeit und merken Artikel mit einem Klick für sich vor – so ist ausgeschlossen, dass ein Stück doppelt vergeben wird. Möchten Sie den gesamten Bestand übernehmen, finden Sie am Ende der Liste ein Paketangebot; melden Sie sich dafür bitte direkt bei uns. Rot markierte Artikelnummern sind Marken- und Designstücke. Abholung nach Terminvereinbarung, Zahlung per Rechnung.</t>
+          <t>So geht's:  Tragen Sie in den drei grau hinterlegten Spalten rechts ein, woran Sie Interesse haben. „Interesse = ja" genügt; lassen Sie die Stückzahl leer, zählt die volle verfügbare Menge. Der Wert Ihrer Auswahl rechnet sich unten automatisch. Rot markierte Artikelnummern sind Marken- und Designstücke. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung — wir stimmen die Mengen anschließend gemeinsam ab. Abholung nach Terminvereinbarung, Zahlung per Rechnung. Möchten Sie den gesamten Bestand übernehmen, finden Sie am Ende ein Paketangebot mit 15 % Nachlass.</t>
         </is>
       </c>
     </row>
@@ -2997,4799 +3081,5581 @@
       </c>
       <c r="K7" s="7" t="inlineStr">
         <is>
+          <t>Einzelpreis brutto</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
           <t>Preis</t>
         </is>
       </c>
-      <c r="L7" s="7" t="inlineStr">
+      <c r="M7" s="7" t="inlineStr">
         <is>
           <t>Lieferung</t>
         </is>
       </c>
-      <c r="M7" s="7" t="inlineStr">
-        <is>
-          <t>Positionswert netto</t>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t>Interesse</t>
+        </is>
+      </c>
+      <c r="O7" s="8" t="inlineStr">
+        <is>
+          <t>Stückzahl</t>
+        </is>
+      </c>
+      <c r="P7" s="8" t="inlineStr">
+        <is>
+          <t>Ihre Bemerkung</t>
+        </is>
+      </c>
+      <c r="Q7" s="7" t="inlineStr">
+        <is>
+          <t>Wert netto</t>
         </is>
       </c>
     </row>
     <row r="8" ht="78" customHeight="1">
-      <c r="A8" s="8" t="n">
+      <c r="A8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>BA04-01</t>
         </is>
       </c>
-      <c r="C8" s="10" t="n"/>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Rattankörbe 8 Stück
 Rattankörbe 8 Stück</t>
         </is>
       </c>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="11" t="inlineStr">
+      <c r="E8" s="13" t="n"/>
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>Gruppenraum 4</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="H8" s="9" t="n">
+      <c r="H8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="J8" s="13" t="n">
+      <c r="J8" s="14" t="n">
         <v>10</v>
       </c>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="inlineStr">
+      <c r="K8" s="15">
+        <f>J8*1.19</f>
+        <v/>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M8" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M8" s="14">
-        <f>H8*J8</f>
+      <c r="N8" s="16" t="n"/>
+      <c r="O8" s="17" t="n"/>
+      <c r="P8" s="18" t="n"/>
+      <c r="Q8" s="19">
+        <f>IF(N8&lt;&gt;"ja","",IF(O8="",H8,O8)*J8)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="78" customHeight="1">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>BA04-02</t>
         </is>
       </c>
-      <c r="C9" s="17" t="n"/>
-      <c r="D9" s="18" t="inlineStr">
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>Holzkiste Obstkistenoptik
 Alte Holzkiste, unbehandelt, als Aufbewahrung</t>
         </is>
       </c>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="18" t="inlineStr">
+      <c r="E9" s="13" t="n"/>
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>Gruppenraum 4</t>
         </is>
       </c>
-      <c r="G9" s="16" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="H9" s="16" t="n">
+      <c r="H9" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J9" s="19" t="n">
+      <c r="J9" s="24" t="n">
         <v>15</v>
       </c>
-      <c r="K9" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L9" s="18" t="inlineStr">
+      <c r="K9" s="25">
+        <f>J9*1.19</f>
+        <v/>
+      </c>
+      <c r="L9" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M9" s="23" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M9" s="20">
-        <f>H9*J9</f>
+      <c r="N9" s="16" t="n"/>
+      <c r="O9" s="17" t="n"/>
+      <c r="P9" s="18" t="n"/>
+      <c r="Q9" s="26">
+        <f>IF(N9&lt;&gt;"ja","",IF(O9="",H9,O9)*J9)</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="78" customHeight="1">
-      <c r="A10" s="8" t="n">
+      <c r="A10" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>BA08-01</t>
         </is>
       </c>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="C10" s="29" t="n"/>
+      <c r="D10" s="30" t="inlineStr">
         <is>
           <t>Konvolut Mal- und Bastelfarben
 Finger-, Plakat-, Gouache-, Acryl- und Textilfarben sowie Bastelkleber, teils angebrochen</t>
         </is>
       </c>
-      <c r="E10" s="12" t="n"/>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="E10" s="30" t="n"/>
+      <c r="F10" s="30" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="G10" s="28" t="inlineStr">
         <is>
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="H10" s="9" t="n">
+      <c r="H10" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="28" t="inlineStr">
         <is>
           <t>Konvolut</t>
         </is>
       </c>
-      <c r="J10" s="13" t="n">
+      <c r="J10" s="31" t="n">
         <v>350</v>
       </c>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="K10" s="32">
+        <f>J10*1.19</f>
+        <v/>
+      </c>
+      <c r="L10" s="28" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M10" s="30" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M10" s="14">
-        <f>H10*J10</f>
+      <c r="N10" s="16" t="n"/>
+      <c r="O10" s="17" t="n"/>
+      <c r="P10" s="18" t="n"/>
+      <c r="Q10" s="33">
+        <f>IF(N10&lt;&gt;"ja","",IF(O10="",H10,O10)*J10)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="78" customHeight="1">
-      <c r="A11" s="15" t="n">
+      <c r="A11" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>BA08-02</t>
         </is>
       </c>
-      <c r="C11" s="17" t="n"/>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="C11" s="22" t="n"/>
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>Acrylfarben-Sortiment im Holzkasten
 Sortierkasten mit Acrylfarben in Tuben und Töpfchen</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n"/>
-      <c r="F11" s="18" t="inlineStr">
+      <c r="E11" s="13" t="n"/>
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="G11" s="16" t="inlineStr">
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H11" s="16" t="n">
+      <c r="H11" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="I11" s="21" t="inlineStr">
         <is>
           <t>Konvolut</t>
         </is>
       </c>
-      <c r="J11" s="19" t="n">
+      <c r="J11" s="24" t="n">
         <v>60</v>
       </c>
-      <c r="K11" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="K11" s="25">
+        <f>J11*1.19</f>
+        <v/>
+      </c>
+      <c r="L11" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M11" s="23" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M11" s="20">
-        <f>H11*J11</f>
+      <c r="N11" s="16" t="n"/>
+      <c r="O11" s="17" t="n"/>
+      <c r="P11" s="18" t="n"/>
+      <c r="Q11" s="26">
+        <f>IF(N11&lt;&gt;"ja","",IF(O11="",H11,O11)*J11)</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="78" customHeight="1">
-      <c r="A12" s="8" t="n">
+      <c r="A12" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>BA08-03</t>
         </is>
       </c>
-      <c r="C12" s="10" t="n"/>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Konvolut Bastelmaterial
 Perlen, Bänder, Glitzer, Holzperlen, Bügelperlen, Schnüre</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="E12" s="13" t="n"/>
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="H12" s="9" t="n">
+      <c r="H12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>Konvolut</t>
         </is>
       </c>
-      <c r="J12" s="13" t="n">
+      <c r="J12" s="14" t="n">
         <v>50</v>
       </c>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L12" s="11" t="inlineStr">
+      <c r="K12" s="15">
+        <f>J12*1.19</f>
+        <v/>
+      </c>
+      <c r="L12" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M12" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M12" s="14">
-        <f>H12*J12</f>
+      <c r="N12" s="16" t="n"/>
+      <c r="O12" s="17" t="n"/>
+      <c r="P12" s="18" t="n"/>
+      <c r="Q12" s="19">
+        <f>IF(N12&lt;&gt;"ja","",IF(O12="",H12,O12)*J12)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="78" customHeight="1">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>BA08-04</t>
         </is>
       </c>
-      <c r="C13" s="17" t="n"/>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="C13" s="22" t="n"/>
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>buntes Papier
 Konvolut Buntes Papier</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="18" t="inlineStr">
+      <c r="E13" s="13" t="n"/>
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>Atelier</t>
         </is>
       </c>
-      <c r="G13" s="16" t="inlineStr">
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H13" s="16" t="n">
+      <c r="H13" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t>Konvolut</t>
         </is>
       </c>
-      <c r="J13" s="19" t="n">
+      <c r="J13" s="24" t="n">
         <v>50</v>
       </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L13" s="18" t="inlineStr">
+      <c r="K13" s="25">
+        <f>J13*1.19</f>
+        <v/>
+      </c>
+      <c r="L13" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M13" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M13" s="20">
-        <f>H13*J13</f>
+      <c r="N13" s="16" t="n"/>
+      <c r="O13" s="17" t="n"/>
+      <c r="P13" s="18" t="n"/>
+      <c r="Q13" s="26">
+        <f>IF(N13&lt;&gt;"ja","",IF(O13="",H13,O13)*J13)</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="78" customHeight="1">
-      <c r="A14" s="8" t="n">
+      <c r="A14" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="9" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>BA09-01</t>
         </is>
       </c>
-      <c r="C14" s="10" t="n"/>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Deko Metallruten mit Pompons
 Metallruten mit roten Wollbommeln in Birkenstammfuß</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="E14" s="13" t="n"/>
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H14" s="9" t="n">
+      <c r="H14" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J14" s="13" t="n">
+      <c r="J14" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="K14" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L14" s="11" t="inlineStr">
+      <c r="K14" s="15">
+        <f>J14*1.19</f>
+        <v/>
+      </c>
+      <c r="L14" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M14" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M14" s="14">
-        <f>H14*J14</f>
+      <c r="N14" s="16" t="n"/>
+      <c r="O14" s="17" t="n"/>
+      <c r="P14" s="18" t="n"/>
+      <c r="Q14" s="19">
+        <f>IF(N14&lt;&gt;"ja","",IF(O14="",H14,O14)*J14)</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="78" customHeight="1">
-      <c r="A15" s="15" t="n">
+      <c r="A15" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>BA09-02</t>
         </is>
       </c>
-      <c r="C15" s="17" t="n"/>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>Elefantenfuß groß
 Beaucarnea, große Zimmerpflanze im Topf und kleine Zimmerpflanze im Topf</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="18" t="inlineStr">
+      <c r="E15" s="13" t="n"/>
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="G15" s="16" t="inlineStr">
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H15" s="16" t="n">
+      <c r="H15" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="J15" s="19" t="n">
+      <c r="J15" s="24" t="n">
         <v>90</v>
       </c>
-      <c r="K15" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L15" s="18" t="inlineStr">
+      <c r="K15" s="25">
+        <f>J15*1.19</f>
+        <v/>
+      </c>
+      <c r="L15" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M15" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M15" s="20">
-        <f>H15*J15</f>
+      <c r="N15" s="16" t="n"/>
+      <c r="O15" s="17" t="n"/>
+      <c r="P15" s="18" t="n"/>
+      <c r="Q15" s="26">
+        <f>IF(N15&lt;&gt;"ja","",IF(O15="",H15,O15)*J15)</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="78" customHeight="1">
-      <c r="A16" s="8" t="n">
+      <c r="A16" s="9" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="9" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>BA09-03</t>
         </is>
       </c>
-      <c r="C16" s="10" t="n"/>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Werte-Rad
 Drehbares Holzrad zur Visualisierung von Leitwerten, Eigenbau</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="11" t="inlineStr">
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H16" s="9" t="n">
+      <c r="H16" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J16" s="13" t="n">
+      <c r="J16" s="14" t="n">
         <v>40</v>
       </c>
-      <c r="K16" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L16" s="11" t="inlineStr">
+      <c r="K16" s="15">
+        <f>J16*1.19</f>
+        <v/>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M16" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M16" s="14">
-        <f>H16*J16</f>
+      <c r="N16" s="16" t="n"/>
+      <c r="O16" s="17" t="n"/>
+      <c r="P16" s="18" t="n"/>
+      <c r="Q16" s="19">
+        <f>IF(N16&lt;&gt;"ja","",IF(O16="",H16,O16)*J16)</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="78" customHeight="1">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="27" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="21" t="inlineStr">
+      <c r="B17" s="34" t="inlineStr">
         <is>
           <t>BA09-04</t>
         </is>
       </c>
-      <c r="C17" s="17" t="n"/>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="C17" s="29" t="n"/>
+      <c r="D17" s="30" t="inlineStr">
         <is>
           <t>USM Haller Tisch
 USM Haller, weiße Tischplatte, verchromtes Rohrgestell mit Kugelverbindern, ca. 200 x 100 cm</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="18" t="inlineStr">
+      <c r="E17" s="30" t="n"/>
+      <c r="F17" s="30" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="G17" s="16" t="inlineStr">
+      <c r="G17" s="28" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H17" s="16" t="n">
+      <c r="H17" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="16" t="inlineStr">
+      <c r="I17" s="28" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J17" s="19" t="n">
+      <c r="J17" s="31" t="n">
         <v>900</v>
       </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L17" s="18" t="inlineStr">
+      <c r="K17" s="32">
+        <f>J17*1.19</f>
+        <v/>
+      </c>
+      <c r="L17" s="28" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M17" s="30" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M17" s="20">
-        <f>H17*J17</f>
+      <c r="N17" s="16" t="n"/>
+      <c r="O17" s="17" t="n"/>
+      <c r="P17" s="18" t="n"/>
+      <c r="Q17" s="33">
+        <f>IF(N17&lt;&gt;"ja","",IF(O17="",H17,O17)*J17)</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="78" customHeight="1">
-      <c r="A18" s="8" t="n">
+      <c r="A18" s="9" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="35" t="inlineStr">
         <is>
           <t>BA09-05</t>
         </is>
       </c>
-      <c r="C18" s="10" t="n"/>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Kartell Masters Stuhl
 Kartell Masters, Design Philippe Starck, schwarz</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="11" t="inlineStr">
+      <c r="E18" s="13" t="n"/>
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>Personal</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="H18" s="9" t="n">
+      <c r="H18" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="I18" s="9" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J18" s="13" t="n">
+      <c r="J18" s="14" t="n">
         <v>120</v>
       </c>
-      <c r="K18" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L18" s="11" t="inlineStr">
+      <c r="K18" s="15">
+        <f>J18*1.19</f>
+        <v/>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M18" s="12" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M18" s="14">
-        <f>H18*J18</f>
+      <c r="N18" s="16" t="n"/>
+      <c r="O18" s="17" t="n"/>
+      <c r="P18" s="18" t="n"/>
+      <c r="Q18" s="19">
+        <f>IF(N18&lt;&gt;"ja","",IF(O18="",H18,O18)*J18)</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="78" customHeight="1">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>BA10-01</t>
         </is>
       </c>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="C19" s="22" t="n"/>
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>Glastisch rund mit Chromgestell
 Runde Glasplatte teilsatiniert, Chromgestell</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="18" t="inlineStr">
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
-      <c r="G19" s="16" t="inlineStr">
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="H19" s="16" t="n">
+      <c r="H19" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J19" s="19" t="n">
+      <c r="J19" s="24" t="n">
         <v>90</v>
       </c>
-      <c r="K19" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L19" s="18" t="inlineStr">
+      <c r="K19" s="25">
+        <f>J19*1.19</f>
+        <v/>
+      </c>
+      <c r="L19" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M19" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M19" s="20">
-        <f>H19*J19</f>
+      <c r="N19" s="16" t="n"/>
+      <c r="O19" s="17" t="n"/>
+      <c r="P19" s="18" t="n"/>
+      <c r="Q19" s="26">
+        <f>IF(N19&lt;&gt;"ja","",IF(O19="",H19,O19)*J19)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="78" customHeight="1">
-      <c r="A20" s="8" t="n">
+      <c r="A20" s="9" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="9" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>BA10-02</t>
         </is>
       </c>
-      <c r="C20" s="10" t="n"/>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Samtsofa bordeaux, 2-Sitzer
 Samtbezug dunkelrot, gesteppte Rückenlehne, dunkle Holzbeine</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="11" t="inlineStr">
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H20" s="9" t="n">
+      <c r="H20" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J20" s="13" t="n">
+      <c r="J20" s="14" t="n">
         <v>250</v>
       </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L20" s="11" t="inlineStr">
+      <c r="K20" s="15">
+        <f>J20*1.19</f>
+        <v/>
+      </c>
+      <c r="L20" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M20" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M20" s="14">
-        <f>H20*J20</f>
+      <c r="N20" s="16" t="n"/>
+      <c r="O20" s="17" t="n"/>
+      <c r="P20" s="18" t="n"/>
+      <c r="Q20" s="19">
+        <f>IF(N20&lt;&gt;"ja","",IF(O20="",H20,O20)*J20)</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="78" customHeight="1">
-      <c r="A21" s="15" t="n">
+      <c r="A21" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>BA10-03</t>
         </is>
       </c>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="C21" s="22" t="n"/>
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>Sessel mit Bezug, weiß lackiert
 Relaxsessel mit Bezug, weiß lackiert
  weiß lackiertes Schichtholz, hellgrauer Bezug</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="18" t="inlineStr">
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
-      <c r="G21" s="16" t="inlineStr">
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H21" s="16" t="n">
+      <c r="H21" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J21" s="19" t="n">
+      <c r="J21" s="24" t="n">
         <v>250</v>
       </c>
-      <c r="K21" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L21" s="18" t="inlineStr">
+      <c r="K21" s="25">
+        <f>J21*1.19</f>
+        <v/>
+      </c>
+      <c r="L21" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M21" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M21" s="20">
-        <f>H21*J21</f>
+      <c r="N21" s="16" t="n"/>
+      <c r="O21" s="17" t="n"/>
+      <c r="P21" s="18" t="n"/>
+      <c r="Q21" s="26">
+        <f>IF(N21&lt;&gt;"ja","",IF(O21="",H21,O21)*J21)</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="78" customHeight="1">
-      <c r="A22" s="8" t="n">
+      <c r="A22" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>BA10-04</t>
         </is>
       </c>
-      <c r="C22" s="10" t="n"/>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>Hocker grau mit Hairpin-Beinen
 Hocker grau 
 Runder Polsterhocker grau, mit Stauraum</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="E22" s="13" t="n"/>
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="G22" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H22" s="9" t="n">
+      <c r="H22" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I22" s="9" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J22" s="13" t="n">
+      <c r="J22" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L22" s="11" t="inlineStr">
+      <c r="K22" s="15">
+        <f>J22*1.19</f>
+        <v/>
+      </c>
+      <c r="L22" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M22" s="12" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M22" s="14">
-        <f>H22*J22</f>
+      <c r="N22" s="16" t="n"/>
+      <c r="O22" s="17" t="n"/>
+      <c r="P22" s="18" t="n"/>
+      <c r="Q22" s="19">
+        <f>IF(N22&lt;&gt;"ja","",IF(O22="",H22,O22)*J22)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="78" customHeight="1">
-      <c r="A23" s="15" t="n">
+      <c r="A23" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>BA10-05</t>
         </is>
       </c>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>Ohrensessel grau mit Kufengestell
 Polstersessel hellgrau, schwarzes Kufengestell aus Rundstahl</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="18" t="inlineStr">
+      <c r="E23" s="13" t="n"/>
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
-      <c r="G23" s="16" t="inlineStr">
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H23" s="16" t="n">
+      <c r="H23" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="I23" s="16" t="inlineStr">
+      <c r="I23" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J23" s="19" t="n">
+      <c r="J23" s="24" t="n">
         <v>130</v>
       </c>
-      <c r="K23" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L23" s="18" t="inlineStr">
+      <c r="K23" s="25">
+        <f>J23*1.19</f>
+        <v/>
+      </c>
+      <c r="L23" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M23" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M23" s="20">
-        <f>H23*J23</f>
+      <c r="N23" s="16" t="n"/>
+      <c r="O23" s="17" t="n"/>
+      <c r="P23" s="18" t="n"/>
+      <c r="Q23" s="26">
+        <f>IF(N23&lt;&gt;"ja","",IF(O23="",H23,O23)*J23)</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="78" customHeight="1">
-      <c r="A24" s="8" t="n">
+      <c r="A24" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>BA10-06</t>
         </is>
       </c>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>Hocker grau, passend
 Polsterhocker hellgrau, schwarzes Kufengestell, passend zu den Sesseln</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="E24" s="13" t="n"/>
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H24" s="9" t="n">
+      <c r="H24" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I24" s="9" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J24" s="13" t="n">
+      <c r="J24" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="K24" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L24" s="11" t="inlineStr">
+      <c r="K24" s="15">
+        <f>J24*1.19</f>
+        <v/>
+      </c>
+      <c r="L24" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M24" s="12" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M24" s="14">
-        <f>H24*J24</f>
+      <c r="N24" s="16" t="n"/>
+      <c r="O24" s="17" t="n"/>
+      <c r="P24" s="18" t="n"/>
+      <c r="Q24" s="19">
+        <f>IF(N24&lt;&gt;"ja","",IF(O24="",H24,O24)*J24)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="78" customHeight="1">
-      <c r="A25" s="15" t="n">
+      <c r="A25" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>BA10-07</t>
         </is>
       </c>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="C25" s="22" t="n"/>
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>Beistelltisch rund grau
 Runde Platte grau, schwarze Hairpin-Beine</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="18" t="inlineStr">
+      <c r="E25" s="13" t="n"/>
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
-      <c r="G25" s="16" t="inlineStr">
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H25" s="16" t="n">
+      <c r="H25" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I25" s="16" t="inlineStr">
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J25" s="19" t="n">
+      <c r="J25" s="24" t="n">
         <v>45</v>
       </c>
-      <c r="K25" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L25" s="18" t="inlineStr">
+      <c r="K25" s="25">
+        <f>J25*1.19</f>
+        <v/>
+      </c>
+      <c r="L25" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M25" s="23" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M25" s="20">
-        <f>H25*J25</f>
+      <c r="N25" s="16" t="n"/>
+      <c r="O25" s="17" t="n"/>
+      <c r="P25" s="18" t="n"/>
+      <c r="Q25" s="26">
+        <f>IF(N25&lt;&gt;"ja","",IF(O25="",H25,O25)*J25)</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="78" customHeight="1">
-      <c r="A26" s="8" t="n">
+      <c r="A26" s="9" t="n">
         <v>19</v>
       </c>
-      <c r="B26" s="9" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>BA10-08</t>
         </is>
       </c>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="12" t="inlineStr">
         <is>
           <t>Pendelleuchte Drahtgeflecht
 Geometrische Drahtleuchte schwarz, Ikosaederform</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="E26" s="13" t="n"/>
+      <c r="F26" s="12" t="inlineStr">
         <is>
           <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr">
+      <c r="G26" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H26" s="9" t="n">
+      <c r="H26" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J26" s="13" t="n">
+      <c r="J26" s="14" t="n">
         <v>55</v>
       </c>
-      <c r="K26" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L26" s="11" t="inlineStr">
+      <c r="K26" s="15">
+        <f>J26*1.19</f>
+        <v/>
+      </c>
+      <c r="L26" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M26" s="12" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M26" s="14">
-        <f>H26*J26</f>
+      <c r="N26" s="16" t="n"/>
+      <c r="O26" s="17" t="n"/>
+      <c r="P26" s="18" t="n"/>
+      <c r="Q26" s="19">
+        <f>IF(N26&lt;&gt;"ja","",IF(O26="",H26,O26)*J26)</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="78" customHeight="1">
-      <c r="A27" s="15" t="n">
+      <c r="A27" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>BA12-01</t>
         </is>
       </c>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="18" t="inlineStr">
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="23" t="inlineStr">
         <is>
           <t>Ast-Mobile mit Papierwaben
 Deko-Mobile: Birkenast mit Papierwaben, Sternen und Filzhäusern</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="18" t="inlineStr">
+      <c r="E27" s="13" t="n"/>
+      <c r="F27" s="23" t="inlineStr">
         <is>
           <t>WC Personal</t>
         </is>
       </c>
-      <c r="G27" s="16" t="inlineStr">
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H27" s="16" t="n">
+      <c r="H27" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I27" s="16" t="inlineStr">
+      <c r="I27" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J27" s="19" t="n">
+      <c r="J27" s="24" t="n">
         <v>30</v>
       </c>
-      <c r="K27" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L27" s="18" t="inlineStr">
+      <c r="K27" s="25">
+        <f>J27*1.19</f>
+        <v/>
+      </c>
+      <c r="L27" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M27" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M27" s="20">
-        <f>H27*J27</f>
+      <c r="N27" s="16" t="n"/>
+      <c r="O27" s="17" t="n"/>
+      <c r="P27" s="18" t="n"/>
+      <c r="Q27" s="26">
+        <f>IF(N27&lt;&gt;"ja","",IF(O27="",H27,O27)*J27)</f>
         <v/>
       </c>
     </row>
     <row r="28" ht="78" customHeight="1">
-      <c r="A28" s="8" t="n">
+      <c r="A28" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>BE01-01</t>
         </is>
       </c>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="12" t="inlineStr">
         <is>
           <t>Barockspiegel schwarz, oval
 Verzierter Rahmen schwarz, oval, zwei Größen</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="E28" s="13" t="n"/>
+      <c r="F28" s="12" t="inlineStr">
         <is>
           <t>Flur 1</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H28" s="9" t="n">
+      <c r="H28" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I28" s="9" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J28" s="13" t="n">
+      <c r="J28" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="K28" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L28" s="11" t="inlineStr">
+      <c r="K28" s="15">
+        <f>J28*1.19</f>
+        <v/>
+      </c>
+      <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M28" s="12" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M28" s="14">
-        <f>H28*J28</f>
+      <c r="N28" s="16" t="n"/>
+      <c r="O28" s="17" t="n"/>
+      <c r="P28" s="18" t="n"/>
+      <c r="Q28" s="19">
+        <f>IF(N28&lt;&gt;"ja","",IF(O28="",H28,O28)*J28)</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="78" customHeight="1">
-      <c r="A29" s="15" t="n">
+      <c r="A29" s="20" t="n">
         <v>22</v>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>BE01-02</t>
         </is>
       </c>
-      <c r="C29" s="17" t="n"/>
-      <c r="D29" s="18" t="inlineStr">
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="23" t="inlineStr">
         <is>
           <t>Bilderrahmen mit Kinderzeichnung
 Gerahmte Kinderzeichnungen/Drucke, schwarz gerahmt</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n"/>
-      <c r="F29" s="18" t="inlineStr">
+      <c r="E29" s="13" t="n"/>
+      <c r="F29" s="23" t="inlineStr">
         <is>
           <t>Flur 1</t>
         </is>
       </c>
-      <c r="G29" s="16" t="inlineStr">
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H29" s="16" t="n">
+      <c r="H29" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="I29" s="16" t="inlineStr">
+      <c r="I29" s="21" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="J29" s="19" t="n">
+      <c r="J29" s="24" t="n">
         <v>40</v>
       </c>
-      <c r="K29" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L29" s="18" t="inlineStr">
+      <c r="K29" s="25">
+        <f>J29*1.19</f>
+        <v/>
+      </c>
+      <c r="L29" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M29" s="23" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M29" s="20">
-        <f>H29*J29</f>
+      <c r="N29" s="16" t="n"/>
+      <c r="O29" s="17" t="n"/>
+      <c r="P29" s="18" t="n"/>
+      <c r="Q29" s="26">
+        <f>IF(N29&lt;&gt;"ja","",IF(O29="",H29,O29)*J29)</f>
         <v/>
       </c>
     </row>
     <row r="30" ht="78" customHeight="1">
-      <c r="A30" s="8" t="n">
+      <c r="A30" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>BE01-03</t>
         </is>
       </c>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>Wandregal-Würfel schwarz
 Offene Regalwürfel zur Wandmontage, schwarz</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="11" t="inlineStr">
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="12" t="inlineStr">
         <is>
           <t>Flur 1</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H30" s="9" t="n">
+      <c r="H30" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J30" s="13" t="n">
+      <c r="J30" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="K30" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L30" s="11" t="inlineStr">
+      <c r="K30" s="15">
+        <f>J30*1.19</f>
+        <v/>
+      </c>
+      <c r="L30" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M30" s="12" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M30" s="14">
-        <f>H30*J30</f>
+      <c r="N30" s="16" t="n"/>
+      <c r="O30" s="17" t="n"/>
+      <c r="P30" s="18" t="n"/>
+      <c r="Q30" s="19">
+        <f>IF(N30&lt;&gt;"ja","",IF(O30="",H30,O30)*J30)</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="78" customHeight="1">
-      <c r="A31" s="15" t="n">
+      <c r="A31" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>BE06-01</t>
         </is>
       </c>
-      <c r="C31" s="17" t="n"/>
-      <c r="D31" s="18" t="inlineStr">
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="23" t="inlineStr">
         <is>
           <t>Wandgestell Holz mit Schnüren
 Holzrahmen mit gespannten Schnüren und Wäscheklammern zum Aufhängen von Bildern</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="18" t="inlineStr">
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="23" t="inlineStr">
         <is>
           <t>Gruppenraum 2</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H31" s="16" t="n">
+      <c r="H31" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I31" s="16" t="inlineStr">
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J31" s="19" t="n">
+      <c r="J31" s="24" t="n">
         <v>35</v>
       </c>
-      <c r="K31" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L31" s="18" t="inlineStr">
+      <c r="K31" s="25">
+        <f>J31*1.19</f>
+        <v/>
+      </c>
+      <c r="L31" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M31" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M31" s="20">
-        <f>H31*J31</f>
+      <c r="N31" s="16" t="n"/>
+      <c r="O31" s="17" t="n"/>
+      <c r="P31" s="18" t="n"/>
+      <c r="Q31" s="26">
+        <f>IF(N31&lt;&gt;"ja","",IF(O31="",H31,O31)*J31)</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="78" customHeight="1">
-      <c r="A32" s="8" t="n">
+      <c r="A32" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="B32" s="21" t="inlineStr">
+      <c r="B32" s="35" t="inlineStr">
         <is>
           <t>BE06-02</t>
         </is>
       </c>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="11" t="inlineStr">
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="12" t="inlineStr">
         <is>
           <t>Designsofa anthrazit
 Geschwungene Form, Wollstoff anthrazit, dunkle Metallbeine, 3-Sitzer</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="11" t="inlineStr">
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="12" t="inlineStr">
         <is>
           <t>Gruppenraum 2</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H32" s="9" t="n">
+      <c r="H32" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I32" s="9" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J32" s="13" t="n">
+      <c r="J32" s="14" t="n">
         <v>450</v>
       </c>
-      <c r="K32" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L32" s="11" t="inlineStr">
+      <c r="K32" s="15">
+        <f>J32*1.19</f>
+        <v/>
+      </c>
+      <c r="L32" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M32" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M32" s="14">
-        <f>H32*J32</f>
+      <c r="N32" s="16" t="n"/>
+      <c r="O32" s="17" t="n"/>
+      <c r="P32" s="18" t="n"/>
+      <c r="Q32" s="19">
+        <f>IF(N32&lt;&gt;"ja","",IF(O32="",H32,O32)*J32)</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="78" customHeight="1">
-      <c r="A33" s="15" t="n">
+      <c r="A33" s="20" t="n">
         <v>26</v>
       </c>
-      <c r="B33" s="21" t="inlineStr">
+      <c r="B33" s="35" t="inlineStr">
         <is>
           <t>BE10-01</t>
         </is>
       </c>
-      <c r="C33" s="17" t="n"/>
-      <c r="D33" s="18" t="inlineStr">
+      <c r="C33" s="22" t="n"/>
+      <c r="D33" s="23" t="inlineStr">
         <is>
           <t>LED-Ring-Pendelleuchte
 Große Pendelleuchte aus mehreren LED-Ringen</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n"/>
-      <c r="F33" s="18" t="inlineStr">
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="23" t="inlineStr">
         <is>
           <t>Büro / Besprechung</t>
         </is>
       </c>
-      <c r="G33" s="16" t="inlineStr">
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H33" s="16" t="n">
+      <c r="H33" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I33" s="16" t="inlineStr">
+      <c r="I33" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J33" s="19" t="n">
+      <c r="J33" s="24" t="n">
         <v>450</v>
       </c>
-      <c r="K33" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L33" s="18" t="inlineStr">
+      <c r="K33" s="25">
+        <f>J33*1.19</f>
+        <v/>
+      </c>
+      <c r="L33" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M33" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M33" s="20">
-        <f>H33*J33</f>
+      <c r="N33" s="16" t="n"/>
+      <c r="O33" s="17" t="n"/>
+      <c r="P33" s="18" t="n"/>
+      <c r="Q33" s="26">
+        <f>IF(N33&lt;&gt;"ja","",IF(O33="",H33,O33)*J33)</f>
         <v/>
       </c>
     </row>
     <row r="34" ht="78" customHeight="1">
-      <c r="A34" s="8" t="n">
+      <c r="A34" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>BE10-02</t>
         </is>
       </c>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>Pachira groß im Übertopf
 Glückskastanie, große Pflanze, weißer Übertopf</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n"/>
-      <c r="F34" s="11" t="inlineStr">
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>Büro / Besprechung</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="G34" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H34" s="9" t="n">
+      <c r="H34" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I34" s="9" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J34" s="13" t="n">
+      <c r="J34" s="14" t="n">
         <v>80</v>
       </c>
-      <c r="K34" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L34" s="11" t="inlineStr">
+      <c r="K34" s="15">
+        <f>J34*1.19</f>
+        <v/>
+      </c>
+      <c r="L34" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M34" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M34" s="14">
-        <f>H34*J34</f>
+      <c r="N34" s="16" t="n"/>
+      <c r="O34" s="17" t="n"/>
+      <c r="P34" s="18" t="n"/>
+      <c r="Q34" s="19">
+        <f>IF(N34&lt;&gt;"ja","",IF(O34="",H34,O34)*J34)</f>
         <v/>
       </c>
     </row>
     <row r="35" ht="78" customHeight="1">
-      <c r="A35" s="15" t="n">
+      <c r="A35" s="20" t="n">
         <v>28</v>
       </c>
-      <c r="B35" s="16" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>BE10-03</t>
         </is>
       </c>
-      <c r="C35" s="17" t="n"/>
-      <c r="D35" s="18" t="inlineStr">
+      <c r="C35" s="22" t="n"/>
+      <c r="D35" s="23" t="inlineStr">
         <is>
           <t>Moderationswand fahrbar
 Pinnwand/Stellwand grau, auf Rollen, beidseitig</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n"/>
-      <c r="F35" s="18" t="inlineStr">
+      <c r="E35" s="13" t="n"/>
+      <c r="F35" s="23" t="inlineStr">
         <is>
           <t>Büro / Besprechung</t>
         </is>
       </c>
-      <c r="G35" s="16" t="inlineStr">
+      <c r="G35" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H35" s="16" t="n">
+      <c r="H35" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I35" s="16" t="inlineStr">
+      <c r="I35" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J35" s="19" t="n">
+      <c r="J35" s="24" t="n">
         <v>110</v>
       </c>
-      <c r="K35" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L35" s="18" t="inlineStr">
+      <c r="K35" s="25">
+        <f>J35*1.19</f>
+        <v/>
+      </c>
+      <c r="L35" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M35" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M35" s="20">
-        <f>H35*J35</f>
+      <c r="N35" s="16" t="n"/>
+      <c r="O35" s="17" t="n"/>
+      <c r="P35" s="18" t="n"/>
+      <c r="Q35" s="26">
+        <f>IF(N35&lt;&gt;"ja","",IF(O35="",H35,O35)*J35)</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="78" customHeight="1">
-      <c r="A36" s="8" t="n">
+      <c r="A36" s="9" t="n">
         <v>29</v>
       </c>
-      <c r="B36" s="9" t="inlineStr">
+      <c r="B36" s="10" t="inlineStr">
         <is>
           <t>BE10-04</t>
         </is>
       </c>
-      <c r="C36" s="10" t="n"/>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>Besprechungstisch weiß, groß
 Konferenztisch, weiße Platte, für ca. 8-10 Personen</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n"/>
-      <c r="F36" s="11" t="inlineStr">
+      <c r="E36" s="13" t="n"/>
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>Büro / Besprechung</t>
         </is>
       </c>
-      <c r="G36" s="9" t="inlineStr">
+      <c r="G36" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H36" s="9" t="n">
+      <c r="H36" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I36" s="9" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J36" s="13" t="n">
+      <c r="J36" s="14" t="n">
         <v>280</v>
       </c>
-      <c r="K36" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L36" s="11" t="inlineStr">
+      <c r="K36" s="15">
+        <f>J36*1.19</f>
+        <v/>
+      </c>
+      <c r="L36" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M36" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M36" s="14">
-        <f>H36*J36</f>
+      <c r="N36" s="16" t="n"/>
+      <c r="O36" s="17" t="n"/>
+      <c r="P36" s="18" t="n"/>
+      <c r="Q36" s="19">
+        <f>IF(N36&lt;&gt;"ja","",IF(O36="",H36,O36)*J36)</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="78" customHeight="1">
-      <c r="A37" s="15" t="n">
+      <c r="A37" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="B37" s="16" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>BU04-01</t>
         </is>
       </c>
-      <c r="C37" s="17" t="n"/>
-      <c r="D37" s="18" t="inlineStr">
+      <c r="C37" s="22" t="n"/>
+      <c r="D37" s="23" t="inlineStr">
         <is>
           <t>Crassula im Topf
 Geldbaum, Zimmerpflanze im weißen Topf</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="18" t="inlineStr">
+      <c r="E37" s="13" t="n"/>
+      <c r="F37" s="23" t="inlineStr">
         <is>
           <t>Gruppenraum</t>
         </is>
       </c>
-      <c r="G37" s="16" t="inlineStr">
+      <c r="G37" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H37" s="16" t="n">
+      <c r="H37" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I37" s="16" t="inlineStr">
+      <c r="I37" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J37" s="19" t="n">
+      <c r="J37" s="24" t="n">
         <v>30</v>
       </c>
-      <c r="K37" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L37" s="18" t="inlineStr">
+      <c r="K37" s="25">
+        <f>J37*1.19</f>
+        <v/>
+      </c>
+      <c r="L37" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M37" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M37" s="20">
-        <f>H37*J37</f>
+      <c r="N37" s="16" t="n"/>
+      <c r="O37" s="17" t="n"/>
+      <c r="P37" s="18" t="n"/>
+      <c r="Q37" s="26">
+        <f>IF(N37&lt;&gt;"ja","",IF(O37="",H37,O37)*J37)</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="78" customHeight="1">
-      <c r="A38" s="8" t="n">
+      <c r="A38" s="9" t="n">
         <v>31</v>
       </c>
-      <c r="B38" s="9" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>BU04-02</t>
         </is>
       </c>
-      <c r="C38" s="10" t="n"/>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>Pflanzkübel Raumteiler weiß Hochglanz
 Rechteckiger Pflanzkübel als Raumteiler, weiß hochglanz, ca. 80 x 30 x 80 cm</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n"/>
-      <c r="F38" s="11" t="inlineStr">
+      <c r="E38" s="13" t="n"/>
+      <c r="F38" s="12" t="inlineStr">
         <is>
           <t>Gruppenraum</t>
         </is>
       </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H38" s="9" t="n">
+      <c r="H38" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I38" s="9" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J38" s="13" t="n">
+      <c r="J38" s="14" t="n">
         <v>220</v>
       </c>
-      <c r="K38" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L38" s="11" t="inlineStr">
+      <c r="K38" s="15">
+        <f>J38*1.19</f>
+        <v/>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M38" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M38" s="14">
-        <f>H38*J38</f>
+      <c r="N38" s="16" t="n"/>
+      <c r="O38" s="17" t="n"/>
+      <c r="P38" s="18" t="n"/>
+      <c r="Q38" s="19">
+        <f>IF(N38&lt;&gt;"ja","",IF(O38="",H38,O38)*J38)</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="78" customHeight="1">
-      <c r="A39" s="15" t="n">
+      <c r="A39" s="20" t="n">
         <v>32</v>
       </c>
-      <c r="B39" s="16" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>BU04-03</t>
         </is>
       </c>
-      <c r="C39" s="17" t="n"/>
-      <c r="D39" s="18" t="inlineStr">
+      <c r="C39" s="22" t="n"/>
+      <c r="D39" s="23" t="inlineStr">
         <is>
           <t>Hochflorteppich beige, rund
 Shaggy, beige, rund, Durchmesser ca. 200 cm</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n"/>
-      <c r="F39" s="18" t="inlineStr">
+      <c r="E39" s="13" t="n"/>
+      <c r="F39" s="23" t="inlineStr">
         <is>
           <t>Gruppenraum</t>
         </is>
       </c>
-      <c r="G39" s="16" t="inlineStr">
+      <c r="G39" s="21" t="inlineStr">
         <is>
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="H39" s="16" t="n">
+      <c r="H39" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I39" s="16" t="inlineStr">
+      <c r="I39" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J39" s="19" t="n">
+      <c r="J39" s="24" t="n">
         <v>40</v>
       </c>
-      <c r="K39" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L39" s="18" t="inlineStr">
+      <c r="K39" s="25">
+        <f>J39*1.19</f>
+        <v/>
+      </c>
+      <c r="L39" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M39" s="23" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M39" s="20">
-        <f>H39*J39</f>
+      <c r="N39" s="16" t="n"/>
+      <c r="O39" s="17" t="n"/>
+      <c r="P39" s="18" t="n"/>
+      <c r="Q39" s="26">
+        <f>IF(N39&lt;&gt;"ja","",IF(O39="",H39,O39)*J39)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="78" customHeight="1">
-      <c r="A40" s="8" t="n">
+      <c r="A40" s="9" t="n">
         <v>33</v>
       </c>
-      <c r="B40" s="9" t="inlineStr">
+      <c r="B40" s="10" t="inlineStr">
         <is>
           <t>BU04-04</t>
         </is>
       </c>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>Regal weiß 2x2
 IKEA Kallax, weiß, 4 Fächer</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n"/>
-      <c r="F40" s="11" t="inlineStr">
+      <c r="E40" s="13" t="n"/>
+      <c r="F40" s="12" t="inlineStr">
         <is>
           <t>Gruppenraum</t>
         </is>
       </c>
-      <c r="G40" s="9" t="inlineStr">
+      <c r="G40" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H40" s="9" t="n">
+      <c r="H40" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I40" s="9" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J40" s="13" t="n">
+      <c r="J40" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="K40" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L40" s="11" t="inlineStr">
+      <c r="K40" s="15">
+        <f>J40*1.19</f>
+        <v/>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M40" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M40" s="14">
-        <f>H40*J40</f>
+      <c r="N40" s="16" t="n"/>
+      <c r="O40" s="17" t="n"/>
+      <c r="P40" s="18" t="n"/>
+      <c r="Q40" s="19">
+        <f>IF(N40&lt;&gt;"ja","",IF(O40="",H40,O40)*J40)</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="78" customHeight="1">
-      <c r="A41" s="15" t="n">
+      <c r="A41" s="20" t="n">
         <v>34</v>
       </c>
-      <c r="B41" s="16" t="inlineStr">
+      <c r="B41" s="21" t="inlineStr">
         <is>
           <t>BU04-05</t>
         </is>
       </c>
-      <c r="C41" s="17" t="n"/>
-      <c r="D41" s="18" t="inlineStr">
+      <c r="C41" s="22" t="n"/>
+      <c r="D41" s="23" t="inlineStr">
         <is>
           <t>Wanddeko Fadenbilder mit Spiegelpunkten
 Fadenbilder auf Holzreifen, dazu runde Spiegelelemente</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n"/>
-      <c r="F41" s="18" t="inlineStr">
+      <c r="E41" s="13" t="n"/>
+      <c r="F41" s="23" t="inlineStr">
         <is>
           <t>Gruppenraum</t>
         </is>
       </c>
-      <c r="G41" s="16" t="inlineStr">
+      <c r="G41" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H41" s="16" t="n">
+      <c r="H41" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I41" s="16" t="inlineStr">
+      <c r="I41" s="21" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="J41" s="19" t="n">
+      <c r="J41" s="24" t="n">
         <v>40</v>
       </c>
-      <c r="K41" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L41" s="18" t="inlineStr">
+      <c r="K41" s="25">
+        <f>J41*1.19</f>
+        <v/>
+      </c>
+      <c r="L41" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M41" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M41" s="20">
-        <f>H41*J41</f>
+      <c r="N41" s="16" t="n"/>
+      <c r="O41" s="17" t="n"/>
+      <c r="P41" s="18" t="n"/>
+      <c r="Q41" s="26">
+        <f>IF(N41&lt;&gt;"ja","",IF(O41="",H41,O41)*J41)</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="78" customHeight="1">
-      <c r="A42" s="8" t="n">
+      <c r="A42" s="9" t="n">
         <v>35</v>
       </c>
-      <c r="B42" s="9" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>BU09-01</t>
         </is>
       </c>
-      <c r="C42" s="10" t="n"/>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>Wurzelholz-Schale groß
 Dekoschale aus einem Wurzelstück, Teak, ca. 50-60 cm</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n"/>
-      <c r="F42" s="11" t="inlineStr">
+      <c r="E42" s="13" t="n"/>
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>Werkraum</t>
         </is>
       </c>
-      <c r="G42" s="9" t="inlineStr">
+      <c r="G42" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H42" s="9" t="n">
+      <c r="H42" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J42" s="13" t="n">
+      <c r="J42" s="14" t="n">
         <v>90</v>
       </c>
-      <c r="K42" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L42" s="11" t="inlineStr">
+      <c r="K42" s="15">
+        <f>J42*1.19</f>
+        <v/>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M42" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M42" s="14">
-        <f>H42*J42</f>
+      <c r="N42" s="16" t="n"/>
+      <c r="O42" s="17" t="n"/>
+      <c r="P42" s="18" t="n"/>
+      <c r="Q42" s="19">
+        <f>IF(N42&lt;&gt;"ja","",IF(O42="",H42,O42)*J42)</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="78" customHeight="1">
-      <c r="A43" s="15" t="n">
+      <c r="A43" s="20" t="n">
         <v>36</v>
       </c>
-      <c r="B43" s="16" t="inlineStr">
+      <c r="B43" s="21" t="inlineStr">
         <is>
           <t>BU09-02</t>
         </is>
       </c>
-      <c r="C43" s="17" t="n"/>
-      <c r="D43" s="18" t="inlineStr">
+      <c r="C43" s="22" t="n"/>
+      <c r="D43" s="23" t="inlineStr">
         <is>
           <t>Konvolut Baumscheiben und Holzscheiben
 Baumscheiben verschiedener Größen und Holzarten, Bastelmaterial</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n"/>
-      <c r="F43" s="18" t="inlineStr">
+      <c r="E43" s="13" t="n"/>
+      <c r="F43" s="23" t="inlineStr">
         <is>
           <t>Werkraum</t>
         </is>
       </c>
-      <c r="G43" s="16" t="inlineStr">
+      <c r="G43" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H43" s="16" t="n">
+      <c r="H43" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I43" s="16" t="inlineStr">
+      <c r="I43" s="21" t="inlineStr">
         <is>
           <t>Konvolut</t>
         </is>
       </c>
-      <c r="J43" s="19" t="n">
+      <c r="J43" s="24" t="n">
         <v>40</v>
       </c>
-      <c r="K43" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L43" s="18" t="inlineStr">
+      <c r="K43" s="25">
+        <f>J43*1.19</f>
+        <v/>
+      </c>
+      <c r="L43" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M43" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M43" s="20">
-        <f>H43*J43</f>
+      <c r="N43" s="16" t="n"/>
+      <c r="O43" s="17" t="n"/>
+      <c r="P43" s="18" t="n"/>
+      <c r="Q43" s="26">
+        <f>IF(N43&lt;&gt;"ja","",IF(O43="",H43,O43)*J43)</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="78" customHeight="1">
-      <c r="A44" s="8" t="n">
+      <c r="A44" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="B44" s="9" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>BU09-03</t>
         </is>
       </c>
-      <c r="C44" s="10" t="n"/>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t>Kreidetafel in Hausform
 Tafelfolie/Kreidetafel in Hausform, beschriftbar</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n"/>
-      <c r="F44" s="11" t="inlineStr">
+      <c r="E44" s="13" t="n"/>
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>Werkraum</t>
         </is>
       </c>
-      <c r="G44" s="9" t="inlineStr">
+      <c r="G44" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H44" s="9" t="n">
+      <c r="H44" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I44" s="9" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J44" s="13" t="n">
+      <c r="J44" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="K44" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L44" s="11" t="inlineStr">
+      <c r="K44" s="15">
+        <f>J44*1.19</f>
+        <v/>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M44" s="12" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M44" s="14">
-        <f>H44*J44</f>
+      <c r="N44" s="16" t="n"/>
+      <c r="O44" s="17" t="n"/>
+      <c r="P44" s="18" t="n"/>
+      <c r="Q44" s="19">
+        <f>IF(N44&lt;&gt;"ja","",IF(O44="",H44,O44)*J44)</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="78" customHeight="1">
-      <c r="A45" s="15" t="n">
+      <c r="A45" s="20" t="n">
         <v>38</v>
       </c>
-      <c r="B45" s="21" t="inlineStr">
+      <c r="B45" s="35" t="inlineStr">
         <is>
           <t>GA01-01</t>
         </is>
       </c>
-      <c r="C45" s="17" t="n"/>
-      <c r="D45" s="18" t="inlineStr">
+      <c r="C45" s="22" t="n"/>
+      <c r="D45" s="23" t="inlineStr">
         <is>
           <t>Holz-Wellenliege, Doppelliege
 Geschwungene Doppelliege aus Holzlatten, ca. 200 cm breit, mit Sponsorenplakette</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n"/>
-      <c r="F45" s="18" t="inlineStr">
+      <c r="E45" s="13" t="n"/>
+      <c r="F45" s="23" t="inlineStr">
         <is>
           <t>Gartenanlage</t>
         </is>
       </c>
-      <c r="G45" s="16" t="inlineStr">
+      <c r="G45" s="21" t="inlineStr">
         <is>
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="H45" s="16" t="n">
+      <c r="H45" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I45" s="16" t="inlineStr">
+      <c r="I45" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J45" s="19" t="n">
+      <c r="J45" s="24" t="n">
         <v>350</v>
       </c>
-      <c r="K45" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L45" s="18" t="inlineStr">
+      <c r="K45" s="25">
+        <f>J45*1.19</f>
+        <v/>
+      </c>
+      <c r="L45" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M45" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M45" s="20">
-        <f>H45*J45</f>
+      <c r="N45" s="16" t="n"/>
+      <c r="O45" s="17" t="n"/>
+      <c r="P45" s="18" t="n"/>
+      <c r="Q45" s="26">
+        <f>IF(N45&lt;&gt;"ja","",IF(O45="",H45,O45)*J45)</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="78" customHeight="1">
-      <c r="A46" s="8" t="n">
+      <c r="A46" s="9" t="n">
         <v>39</v>
       </c>
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>NE01-01</t>
         </is>
       </c>
-      <c r="C46" s="10" t="n"/>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="12" t="inlineStr">
         <is>
           <t>Deko-Hirschkopf weiß
 Kunstharz, weiß, mit schwarzem Geweih, auf Holzschild, Wandmontage</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n"/>
-      <c r="F46" s="11" t="inlineStr">
+      <c r="E46" s="13" t="n"/>
+      <c r="F46" s="12" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G46" s="9" t="inlineStr">
+      <c r="G46" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H46" s="9" t="n">
+      <c r="H46" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I46" s="9" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J46" s="13" t="n">
+      <c r="J46" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="K46" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L46" s="11" t="inlineStr">
+      <c r="K46" s="15">
+        <f>J46*1.19</f>
+        <v/>
+      </c>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M46" s="12" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M46" s="14">
-        <f>H46*J46</f>
+      <c r="N46" s="16" t="n"/>
+      <c r="O46" s="17" t="n"/>
+      <c r="P46" s="18" t="n"/>
+      <c r="Q46" s="19">
+        <f>IF(N46&lt;&gt;"ja","",IF(O46="",H46,O46)*J46)</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="78" customHeight="1">
-      <c r="A47" s="15" t="n">
+      <c r="A47" s="27" t="n">
         <v>40</v>
       </c>
-      <c r="B47" s="16" t="inlineStr">
+      <c r="B47" s="28" t="inlineStr">
         <is>
           <t>NE01-02</t>
         </is>
       </c>
-      <c r="C47" s="17" t="n"/>
-      <c r="D47" s="18" t="inlineStr">
+      <c r="C47" s="29" t="n"/>
+      <c r="D47" s="30" t="inlineStr">
         <is>
           <t>Trachtenfotografie gerahmt, schwarz
 Fotodruck im schwarzen Rahmen mit Passepartout, ca. 30 x 40 cm - Kaufware</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n"/>
-      <c r="F47" s="18" t="inlineStr">
+      <c r="E47" s="30" t="n"/>
+      <c r="F47" s="30" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G47" s="16" t="inlineStr">
+      <c r="G47" s="28" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H47" s="16" t="n">
+      <c r="H47" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="I47" s="16" t="inlineStr">
+      <c r="I47" s="28" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J47" s="19" t="n">
+      <c r="J47" s="31" t="n">
         <v>45</v>
       </c>
-      <c r="K47" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L47" s="18" t="inlineStr">
+      <c r="K47" s="32">
+        <f>J47*1.19</f>
+        <v/>
+      </c>
+      <c r="L47" s="28" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M47" s="30" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M47" s="20">
-        <f>H47*J47</f>
+      <c r="N47" s="16" t="n"/>
+      <c r="O47" s="17" t="n"/>
+      <c r="P47" s="18" t="n"/>
+      <c r="Q47" s="33">
+        <f>IF(N47&lt;&gt;"ja","",IF(O47="",H47,O47)*J47)</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="78" customHeight="1">
-      <c r="A48" s="8" t="n">
+      <c r="A48" s="27" t="n">
         <v>41</v>
       </c>
-      <c r="B48" s="9" t="inlineStr">
+      <c r="B48" s="28" t="inlineStr">
         <is>
           <t>NE01-03</t>
         </is>
       </c>
-      <c r="C48" s="10" t="n"/>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="C48" s="29" t="n"/>
+      <c r="D48" s="30" t="inlineStr">
         <is>
           <t>Trachtenportrait gerahmt, klein
 Fotodruck gerahmt, kleinformatig - Kaufware</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n"/>
-      <c r="F48" s="11" t="inlineStr">
+      <c r="E48" s="30" t="n"/>
+      <c r="F48" s="30" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G48" s="9" t="inlineStr">
+      <c r="G48" s="28" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H48" s="9" t="n">
+      <c r="H48" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="I48" s="9" t="inlineStr">
+      <c r="I48" s="28" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J48" s="13" t="n">
+      <c r="J48" s="31" t="n">
         <v>35</v>
       </c>
-      <c r="K48" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L48" s="11" t="inlineStr">
+      <c r="K48" s="32">
+        <f>J48*1.19</f>
+        <v/>
+      </c>
+      <c r="L48" s="28" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M48" s="30" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M48" s="14">
-        <f>H48*J48</f>
+      <c r="N48" s="16" t="n"/>
+      <c r="O48" s="17" t="n"/>
+      <c r="P48" s="18" t="n"/>
+      <c r="Q48" s="33">
+        <f>IF(N48&lt;&gt;"ja","",IF(O48="",H48,O48)*J48)</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="78" customHeight="1">
-      <c r="A49" s="15" t="n">
+      <c r="A49" s="20" t="n">
         <v>42</v>
       </c>
-      <c r="B49" s="16" t="inlineStr">
+      <c r="B49" s="21" t="inlineStr">
         <is>
           <t>NE01-04</t>
         </is>
       </c>
-      <c r="C49" s="17" t="n"/>
-      <c r="D49" s="18" t="inlineStr">
+      <c r="C49" s="22" t="n"/>
+      <c r="D49" s="23" t="inlineStr">
         <is>
           <t>Gemälde Bollenhut abstrakt, schwarz-weiß
 Acryl auf Leinwand, ca. 90 x 90 cm - Eigenarbeit einer Privatperson</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n"/>
-      <c r="F49" s="18" t="inlineStr">
+      <c r="E49" s="13" t="n"/>
+      <c r="F49" s="23" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G49" s="16" t="inlineStr">
+      <c r="G49" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H49" s="16" t="n">
+      <c r="H49" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I49" s="16" t="inlineStr">
+      <c r="I49" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J49" s="19" t="n">
+      <c r="J49" s="24" t="n">
         <v>150</v>
       </c>
-      <c r="K49" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L49" s="18" t="inlineStr">
+      <c r="K49" s="25">
+        <f>J49*1.19</f>
+        <v/>
+      </c>
+      <c r="L49" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M49" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M49" s="20">
-        <f>H49*J49</f>
+      <c r="N49" s="16" t="n"/>
+      <c r="O49" s="17" t="n"/>
+      <c r="P49" s="18" t="n"/>
+      <c r="Q49" s="26">
+        <f>IF(N49&lt;&gt;"ja","",IF(O49="",H49,O49)*J49)</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="78" customHeight="1">
-      <c r="A50" s="8" t="n">
+      <c r="A50" s="9" t="n">
         <v>43</v>
       </c>
-      <c r="B50" s="9" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>NE01-05</t>
         </is>
       </c>
-      <c r="C50" s="10" t="n"/>
-      <c r="D50" s="11" t="inlineStr">
+      <c r="C50" s="11" t="n"/>
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>Sansevieria groß im Übertopf
 Bogenhanf, große Pflanze, weißer Übertopf</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n"/>
-      <c r="F50" s="11" t="inlineStr">
+      <c r="E50" s="13" t="n"/>
+      <c r="F50" s="12" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G50" s="9" t="inlineStr">
+      <c r="G50" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H50" s="9" t="n">
+      <c r="H50" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I50" s="9" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J50" s="13" t="n">
+      <c r="J50" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="K50" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L50" s="11" t="inlineStr">
+      <c r="K50" s="15">
+        <f>J50*1.19</f>
+        <v/>
+      </c>
+      <c r="L50" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M50" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M50" s="14">
-        <f>H50*J50</f>
+      <c r="N50" s="16" t="n"/>
+      <c r="O50" s="17" t="n"/>
+      <c r="P50" s="18" t="n"/>
+      <c r="Q50" s="19">
+        <f>IF(N50&lt;&gt;"ja","",IF(O50="",H50,O50)*J50)</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="78" customHeight="1">
-      <c r="A51" s="15" t="n">
+      <c r="A51" s="20" t="n">
         <v>44</v>
       </c>
-      <c r="B51" s="16" t="inlineStr">
+      <c r="B51" s="21" t="inlineStr">
         <is>
           <t>NE01-06</t>
         </is>
       </c>
-      <c r="C51" s="17" t="n"/>
-      <c r="D51" s="18" t="inlineStr">
+      <c r="C51" s="22" t="n"/>
+      <c r="D51" s="23" t="inlineStr">
         <is>
           <t>Gemälde Bollenhut rot-weiß
 Acryl auf Leinwand, ca. 50 x 60 cm - Eigenarbeit einer Privatperson</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n"/>
-      <c r="F51" s="18" t="inlineStr">
+      <c r="E51" s="13" t="n"/>
+      <c r="F51" s="23" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G51" s="16" t="inlineStr">
+      <c r="G51" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H51" s="16" t="n">
+      <c r="H51" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I51" s="16" t="inlineStr">
+      <c r="I51" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J51" s="19" t="n">
+      <c r="J51" s="24" t="n">
         <v>140</v>
       </c>
-      <c r="K51" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L51" s="18" t="inlineStr">
+      <c r="K51" s="25">
+        <f>J51*1.19</f>
+        <v/>
+      </c>
+      <c r="L51" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M51" s="23" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M51" s="20">
-        <f>H51*J51</f>
+      <c r="N51" s="16" t="n"/>
+      <c r="O51" s="17" t="n"/>
+      <c r="P51" s="18" t="n"/>
+      <c r="Q51" s="26">
+        <f>IF(N51&lt;&gt;"ja","",IF(O51="",H51,O51)*J51)</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="78" customHeight="1">
-      <c r="A52" s="8" t="n">
+      <c r="A52" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="B52" s="9" t="inlineStr">
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>NE01-07</t>
         </is>
       </c>
-      <c r="C52" s="10" t="n"/>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="C52" s="11" t="n"/>
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>Holz-Schriftzug Heimat
 Dekoschriftzug aus Holz</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n"/>
-      <c r="F52" s="11" t="inlineStr">
+      <c r="E52" s="13" t="n"/>
+      <c r="F52" s="12" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G52" s="9" t="inlineStr">
+      <c r="G52" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H52" s="9" t="n">
+      <c r="H52" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I52" s="9" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J52" s="13" t="n">
+      <c r="J52" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="K52" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L52" s="11" t="inlineStr">
+      <c r="K52" s="15">
+        <f>J52*1.19</f>
+        <v/>
+      </c>
+      <c r="L52" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M52" s="12" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M52" s="14">
-        <f>H52*J52</f>
+      <c r="N52" s="16" t="n"/>
+      <c r="O52" s="17" t="n"/>
+      <c r="P52" s="18" t="n"/>
+      <c r="Q52" s="19">
+        <f>IF(N52&lt;&gt;"ja","",IF(O52="",H52,O52)*J52)</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="78" customHeight="1">
-      <c r="A53" s="15" t="n">
+      <c r="A53" s="20" t="n">
         <v>46</v>
       </c>
-      <c r="B53" s="16" t="inlineStr">
+      <c r="B53" s="21" t="inlineStr">
         <is>
           <t>NE01-08</t>
         </is>
       </c>
-      <c r="C53" s="17" t="n"/>
-      <c r="D53" s="18" t="inlineStr">
+      <c r="C53" s="22" t="n"/>
+      <c r="D53" s="23" t="inlineStr">
         <is>
           <t>Zamioculcas im Übertopf
 Glücksfeder, weißer Übertopf</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n"/>
-      <c r="F53" s="18" t="inlineStr">
+      <c r="E53" s="13" t="n"/>
+      <c r="F53" s="23" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G53" s="16" t="inlineStr">
+      <c r="G53" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H53" s="16" t="n">
+      <c r="H53" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I53" s="16" t="inlineStr">
+      <c r="I53" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J53" s="19" t="n">
+      <c r="J53" s="24" t="n">
         <v>60</v>
       </c>
-      <c r="K53" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L53" s="18" t="inlineStr">
+      <c r="K53" s="25">
+        <f>J53*1.19</f>
+        <v/>
+      </c>
+      <c r="L53" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M53" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M53" s="20">
-        <f>H53*J53</f>
+      <c r="N53" s="16" t="n"/>
+      <c r="O53" s="17" t="n"/>
+      <c r="P53" s="18" t="n"/>
+      <c r="Q53" s="26">
+        <f>IF(N53&lt;&gt;"ja","",IF(O53="",H53,O53)*J53)</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="78" customHeight="1">
-      <c r="A54" s="8" t="n">
+      <c r="A54" s="9" t="n">
         <v>47</v>
       </c>
-      <c r="B54" s="9" t="inlineStr">
+      <c r="B54" s="10" t="inlineStr">
         <is>
           <t>NE01-09</t>
         </is>
       </c>
-      <c r="C54" s="10" t="n"/>
-      <c r="D54" s="11" t="inlineStr">
+      <c r="C54" s="11" t="n"/>
+      <c r="D54" s="12" t="inlineStr">
         <is>
           <t>Wanddeko Fadenbild schwarz
 Schwarzes Fadenbild auf rundem Holzreif, zwei Größen</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n"/>
-      <c r="F54" s="11" t="inlineStr">
+      <c r="E54" s="13" t="n"/>
+      <c r="F54" s="12" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G54" s="9" t="inlineStr">
+      <c r="G54" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H54" s="9" t="n">
+      <c r="H54" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I54" s="9" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J54" s="13" t="n">
+      <c r="J54" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="K54" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L54" s="11" t="inlineStr">
+      <c r="K54" s="15">
+        <f>J54*1.19</f>
+        <v/>
+      </c>
+      <c r="L54" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M54" s="12" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M54" s="14">
-        <f>H54*J54</f>
+      <c r="N54" s="16" t="n"/>
+      <c r="O54" s="17" t="n"/>
+      <c r="P54" s="18" t="n"/>
+      <c r="Q54" s="19">
+        <f>IF(N54&lt;&gt;"ja","",IF(O54="",H54,O54)*J54)</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="78" customHeight="1">
-      <c r="A55" s="15" t="n">
+      <c r="A55" s="20" t="n">
         <v>48</v>
       </c>
-      <c r="B55" s="16" t="inlineStr">
+      <c r="B55" s="21" t="inlineStr">
         <is>
           <t>NE01-10</t>
         </is>
       </c>
-      <c r="C55" s="17" t="n"/>
-      <c r="D55" s="18" t="inlineStr">
+      <c r="C55" s="22" t="n"/>
+      <c r="D55" s="23" t="inlineStr">
         <is>
           <t>Deckenleuchte Pusteblume
 IKEA Maskros, weiß, zwei Größen</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n"/>
-      <c r="F55" s="18" t="inlineStr">
+      <c r="E55" s="13" t="n"/>
+      <c r="F55" s="23" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G55" s="16" t="inlineStr">
+      <c r="G55" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H55" s="16" t="n">
+      <c r="H55" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="I55" s="16" t="inlineStr">
+      <c r="I55" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J55" s="19" t="n">
+      <c r="J55" s="24" t="n">
         <v>35</v>
       </c>
-      <c r="K55" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L55" s="18" t="inlineStr">
+      <c r="K55" s="25">
+        <f>J55*1.19</f>
+        <v/>
+      </c>
+      <c r="L55" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M55" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M55" s="20">
-        <f>H55*J55</f>
+      <c r="N55" s="16" t="n"/>
+      <c r="O55" s="17" t="n"/>
+      <c r="P55" s="18" t="n"/>
+      <c r="Q55" s="26">
+        <f>IF(N55&lt;&gt;"ja","",IF(O55="",H55,O55)*J55)</f>
         <v/>
       </c>
     </row>
     <row r="56" ht="78" customHeight="1">
-      <c r="A56" s="8" t="n">
+      <c r="A56" s="9" t="n">
         <v>49</v>
       </c>
-      <c r="B56" s="9" t="inlineStr">
+      <c r="B56" s="10" t="inlineStr">
         <is>
           <t>NE01-11</t>
         </is>
       </c>
-      <c r="C56" s="10" t="n"/>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="C56" s="11" t="n"/>
+      <c r="D56" s="12" t="inlineStr">
         <is>
           <t>Gemälde Bollenhut-Mädchen
 Acryl auf Leinwand, ca. 60 x 80 cm - Eigenarbeit einer Privatperson</t>
         </is>
       </c>
-      <c r="E56" s="12" t="n"/>
-      <c r="F56" s="11" t="inlineStr">
+      <c r="E56" s="13" t="n"/>
+      <c r="F56" s="12" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G56" s="9" t="inlineStr">
+      <c r="G56" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H56" s="9" t="n">
+      <c r="H56" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I56" s="9" t="inlineStr">
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J56" s="13" t="n">
+      <c r="J56" s="14" t="n">
         <v>360</v>
       </c>
-      <c r="K56" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L56" s="11" t="inlineStr">
+      <c r="K56" s="15">
+        <f>J56*1.19</f>
+        <v/>
+      </c>
+      <c r="L56" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M56" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M56" s="14">
-        <f>H56*J56</f>
+      <c r="N56" s="16" t="n"/>
+      <c r="O56" s="17" t="n"/>
+      <c r="P56" s="18" t="n"/>
+      <c r="Q56" s="19">
+        <f>IF(N56&lt;&gt;"ja","",IF(O56="",H56,O56)*J56)</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="78" customHeight="1">
-      <c r="A57" s="15" t="n">
+      <c r="A57" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="B57" s="16" t="inlineStr">
+      <c r="B57" s="21" t="inlineStr">
         <is>
           <t>NE01-12</t>
         </is>
       </c>
-      <c r="C57" s="17" t="n"/>
-      <c r="D57" s="18" t="inlineStr">
+      <c r="C57" s="22" t="n"/>
+      <c r="D57" s="23" t="inlineStr">
         <is>
           <t>Gemälde Fuchs mit Bollenhut
 Acryl auf Leinwand, ca. 80 x 100 cm - Eigenarbeit einer Privatperson</t>
         </is>
       </c>
-      <c r="E57" s="12" t="n"/>
-      <c r="F57" s="18" t="inlineStr">
+      <c r="E57" s="13" t="n"/>
+      <c r="F57" s="23" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G57" s="16" t="inlineStr">
+      <c r="G57" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H57" s="16" t="n">
+      <c r="H57" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I57" s="16" t="inlineStr">
+      <c r="I57" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J57" s="19" t="n">
+      <c r="J57" s="24" t="n">
         <v>180</v>
       </c>
-      <c r="K57" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L57" s="18" t="inlineStr">
+      <c r="K57" s="25">
+        <f>J57*1.19</f>
+        <v/>
+      </c>
+      <c r="L57" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M57" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M57" s="20">
-        <f>H57*J57</f>
+      <c r="N57" s="16" t="n"/>
+      <c r="O57" s="17" t="n"/>
+      <c r="P57" s="18" t="n"/>
+      <c r="Q57" s="26">
+        <f>IF(N57&lt;&gt;"ja","",IF(O57="",H57,O57)*J57)</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="78" customHeight="1">
-      <c r="A58" s="8" t="n">
+      <c r="A58" s="9" t="n">
         <v>51</v>
       </c>
-      <c r="B58" s="9" t="inlineStr">
+      <c r="B58" s="10" t="inlineStr">
         <is>
           <t>NE01-13</t>
         </is>
       </c>
-      <c r="C58" s="10" t="n"/>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="C58" s="11" t="n"/>
+      <c r="D58" s="12" t="inlineStr">
         <is>
           <t>Gemälde Panorama, 3 Figuren
 Acryl auf Leinwand, Querformat ca. 120 x 40 cm - Eigenarbeit einer Privatperson</t>
         </is>
       </c>
-      <c r="E58" s="12" t="n"/>
-      <c r="F58" s="11" t="inlineStr">
+      <c r="E58" s="13" t="n"/>
+      <c r="F58" s="12" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G58" s="9" t="inlineStr">
+      <c r="G58" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H58" s="9" t="n">
+      <c r="H58" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I58" s="9" t="inlineStr">
+      <c r="I58" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J58" s="13" t="n">
+      <c r="J58" s="14" t="n">
         <v>120</v>
       </c>
-      <c r="K58" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L58" s="11" t="inlineStr">
+      <c r="K58" s="15">
+        <f>J58*1.19</f>
+        <v/>
+      </c>
+      <c r="L58" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M58" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M58" s="14">
-        <f>H58*J58</f>
+      <c r="N58" s="16" t="n"/>
+      <c r="O58" s="17" t="n"/>
+      <c r="P58" s="18" t="n"/>
+      <c r="Q58" s="19">
+        <f>IF(N58&lt;&gt;"ja","",IF(O58="",H58,O58)*J58)</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="78" customHeight="1">
-      <c r="A59" s="15" t="n">
+      <c r="A59" s="20" t="n">
         <v>52</v>
       </c>
-      <c r="B59" s="16" t="inlineStr">
+      <c r="B59" s="21" t="inlineStr">
         <is>
           <t>NE01-14</t>
         </is>
       </c>
-      <c r="C59" s="17" t="n"/>
-      <c r="D59" s="18" t="inlineStr">
+      <c r="C59" s="22" t="n"/>
+      <c r="D59" s="23" t="inlineStr">
         <is>
           <t>Gemälde Panorama, 5 Figuren
 Acryl auf Leinwand, Querformat - Eigenarbeit einer Privatperson</t>
         </is>
       </c>
-      <c r="E59" s="12" t="n"/>
-      <c r="F59" s="18" t="inlineStr">
+      <c r="E59" s="13" t="n"/>
+      <c r="F59" s="23" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G59" s="16" t="inlineStr">
+      <c r="G59" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H59" s="16" t="n">
+      <c r="H59" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I59" s="16" t="inlineStr">
+      <c r="I59" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J59" s="19" t="n">
+      <c r="J59" s="24" t="n">
         <v>120</v>
       </c>
-      <c r="K59" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L59" s="18" t="inlineStr">
+      <c r="K59" s="25">
+        <f>J59*1.19</f>
+        <v/>
+      </c>
+      <c r="L59" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M59" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M59" s="20">
-        <f>H59*J59</f>
+      <c r="N59" s="16" t="n"/>
+      <c r="O59" s="17" t="n"/>
+      <c r="P59" s="18" t="n"/>
+      <c r="Q59" s="26">
+        <f>IF(N59&lt;&gt;"ja","",IF(O59="",H59,O59)*J59)</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="78" customHeight="1">
-      <c r="A60" s="8" t="n">
+      <c r="A60" s="9" t="n">
         <v>53</v>
       </c>
-      <c r="B60" s="9" t="inlineStr">
+      <c r="B60" s="10" t="inlineStr">
         <is>
           <t>NE01-15</t>
         </is>
       </c>
-      <c r="C60" s="10" t="n"/>
-      <c r="D60" s="11" t="inlineStr">
+      <c r="C60" s="11" t="n"/>
+      <c r="D60" s="12" t="inlineStr">
         <is>
           <t>Deko-Tannenbaum schwarz
 Metall-Tannenbaum auf Holzsockel, schwarz, verschiedene Größen</t>
         </is>
       </c>
-      <c r="E60" s="12" t="n"/>
-      <c r="F60" s="11" t="inlineStr">
+      <c r="E60" s="13" t="n"/>
+      <c r="F60" s="12" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G60" s="9" t="inlineStr">
+      <c r="G60" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H60" s="9" t="n">
+      <c r="H60" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="I60" s="9" t="inlineStr">
+      <c r="I60" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J60" s="13" t="n">
+      <c r="J60" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="K60" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L60" s="11" t="inlineStr">
+      <c r="K60" s="15">
+        <f>J60*1.19</f>
+        <v/>
+      </c>
+      <c r="L60" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M60" s="12" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M60" s="14">
-        <f>H60*J60</f>
+      <c r="N60" s="16" t="n"/>
+      <c r="O60" s="17" t="n"/>
+      <c r="P60" s="18" t="n"/>
+      <c r="Q60" s="19">
+        <f>IF(N60&lt;&gt;"ja","",IF(O60="",H60,O60)*J60)</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="78" customHeight="1">
-      <c r="A61" s="15" t="n">
+      <c r="A61" s="20" t="n">
         <v>54</v>
       </c>
-      <c r="B61" s="16" t="inlineStr">
+      <c r="B61" s="21" t="inlineStr">
         <is>
           <t>NE01-16</t>
         </is>
       </c>
-      <c r="C61" s="17" t="n"/>
-      <c r="D61" s="18" t="inlineStr">
+      <c r="C61" s="22" t="n"/>
+      <c r="D61" s="23" t="inlineStr">
         <is>
           <t>Pflanze mit Topf
 Stoffschirm schwarz-weiß gemustert mit Fransenbesatz</t>
         </is>
       </c>
-      <c r="E61" s="12" t="n"/>
-      <c r="F61" s="18" t="inlineStr">
+      <c r="E61" s="13" t="n"/>
+      <c r="F61" s="23" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G61" s="16" t="inlineStr">
+      <c r="G61" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H61" s="16" t="n">
+      <c r="H61" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I61" s="16" t="inlineStr">
+      <c r="I61" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J61" s="19" t="n">
+      <c r="J61" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="K61" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L61" s="18" t="inlineStr">
+      <c r="K61" s="25">
+        <f>J61*1.19</f>
+        <v/>
+      </c>
+      <c r="L61" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M61" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M61" s="20">
-        <f>H61*J61</f>
+      <c r="N61" s="16" t="n"/>
+      <c r="O61" s="17" t="n"/>
+      <c r="P61" s="18" t="n"/>
+      <c r="Q61" s="26">
+        <f>IF(N61&lt;&gt;"ja","",IF(O61="",H61,O61)*J61)</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="78" customHeight="1">
-      <c r="A62" s="8" t="n">
+      <c r="A62" s="9" t="n">
         <v>55</v>
       </c>
-      <c r="B62" s="21" t="inlineStr">
+      <c r="B62" s="35" t="inlineStr">
         <is>
           <t>NE05-01</t>
         </is>
       </c>
-      <c r="C62" s="10" t="n"/>
-      <c r="D62" s="11" t="inlineStr">
+      <c r="C62" s="11" t="n"/>
+      <c r="D62" s="12" t="inlineStr">
         <is>
           <t>Massivholztisch mit Baumkante, Essbereich
 Massivholzplatte mit Baumkante, schwarzes Metallgestell mit Messingfüßen</t>
         </is>
       </c>
-      <c r="E62" s="12" t="n"/>
-      <c r="F62" s="11" t="inlineStr">
+      <c r="E62" s="13" t="n"/>
+      <c r="F62" s="12" t="inlineStr">
         <is>
           <t>Speisesaal</t>
         </is>
       </c>
-      <c r="G62" s="9" t="inlineStr">
+      <c r="G62" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H62" s="9" t="n">
+      <c r="H62" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="I62" s="9" t="inlineStr">
+      <c r="I62" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J62" s="13" t="n">
+      <c r="J62" s="14" t="n">
         <v>450</v>
       </c>
-      <c r="K62" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L62" s="11" t="inlineStr">
+      <c r="K62" s="15">
+        <f>J62*1.19</f>
+        <v/>
+      </c>
+      <c r="L62" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M62" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M62" s="14">
-        <f>H62*J62</f>
+      <c r="N62" s="16" t="n"/>
+      <c r="O62" s="17" t="n"/>
+      <c r="P62" s="18" t="n"/>
+      <c r="Q62" s="19">
+        <f>IF(N62&lt;&gt;"ja","",IF(O62="",H62,O62)*J62)</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="78" customHeight="1">
-      <c r="A63" s="15" t="n">
+      <c r="A63" s="20" t="n">
         <v>56</v>
       </c>
-      <c r="B63" s="16" t="inlineStr">
+      <c r="B63" s="21" t="inlineStr">
         <is>
           <t>NE05-02</t>
         </is>
       </c>
-      <c r="C63" s="17" t="n"/>
-      <c r="D63" s="18" t="inlineStr">
+      <c r="C63" s="22" t="n"/>
+      <c r="D63" s="23" t="inlineStr">
         <is>
           <t>Sitzbank Massivholz
 Passend zu den Baumkantentischen, Massivholz mit Metallgestell</t>
         </is>
       </c>
-      <c r="E63" s="12" t="n"/>
-      <c r="F63" s="18" t="inlineStr">
+      <c r="E63" s="13" t="n"/>
+      <c r="F63" s="23" t="inlineStr">
         <is>
           <t>Speisesaal</t>
         </is>
       </c>
-      <c r="G63" s="16" t="inlineStr">
+      <c r="G63" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H63" s="16" t="n">
+      <c r="H63" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="I63" s="16" t="inlineStr">
+      <c r="I63" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J63" s="19" t="n">
+      <c r="J63" s="24" t="n">
         <v>250</v>
       </c>
-      <c r="K63" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L63" s="18" t="inlineStr">
+      <c r="K63" s="25">
+        <f>J63*1.19</f>
+        <v/>
+      </c>
+      <c r="L63" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M63" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M63" s="20">
-        <f>H63*J63</f>
+      <c r="N63" s="16" t="n"/>
+      <c r="O63" s="17" t="n"/>
+      <c r="P63" s="18" t="n"/>
+      <c r="Q63" s="26">
+        <f>IF(N63&lt;&gt;"ja","",IF(O63="",H63,O63)*J63)</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="78" customHeight="1">
-      <c r="A64" s="8" t="n">
+      <c r="A64" s="9" t="n">
         <v>57</v>
       </c>
-      <c r="B64" s="21" t="inlineStr">
+      <c r="B64" s="35" t="inlineStr">
         <is>
           <t>NE05-03</t>
         </is>
       </c>
-      <c r="C64" s="10" t="n"/>
-      <c r="D64" s="11" t="inlineStr">
+      <c r="C64" s="11" t="n"/>
+      <c r="D64" s="12" t="inlineStr">
         <is>
           <t>Kuckucksuhr groß, geschnitzt
 Schwarzwälder Kuckucksuhr, aufwendig geschnitzt mit Hirschkopf, Eulen und Jagdhorn</t>
         </is>
       </c>
-      <c r="E64" s="12" t="n"/>
-      <c r="F64" s="11" t="inlineStr">
+      <c r="E64" s="13" t="n"/>
+      <c r="F64" s="12" t="inlineStr">
         <is>
           <t>Speisesaal</t>
         </is>
       </c>
-      <c r="G64" s="9" t="inlineStr">
+      <c r="G64" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H64" s="9" t="n">
+      <c r="H64" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I64" s="9" t="inlineStr">
+      <c r="I64" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J64" s="13" t="n">
+      <c r="J64" s="14" t="n">
         <v>550</v>
       </c>
-      <c r="K64" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L64" s="11" t="inlineStr">
+      <c r="K64" s="15">
+        <f>J64*1.19</f>
+        <v/>
+      </c>
+      <c r="L64" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M64" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M64" s="14">
-        <f>H64*J64</f>
+      <c r="N64" s="16" t="n"/>
+      <c r="O64" s="17" t="n"/>
+      <c r="P64" s="18" t="n"/>
+      <c r="Q64" s="19">
+        <f>IF(N64&lt;&gt;"ja","",IF(O64="",H64,O64)*J64)</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="78" customHeight="1">
-      <c r="A65" s="15" t="n">
+      <c r="A65" s="20" t="n">
         <v>58</v>
       </c>
-      <c r="B65" s="21" t="inlineStr">
+      <c r="B65" s="35" t="inlineStr">
         <is>
           <t>NU01-01</t>
         </is>
       </c>
-      <c r="C65" s="17" t="n"/>
-      <c r="D65" s="18" t="inlineStr">
+      <c r="C65" s="22" t="n"/>
+      <c r="D65" s="23" t="inlineStr">
         <is>
           <t>Vitra Alcove Sofa, rot
 Vitra Alcove, Design Ronan &amp; Erwan Bouroullec, rot, hohe Rückenwände, Chrombeine</t>
         </is>
       </c>
-      <c r="E65" s="12" t="n"/>
-      <c r="F65" s="18" t="inlineStr">
+      <c r="E65" s="13" t="n"/>
+      <c r="F65" s="23" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G65" s="16" t="inlineStr">
+      <c r="G65" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H65" s="16" t="n">
+      <c r="H65" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="I65" s="16" t="inlineStr">
+      <c r="I65" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J65" s="19" t="n">
+      <c r="J65" s="24" t="n">
         <v>1200</v>
       </c>
-      <c r="K65" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L65" s="18" t="inlineStr">
+      <c r="K65" s="25">
+        <f>J65*1.19</f>
+        <v/>
+      </c>
+      <c r="L65" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M65" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M65" s="20">
-        <f>H65*J65</f>
+      <c r="N65" s="16" t="n"/>
+      <c r="O65" s="17" t="n"/>
+      <c r="P65" s="18" t="n"/>
+      <c r="Q65" s="26">
+        <f>IF(N65&lt;&gt;"ja","",IF(O65="",H65,O65)*J65)</f>
         <v/>
       </c>
     </row>
     <row r="66" ht="78" customHeight="1">
-      <c r="A66" s="8" t="n">
+      <c r="A66" s="9" t="n">
         <v>59</v>
       </c>
-      <c r="B66" s="21" t="inlineStr">
+      <c r="B66" s="35" t="inlineStr">
         <is>
           <t>NU01-02</t>
         </is>
       </c>
-      <c r="C66" s="10" t="n"/>
-      <c r="D66" s="11" t="inlineStr">
+      <c r="C66" s="11" t="n"/>
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>Kuckucksuhr, Wandgruppe
 Schwarzwälder Kuckucksuhren verschiedener Größe und Ausführung</t>
         </is>
       </c>
-      <c r="E66" s="12" t="n"/>
-      <c r="F66" s="11" t="inlineStr">
+      <c r="E66" s="13" t="n"/>
+      <c r="F66" s="12" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G66" s="9" t="inlineStr">
+      <c r="G66" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H66" s="9" t="n">
+      <c r="H66" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="I66" s="9" t="inlineStr">
+      <c r="I66" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J66" s="13" t="n">
+      <c r="J66" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="K66" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L66" s="11" t="inlineStr">
+      <c r="K66" s="15">
+        <f>J66*1.19</f>
+        <v/>
+      </c>
+      <c r="L66" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M66" s="12" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M66" s="14">
-        <f>H66*J66</f>
+      <c r="N66" s="16" t="n"/>
+      <c r="O66" s="17" t="n"/>
+      <c r="P66" s="18" t="n"/>
+      <c r="Q66" s="19">
+        <f>IF(N66&lt;&gt;"ja","",IF(O66="",H66,O66)*J66)</f>
         <v/>
       </c>
     </row>
     <row r="67" ht="78" customHeight="1">
-      <c r="A67" s="15" t="n">
+      <c r="A67" s="27" t="n">
         <v>60</v>
       </c>
-      <c r="B67" s="16" t="inlineStr">
+      <c r="B67" s="28" t="inlineStr">
         <is>
           <t>NU01-03</t>
         </is>
       </c>
-      <c r="C67" s="17" t="n"/>
-      <c r="D67" s="18" t="inlineStr">
+      <c r="C67" s="29" t="n"/>
+      <c r="D67" s="30" t="inlineStr">
         <is>
           <t>Dekoration in der Vitrine
 Dekoration in der Vitrine</t>
         </is>
       </c>
-      <c r="E67" s="12" t="n"/>
-      <c r="F67" s="18" t="inlineStr">
+      <c r="E67" s="30" t="n"/>
+      <c r="F67" s="30" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G67" s="16" t="inlineStr">
+      <c r="G67" s="28" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H67" s="16" t="n">
+      <c r="H67" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="I67" s="16" t="inlineStr">
+      <c r="I67" s="28" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J67" s="19" t="n">
+      <c r="J67" s="31" t="n">
         <v>50</v>
       </c>
-      <c r="K67" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L67" s="18" t="inlineStr">
+      <c r="K67" s="32">
+        <f>J67*1.19</f>
+        <v/>
+      </c>
+      <c r="L67" s="28" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M67" s="30" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M67" s="20">
-        <f>H67*J67</f>
+      <c r="N67" s="16" t="n"/>
+      <c r="O67" s="17" t="n"/>
+      <c r="P67" s="18" t="n"/>
+      <c r="Q67" s="33">
+        <f>IF(N67&lt;&gt;"ja","",IF(O67="",H67,O67)*J67)</f>
         <v/>
       </c>
     </row>
     <row r="68" ht="78" customHeight="1">
-      <c r="A68" s="8" t="n">
+      <c r="A68" s="9" t="n">
         <v>61</v>
       </c>
-      <c r="B68" s="9" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>NU01-04</t>
         </is>
       </c>
-      <c r="C68" s="10" t="n"/>
-      <c r="D68" s="11" t="inlineStr">
+      <c r="C68" s="11" t="n"/>
+      <c r="D68" s="12" t="inlineStr">
         <is>
           <t>Gemälde Heimweh
 Acryl auf Leinwand, großformatig ca. 100 x 140 cm - Eigenarbeit einer Privatperson</t>
         </is>
       </c>
-      <c r="E68" s="12" t="n"/>
-      <c r="F68" s="11" t="inlineStr">
+      <c r="E68" s="13" t="n"/>
+      <c r="F68" s="12" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G68" s="9" t="inlineStr">
+      <c r="G68" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H68" s="9" t="n">
+      <c r="H68" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I68" s="9" t="inlineStr">
+      <c r="I68" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J68" s="13" t="n">
+      <c r="J68" s="14" t="n">
         <v>450</v>
       </c>
-      <c r="K68" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L68" s="11" t="inlineStr">
+      <c r="K68" s="15">
+        <f>J68*1.19</f>
+        <v/>
+      </c>
+      <c r="L68" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M68" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M68" s="14">
-        <f>H68*J68</f>
+      <c r="N68" s="16" t="n"/>
+      <c r="O68" s="17" t="n"/>
+      <c r="P68" s="18" t="n"/>
+      <c r="Q68" s="19">
+        <f>IF(N68&lt;&gt;"ja","",IF(O68="",H68,O68)*J68)</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="78" customHeight="1">
-      <c r="A69" s="15" t="n">
+      <c r="A69" s="20" t="n">
         <v>62</v>
       </c>
-      <c r="B69" s="16" t="inlineStr">
+      <c r="B69" s="21" t="inlineStr">
         <is>
           <t>NU01-05</t>
         </is>
       </c>
-      <c r="C69" s="17" t="n"/>
-      <c r="D69" s="18" t="inlineStr">
+      <c r="C69" s="22" t="n"/>
+      <c r="D69" s="23" t="inlineStr">
         <is>
           <t>Deko-Hirschkopf geometrisch
 Hirschkopf in geometrischer Form, Beton-/Holzoptik</t>
         </is>
       </c>
-      <c r="E69" s="12" t="n"/>
-      <c r="F69" s="18" t="inlineStr">
+      <c r="E69" s="13" t="n"/>
+      <c r="F69" s="23" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G69" s="16" t="inlineStr">
+      <c r="G69" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H69" s="16" t="n">
+      <c r="H69" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="I69" s="16" t="inlineStr">
+      <c r="I69" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J69" s="19" t="n">
+      <c r="J69" s="24" t="n">
         <v>40</v>
       </c>
-      <c r="K69" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L69" s="18" t="inlineStr">
+      <c r="K69" s="25">
+        <f>J69*1.19</f>
+        <v/>
+      </c>
+      <c r="L69" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M69" s="23" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M69" s="20">
-        <f>H69*J69</f>
+      <c r="N69" s="16" t="n"/>
+      <c r="O69" s="17" t="n"/>
+      <c r="P69" s="18" t="n"/>
+      <c r="Q69" s="26">
+        <f>IF(N69&lt;&gt;"ja","",IF(O69="",H69,O69)*J69)</f>
         <v/>
       </c>
     </row>
     <row r="70" ht="78" customHeight="1">
-      <c r="A70" s="8" t="n">
+      <c r="A70" s="9" t="n">
         <v>63</v>
       </c>
-      <c r="B70" s="9" t="inlineStr">
+      <c r="B70" s="10" t="inlineStr">
         <is>
           <t>NU01-06</t>
         </is>
       </c>
-      <c r="C70" s="10" t="n"/>
-      <c r="D70" s="11" t="inlineStr">
+      <c r="C70" s="11" t="n"/>
+      <c r="D70" s="12" t="inlineStr">
         <is>
           <t>Gemälde Marilyn mit Bollenhut
 Acryl auf Leinwand, großformatig ca. 120 x 120 cm - Eigenarbeit einer Privatperson</t>
         </is>
       </c>
-      <c r="E70" s="12" t="n"/>
-      <c r="F70" s="11" t="inlineStr">
+      <c r="E70" s="13" t="n"/>
+      <c r="F70" s="12" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G70" s="9" t="inlineStr">
+      <c r="G70" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H70" s="9" t="n">
+      <c r="H70" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I70" s="9" t="inlineStr">
+      <c r="I70" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J70" s="13" t="n">
+      <c r="J70" s="14" t="n">
         <v>650</v>
       </c>
-      <c r="K70" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L70" s="11" t="inlineStr">
+      <c r="K70" s="15">
+        <f>J70*1.19</f>
+        <v/>
+      </c>
+      <c r="L70" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M70" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M70" s="14">
-        <f>H70*J70</f>
+      <c r="N70" s="16" t="n"/>
+      <c r="O70" s="17" t="n"/>
+      <c r="P70" s="18" t="n"/>
+      <c r="Q70" s="19">
+        <f>IF(N70&lt;&gt;"ja","",IF(O70="",H70,O70)*J70)</f>
         <v/>
       </c>
     </row>
     <row r="71" ht="78" customHeight="1">
-      <c r="A71" s="15" t="n">
+      <c r="A71" s="27" t="n">
         <v>64</v>
       </c>
-      <c r="B71" s="16" t="inlineStr">
+      <c r="B71" s="28" t="inlineStr">
         <is>
           <t>NU01-07</t>
         </is>
       </c>
-      <c r="C71" s="17" t="n"/>
-      <c r="D71" s="18" t="inlineStr">
+      <c r="C71" s="29" t="n"/>
+      <c r="D71" s="30" t="inlineStr">
         <is>
           <t>Trachtenportrait gerahmt, klein
 Trachtenportrait gerahmt, klein</t>
         </is>
       </c>
-      <c r="E71" s="12" t="n"/>
-      <c r="F71" s="18" t="inlineStr">
+      <c r="E71" s="30" t="n"/>
+      <c r="F71" s="30" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G71" s="16" t="inlineStr">
+      <c r="G71" s="28" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H71" s="16" t="n">
+      <c r="H71" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="I71" s="16" t="inlineStr">
+      <c r="I71" s="28" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="J71" s="19" t="n">
+      <c r="J71" s="31" t="n">
         <v>45</v>
       </c>
-      <c r="K71" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L71" s="18" t="inlineStr">
+      <c r="K71" s="32">
+        <f>J71*1.19</f>
+        <v/>
+      </c>
+      <c r="L71" s="28" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M71" s="30" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M71" s="20">
-        <f>H71*J71</f>
+      <c r="N71" s="16" t="n"/>
+      <c r="O71" s="17" t="n"/>
+      <c r="P71" s="18" t="n"/>
+      <c r="Q71" s="33">
+        <f>IF(N71&lt;&gt;"ja","",IF(O71="",H71,O71)*J71)</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="78" customHeight="1">
-      <c r="A72" s="8" t="n">
+      <c r="A72" s="27" t="n">
         <v>65</v>
       </c>
-      <c r="B72" s="9" t="inlineStr">
+      <c r="B72" s="28" t="inlineStr">
         <is>
           <t>NU01-08</t>
         </is>
       </c>
-      <c r="C72" s="10" t="n"/>
-      <c r="D72" s="11" t="inlineStr">
+      <c r="C72" s="29" t="n"/>
+      <c r="D72" s="30" t="inlineStr">
         <is>
           <t>Trachtenfotografie gerahmt, weiß
 Fotodruck im weißen Rahmen, ca. 20 x 25 cm - Kaufware</t>
         </is>
       </c>
-      <c r="E72" s="12" t="n"/>
-      <c r="F72" s="11" t="inlineStr">
+      <c r="E72" s="30" t="n"/>
+      <c r="F72" s="30" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G72" s="9" t="inlineStr">
+      <c r="G72" s="28" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H72" s="9" t="n">
+      <c r="H72" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="I72" s="9" t="inlineStr">
+      <c r="I72" s="28" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J72" s="13" t="n">
+      <c r="J72" s="31" t="n">
         <v>35</v>
       </c>
-      <c r="K72" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L72" s="11" t="inlineStr">
+      <c r="K72" s="32">
+        <f>J72*1.19</f>
+        <v/>
+      </c>
+      <c r="L72" s="28" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M72" s="30" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M72" s="14">
-        <f>H72*J72</f>
+      <c r="N72" s="16" t="n"/>
+      <c r="O72" s="17" t="n"/>
+      <c r="P72" s="18" t="n"/>
+      <c r="Q72" s="33">
+        <f>IF(N72&lt;&gt;"ja","",IF(O72="",H72,O72)*J72)</f>
         <v/>
       </c>
     </row>
     <row r="73" ht="78" customHeight="1">
-      <c r="A73" s="15" t="n">
+      <c r="A73" s="27" t="n">
         <v>66</v>
       </c>
-      <c r="B73" s="16" t="inlineStr">
+      <c r="B73" s="28" t="inlineStr">
         <is>
           <t>NU01-09</t>
         </is>
       </c>
-      <c r="C73" s="17" t="n"/>
-      <c r="D73" s="18" t="inlineStr">
+      <c r="C73" s="29" t="n"/>
+      <c r="D73" s="30" t="inlineStr">
         <is>
           <t>Trachtenfotografie gerahmt, schwarz
 Fotodruck im schwarzen Rahmen mit Passepartout - Kaufware</t>
         </is>
       </c>
-      <c r="E73" s="12" t="n"/>
-      <c r="F73" s="18" t="inlineStr">
+      <c r="E73" s="30" t="n"/>
+      <c r="F73" s="30" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G73" s="16" t="inlineStr">
+      <c r="G73" s="28" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H73" s="16" t="n">
+      <c r="H73" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="I73" s="16" t="inlineStr">
+      <c r="I73" s="28" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J73" s="19" t="n">
+      <c r="J73" s="31" t="n">
         <v>35</v>
       </c>
-      <c r="K73" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L73" s="18" t="inlineStr">
+      <c r="K73" s="32">
+        <f>J73*1.19</f>
+        <v/>
+      </c>
+      <c r="L73" s="28" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M73" s="30" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M73" s="20">
-        <f>H73*J73</f>
+      <c r="N73" s="16" t="n"/>
+      <c r="O73" s="17" t="n"/>
+      <c r="P73" s="18" t="n"/>
+      <c r="Q73" s="33">
+        <f>IF(N73&lt;&gt;"ja","",IF(O73="",H73,O73)*J73)</f>
         <v/>
       </c>
     </row>
     <row r="74" ht="78" customHeight="1">
-      <c r="A74" s="8" t="n">
+      <c r="A74" s="9" t="n">
         <v>67</v>
       </c>
-      <c r="B74" s="9" t="inlineStr">
+      <c r="B74" s="10" t="inlineStr">
         <is>
           <t>NU01-10</t>
         </is>
       </c>
-      <c r="C74" s="10" t="n"/>
-      <c r="D74" s="11" t="inlineStr">
+      <c r="C74" s="11" t="n"/>
+      <c r="D74" s="12" t="inlineStr">
         <is>
           <t>Gemälde Panorama mit Tanne
 Acryl auf Leinwand, Querformat - Eigenarbeit einer Privatperson</t>
         </is>
       </c>
-      <c r="E74" s="12" t="n"/>
-      <c r="F74" s="11" t="inlineStr">
+      <c r="E74" s="13" t="n"/>
+      <c r="F74" s="12" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G74" s="9" t="inlineStr">
+      <c r="G74" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H74" s="9" t="n">
+      <c r="H74" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I74" s="9" t="inlineStr">
+      <c r="I74" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J74" s="13" t="n">
+      <c r="J74" s="14" t="n">
         <v>120</v>
       </c>
-      <c r="K74" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L74" s="11" t="inlineStr">
+      <c r="K74" s="15">
+        <f>J74*1.19</f>
+        <v/>
+      </c>
+      <c r="L74" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M74" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M74" s="14">
-        <f>H74*J74</f>
+      <c r="N74" s="16" t="n"/>
+      <c r="O74" s="17" t="n"/>
+      <c r="P74" s="18" t="n"/>
+      <c r="Q74" s="19">
+        <f>IF(N74&lt;&gt;"ja","",IF(O74="",H74,O74)*J74)</f>
         <v/>
       </c>
     </row>
     <row r="75" ht="78" customHeight="1">
-      <c r="A75" s="15" t="n">
+      <c r="A75" s="20" t="n">
         <v>68</v>
       </c>
-      <c r="B75" s="16" t="inlineStr">
+      <c r="B75" s="21" t="inlineStr">
         <is>
           <t>NU01-11</t>
         </is>
       </c>
-      <c r="C75" s="17" t="n"/>
-      <c r="D75" s="18" t="inlineStr">
+      <c r="C75" s="22" t="n"/>
+      <c r="D75" s="23" t="inlineStr">
         <is>
           <t>Bilderrahmen schwarz mit Strichfigur
 Gerahmte Drucke mit Bollenhut-Strichfiguren, schwarze Rahmen</t>
         </is>
       </c>
-      <c r="E75" s="12" t="n"/>
-      <c r="F75" s="18" t="inlineStr">
+      <c r="E75" s="13" t="n"/>
+      <c r="F75" s="23" t="inlineStr">
         <is>
           <t>Flur</t>
         </is>
       </c>
-      <c r="G75" s="16" t="inlineStr">
+      <c r="G75" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H75" s="16" t="n">
+      <c r="H75" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="I75" s="16" t="inlineStr">
+      <c r="I75" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J75" s="19" t="n">
+      <c r="J75" s="24" t="n">
         <v>15</v>
       </c>
-      <c r="K75" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L75" s="18" t="inlineStr">
+      <c r="K75" s="25">
+        <f>J75*1.19</f>
+        <v/>
+      </c>
+      <c r="L75" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M75" s="23" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M75" s="20">
-        <f>H75*J75</f>
+      <c r="N75" s="16" t="n"/>
+      <c r="O75" s="17" t="n"/>
+      <c r="P75" s="18" t="n"/>
+      <c r="Q75" s="26">
+        <f>IF(N75&lt;&gt;"ja","",IF(O75="",H75,O75)*J75)</f>
         <v/>
       </c>
     </row>
     <row r="76" ht="78" customHeight="1">
-      <c r="A76" s="8" t="n">
+      <c r="A76" s="9" t="n">
         <v>69</v>
       </c>
-      <c r="B76" s="9" t="inlineStr">
+      <c r="B76" s="10" t="inlineStr">
+        <is>
+          <t>NU01-12</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="n"/>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>Läufer dunkelgrau, IKEA Morum
+IKEA Morum, Flachgewebe dunkelgrau, für innen und außen geeignet, schmaler Läufer – 15 Stück verfügbar</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="n"/>
+      <c r="F76" s="12" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J76" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="K76" s="15">
+        <f>J76*1.19</f>
+        <v/>
+      </c>
+      <c r="L76" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M76" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N76" s="16" t="n"/>
+      <c r="O76" s="17" t="n"/>
+      <c r="P76" s="18" t="n"/>
+      <c r="Q76" s="19">
+        <f>IF(N76&lt;&gt;"ja","",IF(O76="",H76,O76)*J76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" ht="78" customHeight="1">
+      <c r="A77" s="20" t="n">
+        <v>70</v>
+      </c>
+      <c r="B77" s="21" t="inlineStr">
         <is>
           <t>NU02-01</t>
         </is>
       </c>
-      <c r="C76" s="10" t="n"/>
-      <c r="D76" s="11" t="inlineStr">
+      <c r="C77" s="22" t="n"/>
+      <c r="D77" s="23" t="inlineStr">
         <is>
           <t>Kommode weiß, 6 Schubladen
 IKEA Nordli, weiß, hoch, 6 Schubladen</t>
         </is>
       </c>
-      <c r="E76" s="12" t="n"/>
-      <c r="F76" s="11" t="inlineStr">
+      <c r="E77" s="13" t="n"/>
+      <c r="F77" s="23" t="inlineStr">
         <is>
           <t>Gruppenraum 5</t>
         </is>
       </c>
-      <c r="G76" s="9" t="inlineStr">
+      <c r="G77" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H76" s="9" t="n">
+      <c r="H77" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I76" s="9" t="inlineStr">
+      <c r="I77" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J76" s="13" t="n">
+      <c r="J77" s="24" t="n">
         <v>90</v>
       </c>
-      <c r="K76" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L76" s="11" t="inlineStr">
+      <c r="K77" s="25">
+        <f>J77*1.19</f>
+        <v/>
+      </c>
+      <c r="L77" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M77" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M76" s="14">
-        <f>H76*J76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" ht="78" customHeight="1">
-      <c r="A77" s="15" t="n">
-        <v>70</v>
-      </c>
-      <c r="B77" s="16" t="inlineStr">
+      <c r="N77" s="16" t="n"/>
+      <c r="O77" s="17" t="n"/>
+      <c r="P77" s="18" t="n"/>
+      <c r="Q77" s="26">
+        <f>IF(N77&lt;&gt;"ja","",IF(O77="",H77,O77)*J77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" ht="78" customHeight="1">
+      <c r="A78" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="B78" s="10" t="inlineStr">
         <is>
           <t>NU03-01</t>
         </is>
       </c>
-      <c r="C77" s="17" t="n"/>
-      <c r="D77" s="18" t="inlineStr">
+      <c r="C78" s="11" t="n"/>
+      <c r="D78" s="12" t="inlineStr">
         <is>
           <t>Kommode weiß, hoch, 7 Schubladen
 IKEA Nordli, weiß, hohe Ausführung</t>
         </is>
       </c>
-      <c r="E77" s="12" t="n"/>
-      <c r="F77" s="18" t="inlineStr">
+      <c r="E78" s="13" t="n"/>
+      <c r="F78" s="12" t="inlineStr">
         <is>
           <t>Schlafraum 4</t>
         </is>
       </c>
-      <c r="G77" s="16" t="inlineStr">
+      <c r="G78" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H77" s="16" t="n">
+      <c r="H78" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I77" s="16" t="inlineStr">
+      <c r="I78" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J77" s="19" t="n">
+      <c r="J78" s="14" t="n">
         <v>110</v>
       </c>
-      <c r="K77" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L77" s="18" t="inlineStr">
+      <c r="K78" s="15">
+        <f>J78*1.19</f>
+        <v/>
+      </c>
+      <c r="L78" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M78" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M77" s="20">
-        <f>H77*J77</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" ht="78" customHeight="1">
-      <c r="A78" s="8" t="n">
-        <v>71</v>
-      </c>
-      <c r="B78" s="9" t="inlineStr">
+      <c r="N78" s="16" t="n"/>
+      <c r="O78" s="17" t="n"/>
+      <c r="P78" s="18" t="n"/>
+      <c r="Q78" s="19">
+        <f>IF(N78&lt;&gt;"ja","",IF(O78="",H78,O78)*J78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" ht="78" customHeight="1">
+      <c r="A79" s="20" t="n">
+        <v>72</v>
+      </c>
+      <c r="B79" s="21" t="inlineStr">
         <is>
           <t>NU04-01</t>
         </is>
       </c>
-      <c r="C78" s="10" t="n"/>
-      <c r="D78" s="11" t="inlineStr">
+      <c r="C79" s="22" t="n"/>
+      <c r="D79" s="23" t="inlineStr">
         <is>
           <t>Wanddeko Hirschkopf Sperrholz
 3D-Stecksatz aus Sperrholz, schwarz lackiert, Wandmontage</t>
         </is>
       </c>
-      <c r="E78" s="12" t="n"/>
-      <c r="F78" s="11" t="inlineStr">
+      <c r="E79" s="13" t="n"/>
+      <c r="F79" s="23" t="inlineStr">
         <is>
           <t>Schlafraum 5</t>
         </is>
       </c>
-      <c r="G78" s="9" t="inlineStr">
+      <c r="G79" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H78" s="9" t="n">
+      <c r="H79" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="I78" s="9" t="inlineStr">
+      <c r="I79" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J78" s="13" t="n">
+      <c r="J79" s="24" t="n">
         <v>20</v>
       </c>
-      <c r="K78" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L78" s="11" t="inlineStr">
+      <c r="K79" s="25">
+        <f>J79*1.19</f>
+        <v/>
+      </c>
+      <c r="L79" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M79" s="23" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M78" s="14">
-        <f>H78*J78</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" ht="78" customHeight="1">
-      <c r="A79" s="15" t="n">
-        <v>72</v>
-      </c>
-      <c r="B79" s="16" t="inlineStr">
+      <c r="N79" s="16" t="n"/>
+      <c r="O79" s="17" t="n"/>
+      <c r="P79" s="18" t="n"/>
+      <c r="Q79" s="26">
+        <f>IF(N79&lt;&gt;"ja","",IF(O79="",H79,O79)*J79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" ht="78" customHeight="1">
+      <c r="A80" s="9" t="n">
+        <v>73</v>
+      </c>
+      <c r="B80" s="10" t="inlineStr">
         <is>
           <t>NU04-02</t>
         </is>
       </c>
-      <c r="C79" s="17" t="n"/>
-      <c r="D79" s="18" t="inlineStr">
+      <c r="C80" s="11" t="n"/>
+      <c r="D80" s="12" t="inlineStr">
         <is>
           <t>Kommode anthrazit, groß
 IKEA Nordli, anthrazit, große Kombination, ca. 12-14 Schubladen; 2 Schubladen bereits repariert; funktionsfähig</t>
         </is>
       </c>
-      <c r="E79" s="12" t="n"/>
-      <c r="F79" s="18" t="inlineStr">
+      <c r="E80" s="13" t="n"/>
+      <c r="F80" s="12" t="inlineStr">
         <is>
           <t>Schlafraum 5</t>
         </is>
       </c>
-      <c r="G79" s="16" t="inlineStr">
+      <c r="G80" s="10" t="inlineStr">
         <is>
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="H79" s="16" t="n">
+      <c r="H80" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I79" s="16" t="inlineStr">
+      <c r="I80" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J79" s="19" t="n">
+      <c r="J80" s="14" t="n">
         <v>220</v>
       </c>
-      <c r="K79" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L79" s="18" t="inlineStr">
+      <c r="K80" s="15">
+        <f>J80*1.19</f>
+        <v/>
+      </c>
+      <c r="L80" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M80" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M79" s="20">
-        <f>H79*J79</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" ht="78" customHeight="1">
-      <c r="A80" s="8" t="n">
-        <v>73</v>
-      </c>
-      <c r="B80" s="21" t="inlineStr">
+      <c r="N80" s="16" t="n"/>
+      <c r="O80" s="17" t="n"/>
+      <c r="P80" s="18" t="n"/>
+      <c r="Q80" s="19">
+        <f>IF(N80&lt;&gt;"ja","",IF(O80="",H80,O80)*J80)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" ht="78" customHeight="1">
+      <c r="A81" s="20" t="n">
+        <v>74</v>
+      </c>
+      <c r="B81" s="35" t="inlineStr">
         <is>
           <t>NU04-03</t>
         </is>
       </c>
-      <c r="C80" s="10" t="n"/>
-      <c r="D80" s="11" t="inlineStr">
+      <c r="C81" s="22" t="n"/>
+      <c r="D81" s="23" t="inlineStr">
         <is>
           <t>Massivholztisch mit Baumkante
 Massivholzplatte mit natürlicher Baumkante, schwarzes Metallgestell, ca. 200 x 90 cm</t>
         </is>
       </c>
-      <c r="E80" s="12" t="n"/>
-      <c r="F80" s="11" t="inlineStr">
+      <c r="E81" s="13" t="n"/>
+      <c r="F81" s="23" t="inlineStr">
         <is>
           <t>Schlafraum 5</t>
         </is>
       </c>
-      <c r="G80" s="9" t="inlineStr">
+      <c r="G81" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H80" s="9" t="n">
+      <c r="H81" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I80" s="9" t="inlineStr">
+      <c r="I81" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J80" s="13" t="n">
+      <c r="J81" s="24" t="n">
         <v>450</v>
       </c>
-      <c r="K80" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L80" s="11" t="inlineStr">
+      <c r="K81" s="25">
+        <f>J81*1.19</f>
+        <v/>
+      </c>
+      <c r="L81" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M81" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M80" s="14">
-        <f>H80*J80</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" ht="78" customHeight="1">
-      <c r="A81" s="15" t="n">
-        <v>74</v>
-      </c>
-      <c r="B81" s="16" t="inlineStr">
+      <c r="N81" s="16" t="n"/>
+      <c r="O81" s="17" t="n"/>
+      <c r="P81" s="18" t="n"/>
+      <c r="Q81" s="26">
+        <f>IF(N81&lt;&gt;"ja","",IF(O81="",H81,O81)*J81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" ht="78" customHeight="1">
+      <c r="A82" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="B82" s="10" t="inlineStr">
         <is>
           <t>NU04-04</t>
         </is>
       </c>
-      <c r="C81" s="17" t="n"/>
-      <c r="D81" s="18" t="inlineStr">
+      <c r="C82" s="11" t="n"/>
+      <c r="D82" s="12" t="inlineStr">
         <is>
           <t>Magnettafel grau, groß
 Magnet-/Schreibtafel, grau, beschriftet, Wandmontage</t>
         </is>
       </c>
-      <c r="E81" s="12" t="n"/>
-      <c r="F81" s="18" t="inlineStr">
+      <c r="E82" s="13" t="n"/>
+      <c r="F82" s="12" t="inlineStr">
         <is>
           <t>Schlafraum 5</t>
         </is>
       </c>
-      <c r="G81" s="16" t="inlineStr">
+      <c r="G82" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H81" s="16" t="n">
+      <c r="H82" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I81" s="16" t="inlineStr">
+      <c r="I82" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J81" s="19" t="n">
+      <c r="J82" s="14" t="n">
         <v>45</v>
       </c>
-      <c r="K81" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L81" s="18" t="inlineStr">
+      <c r="K82" s="15">
+        <f>J82*1.19</f>
+        <v/>
+      </c>
+      <c r="L82" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M82" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M81" s="20">
-        <f>H81*J81</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" ht="78" customHeight="1">
-      <c r="A82" s="8" t="n">
-        <v>75</v>
-      </c>
-      <c r="B82" s="9" t="inlineStr">
+      <c r="N82" s="16" t="n"/>
+      <c r="O82" s="17" t="n"/>
+      <c r="P82" s="18" t="n"/>
+      <c r="Q82" s="19">
+        <f>IF(N82&lt;&gt;"ja","",IF(O82="",H82,O82)*J82)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" ht="78" customHeight="1">
+      <c r="A83" s="20" t="n">
+        <v>76</v>
+      </c>
+      <c r="B83" s="21" t="inlineStr">
         <is>
           <t>NU04-05</t>
         </is>
       </c>
-      <c r="C82" s="10" t="n"/>
-      <c r="D82" s="11" t="inlineStr">
+      <c r="C83" s="22" t="n"/>
+      <c r="D83" s="23" t="inlineStr">
         <is>
           <t>Hochflorteppich beige
 Shaggy/Hochflor, beige, ca. 200 x 300 cm, gereinigt</t>
         </is>
       </c>
-      <c r="E82" s="12" t="n"/>
-      <c r="F82" s="11" t="inlineStr">
+      <c r="E83" s="13" t="n"/>
+      <c r="F83" s="23" t="inlineStr">
         <is>
           <t>Schlafraum 5</t>
         </is>
       </c>
-      <c r="G82" s="9" t="inlineStr">
+      <c r="G83" s="21" t="inlineStr">
         <is>
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="H82" s="9" t="n">
+      <c r="H83" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="I82" s="9" t="inlineStr">
+      <c r="I83" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J82" s="13" t="n">
+      <c r="J83" s="24" t="n">
         <v>35</v>
       </c>
-      <c r="K82" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L82" s="11" t="inlineStr">
+      <c r="K83" s="25">
+        <f>J83*1.19</f>
+        <v/>
+      </c>
+      <c r="L83" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M83" s="23" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M82" s="14">
-        <f>H82*J82</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" ht="78" customHeight="1">
-      <c r="A83" s="15" t="n">
-        <v>76</v>
-      </c>
-      <c r="B83" s="16" t="inlineStr">
+      <c r="N83" s="16" t="n"/>
+      <c r="O83" s="17" t="n"/>
+      <c r="P83" s="18" t="n"/>
+      <c r="Q83" s="26">
+        <f>IF(N83&lt;&gt;"ja","",IF(O83="",H83,O83)*J83)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="78" customHeight="1">
+      <c r="A84" s="9" t="n">
+        <v>77</v>
+      </c>
+      <c r="B84" s="10" t="inlineStr">
         <is>
           <t>NU04-06</t>
         </is>
       </c>
-      <c r="C83" s="17" t="n"/>
-      <c r="D83" s="18" t="inlineStr">
+      <c r="C84" s="11" t="n"/>
+      <c r="D84" s="12" t="inlineStr">
         <is>
           <t>Teppich schwarz-weiß Rautenmuster
 Flachgewebe, Rautenmuster schwarz/weiß, ca. 200 x 300 cm</t>
         </is>
       </c>
-      <c r="E83" s="12" t="n"/>
-      <c r="F83" s="18" t="inlineStr">
+      <c r="E84" s="13" t="n"/>
+      <c r="F84" s="12" t="inlineStr">
         <is>
           <t>Schlafraum 5</t>
         </is>
       </c>
-      <c r="G83" s="16" t="inlineStr">
+      <c r="G84" s="10" t="inlineStr">
         <is>
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="H83" s="16" t="n">
+      <c r="H84" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I83" s="16" t="inlineStr">
+      <c r="I84" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J83" s="19" t="n">
+      <c r="J84" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="K83" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L83" s="18" t="inlineStr">
+      <c r="K84" s="15">
+        <f>J84*1.19</f>
+        <v/>
+      </c>
+      <c r="L84" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M84" s="12" t="inlineStr">
         <is>
           <t>Versand möglich</t>
         </is>
       </c>
-      <c r="M83" s="20">
-        <f>H83*J83</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" ht="78" customHeight="1">
-      <c r="A84" s="8" t="n">
-        <v>77</v>
-      </c>
-      <c r="B84" s="21" t="inlineStr">
+      <c r="N84" s="16" t="n"/>
+      <c r="O84" s="17" t="n"/>
+      <c r="P84" s="18" t="n"/>
+      <c r="Q84" s="19">
+        <f>IF(N84&lt;&gt;"ja","",IF(O84="",H84,O84)*J84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" ht="78" customHeight="1">
+      <c r="A85" s="20" t="n">
+        <v>78</v>
+      </c>
+      <c r="B85" s="35" t="inlineStr">
         <is>
           <t>TE01-01</t>
         </is>
       </c>
-      <c r="C84" s="10" t="n"/>
-      <c r="D84" s="11" t="inlineStr">
+      <c r="C85" s="22" t="n"/>
+      <c r="D85" s="23" t="inlineStr">
         <is>
           <t>Biohort Freizeitbox weiß (Terrasse)
 Biohort Freizeitbox weiß (Terrasse)
 Alu-Auflagenbox, weiß, abschließbar, wetterfest</t>
         </is>
       </c>
-      <c r="E84" s="12" t="n"/>
-      <c r="F84" s="11" t="inlineStr">
+      <c r="E85" s="13" t="n"/>
+      <c r="F85" s="23" t="inlineStr">
         <is>
           <t>Terrasse</t>
         </is>
       </c>
-      <c r="G84" s="9" t="inlineStr">
+      <c r="G85" s="21" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H84" s="9" t="n">
+      <c r="H85" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I84" s="9" t="inlineStr">
+      <c r="I85" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J84" s="13" t="n">
+      <c r="J85" s="24" t="n">
         <v>410</v>
       </c>
-      <c r="K84" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L84" s="11" t="inlineStr">
+      <c r="K85" s="25">
+        <f>J85*1.19</f>
+        <v/>
+      </c>
+      <c r="L85" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M85" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M84" s="14">
-        <f>H84*J84</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" ht="78" customHeight="1">
-      <c r="A85" s="15" t="n">
-        <v>78</v>
-      </c>
-      <c r="B85" s="21" t="inlineStr">
+      <c r="N85" s="16" t="n"/>
+      <c r="O85" s="17" t="n"/>
+      <c r="P85" s="18" t="n"/>
+      <c r="Q85" s="26">
+        <f>IF(N85&lt;&gt;"ja","",IF(O85="",H85,O85)*J85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" ht="78" customHeight="1">
+      <c r="A86" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="B86" s="35" t="inlineStr">
         <is>
           <t>TE01-02</t>
         </is>
       </c>
-      <c r="C85" s="17" t="n"/>
-      <c r="D85" s="18" t="inlineStr">
+      <c r="C86" s="11" t="n"/>
+      <c r="D86" s="12" t="inlineStr">
         <is>
           <t>Gartentisch mit Granitplatte inkl. Stühle und Schutzhülle
 Granitplatte auf Aluminiumgestell, ca. 160 x 90 cm inkl. Stühle und Schutzhülle</t>
         </is>
       </c>
-      <c r="E85" s="12" t="n"/>
-      <c r="F85" s="18" t="inlineStr">
+      <c r="E86" s="13" t="n"/>
+      <c r="F86" s="12" t="inlineStr">
         <is>
           <t>Terrasse</t>
         </is>
       </c>
-      <c r="G85" s="16" t="inlineStr">
+      <c r="G86" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H85" s="16" t="n">
+      <c r="H86" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I85" s="16" t="inlineStr">
+      <c r="I86" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J85" s="19" t="n">
+      <c r="J86" s="14" t="n">
         <v>280</v>
       </c>
-      <c r="K85" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L85" s="18" t="inlineStr">
+      <c r="K86" s="15">
+        <f>J86*1.19</f>
+        <v/>
+      </c>
+      <c r="L86" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M86" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M85" s="20">
-        <f>H85*J85</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" ht="78" customHeight="1">
-      <c r="A86" s="8" t="n">
-        <v>79</v>
-      </c>
-      <c r="B86" s="9" t="inlineStr">
+      <c r="N86" s="16" t="n"/>
+      <c r="O86" s="17" t="n"/>
+      <c r="P86" s="18" t="n"/>
+      <c r="Q86" s="19">
+        <f>IF(N86&lt;&gt;"ja","",IF(O86="",H86,O86)*J86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" ht="78" customHeight="1">
+      <c r="A87" s="20" t="n">
+        <v>80</v>
+      </c>
+      <c r="B87" s="21" t="inlineStr">
         <is>
           <t>TE01-03</t>
         </is>
       </c>
-      <c r="C86" s="10" t="n"/>
-      <c r="D86" s="11" t="inlineStr">
+      <c r="C87" s="22" t="n"/>
+      <c r="D87" s="23" t="inlineStr">
         <is>
           <t>Textilene-Stapelsessel anthrazit
 Hochlehner, Aluminiumrahmen mit Textilenbespannung, stapelbar</t>
         </is>
       </c>
-      <c r="E86" s="12" t="n"/>
-      <c r="F86" s="11" t="inlineStr">
+      <c r="E87" s="13" t="n"/>
+      <c r="F87" s="23" t="inlineStr">
         <is>
           <t>Terrasse</t>
         </is>
       </c>
-      <c r="G86" s="9" t="inlineStr">
+      <c r="G87" s="21" t="inlineStr">
         <is>
           <t>stark gebraucht</t>
         </is>
       </c>
-      <c r="H86" s="9" t="n">
+      <c r="H87" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="I86" s="9" t="inlineStr">
+      <c r="I87" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J86" s="13" t="n">
+      <c r="J87" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="K86" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L86" s="11" t="inlineStr">
+      <c r="K87" s="25">
+        <f>J87*1.19</f>
+        <v/>
+      </c>
+      <c r="L87" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M87" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M86" s="14">
-        <f>H86*J86</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" ht="78" customHeight="1">
-      <c r="A87" s="15" t="n">
-        <v>80</v>
-      </c>
-      <c r="B87" s="21" t="inlineStr">
+      <c r="N87" s="16" t="n"/>
+      <c r="O87" s="17" t="n"/>
+      <c r="P87" s="18" t="n"/>
+      <c r="Q87" s="26">
+        <f>IF(N87&lt;&gt;"ja","",IF(O87="",H87,O87)*J87)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="78" customHeight="1">
+      <c r="A88" s="27" t="n">
+        <v>81</v>
+      </c>
+      <c r="B88" s="34" t="inlineStr">
         <is>
           <t>TE01-04</t>
         </is>
       </c>
-      <c r="C87" s="17" t="n"/>
-      <c r="D87" s="18" t="inlineStr">
+      <c r="C88" s="29" t="n"/>
+      <c r="D88" s="30" t="inlineStr">
         <is>
           <t>Weber Genesis Gasgrill
 Weber Genesis, Kupfer/Edelstahl, 4 Brenner mit Sear Station, inkl. Gasflasche</t>
         </is>
       </c>
-      <c r="E87" s="12" t="n"/>
-      <c r="F87" s="18" t="inlineStr">
+      <c r="E88" s="30" t="n"/>
+      <c r="F88" s="30" t="inlineStr">
         <is>
           <t>Terrasse</t>
         </is>
       </c>
-      <c r="G87" s="16" t="inlineStr">
+      <c r="G88" s="28" t="inlineStr">
         <is>
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="H87" s="16" t="n">
+      <c r="H88" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="I87" s="16" t="inlineStr">
+      <c r="I88" s="28" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J87" s="19" t="n">
+      <c r="J88" s="31" t="n">
         <v>450</v>
       </c>
-      <c r="K87" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L87" s="18" t="inlineStr">
+      <c r="K88" s="32">
+        <f>J88*1.19</f>
+        <v/>
+      </c>
+      <c r="L88" s="28" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M88" s="30" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M87" s="20">
-        <f>H87*J87</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" ht="78" customHeight="1">
-      <c r="A88" s="8" t="n">
-        <v>81</v>
-      </c>
-      <c r="B88" s="9" t="inlineStr">
+      <c r="N88" s="16" t="n"/>
+      <c r="O88" s="17" t="n"/>
+      <c r="P88" s="18" t="n"/>
+      <c r="Q88" s="33">
+        <f>IF(N88&lt;&gt;"ja","",IF(O88="",H88,O88)*J88)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" ht="78" customHeight="1">
+      <c r="A89" s="20" t="n">
+        <v>82</v>
+      </c>
+      <c r="B89" s="21" t="inlineStr">
         <is>
           <t>TE01-05</t>
         </is>
       </c>
-      <c r="C88" s="10" t="n"/>
-      <c r="D88" s="11" t="inlineStr">
+      <c r="C89" s="22" t="n"/>
+      <c r="D89" s="23" t="inlineStr">
         <is>
           <t>Sonnenschirm creme
 Marktschirm mit Holzstiel, creme, ca. 3 m Durchmesser</t>
         </is>
       </c>
-      <c r="E88" s="12" t="n"/>
-      <c r="F88" s="11" t="inlineStr">
+      <c r="E89" s="13" t="n"/>
+      <c r="F89" s="23" t="inlineStr">
         <is>
           <t>Terrasse</t>
         </is>
       </c>
-      <c r="G88" s="9" t="inlineStr">
+      <c r="G89" s="21" t="inlineStr">
         <is>
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="H88" s="9" t="n">
+      <c r="H89" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I88" s="9" t="inlineStr">
+      <c r="I89" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J88" s="13" t="n">
+      <c r="J89" s="24" t="n">
         <v>70</v>
       </c>
-      <c r="K88" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L88" s="11" t="inlineStr">
+      <c r="K89" s="25">
+        <f>J89*1.19</f>
+        <v/>
+      </c>
+      <c r="L89" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M89" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M88" s="14">
-        <f>H88*J88</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" ht="78" customHeight="1">
-      <c r="A89" s="15" t="n">
-        <v>82</v>
-      </c>
-      <c r="B89" s="16" t="inlineStr">
+      <c r="N89" s="16" t="n"/>
+      <c r="O89" s="17" t="n"/>
+      <c r="P89" s="18" t="n"/>
+      <c r="Q89" s="26">
+        <f>IF(N89&lt;&gt;"ja","",IF(O89="",H89,O89)*J89)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" ht="78" customHeight="1">
+      <c r="A90" s="9" t="n">
+        <v>83</v>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
         <is>
           <t>TE02-01</t>
         </is>
       </c>
-      <c r="C89" s="17" t="n"/>
-      <c r="D89" s="18" t="inlineStr">
+      <c r="C90" s="11" t="n"/>
+      <c r="D90" s="12" t="inlineStr">
         <is>
           <t>Pflanzkübel Plastik weiß
 Runder Pflanzkübel, Betonoptik weiß, Durchmesser ca. 50 cm</t>
         </is>
       </c>
-      <c r="E89" s="12" t="n"/>
-      <c r="F89" s="18" t="inlineStr">
+      <c r="E90" s="13" t="n"/>
+      <c r="F90" s="12" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="G89" s="16" t="inlineStr">
+      <c r="G90" s="10" t="inlineStr">
         <is>
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="H89" s="16" t="n">
+      <c r="H90" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="I89" s="16" t="inlineStr">
+      <c r="I90" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J89" s="19" t="n">
+      <c r="J90" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="K89" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L89" s="18" t="inlineStr">
+      <c r="K90" s="15">
+        <f>J90*1.19</f>
+        <v/>
+      </c>
+      <c r="L90" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M90" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M89" s="20">
-        <f>H89*J89</f>
-        <v/>
-      </c>
-    </row>
-    <row r="90" ht="78" customHeight="1">
-      <c r="A90" s="8" t="n">
-        <v>83</v>
-      </c>
-      <c r="B90" s="9" t="inlineStr">
+      <c r="N90" s="16" t="n"/>
+      <c r="O90" s="17" t="n"/>
+      <c r="P90" s="18" t="n"/>
+      <c r="Q90" s="19">
+        <f>IF(N90&lt;&gt;"ja","",IF(O90="",H90,O90)*J90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" ht="78" customHeight="1">
+      <c r="A91" s="20" t="n">
+        <v>84</v>
+      </c>
+      <c r="B91" s="21" t="inlineStr">
         <is>
           <t>TE02-02</t>
         </is>
       </c>
-      <c r="C90" s="10" t="n"/>
-      <c r="D90" s="11" t="inlineStr">
+      <c r="C91" s="22" t="n"/>
+      <c r="D91" s="23" t="inlineStr">
         <is>
           <t>Gartenstuhl Kunststoff anthrazit
 Stapelbarer Gartenstuhl mit Armlehnen, anthrazit</t>
         </is>
       </c>
-      <c r="E90" s="12" t="n"/>
-      <c r="F90" s="11" t="inlineStr">
+      <c r="E91" s="13" t="n"/>
+      <c r="F91" s="23" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="G90" s="9" t="inlineStr">
+      <c r="G91" s="21" t="inlineStr">
         <is>
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="H90" s="9" t="n">
+      <c r="H91" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="I90" s="9" t="inlineStr">
+      <c r="I91" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J90" s="13" t="n">
+      <c r="J91" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="K90" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L90" s="11" t="inlineStr">
+      <c r="K91" s="25">
+        <f>J91*1.19</f>
+        <v/>
+      </c>
+      <c r="L91" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M91" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M90" s="14">
-        <f>H90*J90</f>
-        <v/>
-      </c>
-    </row>
-    <row r="91" ht="78" customHeight="1">
-      <c r="A91" s="15" t="n">
-        <v>84</v>
-      </c>
-      <c r="B91" s="16" t="inlineStr">
+      <c r="N91" s="16" t="n"/>
+      <c r="O91" s="17" t="n"/>
+      <c r="P91" s="18" t="n"/>
+      <c r="Q91" s="26">
+        <f>IF(N91&lt;&gt;"ja","",IF(O91="",H91,O91)*J91)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" ht="78" customHeight="1">
+      <c r="A92" s="9" t="n">
+        <v>85</v>
+      </c>
+      <c r="B92" s="10" t="inlineStr">
         <is>
           <t>TE02-03</t>
         </is>
       </c>
-      <c r="C91" s="17" t="n"/>
-      <c r="D91" s="18" t="inlineStr">
+      <c r="C92" s="11" t="n"/>
+      <c r="D92" s="12" t="inlineStr">
         <is>
           <t>Gartentisch anthrazit
 Aluminiumrahmen mit Lamellenplatte in Holzoptik, anthrazit inkl. Stühle</t>
         </is>
       </c>
-      <c r="E91" s="12" t="n"/>
-      <c r="F91" s="18" t="inlineStr">
+      <c r="E92" s="13" t="n"/>
+      <c r="F92" s="12" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="G91" s="16" t="inlineStr">
+      <c r="G92" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H91" s="16" t="n">
+      <c r="H92" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="I91" s="16" t="inlineStr">
+      <c r="I92" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J91" s="19" t="n">
+      <c r="J92" s="14" t="n">
         <v>150</v>
       </c>
-      <c r="K91" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L91" s="18" t="inlineStr">
+      <c r="K92" s="15">
+        <f>J92*1.19</f>
+        <v/>
+      </c>
+      <c r="L92" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M92" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M91" s="20">
-        <f>H91*J91</f>
-        <v/>
-      </c>
-    </row>
-    <row r="92" ht="78" customHeight="1">
-      <c r="A92" s="8" t="n">
-        <v>85</v>
-      </c>
-      <c r="B92" s="21" t="inlineStr">
+      <c r="N92" s="16" t="n"/>
+      <c r="O92" s="17" t="n"/>
+      <c r="P92" s="18" t="n"/>
+      <c r="Q92" s="19">
+        <f>IF(N92&lt;&gt;"ja","",IF(O92="",H92,O92)*J92)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" ht="78" customHeight="1">
+      <c r="A93" s="20" t="n">
+        <v>86</v>
+      </c>
+      <c r="B93" s="35" t="inlineStr">
         <is>
           <t>TE02-04</t>
         </is>
       </c>
-      <c r="C92" s="10" t="n"/>
-      <c r="D92" s="11" t="inlineStr">
+      <c r="C93" s="22" t="n"/>
+      <c r="D93" s="23" t="inlineStr">
         <is>
           <t>Teak-Klapptisch rund
 Runder Gartenklapptisch aus Hartholz/Teak inkl. Stühle</t>
         </is>
       </c>
-      <c r="E92" s="12" t="n"/>
-      <c r="F92" s="11" t="inlineStr">
+      <c r="E93" s="13" t="n"/>
+      <c r="F93" s="23" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="G92" s="9" t="inlineStr">
+      <c r="G93" s="21" t="inlineStr">
         <is>
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="H92" s="9" t="n">
+      <c r="H93" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I92" s="9" t="inlineStr">
+      <c r="I93" s="21" t="inlineStr">
         <is>
           <t>Set</t>
         </is>
       </c>
-      <c r="J92" s="13" t="n">
+      <c r="J93" s="24" t="n">
         <v>150</v>
       </c>
-      <c r="K92" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L92" s="11" t="inlineStr">
+      <c r="K93" s="25">
+        <f>J93*1.19</f>
+        <v/>
+      </c>
+      <c r="L93" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M93" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M92" s="14">
-        <f>H92*J92</f>
-        <v/>
-      </c>
-    </row>
-    <row r="93" ht="78" customHeight="1">
-      <c r="A93" s="15" t="n">
-        <v>86</v>
-      </c>
-      <c r="B93" s="16" t="inlineStr">
+      <c r="N93" s="16" t="n"/>
+      <c r="O93" s="17" t="n"/>
+      <c r="P93" s="18" t="n"/>
+      <c r="Q93" s="26">
+        <f>IF(N93&lt;&gt;"ja","",IF(O93="",H93,O93)*J93)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" ht="78" customHeight="1">
+      <c r="A94" s="9" t="n">
+        <v>87</v>
+      </c>
+      <c r="B94" s="10" t="inlineStr">
         <is>
           <t>TE02-05</t>
         </is>
       </c>
-      <c r="C93" s="17" t="n"/>
-      <c r="D93" s="18" t="inlineStr">
+      <c r="C94" s="11" t="n"/>
+      <c r="D94" s="12" t="inlineStr">
         <is>
           <t>Pflanzkübel grau, groß
 Kunststoff-Pflanzkübel grau, Durchmesser ca. 60 cm</t>
         </is>
       </c>
-      <c r="E93" s="12" t="n"/>
-      <c r="F93" s="18" t="inlineStr">
+      <c r="E94" s="13" t="n"/>
+      <c r="F94" s="12" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="G93" s="16" t="inlineStr">
+      <c r="G94" s="10" t="inlineStr">
         <is>
           <t>gut</t>
         </is>
       </c>
-      <c r="H93" s="16" t="n">
+      <c r="H94" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I93" s="16" t="inlineStr">
+      <c r="I94" s="10" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J93" s="19" t="n">
+      <c r="J94" s="14" t="n">
         <v>90</v>
       </c>
-      <c r="K93" s="16" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L93" s="18" t="inlineStr">
+      <c r="K94" s="15">
+        <f>J94*1.19</f>
+        <v/>
+      </c>
+      <c r="L94" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M94" s="12" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M93" s="20">
-        <f>H93*J93</f>
-        <v/>
-      </c>
-    </row>
-    <row r="94" ht="78" customHeight="1">
-      <c r="A94" s="8" t="n">
-        <v>87</v>
-      </c>
-      <c r="B94" s="9" t="inlineStr">
+      <c r="N94" s="16" t="n"/>
+      <c r="O94" s="17" t="n"/>
+      <c r="P94" s="18" t="n"/>
+      <c r="Q94" s="19">
+        <f>IF(N94&lt;&gt;"ja","",IF(O94="",H94,O94)*J94)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" ht="78" customHeight="1">
+      <c r="A95" s="20" t="n">
+        <v>88</v>
+      </c>
+      <c r="B95" s="21" t="inlineStr">
         <is>
           <t>TE02-06</t>
         </is>
       </c>
-      <c r="C94" s="10" t="n"/>
-      <c r="D94" s="11" t="inlineStr">
+      <c r="C95" s="22" t="n"/>
+      <c r="D95" s="23" t="inlineStr">
         <is>
           <t>Holzstern mit Lichterkette
 Großer Dekostern aus Holzlatten mit Lichterkette, ca. 2 m</t>
         </is>
       </c>
-      <c r="E94" s="12" t="n"/>
-      <c r="F94" s="11" t="inlineStr">
+      <c r="E95" s="13" t="n"/>
+      <c r="F95" s="23" t="inlineStr">
         <is>
           <t>Dachterrasse</t>
         </is>
       </c>
-      <c r="G94" s="9" t="inlineStr">
+      <c r="G95" s="21" t="inlineStr">
         <is>
           <t>gebraucht</t>
         </is>
       </c>
-      <c r="H94" s="9" t="n">
+      <c r="H95" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="I94" s="9" t="inlineStr">
+      <c r="I95" s="21" t="inlineStr">
         <is>
           <t>Stück</t>
         </is>
       </c>
-      <c r="J94" s="13" t="n">
+      <c r="J95" s="24" t="n">
         <v>180</v>
       </c>
-      <c r="K94" s="9" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="L94" s="11" t="inlineStr">
+      <c r="K95" s="25">
+        <f>J95*1.19</f>
+        <v/>
+      </c>
+      <c r="L95" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M95" s="23" t="inlineStr">
         <is>
           <t>nur Abholung</t>
         </is>
       </c>
-      <c r="M94" s="14">
-        <f>H94*J94</f>
-        <v/>
-      </c>
-    </row>
-    <row r="96" ht="24" customHeight="1">
-      <c r="A96" s="22" t="inlineStr">
-        <is>
-          <t>A · EINZELVERKAUF  (Reservierung über den Onlinekatalog)</t>
-        </is>
-      </c>
-      <c r="B96" s="1" t="n"/>
-      <c r="C96" s="1" t="n"/>
-      <c r="D96" s="1" t="n"/>
-      <c r="E96" s="1" t="n"/>
-      <c r="F96" s="1" t="n"/>
-      <c r="G96" s="1" t="n"/>
-      <c r="H96" s="1" t="n"/>
-      <c r="I96" s="1" t="n"/>
-      <c r="J96" s="1" t="n"/>
-      <c r="K96" s="1" t="n"/>
-      <c r="L96" s="1" t="n"/>
-      <c r="M96" s="1" t="n"/>
-    </row>
-    <row r="97" ht="22" customHeight="1">
-      <c r="A97" s="23" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller Positionen netto</t>
-        </is>
-      </c>
-      <c r="M97" s="24">
-        <f>SUM(M8:M94)</f>
-        <v/>
-      </c>
+      <c r="N95" s="16" t="n"/>
+      <c r="O95" s="17" t="n"/>
+      <c r="P95" s="18" t="n"/>
+      <c r="Q95" s="26">
+        <f>IF(N95&lt;&gt;"ja","",IF(O95="",H95,O95)*J95)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" ht="24" customHeight="1">
+      <c r="A97" s="36" t="inlineStr">
+        <is>
+          <t>A · IHRE AUSWAHL</t>
+        </is>
+      </c>
+      <c r="B97" s="1" t="n"/>
+      <c r="C97" s="1" t="n"/>
+      <c r="D97" s="1" t="n"/>
+      <c r="E97" s="1" t="n"/>
+      <c r="F97" s="1" t="n"/>
+      <c r="G97" s="1" t="n"/>
+      <c r="H97" s="1" t="n"/>
+      <c r="I97" s="1" t="n"/>
+      <c r="J97" s="1" t="n"/>
+      <c r="K97" s="1" t="n"/>
+      <c r="L97" s="1" t="n"/>
+      <c r="M97" s="1" t="n"/>
+      <c r="N97" s="1" t="n"/>
+      <c r="O97" s="1" t="n"/>
+      <c r="P97" s="1" t="n"/>
+      <c r="Q97" s="1" t="n"/>
     </row>
     <row r="98" ht="22" customHeight="1">
-      <c r="A98" s="23" t="inlineStr">
+      <c r="A98" s="37" t="inlineStr">
+        <is>
+          <t>Wert Ihrer Auswahl netto</t>
+        </is>
+      </c>
+      <c r="Q98" s="38">
+        <f>SUM(Q8:Q95)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" ht="22" customHeight="1">
+      <c r="A99" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="M98" s="24">
-        <f>M97*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99" ht="26" customHeight="1">
-      <c r="A99" s="25" t="inlineStr">
+      <c r="Q99" s="38">
+        <f>Q98*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" ht="26" customHeight="1">
+      <c r="A100" s="39" t="inlineStr">
+        <is>
+          <t>Wert Ihrer Auswahl brutto</t>
+        </is>
+      </c>
+      <c r="Q100" s="40">
+        <f>Q98+Q99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" ht="22" customHeight="1">
+      <c r="A101" s="37" t="inlineStr">
+        <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q101" s="41">
+        <f>COUNTIF(N8:N95,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="24" customHeight="1">
+      <c r="A104" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B104" s="44" t="n"/>
+      <c r="C104" s="44" t="n"/>
+      <c r="D104" s="44" t="n"/>
+      <c r="E104" s="44" t="n"/>
+      <c r="F104" s="44" t="n"/>
+      <c r="G104" s="44" t="n"/>
+      <c r="H104" s="44" t="n"/>
+      <c r="I104" s="44" t="n"/>
+      <c r="J104" s="44" t="n"/>
+      <c r="K104" s="44" t="n"/>
+      <c r="L104" s="44" t="n"/>
+      <c r="M104" s="44" t="n"/>
+      <c r="N104" s="44" t="n"/>
+      <c r="O104" s="44" t="n"/>
+      <c r="P104" s="44" t="n"/>
+      <c r="Q104" s="44" t="n"/>
+    </row>
+    <row r="105" ht="22" customHeight="1">
+      <c r="A105" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q105" s="38">
+        <f>SUMPRODUCT(H8:H95,J8:J95)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="1">
+      <c r="A106" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q106" s="38">
+        <f>Q105*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="1">
+      <c r="A107" s="45" t="inlineStr">
         <is>
           <t>Gesamtwert brutto</t>
         </is>
       </c>
-      <c r="M99" s="26">
-        <f>M97+M98</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="27" t="inlineStr">
-        <is>
-          <t>Einzelne Artikel reservieren Sie bitte im Onlinekatalog; der Wert oben ist die Summe aller hier gelisteten Positionen.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="24" customHeight="1">
-      <c r="A102" s="28" t="inlineStr">
-        <is>
-          <t>B · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B102" s="29" t="n"/>
-      <c r="C102" s="29" t="n"/>
-      <c r="D102" s="29" t="n"/>
-      <c r="E102" s="29" t="n"/>
-      <c r="F102" s="29" t="n"/>
-      <c r="G102" s="29" t="n"/>
-      <c r="H102" s="29" t="n"/>
-      <c r="I102" s="29" t="n"/>
-      <c r="J102" s="29" t="n"/>
-      <c r="K102" s="29" t="n"/>
-      <c r="L102" s="29" t="n"/>
-      <c r="M102" s="29" t="n"/>
-    </row>
-    <row r="103" ht="22" customHeight="1">
-      <c r="A103" s="23" t="inlineStr">
-        <is>
-          <t>Gesamtwert netto abzüglich Paketnachlass 20 %</t>
-        </is>
-      </c>
-      <c r="M103" s="24">
-        <f>-M97*0.2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104" ht="22" customHeight="1">
-      <c r="A104" s="30" t="inlineStr">
+      <c r="Q107" s="46">
+        <f>Q105+Q106</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" ht="24" customHeight="1">
+      <c r="A109" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B109" s="48" t="n"/>
+      <c r="C109" s="48" t="n"/>
+      <c r="D109" s="48" t="n"/>
+      <c r="E109" s="48" t="n"/>
+      <c r="F109" s="48" t="n"/>
+      <c r="G109" s="48" t="n"/>
+      <c r="H109" s="48" t="n"/>
+      <c r="I109" s="48" t="n"/>
+      <c r="J109" s="48" t="n"/>
+      <c r="K109" s="48" t="n"/>
+      <c r="L109" s="48" t="n"/>
+      <c r="M109" s="48" t="n"/>
+      <c r="N109" s="48" t="n"/>
+      <c r="O109" s="48" t="n"/>
+      <c r="P109" s="48" t="n"/>
+      <c r="Q109" s="48" t="n"/>
+    </row>
+    <row r="110" ht="22" customHeight="1">
+      <c r="A110" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
+        </is>
+      </c>
+      <c r="Q110" s="38">
+        <f>-Q105*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="45" t="inlineStr">
         <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="M104" s="31">
-        <f>M97+M103</f>
-        <v/>
-      </c>
-    </row>
-    <row r="105" ht="22" customHeight="1">
-      <c r="A105" s="23" t="inlineStr">
+      <c r="Q111" s="46">
+        <f>Q105+Q110</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112" ht="22" customHeight="1">
+      <c r="A112" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="M105" s="24">
-        <f>M104*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="106" ht="26" customHeight="1">
-      <c r="A106" s="25" t="inlineStr">
+      <c r="Q112" s="38">
+        <f>Q111*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" ht="26" customHeight="1">
+      <c r="A113" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="M106" s="26">
-        <f>M104+M105</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="27" t="inlineStr">
+      <c r="Q113" s="40">
+        <f>Q111+Q112</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="32" t="inlineStr">
-        <is>
-          <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Eine Reservierung wird erst mit unserer Bestätigung verbindlich; Reservierungen nehmen wir ausschließlich über den Onlinekatalog entgegen. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
+    <row r="116">
+      <c r="A116" s="49" t="inlineStr">
+        <is>
+          <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="110"/>
-    <row r="111"/>
-    <row r="112"/>
+    <row r="117"/>
+    <row r="118"/>
+    <row r="119"/>
   </sheetData>
-  <autoFilter ref="A7:M94"/>
-  <mergeCells count="21">
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="A99:L99"/>
-    <mergeCell ref="A100:M100"/>
+  <autoFilter ref="A7:Q95"/>
+  <mergeCells count="26">
+    <mergeCell ref="C1:Q1"/>
+    <mergeCell ref="A114:Q114"/>
+    <mergeCell ref="A106:P106"/>
+    <mergeCell ref="A100:P100"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A96:M96"/>
-    <mergeCell ref="A105:L105"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="A104:L104"/>
-    <mergeCell ref="A102:M102"/>
+    <mergeCell ref="L4:Q4"/>
+    <mergeCell ref="A112:P112"/>
+    <mergeCell ref="A111:P111"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="C1:M1"/>
-    <mergeCell ref="A97:L97"/>
-    <mergeCell ref="A106:L106"/>
-    <mergeCell ref="A107:M107"/>
-    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="A116:Q119"/>
+    <mergeCell ref="A98:P98"/>
+    <mergeCell ref="A107:P107"/>
+    <mergeCell ref="A110:P110"/>
     <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A98:L98"/>
-    <mergeCell ref="A103:L103"/>
-    <mergeCell ref="A109:M112"/>
+    <mergeCell ref="A104:Q104"/>
+    <mergeCell ref="A5:Q5"/>
+    <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="A99:P99"/>
+    <mergeCell ref="A97:Q97"/>
+    <mergeCell ref="A109:Q109"/>
+    <mergeCell ref="A105:P105"/>
     <mergeCell ref="C2:I2"/>
+    <mergeCell ref="L3:Q3"/>
+    <mergeCell ref="A101:P101"/>
+    <mergeCell ref="A102:Q102"/>
+    <mergeCell ref="A113:P113"/>
   </mergeCells>
+  <conditionalFormatting sqref="A8:Q95">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
+      <formula>$N8="ja"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="N8:N95" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+      <formula1>"ja,nein"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O8:O95" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2618,6 +2618,231 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>95</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="89" name="Image 89" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId89"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>96</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="90" name="Image 90" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId90"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>97</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="91" name="Image 91" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId91"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>98</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="92" name="Image 92" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId92"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>99</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="93" name="Image 93" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId93"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>100</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="94" name="Image 94" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId94"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>101</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="95" name="Image 95" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId95"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>102</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="96" name="Image 96" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId96"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>103</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="97" name="Image 97" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId97"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -2910,7 +3135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q119"/>
+  <dimension ref="A1:Q128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8398,261 +8623,805 @@
         <v/>
       </c>
     </row>
-    <row r="97" ht="24" customHeight="1">
-      <c r="A97" s="36" t="inlineStr">
+    <row r="96" ht="78" customHeight="1">
+      <c r="A96" s="9" t="n">
+        <v>89</v>
+      </c>
+      <c r="B96" s="10" t="inlineStr">
+        <is>
+          <t>NU01-13</t>
+        </is>
+      </c>
+      <c r="C96" s="11" t="n"/>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>Vitrine Nussbaum, vierteilig
+Wohnzimmervitrine im Barockstil, Nussbaum furniert. Vier Türen, davon zwei mit Glas und Glaseinlegeböden, geschnitzte Zierleisten, Schloss vorhanden.</t>
+        </is>
+      </c>
+      <c r="E96" s="13" t="n"/>
+      <c r="F96" s="12" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H96" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J96" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="K96" s="15">
+        <f>J96*1.19</f>
+        <v/>
+      </c>
+      <c r="L96" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M96" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N96" s="16" t="n"/>
+      <c r="O96" s="17" t="n"/>
+      <c r="P96" s="18" t="n"/>
+      <c r="Q96" s="19">
+        <f>IF(N96&lt;&gt;"ja","",IF(O96="",H96,O96)*J96)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" ht="78" customHeight="1">
+      <c r="A97" s="20" t="n">
+        <v>90</v>
+      </c>
+      <c r="B97" s="21" t="inlineStr">
+        <is>
+          <t>NU01-14</t>
+        </is>
+      </c>
+      <c r="C97" s="22" t="n"/>
+      <c r="D97" s="23" t="inlineStr">
+        <is>
+          <t>Kindergarderobe mit Sitzbank, weiß
+Schreinerarbeit aus weiß beschichteter Platte mit Multiplex-Kanten. Oben vier offene Fächer, darunter vier weiße Doppelhaken, Sitzbank mit Schuhrost aus Holzlatten.</t>
+        </is>
+      </c>
+      <c r="E97" s="13" t="n"/>
+      <c r="F97" s="23" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="G97" s="21" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H97" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I97" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J97" s="24" t="n">
+        <v>90</v>
+      </c>
+      <c r="K97" s="25">
+        <f>J97*1.19</f>
+        <v/>
+      </c>
+      <c r="L97" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M97" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N97" s="16" t="n"/>
+      <c r="O97" s="17" t="n"/>
+      <c r="P97" s="18" t="n"/>
+      <c r="Q97" s="26">
+        <f>IF(N97&lt;&gt;"ja","",IF(O97="",H97,O97)*J97)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" ht="78" customHeight="1">
+      <c r="A98" s="9" t="n">
+        <v>91</v>
+      </c>
+      <c r="B98" s="10" t="inlineStr">
+        <is>
+          <t>NU01-15</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="n"/>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>Garderobenschrank weiß mit Grafikfront
+Weiß beschichteter Schrank mit hoher Tür und Schubladen, Griffmulden ohne Beschläge. Die Fronten tragen eine schwarze Grafik (Straße mit Fahrzeugen), die sich über alle vier Schränke fortsetzt und nur zusammen ein Bild ergibt.</t>
+        </is>
+      </c>
+      <c r="E98" s="13" t="n"/>
+      <c r="F98" s="12" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H98" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I98" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J98" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="K98" s="15">
+        <f>J98*1.19</f>
+        <v/>
+      </c>
+      <c r="L98" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M98" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N98" s="16" t="n"/>
+      <c r="O98" s="17" t="n"/>
+      <c r="P98" s="18" t="n"/>
+      <c r="Q98" s="19">
+        <f>IF(N98&lt;&gt;"ja","",IF(O98="",H98,O98)*J98)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" ht="78" customHeight="1">
+      <c r="A99" s="20" t="n">
+        <v>92</v>
+      </c>
+      <c r="B99" s="35" t="inlineStr">
+        <is>
+          <t>NU01-16</t>
+        </is>
+      </c>
+      <c r="C99" s="22" t="n"/>
+      <c r="D99" s="23" t="inlineStr">
+        <is>
+          <t>Waschmaschine LG 17 kg, F11WM17VT2
+LG Vollwaschautomat, Inverter Direct Drive, TrueSteam, 17 kg Füllmenge. Modell F11WM17VT2 laut Typenschild, 2000–2250 W. Gewerblich genutzt.</t>
+        </is>
+      </c>
+      <c r="E99" s="13" t="inlineStr">
+        <is>
+          <t>99 × 70 × 77 cm (H×B×T)</t>
+        </is>
+      </c>
+      <c r="F99" s="23" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="G99" s="21" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H99" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I99" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J99" s="24" t="n">
+        <v>350</v>
+      </c>
+      <c r="K99" s="25">
+        <f>J99*1.19</f>
+        <v/>
+      </c>
+      <c r="L99" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M99" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N99" s="16" t="n"/>
+      <c r="O99" s="17" t="n"/>
+      <c r="P99" s="18" t="n"/>
+      <c r="Q99" s="26">
+        <f>IF(N99&lt;&gt;"ja","",IF(O99="",H99,O99)*J99)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" ht="78" customHeight="1">
+      <c r="A100" s="9" t="n">
+        <v>93</v>
+      </c>
+      <c r="B100" s="35" t="inlineStr">
+        <is>
+          <t>NU01-17</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="n"/>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>Wärmepumpentrockner Miele T1 Excellence, 8 kg
+Miele Wärmepumpentrockner der Reihe T1 Excellence, 8 kg. Typenschild: TEC235WP, Type HT30. Aufkleber des Elektrofachbetriebs Frommer, VS-Schwenningen.</t>
+        </is>
+      </c>
+      <c r="E100" s="13" t="n"/>
+      <c r="F100" s="12" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="G100" s="10" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H100" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J100" s="14" t="n">
+        <v>400</v>
+      </c>
+      <c r="K100" s="15">
+        <f>J100*1.19</f>
+        <v/>
+      </c>
+      <c r="L100" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M100" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N100" s="16" t="n"/>
+      <c r="O100" s="17" t="n"/>
+      <c r="P100" s="18" t="n"/>
+      <c r="Q100" s="19">
+        <f>IF(N100&lt;&gt;"ja","",IF(O100="",H100,O100)*J100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" ht="78" customHeight="1">
+      <c r="A101" s="20" t="n">
+        <v>94</v>
+      </c>
+      <c r="B101" s="21" t="inlineStr">
+        <is>
+          <t>NU01-18</t>
+        </is>
+      </c>
+      <c r="C101" s="22" t="n"/>
+      <c r="D101" s="23" t="inlineStr">
+        <is>
+          <t>Waschmaschine Candy RapidÓ, 9 kg
+Candy RapidÓ, 9 kg, 1400 Touren, Speed-Drive-Inverter, Simply-Fi (App-Anbindung), Kg Detector. Modell RO14960WMC5/1-S laut Typenschild, 1600 W.</t>
+        </is>
+      </c>
+      <c r="E101" s="13" t="n"/>
+      <c r="F101" s="23" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="G101" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H101" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J101" s="24" t="n">
+        <v>140</v>
+      </c>
+      <c r="K101" s="25">
+        <f>J101*1.19</f>
+        <v/>
+      </c>
+      <c r="L101" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M101" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N101" s="16" t="n"/>
+      <c r="O101" s="17" t="n"/>
+      <c r="P101" s="18" t="n"/>
+      <c r="Q101" s="26">
+        <f>IF(N101&lt;&gt;"ja","",IF(O101="",H101,O101)*J101)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" ht="78" customHeight="1">
+      <c r="A102" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="B102" s="10" t="inlineStr">
+        <is>
+          <t>NU01-19</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="n"/>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>Kindergarderobe mit Hakenleiste und Wannen, weiß
+Weißes Wandelement mit vier offenen Fächern und darin liegenden Kunststoffwannen, darunter vier rote Doppelhaken. Davor eine weiße Sitzbank aus Holz mit Schublade.</t>
+        </is>
+      </c>
+      <c r="E102" s="13" t="n"/>
+      <c r="F102" s="12" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="G102" s="10" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H102" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I102" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J102" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="K102" s="15">
+        <f>J102*1.19</f>
+        <v/>
+      </c>
+      <c r="L102" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M102" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N102" s="16" t="n"/>
+      <c r="O102" s="17" t="n"/>
+      <c r="P102" s="18" t="n"/>
+      <c r="Q102" s="19">
+        <f>IF(N102&lt;&gt;"ja","",IF(O102="",H102,O102)*J102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103" ht="78" customHeight="1">
+      <c r="A103" s="20" t="n">
+        <v>96</v>
+      </c>
+      <c r="B103" s="21" t="inlineStr">
+        <is>
+          <t>NU01-20</t>
+        </is>
+      </c>
+      <c r="C103" s="22" t="n"/>
+      <c r="D103" s="23" t="inlineStr">
+        <is>
+          <t>Clubsessel rot, Kunstleder
+Runder Clubsessel in Tonnenform, roter Kunstlederbezug, niedrige Sitzhöhe – im Haus als Kindersessel genutzt. Gebrauchsspuren an Kanten und Sitzfläche, kleine Risse im Bezug.</t>
+        </is>
+      </c>
+      <c r="E103" s="13" t="n"/>
+      <c r="F103" s="23" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="G103" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H103" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I103" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J103" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="K103" s="25">
+        <f>J103*1.19</f>
+        <v/>
+      </c>
+      <c r="L103" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M103" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N103" s="16" t="n"/>
+      <c r="O103" s="17" t="n"/>
+      <c r="P103" s="18" t="n"/>
+      <c r="Q103" s="26">
+        <f>IF(N103&lt;&gt;"ja","",IF(O103="",H103,O103)*J103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" ht="78" customHeight="1">
+      <c r="A104" s="9" t="n">
+        <v>97</v>
+      </c>
+      <c r="B104" s="35" t="inlineStr">
+        <is>
+          <t>NU01-21</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="n"/>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>Leuchte Mr Maria „Miffy“, groß und klein
+Zwei Leuchten in Hasenform von Mr Maria (Amsterdam), Motiv Miffy, weißer Kunststoff, LED, Anschluss über Netzteil mit USB. Typenschild: MR LED8. Ein großes und ein kleines Exemplar.</t>
+        </is>
+      </c>
+      <c r="E104" s="13" t="n"/>
+      <c r="F104" s="12" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="G104" s="10" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H104" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I104" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J104" s="14" t="n">
+        <v>95</v>
+      </c>
+      <c r="K104" s="15">
+        <f>J104*1.19</f>
+        <v/>
+      </c>
+      <c r="L104" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M104" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N104" s="16" t="n"/>
+      <c r="O104" s="17" t="n"/>
+      <c r="P104" s="18" t="n"/>
+      <c r="Q104" s="19">
+        <f>IF(N104&lt;&gt;"ja","",IF(O104="",H104,O104)*J104)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" ht="24" customHeight="1">
+      <c r="A106" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B97" s="1" t="n"/>
-      <c r="C97" s="1" t="n"/>
-      <c r="D97" s="1" t="n"/>
-      <c r="E97" s="1" t="n"/>
-      <c r="F97" s="1" t="n"/>
-      <c r="G97" s="1" t="n"/>
-      <c r="H97" s="1" t="n"/>
-      <c r="I97" s="1" t="n"/>
-      <c r="J97" s="1" t="n"/>
-      <c r="K97" s="1" t="n"/>
-      <c r="L97" s="1" t="n"/>
-      <c r="M97" s="1" t="n"/>
-      <c r="N97" s="1" t="n"/>
-      <c r="O97" s="1" t="n"/>
-      <c r="P97" s="1" t="n"/>
-      <c r="Q97" s="1" t="n"/>
-    </row>
-    <row r="98" ht="22" customHeight="1">
-      <c r="A98" s="37" t="inlineStr">
+      <c r="B106" s="1" t="n"/>
+      <c r="C106" s="1" t="n"/>
+      <c r="D106" s="1" t="n"/>
+      <c r="E106" s="1" t="n"/>
+      <c r="F106" s="1" t="n"/>
+      <c r="G106" s="1" t="n"/>
+      <c r="H106" s="1" t="n"/>
+      <c r="I106" s="1" t="n"/>
+      <c r="J106" s="1" t="n"/>
+      <c r="K106" s="1" t="n"/>
+      <c r="L106" s="1" t="n"/>
+      <c r="M106" s="1" t="n"/>
+      <c r="N106" s="1" t="n"/>
+      <c r="O106" s="1" t="n"/>
+      <c r="P106" s="1" t="n"/>
+      <c r="Q106" s="1" t="n"/>
+    </row>
+    <row r="107" ht="22" customHeight="1">
+      <c r="A107" s="37" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl netto</t>
         </is>
       </c>
-      <c r="Q98" s="38">
-        <f>SUM(Q8:Q95)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="99" ht="22" customHeight="1">
-      <c r="A99" s="37" t="inlineStr">
+      <c r="Q107" s="38">
+        <f>SUM(Q8:Q104)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="1">
+      <c r="A108" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q99" s="38">
-        <f>Q98*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="100" ht="26" customHeight="1">
-      <c r="A100" s="39" t="inlineStr">
+      <c r="Q108" s="38">
+        <f>Q107*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" ht="26" customHeight="1">
+      <c r="A109" s="39" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl brutto</t>
         </is>
       </c>
-      <c r="Q100" s="40">
-        <f>Q98+Q99</f>
-        <v/>
-      </c>
-    </row>
-    <row r="101" ht="22" customHeight="1">
-      <c r="A101" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q101" s="41">
-        <f>COUNTIF(N8:N95,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="24" customHeight="1">
-      <c r="A104" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B104" s="44" t="n"/>
-      <c r="C104" s="44" t="n"/>
-      <c r="D104" s="44" t="n"/>
-      <c r="E104" s="44" t="n"/>
-      <c r="F104" s="44" t="n"/>
-      <c r="G104" s="44" t="n"/>
-      <c r="H104" s="44" t="n"/>
-      <c r="I104" s="44" t="n"/>
-      <c r="J104" s="44" t="n"/>
-      <c r="K104" s="44" t="n"/>
-      <c r="L104" s="44" t="n"/>
-      <c r="M104" s="44" t="n"/>
-      <c r="N104" s="44" t="n"/>
-      <c r="O104" s="44" t="n"/>
-      <c r="P104" s="44" t="n"/>
-      <c r="Q104" s="44" t="n"/>
-    </row>
-    <row r="105" ht="22" customHeight="1">
-      <c r="A105" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
-        </is>
-      </c>
-      <c r="Q105" s="38">
-        <f>SUMPRODUCT(H8:H95,J8:J95)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="106" ht="22" customHeight="1">
-      <c r="A106" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q106" s="38">
-        <f>Q105*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="107" ht="22" customHeight="1">
-      <c r="A107" s="45" t="inlineStr">
-        <is>
-          <t>Gesamtwert brutto</t>
-        </is>
-      </c>
-      <c r="Q107" s="46">
-        <f>Q105+Q106</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109" ht="24" customHeight="1">
-      <c r="A109" s="47" t="inlineStr">
-        <is>
-          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B109" s="48" t="n"/>
-      <c r="C109" s="48" t="n"/>
-      <c r="D109" s="48" t="n"/>
-      <c r="E109" s="48" t="n"/>
-      <c r="F109" s="48" t="n"/>
-      <c r="G109" s="48" t="n"/>
-      <c r="H109" s="48" t="n"/>
-      <c r="I109" s="48" t="n"/>
-      <c r="J109" s="48" t="n"/>
-      <c r="K109" s="48" t="n"/>
-      <c r="L109" s="48" t="n"/>
-      <c r="M109" s="48" t="n"/>
-      <c r="N109" s="48" t="n"/>
-      <c r="O109" s="48" t="n"/>
-      <c r="P109" s="48" t="n"/>
-      <c r="Q109" s="48" t="n"/>
+      <c r="Q109" s="40">
+        <f>Q107+Q108</f>
+        <v/>
+      </c>
     </row>
     <row r="110" ht="22" customHeight="1">
       <c r="A110" s="37" t="inlineStr">
         <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q110" s="41">
+        <f>COUNTIF(N8:N104,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="24" customHeight="1">
+      <c r="A113" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B113" s="44" t="n"/>
+      <c r="C113" s="44" t="n"/>
+      <c r="D113" s="44" t="n"/>
+      <c r="E113" s="44" t="n"/>
+      <c r="F113" s="44" t="n"/>
+      <c r="G113" s="44" t="n"/>
+      <c r="H113" s="44" t="n"/>
+      <c r="I113" s="44" t="n"/>
+      <c r="J113" s="44" t="n"/>
+      <c r="K113" s="44" t="n"/>
+      <c r="L113" s="44" t="n"/>
+      <c r="M113" s="44" t="n"/>
+      <c r="N113" s="44" t="n"/>
+      <c r="O113" s="44" t="n"/>
+      <c r="P113" s="44" t="n"/>
+      <c r="Q113" s="44" t="n"/>
+    </row>
+    <row r="114" ht="22" customHeight="1">
+      <c r="A114" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q114" s="38">
+        <f>SUMPRODUCT(H8:H104,J8:J104)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" ht="22" customHeight="1">
+      <c r="A115" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q115" s="38">
+        <f>Q114*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" ht="22" customHeight="1">
+      <c r="A116" s="45" t="inlineStr">
+        <is>
+          <t>Gesamtwert brutto</t>
+        </is>
+      </c>
+      <c r="Q116" s="46">
+        <f>Q114+Q115</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" ht="24" customHeight="1">
+      <c r="A118" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B118" s="48" t="n"/>
+      <c r="C118" s="48" t="n"/>
+      <c r="D118" s="48" t="n"/>
+      <c r="E118" s="48" t="n"/>
+      <c r="F118" s="48" t="n"/>
+      <c r="G118" s="48" t="n"/>
+      <c r="H118" s="48" t="n"/>
+      <c r="I118" s="48" t="n"/>
+      <c r="J118" s="48" t="n"/>
+      <c r="K118" s="48" t="n"/>
+      <c r="L118" s="48" t="n"/>
+      <c r="M118" s="48" t="n"/>
+      <c r="N118" s="48" t="n"/>
+      <c r="O118" s="48" t="n"/>
+      <c r="P118" s="48" t="n"/>
+      <c r="Q118" s="48" t="n"/>
+    </row>
+    <row r="119" ht="22" customHeight="1">
+      <c r="A119" s="37" t="inlineStr">
+        <is>
           <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
         </is>
       </c>
-      <c r="Q110" s="38">
-        <f>-Q105*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111" ht="22" customHeight="1">
-      <c r="A111" s="45" t="inlineStr">
+      <c r="Q119" s="38">
+        <f>-Q114*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120" ht="22" customHeight="1">
+      <c r="A120" s="45" t="inlineStr">
         <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="Q111" s="46">
-        <f>Q105+Q110</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112" ht="22" customHeight="1">
-      <c r="A112" s="37" t="inlineStr">
+      <c r="Q120" s="46">
+        <f>Q114+Q119</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" ht="22" customHeight="1">
+      <c r="A121" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q112" s="38">
-        <f>Q111*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113" ht="26" customHeight="1">
-      <c r="A113" s="39" t="inlineStr">
+      <c r="Q121" s="38">
+        <f>Q120*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" ht="26" customHeight="1">
+      <c r="A122" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q113" s="40">
-        <f>Q111+Q112</f>
-        <v/>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="42" t="inlineStr">
+      <c r="Q122" s="40">
+        <f>Q120+Q121</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="49" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="117"/>
-    <row r="118"/>
-    <row r="119"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128"/>
   </sheetData>
-  <autoFilter ref="A7:Q95"/>
+  <autoFilter ref="A7:Q104"/>
   <mergeCells count="26">
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A114:Q114"/>
-    <mergeCell ref="A106:P106"/>
-    <mergeCell ref="A100:P100"/>
+    <mergeCell ref="A116:P116"/>
+    <mergeCell ref="A122:P122"/>
+    <mergeCell ref="A109:P109"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="L4:Q4"/>
-    <mergeCell ref="A112:P112"/>
-    <mergeCell ref="A111:P111"/>
+    <mergeCell ref="A123:Q123"/>
+    <mergeCell ref="A121:P121"/>
+    <mergeCell ref="A115:P115"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A116:Q119"/>
-    <mergeCell ref="A98:P98"/>
+    <mergeCell ref="A114:P114"/>
+    <mergeCell ref="A125:Q128"/>
+    <mergeCell ref="A118:Q118"/>
     <mergeCell ref="A107:P107"/>
     <mergeCell ref="A110:P110"/>
     <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A104:Q104"/>
+    <mergeCell ref="A113:Q113"/>
+    <mergeCell ref="A119:P119"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A99:P99"/>
-    <mergeCell ref="A97:Q97"/>
-    <mergeCell ref="A109:Q109"/>
-    <mergeCell ref="A105:P105"/>
+    <mergeCell ref="A108:P108"/>
+    <mergeCell ref="A106:Q106"/>
+    <mergeCell ref="A120:P120"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A101:P101"/>
-    <mergeCell ref="A102:Q102"/>
-    <mergeCell ref="A113:P113"/>
+    <mergeCell ref="A111:Q111"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q95">
+  <conditionalFormatting sqref="A8:Q104">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N95" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N104" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O95" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O104" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$105</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -2147,17 +2147,42 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
+      <row>75</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="70" name="Image 70" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
       <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="70" name="Image 70" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
+        <cNvPr id="71" name="Image 71" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId71"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2178,11 +2203,11 @@
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="71" name="Image 71" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId71"/>
+        <cNvPr id="72" name="Image 72" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId72"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2203,11 +2228,11 @@
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="72" name="Image 72" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId72"/>
+        <cNvPr id="73" name="Image 73" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId73"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2228,11 +2253,11 @@
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="73" name="Image 73" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId73"/>
+        <cNvPr id="74" name="Image 74" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2253,11 +2278,11 @@
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="74" name="Image 74" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
+        <cNvPr id="75" name="Image 75" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2278,11 +2303,11 @@
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="75" name="Image 75" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
+        <cNvPr id="76" name="Image 76" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId76"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2303,11 +2328,11 @@
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="76" name="Image 76" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId76"/>
+        <cNvPr id="77" name="Image 77" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId77"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2328,11 +2353,11 @@
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="77" name="Image 77" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId77"/>
+        <cNvPr id="78" name="Image 78" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2353,11 +2378,11 @@
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="78" name="Image 78" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
+        <cNvPr id="79" name="Image 79" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId79"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2378,11 +2403,11 @@
     <ext cx="1257300" cy="619125"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="79" name="Image 79" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId79"/>
+        <cNvPr id="80" name="Image 80" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId80"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2403,11 +2428,11 @@
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="80" name="Image 80" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId80"/>
+        <cNvPr id="81" name="Image 81" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId81"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2428,11 +2453,11 @@
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="81" name="Image 81" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId81"/>
+        <cNvPr id="82" name="Image 82" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId82"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2453,11 +2478,11 @@
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="82" name="Image 82" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId82"/>
+        <cNvPr id="83" name="Image 83" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId83"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2478,11 +2503,11 @@
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="83" name="Image 83" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId83"/>
+        <cNvPr id="84" name="Image 84" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId84"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2503,11 +2528,11 @@
     <ext cx="885825" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="84" name="Image 84" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId84"/>
+        <cNvPr id="85" name="Image 85" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId85"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2528,11 +2553,11 @@
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="85" name="Image 85" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId85"/>
+        <cNvPr id="86" name="Image 86" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId86"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2553,11 +2578,11 @@
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="86" name="Image 86" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId86"/>
+        <cNvPr id="87" name="Image 87" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId87"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2578,11 +2603,11 @@
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="87" name="Image 87" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId87"/>
+        <cNvPr id="88" name="Image 88" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId88"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2603,11 +2628,11 @@
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="88" name="Image 88" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId88"/>
+        <cNvPr id="89" name="Image 89" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId89"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2628,11 +2653,11 @@
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="89" name="Image 89" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId89"/>
+        <cNvPr id="90" name="Image 90" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId90"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2653,11 +2678,11 @@
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="90" name="Image 90" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId90"/>
+        <cNvPr id="91" name="Image 91" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId91"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2678,11 +2703,11 @@
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="91" name="Image 91" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId91"/>
+        <cNvPr id="92" name="Image 92" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId92"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2703,11 +2728,11 @@
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="92" name="Image 92" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId92"/>
+        <cNvPr id="93" name="Image 93" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId93"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2728,11 +2753,11 @@
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="93" name="Image 93" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId93"/>
+        <cNvPr id="94" name="Image 94" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId94"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2753,11 +2778,11 @@
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="94" name="Image 94" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId94"/>
+        <cNvPr id="95" name="Image 95" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId95"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2778,11 +2803,11 @@
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="95" name="Image 95" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId95"/>
+        <cNvPr id="96" name="Image 96" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId96"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2803,11 +2828,11 @@
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="96" name="Image 96" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId96"/>
+        <cNvPr id="97" name="Image 97" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId97"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2828,11 +2853,36 @@
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="97" name="Image 97" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId97"/>
+        <cNvPr id="98" name="Image 98" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId98"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>104</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="99" name="Image 99" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId99"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3135,7 +3185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q128"/>
+  <dimension ref="A1:Q129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3249,7 +3299,7 @@
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>So geht's:  Tragen Sie in den drei grau hinterlegten Spalten rechts ein, woran Sie Interesse haben. „Interesse = ja" genügt; lassen Sie die Stückzahl leer, zählt die volle verfügbare Menge. Der Wert Ihrer Auswahl rechnet sich unten automatisch. Rot markierte Artikelnummern sind Marken- und Designstücke. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung — wir stimmen die Mengen anschließend gemeinsam ab. Abholung nach Terminvereinbarung, Zahlung per Rechnung. Möchten Sie den gesamten Bestand übernehmen, finden Sie am Ende ein Paketangebot mit 15 % Nachlass.</t>
+          <t>So geht's:  Tragen Sie in den drei grau hinterlegten Spalten rechts ein, woran Sie Interesse haben. „Interesse = ja" genügt; lassen Sie die Stückzahl leer, zählt die volle verfügbare Menge. Der Wert Ihrer Auswahl rechnet sich unten automatisch. Rot markierte Artikelnummern sind Markenware oder Designstücke. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung — wir stimmen die Mengen anschließend gemeinsam ab. Abholung nach Terminvereinbarung, Zahlung per Rechnung. Möchten Sie den gesamten Bestand übernehmen, finden Sie am Ende ein Paketangebot mit 15 % Nachlass.</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3426,7 @@
         </is>
       </c>
       <c r="J8" s="14" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K8" s="15">
         <f>J8*1.19</f>
@@ -6798,7 +6848,7 @@
         </is>
       </c>
       <c r="J65" s="24" t="n">
-        <v>1200</v>
+        <v>1600</v>
       </c>
       <c r="K65" s="25">
         <f>J65*1.19</f>
@@ -7435,7 +7485,7 @@
       <c r="D76" s="12" t="inlineStr">
         <is>
           <t>Läufer dunkelgrau, IKEA Morum
-IKEA Morum, Flachgewebe dunkelgrau, für innen und außen geeignet, schmaler Läufer – 15 Stück verfügbar</t>
+Flachgewebter Läufer in Dunkelgrau, IKEA Morum (In-/Outdoor-Qualität), strukturierte Webung. 15 gleiche Läufer aus den Fluren.</t>
         </is>
       </c>
       <c r="E76" s="13" t="n"/>
@@ -7458,7 +7508,7 @@
         </is>
       </c>
       <c r="J76" s="14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K76" s="15">
         <f>J76*1.19</f>
@@ -9000,7 +9050,7 @@
       <c r="D102" s="12" t="inlineStr">
         <is>
           <t>Kindergarderobe mit Hakenleiste und Wannen, weiß
-Weißes Wandelement mit vier offenen Fächern und darin liegenden Kunststoffwannen, darunter vier rote Doppelhaken. Davor eine weiße Sitzbank aus Holz mit Schublade.</t>
+Zweiteilige Kindergarderobe: oben ein Wandelement mit vier offenen Fächern und darin liegenden Kunststoffwannen sowie vier roten Doppelhaken, unten eine weiße Sitzbank aus Holz mit Schublade. Beide Teile gehören zusammen.</t>
         </is>
       </c>
       <c r="E102" s="13" t="n"/>
@@ -9023,7 +9073,7 @@
         </is>
       </c>
       <c r="J102" s="14" t="n">
-        <v>70</v>
+        <v>110</v>
       </c>
       <c r="K102" s="15">
         <f>J102*1.19</f>
@@ -9119,8 +9169,8 @@
       <c r="C104" s="11" t="n"/>
       <c r="D104" s="12" t="inlineStr">
         <is>
-          <t>Leuchte Mr Maria „Miffy“, groß und klein
-Zwei Leuchten in Hasenform von Mr Maria (Amsterdam), Motiv Miffy, weißer Kunststoff, LED, Anschluss über Netzteil mit USB. Typenschild: MR LED8. Ein großes und ein kleines Exemplar.</t>
+          <t>Leuchte Mr Maria „Miffy", groß
+Steh-/Tischleuchte in Hasenform von Mr Maria (Amsterdam), Motiv Miffy, weißer Kunststoff, LED, Anschluss über Netzteil mit USB. Typenschild: MR LED8. Das größere der beiden Exemplare.</t>
         </is>
       </c>
       <c r="E104" s="13" t="n"/>
@@ -9135,7 +9185,7 @@
         </is>
       </c>
       <c r="H104" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I104" s="10" t="inlineStr">
         <is>
@@ -9143,7 +9193,7 @@
         </is>
       </c>
       <c r="J104" s="14" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="K104" s="15">
         <f>J104*1.19</f>
@@ -9167,261 +9217,321 @@
         <v/>
       </c>
     </row>
-    <row r="106" ht="24" customHeight="1">
-      <c r="A106" s="36" t="inlineStr">
+    <row r="105" ht="78" customHeight="1">
+      <c r="A105" s="20" t="n">
+        <v>98</v>
+      </c>
+      <c r="B105" s="35" t="inlineStr">
+        <is>
+          <t>NU01-22</t>
+        </is>
+      </c>
+      <c r="C105" s="22" t="n"/>
+      <c r="D105" s="23" t="inlineStr">
+        <is>
+          <t>Leuchte Mr Maria „Miffy", klein
+Tischleuchte in Hasenform von Mr Maria (Amsterdam), Motiv Miffy, weißer Kunststoff, LED, Anschluss über Netzteil mit USB. Das kleinere der beiden Exemplare.</t>
+        </is>
+      </c>
+      <c r="E105" s="13" t="n"/>
+      <c r="F105" s="23" t="inlineStr">
+        <is>
+          <t>Flur</t>
+        </is>
+      </c>
+      <c r="G105" s="21" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H105" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I105" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J105" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="K105" s="25">
+        <f>J105*1.19</f>
+        <v/>
+      </c>
+      <c r="L105" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M105" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N105" s="16" t="n"/>
+      <c r="O105" s="17" t="n"/>
+      <c r="P105" s="18" t="n"/>
+      <c r="Q105" s="26">
+        <f>IF(N105&lt;&gt;"ja","",IF(O105="",H105,O105)*J105)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" ht="24" customHeight="1">
+      <c r="A107" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B106" s="1" t="n"/>
-      <c r="C106" s="1" t="n"/>
-      <c r="D106" s="1" t="n"/>
-      <c r="E106" s="1" t="n"/>
-      <c r="F106" s="1" t="n"/>
-      <c r="G106" s="1" t="n"/>
-      <c r="H106" s="1" t="n"/>
-      <c r="I106" s="1" t="n"/>
-      <c r="J106" s="1" t="n"/>
-      <c r="K106" s="1" t="n"/>
-      <c r="L106" s="1" t="n"/>
-      <c r="M106" s="1" t="n"/>
-      <c r="N106" s="1" t="n"/>
-      <c r="O106" s="1" t="n"/>
-      <c r="P106" s="1" t="n"/>
-      <c r="Q106" s="1" t="n"/>
-    </row>
-    <row r="107" ht="22" customHeight="1">
-      <c r="A107" s="37" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl netto</t>
-        </is>
-      </c>
-      <c r="Q107" s="38">
-        <f>SUM(Q8:Q104)</f>
-        <v/>
-      </c>
+      <c r="B107" s="1" t="n"/>
+      <c r="C107" s="1" t="n"/>
+      <c r="D107" s="1" t="n"/>
+      <c r="E107" s="1" t="n"/>
+      <c r="F107" s="1" t="n"/>
+      <c r="G107" s="1" t="n"/>
+      <c r="H107" s="1" t="n"/>
+      <c r="I107" s="1" t="n"/>
+      <c r="J107" s="1" t="n"/>
+      <c r="K107" s="1" t="n"/>
+      <c r="L107" s="1" t="n"/>
+      <c r="M107" s="1" t="n"/>
+      <c r="N107" s="1" t="n"/>
+      <c r="O107" s="1" t="n"/>
+      <c r="P107" s="1" t="n"/>
+      <c r="Q107" s="1" t="n"/>
     </row>
     <row r="108" ht="22" customHeight="1">
       <c r="A108" s="37" t="inlineStr">
         <is>
+          <t>Wert Ihrer Auswahl netto</t>
+        </is>
+      </c>
+      <c r="Q108" s="38">
+        <f>SUM(Q8:Q105)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" ht="22" customHeight="1">
+      <c r="A109" s="37" t="inlineStr">
+        <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q108" s="38">
-        <f>Q107*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109" ht="26" customHeight="1">
-      <c r="A109" s="39" t="inlineStr">
+      <c r="Q109" s="38">
+        <f>Q108*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" ht="26" customHeight="1">
+      <c r="A110" s="39" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl brutto</t>
         </is>
       </c>
-      <c r="Q109" s="40">
-        <f>Q107+Q108</f>
-        <v/>
-      </c>
-    </row>
-    <row r="110" ht="22" customHeight="1">
-      <c r="A110" s="37" t="inlineStr">
+      <c r="Q110" s="40">
+        <f>Q108+Q109</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="37" t="inlineStr">
         <is>
           <t>gewählte Positionen</t>
         </is>
       </c>
-      <c r="Q110" s="41">
-        <f>COUNTIF(N8:N104,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="42" t="inlineStr">
+      <c r="Q111" s="41">
+        <f>COUNTIF(N8:N105,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="42" t="inlineStr">
         <is>
           <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
         </is>
       </c>
     </row>
-    <row r="113" ht="24" customHeight="1">
-      <c r="A113" s="43" t="inlineStr">
+    <row r="114" ht="24" customHeight="1">
+      <c r="A114" s="43" t="inlineStr">
         <is>
           <t>B · GESAMTBESTAND</t>
         </is>
       </c>
-      <c r="B113" s="44" t="n"/>
-      <c r="C113" s="44" t="n"/>
-      <c r="D113" s="44" t="n"/>
-      <c r="E113" s="44" t="n"/>
-      <c r="F113" s="44" t="n"/>
-      <c r="G113" s="44" t="n"/>
-      <c r="H113" s="44" t="n"/>
-      <c r="I113" s="44" t="n"/>
-      <c r="J113" s="44" t="n"/>
-      <c r="K113" s="44" t="n"/>
-      <c r="L113" s="44" t="n"/>
-      <c r="M113" s="44" t="n"/>
-      <c r="N113" s="44" t="n"/>
-      <c r="O113" s="44" t="n"/>
-      <c r="P113" s="44" t="n"/>
-      <c r="Q113" s="44" t="n"/>
-    </row>
-    <row r="114" ht="22" customHeight="1">
-      <c r="A114" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
-        </is>
-      </c>
-      <c r="Q114" s="38">
-        <f>SUMPRODUCT(H8:H104,J8:J104)</f>
-        <v/>
-      </c>
+      <c r="B114" s="44" t="n"/>
+      <c r="C114" s="44" t="n"/>
+      <c r="D114" s="44" t="n"/>
+      <c r="E114" s="44" t="n"/>
+      <c r="F114" s="44" t="n"/>
+      <c r="G114" s="44" t="n"/>
+      <c r="H114" s="44" t="n"/>
+      <c r="I114" s="44" t="n"/>
+      <c r="J114" s="44" t="n"/>
+      <c r="K114" s="44" t="n"/>
+      <c r="L114" s="44" t="n"/>
+      <c r="M114" s="44" t="n"/>
+      <c r="N114" s="44" t="n"/>
+      <c r="O114" s="44" t="n"/>
+      <c r="P114" s="44" t="n"/>
+      <c r="Q114" s="44" t="n"/>
     </row>
     <row r="115" ht="22" customHeight="1">
       <c r="A115" s="37" t="inlineStr">
         <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q115" s="38">
+        <f>SUMPRODUCT(H8:H105,J8:J105)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" ht="22" customHeight="1">
+      <c r="A116" s="37" t="inlineStr">
+        <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q115" s="38">
-        <f>Q114*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116" ht="22" customHeight="1">
-      <c r="A116" s="45" t="inlineStr">
+      <c r="Q116" s="38">
+        <f>Q115*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" ht="22" customHeight="1">
+      <c r="A117" s="45" t="inlineStr">
         <is>
           <t>Gesamtwert brutto</t>
         </is>
       </c>
-      <c r="Q116" s="46">
-        <f>Q114+Q115</f>
-        <v/>
-      </c>
-    </row>
-    <row r="118" ht="24" customHeight="1">
-      <c r="A118" s="47" t="inlineStr">
+      <c r="Q117" s="46">
+        <f>Q115+Q116</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" ht="24" customHeight="1">
+      <c r="A119" s="47" t="inlineStr">
         <is>
           <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
         </is>
       </c>
-      <c r="B118" s="48" t="n"/>
-      <c r="C118" s="48" t="n"/>
-      <c r="D118" s="48" t="n"/>
-      <c r="E118" s="48" t="n"/>
-      <c r="F118" s="48" t="n"/>
-      <c r="G118" s="48" t="n"/>
-      <c r="H118" s="48" t="n"/>
-      <c r="I118" s="48" t="n"/>
-      <c r="J118" s="48" t="n"/>
-      <c r="K118" s="48" t="n"/>
-      <c r="L118" s="48" t="n"/>
-      <c r="M118" s="48" t="n"/>
-      <c r="N118" s="48" t="n"/>
-      <c r="O118" s="48" t="n"/>
-      <c r="P118" s="48" t="n"/>
-      <c r="Q118" s="48" t="n"/>
-    </row>
-    <row r="119" ht="22" customHeight="1">
-      <c r="A119" s="37" t="inlineStr">
+      <c r="B119" s="48" t="n"/>
+      <c r="C119" s="48" t="n"/>
+      <c r="D119" s="48" t="n"/>
+      <c r="E119" s="48" t="n"/>
+      <c r="F119" s="48" t="n"/>
+      <c r="G119" s="48" t="n"/>
+      <c r="H119" s="48" t="n"/>
+      <c r="I119" s="48" t="n"/>
+      <c r="J119" s="48" t="n"/>
+      <c r="K119" s="48" t="n"/>
+      <c r="L119" s="48" t="n"/>
+      <c r="M119" s="48" t="n"/>
+      <c r="N119" s="48" t="n"/>
+      <c r="O119" s="48" t="n"/>
+      <c r="P119" s="48" t="n"/>
+      <c r="Q119" s="48" t="n"/>
+    </row>
+    <row r="120" ht="22" customHeight="1">
+      <c r="A120" s="37" t="inlineStr">
         <is>
           <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
         </is>
       </c>
-      <c r="Q119" s="38">
-        <f>-Q114*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="120" ht="22" customHeight="1">
-      <c r="A120" s="45" t="inlineStr">
+      <c r="Q120" s="38">
+        <f>-Q115*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" ht="22" customHeight="1">
+      <c r="A121" s="45" t="inlineStr">
         <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="Q120" s="46">
-        <f>Q114+Q119</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121" ht="22" customHeight="1">
-      <c r="A121" s="37" t="inlineStr">
+      <c r="Q121" s="46">
+        <f>Q115+Q120</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" ht="22" customHeight="1">
+      <c r="A122" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q121" s="38">
-        <f>Q120*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122" ht="26" customHeight="1">
-      <c r="A122" s="39" t="inlineStr">
+      <c r="Q122" s="38">
+        <f>Q121*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" ht="26" customHeight="1">
+      <c r="A123" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q122" s="40">
-        <f>Q120+Q121</f>
-        <v/>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="42" t="inlineStr">
+      <c r="Q123" s="40">
+        <f>Q121+Q122</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="49" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="126"/>
     <row r="127"/>
     <row r="128"/>
+    <row r="129"/>
   </sheetData>
-  <autoFilter ref="A7:Q104"/>
+  <autoFilter ref="A7:Q105"/>
   <mergeCells count="26">
     <mergeCell ref="C1:Q1"/>
     <mergeCell ref="A116:P116"/>
+    <mergeCell ref="A114:Q114"/>
     <mergeCell ref="A122:P122"/>
     <mergeCell ref="A109:P109"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A107:Q107"/>
     <mergeCell ref="L4:Q4"/>
-    <mergeCell ref="A123:Q123"/>
     <mergeCell ref="A121:P121"/>
+    <mergeCell ref="A119:Q119"/>
     <mergeCell ref="A115:P115"/>
+    <mergeCell ref="A117:P117"/>
+    <mergeCell ref="A111:P111"/>
+    <mergeCell ref="A126:Q129"/>
+    <mergeCell ref="A124:Q124"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A114:P114"/>
-    <mergeCell ref="A125:Q128"/>
-    <mergeCell ref="A118:Q118"/>
-    <mergeCell ref="A107:P107"/>
+    <mergeCell ref="A123:P123"/>
     <mergeCell ref="A110:P110"/>
     <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A113:Q113"/>
-    <mergeCell ref="A119:P119"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
     <mergeCell ref="A108:P108"/>
-    <mergeCell ref="A106:Q106"/>
     <mergeCell ref="A120:P120"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A111:Q111"/>
+    <mergeCell ref="A112:Q112"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q104">
+  <conditionalFormatting sqref="A8:Q105">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N104" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O104" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -3414,7 +3414,7 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>stark gebraucht</t>
         </is>
       </c>
       <c r="H8" s="10" t="n">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="J8" s="14" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K8" s="15">
         <f>J8*1.19</f>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -4134,7 +4134,7 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H20" s="10" t="n">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="G21" s="21" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H21" s="21" t="n">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H22" s="10" t="n">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="G23" s="21" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H23" s="21" t="n">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H24" s="10" t="n">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="G25" s="21" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H25" s="21" t="n">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H30" s="10" t="n">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="G31" s="21" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H31" s="21" t="n">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H32" s="10" t="n">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H40" s="10" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H44" s="10" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H62" s="10" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="G63" s="21" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H63" s="21" t="n">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="G65" s="21" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H65" s="21" t="n">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="G77" s="21" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H77" s="21" t="n">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H78" s="10" t="n">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="G81" s="21" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H81" s="21" t="n">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H82" s="10" t="n">
@@ -8757,7 +8757,7 @@
       </c>
       <c r="G97" s="21" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H97" s="21" t="n">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H98" s="10" t="n">
@@ -9061,7 +9061,7 @@
       </c>
       <c r="G102" s="10" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H102" s="10" t="n">
@@ -9230,7 +9230,7 @@
       <c r="D105" s="23" t="inlineStr">
         <is>
           <t>Leuchte Mr Maria „Miffy", klein
-Tischleuchte in Hasenform von Mr Maria (Amsterdam), Motiv Miffy, weißer Kunststoff, LED, Anschluss über Netzteil mit USB. Das kleinere der beiden Exemplare.</t>
+Tischleuchte in Hasenform von Mr Maria (Amsterdam), Motiv Miffy, weißer Kunststoff, LED, Anschluss über Netzteil mit USB. Die kleinere Ausführung.</t>
         </is>
       </c>
       <c r="E105" s="13" t="n"/>
@@ -9245,7 +9245,7 @@
         </is>
       </c>
       <c r="H105" s="21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I105" s="21" t="inlineStr">
         <is>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$126</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1225,1664 +1225,2189 @@
       <row>38</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="33" name="Image 33" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>39</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="33" name="Image 33" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId33"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>39</row>
+        <cNvPr id="34" name="Image 34" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>40</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="35" name="Image 35" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>41</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="34" name="Image 34" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId34"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>40</row>
+        <cNvPr id="36" name="Image 36" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="35" name="Image 35" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId35"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>41</row>
+        <cNvPr id="37" name="Image 37" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="36" name="Image 36" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId36"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>42</row>
+        <cNvPr id="38" name="Image 38" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>44</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="37" name="Image 37" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId37"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>43</row>
+        <cNvPr id="39" name="Image 39" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>45</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="38" name="Image 38" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId38"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>44</row>
+        <cNvPr id="40" name="Image 40" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="39" name="Image 39" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId39"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>45</row>
+        <cNvPr id="41" name="Image 41" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>47</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="40" name="Image 40" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId40"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>46</row>
+        <cNvPr id="42" name="Image 42" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="41" name="Image 41" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId41"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>47</row>
+        <cNvPr id="43" name="Image 43" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>49</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="42" name="Image 42" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId42"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>48</row>
+        <cNvPr id="44" name="Image 44" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>50</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="45" name="Image 45" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>51</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="46" name="Image 46" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>52</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="47" name="Image 47" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>53</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="43" name="Image 43" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId43"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>49</row>
+        <cNvPr id="48" name="Image 48" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>54</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="44" name="Image 44" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId44"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>50</row>
+        <cNvPr id="49" name="Image 49" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="45" name="Image 45" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId45"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>51</row>
+        <cNvPr id="50" name="Image 50" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>56</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="46" name="Image 46" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId46"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>52</row>
+        <cNvPr id="51" name="Image 51" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>57</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="52" name="Image 52" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>58</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="53" name="Image 53" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>59</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="54" name="Image 54" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>60</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="55" name="Image 55" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>61</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="56" name="Image 56" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>62</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="57" name="Image 57" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="47" name="Image 47" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId47"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>53</row>
+        <cNvPr id="58" name="Image 58" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="48" name="Image 48" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId48"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>54</row>
+        <cNvPr id="59" name="Image 59" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>65</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="60" name="Image 60" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>66</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="428625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="61" name="Image 61" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>67</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="49" name="Image 49" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId49"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>55</row>
+        <cNvPr id="62" name="Image 62" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>68</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="50" name="Image 50" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId50"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>56</row>
+        <cNvPr id="63" name="Image 63" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>69</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="51" name="Image 51" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId51"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>57</row>
+        <cNvPr id="64" name="Image 64" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>70</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="65" name="Image 65" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>71</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="66" name="Image 66" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>72</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="67" name="Image 67" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>73</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="52" name="Image 52" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId52"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>58</row>
+        <cNvPr id="68" name="Image 68" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId68"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>74</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="53" name="Image 53" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId53"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>59</row>
+        <cNvPr id="69" name="Image 69" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>75</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="70" name="Image 70" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>76</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="54" name="Image 54" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId54"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>60</row>
+        <cNvPr id="71" name="Image 71" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId71"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>77</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="72" name="Image 72" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId72"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>78</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="55" name="Image 55" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId55"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>61</row>
+        <cNvPr id="73" name="Image 73" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId73"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>79</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="56" name="Image 56" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId56"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>62</row>
+        <cNvPr id="74" name="Image 74" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>80</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="57" name="Image 57" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId57"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>63</row>
+        <cNvPr id="75" name="Image 75" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>81</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="58" name="Image 58" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId58"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>64</row>
+        <cNvPr id="76" name="Image 76" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId76"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>82</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="77" name="Image 77" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId77"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>83</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="59" name="Image 59" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId59"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>65</row>
+        <cNvPr id="78" name="Image 78" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>84</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="60" name="Image 60" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId60"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>66</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="428625"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="61" name="Image 61" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId61"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>67</row>
+        <cNvPr id="79" name="Image 79" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId79"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>85</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="619125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="80" name="Image 80" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId80"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>86</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="62" name="Image 62" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId62"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>68</row>
+        <cNvPr id="81" name="Image 81" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId81"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>87</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="63" name="Image 63" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId63"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>69</row>
+        <cNvPr id="82" name="Image 82" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId82"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>88</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="64" name="Image 64" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId64"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>70</row>
+        <cNvPr id="83" name="Image 83" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId83"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>89</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="84" name="Image 84" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId84"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>90</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="885825" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="85" name="Image 85" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId85"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>91</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="65" name="Image 65" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId65"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>71</row>
+        <cNvPr id="86" name="Image 86" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId86"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>92</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="87" name="Image 87" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId87"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="66" name="Image 66" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId66"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>72</row>
+        <cNvPr id="88" name="Image 88" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId88"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>94</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="67" name="Image 67" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId67"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>73</row>
+        <cNvPr id="89" name="Image 89" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId89"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>95</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="68" name="Image 68" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId68"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>74</row>
+        <cNvPr id="90" name="Image 90" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId90"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>96</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="91" name="Image 91" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId91"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>97</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="69" name="Image 69" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId69"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>75</row>
+        <cNvPr id="92" name="Image 92" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId92"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>98</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="70" name="Image 70" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId70"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>76</row>
+        <cNvPr id="93" name="Image 93" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId93"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>99</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="94" name="Image 94" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId94"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>100</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="95" name="Image 95" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId95"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>101</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="96" name="Image 96" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId96"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>102</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="71" name="Image 71" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId71"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>77</row>
+        <cNvPr id="97" name="Image 97" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId97"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>103</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="72" name="Image 72" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId72"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>78</row>
+        <cNvPr id="98" name="Image 98" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId98"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>104</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="99" name="Image 99" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId99"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>105</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="100" name="Image 100" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId100"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>106</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="101" name="Image 101" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId101"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>107</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="102" name="Image 102" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId102"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>108</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="103" name="Image 103" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId103"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>109</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="104" name="Image 104" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId104"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>110</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="105" name="Image 105" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId105"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>111</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="106" name="Image 106" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId106"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>112</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="73" name="Image 73" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId73"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>79</row>
+        <cNvPr id="107" name="Image 107" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId107"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>113</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="108" name="Image 108" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId108"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>114</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="74" name="Image 74" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId74"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>80</row>
+        <cNvPr id="109" name="Image 109" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId109"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>115</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="110" name="Image 110" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId110"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>116</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="111" name="Image 111" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId111"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>117</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="112" name="Image 112" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId112"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>118</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="113" name="Image 113" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId113"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>119</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="75" name="Image 75" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId75"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>81</row>
+        <cNvPr id="114" name="Image 114" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId114"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>120</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="76" name="Image 76" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId76"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>82</row>
+        <cNvPr id="115" name="Image 115" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId115"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>121</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="77" name="Image 77" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId77"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>83</row>
+        <cNvPr id="116" name="Image 116" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId116"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>122</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="117" name="Image 117" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId117"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>123</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="78" name="Image 78" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId78"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>84</row>
+        <cNvPr id="118" name="Image 118" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId118"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>124</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="79" name="Image 79" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId79"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>85</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="619125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="80" name="Image 80" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId80"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>86</row>
+        <cNvPr id="119" name="Image 119" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId119"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>125</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="81" name="Image 81" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId81"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>87</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="82" name="Image 82" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId82"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>88</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="83" name="Image 83" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId83"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>89</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="84" name="Image 84" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId84"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>90</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="885825" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="85" name="Image 85" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId85"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>91</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="86" name="Image 86" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId86"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>92</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="87" name="Image 87" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId87"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>93</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="88" name="Image 88" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId88"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>94</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="89" name="Image 89" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId89"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>95</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="90" name="Image 90" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId90"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>96</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="91" name="Image 91" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId91"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>97</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="92" name="Image 92" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId92"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>98</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="93" name="Image 93" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId93"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>99</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="94" name="Image 94" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId94"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>100</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="95" name="Image 95" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId95"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>101</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="96" name="Image 96" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId96"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>102</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="97" name="Image 97" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId97"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>103</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="98" name="Image 98" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId98"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>104</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="99" name="Image 99" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId99"/>
+        <cNvPr id="120" name="Image 120" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId120"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -3185,7 +3710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q129"/>
+  <dimension ref="A1:Q150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5265,10 +5790,14 @@
       <c r="D39" s="23" t="inlineStr">
         <is>
           <t>Hochflorteppich beige, rund
-Shaggy, beige, rund, Durchmesser ca. 200 cm</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="n"/>
+Runder Hochflorteppich in Beige, 100 % Polypropylen, Flor hoch. Etikett auf der Unterseite: IKEA, 195 cm Durchmesser, 9,85 kg.</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>Ø 195 cm</t>
+        </is>
+      </c>
       <c r="F39" s="23" t="inlineStr">
         <is>
           <t>Gruppenraum</t>
@@ -5280,7 +5809,7 @@
         </is>
       </c>
       <c r="H39" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I39" s="21" t="inlineStr">
         <is>
@@ -5324,8 +5853,8 @@
       <c r="C40" s="11" t="n"/>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Regal weiß 2x2
-IKEA Kallax, weiß, 4 Fächer</t>
+          <t>Regal weiß, 4 Fächer (IKEA Kallax)
+IKEA Kallax 2x2, weiß, vier Fächer.</t>
         </is>
       </c>
       <c r="E40" s="13" t="n"/>
@@ -5340,7 +5869,7 @@
         </is>
       </c>
       <c r="H40" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
@@ -9277,261 +9806,1521 @@
         <v/>
       </c>
     </row>
-    <row r="107" ht="24" customHeight="1">
-      <c r="A107" s="36" t="inlineStr">
+    <row r="106" ht="78" customHeight="1">
+      <c r="A106" s="9" t="n">
+        <v>99</v>
+      </c>
+      <c r="B106" s="10" t="inlineStr">
+        <is>
+          <t>NU02-02</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="n"/>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>Kinderstuhl IKEA Kritter, weiß
+Kinderstuhl aus Massivholz, weiß lackiert, Rückenlehne mit ausgestanzter Katze und Hund. Etikett an der Unterseite: IKEA Kritter, Herstelldatum 2019. Farbe an Sitzkanten und Ecken abgeplatzt.</t>
+        </is>
+      </c>
+      <c r="E106" s="13" t="n"/>
+      <c r="F106" s="12" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G106" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H106" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I106" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J106" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K106" s="15">
+        <f>J106*1.19</f>
+        <v/>
+      </c>
+      <c r="L106" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M106" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N106" s="16" t="n"/>
+      <c r="O106" s="17" t="n"/>
+      <c r="P106" s="18" t="n"/>
+      <c r="Q106" s="19">
+        <f>IF(N106&lt;&gt;"ja","",IF(O106="",H106,O106)*J106)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" ht="78" customHeight="1">
+      <c r="A107" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="B107" s="21" t="inlineStr">
+        <is>
+          <t>NU02-03</t>
+        </is>
+      </c>
+      <c r="C107" s="22" t="n"/>
+      <c r="D107" s="23" t="inlineStr">
+        <is>
+          <t>Kindertisch rund, weiß
+Runde Tischplatte in Weiß mit Multiplex-Kante auf verchromten Rundfüßen. Oberfläche verkratzt und mit Farbspuren.</t>
+        </is>
+      </c>
+      <c r="E107" s="13" t="n"/>
+      <c r="F107" s="23" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G107" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H107" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I107" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J107" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="K107" s="25">
+        <f>J107*1.19</f>
+        <v/>
+      </c>
+      <c r="L107" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M107" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N107" s="16" t="n"/>
+      <c r="O107" s="17" t="n"/>
+      <c r="P107" s="18" t="n"/>
+      <c r="Q107" s="26">
+        <f>IF(N107&lt;&gt;"ja","",IF(O107="",H107,O107)*J107)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108" ht="78" customHeight="1">
+      <c r="A108" s="9" t="n">
+        <v>101</v>
+      </c>
+      <c r="B108" s="10" t="inlineStr">
+        <is>
+          <t>NU02-04</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="n"/>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>Kinderstuhl VS, grau
+Schalenstuhl von VS (Vereinigte Spezialmöbelfabriken) auf grauem Kufengestell. Kunststoffschale mit Griffloch in der Lehne, Sitzfläche mit Belüftungslöchern. Schulmöbelqualität.</t>
+        </is>
+      </c>
+      <c r="E108" s="13" t="n"/>
+      <c r="F108" s="12" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G108" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H108" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I108" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J108" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="K108" s="15">
+        <f>J108*1.19</f>
+        <v/>
+      </c>
+      <c r="L108" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M108" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N108" s="16" t="n"/>
+      <c r="O108" s="17" t="n"/>
+      <c r="P108" s="18" t="n"/>
+      <c r="Q108" s="19">
+        <f>IF(N108&lt;&gt;"ja","",IF(O108="",H108,O108)*J108)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" ht="78" customHeight="1">
+      <c r="A109" s="20" t="n">
+        <v>102</v>
+      </c>
+      <c r="B109" s="21" t="inlineStr">
+        <is>
+          <t>NU02-05</t>
+        </is>
+      </c>
+      <c r="C109" s="22" t="n"/>
+      <c r="D109" s="23" t="inlineStr">
+        <is>
+          <t>Kindertisch halbrund, weiß
+Halbrunde Tischplatte in Weiß mit Holzkante, auf dunklen Rundfüßen. Zwei Tische ergeben zusammen einen ovalen Tisch.</t>
+        </is>
+      </c>
+      <c r="E109" s="13" t="n"/>
+      <c r="F109" s="23" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G109" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H109" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I109" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J109" s="24" t="n">
+        <v>45</v>
+      </c>
+      <c r="K109" s="25">
+        <f>J109*1.19</f>
+        <v/>
+      </c>
+      <c r="L109" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M109" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N109" s="16" t="n"/>
+      <c r="O109" s="17" t="n"/>
+      <c r="P109" s="18" t="n"/>
+      <c r="Q109" s="26">
+        <f>IF(N109&lt;&gt;"ja","",IF(O109="",H109,O109)*J109)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" ht="78" customHeight="1">
+      <c r="A110" s="9" t="n">
+        <v>103</v>
+      </c>
+      <c r="B110" s="10" t="inlineStr">
+        <is>
+          <t>NU02-07</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="n"/>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>Beistelltisch Drahtkorb, Kupfer
+Runder Beistelltisch: Drahtkorb in Kupferoptik mit abnehmbarer Platte in Holzoptik. Der Korb lässt sich als Ablage nutzen.</t>
+        </is>
+      </c>
+      <c r="E110" s="13" t="n"/>
+      <c r="F110" s="12" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G110" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H110" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I110" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J110" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K110" s="15">
+        <f>J110*1.19</f>
+        <v/>
+      </c>
+      <c r="L110" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M110" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N110" s="16" t="n"/>
+      <c r="O110" s="17" t="n"/>
+      <c r="P110" s="18" t="n"/>
+      <c r="Q110" s="19">
+        <f>IF(N110&lt;&gt;"ja","",IF(O110="",H110,O110)*J110)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" ht="78" customHeight="1">
+      <c r="A111" s="20" t="n">
+        <v>104</v>
+      </c>
+      <c r="B111" s="21" t="inlineStr">
+        <is>
+          <t>NU02-08</t>
+        </is>
+      </c>
+      <c r="C111" s="22" t="n"/>
+      <c r="D111" s="23" t="inlineStr">
+        <is>
+          <t>Ohrensessel klein, creme
+Kleiner Ohrensessel mit cremefarbenem Bouclé-Bezug und schwarz lackierten, geschwungenen Holzbeinen. Niedrige Sitzhöhe.</t>
+        </is>
+      </c>
+      <c r="E111" s="13" t="n"/>
+      <c r="F111" s="23" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G111" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H111" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I111" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J111" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="K111" s="25">
+        <f>J111*1.19</f>
+        <v/>
+      </c>
+      <c r="L111" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M111" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N111" s="16" t="n"/>
+      <c r="O111" s="17" t="n"/>
+      <c r="P111" s="18" t="n"/>
+      <c r="Q111" s="26">
+        <f>IF(N111&lt;&gt;"ja","",IF(O111="",H111,O111)*J111)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112" ht="78" customHeight="1">
+      <c r="A112" s="9" t="n">
+        <v>105</v>
+      </c>
+      <c r="B112" s="10" t="inlineStr">
+        <is>
+          <t>NU02-09</t>
+        </is>
+      </c>
+      <c r="C112" s="11" t="n"/>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>Spieltisch Kiefer mit weißen Einlagen
+Quadratischer Tisch: Rahmen und Beine aus Kiefer massiv, zwei weiße Einlegeplatten in der Tischfläche mit Griffloch. Kanten und Platten mit Gebrauchsspuren.</t>
+        </is>
+      </c>
+      <c r="E112" s="13" t="n"/>
+      <c r="F112" s="12" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G112" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H112" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J112" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="K112" s="15">
+        <f>J112*1.19</f>
+        <v/>
+      </c>
+      <c r="L112" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M112" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N112" s="16" t="n"/>
+      <c r="O112" s="17" t="n"/>
+      <c r="P112" s="18" t="n"/>
+      <c r="Q112" s="19">
+        <f>IF(N112&lt;&gt;"ja","",IF(O112="",H112,O112)*J112)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" ht="78" customHeight="1">
+      <c r="A113" s="20" t="n">
+        <v>106</v>
+      </c>
+      <c r="B113" s="21" t="inlineStr">
+        <is>
+          <t>NU02-11</t>
+        </is>
+      </c>
+      <c r="C113" s="22" t="n"/>
+      <c r="D113" s="23" t="inlineStr">
+        <is>
+          <t>Tisch weiß mit grauer Platte
+Tisch mit weißen Seitenwangen und dunkelgrauer Platte, auf Gleitern. Schlichte Bauweise, als Arbeits- oder Basteltisch genutzt.</t>
+        </is>
+      </c>
+      <c r="E113" s="13" t="n"/>
+      <c r="F113" s="23" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G113" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H113" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I113" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J113" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="K113" s="25">
+        <f>J113*1.19</f>
+        <v/>
+      </c>
+      <c r="L113" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M113" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N113" s="16" t="n"/>
+      <c r="O113" s="17" t="n"/>
+      <c r="P113" s="18" t="n"/>
+      <c r="Q113" s="26">
+        <f>IF(N113&lt;&gt;"ja","",IF(O113="",H113,O113)*J113)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" ht="78" customHeight="1">
+      <c r="A114" s="9" t="n">
+        <v>107</v>
+      </c>
+      <c r="B114" s="10" t="inlineStr">
+        <is>
+          <t>NU02-12</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="n"/>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>Pinolino Kindersitzgruppe rund, Holz
+Runder Kindertisch mit vier angebauten, geschwungenen Sitzbänken, Nadelholz. Von Pinolino. Stand im Freien und ist vergraut, Holz sonst fest.</t>
+        </is>
+      </c>
+      <c r="E114" s="13" t="n"/>
+      <c r="F114" s="12" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G114" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H114" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I114" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J114" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="K114" s="15">
+        <f>J114*1.19</f>
+        <v/>
+      </c>
+      <c r="L114" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M114" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N114" s="16" t="n"/>
+      <c r="O114" s="17" t="n"/>
+      <c r="P114" s="18" t="n"/>
+      <c r="Q114" s="19">
+        <f>IF(N114&lt;&gt;"ja","",IF(O114="",H114,O114)*J114)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" ht="78" customHeight="1">
+      <c r="A115" s="20" t="n">
+        <v>108</v>
+      </c>
+      <c r="B115" s="21" t="inlineStr">
+        <is>
+          <t>NU02-13</t>
+        </is>
+      </c>
+      <c r="C115" s="22" t="n"/>
+      <c r="D115" s="23" t="inlineStr">
+        <is>
+          <t>IKEA Mammut Kindertisch mit vier Stühlen
+Kindertisch und vier Kinderstühle aus weißem Kunststoff, IKEA Mammut. Stand im Freien, Oberflächen verschmutzt und stumpf.</t>
+        </is>
+      </c>
+      <c r="E115" s="13" t="n"/>
+      <c r="F115" s="23" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G115" s="21" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="H115" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I115" s="21" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="J115" s="24" t="n">
+        <v>35</v>
+      </c>
+      <c r="K115" s="25">
+        <f>J115*1.19</f>
+        <v/>
+      </c>
+      <c r="L115" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M115" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N115" s="16" t="n"/>
+      <c r="O115" s="17" t="n"/>
+      <c r="P115" s="18" t="n"/>
+      <c r="Q115" s="26">
+        <f>IF(N115&lt;&gt;"ja","",IF(O115="",H115,O115)*J115)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" ht="78" customHeight="1">
+      <c r="A116" s="9" t="n">
+        <v>109</v>
+      </c>
+      <c r="B116" s="10" t="inlineStr">
+        <is>
+          <t>NU02-14</t>
+        </is>
+      </c>
+      <c r="C116" s="11" t="n"/>
+      <c r="D116" s="12" t="inlineStr">
+        <is>
+          <t>IKEA Mammut Kinderstuhl, rosa und grün
+Kinderstuhl aus Kunststoff, IKEA Mammut. Stand im Freien, Farbe deutlich ausgeblichen.</t>
+        </is>
+      </c>
+      <c r="E116" s="13" t="n"/>
+      <c r="F116" s="12" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G116" s="10" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="H116" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I116" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J116" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K116" s="15">
+        <f>J116*1.19</f>
+        <v/>
+      </c>
+      <c r="L116" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M116" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N116" s="16" t="n"/>
+      <c r="O116" s="17" t="n"/>
+      <c r="P116" s="18" t="n"/>
+      <c r="Q116" s="19">
+        <f>IF(N116&lt;&gt;"ja","",IF(O116="",H116,O116)*J116)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" ht="78" customHeight="1">
+      <c r="A117" s="20" t="n">
+        <v>110</v>
+      </c>
+      <c r="B117" s="21" t="inlineStr">
+        <is>
+          <t>NU02-15</t>
+        </is>
+      </c>
+      <c r="C117" s="22" t="n"/>
+      <c r="D117" s="23" t="inlineStr">
+        <is>
+          <t>Konsole Bambus mit weißer Ablagewanne
+Schmales Gestell aus Bambus mit Lattenboden und aufgelegter weißer Wanne als Ablage.</t>
+        </is>
+      </c>
+      <c r="E117" s="13" t="n"/>
+      <c r="F117" s="23" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G117" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H117" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I117" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J117" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="K117" s="25">
+        <f>J117*1.19</f>
+        <v/>
+      </c>
+      <c r="L117" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M117" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N117" s="16" t="n"/>
+      <c r="O117" s="17" t="n"/>
+      <c r="P117" s="18" t="n"/>
+      <c r="Q117" s="26">
+        <f>IF(N117&lt;&gt;"ja","",IF(O117="",H117,O117)*J117)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" ht="78" customHeight="1">
+      <c r="A118" s="9" t="n">
+        <v>111</v>
+      </c>
+      <c r="B118" s="10" t="inlineStr">
+        <is>
+          <t>NU02-16</t>
+        </is>
+      </c>
+      <c r="C118" s="11" t="n"/>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>Wandregal beige, lang
+Langes Wandregal mit hoher Rückkante, beige beschichtet.</t>
+        </is>
+      </c>
+      <c r="E118" s="13" t="n"/>
+      <c r="F118" s="12" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G118" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H118" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I118" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J118" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="K118" s="15">
+        <f>J118*1.19</f>
+        <v/>
+      </c>
+      <c r="L118" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M118" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N118" s="16" t="n"/>
+      <c r="O118" s="17" t="n"/>
+      <c r="P118" s="18" t="n"/>
+      <c r="Q118" s="19">
+        <f>IF(N118&lt;&gt;"ja","",IF(O118="",H118,O118)*J118)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" ht="78" customHeight="1">
+      <c r="A119" s="20" t="n">
+        <v>112</v>
+      </c>
+      <c r="B119" s="21" t="inlineStr">
+        <is>
+          <t>NU02-17</t>
+        </is>
+      </c>
+      <c r="C119" s="22" t="n"/>
+      <c r="D119" s="23" t="inlineStr">
+        <is>
+          <t>Wandregal weiß, kurz
+Kurzes Wandregal mit Rückkante, weiß beschichtet, sichtbar verschraubt.</t>
+        </is>
+      </c>
+      <c r="E119" s="13" t="n"/>
+      <c r="F119" s="23" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G119" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H119" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I119" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J119" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="K119" s="25">
+        <f>J119*1.19</f>
+        <v/>
+      </c>
+      <c r="L119" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M119" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N119" s="16" t="n"/>
+      <c r="O119" s="17" t="n"/>
+      <c r="P119" s="18" t="n"/>
+      <c r="Q119" s="26">
+        <f>IF(N119&lt;&gt;"ja","",IF(O119="",H119,O119)*J119)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120" ht="78" customHeight="1">
+      <c r="A120" s="9" t="n">
+        <v>113</v>
+      </c>
+      <c r="B120" s="35" t="inlineStr">
+        <is>
+          <t>NU02-18</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="n"/>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>Sitztier Elefant, weiß
+Sitztier in Elefantenform aus weißem Kunststoff. Am Ohr ein ovales Metallplättchen mit eingravierter Signatur.</t>
+        </is>
+      </c>
+      <c r="E120" s="13" t="n"/>
+      <c r="F120" s="12" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G120" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H120" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I120" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J120" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="K120" s="15">
+        <f>J120*1.19</f>
+        <v/>
+      </c>
+      <c r="L120" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M120" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N120" s="16" t="n"/>
+      <c r="O120" s="17" t="n"/>
+      <c r="P120" s="18" t="n"/>
+      <c r="Q120" s="19">
+        <f>IF(N120&lt;&gt;"ja","",IF(O120="",H120,O120)*J120)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" ht="78" customHeight="1">
+      <c r="A121" s="20" t="n">
+        <v>114</v>
+      </c>
+      <c r="B121" s="21" t="inlineStr">
+        <is>
+          <t>NU02-19</t>
+        </is>
+      </c>
+      <c r="C121" s="22" t="n"/>
+      <c r="D121" s="23" t="inlineStr">
+        <is>
+          <t>Schrank weiß, zwei Türen
+Hoher Schrank in Weiß mit zwei Türen und schwarzen Griffmulden, beschriftet.</t>
+        </is>
+      </c>
+      <c r="E121" s="13" t="n"/>
+      <c r="F121" s="23" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G121" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H121" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J121" s="24" t="n">
+        <v>70</v>
+      </c>
+      <c r="K121" s="25">
+        <f>J121*1.19</f>
+        <v/>
+      </c>
+      <c r="L121" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M121" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N121" s="16" t="n"/>
+      <c r="O121" s="17" t="n"/>
+      <c r="P121" s="18" t="n"/>
+      <c r="Q121" s="26">
+        <f>IF(N121&lt;&gt;"ja","",IF(O121="",H121,O121)*J121)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" ht="78" customHeight="1">
+      <c r="A122" s="9" t="n">
+        <v>115</v>
+      </c>
+      <c r="B122" s="10" t="inlineStr">
+        <is>
+          <t>NU02-20</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="n"/>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>Schrank weiß mit zwei Schubladen
+Schrank in Weiß mit zwei Türen oben und zwei großen Schubladen mit ovalen Griffmulden darunter, beschriftet.</t>
+        </is>
+      </c>
+      <c r="E122" s="13" t="n"/>
+      <c r="F122" s="12" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G122" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H122" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I122" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J122" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="K122" s="15">
+        <f>J122*1.19</f>
+        <v/>
+      </c>
+      <c r="L122" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M122" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N122" s="16" t="n"/>
+      <c r="O122" s="17" t="n"/>
+      <c r="P122" s="18" t="n"/>
+      <c r="Q122" s="19">
+        <f>IF(N122&lt;&gt;"ja","",IF(O122="",H122,O122)*J122)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" ht="78" customHeight="1">
+      <c r="A123" s="20" t="n">
+        <v>116</v>
+      </c>
+      <c r="B123" s="21" t="inlineStr">
+        <is>
+          <t>NU02-21</t>
+        </is>
+      </c>
+      <c r="C123" s="22" t="n"/>
+      <c r="D123" s="23" t="inlineStr">
+        <is>
+          <t>Regal weiß, hoch, drei Fächer
+Hohes offenes Regal in Weiß mit drei Fächern und verstellbaren Böden. Die Rückwand ist auf Höhe des mittleren Bodens ausgebrochen.</t>
+        </is>
+      </c>
+      <c r="E123" s="13" t="n"/>
+      <c r="F123" s="23" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G123" s="21" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="H123" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I123" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J123" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="K123" s="25">
+        <f>J123*1.19</f>
+        <v/>
+      </c>
+      <c r="L123" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M123" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N123" s="16" t="n"/>
+      <c r="O123" s="17" t="n"/>
+      <c r="P123" s="18" t="n"/>
+      <c r="Q123" s="26">
+        <f>IF(N123&lt;&gt;"ja","",IF(O123="",H123,O123)*J123)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124" ht="78" customHeight="1">
+      <c r="A124" s="9" t="n">
+        <v>117</v>
+      </c>
+      <c r="B124" s="10" t="inlineStr">
+        <is>
+          <t>NU02-22</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="n"/>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>Acrylbild schwarz-weiß, abstrakt
+Acryl auf Leinwand, abstrakte schwarz-weiße Komposition mit breitem Pinselzug und Farbspritzern. Eigenarbeit einer Privatperson, nicht signiert.</t>
+        </is>
+      </c>
+      <c r="E124" s="13" t="n"/>
+      <c r="F124" s="12" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G124" s="10" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H124" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I124" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J124" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="K124" s="15">
+        <f>J124*1.19</f>
+        <v/>
+      </c>
+      <c r="L124" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M124" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N124" s="16" t="n"/>
+      <c r="O124" s="17" t="n"/>
+      <c r="P124" s="18" t="n"/>
+      <c r="Q124" s="19">
+        <f>IF(N124&lt;&gt;"ja","",IF(O124="",H124,O124)*J124)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" ht="78" customHeight="1">
+      <c r="A125" s="20" t="n">
+        <v>118</v>
+      </c>
+      <c r="B125" s="35" t="inlineStr">
+        <is>
+          <t>NU02-23</t>
+        </is>
+      </c>
+      <c r="C125" s="22" t="n"/>
+      <c r="D125" s="23" t="inlineStr">
+        <is>
+          <t>Konferenztisch weiß aus Segmenten
+Mehrere trapezförmige Tischsegmente mit weißer Platte, Multiplex-Kante und verchromten Rundfüßen. Zusammengestellt ergeben sie einen großen Besprechungstisch, einzeln sind sie als Gruppentische nutzbar.</t>
+        </is>
+      </c>
+      <c r="E125" s="13" t="n"/>
+      <c r="F125" s="23" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G125" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H125" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I125" s="21" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="J125" s="24" t="n">
+        <v>180</v>
+      </c>
+      <c r="K125" s="25">
+        <f>J125*1.19</f>
+        <v/>
+      </c>
+      <c r="L125" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M125" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N125" s="16" t="n"/>
+      <c r="O125" s="17" t="n"/>
+      <c r="P125" s="18" t="n"/>
+      <c r="Q125" s="26">
+        <f>IF(N125&lt;&gt;"ja","",IF(O125="",H125,O125)*J125)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126" ht="78" customHeight="1">
+      <c r="A126" s="9" t="n">
+        <v>119</v>
+      </c>
+      <c r="B126" s="10" t="inlineStr">
+        <is>
+          <t>NU02-24</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="n"/>
+      <c r="D126" s="12" t="inlineStr">
+        <is>
+          <t>Regal weiß, niedrig, drei Fächer
+Niedriges offenes Regal in Weiß mit grauem Boden auf Rundfüßen aus Metall, drei Fächer.</t>
+        </is>
+      </c>
+      <c r="E126" s="13" t="n"/>
+      <c r="F126" s="12" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G126" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H126" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I126" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J126" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K126" s="15">
+        <f>J126*1.19</f>
+        <v/>
+      </c>
+      <c r="L126" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M126" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N126" s="16" t="n"/>
+      <c r="O126" s="17" t="n"/>
+      <c r="P126" s="18" t="n"/>
+      <c r="Q126" s="19">
+        <f>IF(N126&lt;&gt;"ja","",IF(O126="",H126,O126)*J126)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128" ht="24" customHeight="1">
+      <c r="A128" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B107" s="1" t="n"/>
-      <c r="C107" s="1" t="n"/>
-      <c r="D107" s="1" t="n"/>
-      <c r="E107" s="1" t="n"/>
-      <c r="F107" s="1" t="n"/>
-      <c r="G107" s="1" t="n"/>
-      <c r="H107" s="1" t="n"/>
-      <c r="I107" s="1" t="n"/>
-      <c r="J107" s="1" t="n"/>
-      <c r="K107" s="1" t="n"/>
-      <c r="L107" s="1" t="n"/>
-      <c r="M107" s="1" t="n"/>
-      <c r="N107" s="1" t="n"/>
-      <c r="O107" s="1" t="n"/>
-      <c r="P107" s="1" t="n"/>
-      <c r="Q107" s="1" t="n"/>
-    </row>
-    <row r="108" ht="22" customHeight="1">
-      <c r="A108" s="37" t="inlineStr">
+      <c r="B128" s="1" t="n"/>
+      <c r="C128" s="1" t="n"/>
+      <c r="D128" s="1" t="n"/>
+      <c r="E128" s="1" t="n"/>
+      <c r="F128" s="1" t="n"/>
+      <c r="G128" s="1" t="n"/>
+      <c r="H128" s="1" t="n"/>
+      <c r="I128" s="1" t="n"/>
+      <c r="J128" s="1" t="n"/>
+      <c r="K128" s="1" t="n"/>
+      <c r="L128" s="1" t="n"/>
+      <c r="M128" s="1" t="n"/>
+      <c r="N128" s="1" t="n"/>
+      <c r="O128" s="1" t="n"/>
+      <c r="P128" s="1" t="n"/>
+      <c r="Q128" s="1" t="n"/>
+    </row>
+    <row r="129" ht="22" customHeight="1">
+      <c r="A129" s="37" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl netto</t>
         </is>
       </c>
-      <c r="Q108" s="38">
-        <f>SUM(Q8:Q105)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="109" ht="22" customHeight="1">
-      <c r="A109" s="37" t="inlineStr">
+      <c r="Q129" s="38">
+        <f>SUM(Q8:Q126)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130" ht="22" customHeight="1">
+      <c r="A130" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q109" s="38">
-        <f>Q108*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="110" ht="26" customHeight="1">
-      <c r="A110" s="39" t="inlineStr">
+      <c r="Q130" s="38">
+        <f>Q129*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131" ht="26" customHeight="1">
+      <c r="A131" s="39" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl brutto</t>
         </is>
       </c>
-      <c r="Q110" s="40">
-        <f>Q108+Q109</f>
-        <v/>
-      </c>
-    </row>
-    <row r="111" ht="22" customHeight="1">
-      <c r="A111" s="37" t="inlineStr">
+      <c r="Q131" s="40">
+        <f>Q129+Q130</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132" ht="22" customHeight="1">
+      <c r="A132" s="37" t="inlineStr">
         <is>
           <t>gewählte Positionen</t>
         </is>
       </c>
-      <c r="Q111" s="41">
-        <f>COUNTIF(N8:N105,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="42" t="inlineStr">
+      <c r="Q132" s="41">
+        <f>COUNTIF(N8:N126,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="42" t="inlineStr">
         <is>
           <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
         </is>
       </c>
     </row>
-    <row r="114" ht="24" customHeight="1">
-      <c r="A114" s="43" t="inlineStr">
+    <row r="135" ht="24" customHeight="1">
+      <c r="A135" s="43" t="inlineStr">
         <is>
           <t>B · GESAMTBESTAND</t>
         </is>
       </c>
-      <c r="B114" s="44" t="n"/>
-      <c r="C114" s="44" t="n"/>
-      <c r="D114" s="44" t="n"/>
-      <c r="E114" s="44" t="n"/>
-      <c r="F114" s="44" t="n"/>
-      <c r="G114" s="44" t="n"/>
-      <c r="H114" s="44" t="n"/>
-      <c r="I114" s="44" t="n"/>
-      <c r="J114" s="44" t="n"/>
-      <c r="K114" s="44" t="n"/>
-      <c r="L114" s="44" t="n"/>
-      <c r="M114" s="44" t="n"/>
-      <c r="N114" s="44" t="n"/>
-      <c r="O114" s="44" t="n"/>
-      <c r="P114" s="44" t="n"/>
-      <c r="Q114" s="44" t="n"/>
-    </row>
-    <row r="115" ht="22" customHeight="1">
-      <c r="A115" s="37" t="inlineStr">
+      <c r="B135" s="44" t="n"/>
+      <c r="C135" s="44" t="n"/>
+      <c r="D135" s="44" t="n"/>
+      <c r="E135" s="44" t="n"/>
+      <c r="F135" s="44" t="n"/>
+      <c r="G135" s="44" t="n"/>
+      <c r="H135" s="44" t="n"/>
+      <c r="I135" s="44" t="n"/>
+      <c r="J135" s="44" t="n"/>
+      <c r="K135" s="44" t="n"/>
+      <c r="L135" s="44" t="n"/>
+      <c r="M135" s="44" t="n"/>
+      <c r="N135" s="44" t="n"/>
+      <c r="O135" s="44" t="n"/>
+      <c r="P135" s="44" t="n"/>
+      <c r="Q135" s="44" t="n"/>
+    </row>
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="37" t="inlineStr">
         <is>
           <t>Gesamtwert aller gelisteten Positionen netto</t>
         </is>
       </c>
-      <c r="Q115" s="38">
-        <f>SUMPRODUCT(H8:H105,J8:J105)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="116" ht="22" customHeight="1">
-      <c r="A116" s="37" t="inlineStr">
+      <c r="Q136" s="38">
+        <f>SUMPRODUCT(H8:H126,J8:J126)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137" ht="22" customHeight="1">
+      <c r="A137" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q116" s="38">
-        <f>Q115*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="117" ht="22" customHeight="1">
-      <c r="A117" s="45" t="inlineStr">
+      <c r="Q137" s="38">
+        <f>Q136*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138" ht="22" customHeight="1">
+      <c r="A138" s="45" t="inlineStr">
         <is>
           <t>Gesamtwert brutto</t>
         </is>
       </c>
-      <c r="Q117" s="46">
-        <f>Q115+Q116</f>
-        <v/>
-      </c>
-    </row>
-    <row r="119" ht="24" customHeight="1">
-      <c r="A119" s="47" t="inlineStr">
+      <c r="Q138" s="46">
+        <f>Q136+Q137</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" ht="24" customHeight="1">
+      <c r="A140" s="47" t="inlineStr">
         <is>
           <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
         </is>
       </c>
-      <c r="B119" s="48" t="n"/>
-      <c r="C119" s="48" t="n"/>
-      <c r="D119" s="48" t="n"/>
-      <c r="E119" s="48" t="n"/>
-      <c r="F119" s="48" t="n"/>
-      <c r="G119" s="48" t="n"/>
-      <c r="H119" s="48" t="n"/>
-      <c r="I119" s="48" t="n"/>
-      <c r="J119" s="48" t="n"/>
-      <c r="K119" s="48" t="n"/>
-      <c r="L119" s="48" t="n"/>
-      <c r="M119" s="48" t="n"/>
-      <c r="N119" s="48" t="n"/>
-      <c r="O119" s="48" t="n"/>
-      <c r="P119" s="48" t="n"/>
-      <c r="Q119" s="48" t="n"/>
-    </row>
-    <row r="120" ht="22" customHeight="1">
-      <c r="A120" s="37" t="inlineStr">
+      <c r="B140" s="48" t="n"/>
+      <c r="C140" s="48" t="n"/>
+      <c r="D140" s="48" t="n"/>
+      <c r="E140" s="48" t="n"/>
+      <c r="F140" s="48" t="n"/>
+      <c r="G140" s="48" t="n"/>
+      <c r="H140" s="48" t="n"/>
+      <c r="I140" s="48" t="n"/>
+      <c r="J140" s="48" t="n"/>
+      <c r="K140" s="48" t="n"/>
+      <c r="L140" s="48" t="n"/>
+      <c r="M140" s="48" t="n"/>
+      <c r="N140" s="48" t="n"/>
+      <c r="O140" s="48" t="n"/>
+      <c r="P140" s="48" t="n"/>
+      <c r="Q140" s="48" t="n"/>
+    </row>
+    <row r="141" ht="22" customHeight="1">
+      <c r="A141" s="37" t="inlineStr">
         <is>
           <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
         </is>
       </c>
-      <c r="Q120" s="38">
-        <f>-Q115*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="121" ht="22" customHeight="1">
-      <c r="A121" s="45" t="inlineStr">
+      <c r="Q141" s="38">
+        <f>-Q136*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142" ht="22" customHeight="1">
+      <c r="A142" s="45" t="inlineStr">
         <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="Q121" s="46">
-        <f>Q115+Q120</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122" ht="22" customHeight="1">
-      <c r="A122" s="37" t="inlineStr">
+      <c r="Q142" s="46">
+        <f>Q136+Q141</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143" ht="22" customHeight="1">
+      <c r="A143" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q122" s="38">
-        <f>Q121*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="123" ht="26" customHeight="1">
-      <c r="A123" s="39" t="inlineStr">
+      <c r="Q143" s="38">
+        <f>Q142*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144" ht="26" customHeight="1">
+      <c r="A144" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q123" s="40">
-        <f>Q121+Q122</f>
-        <v/>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="42" t="inlineStr">
+      <c r="Q144" s="40">
+        <f>Q142+Q143</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="49" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="127"/>
-    <row r="128"/>
-    <row r="129"/>
+    <row r="148"/>
+    <row r="149"/>
+    <row r="150"/>
   </sheetData>
-  <autoFilter ref="A7:Q105"/>
+  <autoFilter ref="A7:Q126"/>
   <mergeCells count="26">
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A116:P116"/>
-    <mergeCell ref="A114:Q114"/>
-    <mergeCell ref="A122:P122"/>
-    <mergeCell ref="A109:P109"/>
+    <mergeCell ref="A141:P141"/>
+    <mergeCell ref="A144:P144"/>
+    <mergeCell ref="A131:P131"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A107:Q107"/>
     <mergeCell ref="L4:Q4"/>
-    <mergeCell ref="A121:P121"/>
-    <mergeCell ref="A119:Q119"/>
-    <mergeCell ref="A115:P115"/>
-    <mergeCell ref="A117:P117"/>
-    <mergeCell ref="A111:P111"/>
-    <mergeCell ref="A126:Q129"/>
-    <mergeCell ref="A124:Q124"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A123:P123"/>
-    <mergeCell ref="A110:P110"/>
+    <mergeCell ref="A147:Q150"/>
+    <mergeCell ref="A143:P143"/>
+    <mergeCell ref="A130:P130"/>
+    <mergeCell ref="A128:Q128"/>
+    <mergeCell ref="A133:Q133"/>
+    <mergeCell ref="A142:P142"/>
+    <mergeCell ref="A145:Q145"/>
+    <mergeCell ref="A138:P138"/>
+    <mergeCell ref="A132:P132"/>
     <mergeCell ref="C4:I4"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A108:P108"/>
-    <mergeCell ref="A120:P120"/>
+    <mergeCell ref="A137:P137"/>
+    <mergeCell ref="A135:Q135"/>
+    <mergeCell ref="A140:Q140"/>
+    <mergeCell ref="A136:P136"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A112:Q112"/>
+    <mergeCell ref="A129:P129"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q105">
+  <conditionalFormatting sqref="A8:Q126">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N126" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O105" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O126" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -5877,7 +5877,7 @@
         </is>
       </c>
       <c r="J40" s="14" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="K40" s="15">
         <f>J40*1.19</f>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H108" s="10" t="n">
@@ -9962,7 +9962,7 @@
         </is>
       </c>
       <c r="J108" s="14" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="K108" s="15">
         <f>J108*1.19</f>
@@ -10418,8 +10418,8 @@
       <c r="C116" s="11" t="n"/>
       <c r="D116" s="12" t="inlineStr">
         <is>
-          <t>IKEA Mammut Kinderstuhl, rosa und grün
-Kinderstuhl aus Kunststoff, IKEA Mammut. Stand im Freien, Farbe deutlich ausgeblichen.</t>
+          <t>IKEA Mammut Kinderstuhl, verschiedene Farben
+Kinderstuhl aus Kunststoff, IKEA Mammut, in verschiedenen Farben. Stand im Freien, Farben deutlich ausgeblichen.</t>
         </is>
       </c>
       <c r="E116" s="13" t="n"/>
@@ -10478,8 +10478,8 @@
       <c r="C117" s="22" t="n"/>
       <c r="D117" s="23" t="inlineStr">
         <is>
-          <t>Konsole Bambus mit weißer Ablagewanne
-Schmales Gestell aus Bambus mit Lattenboden und aufgelegter weißer Wanne als Ablage.</t>
+          <t>Ablagetisch Bambus mit Wanne
+Schmales Gestell aus Bambus mit Lattenboden und aufgelegter weißer Wanne. Im Haus als Aufbewahrung und Servierwagen genutzt.</t>
         </is>
       </c>
       <c r="E117" s="13" t="n"/>
@@ -10658,8 +10658,8 @@
       <c r="C120" s="11" t="n"/>
       <c r="D120" s="12" t="inlineStr">
         <is>
-          <t>Sitztier Elefant, weiß
-Sitztier in Elefantenform aus weißem Kunststoff. Am Ohr ein ovales Metallplättchen mit eingravierter Signatur.</t>
+          <t>Sitztier Elefant, weiß und schwarz
+Sitztier in Elefantenform aus Kunststoff, ein weißes und ein schwarzes Exemplar in gleicher Größe. Am Ohr ein ovales Metallplättchen mit eingravierter Signatur.</t>
         </is>
       </c>
       <c r="E120" s="13" t="n"/>
@@ -10674,7 +10674,7 @@
         </is>
       </c>
       <c r="H120" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I120" s="10" t="inlineStr">
         <is>
@@ -10958,8 +10958,8 @@
       <c r="C125" s="22" t="n"/>
       <c r="D125" s="23" t="inlineStr">
         <is>
-          <t>Konferenztisch weiß aus Segmenten
-Mehrere trapezförmige Tischsegmente mit weißer Platte, Multiplex-Kante und verchromten Rundfüßen. Zusammengestellt ergeben sie einen großen Besprechungstisch, einzeln sind sie als Gruppentische nutzbar.</t>
+          <t>Kindertisch weiß aus vier Segmenten
+Vier trapezförmige Tischsegmente mit weißer Platte, Multiplex-Kante und verchromten Rundfüßen in Kinderhöhe. Zusammengestellt ergeben sie einen großen Gruppentisch, einzeln sind sie frei kombinierbar.</t>
         </is>
       </c>
       <c r="E125" s="13" t="n"/>
@@ -10982,7 +10982,7 @@
         </is>
       </c>
       <c r="J125" s="24" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="K125" s="25">
         <f>J125*1.19</f>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$126</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$135</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3418,6 +3418,231 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>126</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="121" name="Image 121" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId121"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>127</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="122" name="Image 122" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId122"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>128</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="123" name="Image 123" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId123"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>129</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="124" name="Image 124" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId124"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>130</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="125" name="Image 125" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId125"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>131</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="126" name="Image 126" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId126"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>132</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="127" name="Image 127" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId127"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>133</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="128" name="Image 128" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId128"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>134</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="129" name="Image 129" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId129"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -3710,7 +3935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q150"/>
+  <dimension ref="A1:Q159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11066,261 +11291,801 @@
         <v/>
       </c>
     </row>
-    <row r="128" ht="24" customHeight="1">
-      <c r="A128" s="36" t="inlineStr">
+    <row r="127" ht="78" customHeight="1">
+      <c r="A127" s="20" t="n">
+        <v>120</v>
+      </c>
+      <c r="B127" s="35" t="inlineStr">
+        <is>
+          <t>NU03-02</t>
+        </is>
+      </c>
+      <c r="C127" s="22" t="n"/>
+      <c r="D127" s="23" t="inlineStr">
+        <is>
+          <t>Stockbett weiß mit Absturzsicherung
+Etagenbett in Weiß mit sichtbaren Multiplex-Kanten, abgerundeten Ausschnitten und durchgehender Absturzsicherung oben. Solide Bauweise aus dem Kita-Betrieb.</t>
+        </is>
+      </c>
+      <c r="E127" s="13" t="n"/>
+      <c r="F127" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 4</t>
+        </is>
+      </c>
+      <c r="G127" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H127" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I127" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J127" s="24" t="n">
+        <v>300</v>
+      </c>
+      <c r="K127" s="25">
+        <f>J127*1.19</f>
+        <v/>
+      </c>
+      <c r="L127" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M127" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N127" s="16" t="n"/>
+      <c r="O127" s="17" t="n"/>
+      <c r="P127" s="18" t="n"/>
+      <c r="Q127" s="26">
+        <f>IF(N127&lt;&gt;"ja","",IF(O127="",H127,O127)*J127)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128" ht="78" customHeight="1">
+      <c r="A128" s="9" t="n">
+        <v>121</v>
+      </c>
+      <c r="B128" s="35" t="inlineStr">
+        <is>
+          <t>NU03-03</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="n"/>
+      <c r="D128" s="12" t="inlineStr">
+        <is>
+          <t>Wesco Spielküche, mehrteilig
+Spielküche von Wesco aus Birke-Multiplex: Spülmodul mit Becken, Kochmodul mit Drehknöpfen, Backofenmodul mit Sichtfenster sowie Kühl- und Gefriermodule. Weiße Fronten mit Holzgriffen, Module einzeln stellbar.</t>
+        </is>
+      </c>
+      <c r="E128" s="13" t="n"/>
+      <c r="F128" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 4</t>
+        </is>
+      </c>
+      <c r="G128" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H128" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I128" s="10" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="J128" s="14" t="n">
+        <v>650</v>
+      </c>
+      <c r="K128" s="15">
+        <f>J128*1.19</f>
+        <v/>
+      </c>
+      <c r="L128" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M128" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N128" s="16" t="n"/>
+      <c r="O128" s="17" t="n"/>
+      <c r="P128" s="18" t="n"/>
+      <c r="Q128" s="19">
+        <f>IF(N128&lt;&gt;"ja","",IF(O128="",H128,O128)*J128)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129" ht="78" customHeight="1">
+      <c r="A129" s="20" t="n">
+        <v>122</v>
+      </c>
+      <c r="B129" s="21" t="inlineStr">
+        <is>
+          <t>NU03-04</t>
+        </is>
+      </c>
+      <c r="C129" s="22" t="n"/>
+      <c r="D129" s="23" t="inlineStr">
+        <is>
+          <t>Wesco Bügelbrett und Wäscheständer, Kindergröße
+Kinder-Bügelbrett von Wesco aus Birke-Multiplex mit gelbem Aufdruck, klappbar, sowie ein passender Wäscheständer aus Holz mit Schnüren.</t>
+        </is>
+      </c>
+      <c r="E129" s="13" t="n"/>
+      <c r="F129" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 4</t>
+        </is>
+      </c>
+      <c r="G129" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H129" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I129" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J129" s="24" t="n">
+        <v>35</v>
+      </c>
+      <c r="K129" s="25">
+        <f>J129*1.19</f>
+        <v/>
+      </c>
+      <c r="L129" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M129" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N129" s="16" t="n"/>
+      <c r="O129" s="17" t="n"/>
+      <c r="P129" s="18" t="n"/>
+      <c r="Q129" s="26">
+        <f>IF(N129&lt;&gt;"ja","",IF(O129="",H129,O129)*J129)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130" ht="78" customHeight="1">
+      <c r="A130" s="9" t="n">
+        <v>123</v>
+      </c>
+      <c r="B130" s="10" t="inlineStr">
+        <is>
+          <t>NU03-05</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="n"/>
+      <c r="D130" s="12" t="inlineStr">
+        <is>
+          <t>Flumi Kindersessel, beige Bouclé
+Kindersessel von Flumi, beigefarbener Bouclé-Bezug, runde Form mit zwei kleinen Ohren an der Lehne. Markenetikett an der Vorderseite.</t>
+        </is>
+      </c>
+      <c r="E130" s="13" t="n"/>
+      <c r="F130" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 4</t>
+        </is>
+      </c>
+      <c r="G130" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H130" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I130" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J130" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="K130" s="15">
+        <f>J130*1.19</f>
+        <v/>
+      </c>
+      <c r="L130" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M130" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N130" s="16" t="n"/>
+      <c r="O130" s="17" t="n"/>
+      <c r="P130" s="18" t="n"/>
+      <c r="Q130" s="19">
+        <f>IF(N130&lt;&gt;"ja","",IF(O130="",H130,O130)*J130)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131" ht="78" customHeight="1">
+      <c r="A131" s="20" t="n">
+        <v>124</v>
+      </c>
+      <c r="B131" s="21" t="inlineStr">
+        <is>
+          <t>NU03-06</t>
+        </is>
+      </c>
+      <c r="C131" s="22" t="n"/>
+      <c r="D131" s="23" t="inlineStr">
+        <is>
+          <t>Wandregal Kiefer mit Fächern
+Wandregal aus Kiefer massiv mit eingenuteten Trennbrettern, drei Fächer.</t>
+        </is>
+      </c>
+      <c r="E131" s="13" t="n"/>
+      <c r="F131" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 4</t>
+        </is>
+      </c>
+      <c r="G131" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H131" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I131" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J131" s="24" t="n">
+        <v>35</v>
+      </c>
+      <c r="K131" s="25">
+        <f>J131*1.19</f>
+        <v/>
+      </c>
+      <c r="L131" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M131" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N131" s="16" t="n"/>
+      <c r="O131" s="17" t="n"/>
+      <c r="P131" s="18" t="n"/>
+      <c r="Q131" s="26">
+        <f>IF(N131&lt;&gt;"ja","",IF(O131="",H131,O131)*J131)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132" ht="78" customHeight="1">
+      <c r="A132" s="9" t="n">
+        <v>125</v>
+      </c>
+      <c r="B132" s="10" t="inlineStr">
+        <is>
+          <t>NU03-07</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="n"/>
+      <c r="D132" s="12" t="inlineStr">
+        <is>
+          <t>Offenes Regal Kiefer, drei Fächer
+Niedriges offenes Regal aus Kiefer massiv mit eingenuteten Trennbrettern, drei Fächer, zum Stellen oder Stapeln.</t>
+        </is>
+      </c>
+      <c r="E132" s="13" t="n"/>
+      <c r="F132" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 4</t>
+        </is>
+      </c>
+      <c r="G132" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H132" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I132" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J132" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="K132" s="15">
+        <f>J132*1.19</f>
+        <v/>
+      </c>
+      <c r="L132" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M132" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N132" s="16" t="n"/>
+      <c r="O132" s="17" t="n"/>
+      <c r="P132" s="18" t="n"/>
+      <c r="Q132" s="19">
+        <f>IF(N132&lt;&gt;"ja","",IF(O132="",H132,O132)*J132)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133" ht="78" customHeight="1">
+      <c r="A133" s="20" t="n">
+        <v>126</v>
+      </c>
+      <c r="B133" s="21" t="inlineStr">
+        <is>
+          <t>NU03-08</t>
+        </is>
+      </c>
+      <c r="C133" s="22" t="n"/>
+      <c r="D133" s="23" t="inlineStr">
+        <is>
+          <t>IKEA Malm Kommode, 3 Schubladen, weiß
+Kommode IKEA Malm in Weiß mit drei Schubladen, griffmuldenlos. Fronten mit Beschriftungsaufklebern, die sich abziehen lassen.</t>
+        </is>
+      </c>
+      <c r="E133" s="13" t="n"/>
+      <c r="F133" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 4</t>
+        </is>
+      </c>
+      <c r="G133" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H133" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I133" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J133" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="K133" s="25">
+        <f>J133*1.19</f>
+        <v/>
+      </c>
+      <c r="L133" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M133" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N133" s="16" t="n"/>
+      <c r="O133" s="17" t="n"/>
+      <c r="P133" s="18" t="n"/>
+      <c r="Q133" s="26">
+        <f>IF(N133&lt;&gt;"ja","",IF(O133="",H133,O133)*J133)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134" ht="78" customHeight="1">
+      <c r="A134" s="9" t="n">
+        <v>127</v>
+      </c>
+      <c r="B134" s="10" t="inlineStr">
+        <is>
+          <t>NU03-09</t>
+        </is>
+      </c>
+      <c r="C134" s="11" t="n"/>
+      <c r="D134" s="12" t="inlineStr">
+        <is>
+          <t>Treppenregal Kiefer mit Wannen
+Stufenförmiges Regal aus Kiefer massiv mit eingehängten Kunststoffwannen, als Raumteiler und Spielzeugaufbewahrung genutzt.</t>
+        </is>
+      </c>
+      <c r="E134" s="13" t="n"/>
+      <c r="F134" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 4</t>
+        </is>
+      </c>
+      <c r="G134" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H134" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I134" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J134" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="K134" s="15">
+        <f>J134*1.19</f>
+        <v/>
+      </c>
+      <c r="L134" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M134" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N134" s="16" t="n"/>
+      <c r="O134" s="17" t="n"/>
+      <c r="P134" s="18" t="n"/>
+      <c r="Q134" s="19">
+        <f>IF(N134&lt;&gt;"ja","",IF(O134="",H134,O134)*J134)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135" ht="78" customHeight="1">
+      <c r="A135" s="20" t="n">
+        <v>128</v>
+      </c>
+      <c r="B135" s="21" t="inlineStr">
+        <is>
+          <t>NU03-10</t>
+        </is>
+      </c>
+      <c r="C135" s="22" t="n"/>
+      <c r="D135" s="23" t="inlineStr">
+        <is>
+          <t>Kinderhochstuhl Kunststoff mit Gurt
+Hochstuhl mit weißer Kunststoffschale, grauen Stahlbeinen und Sicherheitsgurt. Ohne Esstablett.</t>
+        </is>
+      </c>
+      <c r="E135" s="13" t="n"/>
+      <c r="F135" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 4</t>
+        </is>
+      </c>
+      <c r="G135" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H135" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="I135" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J135" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="K135" s="25">
+        <f>J135*1.19</f>
+        <v/>
+      </c>
+      <c r="L135" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M135" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N135" s="16" t="n"/>
+      <c r="O135" s="17" t="n"/>
+      <c r="P135" s="18" t="n"/>
+      <c r="Q135" s="26">
+        <f>IF(N135&lt;&gt;"ja","",IF(O135="",H135,O135)*J135)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137" ht="24" customHeight="1">
+      <c r="A137" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B128" s="1" t="n"/>
-      <c r="C128" s="1" t="n"/>
-      <c r="D128" s="1" t="n"/>
-      <c r="E128" s="1" t="n"/>
-      <c r="F128" s="1" t="n"/>
-      <c r="G128" s="1" t="n"/>
-      <c r="H128" s="1" t="n"/>
-      <c r="I128" s="1" t="n"/>
-      <c r="J128" s="1" t="n"/>
-      <c r="K128" s="1" t="n"/>
-      <c r="L128" s="1" t="n"/>
-      <c r="M128" s="1" t="n"/>
-      <c r="N128" s="1" t="n"/>
-      <c r="O128" s="1" t="n"/>
-      <c r="P128" s="1" t="n"/>
-      <c r="Q128" s="1" t="n"/>
-    </row>
-    <row r="129" ht="22" customHeight="1">
-      <c r="A129" s="37" t="inlineStr">
+      <c r="B137" s="1" t="n"/>
+      <c r="C137" s="1" t="n"/>
+      <c r="D137" s="1" t="n"/>
+      <c r="E137" s="1" t="n"/>
+      <c r="F137" s="1" t="n"/>
+      <c r="G137" s="1" t="n"/>
+      <c r="H137" s="1" t="n"/>
+      <c r="I137" s="1" t="n"/>
+      <c r="J137" s="1" t="n"/>
+      <c r="K137" s="1" t="n"/>
+      <c r="L137" s="1" t="n"/>
+      <c r="M137" s="1" t="n"/>
+      <c r="N137" s="1" t="n"/>
+      <c r="O137" s="1" t="n"/>
+      <c r="P137" s="1" t="n"/>
+      <c r="Q137" s="1" t="n"/>
+    </row>
+    <row r="138" ht="22" customHeight="1">
+      <c r="A138" s="37" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl netto</t>
         </is>
       </c>
-      <c r="Q129" s="38">
-        <f>SUM(Q8:Q126)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130" ht="22" customHeight="1">
-      <c r="A130" s="37" t="inlineStr">
+      <c r="Q138" s="38">
+        <f>SUM(Q8:Q135)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139" ht="22" customHeight="1">
+      <c r="A139" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q130" s="38">
-        <f>Q129*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131" ht="26" customHeight="1">
-      <c r="A131" s="39" t="inlineStr">
+      <c r="Q139" s="38">
+        <f>Q138*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" ht="26" customHeight="1">
+      <c r="A140" s="39" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl brutto</t>
         </is>
       </c>
-      <c r="Q131" s="40">
-        <f>Q129+Q130</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132" ht="22" customHeight="1">
-      <c r="A132" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q132" s="41">
-        <f>COUNTIF(N8:N126,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="24" customHeight="1">
-      <c r="A135" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B135" s="44" t="n"/>
-      <c r="C135" s="44" t="n"/>
-      <c r="D135" s="44" t="n"/>
-      <c r="E135" s="44" t="n"/>
-      <c r="F135" s="44" t="n"/>
-      <c r="G135" s="44" t="n"/>
-      <c r="H135" s="44" t="n"/>
-      <c r="I135" s="44" t="n"/>
-      <c r="J135" s="44" t="n"/>
-      <c r="K135" s="44" t="n"/>
-      <c r="L135" s="44" t="n"/>
-      <c r="M135" s="44" t="n"/>
-      <c r="N135" s="44" t="n"/>
-      <c r="O135" s="44" t="n"/>
-      <c r="P135" s="44" t="n"/>
-      <c r="Q135" s="44" t="n"/>
-    </row>
-    <row r="136" ht="22" customHeight="1">
-      <c r="A136" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
-        </is>
-      </c>
-      <c r="Q136" s="38">
-        <f>SUMPRODUCT(H8:H126,J8:J126)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137" ht="22" customHeight="1">
-      <c r="A137" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q137" s="38">
-        <f>Q136*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="138" ht="22" customHeight="1">
-      <c r="A138" s="45" t="inlineStr">
-        <is>
-          <t>Gesamtwert brutto</t>
-        </is>
-      </c>
-      <c r="Q138" s="46">
-        <f>Q136+Q137</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140" ht="24" customHeight="1">
-      <c r="A140" s="47" t="inlineStr">
-        <is>
-          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B140" s="48" t="n"/>
-      <c r="C140" s="48" t="n"/>
-      <c r="D140" s="48" t="n"/>
-      <c r="E140" s="48" t="n"/>
-      <c r="F140" s="48" t="n"/>
-      <c r="G140" s="48" t="n"/>
-      <c r="H140" s="48" t="n"/>
-      <c r="I140" s="48" t="n"/>
-      <c r="J140" s="48" t="n"/>
-      <c r="K140" s="48" t="n"/>
-      <c r="L140" s="48" t="n"/>
-      <c r="M140" s="48" t="n"/>
-      <c r="N140" s="48" t="n"/>
-      <c r="O140" s="48" t="n"/>
-      <c r="P140" s="48" t="n"/>
-      <c r="Q140" s="48" t="n"/>
+      <c r="Q140" s="40">
+        <f>Q138+Q139</f>
+        <v/>
+      </c>
     </row>
     <row r="141" ht="22" customHeight="1">
       <c r="A141" s="37" t="inlineStr">
         <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q141" s="41">
+        <f>COUNTIF(N8:N135,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="24" customHeight="1">
+      <c r="A144" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B144" s="44" t="n"/>
+      <c r="C144" s="44" t="n"/>
+      <c r="D144" s="44" t="n"/>
+      <c r="E144" s="44" t="n"/>
+      <c r="F144" s="44" t="n"/>
+      <c r="G144" s="44" t="n"/>
+      <c r="H144" s="44" t="n"/>
+      <c r="I144" s="44" t="n"/>
+      <c r="J144" s="44" t="n"/>
+      <c r="K144" s="44" t="n"/>
+      <c r="L144" s="44" t="n"/>
+      <c r="M144" s="44" t="n"/>
+      <c r="N144" s="44" t="n"/>
+      <c r="O144" s="44" t="n"/>
+      <c r="P144" s="44" t="n"/>
+      <c r="Q144" s="44" t="n"/>
+    </row>
+    <row r="145" ht="22" customHeight="1">
+      <c r="A145" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q145" s="38">
+        <f>SUMPRODUCT(H8:H135,J8:J135)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" ht="22" customHeight="1">
+      <c r="A146" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q146" s="38">
+        <f>Q145*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147" ht="22" customHeight="1">
+      <c r="A147" s="45" t="inlineStr">
+        <is>
+          <t>Gesamtwert brutto</t>
+        </is>
+      </c>
+      <c r="Q147" s="46">
+        <f>Q145+Q146</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" ht="24" customHeight="1">
+      <c r="A149" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B149" s="48" t="n"/>
+      <c r="C149" s="48" t="n"/>
+      <c r="D149" s="48" t="n"/>
+      <c r="E149" s="48" t="n"/>
+      <c r="F149" s="48" t="n"/>
+      <c r="G149" s="48" t="n"/>
+      <c r="H149" s="48" t="n"/>
+      <c r="I149" s="48" t="n"/>
+      <c r="J149" s="48" t="n"/>
+      <c r="K149" s="48" t="n"/>
+      <c r="L149" s="48" t="n"/>
+      <c r="M149" s="48" t="n"/>
+      <c r="N149" s="48" t="n"/>
+      <c r="O149" s="48" t="n"/>
+      <c r="P149" s="48" t="n"/>
+      <c r="Q149" s="48" t="n"/>
+    </row>
+    <row r="150" ht="22" customHeight="1">
+      <c r="A150" s="37" t="inlineStr">
+        <is>
           <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
         </is>
       </c>
-      <c r="Q141" s="38">
-        <f>-Q136*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142" ht="22" customHeight="1">
-      <c r="A142" s="45" t="inlineStr">
+      <c r="Q150" s="38">
+        <f>-Q145*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" ht="22" customHeight="1">
+      <c r="A151" s="45" t="inlineStr">
         <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="Q142" s="46">
-        <f>Q136+Q141</f>
-        <v/>
-      </c>
-    </row>
-    <row r="143" ht="22" customHeight="1">
-      <c r="A143" s="37" t="inlineStr">
+      <c r="Q151" s="46">
+        <f>Q145+Q150</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152" ht="22" customHeight="1">
+      <c r="A152" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q143" s="38">
-        <f>Q142*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="144" ht="26" customHeight="1">
-      <c r="A144" s="39" t="inlineStr">
+      <c r="Q152" s="38">
+        <f>Q151*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153" ht="26" customHeight="1">
+      <c r="A153" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q144" s="40">
-        <f>Q142+Q143</f>
-        <v/>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="42" t="inlineStr">
+      <c r="Q153" s="40">
+        <f>Q151+Q152</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="49" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="148"/>
-    <row r="149"/>
-    <row r="150"/>
+    <row r="157"/>
+    <row r="158"/>
+    <row r="159"/>
   </sheetData>
-  <autoFilter ref="A7:Q126"/>
+  <autoFilter ref="A7:Q135"/>
   <mergeCells count="26">
     <mergeCell ref="C1:Q1"/>
     <mergeCell ref="A141:P141"/>
-    <mergeCell ref="A144:P144"/>
-    <mergeCell ref="A131:P131"/>
+    <mergeCell ref="A150:P150"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A140:P140"/>
+    <mergeCell ref="A142:Q142"/>
+    <mergeCell ref="A147:P147"/>
     <mergeCell ref="L4:Q4"/>
+    <mergeCell ref="A152:P152"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A147:Q150"/>
-    <mergeCell ref="A143:P143"/>
-    <mergeCell ref="A130:P130"/>
-    <mergeCell ref="A128:Q128"/>
-    <mergeCell ref="A133:Q133"/>
-    <mergeCell ref="A142:P142"/>
-    <mergeCell ref="A145:Q145"/>
+    <mergeCell ref="A156:Q159"/>
+    <mergeCell ref="A137:Q137"/>
+    <mergeCell ref="A149:Q149"/>
     <mergeCell ref="A138:P138"/>
-    <mergeCell ref="A132:P132"/>
+    <mergeCell ref="A154:Q154"/>
+    <mergeCell ref="A146:P146"/>
     <mergeCell ref="C4:I4"/>
+    <mergeCell ref="A153:P153"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A137:P137"/>
-    <mergeCell ref="A135:Q135"/>
-    <mergeCell ref="A140:Q140"/>
-    <mergeCell ref="A136:P136"/>
+    <mergeCell ref="A144:Q144"/>
+    <mergeCell ref="A145:P145"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A129:P129"/>
+    <mergeCell ref="A139:P139"/>
+    <mergeCell ref="A151:P151"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q126">
+  <conditionalFormatting sqref="A8:Q135">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N126" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N135" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O126" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O135" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -11304,7 +11304,7 @@
       <c r="D127" s="23" t="inlineStr">
         <is>
           <t>Stockbett weiß mit Absturzsicherung
-Etagenbett in Weiß mit sichtbaren Multiplex-Kanten, abgerundeten Ausschnitten und durchgehender Absturzsicherung oben. Solide Bauweise aus dem Kita-Betrieb.</t>
+Etagenbett in Weiß mit sichtbaren Multiplex-Kanten, abgerundeten Ausschnitten und durchgehender Absturzsicherung oben. Solide Bauweise aus dem Kita-Betrieb. Die Matratzen können auf Wunsch mitgenommen werden.</t>
         </is>
       </c>
       <c r="E127" s="13" t="n"/>
@@ -11363,8 +11363,8 @@
       <c r="C128" s="11" t="n"/>
       <c r="D128" s="12" t="inlineStr">
         <is>
-          <t>Wesco Spielküche, mehrteilig
-Spielküche von Wesco aus Birke-Multiplex: Spülmodul mit Becken, Kochmodul mit Drehknöpfen, Backofenmodul mit Sichtfenster sowie Kühl- und Gefriermodule. Weiße Fronten mit Holzgriffen, Module einzeln stellbar.</t>
+          <t>Wesco Spielküche, 5 Module
+Spielküche von Wesco aus Birke-Multiplex, fünf Module: Spüle mit Becken, Kochfeld mit Drehknöpfen, Backofen mit Sichtfenster sowie Kühl- und Gefriermodul. Weiße Fronten mit Holzgriffen, die Module stehen frei und sind einzeln aufstellbar.</t>
         </is>
       </c>
       <c r="E128" s="13" t="n"/>
@@ -11783,8 +11783,8 @@
       <c r="C135" s="22" t="n"/>
       <c r="D135" s="23" t="inlineStr">
         <is>
-          <t>Kinderhochstuhl Kunststoff mit Gurt
-Hochstuhl mit weißer Kunststoffschale, grauen Stahlbeinen und Sicherheitsgurt. Ohne Esstablett.</t>
+          <t>IKEA Kinderhochstuhl mit Gurt
+Kinderhochstuhl von IKEA: weiße Kunststoffschale, graue Stahlbeine, Sicherheitsgurt. Ohne Esstablett.</t>
         </is>
       </c>
       <c r="E135" s="13" t="n"/>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$150</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3643,6 +3643,381 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>135</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="130" name="Image 130" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId130"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>136</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="131" name="Image 131" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId131"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>137</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="132" name="Image 132" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId132"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>138</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="133" name="Image 133" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId133"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>139</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="134" name="Image 134" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId134"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>140</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="135" name="Image 135" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId135"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>141</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="136" name="Image 136" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId136"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>142</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="137" name="Image 137" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId137"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>143</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="138" name="Image 138" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId138"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>144</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="139" name="Image 139" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId139"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>145</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="140" name="Image 140" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId140"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>146</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="141" name="Image 141" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId141"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>147</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="142" name="Image 142" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId142"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>148</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="143" name="Image 143" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId143"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>149</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="144" name="Image 144" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId144"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -3935,7 +4310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q159"/>
+  <dimension ref="A1:Q174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -8659,10 +9034,14 @@
       <c r="D83" s="23" t="inlineStr">
         <is>
           <t>Hochflorteppich beige
-Shaggy/Hochflor, beige, ca. 200 x 300 cm, gereinigt</t>
-        </is>
-      </c>
-      <c r="E83" s="13" t="n"/>
+Hochflorteppich in Beige, IKEA Ådum. Gereinigt.</t>
+        </is>
+      </c>
+      <c r="E83" s="13" t="inlineStr">
+        <is>
+          <t>120 × 240 cm</t>
+        </is>
+      </c>
       <c r="F83" s="23" t="inlineStr">
         <is>
           <t>Schlafraum 5</t>
@@ -8719,10 +9098,14 @@
       <c r="D84" s="12" t="inlineStr">
         <is>
           <t>Teppich schwarz-weiß Rautenmuster
-Flachgewebe, Rautenmuster schwarz/weiß, ca. 200 x 300 cm</t>
-        </is>
-      </c>
-      <c r="E84" s="13" t="n"/>
+Flachgewebter Teppich mit schwarz-weißem Rautenmuster, IKEA Lappljung Ruta.</t>
+        </is>
+      </c>
+      <c r="E84" s="13" t="inlineStr">
+        <is>
+          <t>200 × 300 cm</t>
+        </is>
+      </c>
       <c r="F84" s="12" t="inlineStr">
         <is>
           <t>Schlafraum 5</t>
@@ -10059,7 +10442,7 @@
         </is>
       </c>
       <c r="H106" s="10" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I106" s="10" t="inlineStr">
         <is>
@@ -11831,261 +12214,1161 @@
         <v/>
       </c>
     </row>
-    <row r="137" ht="24" customHeight="1">
-      <c r="A137" s="36" t="inlineStr">
+    <row r="136" ht="78" customHeight="1">
+      <c r="A136" s="9" t="n">
+        <v>129</v>
+      </c>
+      <c r="B136" s="10" t="inlineStr">
+        <is>
+          <t>NU04-07</t>
+        </is>
+      </c>
+      <c r="C136" s="11" t="n"/>
+      <c r="D136" s="12" t="inlineStr">
+        <is>
+          <t>IKEA Agam Kinderstuhl, schwarz
+Kinderstuhl IKEA Agam aus Massivholz, schwarz lackiert, mit Sprossenlehne. Etikett an der Unterseite: Agam, Herstelldatum 2019. Sitzfläche mit Kratzern.</t>
+        </is>
+      </c>
+      <c r="E136" s="13" t="n"/>
+      <c r="F136" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="G136" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H136" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="I136" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J136" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="K136" s="15">
+        <f>J136*1.19</f>
+        <v/>
+      </c>
+      <c r="L136" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M136" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N136" s="16" t="n"/>
+      <c r="O136" s="17" t="n"/>
+      <c r="P136" s="18" t="n"/>
+      <c r="Q136" s="19">
+        <f>IF(N136&lt;&gt;"ja","",IF(O136="",H136,O136)*J136)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137" ht="78" customHeight="1">
+      <c r="A137" s="20" t="n">
+        <v>130</v>
+      </c>
+      <c r="B137" s="21" t="inlineStr">
+        <is>
+          <t>NU04-08</t>
+        </is>
+      </c>
+      <c r="C137" s="22" t="n"/>
+      <c r="D137" s="23" t="inlineStr">
+        <is>
+          <t>IKEA Urban Kinderstuhl, Kunststoff
+Kinderstuhl IKEA Urban, Sitzschale aus Kunststoff mit Fußstütze am Gestell. Etikett an der Unterseite: Urban, 001.652.13.</t>
+        </is>
+      </c>
+      <c r="E137" s="13" t="n"/>
+      <c r="F137" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="G137" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H137" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I137" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J137" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="K137" s="25">
+        <f>J137*1.19</f>
+        <v/>
+      </c>
+      <c r="L137" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M137" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N137" s="16" t="n"/>
+      <c r="O137" s="17" t="n"/>
+      <c r="P137" s="18" t="n"/>
+      <c r="Q137" s="26">
+        <f>IF(N137&lt;&gt;"ja","",IF(O137="",H137,O137)*J137)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138" ht="78" customHeight="1">
+      <c r="A138" s="9" t="n">
+        <v>131</v>
+      </c>
+      <c r="B138" s="10" t="inlineStr">
+        <is>
+          <t>NU04-09</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="n"/>
+      <c r="D138" s="12" t="inlineStr">
+        <is>
+          <t>IKEA Regal weiß, 8 Fächer
+Regal IKEA in Weiß mit acht Fächern, liegend oder stehend nutzbar.</t>
+        </is>
+      </c>
+      <c r="E138" s="13" t="n"/>
+      <c r="F138" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="G138" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H138" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I138" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J138" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="K138" s="15">
+        <f>J138*1.19</f>
+        <v/>
+      </c>
+      <c r="L138" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M138" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N138" s="16" t="n"/>
+      <c r="O138" s="17" t="n"/>
+      <c r="P138" s="18" t="n"/>
+      <c r="Q138" s="19">
+        <f>IF(N138&lt;&gt;"ja","",IF(O138="",H138,O138)*J138)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139" ht="78" customHeight="1">
+      <c r="A139" s="20" t="n">
+        <v>132</v>
+      </c>
+      <c r="B139" s="21" t="inlineStr">
+        <is>
+          <t>NU04-10</t>
+        </is>
+      </c>
+      <c r="C139" s="22" t="n"/>
+      <c r="D139" s="23" t="inlineStr">
+        <is>
+          <t>Schalenstuhl mit Sitzpolster und Holzbeinen
+Schalenstuhl mit grauer Kunststoffschale, hellem Sitzpolster und konischen Beinen aus massivem Holz.</t>
+        </is>
+      </c>
+      <c r="E139" s="13" t="n"/>
+      <c r="F139" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="G139" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H139" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I139" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J139" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="K139" s="25">
+        <f>J139*1.19</f>
+        <v/>
+      </c>
+      <c r="L139" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M139" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N139" s="16" t="n"/>
+      <c r="O139" s="17" t="n"/>
+      <c r="P139" s="18" t="n"/>
+      <c r="Q139" s="26">
+        <f>IF(N139&lt;&gt;"ja","",IF(O139="",H139,O139)*J139)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" ht="78" customHeight="1">
+      <c r="A140" s="9" t="n">
+        <v>133</v>
+      </c>
+      <c r="B140" s="10" t="inlineStr">
+        <is>
+          <t>NU04-11</t>
+        </is>
+      </c>
+      <c r="C140" s="11" t="n"/>
+      <c r="D140" s="12" t="inlineStr">
+        <is>
+          <t>IKEA Stuva Tisch weiß
+Tisch beziehungsweise Sitzbank IKEA Stuva in Weiß mit Seitenwangen und Gleitern. Etikett an der Unterseite: Stuva.</t>
+        </is>
+      </c>
+      <c r="E140" s="13" t="n"/>
+      <c r="F140" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="G140" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H140" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I140" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J140" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K140" s="15">
+        <f>J140*1.19</f>
+        <v/>
+      </c>
+      <c r="L140" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M140" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N140" s="16" t="n"/>
+      <c r="O140" s="17" t="n"/>
+      <c r="P140" s="18" t="n"/>
+      <c r="Q140" s="19">
+        <f>IF(N140&lt;&gt;"ja","",IF(O140="",H140,O140)*J140)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" ht="78" customHeight="1">
+      <c r="A141" s="20" t="n">
+        <v>134</v>
+      </c>
+      <c r="B141" s="21" t="inlineStr">
+        <is>
+          <t>NU04-13</t>
+        </is>
+      </c>
+      <c r="C141" s="22" t="n"/>
+      <c r="D141" s="23" t="inlineStr">
+        <is>
+          <t>Kindertisch rund weiß mit Holzbeinen
+Runder Kindertisch, weiße Platte auf konischen Beinen aus massivem Holz. Die Plattenkante ist an einer Stelle beschädigt und dunkel abgestoßen.</t>
+        </is>
+      </c>
+      <c r="E141" s="13" t="n"/>
+      <c r="F141" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="G141" s="21" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="H141" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I141" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J141" s="24" t="n">
+        <v>45</v>
+      </c>
+      <c r="K141" s="25">
+        <f>J141*1.19</f>
+        <v/>
+      </c>
+      <c r="L141" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M141" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N141" s="16" t="n"/>
+      <c r="O141" s="17" t="n"/>
+      <c r="P141" s="18" t="n"/>
+      <c r="Q141" s="26">
+        <f>IF(N141&lt;&gt;"ja","",IF(O141="",H141,O141)*J141)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142" ht="78" customHeight="1">
+      <c r="A142" s="9" t="n">
+        <v>135</v>
+      </c>
+      <c r="B142" s="10" t="inlineStr">
+        <is>
+          <t>NU04-14</t>
+        </is>
+      </c>
+      <c r="C142" s="11" t="n"/>
+      <c r="D142" s="12" t="inlineStr">
+        <is>
+          <t>Raumteiler Metallgitter, schwarz
+Freistehender Raumteiler: schwarz beschichtetes Metallgitter mit Rautenmuster auf ovalem Standfuß. Auch als Rankgitter oder zum Aufhängen nutzbar.</t>
+        </is>
+      </c>
+      <c r="E142" s="13" t="n"/>
+      <c r="F142" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="G142" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H142" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I142" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J142" s="14" t="n">
+        <v>50</v>
+      </c>
+      <c r="K142" s="15">
+        <f>J142*1.19</f>
+        <v/>
+      </c>
+      <c r="L142" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M142" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N142" s="16" t="n"/>
+      <c r="O142" s="17" t="n"/>
+      <c r="P142" s="18" t="n"/>
+      <c r="Q142" s="19">
+        <f>IF(N142&lt;&gt;"ja","",IF(O142="",H142,O142)*J142)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143" ht="78" customHeight="1">
+      <c r="A143" s="20" t="n">
+        <v>136</v>
+      </c>
+      <c r="B143" s="21" t="inlineStr">
+        <is>
+          <t>NU04-15</t>
+        </is>
+      </c>
+      <c r="C143" s="22" t="n"/>
+      <c r="D143" s="23" t="inlineStr">
+        <is>
+          <t>IKEA Regal weiß, 3 Fächer, schmal
+Schmales hohes Regal IKEA in Weiß mit drei Fächern.</t>
+        </is>
+      </c>
+      <c r="E143" s="13" t="n"/>
+      <c r="F143" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="G143" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H143" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I143" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J143" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="K143" s="25">
+        <f>J143*1.19</f>
+        <v/>
+      </c>
+      <c r="L143" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M143" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N143" s="16" t="n"/>
+      <c r="O143" s="17" t="n"/>
+      <c r="P143" s="18" t="n"/>
+      <c r="Q143" s="26">
+        <f>IF(N143&lt;&gt;"ja","",IF(O143="",H143,O143)*J143)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144" ht="78" customHeight="1">
+      <c r="A144" s="9" t="n">
+        <v>137</v>
+      </c>
+      <c r="B144" s="10" t="inlineStr">
+        <is>
+          <t>NU04-16</t>
+        </is>
+      </c>
+      <c r="C144" s="11" t="n"/>
+      <c r="D144" s="12" t="inlineStr">
+        <is>
+          <t>Bällebad mit Bällen
+Bällebad in Quadratform: Polsterrand in Grau, Sockel in weißem Kunstleder mit Rautennaht, einschließlich der Bälle in Grau, Weiß und Bunt.</t>
+        </is>
+      </c>
+      <c r="E144" s="13" t="n"/>
+      <c r="F144" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="G144" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H144" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I144" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J144" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="K144" s="15">
+        <f>J144*1.19</f>
+        <v/>
+      </c>
+      <c r="L144" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M144" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N144" s="16" t="n"/>
+      <c r="O144" s="17" t="n"/>
+      <c r="P144" s="18" t="n"/>
+      <c r="Q144" s="19">
+        <f>IF(N144&lt;&gt;"ja","",IF(O144="",H144,O144)*J144)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145" ht="78" customHeight="1">
+      <c r="A145" s="20" t="n">
+        <v>138</v>
+      </c>
+      <c r="B145" s="21" t="inlineStr">
+        <is>
+          <t>NU04-17</t>
+        </is>
+      </c>
+      <c r="C145" s="22" t="n"/>
+      <c r="D145" s="23" t="inlineStr">
+        <is>
+          <t>Spielregal Kiefer mit Wannen und Wandaufsatz
+Werkbankhohes Gestell aus Kiefer massiv mit weißen Kunststoffwannen und durchgehender Arbeitsplatte, dazu ein passender Wandaufsatz mit sechs Wannen.</t>
+        </is>
+      </c>
+      <c r="E145" s="13" t="n"/>
+      <c r="F145" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="G145" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H145" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I145" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J145" s="24" t="n">
+        <v>70</v>
+      </c>
+      <c r="K145" s="25">
+        <f>J145*1.19</f>
+        <v/>
+      </c>
+      <c r="L145" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M145" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N145" s="16" t="n"/>
+      <c r="O145" s="17" t="n"/>
+      <c r="P145" s="18" t="n"/>
+      <c r="Q145" s="26">
+        <f>IF(N145&lt;&gt;"ja","",IF(O145="",H145,O145)*J145)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" ht="78" customHeight="1">
+      <c r="A146" s="9" t="n">
+        <v>139</v>
+      </c>
+      <c r="B146" s="10" t="inlineStr">
+        <is>
+          <t>NU04-18</t>
+        </is>
+      </c>
+      <c r="C146" s="11" t="n"/>
+      <c r="D146" s="12" t="inlineStr">
+        <is>
+          <t>Kinderwerkbank Holz mit Tafel
+Kinderwerkbank aus Holz mit Lochplatte, drei Werkzeugkästen, Tafellackfläche oben, Zollstockaufdruck an der Kante und Ablage unten.</t>
+        </is>
+      </c>
+      <c r="E146" s="13" t="n"/>
+      <c r="F146" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="G146" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H146" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I146" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J146" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K146" s="15">
+        <f>J146*1.19</f>
+        <v/>
+      </c>
+      <c r="L146" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M146" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N146" s="16" t="n"/>
+      <c r="O146" s="17" t="n"/>
+      <c r="P146" s="18" t="n"/>
+      <c r="Q146" s="19">
+        <f>IF(N146&lt;&gt;"ja","",IF(O146="",H146,O146)*J146)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147" ht="78" customHeight="1">
+      <c r="A147" s="20" t="n">
+        <v>140</v>
+      </c>
+      <c r="B147" s="21" t="inlineStr">
+        <is>
+          <t>NU04-19</t>
+        </is>
+      </c>
+      <c r="C147" s="22" t="n"/>
+      <c r="D147" s="23" t="inlineStr">
+        <is>
+          <t>IKEA Kleiderschrank weiß mit drei Böden
+Hoher Schrank IKEA in Weiß mit zwei Türen, ovalen Griffmulden und drei Einlegeböden.</t>
+        </is>
+      </c>
+      <c r="E147" s="13" t="n"/>
+      <c r="F147" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="G147" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H147" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I147" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J147" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="K147" s="25">
+        <f>J147*1.19</f>
+        <v/>
+      </c>
+      <c r="L147" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M147" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N147" s="16" t="n"/>
+      <c r="O147" s="17" t="n"/>
+      <c r="P147" s="18" t="n"/>
+      <c r="Q147" s="26">
+        <f>IF(N147&lt;&gt;"ja","",IF(O147="",H147,O147)*J147)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" ht="78" customHeight="1">
+      <c r="A148" s="9" t="n">
+        <v>141</v>
+      </c>
+      <c r="B148" s="35" t="inlineStr">
+        <is>
+          <t>NU04-20</t>
+        </is>
+      </c>
+      <c r="C148" s="11" t="n"/>
+      <c r="D148" s="12" t="inlineStr">
+        <is>
+          <t>Freischwinger schwarz, Kunststoff
+Freischwinger aus einem Stück Kunststoff, schwarz matt, S-förmig geschwungen. Erwachsenengröße.</t>
+        </is>
+      </c>
+      <c r="E148" s="13" t="n"/>
+      <c r="F148" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="G148" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H148" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I148" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J148" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="K148" s="15">
+        <f>J148*1.19</f>
+        <v/>
+      </c>
+      <c r="L148" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M148" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N148" s="16" t="n"/>
+      <c r="O148" s="17" t="n"/>
+      <c r="P148" s="18" t="n"/>
+      <c r="Q148" s="19">
+        <f>IF(N148&lt;&gt;"ja","",IF(O148="",H148,O148)*J148)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" ht="78" customHeight="1">
+      <c r="A149" s="20" t="n">
+        <v>142</v>
+      </c>
+      <c r="B149" s="21" t="inlineStr">
+        <is>
+          <t>NU04-21</t>
+        </is>
+      </c>
+      <c r="C149" s="22" t="n"/>
+      <c r="D149" s="23" t="inlineStr">
+        <is>
+          <t>Spieltisch Kiefer mit abnehmbaren Platten
+Tisch aus Kiefer massiv mit zwei abnehmbaren weißen Kunststoffplatten. Darunter lässt sich eine Wanne einsetzen, im Haus für Bausteine und Sandspiel genutzt.</t>
+        </is>
+      </c>
+      <c r="E149" s="13" t="n"/>
+      <c r="F149" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="G149" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H149" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I149" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J149" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="K149" s="25">
+        <f>J149*1.19</f>
+        <v/>
+      </c>
+      <c r="L149" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M149" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N149" s="16" t="n"/>
+      <c r="O149" s="17" t="n"/>
+      <c r="P149" s="18" t="n"/>
+      <c r="Q149" s="26">
+        <f>IF(N149&lt;&gt;"ja","",IF(O149="",H149,O149)*J149)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" ht="78" customHeight="1">
+      <c r="A150" s="9" t="n">
+        <v>143</v>
+      </c>
+      <c r="B150" s="10" t="inlineStr">
+        <is>
+          <t>NU04-22</t>
+        </is>
+      </c>
+      <c r="C150" s="11" t="n"/>
+      <c r="D150" s="12" t="inlineStr">
+        <is>
+          <t>Wandregal weiß, schmal
+Schmales weißes Wandregal, sichtbar verschraubt.</t>
+        </is>
+      </c>
+      <c r="E150" s="13" t="n"/>
+      <c r="F150" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 5</t>
+        </is>
+      </c>
+      <c r="G150" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H150" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I150" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J150" s="14" t="n">
+        <v>10</v>
+      </c>
+      <c r="K150" s="15">
+        <f>J150*1.19</f>
+        <v/>
+      </c>
+      <c r="L150" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M150" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N150" s="16" t="n"/>
+      <c r="O150" s="17" t="n"/>
+      <c r="P150" s="18" t="n"/>
+      <c r="Q150" s="19">
+        <f>IF(N150&lt;&gt;"ja","",IF(O150="",H150,O150)*J150)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152" ht="24" customHeight="1">
+      <c r="A152" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B137" s="1" t="n"/>
-      <c r="C137" s="1" t="n"/>
-      <c r="D137" s="1" t="n"/>
-      <c r="E137" s="1" t="n"/>
-      <c r="F137" s="1" t="n"/>
-      <c r="G137" s="1" t="n"/>
-      <c r="H137" s="1" t="n"/>
-      <c r="I137" s="1" t="n"/>
-      <c r="J137" s="1" t="n"/>
-      <c r="K137" s="1" t="n"/>
-      <c r="L137" s="1" t="n"/>
-      <c r="M137" s="1" t="n"/>
-      <c r="N137" s="1" t="n"/>
-      <c r="O137" s="1" t="n"/>
-      <c r="P137" s="1" t="n"/>
-      <c r="Q137" s="1" t="n"/>
-    </row>
-    <row r="138" ht="22" customHeight="1">
-      <c r="A138" s="37" t="inlineStr">
+      <c r="B152" s="1" t="n"/>
+      <c r="C152" s="1" t="n"/>
+      <c r="D152" s="1" t="n"/>
+      <c r="E152" s="1" t="n"/>
+      <c r="F152" s="1" t="n"/>
+      <c r="G152" s="1" t="n"/>
+      <c r="H152" s="1" t="n"/>
+      <c r="I152" s="1" t="n"/>
+      <c r="J152" s="1" t="n"/>
+      <c r="K152" s="1" t="n"/>
+      <c r="L152" s="1" t="n"/>
+      <c r="M152" s="1" t="n"/>
+      <c r="N152" s="1" t="n"/>
+      <c r="O152" s="1" t="n"/>
+      <c r="P152" s="1" t="n"/>
+      <c r="Q152" s="1" t="n"/>
+    </row>
+    <row r="153" ht="22" customHeight="1">
+      <c r="A153" s="37" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl netto</t>
         </is>
       </c>
-      <c r="Q138" s="38">
-        <f>SUM(Q8:Q135)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="139" ht="22" customHeight="1">
-      <c r="A139" s="37" t="inlineStr">
+      <c r="Q153" s="38">
+        <f>SUM(Q8:Q150)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154" ht="22" customHeight="1">
+      <c r="A154" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q139" s="38">
-        <f>Q138*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="140" ht="26" customHeight="1">
-      <c r="A140" s="39" t="inlineStr">
+      <c r="Q154" s="38">
+        <f>Q153*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155" ht="26" customHeight="1">
+      <c r="A155" s="39" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl brutto</t>
         </is>
       </c>
-      <c r="Q140" s="40">
-        <f>Q138+Q139</f>
-        <v/>
-      </c>
-    </row>
-    <row r="141" ht="22" customHeight="1">
-      <c r="A141" s="37" t="inlineStr">
+      <c r="Q155" s="40">
+        <f>Q153+Q154</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" ht="22" customHeight="1">
+      <c r="A156" s="37" t="inlineStr">
         <is>
           <t>gewählte Positionen</t>
         </is>
       </c>
-      <c r="Q141" s="41">
-        <f>COUNTIF(N8:N135,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="42" t="inlineStr">
+      <c r="Q156" s="41">
+        <f>COUNTIF(N8:N150,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="42" t="inlineStr">
         <is>
           <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
         </is>
       </c>
     </row>
-    <row r="144" ht="24" customHeight="1">
-      <c r="A144" s="43" t="inlineStr">
+    <row r="159" ht="24" customHeight="1">
+      <c r="A159" s="43" t="inlineStr">
         <is>
           <t>B · GESAMTBESTAND</t>
         </is>
       </c>
-      <c r="B144" s="44" t="n"/>
-      <c r="C144" s="44" t="n"/>
-      <c r="D144" s="44" t="n"/>
-      <c r="E144" s="44" t="n"/>
-      <c r="F144" s="44" t="n"/>
-      <c r="G144" s="44" t="n"/>
-      <c r="H144" s="44" t="n"/>
-      <c r="I144" s="44" t="n"/>
-      <c r="J144" s="44" t="n"/>
-      <c r="K144" s="44" t="n"/>
-      <c r="L144" s="44" t="n"/>
-      <c r="M144" s="44" t="n"/>
-      <c r="N144" s="44" t="n"/>
-      <c r="O144" s="44" t="n"/>
-      <c r="P144" s="44" t="n"/>
-      <c r="Q144" s="44" t="n"/>
-    </row>
-    <row r="145" ht="22" customHeight="1">
-      <c r="A145" s="37" t="inlineStr">
+      <c r="B159" s="44" t="n"/>
+      <c r="C159" s="44" t="n"/>
+      <c r="D159" s="44" t="n"/>
+      <c r="E159" s="44" t="n"/>
+      <c r="F159" s="44" t="n"/>
+      <c r="G159" s="44" t="n"/>
+      <c r="H159" s="44" t="n"/>
+      <c r="I159" s="44" t="n"/>
+      <c r="J159" s="44" t="n"/>
+      <c r="K159" s="44" t="n"/>
+      <c r="L159" s="44" t="n"/>
+      <c r="M159" s="44" t="n"/>
+      <c r="N159" s="44" t="n"/>
+      <c r="O159" s="44" t="n"/>
+      <c r="P159" s="44" t="n"/>
+      <c r="Q159" s="44" t="n"/>
+    </row>
+    <row r="160" ht="22" customHeight="1">
+      <c r="A160" s="37" t="inlineStr">
         <is>
           <t>Gesamtwert aller gelisteten Positionen netto</t>
         </is>
       </c>
-      <c r="Q145" s="38">
-        <f>SUMPRODUCT(H8:H135,J8:J135)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="146" ht="22" customHeight="1">
-      <c r="A146" s="37" t="inlineStr">
+      <c r="Q160" s="38">
+        <f>SUMPRODUCT(H8:H150,J8:J150)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161" ht="22" customHeight="1">
+      <c r="A161" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q146" s="38">
-        <f>Q145*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="147" ht="22" customHeight="1">
-      <c r="A147" s="45" t="inlineStr">
+      <c r="Q161" s="38">
+        <f>Q160*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162" ht="22" customHeight="1">
+      <c r="A162" s="45" t="inlineStr">
         <is>
           <t>Gesamtwert brutto</t>
         </is>
       </c>
-      <c r="Q147" s="46">
-        <f>Q145+Q146</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149" ht="24" customHeight="1">
-      <c r="A149" s="47" t="inlineStr">
+      <c r="Q162" s="46">
+        <f>Q160+Q161</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" ht="24" customHeight="1">
+      <c r="A164" s="47" t="inlineStr">
         <is>
           <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
         </is>
       </c>
-      <c r="B149" s="48" t="n"/>
-      <c r="C149" s="48" t="n"/>
-      <c r="D149" s="48" t="n"/>
-      <c r="E149" s="48" t="n"/>
-      <c r="F149" s="48" t="n"/>
-      <c r="G149" s="48" t="n"/>
-      <c r="H149" s="48" t="n"/>
-      <c r="I149" s="48" t="n"/>
-      <c r="J149" s="48" t="n"/>
-      <c r="K149" s="48" t="n"/>
-      <c r="L149" s="48" t="n"/>
-      <c r="M149" s="48" t="n"/>
-      <c r="N149" s="48" t="n"/>
-      <c r="O149" s="48" t="n"/>
-      <c r="P149" s="48" t="n"/>
-      <c r="Q149" s="48" t="n"/>
-    </row>
-    <row r="150" ht="22" customHeight="1">
-      <c r="A150" s="37" t="inlineStr">
+      <c r="B164" s="48" t="n"/>
+      <c r="C164" s="48" t="n"/>
+      <c r="D164" s="48" t="n"/>
+      <c r="E164" s="48" t="n"/>
+      <c r="F164" s="48" t="n"/>
+      <c r="G164" s="48" t="n"/>
+      <c r="H164" s="48" t="n"/>
+      <c r="I164" s="48" t="n"/>
+      <c r="J164" s="48" t="n"/>
+      <c r="K164" s="48" t="n"/>
+      <c r="L164" s="48" t="n"/>
+      <c r="M164" s="48" t="n"/>
+      <c r="N164" s="48" t="n"/>
+      <c r="O164" s="48" t="n"/>
+      <c r="P164" s="48" t="n"/>
+      <c r="Q164" s="48" t="n"/>
+    </row>
+    <row r="165" ht="22" customHeight="1">
+      <c r="A165" s="37" t="inlineStr">
         <is>
           <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
         </is>
       </c>
-      <c r="Q150" s="38">
-        <f>-Q145*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151" ht="22" customHeight="1">
-      <c r="A151" s="45" t="inlineStr">
+      <c r="Q165" s="38">
+        <f>-Q160*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" ht="22" customHeight="1">
+      <c r="A166" s="45" t="inlineStr">
         <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="Q151" s="46">
-        <f>Q145+Q150</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152" ht="22" customHeight="1">
-      <c r="A152" s="37" t="inlineStr">
+      <c r="Q166" s="46">
+        <f>Q160+Q165</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" ht="22" customHeight="1">
+      <c r="A167" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q152" s="38">
-        <f>Q151*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="153" ht="26" customHeight="1">
-      <c r="A153" s="39" t="inlineStr">
+      <c r="Q167" s="38">
+        <f>Q166*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168" ht="26" customHeight="1">
+      <c r="A168" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q153" s="40">
-        <f>Q151+Q152</f>
-        <v/>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="42" t="inlineStr">
+      <c r="Q168" s="40">
+        <f>Q166+Q167</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="49" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="157"/>
-    <row r="158"/>
-    <row r="159"/>
+    <row r="172"/>
+    <row r="173"/>
+    <row r="174"/>
   </sheetData>
-  <autoFilter ref="A7:Q135"/>
+  <autoFilter ref="A7:Q150"/>
   <mergeCells count="26">
+    <mergeCell ref="A160:P160"/>
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A141:P141"/>
-    <mergeCell ref="A150:P150"/>
+    <mergeCell ref="A157:Q157"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A140:P140"/>
-    <mergeCell ref="A142:Q142"/>
-    <mergeCell ref="A147:P147"/>
+    <mergeCell ref="A169:Q169"/>
+    <mergeCell ref="A165:P165"/>
     <mergeCell ref="L4:Q4"/>
-    <mergeCell ref="A152:P152"/>
+    <mergeCell ref="A156:P156"/>
+    <mergeCell ref="A155:P155"/>
+    <mergeCell ref="A161:P161"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A156:Q159"/>
-    <mergeCell ref="A137:Q137"/>
-    <mergeCell ref="A149:Q149"/>
-    <mergeCell ref="A138:P138"/>
-    <mergeCell ref="A154:Q154"/>
-    <mergeCell ref="A146:P146"/>
+    <mergeCell ref="A167:P167"/>
+    <mergeCell ref="A171:Q174"/>
+    <mergeCell ref="A166:P166"/>
+    <mergeCell ref="A164:Q164"/>
     <mergeCell ref="C4:I4"/>
+    <mergeCell ref="A162:P162"/>
+    <mergeCell ref="A168:P168"/>
     <mergeCell ref="A153:P153"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A144:Q144"/>
-    <mergeCell ref="A145:P145"/>
+    <mergeCell ref="A159:Q159"/>
+    <mergeCell ref="A154:P154"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A139:P139"/>
-    <mergeCell ref="A151:P151"/>
+    <mergeCell ref="A152:Q152"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q135">
+  <conditionalFormatting sqref="A8:Q150">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N135" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N150" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O135" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O150" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$157</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4018,6 +4018,181 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>150</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="145" name="Image 145" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId145"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>151</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="146" name="Image 146" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId146"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>152</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="147" name="Image 147" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId147"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>153</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="148" name="Image 148" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId148"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>154</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="149" name="Image 149" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId149"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>155</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="150" name="Image 150" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId150"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>156</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="151" name="Image 151" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId151"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -4310,7 +4485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q174"/>
+  <dimension ref="A1:Q181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -12362,7 +12537,7 @@
         </is>
       </c>
       <c r="H138" s="10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I138" s="10" t="inlineStr">
         <is>
@@ -12406,8 +12581,8 @@
       <c r="C139" s="22" t="n"/>
       <c r="D139" s="23" t="inlineStr">
         <is>
-          <t>Schalenstuhl mit Sitzpolster und Holzbeinen
-Schalenstuhl mit grauer Kunststoffschale, hellem Sitzpolster und konischen Beinen aus massivem Holz.</t>
+          <t>Schalenstuhl weiß mit Sitzpolster und Holzbeinen
+Schalenstuhl mit weißer Schale und fest verbundenem Sitzpolster, konische Beine aus braunem Massivholz.</t>
         </is>
       </c>
       <c r="E139" s="13" t="n"/>
@@ -12827,7 +13002,7 @@
       <c r="D146" s="12" t="inlineStr">
         <is>
           <t>Kinderwerkbank Holz mit Tafel
-Kinderwerkbank aus Holz mit Lochplatte, drei Werkzeugkästen, Tafellackfläche oben, Zollstockaufdruck an der Kante und Ablage unten.</t>
+Kinderwerkbank aus Holz mit Lochplatte, drei Werkzeugkästen, Tafellackfläche oben, Zollstockaufdruck an der Kante und Ablage unten. Einschließlich der Wandaufhängung.</t>
         </is>
       </c>
       <c r="E146" s="13" t="n"/>
@@ -13114,111 +13289,457 @@
         <v/>
       </c>
     </row>
-    <row r="152" ht="24" customHeight="1">
-      <c r="A152" s="36" t="inlineStr">
+    <row r="151" ht="78" customHeight="1">
+      <c r="A151" s="20" t="n">
+        <v>144</v>
+      </c>
+      <c r="B151" s="21" t="inlineStr">
+        <is>
+          <t>NU05-01</t>
+        </is>
+      </c>
+      <c r="C151" s="22" t="n"/>
+      <c r="D151" s="23" t="inlineStr">
+        <is>
+          <t>Mitwachsender Treppenhochstuhl, weiß
+Treppenhochstuhl aus Buche mit weißen Sitz- und Rückenplatten, Sitz und Fußbrett in der Höhe verstellbar. Die Seitenwangen tragen Lochreihen für die Verstellung.</t>
+        </is>
+      </c>
+      <c r="E151" s="13" t="n"/>
+      <c r="F151" s="23" t="inlineStr">
+        <is>
+          <t>Treppenraum 1</t>
+        </is>
+      </c>
+      <c r="G151" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H151" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="I151" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J151" s="24" t="n">
+        <v>90</v>
+      </c>
+      <c r="K151" s="25">
+        <f>J151*1.19</f>
+        <v/>
+      </c>
+      <c r="L151" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M151" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N151" s="16" t="n"/>
+      <c r="O151" s="17" t="n"/>
+      <c r="P151" s="18" t="n"/>
+      <c r="Q151" s="26">
+        <f>IF(N151&lt;&gt;"ja","",IF(O151="",H151,O151)*J151)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152" ht="78" customHeight="1">
+      <c r="A152" s="9" t="n">
+        <v>145</v>
+      </c>
+      <c r="B152" s="10" t="inlineStr">
+        <is>
+          <t>NU05-02</t>
+        </is>
+      </c>
+      <c r="C152" s="11" t="n"/>
+      <c r="D152" s="12" t="inlineStr">
+        <is>
+          <t>Juniorstuhl Holz weiß mit Kreuzlehne
+Juniorstuhl aus Massivholz, weiß lackiert, Rückenlehne mit gekreuzten Streben, Fußstütze als Querstrebe. Lack an Kanten und Sitzfläche abgestoßen.</t>
+        </is>
+      </c>
+      <c r="E152" s="13" t="n"/>
+      <c r="F152" s="12" t="inlineStr">
+        <is>
+          <t>Treppenraum 1</t>
+        </is>
+      </c>
+      <c r="G152" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H152" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I152" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J152" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K152" s="15">
+        <f>J152*1.19</f>
+        <v/>
+      </c>
+      <c r="L152" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M152" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N152" s="16" t="n"/>
+      <c r="O152" s="17" t="n"/>
+      <c r="P152" s="18" t="n"/>
+      <c r="Q152" s="19">
+        <f>IF(N152&lt;&gt;"ja","",IF(O152="",H152,O152)*J152)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153" ht="78" customHeight="1">
+      <c r="A153" s="20" t="n">
+        <v>146</v>
+      </c>
+      <c r="B153" s="21" t="inlineStr">
+        <is>
+          <t>NU05-03</t>
+        </is>
+      </c>
+      <c r="C153" s="22" t="n"/>
+      <c r="D153" s="23" t="inlineStr">
+        <is>
+          <t>Kindertisch weiß groß mit Holzbeinen
+Großer Kindertisch: weiße Platte mit abgerundeten Ecken und Multiplex-Kante auf konischen Beinen aus Buche.</t>
+        </is>
+      </c>
+      <c r="E153" s="13" t="n"/>
+      <c r="F153" s="23" t="inlineStr">
+        <is>
+          <t>Treppenraum 1</t>
+        </is>
+      </c>
+      <c r="G153" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H153" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I153" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J153" s="24" t="n">
+        <v>90</v>
+      </c>
+      <c r="K153" s="25">
+        <f>J153*1.19</f>
+        <v/>
+      </c>
+      <c r="L153" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M153" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N153" s="16" t="n"/>
+      <c r="O153" s="17" t="n"/>
+      <c r="P153" s="18" t="n"/>
+      <c r="Q153" s="26">
+        <f>IF(N153&lt;&gt;"ja","",IF(O153="",H153,O153)*J153)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154" ht="78" customHeight="1">
+      <c r="A154" s="9" t="n">
+        <v>147</v>
+      </c>
+      <c r="B154" s="10" t="inlineStr">
+        <is>
+          <t>NU05-04</t>
+        </is>
+      </c>
+      <c r="C154" s="11" t="n"/>
+      <c r="D154" s="12" t="inlineStr">
+        <is>
+          <t>Regal weiß hoch, vier Böden
+Hohes weißes Regal mit vier Einlegeböden, Bohrreihen zum Verstellen.</t>
+        </is>
+      </c>
+      <c r="E154" s="13" t="n"/>
+      <c r="F154" s="12" t="inlineStr">
+        <is>
+          <t>Treppenraum 1</t>
+        </is>
+      </c>
+      <c r="G154" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H154" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I154" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J154" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K154" s="15">
+        <f>J154*1.19</f>
+        <v/>
+      </c>
+      <c r="L154" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M154" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N154" s="16" t="n"/>
+      <c r="O154" s="17" t="n"/>
+      <c r="P154" s="18" t="n"/>
+      <c r="Q154" s="19">
+        <f>IF(N154&lt;&gt;"ja","",IF(O154="",H154,O154)*J154)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155" ht="78" customHeight="1">
+      <c r="A155" s="20" t="n">
+        <v>148</v>
+      </c>
+      <c r="B155" s="21" t="inlineStr">
+        <is>
+          <t>NU05-06</t>
+        </is>
+      </c>
+      <c r="C155" s="22" t="n"/>
+      <c r="D155" s="23" t="inlineStr">
+        <is>
+          <t>Regal weiß mit zwei Schubladen und zwei Böden
+Weißes Regal mit zwei Einlegeböden oben und zwei großen Schubladen mit Griffmulden unten, Front der Schubladen dunkel.</t>
+        </is>
+      </c>
+      <c r="E155" s="13" t="n"/>
+      <c r="F155" s="23" t="inlineStr">
+        <is>
+          <t>Treppenraum 1</t>
+        </is>
+      </c>
+      <c r="G155" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H155" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I155" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J155" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="K155" s="25">
+        <f>J155*1.19</f>
+        <v/>
+      </c>
+      <c r="L155" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M155" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N155" s="16" t="n"/>
+      <c r="O155" s="17" t="n"/>
+      <c r="P155" s="18" t="n"/>
+      <c r="Q155" s="26">
+        <f>IF(N155&lt;&gt;"ja","",IF(O155="",H155,O155)*J155)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" ht="78" customHeight="1">
+      <c r="A156" s="9" t="n">
+        <v>149</v>
+      </c>
+      <c r="B156" s="10" t="inlineStr">
+        <is>
+          <t>NU05-07</t>
+        </is>
+      </c>
+      <c r="C156" s="11" t="n"/>
+      <c r="D156" s="12" t="inlineStr">
+        <is>
+          <t>Mal- und Trockengestell fahrbar
+Fahrbares Gestell aus Holz mit acht herausziehbaren Drahtgitter-Einschüben zum Trocknen von Bildern, Griffstange oben, auf Rollen.</t>
+        </is>
+      </c>
+      <c r="E156" s="13" t="n"/>
+      <c r="F156" s="12" t="inlineStr">
+        <is>
+          <t>Treppenraum 1</t>
+        </is>
+      </c>
+      <c r="G156" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H156" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I156" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J156" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="K156" s="15">
+        <f>J156*1.19</f>
+        <v/>
+      </c>
+      <c r="L156" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M156" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N156" s="16" t="n"/>
+      <c r="O156" s="17" t="n"/>
+      <c r="P156" s="18" t="n"/>
+      <c r="Q156" s="19">
+        <f>IF(N156&lt;&gt;"ja","",IF(O156="",H156,O156)*J156)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" ht="78" customHeight="1">
+      <c r="A157" s="20" t="n">
+        <v>150</v>
+      </c>
+      <c r="B157" s="21" t="inlineStr">
+        <is>
+          <t>NU05-08</t>
+        </is>
+      </c>
+      <c r="C157" s="22" t="n"/>
+      <c r="D157" s="23" t="inlineStr">
+        <is>
+          <t>Maltafel Holz mit Kreidetafel und Farbablage
+Standtafel aus Holz mit schwarzer Kreidetafel, Ablage mit Aussparungen für Farbbecher und Schwamm, Papierrollenhalter oben. Farbspuren am Rahmen.</t>
+        </is>
+      </c>
+      <c r="E157" s="13" t="n"/>
+      <c r="F157" s="23" t="inlineStr">
+        <is>
+          <t>Treppenraum 1</t>
+        </is>
+      </c>
+      <c r="G157" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H157" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I157" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J157" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="K157" s="25">
+        <f>J157*1.19</f>
+        <v/>
+      </c>
+      <c r="L157" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M157" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N157" s="16" t="n"/>
+      <c r="O157" s="17" t="n"/>
+      <c r="P157" s="18" t="n"/>
+      <c r="Q157" s="26">
+        <f>IF(N157&lt;&gt;"ja","",IF(O157="",H157,O157)*J157)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" ht="24" customHeight="1">
+      <c r="A159" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B152" s="1" t="n"/>
-      <c r="C152" s="1" t="n"/>
-      <c r="D152" s="1" t="n"/>
-      <c r="E152" s="1" t="n"/>
-      <c r="F152" s="1" t="n"/>
-      <c r="G152" s="1" t="n"/>
-      <c r="H152" s="1" t="n"/>
-      <c r="I152" s="1" t="n"/>
-      <c r="J152" s="1" t="n"/>
-      <c r="K152" s="1" t="n"/>
-      <c r="L152" s="1" t="n"/>
-      <c r="M152" s="1" t="n"/>
-      <c r="N152" s="1" t="n"/>
-      <c r="O152" s="1" t="n"/>
-      <c r="P152" s="1" t="n"/>
-      <c r="Q152" s="1" t="n"/>
-    </row>
-    <row r="153" ht="22" customHeight="1">
-      <c r="A153" s="37" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl netto</t>
-        </is>
-      </c>
-      <c r="Q153" s="38">
-        <f>SUM(Q8:Q150)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="154" ht="22" customHeight="1">
-      <c r="A154" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q154" s="38">
-        <f>Q153*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="155" ht="26" customHeight="1">
-      <c r="A155" s="39" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl brutto</t>
-        </is>
-      </c>
-      <c r="Q155" s="40">
-        <f>Q153+Q154</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156" ht="22" customHeight="1">
-      <c r="A156" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q156" s="41">
-        <f>COUNTIF(N8:N150,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="24" customHeight="1">
-      <c r="A159" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B159" s="44" t="n"/>
-      <c r="C159" s="44" t="n"/>
-      <c r="D159" s="44" t="n"/>
-      <c r="E159" s="44" t="n"/>
-      <c r="F159" s="44" t="n"/>
-      <c r="G159" s="44" t="n"/>
-      <c r="H159" s="44" t="n"/>
-      <c r="I159" s="44" t="n"/>
-      <c r="J159" s="44" t="n"/>
-      <c r="K159" s="44" t="n"/>
-      <c r="L159" s="44" t="n"/>
-      <c r="M159" s="44" t="n"/>
-      <c r="N159" s="44" t="n"/>
-      <c r="O159" s="44" t="n"/>
-      <c r="P159" s="44" t="n"/>
-      <c r="Q159" s="44" t="n"/>
+      <c r="B159" s="1" t="n"/>
+      <c r="C159" s="1" t="n"/>
+      <c r="D159" s="1" t="n"/>
+      <c r="E159" s="1" t="n"/>
+      <c r="F159" s="1" t="n"/>
+      <c r="G159" s="1" t="n"/>
+      <c r="H159" s="1" t="n"/>
+      <c r="I159" s="1" t="n"/>
+      <c r="J159" s="1" t="n"/>
+      <c r="K159" s="1" t="n"/>
+      <c r="L159" s="1" t="n"/>
+      <c r="M159" s="1" t="n"/>
+      <c r="N159" s="1" t="n"/>
+      <c r="O159" s="1" t="n"/>
+      <c r="P159" s="1" t="n"/>
+      <c r="Q159" s="1" t="n"/>
     </row>
     <row r="160" ht="22" customHeight="1">
       <c r="A160" s="37" t="inlineStr">
         <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
+          <t>Wert Ihrer Auswahl netto</t>
         </is>
       </c>
       <c r="Q160" s="38">
-        <f>SUMPRODUCT(H8:H150,J8:J150)</f>
+        <f>SUM(Q8:Q157)</f>
         <v/>
       </c>
     </row>
@@ -13233,142 +13754,216 @@
         <v/>
       </c>
     </row>
-    <row r="162" ht="22" customHeight="1">
-      <c r="A162" s="45" t="inlineStr">
-        <is>
-          <t>Gesamtwert brutto</t>
-        </is>
-      </c>
-      <c r="Q162" s="46">
+    <row r="162" ht="26" customHeight="1">
+      <c r="A162" s="39" t="inlineStr">
+        <is>
+          <t>Wert Ihrer Auswahl brutto</t>
+        </is>
+      </c>
+      <c r="Q162" s="40">
         <f>Q160+Q161</f>
         <v/>
       </c>
     </row>
-    <row r="164" ht="24" customHeight="1">
-      <c r="A164" s="47" t="inlineStr">
-        <is>
-          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B164" s="48" t="n"/>
-      <c r="C164" s="48" t="n"/>
-      <c r="D164" s="48" t="n"/>
-      <c r="E164" s="48" t="n"/>
-      <c r="F164" s="48" t="n"/>
-      <c r="G164" s="48" t="n"/>
-      <c r="H164" s="48" t="n"/>
-      <c r="I164" s="48" t="n"/>
-      <c r="J164" s="48" t="n"/>
-      <c r="K164" s="48" t="n"/>
-      <c r="L164" s="48" t="n"/>
-      <c r="M164" s="48" t="n"/>
-      <c r="N164" s="48" t="n"/>
-      <c r="O164" s="48" t="n"/>
-      <c r="P164" s="48" t="n"/>
-      <c r="Q164" s="48" t="n"/>
-    </row>
-    <row r="165" ht="22" customHeight="1">
-      <c r="A165" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
-        </is>
-      </c>
-      <c r="Q165" s="38">
-        <f>-Q160*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="166" ht="22" customHeight="1">
-      <c r="A166" s="45" t="inlineStr">
-        <is>
-          <t>Paketpreis netto</t>
-        </is>
-      </c>
-      <c r="Q166" s="46">
-        <f>Q160+Q165</f>
-        <v/>
-      </c>
+    <row r="163" ht="22" customHeight="1">
+      <c r="A163" s="37" t="inlineStr">
+        <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q163" s="41">
+        <f>COUNTIF(N8:N157,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="24" customHeight="1">
+      <c r="A166" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B166" s="44" t="n"/>
+      <c r="C166" s="44" t="n"/>
+      <c r="D166" s="44" t="n"/>
+      <c r="E166" s="44" t="n"/>
+      <c r="F166" s="44" t="n"/>
+      <c r="G166" s="44" t="n"/>
+      <c r="H166" s="44" t="n"/>
+      <c r="I166" s="44" t="n"/>
+      <c r="J166" s="44" t="n"/>
+      <c r="K166" s="44" t="n"/>
+      <c r="L166" s="44" t="n"/>
+      <c r="M166" s="44" t="n"/>
+      <c r="N166" s="44" t="n"/>
+      <c r="O166" s="44" t="n"/>
+      <c r="P166" s="44" t="n"/>
+      <c r="Q166" s="44" t="n"/>
     </row>
     <row r="167" ht="22" customHeight="1">
       <c r="A167" s="37" t="inlineStr">
         <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q167" s="38">
+        <f>SUMPRODUCT(H8:H157,J8:J157)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168" ht="22" customHeight="1">
+      <c r="A168" s="37" t="inlineStr">
+        <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q167" s="38">
-        <f>Q166*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="168" ht="26" customHeight="1">
-      <c r="A168" s="39" t="inlineStr">
+      <c r="Q168" s="38">
+        <f>Q167*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169" ht="22" customHeight="1">
+      <c r="A169" s="45" t="inlineStr">
+        <is>
+          <t>Gesamtwert brutto</t>
+        </is>
+      </c>
+      <c r="Q169" s="46">
+        <f>Q167+Q168</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171" ht="24" customHeight="1">
+      <c r="A171" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B171" s="48" t="n"/>
+      <c r="C171" s="48" t="n"/>
+      <c r="D171" s="48" t="n"/>
+      <c r="E171" s="48" t="n"/>
+      <c r="F171" s="48" t="n"/>
+      <c r="G171" s="48" t="n"/>
+      <c r="H171" s="48" t="n"/>
+      <c r="I171" s="48" t="n"/>
+      <c r="J171" s="48" t="n"/>
+      <c r="K171" s="48" t="n"/>
+      <c r="L171" s="48" t="n"/>
+      <c r="M171" s="48" t="n"/>
+      <c r="N171" s="48" t="n"/>
+      <c r="O171" s="48" t="n"/>
+      <c r="P171" s="48" t="n"/>
+      <c r="Q171" s="48" t="n"/>
+    </row>
+    <row r="172" ht="22" customHeight="1">
+      <c r="A172" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
+        </is>
+      </c>
+      <c r="Q172" s="38">
+        <f>-Q167*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173" ht="22" customHeight="1">
+      <c r="A173" s="45" t="inlineStr">
+        <is>
+          <t>Paketpreis netto</t>
+        </is>
+      </c>
+      <c r="Q173" s="46">
+        <f>Q167+Q172</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" ht="22" customHeight="1">
+      <c r="A174" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q174" s="38">
+        <f>Q173*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" ht="26" customHeight="1">
+      <c r="A175" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q168" s="40">
-        <f>Q166+Q167</f>
-        <v/>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="42" t="inlineStr">
+      <c r="Q175" s="40">
+        <f>Q173+Q174</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="49" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="172"/>
-    <row r="173"/>
-    <row r="174"/>
+    <row r="179"/>
+    <row r="180"/>
+    <row r="181"/>
   </sheetData>
-  <autoFilter ref="A7:Q150"/>
+  <autoFilter ref="A7:Q157"/>
   <mergeCells count="26">
     <mergeCell ref="A160:P160"/>
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A157:Q157"/>
+    <mergeCell ref="A178:Q181"/>
+    <mergeCell ref="A176:Q176"/>
+    <mergeCell ref="A166:Q166"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A169:Q169"/>
-    <mergeCell ref="A165:P165"/>
     <mergeCell ref="L4:Q4"/>
-    <mergeCell ref="A156:P156"/>
-    <mergeCell ref="A155:P155"/>
     <mergeCell ref="A161:P161"/>
     <mergeCell ref="C3:I3"/>
+    <mergeCell ref="A173:P173"/>
     <mergeCell ref="A167:P167"/>
-    <mergeCell ref="A171:Q174"/>
-    <mergeCell ref="A166:P166"/>
     <mergeCell ref="A164:Q164"/>
+    <mergeCell ref="A169:P169"/>
     <mergeCell ref="C4:I4"/>
     <mergeCell ref="A162:P162"/>
     <mergeCell ref="A168:P168"/>
-    <mergeCell ref="A153:P153"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="A172:P172"/>
+    <mergeCell ref="A174:P174"/>
     <mergeCell ref="A159:Q159"/>
-    <mergeCell ref="A154:P154"/>
+    <mergeCell ref="A171:Q171"/>
+    <mergeCell ref="A163:P163"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A152:Q152"/>
+    <mergeCell ref="A175:P175"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q150">
+  <conditionalFormatting sqref="A8:Q157">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N150" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N157" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O150" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O157" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$164</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4193,6 +4193,181 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>157</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="152" name="Image 152" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId152"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>158</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="153" name="Image 153" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId153"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>159</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="154" name="Image 154" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId154"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>160</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="155" name="Image 155" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId155"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>161</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="156" name="Image 156" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId156"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>162</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="157" name="Image 157" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId157"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>163</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="158" name="Image 158" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId158"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -4485,7 +4660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q181"/>
+  <dimension ref="A1:Q188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13709,111 +13884,457 @@
         <v/>
       </c>
     </row>
-    <row r="159" ht="24" customHeight="1">
-      <c r="A159" s="36" t="inlineStr">
+    <row r="158" ht="78" customHeight="1">
+      <c r="A158" s="9" t="n">
+        <v>151</v>
+      </c>
+      <c r="B158" s="35" t="inlineStr">
+        <is>
+          <t>NU06-01</t>
+        </is>
+      </c>
+      <c r="C158" s="11" t="n"/>
+      <c r="D158" s="12" t="inlineStr">
+        <is>
+          <t>Garderobenwand weiß, 13 Plätze
+Lange Garderobenwand in Weiß: oben ein durchgehendes Ablagefach, darunter eine Leiste mit 13 Doppelhaken, unten eine Sitzbank mit offenen Schuhfächern. Schreinerarbeit.</t>
+        </is>
+      </c>
+      <c r="E158" s="13" t="n"/>
+      <c r="F158" s="12" t="inlineStr">
+        <is>
+          <t>WC</t>
+        </is>
+      </c>
+      <c r="G158" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H158" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I158" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J158" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="K158" s="15">
+        <f>J158*1.19</f>
+        <v/>
+      </c>
+      <c r="L158" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M158" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N158" s="16" t="n"/>
+      <c r="O158" s="17" t="n"/>
+      <c r="P158" s="18" t="n"/>
+      <c r="Q158" s="19">
+        <f>IF(N158&lt;&gt;"ja","",IF(O158="",H158,O158)*J158)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" ht="78" customHeight="1">
+      <c r="A159" s="20" t="n">
+        <v>152</v>
+      </c>
+      <c r="B159" s="35" t="inlineStr">
+        <is>
+          <t>NU06-02</t>
+        </is>
+      </c>
+      <c r="C159" s="22" t="n"/>
+      <c r="D159" s="23" t="inlineStr">
+        <is>
+          <t>Garderobenwand weiß, 9 Plätze
+Garderobenwand in Weiß: oben ein durchgehendes Ablagefach, darunter eine Leiste mit neun Doppelhaken, unten eine Sitzbank mit offenen Schuhfächern. Schreinerarbeit.</t>
+        </is>
+      </c>
+      <c r="E159" s="13" t="n"/>
+      <c r="F159" s="23" t="inlineStr">
+        <is>
+          <t>WC</t>
+        </is>
+      </c>
+      <c r="G159" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H159" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="I159" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J159" s="24" t="n">
+        <v>180</v>
+      </c>
+      <c r="K159" s="25">
+        <f>J159*1.19</f>
+        <v/>
+      </c>
+      <c r="L159" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M159" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N159" s="16" t="n"/>
+      <c r="O159" s="17" t="n"/>
+      <c r="P159" s="18" t="n"/>
+      <c r="Q159" s="26">
+        <f>IF(N159&lt;&gt;"ja","",IF(O159="",H159,O159)*J159)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160" ht="78" customHeight="1">
+      <c r="A160" s="9" t="n">
+        <v>153</v>
+      </c>
+      <c r="B160" s="10" t="inlineStr">
+        <is>
+          <t>NU06-03</t>
+        </is>
+      </c>
+      <c r="C160" s="11" t="n"/>
+      <c r="D160" s="12" t="inlineStr">
+        <is>
+          <t>Hängegarderobe weiß mit Wannen
+Wandelement in Weiß mit sechs eingeschobenen Kunststoffwannen, darunter drei rote Doppelhaken.</t>
+        </is>
+      </c>
+      <c r="E160" s="13" t="n"/>
+      <c r="F160" s="12" t="inlineStr">
+        <is>
+          <t>WC</t>
+        </is>
+      </c>
+      <c r="G160" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H160" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I160" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J160" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="K160" s="15">
+        <f>J160*1.19</f>
+        <v/>
+      </c>
+      <c r="L160" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M160" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N160" s="16" t="n"/>
+      <c r="O160" s="17" t="n"/>
+      <c r="P160" s="18" t="n"/>
+      <c r="Q160" s="19">
+        <f>IF(N160&lt;&gt;"ja","",IF(O160="",H160,O160)*J160)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161" ht="78" customHeight="1">
+      <c r="A161" s="20" t="n">
+        <v>154</v>
+      </c>
+      <c r="B161" s="21" t="inlineStr">
+        <is>
+          <t>NU06-04</t>
+        </is>
+      </c>
+      <c r="C161" s="22" t="n"/>
+      <c r="D161" s="23" t="inlineStr">
+        <is>
+          <t>Holzregal weiß, sechs Fächer
+Regal aus Holz, weiß gestrichen, sechs Fächer in zwei Reihen. Farbe an Kanten und Fachböden großflächig abgeplatzt.</t>
+        </is>
+      </c>
+      <c r="E161" s="13" t="n"/>
+      <c r="F161" s="23" t="inlineStr">
+        <is>
+          <t>WC</t>
+        </is>
+      </c>
+      <c r="G161" s="21" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="H161" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I161" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J161" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="K161" s="25">
+        <f>J161*1.19</f>
+        <v/>
+      </c>
+      <c r="L161" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M161" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N161" s="16" t="n"/>
+      <c r="O161" s="17" t="n"/>
+      <c r="P161" s="18" t="n"/>
+      <c r="Q161" s="26">
+        <f>IF(N161&lt;&gt;"ja","",IF(O161="",H161,O161)*J161)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162" ht="78" customHeight="1">
+      <c r="A162" s="9" t="n">
+        <v>155</v>
+      </c>
+      <c r="B162" s="35" t="inlineStr">
+        <is>
+          <t>NU06-05</t>
+        </is>
+      </c>
+      <c r="C162" s="11" t="n"/>
+      <c r="D162" s="12" t="inlineStr">
+        <is>
+          <t>Bauknecht Kühl-Gefrierkombination, Standgerät
+Standgerät von Bauknecht in Edelstahloptik: Kühlteil oben mit Glasböden, Gemüsefach und Innenbeleuchtung, Gefrierteil unten. No Frost.</t>
+        </is>
+      </c>
+      <c r="E162" s="13" t="n"/>
+      <c r="F162" s="12" t="inlineStr">
+        <is>
+          <t>WC</t>
+        </is>
+      </c>
+      <c r="G162" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H162" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I162" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J162" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="K162" s="15">
+        <f>J162*1.19</f>
+        <v/>
+      </c>
+      <c r="L162" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M162" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N162" s="16" t="n"/>
+      <c r="O162" s="17" t="n"/>
+      <c r="P162" s="18" t="n"/>
+      <c r="Q162" s="19">
+        <f>IF(N162&lt;&gt;"ja","",IF(O162="",H162,O162)*J162)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163" ht="78" customHeight="1">
+      <c r="A163" s="20" t="n">
+        <v>156</v>
+      </c>
+      <c r="B163" s="21" t="inlineStr">
+        <is>
+          <t>NU06-06</t>
+        </is>
+      </c>
+      <c r="C163" s="22" t="n"/>
+      <c r="D163" s="23" t="inlineStr">
+        <is>
+          <t>Schwerlastregal verzinkt, vier Böden
+Steckregal aus verzinktem Stahl mit vier Holzböden, höhenverstellbar.</t>
+        </is>
+      </c>
+      <c r="E163" s="13" t="n"/>
+      <c r="F163" s="23" t="inlineStr">
+        <is>
+          <t>WC</t>
+        </is>
+      </c>
+      <c r="G163" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H163" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I163" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J163" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="K163" s="25">
+        <f>J163*1.19</f>
+        <v/>
+      </c>
+      <c r="L163" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M163" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N163" s="16" t="n"/>
+      <c r="O163" s="17" t="n"/>
+      <c r="P163" s="18" t="n"/>
+      <c r="Q163" s="26">
+        <f>IF(N163&lt;&gt;"ja","",IF(O163="",H163,O163)*J163)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" ht="78" customHeight="1">
+      <c r="A164" s="9" t="n">
+        <v>157</v>
+      </c>
+      <c r="B164" s="10" t="inlineStr">
+        <is>
+          <t>NU06-07</t>
+        </is>
+      </c>
+      <c r="C164" s="11" t="n"/>
+      <c r="D164" s="12" t="inlineStr">
+        <is>
+          <t>Bild Paris bei Nacht, groß gerahmt
+Großformatiges Bild von Paris bei Nacht mit beleuchtetem Eiffelturm, schwarz-weiß mit goldenen Lichtern, in silberfarbenem Aluminiumrahmen. Aufdruck am unteren Rand: „Paris" Scanpix/age fotostock, Jean-Marc Charles, gedruckt für IKEA.</t>
+        </is>
+      </c>
+      <c r="E164" s="13" t="n"/>
+      <c r="F164" s="12" t="inlineStr">
+        <is>
+          <t>WC</t>
+        </is>
+      </c>
+      <c r="G164" s="10" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H164" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I164" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J164" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K164" s="15">
+        <f>J164*1.19</f>
+        <v/>
+      </c>
+      <c r="L164" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M164" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N164" s="16" t="n"/>
+      <c r="O164" s="17" t="n"/>
+      <c r="P164" s="18" t="n"/>
+      <c r="Q164" s="19">
+        <f>IF(N164&lt;&gt;"ja","",IF(O164="",H164,O164)*J164)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" ht="24" customHeight="1">
+      <c r="A166" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B159" s="1" t="n"/>
-      <c r="C159" s="1" t="n"/>
-      <c r="D159" s="1" t="n"/>
-      <c r="E159" s="1" t="n"/>
-      <c r="F159" s="1" t="n"/>
-      <c r="G159" s="1" t="n"/>
-      <c r="H159" s="1" t="n"/>
-      <c r="I159" s="1" t="n"/>
-      <c r="J159" s="1" t="n"/>
-      <c r="K159" s="1" t="n"/>
-      <c r="L159" s="1" t="n"/>
-      <c r="M159" s="1" t="n"/>
-      <c r="N159" s="1" t="n"/>
-      <c r="O159" s="1" t="n"/>
-      <c r="P159" s="1" t="n"/>
-      <c r="Q159" s="1" t="n"/>
-    </row>
-    <row r="160" ht="22" customHeight="1">
-      <c r="A160" s="37" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl netto</t>
-        </is>
-      </c>
-      <c r="Q160" s="38">
-        <f>SUM(Q8:Q157)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="161" ht="22" customHeight="1">
-      <c r="A161" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q161" s="38">
-        <f>Q160*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="162" ht="26" customHeight="1">
-      <c r="A162" s="39" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl brutto</t>
-        </is>
-      </c>
-      <c r="Q162" s="40">
-        <f>Q160+Q161</f>
-        <v/>
-      </c>
-    </row>
-    <row r="163" ht="22" customHeight="1">
-      <c r="A163" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q163" s="41">
-        <f>COUNTIF(N8:N157,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="24" customHeight="1">
-      <c r="A166" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B166" s="44" t="n"/>
-      <c r="C166" s="44" t="n"/>
-      <c r="D166" s="44" t="n"/>
-      <c r="E166" s="44" t="n"/>
-      <c r="F166" s="44" t="n"/>
-      <c r="G166" s="44" t="n"/>
-      <c r="H166" s="44" t="n"/>
-      <c r="I166" s="44" t="n"/>
-      <c r="J166" s="44" t="n"/>
-      <c r="K166" s="44" t="n"/>
-      <c r="L166" s="44" t="n"/>
-      <c r="M166" s="44" t="n"/>
-      <c r="N166" s="44" t="n"/>
-      <c r="O166" s="44" t="n"/>
-      <c r="P166" s="44" t="n"/>
-      <c r="Q166" s="44" t="n"/>
+      <c r="B166" s="1" t="n"/>
+      <c r="C166" s="1" t="n"/>
+      <c r="D166" s="1" t="n"/>
+      <c r="E166" s="1" t="n"/>
+      <c r="F166" s="1" t="n"/>
+      <c r="G166" s="1" t="n"/>
+      <c r="H166" s="1" t="n"/>
+      <c r="I166" s="1" t="n"/>
+      <c r="J166" s="1" t="n"/>
+      <c r="K166" s="1" t="n"/>
+      <c r="L166" s="1" t="n"/>
+      <c r="M166" s="1" t="n"/>
+      <c r="N166" s="1" t="n"/>
+      <c r="O166" s="1" t="n"/>
+      <c r="P166" s="1" t="n"/>
+      <c r="Q166" s="1" t="n"/>
     </row>
     <row r="167" ht="22" customHeight="1">
       <c r="A167" s="37" t="inlineStr">
         <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
+          <t>Wert Ihrer Auswahl netto</t>
         </is>
       </c>
       <c r="Q167" s="38">
-        <f>SUMPRODUCT(H8:H157,J8:J157)</f>
+        <f>SUM(Q8:Q164)</f>
         <v/>
       </c>
     </row>
@@ -13828,142 +14349,216 @@
         <v/>
       </c>
     </row>
-    <row r="169" ht="22" customHeight="1">
-      <c r="A169" s="45" t="inlineStr">
-        <is>
-          <t>Gesamtwert brutto</t>
-        </is>
-      </c>
-      <c r="Q169" s="46">
+    <row r="169" ht="26" customHeight="1">
+      <c r="A169" s="39" t="inlineStr">
+        <is>
+          <t>Wert Ihrer Auswahl brutto</t>
+        </is>
+      </c>
+      <c r="Q169" s="40">
         <f>Q167+Q168</f>
         <v/>
       </c>
     </row>
-    <row r="171" ht="24" customHeight="1">
-      <c r="A171" s="47" t="inlineStr">
-        <is>
-          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B171" s="48" t="n"/>
-      <c r="C171" s="48" t="n"/>
-      <c r="D171" s="48" t="n"/>
-      <c r="E171" s="48" t="n"/>
-      <c r="F171" s="48" t="n"/>
-      <c r="G171" s="48" t="n"/>
-      <c r="H171" s="48" t="n"/>
-      <c r="I171" s="48" t="n"/>
-      <c r="J171" s="48" t="n"/>
-      <c r="K171" s="48" t="n"/>
-      <c r="L171" s="48" t="n"/>
-      <c r="M171" s="48" t="n"/>
-      <c r="N171" s="48" t="n"/>
-      <c r="O171" s="48" t="n"/>
-      <c r="P171" s="48" t="n"/>
-      <c r="Q171" s="48" t="n"/>
-    </row>
-    <row r="172" ht="22" customHeight="1">
-      <c r="A172" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
-        </is>
-      </c>
-      <c r="Q172" s="38">
-        <f>-Q167*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="173" ht="22" customHeight="1">
-      <c r="A173" s="45" t="inlineStr">
-        <is>
-          <t>Paketpreis netto</t>
-        </is>
-      </c>
-      <c r="Q173" s="46">
-        <f>Q167+Q172</f>
-        <v/>
-      </c>
+    <row r="170" ht="22" customHeight="1">
+      <c r="A170" s="37" t="inlineStr">
+        <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q170" s="41">
+        <f>COUNTIF(N8:N164,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="24" customHeight="1">
+      <c r="A173" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B173" s="44" t="n"/>
+      <c r="C173" s="44" t="n"/>
+      <c r="D173" s="44" t="n"/>
+      <c r="E173" s="44" t="n"/>
+      <c r="F173" s="44" t="n"/>
+      <c r="G173" s="44" t="n"/>
+      <c r="H173" s="44" t="n"/>
+      <c r="I173" s="44" t="n"/>
+      <c r="J173" s="44" t="n"/>
+      <c r="K173" s="44" t="n"/>
+      <c r="L173" s="44" t="n"/>
+      <c r="M173" s="44" t="n"/>
+      <c r="N173" s="44" t="n"/>
+      <c r="O173" s="44" t="n"/>
+      <c r="P173" s="44" t="n"/>
+      <c r="Q173" s="44" t="n"/>
     </row>
     <row r="174" ht="22" customHeight="1">
       <c r="A174" s="37" t="inlineStr">
         <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q174" s="38">
+        <f>SUMPRODUCT(H8:H164,J8:J164)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" ht="22" customHeight="1">
+      <c r="A175" s="37" t="inlineStr">
+        <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q174" s="38">
-        <f>Q173*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="175" ht="26" customHeight="1">
-      <c r="A175" s="39" t="inlineStr">
+      <c r="Q175" s="38">
+        <f>Q174*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176" ht="22" customHeight="1">
+      <c r="A176" s="45" t="inlineStr">
+        <is>
+          <t>Gesamtwert brutto</t>
+        </is>
+      </c>
+      <c r="Q176" s="46">
+        <f>Q174+Q175</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178" ht="24" customHeight="1">
+      <c r="A178" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B178" s="48" t="n"/>
+      <c r="C178" s="48" t="n"/>
+      <c r="D178" s="48" t="n"/>
+      <c r="E178" s="48" t="n"/>
+      <c r="F178" s="48" t="n"/>
+      <c r="G178" s="48" t="n"/>
+      <c r="H178" s="48" t="n"/>
+      <c r="I178" s="48" t="n"/>
+      <c r="J178" s="48" t="n"/>
+      <c r="K178" s="48" t="n"/>
+      <c r="L178" s="48" t="n"/>
+      <c r="M178" s="48" t="n"/>
+      <c r="N178" s="48" t="n"/>
+      <c r="O178" s="48" t="n"/>
+      <c r="P178" s="48" t="n"/>
+      <c r="Q178" s="48" t="n"/>
+    </row>
+    <row r="179" ht="22" customHeight="1">
+      <c r="A179" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
+        </is>
+      </c>
+      <c r="Q179" s="38">
+        <f>-Q174*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180" ht="22" customHeight="1">
+      <c r="A180" s="45" t="inlineStr">
+        <is>
+          <t>Paketpreis netto</t>
+        </is>
+      </c>
+      <c r="Q180" s="46">
+        <f>Q174+Q179</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181" ht="22" customHeight="1">
+      <c r="A181" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q181" s="38">
+        <f>Q180*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182" ht="26" customHeight="1">
+      <c r="A182" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q175" s="40">
-        <f>Q173+Q174</f>
-        <v/>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="42" t="inlineStr">
+      <c r="Q182" s="40">
+        <f>Q180+Q181</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="49" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="179"/>
-    <row r="180"/>
-    <row r="181"/>
+    <row r="186"/>
+    <row r="187"/>
+    <row r="188"/>
   </sheetData>
-  <autoFilter ref="A7:Q157"/>
+  <autoFilter ref="A7:Q164"/>
   <mergeCells count="26">
-    <mergeCell ref="A160:P160"/>
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A178:Q181"/>
-    <mergeCell ref="A176:Q176"/>
+    <mergeCell ref="A173:Q173"/>
+    <mergeCell ref="A181:P181"/>
     <mergeCell ref="A166:Q166"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A180:P180"/>
     <mergeCell ref="L4:Q4"/>
-    <mergeCell ref="A161:P161"/>
+    <mergeCell ref="A178:Q178"/>
+    <mergeCell ref="A170:P170"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A173:P173"/>
+    <mergeCell ref="A176:P176"/>
     <mergeCell ref="A167:P167"/>
-    <mergeCell ref="A164:Q164"/>
+    <mergeCell ref="A185:Q188"/>
+    <mergeCell ref="A183:Q183"/>
+    <mergeCell ref="A182:P182"/>
     <mergeCell ref="A169:P169"/>
     <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A162:P162"/>
     <mergeCell ref="A168:P168"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A172:P172"/>
     <mergeCell ref="A174:P174"/>
-    <mergeCell ref="A159:Q159"/>
     <mergeCell ref="A171:Q171"/>
-    <mergeCell ref="A163:P163"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
+    <mergeCell ref="A179:P179"/>
     <mergeCell ref="A175:P175"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q157">
+  <conditionalFormatting sqref="A8:Q164">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N157" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N164" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O157" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O164" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4368,6 +4368,181 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>164</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="159" name="Image 159" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId159"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>165</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="160" name="Image 160" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId160"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>166</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="161" name="Image 161" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId161"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>167</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="162" name="Image 162" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId162"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>168</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="163" name="Image 163" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId163"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>169</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="164" name="Image 164" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId164"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>170</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="165" name="Image 165" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId165"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -4660,7 +4835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q188"/>
+  <dimension ref="A1:Q195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -12712,7 +12887,7 @@
         </is>
       </c>
       <c r="H138" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I138" s="10" t="inlineStr">
         <is>
@@ -14304,111 +14479,457 @@
         <v/>
       </c>
     </row>
-    <row r="166" ht="24" customHeight="1">
-      <c r="A166" s="36" t="inlineStr">
+    <row r="165" ht="78" customHeight="1">
+      <c r="A165" s="20" t="n">
+        <v>158</v>
+      </c>
+      <c r="B165" s="35" t="inlineStr">
+        <is>
+          <t>NU07-01</t>
+        </is>
+      </c>
+      <c r="C165" s="22" t="n"/>
+      <c r="D165" s="23" t="inlineStr">
+        <is>
+          <t>Hausbett schwarz mit Dach
+Kinderbett in Hausform, dunkelbraun-schwarz lackiert, mit Satteldach, Firstbalken und ausgesägten Sprossenfenstern an beiden Seiten. Matratze liegt auf und kann auf Wunsch mitgenommen werden.</t>
+        </is>
+      </c>
+      <c r="E165" s="13" t="n"/>
+      <c r="F165" s="23" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="G165" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H165" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I165" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J165" s="24" t="n">
+        <v>180</v>
+      </c>
+      <c r="K165" s="25">
+        <f>J165*1.19</f>
+        <v/>
+      </c>
+      <c r="L165" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M165" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N165" s="16" t="n"/>
+      <c r="O165" s="17" t="n"/>
+      <c r="P165" s="18" t="n"/>
+      <c r="Q165" s="26">
+        <f>IF(N165&lt;&gt;"ja","",IF(O165="",H165,O165)*J165)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" ht="78" customHeight="1">
+      <c r="A166" s="9" t="n">
+        <v>159</v>
+      </c>
+      <c r="B166" s="10" t="inlineStr">
+        <is>
+          <t>NU07-02</t>
+        </is>
+      </c>
+      <c r="C166" s="11" t="n"/>
+      <c r="D166" s="12" t="inlineStr">
+        <is>
+          <t>Kaufladen weiß mit Aufsatz
+Kaufladen aus Holz, weiß mit grauer Rückwand: Verkaufstheke mit Ablage unten, Aufsatz mit sechs Fächern und geschwungener Blende.</t>
+        </is>
+      </c>
+      <c r="E166" s="13" t="n"/>
+      <c r="F166" s="12" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="G166" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H166" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I166" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J166" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="K166" s="15">
+        <f>J166*1.19</f>
+        <v/>
+      </c>
+      <c r="L166" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M166" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N166" s="16" t="n"/>
+      <c r="O166" s="17" t="n"/>
+      <c r="P166" s="18" t="n"/>
+      <c r="Q166" s="19">
+        <f>IF(N166&lt;&gt;"ja","",IF(O166="",H166,O166)*J166)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" ht="78" customHeight="1">
+      <c r="A167" s="20" t="n">
+        <v>160</v>
+      </c>
+      <c r="B167" s="35" t="inlineStr">
+        <is>
+          <t>NU07-03</t>
+        </is>
+      </c>
+      <c r="C167" s="22" t="n"/>
+      <c r="D167" s="23" t="inlineStr">
+        <is>
+          <t>Wesco Spielküche, mehrteilig
+Zweite Spielküche von Wesco aus Birke-Multiplex: Mikrowellenmodul und Hängeschrank für die Wand, dazu Unterschränke mit Kochfeld, Spülbecken und Herdplatte. Weiße Klappen mit Holzgriffen, Module stehen frei.</t>
+        </is>
+      </c>
+      <c r="E167" s="13" t="n"/>
+      <c r="F167" s="23" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="G167" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H167" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I167" s="21" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="J167" s="24" t="n">
+        <v>650</v>
+      </c>
+      <c r="K167" s="25">
+        <f>J167*1.19</f>
+        <v/>
+      </c>
+      <c r="L167" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M167" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N167" s="16" t="n"/>
+      <c r="O167" s="17" t="n"/>
+      <c r="P167" s="18" t="n"/>
+      <c r="Q167" s="26">
+        <f>IF(N167&lt;&gt;"ja","",IF(O167="",H167,O167)*J167)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168" ht="78" customHeight="1">
+      <c r="A168" s="9" t="n">
+        <v>161</v>
+      </c>
+      <c r="B168" s="10" t="inlineStr">
+        <is>
+          <t>NU07-04</t>
+        </is>
+      </c>
+      <c r="C168" s="11" t="n"/>
+      <c r="D168" s="12" t="inlineStr">
+        <is>
+          <t>howa Kinderspielgrill
+Spielgrill aus Holz von howa: Rollklappe in Alu-Optik, Grillrost, zwei Drehknöpfe mit Digitalanzeige, seitliche Kochstelle und Ablageboden. Farbe an Kanten abgeplatzt.</t>
+        </is>
+      </c>
+      <c r="E168" s="13" t="n"/>
+      <c r="F168" s="12" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="G168" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H168" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I168" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J168" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K168" s="15">
+        <f>J168*1.19</f>
+        <v/>
+      </c>
+      <c r="L168" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M168" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N168" s="16" t="n"/>
+      <c r="O168" s="17" t="n"/>
+      <c r="P168" s="18" t="n"/>
+      <c r="Q168" s="19">
+        <f>IF(N168&lt;&gt;"ja","",IF(O168="",H168,O168)*J168)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169" ht="78" customHeight="1">
+      <c r="A169" s="20" t="n">
+        <v>162</v>
+      </c>
+      <c r="B169" s="21" t="inlineStr">
+        <is>
+          <t>NU07-05</t>
+        </is>
+      </c>
+      <c r="C169" s="22" t="n"/>
+      <c r="D169" s="23" t="inlineStr">
+        <is>
+          <t>Kinderkleiderschrank Birke mit zwei Türen
+Kleiderschrank aus Birke-Multiplex mit zwei weißen Türen und Griffmulden. Innen links eine Kleiderstange, rechts zwei Einlegeböden mit Durchgriff.</t>
+        </is>
+      </c>
+      <c r="E169" s="13" t="n"/>
+      <c r="F169" s="23" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="G169" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H169" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I169" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J169" s="24" t="n">
+        <v>140</v>
+      </c>
+      <c r="K169" s="25">
+        <f>J169*1.19</f>
+        <v/>
+      </c>
+      <c r="L169" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M169" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N169" s="16" t="n"/>
+      <c r="O169" s="17" t="n"/>
+      <c r="P169" s="18" t="n"/>
+      <c r="Q169" s="26">
+        <f>IF(N169&lt;&gt;"ja","",IF(O169="",H169,O169)*J169)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170" ht="78" customHeight="1">
+      <c r="A170" s="9" t="n">
+        <v>163</v>
+      </c>
+      <c r="B170" s="10" t="inlineStr">
+        <is>
+          <t>NU07-07</t>
+        </is>
+      </c>
+      <c r="C170" s="11" t="n"/>
+      <c r="D170" s="12" t="inlineStr">
+        <is>
+          <t>Aufbewahrungsregal weiß mit zehn Einschüben
+Schmales hohes Regal in Weiß mit zehn Einschubschienen, für flache Kästen oder Papier.</t>
+        </is>
+      </c>
+      <c r="E170" s="13" t="n"/>
+      <c r="F170" s="12" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="G170" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H170" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I170" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J170" s="14" t="n">
+        <v>75</v>
+      </c>
+      <c r="K170" s="15">
+        <f>J170*1.19</f>
+        <v/>
+      </c>
+      <c r="L170" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M170" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N170" s="16" t="n"/>
+      <c r="O170" s="17" t="n"/>
+      <c r="P170" s="18" t="n"/>
+      <c r="Q170" s="19">
+        <f>IF(N170&lt;&gt;"ja","",IF(O170="",H170,O170)*J170)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171" ht="78" customHeight="1">
+      <c r="A171" s="20" t="n">
+        <v>164</v>
+      </c>
+      <c r="B171" s="21" t="inlineStr">
+        <is>
+          <t>NU07-08</t>
+        </is>
+      </c>
+      <c r="C171" s="22" t="n"/>
+      <c r="D171" s="23" t="inlineStr">
+        <is>
+          <t>Sitzgruppe: Tisch und zwei Truhenbänke
+Sitzgruppe aus einem Kindertisch und zwei Sitzbänken mit Rückenlehne. Die Sitzflächen lassen sich anheben und geben je einen Stauraum frei, gedämpft über eine Gasdruckfeder. Weiße Platten auf Beinen aus Buche.</t>
+        </is>
+      </c>
+      <c r="E171" s="13" t="n"/>
+      <c r="F171" s="23" t="inlineStr">
+        <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="G171" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H171" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I171" s="21" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="J171" s="24" t="n">
+        <v>150</v>
+      </c>
+      <c r="K171" s="25">
+        <f>J171*1.19</f>
+        <v/>
+      </c>
+      <c r="L171" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M171" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N171" s="16" t="n"/>
+      <c r="O171" s="17" t="n"/>
+      <c r="P171" s="18" t="n"/>
+      <c r="Q171" s="26">
+        <f>IF(N171&lt;&gt;"ja","",IF(O171="",H171,O171)*J171)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173" ht="24" customHeight="1">
+      <c r="A173" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B166" s="1" t="n"/>
-      <c r="C166" s="1" t="n"/>
-      <c r="D166" s="1" t="n"/>
-      <c r="E166" s="1" t="n"/>
-      <c r="F166" s="1" t="n"/>
-      <c r="G166" s="1" t="n"/>
-      <c r="H166" s="1" t="n"/>
-      <c r="I166" s="1" t="n"/>
-      <c r="J166" s="1" t="n"/>
-      <c r="K166" s="1" t="n"/>
-      <c r="L166" s="1" t="n"/>
-      <c r="M166" s="1" t="n"/>
-      <c r="N166" s="1" t="n"/>
-      <c r="O166" s="1" t="n"/>
-      <c r="P166" s="1" t="n"/>
-      <c r="Q166" s="1" t="n"/>
-    </row>
-    <row r="167" ht="22" customHeight="1">
-      <c r="A167" s="37" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl netto</t>
-        </is>
-      </c>
-      <c r="Q167" s="38">
-        <f>SUM(Q8:Q164)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="168" ht="22" customHeight="1">
-      <c r="A168" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q168" s="38">
-        <f>Q167*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="169" ht="26" customHeight="1">
-      <c r="A169" s="39" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl brutto</t>
-        </is>
-      </c>
-      <c r="Q169" s="40">
-        <f>Q167+Q168</f>
-        <v/>
-      </c>
-    </row>
-    <row r="170" ht="22" customHeight="1">
-      <c r="A170" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q170" s="41">
-        <f>COUNTIF(N8:N164,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="24" customHeight="1">
-      <c r="A173" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B173" s="44" t="n"/>
-      <c r="C173" s="44" t="n"/>
-      <c r="D173" s="44" t="n"/>
-      <c r="E173" s="44" t="n"/>
-      <c r="F173" s="44" t="n"/>
-      <c r="G173" s="44" t="n"/>
-      <c r="H173" s="44" t="n"/>
-      <c r="I173" s="44" t="n"/>
-      <c r="J173" s="44" t="n"/>
-      <c r="K173" s="44" t="n"/>
-      <c r="L173" s="44" t="n"/>
-      <c r="M173" s="44" t="n"/>
-      <c r="N173" s="44" t="n"/>
-      <c r="O173" s="44" t="n"/>
-      <c r="P173" s="44" t="n"/>
-      <c r="Q173" s="44" t="n"/>
+      <c r="B173" s="1" t="n"/>
+      <c r="C173" s="1" t="n"/>
+      <c r="D173" s="1" t="n"/>
+      <c r="E173" s="1" t="n"/>
+      <c r="F173" s="1" t="n"/>
+      <c r="G173" s="1" t="n"/>
+      <c r="H173" s="1" t="n"/>
+      <c r="I173" s="1" t="n"/>
+      <c r="J173" s="1" t="n"/>
+      <c r="K173" s="1" t="n"/>
+      <c r="L173" s="1" t="n"/>
+      <c r="M173" s="1" t="n"/>
+      <c r="N173" s="1" t="n"/>
+      <c r="O173" s="1" t="n"/>
+      <c r="P173" s="1" t="n"/>
+      <c r="Q173" s="1" t="n"/>
     </row>
     <row r="174" ht="22" customHeight="1">
       <c r="A174" s="37" t="inlineStr">
         <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
+          <t>Wert Ihrer Auswahl netto</t>
         </is>
       </c>
       <c r="Q174" s="38">
-        <f>SUMPRODUCT(H8:H164,J8:J164)</f>
+        <f>SUM(Q8:Q171)</f>
         <v/>
       </c>
     </row>
@@ -14423,142 +14944,216 @@
         <v/>
       </c>
     </row>
-    <row r="176" ht="22" customHeight="1">
-      <c r="A176" s="45" t="inlineStr">
-        <is>
-          <t>Gesamtwert brutto</t>
-        </is>
-      </c>
-      <c r="Q176" s="46">
+    <row r="176" ht="26" customHeight="1">
+      <c r="A176" s="39" t="inlineStr">
+        <is>
+          <t>Wert Ihrer Auswahl brutto</t>
+        </is>
+      </c>
+      <c r="Q176" s="40">
         <f>Q174+Q175</f>
         <v/>
       </c>
     </row>
-    <row r="178" ht="24" customHeight="1">
-      <c r="A178" s="47" t="inlineStr">
-        <is>
-          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B178" s="48" t="n"/>
-      <c r="C178" s="48" t="n"/>
-      <c r="D178" s="48" t="n"/>
-      <c r="E178" s="48" t="n"/>
-      <c r="F178" s="48" t="n"/>
-      <c r="G178" s="48" t="n"/>
-      <c r="H178" s="48" t="n"/>
-      <c r="I178" s="48" t="n"/>
-      <c r="J178" s="48" t="n"/>
-      <c r="K178" s="48" t="n"/>
-      <c r="L178" s="48" t="n"/>
-      <c r="M178" s="48" t="n"/>
-      <c r="N178" s="48" t="n"/>
-      <c r="O178" s="48" t="n"/>
-      <c r="P178" s="48" t="n"/>
-      <c r="Q178" s="48" t="n"/>
-    </row>
-    <row r="179" ht="22" customHeight="1">
-      <c r="A179" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
-        </is>
-      </c>
-      <c r="Q179" s="38">
-        <f>-Q174*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="180" ht="22" customHeight="1">
-      <c r="A180" s="45" t="inlineStr">
-        <is>
-          <t>Paketpreis netto</t>
-        </is>
-      </c>
-      <c r="Q180" s="46">
-        <f>Q174+Q179</f>
-        <v/>
-      </c>
+    <row r="177" ht="22" customHeight="1">
+      <c r="A177" s="37" t="inlineStr">
+        <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q177" s="41">
+        <f>COUNTIF(N8:N171,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="24" customHeight="1">
+      <c r="A180" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B180" s="44" t="n"/>
+      <c r="C180" s="44" t="n"/>
+      <c r="D180" s="44" t="n"/>
+      <c r="E180" s="44" t="n"/>
+      <c r="F180" s="44" t="n"/>
+      <c r="G180" s="44" t="n"/>
+      <c r="H180" s="44" t="n"/>
+      <c r="I180" s="44" t="n"/>
+      <c r="J180" s="44" t="n"/>
+      <c r="K180" s="44" t="n"/>
+      <c r="L180" s="44" t="n"/>
+      <c r="M180" s="44" t="n"/>
+      <c r="N180" s="44" t="n"/>
+      <c r="O180" s="44" t="n"/>
+      <c r="P180" s="44" t="n"/>
+      <c r="Q180" s="44" t="n"/>
     </row>
     <row r="181" ht="22" customHeight="1">
       <c r="A181" s="37" t="inlineStr">
         <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q181" s="38">
+        <f>SUMPRODUCT(H8:H171,J8:J171)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182" ht="22" customHeight="1">
+      <c r="A182" s="37" t="inlineStr">
+        <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q181" s="38">
-        <f>Q180*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="182" ht="26" customHeight="1">
-      <c r="A182" s="39" t="inlineStr">
+      <c r="Q182" s="38">
+        <f>Q181*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183" ht="22" customHeight="1">
+      <c r="A183" s="45" t="inlineStr">
+        <is>
+          <t>Gesamtwert brutto</t>
+        </is>
+      </c>
+      <c r="Q183" s="46">
+        <f>Q181+Q182</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185" ht="24" customHeight="1">
+      <c r="A185" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B185" s="48" t="n"/>
+      <c r="C185" s="48" t="n"/>
+      <c r="D185" s="48" t="n"/>
+      <c r="E185" s="48" t="n"/>
+      <c r="F185" s="48" t="n"/>
+      <c r="G185" s="48" t="n"/>
+      <c r="H185" s="48" t="n"/>
+      <c r="I185" s="48" t="n"/>
+      <c r="J185" s="48" t="n"/>
+      <c r="K185" s="48" t="n"/>
+      <c r="L185" s="48" t="n"/>
+      <c r="M185" s="48" t="n"/>
+      <c r="N185" s="48" t="n"/>
+      <c r="O185" s="48" t="n"/>
+      <c r="P185" s="48" t="n"/>
+      <c r="Q185" s="48" t="n"/>
+    </row>
+    <row r="186" ht="22" customHeight="1">
+      <c r="A186" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
+        </is>
+      </c>
+      <c r="Q186" s="38">
+        <f>-Q181*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187" ht="22" customHeight="1">
+      <c r="A187" s="45" t="inlineStr">
+        <is>
+          <t>Paketpreis netto</t>
+        </is>
+      </c>
+      <c r="Q187" s="46">
+        <f>Q181+Q186</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188" ht="22" customHeight="1">
+      <c r="A188" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q188" s="38">
+        <f>Q187*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189" ht="26" customHeight="1">
+      <c r="A189" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q182" s="40">
-        <f>Q180+Q181</f>
-        <v/>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" s="42" t="inlineStr">
+      <c r="Q189" s="40">
+        <f>Q187+Q188</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="49" t="inlineStr">
+    <row r="192">
+      <c r="A192" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="186"/>
-    <row r="187"/>
-    <row r="188"/>
+    <row r="193"/>
+    <row r="194"/>
+    <row r="195"/>
   </sheetData>
-  <autoFilter ref="A7:Q164"/>
+  <autoFilter ref="A7:Q171"/>
   <mergeCells count="26">
     <mergeCell ref="C1:Q1"/>
     <mergeCell ref="A173:Q173"/>
     <mergeCell ref="A181:P181"/>
-    <mergeCell ref="A166:Q166"/>
+    <mergeCell ref="A188:P188"/>
+    <mergeCell ref="A192:Q195"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A180:P180"/>
+    <mergeCell ref="A178:Q178"/>
     <mergeCell ref="L4:Q4"/>
-    <mergeCell ref="A178:Q178"/>
-    <mergeCell ref="A170:P170"/>
     <mergeCell ref="C3:I3"/>
     <mergeCell ref="A176:P176"/>
-    <mergeCell ref="A167:P167"/>
-    <mergeCell ref="A185:Q188"/>
-    <mergeCell ref="A183:Q183"/>
+    <mergeCell ref="A186:P186"/>
     <mergeCell ref="A182:P182"/>
-    <mergeCell ref="A169:P169"/>
     <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A168:P168"/>
+    <mergeCell ref="A187:P187"/>
+    <mergeCell ref="A185:Q185"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
     <mergeCell ref="A174:P174"/>
-    <mergeCell ref="A171:Q171"/>
+    <mergeCell ref="A183:P183"/>
+    <mergeCell ref="A177:P177"/>
+    <mergeCell ref="A189:P189"/>
+    <mergeCell ref="A180:Q180"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A179:P179"/>
+    <mergeCell ref="A190:Q190"/>
     <mergeCell ref="A175:P175"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q164">
+  <conditionalFormatting sqref="A8:Q171">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N164" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N171" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O164" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O171" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$184</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4768,6 +4768,81 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>180</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="175" name="Image 175" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId175"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>181</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="176" name="Image 176" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId176"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>183</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="177" name="Image 177" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId177"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -5060,7 +5135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q204"/>
+  <dimension ref="A1:Q208"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -15664,261 +15739,501 @@
         <v/>
       </c>
     </row>
-    <row r="182" ht="24" customHeight="1">
-      <c r="A182" s="36" t="inlineStr">
+    <row r="181" ht="78" customHeight="1">
+      <c r="A181" s="20" t="n">
+        <v>174</v>
+      </c>
+      <c r="B181" s="35" t="inlineStr">
+        <is>
+          <t>BA01-01</t>
+        </is>
+      </c>
+      <c r="C181" s="22" t="n"/>
+      <c r="D181" s="23" t="inlineStr">
+        <is>
+          <t>Gemälde Mona Lisa, Pop-Art
+Acryl auf Leinwand im Hochformat: Mona Lisa als flächige Schablonenmalerei in Grau und Creme, darüber grüne Farbläufe vom oberen Rand. Eigenarbeit einer Privatperson, nicht signiert. Großes Format.</t>
+        </is>
+      </c>
+      <c r="E181" s="13" t="n"/>
+      <c r="F181" s="23" t="inlineStr">
+        <is>
+          <t>Flur 1</t>
+        </is>
+      </c>
+      <c r="G181" s="21" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H181" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I181" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J181" s="24" t="n">
+        <v>250</v>
+      </c>
+      <c r="K181" s="25">
+        <f>J181*1.19</f>
+        <v/>
+      </c>
+      <c r="L181" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M181" s="23" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N181" s="16" t="n"/>
+      <c r="O181" s="17" t="n"/>
+      <c r="P181" s="18" t="n"/>
+      <c r="Q181" s="26">
+        <f>IF(N181&lt;&gt;"ja","",IF(O181="",H181,O181)*J181)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182" ht="78" customHeight="1">
+      <c r="A182" s="9" t="n">
+        <v>175</v>
+      </c>
+      <c r="B182" s="10" t="inlineStr">
+        <is>
+          <t>BA01-02</t>
+        </is>
+      </c>
+      <c r="C182" s="11" t="n"/>
+      <c r="D182" s="12" t="inlineStr">
+        <is>
+          <t>Acrylbild abstrakt, Neonfarben
+Acryl auf Leinwand: abstrakte Komposition mit breiten Pinselzügen in Grün und Blau, darüber Schleudertechnik in Neongelb, Neonrot und Pink. Eigenarbeit einer Privatperson, nicht signiert.</t>
+        </is>
+      </c>
+      <c r="E182" s="13" t="n"/>
+      <c r="F182" s="12" t="inlineStr">
+        <is>
+          <t>Flur 1</t>
+        </is>
+      </c>
+      <c r="G182" s="10" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H182" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I182" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J182" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="K182" s="15">
+        <f>J182*1.19</f>
+        <v/>
+      </c>
+      <c r="L182" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M182" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N182" s="16" t="n"/>
+      <c r="O182" s="17" t="n"/>
+      <c r="P182" s="18" t="n"/>
+      <c r="Q182" s="19">
+        <f>IF(N182&lt;&gt;"ja","",IF(O182="",H182,O182)*J182)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183" ht="78" customHeight="1">
+      <c r="A183" s="20" t="n">
+        <v>176</v>
+      </c>
+      <c r="B183" s="21" t="inlineStr">
+        <is>
+          <t>BA01-03</t>
+        </is>
+      </c>
+      <c r="C183" s="22" t="n"/>
+      <c r="D183" s="23" t="inlineStr">
+        <is>
+          <t>Tannen-Dekoration
+Dekoration in Tannenform.</t>
+        </is>
+      </c>
+      <c r="E183" s="13" t="n"/>
+      <c r="F183" s="23" t="inlineStr">
+        <is>
+          <t>Flur 1</t>
+        </is>
+      </c>
+      <c r="G183" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H183" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I183" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J183" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="K183" s="25">
+        <f>J183*1.19</f>
+        <v/>
+      </c>
+      <c r="L183" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M183" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N183" s="16" t="n"/>
+      <c r="O183" s="17" t="n"/>
+      <c r="P183" s="18" t="n"/>
+      <c r="Q183" s="26">
+        <f>IF(N183&lt;&gt;"ja","",IF(O183="",H183,O183)*J183)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184" ht="78" customHeight="1">
+      <c r="A184" s="9" t="n">
+        <v>177</v>
+      </c>
+      <c r="B184" s="10" t="inlineStr">
+        <is>
+          <t>BA01-04</t>
+        </is>
+      </c>
+      <c r="C184" s="11" t="n"/>
+      <c r="D184" s="12" t="inlineStr">
+        <is>
+          <t>Leuchtbuchstabe K, schwarz
+Buchstabe K aus schwarz beschichtetem Metall mit sechs runden Leuchtmitteln auf der Front, zum Aufstellen.</t>
+        </is>
+      </c>
+      <c r="E184" s="13" t="n"/>
+      <c r="F184" s="12" t="inlineStr">
+        <is>
+          <t>Flur 1</t>
+        </is>
+      </c>
+      <c r="G184" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H184" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I184" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J184" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="K184" s="15">
+        <f>J184*1.19</f>
+        <v/>
+      </c>
+      <c r="L184" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M184" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N184" s="16" t="n"/>
+      <c r="O184" s="17" t="n"/>
+      <c r="P184" s="18" t="n"/>
+      <c r="Q184" s="19">
+        <f>IF(N184&lt;&gt;"ja","",IF(O184="",H184,O184)*J184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186" ht="24" customHeight="1">
+      <c r="A186" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B182" s="1" t="n"/>
-      <c r="C182" s="1" t="n"/>
-      <c r="D182" s="1" t="n"/>
-      <c r="E182" s="1" t="n"/>
-      <c r="F182" s="1" t="n"/>
-      <c r="G182" s="1" t="n"/>
-      <c r="H182" s="1" t="n"/>
-      <c r="I182" s="1" t="n"/>
-      <c r="J182" s="1" t="n"/>
-      <c r="K182" s="1" t="n"/>
-      <c r="L182" s="1" t="n"/>
-      <c r="M182" s="1" t="n"/>
-      <c r="N182" s="1" t="n"/>
-      <c r="O182" s="1" t="n"/>
-      <c r="P182" s="1" t="n"/>
-      <c r="Q182" s="1" t="n"/>
-    </row>
-    <row r="183" ht="22" customHeight="1">
-      <c r="A183" s="37" t="inlineStr">
+      <c r="B186" s="1" t="n"/>
+      <c r="C186" s="1" t="n"/>
+      <c r="D186" s="1" t="n"/>
+      <c r="E186" s="1" t="n"/>
+      <c r="F186" s="1" t="n"/>
+      <c r="G186" s="1" t="n"/>
+      <c r="H186" s="1" t="n"/>
+      <c r="I186" s="1" t="n"/>
+      <c r="J186" s="1" t="n"/>
+      <c r="K186" s="1" t="n"/>
+      <c r="L186" s="1" t="n"/>
+      <c r="M186" s="1" t="n"/>
+      <c r="N186" s="1" t="n"/>
+      <c r="O186" s="1" t="n"/>
+      <c r="P186" s="1" t="n"/>
+      <c r="Q186" s="1" t="n"/>
+    </row>
+    <row r="187" ht="22" customHeight="1">
+      <c r="A187" s="37" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl netto</t>
         </is>
       </c>
-      <c r="Q183" s="38">
-        <f>SUM(Q8:Q180)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="184" ht="22" customHeight="1">
-      <c r="A184" s="37" t="inlineStr">
+      <c r="Q187" s="38">
+        <f>SUM(Q8:Q184)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188" ht="22" customHeight="1">
+      <c r="A188" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q184" s="38">
-        <f>Q183*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="185" ht="26" customHeight="1">
-      <c r="A185" s="39" t="inlineStr">
+      <c r="Q188" s="38">
+        <f>Q187*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189" ht="26" customHeight="1">
+      <c r="A189" s="39" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl brutto</t>
         </is>
       </c>
-      <c r="Q185" s="40">
-        <f>Q183+Q184</f>
-        <v/>
-      </c>
-    </row>
-    <row r="186" ht="22" customHeight="1">
-      <c r="A186" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q186" s="41">
-        <f>COUNTIF(N8:N180,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="24" customHeight="1">
-      <c r="A189" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B189" s="44" t="n"/>
-      <c r="C189" s="44" t="n"/>
-      <c r="D189" s="44" t="n"/>
-      <c r="E189" s="44" t="n"/>
-      <c r="F189" s="44" t="n"/>
-      <c r="G189" s="44" t="n"/>
-      <c r="H189" s="44" t="n"/>
-      <c r="I189" s="44" t="n"/>
-      <c r="J189" s="44" t="n"/>
-      <c r="K189" s="44" t="n"/>
-      <c r="L189" s="44" t="n"/>
-      <c r="M189" s="44" t="n"/>
-      <c r="N189" s="44" t="n"/>
-      <c r="O189" s="44" t="n"/>
-      <c r="P189" s="44" t="n"/>
-      <c r="Q189" s="44" t="n"/>
+      <c r="Q189" s="40">
+        <f>Q187+Q188</f>
+        <v/>
+      </c>
     </row>
     <row r="190" ht="22" customHeight="1">
       <c r="A190" s="37" t="inlineStr">
         <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q190" s="41">
+        <f>COUNTIF(N8:N184,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="24" customHeight="1">
+      <c r="A193" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B193" s="44" t="n"/>
+      <c r="C193" s="44" t="n"/>
+      <c r="D193" s="44" t="n"/>
+      <c r="E193" s="44" t="n"/>
+      <c r="F193" s="44" t="n"/>
+      <c r="G193" s="44" t="n"/>
+      <c r="H193" s="44" t="n"/>
+      <c r="I193" s="44" t="n"/>
+      <c r="J193" s="44" t="n"/>
+      <c r="K193" s="44" t="n"/>
+      <c r="L193" s="44" t="n"/>
+      <c r="M193" s="44" t="n"/>
+      <c r="N193" s="44" t="n"/>
+      <c r="O193" s="44" t="n"/>
+      <c r="P193" s="44" t="n"/>
+      <c r="Q193" s="44" t="n"/>
+    </row>
+    <row r="194" ht="22" customHeight="1">
+      <c r="A194" s="37" t="inlineStr">
+        <is>
           <t>Gesamtwert aller gelisteten Positionen netto</t>
         </is>
       </c>
-      <c r="Q190" s="38">
-        <f>SUMPRODUCT(H8:H180,J8:J180)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="191" ht="22" customHeight="1">
-      <c r="A191" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q191" s="38">
-        <f>Q190*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="192" ht="22" customHeight="1">
-      <c r="A192" s="45" t="inlineStr">
-        <is>
-          <t>Gesamtwert brutto</t>
-        </is>
-      </c>
-      <c r="Q192" s="46">
-        <f>Q190+Q191</f>
-        <v/>
-      </c>
-    </row>
-    <row r="194" ht="24" customHeight="1">
-      <c r="A194" s="47" t="inlineStr">
-        <is>
-          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B194" s="48" t="n"/>
-      <c r="C194" s="48" t="n"/>
-      <c r="D194" s="48" t="n"/>
-      <c r="E194" s="48" t="n"/>
-      <c r="F194" s="48" t="n"/>
-      <c r="G194" s="48" t="n"/>
-      <c r="H194" s="48" t="n"/>
-      <c r="I194" s="48" t="n"/>
-      <c r="J194" s="48" t="n"/>
-      <c r="K194" s="48" t="n"/>
-      <c r="L194" s="48" t="n"/>
-      <c r="M194" s="48" t="n"/>
-      <c r="N194" s="48" t="n"/>
-      <c r="O194" s="48" t="n"/>
-      <c r="P194" s="48" t="n"/>
-      <c r="Q194" s="48" t="n"/>
+      <c r="Q194" s="38">
+        <f>SUMPRODUCT(H8:H184,J8:J184)</f>
+        <v/>
+      </c>
     </row>
     <row r="195" ht="22" customHeight="1">
       <c r="A195" s="37" t="inlineStr">
         <is>
-          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
+          <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
       <c r="Q195" s="38">
-        <f>-Q190*0.15</f>
+        <f>Q194*0.19</f>
         <v/>
       </c>
     </row>
     <row r="196" ht="22" customHeight="1">
       <c r="A196" s="45" t="inlineStr">
         <is>
+          <t>Gesamtwert brutto</t>
+        </is>
+      </c>
+      <c r="Q196" s="46">
+        <f>Q194+Q195</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198" ht="24" customHeight="1">
+      <c r="A198" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B198" s="48" t="n"/>
+      <c r="C198" s="48" t="n"/>
+      <c r="D198" s="48" t="n"/>
+      <c r="E198" s="48" t="n"/>
+      <c r="F198" s="48" t="n"/>
+      <c r="G198" s="48" t="n"/>
+      <c r="H198" s="48" t="n"/>
+      <c r="I198" s="48" t="n"/>
+      <c r="J198" s="48" t="n"/>
+      <c r="K198" s="48" t="n"/>
+      <c r="L198" s="48" t="n"/>
+      <c r="M198" s="48" t="n"/>
+      <c r="N198" s="48" t="n"/>
+      <c r="O198" s="48" t="n"/>
+      <c r="P198" s="48" t="n"/>
+      <c r="Q198" s="48" t="n"/>
+    </row>
+    <row r="199" ht="22" customHeight="1">
+      <c r="A199" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
+        </is>
+      </c>
+      <c r="Q199" s="38">
+        <f>-Q194*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200" ht="22" customHeight="1">
+      <c r="A200" s="45" t="inlineStr">
+        <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="Q196" s="46">
-        <f>Q190+Q195</f>
-        <v/>
-      </c>
-    </row>
-    <row r="197" ht="22" customHeight="1">
-      <c r="A197" s="37" t="inlineStr">
+      <c r="Q200" s="46">
+        <f>Q194+Q199</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201" ht="22" customHeight="1">
+      <c r="A201" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q197" s="38">
-        <f>Q196*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198" ht="26" customHeight="1">
-      <c r="A198" s="39" t="inlineStr">
+      <c r="Q201" s="38">
+        <f>Q200*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202" ht="26" customHeight="1">
+      <c r="A202" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q198" s="40">
-        <f>Q196+Q197</f>
-        <v/>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="42" t="inlineStr">
+      <c r="Q202" s="40">
+        <f>Q200+Q201</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="201">
-      <c r="A201" s="49" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="202"/>
-    <row r="203"/>
-    <row r="204"/>
+    <row r="206"/>
+    <row r="207"/>
+    <row r="208"/>
   </sheetData>
-  <autoFilter ref="A7:Q180"/>
+  <autoFilter ref="A7:Q184"/>
   <mergeCells count="26">
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A185:P185"/>
-    <mergeCell ref="A184:P184"/>
-    <mergeCell ref="A182:Q182"/>
+    <mergeCell ref="A194:P194"/>
+    <mergeCell ref="A188:P188"/>
+    <mergeCell ref="A186:Q186"/>
+    <mergeCell ref="A200:P200"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A191:Q191"/>
     <mergeCell ref="L4:Q4"/>
     <mergeCell ref="A190:P190"/>
+    <mergeCell ref="A199:P199"/>
+    <mergeCell ref="A202:P202"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A187:Q187"/>
-    <mergeCell ref="A186:P186"/>
-    <mergeCell ref="A191:P191"/>
-    <mergeCell ref="A189:Q189"/>
-    <mergeCell ref="A197:P197"/>
+    <mergeCell ref="A193:Q193"/>
+    <mergeCell ref="A201:P201"/>
+    <mergeCell ref="A198:Q198"/>
     <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A201:Q204"/>
+    <mergeCell ref="A187:P187"/>
+    <mergeCell ref="A203:Q203"/>
+    <mergeCell ref="A196:P196"/>
+    <mergeCell ref="L2:Q2"/>
     <mergeCell ref="A5:Q5"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A194:Q194"/>
-    <mergeCell ref="A196:P196"/>
-    <mergeCell ref="A183:P183"/>
-    <mergeCell ref="A192:P192"/>
-    <mergeCell ref="A198:P198"/>
-    <mergeCell ref="A199:Q199"/>
+    <mergeCell ref="A189:P189"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
+    <mergeCell ref="A205:Q208"/>
     <mergeCell ref="A195:P195"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q180">
+  <conditionalFormatting sqref="A8:Q184">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N180" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N184" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O180" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O184" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -4822,17 +4822,42 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
+      <row>182</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="177" name="Image 177" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId177"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
       <row>183</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="177" name="Image 177" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId177"/>
+        <cNvPr id="178" name="Image 178" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId178"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -15871,8 +15896,8 @@
       <c r="C183" s="22" t="n"/>
       <c r="D183" s="23" t="inlineStr">
         <is>
-          <t>Tannen-Dekoration
-Dekoration in Tannenform.</t>
+          <t>Deko-Tannen Metall auf Holzsockel
+Stilisierte Tannen aus schwarz mattiertem Metall, auf ovalen Sockeln aus Massivholz. Skandinavischer Stil, standfest.</t>
         </is>
       </c>
       <c r="E183" s="13" t="n"/>
@@ -15883,11 +15908,11 @@
       </c>
       <c r="G183" s="21" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H183" s="21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I183" s="21" t="inlineStr">
         <is>
@@ -15908,7 +15933,7 @@
       </c>
       <c r="M183" s="23" t="inlineStr">
         <is>
-          <t>nur Abholung</t>
+          <t>Versand möglich</t>
         </is>
       </c>
       <c r="N183" s="16" t="n"/>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$184</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$192</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4868,6 +4868,181 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>185</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="179" name="Image 179" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId179"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>186</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="180" name="Image 180" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId180"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>187</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="181" name="Image 181" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId181"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>188</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="182" name="Image 182" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId182"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>189</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="183" name="Image 183" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId183"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>190</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="184" name="Image 184" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId184"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>191</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="185" name="Image 185" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId185"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -5160,7 +5335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q208"/>
+  <dimension ref="A1:Q216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -15972,7 +16147,7 @@
         </is>
       </c>
       <c r="H184" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I184" s="10" t="inlineStr">
         <is>
@@ -16004,261 +16179,741 @@
         <v/>
       </c>
     </row>
-    <row r="186" ht="24" customHeight="1">
-      <c r="A186" s="36" t="inlineStr">
+    <row r="185" ht="78" customHeight="1">
+      <c r="A185" s="20" t="n">
+        <v>178</v>
+      </c>
+      <c r="B185" s="21" t="inlineStr">
+        <is>
+          <t>BA02-01</t>
+        </is>
+      </c>
+      <c r="C185" s="22" t="n"/>
+      <c r="D185" s="23" t="inlineStr">
+        <is>
+          <t>Kindergarderobe weiß
+Kindergarderobe in Weiß.</t>
+        </is>
+      </c>
+      <c r="E185" s="13" t="n"/>
+      <c r="F185" s="23" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G185" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H185" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I185" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J185" s="24" t="n">
+        <v>90</v>
+      </c>
+      <c r="K185" s="25">
+        <f>J185*1.19</f>
+        <v/>
+      </c>
+      <c r="L185" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M185" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N185" s="16" t="n"/>
+      <c r="O185" s="17" t="n"/>
+      <c r="P185" s="18" t="n"/>
+      <c r="Q185" s="26">
+        <f>IF(N185&lt;&gt;"ja","",IF(O185="",H185,O185)*J185)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186" ht="78" customHeight="1">
+      <c r="A186" s="9" t="n">
+        <v>179</v>
+      </c>
+      <c r="B186" s="10" t="inlineStr">
+        <is>
+          <t>BA02-02</t>
+        </is>
+      </c>
+      <c r="C186" s="11" t="n"/>
+      <c r="D186" s="12" t="inlineStr">
+        <is>
+          <t>Rutscherauto rot
+Rutscherauto in Sportwagenform, roter Kunststoffkorpus mit schwarzer Sitzfläche in Rautensteppung, verchromte Felgen, Lehne hinten zum Schieben.</t>
+        </is>
+      </c>
+      <c r="E186" s="13" t="n"/>
+      <c r="F186" s="12" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G186" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H186" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I186" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J186" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K186" s="15">
+        <f>J186*1.19</f>
+        <v/>
+      </c>
+      <c r="L186" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M186" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N186" s="16" t="n"/>
+      <c r="O186" s="17" t="n"/>
+      <c r="P186" s="18" t="n"/>
+      <c r="Q186" s="19">
+        <f>IF(N186&lt;&gt;"ja","",IF(O186="",H186,O186)*J186)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187" ht="78" customHeight="1">
+      <c r="A187" s="20" t="n">
+        <v>180</v>
+      </c>
+      <c r="B187" s="21" t="inlineStr">
+        <is>
+          <t>BA02-03</t>
+        </is>
+      </c>
+      <c r="C187" s="22" t="n"/>
+      <c r="D187" s="23" t="inlineStr">
+        <is>
+          <t>Bilder Schwarzwald, gerahmt
+Schwarz gerahmte Zeichnungen hinter Glas in schlichter Strichtechnik: Bergkette, Mädchen mit Bollenhut und Tannenwald. Motivgruppe Schwarzwald.</t>
+        </is>
+      </c>
+      <c r="E187" s="13" t="n"/>
+      <c r="F187" s="23" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G187" s="21" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H187" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I187" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J187" s="24" t="n">
+        <v>45</v>
+      </c>
+      <c r="K187" s="25">
+        <f>J187*1.19</f>
+        <v/>
+      </c>
+      <c r="L187" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M187" s="23" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N187" s="16" t="n"/>
+      <c r="O187" s="17" t="n"/>
+      <c r="P187" s="18" t="n"/>
+      <c r="Q187" s="26">
+        <f>IF(N187&lt;&gt;"ja","",IF(O187="",H187,O187)*J187)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188" ht="78" customHeight="1">
+      <c r="A188" s="9" t="n">
+        <v>181</v>
+      </c>
+      <c r="B188" s="10" t="inlineStr">
+        <is>
+          <t>BA02-04</t>
+        </is>
+      </c>
+      <c r="C188" s="11" t="n"/>
+      <c r="D188" s="12" t="inlineStr">
+        <is>
+          <t>Kinder-Ohrensessel grau, Kunstleder
+Ohrensessel in Kindergröße, hellgrauer Kunstlederbezug, geschwungene schwarze Holzbeine.</t>
+        </is>
+      </c>
+      <c r="E188" s="13" t="n"/>
+      <c r="F188" s="12" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G188" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H188" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I188" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J188" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="K188" s="15">
+        <f>J188*1.19</f>
+        <v/>
+      </c>
+      <c r="L188" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M188" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N188" s="16" t="n"/>
+      <c r="O188" s="17" t="n"/>
+      <c r="P188" s="18" t="n"/>
+      <c r="Q188" s="19">
+        <f>IF(N188&lt;&gt;"ja","",IF(O188="",H188,O188)*J188)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189" ht="78" customHeight="1">
+      <c r="A189" s="20" t="n">
+        <v>182</v>
+      </c>
+      <c r="B189" s="21" t="inlineStr">
+        <is>
+          <t>BA02-05</t>
+        </is>
+      </c>
+      <c r="C189" s="22" t="n"/>
+      <c r="D189" s="23" t="inlineStr">
+        <is>
+          <t>Ablagepult Holz auf Metallgestell
+Pult mit geneigter Platte aus dunklem Holz mit schwarzer Auflage, auf einem C-förmigen schwarzen Metallgestell. Untergreifbar, im Haus als Stehpult für die Anwesenheitsliste genutzt.</t>
+        </is>
+      </c>
+      <c r="E189" s="13" t="n"/>
+      <c r="F189" s="23" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G189" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H189" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I189" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J189" s="24" t="n">
+        <v>45</v>
+      </c>
+      <c r="K189" s="25">
+        <f>J189*1.19</f>
+        <v/>
+      </c>
+      <c r="L189" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M189" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N189" s="16" t="n"/>
+      <c r="O189" s="17" t="n"/>
+      <c r="P189" s="18" t="n"/>
+      <c r="Q189" s="26">
+        <f>IF(N189&lt;&gt;"ja","",IF(O189="",H189,O189)*J189)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190" ht="78" customHeight="1">
+      <c r="A190" s="9" t="n">
+        <v>183</v>
+      </c>
+      <c r="B190" s="10" t="inlineStr">
+        <is>
+          <t>BA02-06</t>
+        </is>
+      </c>
+      <c r="C190" s="11" t="n"/>
+      <c r="D190" s="12" t="inlineStr">
+        <is>
+          <t>Truhenbank weiß mit Fellauflage
+Sitzbank in Weiß mit geschwungenen Seitenteilen, Rückenbrett und aufklappbarer Sitzfläche mit Beschlägen. Darunter ein großer Stauraum. Eine weiße Fellauflage liegt auf der Sitzfläche.</t>
+        </is>
+      </c>
+      <c r="E190" s="13" t="n"/>
+      <c r="F190" s="12" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G190" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H190" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I190" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J190" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="K190" s="15">
+        <f>J190*1.19</f>
+        <v/>
+      </c>
+      <c r="L190" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M190" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N190" s="16" t="n"/>
+      <c r="O190" s="17" t="n"/>
+      <c r="P190" s="18" t="n"/>
+      <c r="Q190" s="19">
+        <f>IF(N190&lt;&gt;"ja","",IF(O190="",H190,O190)*J190)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191" ht="78" customHeight="1">
+      <c r="A191" s="20" t="n">
+        <v>184</v>
+      </c>
+      <c r="B191" s="21" t="inlineStr">
+        <is>
+          <t>BA02-08</t>
+        </is>
+      </c>
+      <c r="C191" s="22" t="n"/>
+      <c r="D191" s="23" t="inlineStr">
+        <is>
+          <t>Kinderschrank weiß mit Handabdrücken
+Hoher Schrank in Weiß mit Türen und Schubladen, Griffmulden. Auf den Fronten kleben Aufkleber mit Kinderhandabdrücken in Schwarz und Rot; sie lassen sich abziehen.</t>
+        </is>
+      </c>
+      <c r="E191" s="13" t="n"/>
+      <c r="F191" s="23" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G191" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H191" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I191" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J191" s="24" t="n">
+        <v>90</v>
+      </c>
+      <c r="K191" s="25">
+        <f>J191*1.19</f>
+        <v/>
+      </c>
+      <c r="L191" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M191" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N191" s="16" t="n"/>
+      <c r="O191" s="17" t="n"/>
+      <c r="P191" s="18" t="n"/>
+      <c r="Q191" s="26">
+        <f>IF(N191&lt;&gt;"ja","",IF(O191="",H191,O191)*J191)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192" ht="78" customHeight="1">
+      <c r="A192" s="9" t="n">
+        <v>185</v>
+      </c>
+      <c r="B192" s="10" t="inlineStr">
+        <is>
+          <t>BA02-09</t>
+        </is>
+      </c>
+      <c r="C192" s="11" t="n"/>
+      <c r="D192" s="12" t="inlineStr">
+        <is>
+          <t>Deko-Häuser Keramik
+Drei Häuschen aus Keramik mit ausgestanzten Fenstern, zum Beleuchten mit einem Teelicht: eines craquelé-grau, eines cremeweiß glasiert, eines dunkelgrau mit rundem Fenster.</t>
+        </is>
+      </c>
+      <c r="E192" s="13" t="n"/>
+      <c r="F192" s="12" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G192" s="10" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H192" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I192" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J192" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="K192" s="15">
+        <f>J192*1.19</f>
+        <v/>
+      </c>
+      <c r="L192" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M192" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N192" s="16" t="n"/>
+      <c r="O192" s="17" t="n"/>
+      <c r="P192" s="18" t="n"/>
+      <c r="Q192" s="19">
+        <f>IF(N192&lt;&gt;"ja","",IF(O192="",H192,O192)*J192)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194" ht="24" customHeight="1">
+      <c r="A194" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B186" s="1" t="n"/>
-      <c r="C186" s="1" t="n"/>
-      <c r="D186" s="1" t="n"/>
-      <c r="E186" s="1" t="n"/>
-      <c r="F186" s="1" t="n"/>
-      <c r="G186" s="1" t="n"/>
-      <c r="H186" s="1" t="n"/>
-      <c r="I186" s="1" t="n"/>
-      <c r="J186" s="1" t="n"/>
-      <c r="K186" s="1" t="n"/>
-      <c r="L186" s="1" t="n"/>
-      <c r="M186" s="1" t="n"/>
-      <c r="N186" s="1" t="n"/>
-      <c r="O186" s="1" t="n"/>
-      <c r="P186" s="1" t="n"/>
-      <c r="Q186" s="1" t="n"/>
-    </row>
-    <row r="187" ht="22" customHeight="1">
-      <c r="A187" s="37" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl netto</t>
-        </is>
-      </c>
-      <c r="Q187" s="38">
-        <f>SUM(Q8:Q184)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="188" ht="22" customHeight="1">
-      <c r="A188" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q188" s="38">
-        <f>Q187*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="189" ht="26" customHeight="1">
-      <c r="A189" s="39" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl brutto</t>
-        </is>
-      </c>
-      <c r="Q189" s="40">
-        <f>Q187+Q188</f>
-        <v/>
-      </c>
-    </row>
-    <row r="190" ht="22" customHeight="1">
-      <c r="A190" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q190" s="41">
-        <f>COUNTIF(N8:N184,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="24" customHeight="1">
-      <c r="A193" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B193" s="44" t="n"/>
-      <c r="C193" s="44" t="n"/>
-      <c r="D193" s="44" t="n"/>
-      <c r="E193" s="44" t="n"/>
-      <c r="F193" s="44" t="n"/>
-      <c r="G193" s="44" t="n"/>
-      <c r="H193" s="44" t="n"/>
-      <c r="I193" s="44" t="n"/>
-      <c r="J193" s="44" t="n"/>
-      <c r="K193" s="44" t="n"/>
-      <c r="L193" s="44" t="n"/>
-      <c r="M193" s="44" t="n"/>
-      <c r="N193" s="44" t="n"/>
-      <c r="O193" s="44" t="n"/>
-      <c r="P193" s="44" t="n"/>
-      <c r="Q193" s="44" t="n"/>
-    </row>
-    <row r="194" ht="22" customHeight="1">
-      <c r="A194" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
-        </is>
-      </c>
-      <c r="Q194" s="38">
-        <f>SUMPRODUCT(H8:H184,J8:J184)</f>
-        <v/>
-      </c>
+      <c r="B194" s="1" t="n"/>
+      <c r="C194" s="1" t="n"/>
+      <c r="D194" s="1" t="n"/>
+      <c r="E194" s="1" t="n"/>
+      <c r="F194" s="1" t="n"/>
+      <c r="G194" s="1" t="n"/>
+      <c r="H194" s="1" t="n"/>
+      <c r="I194" s="1" t="n"/>
+      <c r="J194" s="1" t="n"/>
+      <c r="K194" s="1" t="n"/>
+      <c r="L194" s="1" t="n"/>
+      <c r="M194" s="1" t="n"/>
+      <c r="N194" s="1" t="n"/>
+      <c r="O194" s="1" t="n"/>
+      <c r="P194" s="1" t="n"/>
+      <c r="Q194" s="1" t="n"/>
     </row>
     <row r="195" ht="22" customHeight="1">
       <c r="A195" s="37" t="inlineStr">
         <is>
+          <t>Wert Ihrer Auswahl netto</t>
+        </is>
+      </c>
+      <c r="Q195" s="38">
+        <f>SUM(Q8:Q192)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196" ht="22" customHeight="1">
+      <c r="A196" s="37" t="inlineStr">
+        <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q195" s="38">
-        <f>Q194*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196" ht="22" customHeight="1">
-      <c r="A196" s="45" t="inlineStr">
+      <c r="Q196" s="38">
+        <f>Q195*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197" ht="26" customHeight="1">
+      <c r="A197" s="39" t="inlineStr">
+        <is>
+          <t>Wert Ihrer Auswahl brutto</t>
+        </is>
+      </c>
+      <c r="Q197" s="40">
+        <f>Q195+Q196</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198" ht="22" customHeight="1">
+      <c r="A198" s="37" t="inlineStr">
+        <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q198" s="41">
+        <f>COUNTIF(N8:N192,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="24" customHeight="1">
+      <c r="A201" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B201" s="44" t="n"/>
+      <c r="C201" s="44" t="n"/>
+      <c r="D201" s="44" t="n"/>
+      <c r="E201" s="44" t="n"/>
+      <c r="F201" s="44" t="n"/>
+      <c r="G201" s="44" t="n"/>
+      <c r="H201" s="44" t="n"/>
+      <c r="I201" s="44" t="n"/>
+      <c r="J201" s="44" t="n"/>
+      <c r="K201" s="44" t="n"/>
+      <c r="L201" s="44" t="n"/>
+      <c r="M201" s="44" t="n"/>
+      <c r="N201" s="44" t="n"/>
+      <c r="O201" s="44" t="n"/>
+      <c r="P201" s="44" t="n"/>
+      <c r="Q201" s="44" t="n"/>
+    </row>
+    <row r="202" ht="22" customHeight="1">
+      <c r="A202" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q202" s="38">
+        <f>SUMPRODUCT(H8:H192,J8:J192)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203" ht="22" customHeight="1">
+      <c r="A203" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q203" s="38">
+        <f>Q202*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204" ht="22" customHeight="1">
+      <c r="A204" s="45" t="inlineStr">
         <is>
           <t>Gesamtwert brutto</t>
         </is>
       </c>
-      <c r="Q196" s="46">
-        <f>Q194+Q195</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198" ht="24" customHeight="1">
-      <c r="A198" s="47" t="inlineStr">
+      <c r="Q204" s="46">
+        <f>Q202+Q203</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206" ht="24" customHeight="1">
+      <c r="A206" s="47" t="inlineStr">
         <is>
           <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
         </is>
       </c>
-      <c r="B198" s="48" t="n"/>
-      <c r="C198" s="48" t="n"/>
-      <c r="D198" s="48" t="n"/>
-      <c r="E198" s="48" t="n"/>
-      <c r="F198" s="48" t="n"/>
-      <c r="G198" s="48" t="n"/>
-      <c r="H198" s="48" t="n"/>
-      <c r="I198" s="48" t="n"/>
-      <c r="J198" s="48" t="n"/>
-      <c r="K198" s="48" t="n"/>
-      <c r="L198" s="48" t="n"/>
-      <c r="M198" s="48" t="n"/>
-      <c r="N198" s="48" t="n"/>
-      <c r="O198" s="48" t="n"/>
-      <c r="P198" s="48" t="n"/>
-      <c r="Q198" s="48" t="n"/>
-    </row>
-    <row r="199" ht="22" customHeight="1">
-      <c r="A199" s="37" t="inlineStr">
+      <c r="B206" s="48" t="n"/>
+      <c r="C206" s="48" t="n"/>
+      <c r="D206" s="48" t="n"/>
+      <c r="E206" s="48" t="n"/>
+      <c r="F206" s="48" t="n"/>
+      <c r="G206" s="48" t="n"/>
+      <c r="H206" s="48" t="n"/>
+      <c r="I206" s="48" t="n"/>
+      <c r="J206" s="48" t="n"/>
+      <c r="K206" s="48" t="n"/>
+      <c r="L206" s="48" t="n"/>
+      <c r="M206" s="48" t="n"/>
+      <c r="N206" s="48" t="n"/>
+      <c r="O206" s="48" t="n"/>
+      <c r="P206" s="48" t="n"/>
+      <c r="Q206" s="48" t="n"/>
+    </row>
+    <row r="207" ht="22" customHeight="1">
+      <c r="A207" s="37" t="inlineStr">
         <is>
           <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
         </is>
       </c>
-      <c r="Q199" s="38">
-        <f>-Q194*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="200" ht="22" customHeight="1">
-      <c r="A200" s="45" t="inlineStr">
+      <c r="Q207" s="38">
+        <f>-Q202*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208" ht="22" customHeight="1">
+      <c r="A208" s="45" t="inlineStr">
         <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="Q200" s="46">
-        <f>Q194+Q199</f>
-        <v/>
-      </c>
-    </row>
-    <row r="201" ht="22" customHeight="1">
-      <c r="A201" s="37" t="inlineStr">
+      <c r="Q208" s="46">
+        <f>Q202+Q207</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209" ht="22" customHeight="1">
+      <c r="A209" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q201" s="38">
-        <f>Q200*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="202" ht="26" customHeight="1">
-      <c r="A202" s="39" t="inlineStr">
+      <c r="Q209" s="38">
+        <f>Q208*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210" ht="26" customHeight="1">
+      <c r="A210" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q202" s="40">
-        <f>Q200+Q201</f>
-        <v/>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="42" t="inlineStr">
+      <c r="Q210" s="40">
+        <f>Q208+Q209</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="49" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="206"/>
-    <row r="207"/>
-    <row r="208"/>
+    <row r="214"/>
+    <row r="215"/>
+    <row r="216"/>
   </sheetData>
-  <autoFilter ref="A7:Q184"/>
+  <autoFilter ref="A7:Q192"/>
   <mergeCells count="26">
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A194:P194"/>
-    <mergeCell ref="A188:P188"/>
-    <mergeCell ref="A186:Q186"/>
-    <mergeCell ref="A200:P200"/>
+    <mergeCell ref="A211:Q211"/>
+    <mergeCell ref="A203:P203"/>
+    <mergeCell ref="A201:Q201"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A191:Q191"/>
+    <mergeCell ref="A209:P209"/>
     <mergeCell ref="L4:Q4"/>
-    <mergeCell ref="A190:P190"/>
-    <mergeCell ref="A199:P199"/>
+    <mergeCell ref="A213:Q216"/>
     <mergeCell ref="A202:P202"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A193:Q193"/>
-    <mergeCell ref="A201:P201"/>
-    <mergeCell ref="A198:Q198"/>
+    <mergeCell ref="A207:P207"/>
+    <mergeCell ref="A197:P197"/>
     <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A187:P187"/>
-    <mergeCell ref="A203:Q203"/>
     <mergeCell ref="A196:P196"/>
+    <mergeCell ref="A194:Q194"/>
     <mergeCell ref="L2:Q2"/>
     <mergeCell ref="A5:Q5"/>
-    <mergeCell ref="A189:P189"/>
+    <mergeCell ref="A208:P208"/>
+    <mergeCell ref="A206:Q206"/>
+    <mergeCell ref="A198:P198"/>
+    <mergeCell ref="A199:Q199"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A205:Q208"/>
+    <mergeCell ref="A210:P210"/>
     <mergeCell ref="A195:P195"/>
+    <mergeCell ref="A204:P204"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q184">
+  <conditionalFormatting sqref="A8:Q192">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N184" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N192" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O184" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O192" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$191</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -4872,17 +4872,42 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
+      <row>184</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="179" name="Image 179" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId179"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
       <row>185</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="179" name="Image 179" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId179"/>
+        <cNvPr id="180" name="Image 180" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId180"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -4900,89 +4925,89 @@
       <row>186</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="181" name="Image 181" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId181"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>187</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="182" name="Image 182" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId182"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>188</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="180" name="Image 180" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId180"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>187</row>
+        <cNvPr id="183" name="Image 183" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId183"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>189</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="181" name="Image 181" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId181"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>188</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="182" name="Image 182" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId182"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>189</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="183" name="Image 183" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId183"/>
+        <cNvPr id="184" name="Image 184" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId184"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -4998,31 +5023,6 @@
       <col>2</col>
       <colOff>0</colOff>
       <row>190</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="184" name="Image 184" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId184"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>191</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
@@ -5335,7 +5335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q216"/>
+  <dimension ref="A1:Q215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -10863,7 +10863,7 @@
         </is>
       </c>
       <c r="H96" s="10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I96" s="10" t="inlineStr">
         <is>
@@ -16185,14 +16185,14 @@
       </c>
       <c r="B185" s="21" t="inlineStr">
         <is>
-          <t>BA02-01</t>
+          <t>BA02-02</t>
         </is>
       </c>
       <c r="C185" s="22" t="n"/>
       <c r="D185" s="23" t="inlineStr">
         <is>
-          <t>Kindergarderobe weiß
-Kindergarderobe in Weiß.</t>
+          <t>Rutscherauto rot
+Rutscherauto in Sportwagenform, roter Kunststoffkorpus mit schwarzer Sitzfläche in Rautensteppung, verchromte Felgen, Lehne hinten zum Schieben.</t>
         </is>
       </c>
       <c r="E185" s="13" t="n"/>
@@ -16207,7 +16207,7 @@
         </is>
       </c>
       <c r="H185" s="21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I185" s="21" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         </is>
       </c>
       <c r="J185" s="24" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="K185" s="25">
         <f>J185*1.19</f>
@@ -16245,14 +16245,14 @@
       </c>
       <c r="B186" s="10" t="inlineStr">
         <is>
-          <t>BA02-02</t>
+          <t>BA02-03</t>
         </is>
       </c>
       <c r="C186" s="11" t="n"/>
       <c r="D186" s="12" t="inlineStr">
         <is>
-          <t>Rutscherauto rot
-Rutscherauto in Sportwagenform, roter Kunststoffkorpus mit schwarzer Sitzfläche in Rautensteppung, verchromte Felgen, Lehne hinten zum Schieben.</t>
+          <t>Bilder Schwarzwald, gerahmt
+Schwarz gerahmte Zeichnungen hinter Glas in schlichter Strichtechnik: Bergkette, Mädchen mit Bollenhut und Tannenwald. Motivgruppe Schwarzwald.</t>
         </is>
       </c>
       <c r="E186" s="13" t="n"/>
@@ -16263,11 +16263,11 @@
       </c>
       <c r="G186" s="10" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H186" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I186" s="10" t="inlineStr">
         <is>
@@ -16275,7 +16275,7 @@
         </is>
       </c>
       <c r="J186" s="14" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K186" s="15">
         <f>J186*1.19</f>
@@ -16288,7 +16288,7 @@
       </c>
       <c r="M186" s="12" t="inlineStr">
         <is>
-          <t>nur Abholung</t>
+          <t>Versand möglich</t>
         </is>
       </c>
       <c r="N186" s="16" t="n"/>
@@ -16305,14 +16305,14 @@
       </c>
       <c r="B187" s="21" t="inlineStr">
         <is>
-          <t>BA02-03</t>
+          <t>BA02-04</t>
         </is>
       </c>
       <c r="C187" s="22" t="n"/>
       <c r="D187" s="23" t="inlineStr">
         <is>
-          <t>Bilder Schwarzwald, gerahmt
-Schwarz gerahmte Zeichnungen hinter Glas in schlichter Strichtechnik: Bergkette, Mädchen mit Bollenhut und Tannenwald. Motivgruppe Schwarzwald.</t>
+          <t>Kinder-Ohrensessel grau, Kunstleder
+Ohrensessel in Kindergröße, hellgrauer Kunstlederbezug, geschwungene schwarze Holzbeine.</t>
         </is>
       </c>
       <c r="E187" s="13" t="n"/>
@@ -16323,11 +16323,11 @@
       </c>
       <c r="G187" s="21" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H187" s="21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I187" s="21" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         </is>
       </c>
       <c r="J187" s="24" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="K187" s="25">
         <f>J187*1.19</f>
@@ -16348,7 +16348,7 @@
       </c>
       <c r="M187" s="23" t="inlineStr">
         <is>
-          <t>Versand möglich</t>
+          <t>nur Abholung</t>
         </is>
       </c>
       <c r="N187" s="16" t="n"/>
@@ -16365,14 +16365,14 @@
       </c>
       <c r="B188" s="10" t="inlineStr">
         <is>
-          <t>BA02-04</t>
+          <t>BA02-05</t>
         </is>
       </c>
       <c r="C188" s="11" t="n"/>
       <c r="D188" s="12" t="inlineStr">
         <is>
-          <t>Kinder-Ohrensessel grau, Kunstleder
-Ohrensessel in Kindergröße, hellgrauer Kunstlederbezug, geschwungene schwarze Holzbeine.</t>
+          <t>Ablagepult Holz auf Metallgestell
+Pult mit geneigter Platte aus dunklem Holz mit schwarzer Auflage, auf einem C-förmigen schwarzen Metallgestell. Untergreifbar, im Haus als Stehpult für die Anwesenheitsliste genutzt.</t>
         </is>
       </c>
       <c r="E188" s="13" t="n"/>
@@ -16395,7 +16395,7 @@
         </is>
       </c>
       <c r="J188" s="14" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="K188" s="15">
         <f>J188*1.19</f>
@@ -16425,14 +16425,14 @@
       </c>
       <c r="B189" s="21" t="inlineStr">
         <is>
-          <t>BA02-05</t>
+          <t>BA02-06</t>
         </is>
       </c>
       <c r="C189" s="22" t="n"/>
       <c r="D189" s="23" t="inlineStr">
         <is>
-          <t>Ablagepult Holz auf Metallgestell
-Pult mit geneigter Platte aus dunklem Holz mit schwarzer Auflage, auf einem C-förmigen schwarzen Metallgestell. Untergreifbar, im Haus als Stehpult für die Anwesenheitsliste genutzt.</t>
+          <t>Truhenbank weiß mit Fellauflage
+Sitzbank in Weiß mit geschwungenen Seitenteilen, Rückenbrett und aufklappbarer Sitzfläche mit Beschlägen. Darunter ein großer Stauraum. Eine weiße Fellauflage liegt auf der Sitzfläche.</t>
         </is>
       </c>
       <c r="E189" s="13" t="n"/>
@@ -16485,14 +16485,14 @@
       </c>
       <c r="B190" s="10" t="inlineStr">
         <is>
-          <t>BA02-06</t>
+          <t>BA02-08</t>
         </is>
       </c>
       <c r="C190" s="11" t="n"/>
       <c r="D190" s="12" t="inlineStr">
         <is>
-          <t>Truhenbank weiß mit Fellauflage
-Sitzbank in Weiß mit geschwungenen Seitenteilen, Rückenbrett und aufklappbarer Sitzfläche mit Beschlägen. Darunter ein großer Stauraum. Eine weiße Fellauflage liegt auf der Sitzfläche.</t>
+          <t>Kinderschrank weiß mit Handabdrücken
+Hoher Schrank in Weiß mit Türen und Schubladen, Griffmulden. Auf den Fronten kleben Aufkleber mit Kinderhandabdrücken in Schwarz und Rot; sie lassen sich abziehen.</t>
         </is>
       </c>
       <c r="E190" s="13" t="n"/>
@@ -16507,7 +16507,7 @@
         </is>
       </c>
       <c r="H190" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I190" s="10" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         </is>
       </c>
       <c r="J190" s="14" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="K190" s="15">
         <f>J190*1.19</f>
@@ -16545,14 +16545,14 @@
       </c>
       <c r="B191" s="21" t="inlineStr">
         <is>
-          <t>BA02-08</t>
+          <t>BA02-09</t>
         </is>
       </c>
       <c r="C191" s="22" t="n"/>
       <c r="D191" s="23" t="inlineStr">
         <is>
-          <t>Kinderschrank weiß mit Handabdrücken
-Hoher Schrank in Weiß mit Türen und Schubladen, Griffmulden. Auf den Fronten kleben Aufkleber mit Kinderhandabdrücken in Schwarz und Rot; sie lassen sich abziehen.</t>
+          <t>Deko-Häuser Keramik
+Drei Häuschen aus Keramik mit ausgestanzten Fenstern, zum Beleuchten mit einem Teelicht: eines craquelé-grau, eines cremeweiß glasiert, eines dunkelgrau mit rundem Fenster.</t>
         </is>
       </c>
       <c r="E191" s="13" t="n"/>
@@ -16563,11 +16563,11 @@
       </c>
       <c r="G191" s="21" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H191" s="21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I191" s="21" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         </is>
       </c>
       <c r="J191" s="24" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="K191" s="25">
         <f>J191*1.19</f>
@@ -16588,7 +16588,7 @@
       </c>
       <c r="M191" s="23" t="inlineStr">
         <is>
-          <t>nur Abholung</t>
+          <t>Versand möglich</t>
         </is>
       </c>
       <c r="N191" s="16" t="n"/>
@@ -16599,321 +16599,261 @@
         <v/>
       </c>
     </row>
-    <row r="192" ht="78" customHeight="1">
-      <c r="A192" s="9" t="n">
-        <v>185</v>
-      </c>
-      <c r="B192" s="10" t="inlineStr">
-        <is>
-          <t>BA02-09</t>
-        </is>
-      </c>
-      <c r="C192" s="11" t="n"/>
-      <c r="D192" s="12" t="inlineStr">
-        <is>
-          <t>Deko-Häuser Keramik
-Drei Häuschen aus Keramik mit ausgestanzten Fenstern, zum Beleuchten mit einem Teelicht: eines craquelé-grau, eines cremeweiß glasiert, eines dunkelgrau mit rundem Fenster.</t>
-        </is>
-      </c>
-      <c r="E192" s="13" t="n"/>
-      <c r="F192" s="12" t="inlineStr">
-        <is>
-          <t>Flur 2</t>
-        </is>
-      </c>
-      <c r="G192" s="10" t="inlineStr">
-        <is>
-          <t>gut</t>
-        </is>
-      </c>
-      <c r="H192" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="I192" s="10" t="inlineStr">
-        <is>
-          <t>Stück</t>
-        </is>
-      </c>
-      <c r="J192" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="K192" s="15">
-        <f>J192*1.19</f>
-        <v/>
-      </c>
-      <c r="L192" s="10" t="inlineStr">
-        <is>
-          <t>VHB</t>
-        </is>
-      </c>
-      <c r="M192" s="12" t="inlineStr">
-        <is>
-          <t>Versand möglich</t>
-        </is>
-      </c>
-      <c r="N192" s="16" t="n"/>
-      <c r="O192" s="17" t="n"/>
-      <c r="P192" s="18" t="n"/>
-      <c r="Q192" s="19">
-        <f>IF(N192&lt;&gt;"ja","",IF(O192="",H192,O192)*J192)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="194" ht="24" customHeight="1">
-      <c r="A194" s="36" t="inlineStr">
+    <row r="193" ht="24" customHeight="1">
+      <c r="A193" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B194" s="1" t="n"/>
-      <c r="C194" s="1" t="n"/>
-      <c r="D194" s="1" t="n"/>
-      <c r="E194" s="1" t="n"/>
-      <c r="F194" s="1" t="n"/>
-      <c r="G194" s="1" t="n"/>
-      <c r="H194" s="1" t="n"/>
-      <c r="I194" s="1" t="n"/>
-      <c r="J194" s="1" t="n"/>
-      <c r="K194" s="1" t="n"/>
-      <c r="L194" s="1" t="n"/>
-      <c r="M194" s="1" t="n"/>
-      <c r="N194" s="1" t="n"/>
-      <c r="O194" s="1" t="n"/>
-      <c r="P194" s="1" t="n"/>
-      <c r="Q194" s="1" t="n"/>
+      <c r="B193" s="1" t="n"/>
+      <c r="C193" s="1" t="n"/>
+      <c r="D193" s="1" t="n"/>
+      <c r="E193" s="1" t="n"/>
+      <c r="F193" s="1" t="n"/>
+      <c r="G193" s="1" t="n"/>
+      <c r="H193" s="1" t="n"/>
+      <c r="I193" s="1" t="n"/>
+      <c r="J193" s="1" t="n"/>
+      <c r="K193" s="1" t="n"/>
+      <c r="L193" s="1" t="n"/>
+      <c r="M193" s="1" t="n"/>
+      <c r="N193" s="1" t="n"/>
+      <c r="O193" s="1" t="n"/>
+      <c r="P193" s="1" t="n"/>
+      <c r="Q193" s="1" t="n"/>
+    </row>
+    <row r="194" ht="22" customHeight="1">
+      <c r="A194" s="37" t="inlineStr">
+        <is>
+          <t>Wert Ihrer Auswahl netto</t>
+        </is>
+      </c>
+      <c r="Q194" s="38">
+        <f>SUM(Q8:Q191)</f>
+        <v/>
+      </c>
     </row>
     <row r="195" ht="22" customHeight="1">
       <c r="A195" s="37" t="inlineStr">
         <is>
-          <t>Wert Ihrer Auswahl netto</t>
+          <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
       <c r="Q195" s="38">
-        <f>SUM(Q8:Q192)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196" ht="22" customHeight="1">
-      <c r="A196" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q196" s="38">
-        <f>Q195*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="197" ht="26" customHeight="1">
-      <c r="A197" s="39" t="inlineStr">
+        <f>Q194*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196" ht="26" customHeight="1">
+      <c r="A196" s="39" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl brutto</t>
         </is>
       </c>
-      <c r="Q197" s="40">
-        <f>Q195+Q196</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198" ht="22" customHeight="1">
-      <c r="A198" s="37" t="inlineStr">
+      <c r="Q196" s="40">
+        <f>Q194+Q195</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197" ht="22" customHeight="1">
+      <c r="A197" s="37" t="inlineStr">
         <is>
           <t>gewählte Positionen</t>
         </is>
       </c>
-      <c r="Q198" s="41">
-        <f>COUNTIF(N8:N192,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="42" t="inlineStr">
+      <c r="Q197" s="41">
+        <f>COUNTIF(N8:N191,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="42" t="inlineStr">
         <is>
           <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
         </is>
       </c>
     </row>
-    <row r="201" ht="24" customHeight="1">
-      <c r="A201" s="43" t="inlineStr">
+    <row r="200" ht="24" customHeight="1">
+      <c r="A200" s="43" t="inlineStr">
         <is>
           <t>B · GESAMTBESTAND</t>
         </is>
       </c>
-      <c r="B201" s="44" t="n"/>
-      <c r="C201" s="44" t="n"/>
-      <c r="D201" s="44" t="n"/>
-      <c r="E201" s="44" t="n"/>
-      <c r="F201" s="44" t="n"/>
-      <c r="G201" s="44" t="n"/>
-      <c r="H201" s="44" t="n"/>
-      <c r="I201" s="44" t="n"/>
-      <c r="J201" s="44" t="n"/>
-      <c r="K201" s="44" t="n"/>
-      <c r="L201" s="44" t="n"/>
-      <c r="M201" s="44" t="n"/>
-      <c r="N201" s="44" t="n"/>
-      <c r="O201" s="44" t="n"/>
-      <c r="P201" s="44" t="n"/>
-      <c r="Q201" s="44" t="n"/>
+      <c r="B200" s="44" t="n"/>
+      <c r="C200" s="44" t="n"/>
+      <c r="D200" s="44" t="n"/>
+      <c r="E200" s="44" t="n"/>
+      <c r="F200" s="44" t="n"/>
+      <c r="G200" s="44" t="n"/>
+      <c r="H200" s="44" t="n"/>
+      <c r="I200" s="44" t="n"/>
+      <c r="J200" s="44" t="n"/>
+      <c r="K200" s="44" t="n"/>
+      <c r="L200" s="44" t="n"/>
+      <c r="M200" s="44" t="n"/>
+      <c r="N200" s="44" t="n"/>
+      <c r="O200" s="44" t="n"/>
+      <c r="P200" s="44" t="n"/>
+      <c r="Q200" s="44" t="n"/>
+    </row>
+    <row r="201" ht="22" customHeight="1">
+      <c r="A201" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q201" s="38">
+        <f>SUMPRODUCT(H8:H191,J8:J191)</f>
+        <v/>
+      </c>
     </row>
     <row r="202" ht="22" customHeight="1">
       <c r="A202" s="37" t="inlineStr">
         <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
+          <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
       <c r="Q202" s="38">
-        <f>SUMPRODUCT(H8:H192,J8:J192)</f>
+        <f>Q201*0.19</f>
         <v/>
       </c>
     </row>
     <row r="203" ht="22" customHeight="1">
-      <c r="A203" s="37" t="inlineStr">
+      <c r="A203" s="45" t="inlineStr">
+        <is>
+          <t>Gesamtwert brutto</t>
+        </is>
+      </c>
+      <c r="Q203" s="46">
+        <f>Q201+Q202</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205" ht="24" customHeight="1">
+      <c r="A205" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B205" s="48" t="n"/>
+      <c r="C205" s="48" t="n"/>
+      <c r="D205" s="48" t="n"/>
+      <c r="E205" s="48" t="n"/>
+      <c r="F205" s="48" t="n"/>
+      <c r="G205" s="48" t="n"/>
+      <c r="H205" s="48" t="n"/>
+      <c r="I205" s="48" t="n"/>
+      <c r="J205" s="48" t="n"/>
+      <c r="K205" s="48" t="n"/>
+      <c r="L205" s="48" t="n"/>
+      <c r="M205" s="48" t="n"/>
+      <c r="N205" s="48" t="n"/>
+      <c r="O205" s="48" t="n"/>
+      <c r="P205" s="48" t="n"/>
+      <c r="Q205" s="48" t="n"/>
+    </row>
+    <row r="206" ht="22" customHeight="1">
+      <c r="A206" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
+        </is>
+      </c>
+      <c r="Q206" s="38">
+        <f>-Q201*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207" ht="22" customHeight="1">
+      <c r="A207" s="45" t="inlineStr">
+        <is>
+          <t>Paketpreis netto</t>
+        </is>
+      </c>
+      <c r="Q207" s="46">
+        <f>Q201+Q206</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208" ht="22" customHeight="1">
+      <c r="A208" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q203" s="38">
-        <f>Q202*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="204" ht="22" customHeight="1">
-      <c r="A204" s="45" t="inlineStr">
-        <is>
-          <t>Gesamtwert brutto</t>
-        </is>
-      </c>
-      <c r="Q204" s="46">
-        <f>Q202+Q203</f>
-        <v/>
-      </c>
-    </row>
-    <row r="206" ht="24" customHeight="1">
-      <c r="A206" s="47" t="inlineStr">
-        <is>
-          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B206" s="48" t="n"/>
-      <c r="C206" s="48" t="n"/>
-      <c r="D206" s="48" t="n"/>
-      <c r="E206" s="48" t="n"/>
-      <c r="F206" s="48" t="n"/>
-      <c r="G206" s="48" t="n"/>
-      <c r="H206" s="48" t="n"/>
-      <c r="I206" s="48" t="n"/>
-      <c r="J206" s="48" t="n"/>
-      <c r="K206" s="48" t="n"/>
-      <c r="L206" s="48" t="n"/>
-      <c r="M206" s="48" t="n"/>
-      <c r="N206" s="48" t="n"/>
-      <c r="O206" s="48" t="n"/>
-      <c r="P206" s="48" t="n"/>
-      <c r="Q206" s="48" t="n"/>
-    </row>
-    <row r="207" ht="22" customHeight="1">
-      <c r="A207" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
-        </is>
-      </c>
-      <c r="Q207" s="38">
-        <f>-Q202*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="208" ht="22" customHeight="1">
-      <c r="A208" s="45" t="inlineStr">
-        <is>
-          <t>Paketpreis netto</t>
-        </is>
-      </c>
-      <c r="Q208" s="46">
-        <f>Q202+Q207</f>
-        <v/>
-      </c>
-    </row>
-    <row r="209" ht="22" customHeight="1">
-      <c r="A209" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q209" s="38">
-        <f>Q208*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="210" ht="26" customHeight="1">
-      <c r="A210" s="39" t="inlineStr">
+      <c r="Q208" s="38">
+        <f>Q207*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209" ht="26" customHeight="1">
+      <c r="A209" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q210" s="40">
-        <f>Q208+Q209</f>
-        <v/>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="42" t="inlineStr">
+      <c r="Q209" s="40">
+        <f>Q207+Q208</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="49" t="inlineStr">
+    <row r="212">
+      <c r="A212" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
+    <row r="213"/>
     <row r="214"/>
     <row r="215"/>
-    <row r="216"/>
   </sheetData>
-  <autoFilter ref="A7:Q192"/>
+  <autoFilter ref="A7:Q191"/>
   <mergeCells count="26">
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A211:Q211"/>
+    <mergeCell ref="A194:P194"/>
     <mergeCell ref="A203:P203"/>
-    <mergeCell ref="A201:Q201"/>
+    <mergeCell ref="A206:P206"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A209:P209"/>
     <mergeCell ref="L4:Q4"/>
-    <mergeCell ref="A213:Q216"/>
     <mergeCell ref="A202:P202"/>
     <mergeCell ref="C3:I3"/>
+    <mergeCell ref="A205:Q205"/>
+    <mergeCell ref="A201:P201"/>
+    <mergeCell ref="A193:Q193"/>
+    <mergeCell ref="A198:Q198"/>
     <mergeCell ref="A207:P207"/>
     <mergeCell ref="A197:P197"/>
     <mergeCell ref="C4:I4"/>
+    <mergeCell ref="A210:Q210"/>
     <mergeCell ref="A196:P196"/>
-    <mergeCell ref="A194:Q194"/>
     <mergeCell ref="L2:Q2"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="A208:P208"/>
-    <mergeCell ref="A206:Q206"/>
-    <mergeCell ref="A198:P198"/>
-    <mergeCell ref="A199:Q199"/>
+    <mergeCell ref="A200:Q200"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A210:P210"/>
+    <mergeCell ref="A212:Q215"/>
     <mergeCell ref="A195:P195"/>
-    <mergeCell ref="A204:P204"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q192">
+  <conditionalFormatting sqref="A8:Q191">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N192" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N191" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O192" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O191" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$192</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5043,6 +5043,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>191</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="186" name="Image 186" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId186"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -5335,7 +5360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q215"/>
+  <dimension ref="A1:Q216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6168,7 +6193,7 @@
         </is>
       </c>
       <c r="H18" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I18" s="10" t="inlineStr">
         <is>
@@ -16599,261 +16624,321 @@
         <v/>
       </c>
     </row>
-    <row r="193" ht="24" customHeight="1">
-      <c r="A193" s="36" t="inlineStr">
+    <row r="192" ht="78" customHeight="1">
+      <c r="A192" s="9" t="n">
+        <v>185</v>
+      </c>
+      <c r="B192" s="10" t="inlineStr">
+        <is>
+          <t>BA09-06</t>
+        </is>
+      </c>
+      <c r="C192" s="11" t="n"/>
+      <c r="D192" s="12" t="inlineStr">
+        <is>
+          <t>Sitzhocker rund, drehbar auf Rollen
+Runder Sitzhocker mit schwarzem Netzstoffbezug und umlaufendem Reißverschluss, auf einem silberfarbenen Fünffußkreuz mit Rollen, höhenverstellbar.</t>
+        </is>
+      </c>
+      <c r="E192" s="13" t="n"/>
+      <c r="F192" s="12" t="inlineStr">
+        <is>
+          <t>Personal</t>
+        </is>
+      </c>
+      <c r="G192" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H192" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I192" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J192" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="K192" s="15">
+        <f>J192*1.19</f>
+        <v/>
+      </c>
+      <c r="L192" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M192" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N192" s="16" t="n"/>
+      <c r="O192" s="17" t="n"/>
+      <c r="P192" s="18" t="n"/>
+      <c r="Q192" s="19">
+        <f>IF(N192&lt;&gt;"ja","",IF(O192="",H192,O192)*J192)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194" ht="24" customHeight="1">
+      <c r="A194" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B193" s="1" t="n"/>
-      <c r="C193" s="1" t="n"/>
-      <c r="D193" s="1" t="n"/>
-      <c r="E193" s="1" t="n"/>
-      <c r="F193" s="1" t="n"/>
-      <c r="G193" s="1" t="n"/>
-      <c r="H193" s="1" t="n"/>
-      <c r="I193" s="1" t="n"/>
-      <c r="J193" s="1" t="n"/>
-      <c r="K193" s="1" t="n"/>
-      <c r="L193" s="1" t="n"/>
-      <c r="M193" s="1" t="n"/>
-      <c r="N193" s="1" t="n"/>
-      <c r="O193" s="1" t="n"/>
-      <c r="P193" s="1" t="n"/>
-      <c r="Q193" s="1" t="n"/>
-    </row>
-    <row r="194" ht="22" customHeight="1">
-      <c r="A194" s="37" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl netto</t>
-        </is>
-      </c>
-      <c r="Q194" s="38">
-        <f>SUM(Q8:Q191)</f>
-        <v/>
-      </c>
+      <c r="B194" s="1" t="n"/>
+      <c r="C194" s="1" t="n"/>
+      <c r="D194" s="1" t="n"/>
+      <c r="E194" s="1" t="n"/>
+      <c r="F194" s="1" t="n"/>
+      <c r="G194" s="1" t="n"/>
+      <c r="H194" s="1" t="n"/>
+      <c r="I194" s="1" t="n"/>
+      <c r="J194" s="1" t="n"/>
+      <c r="K194" s="1" t="n"/>
+      <c r="L194" s="1" t="n"/>
+      <c r="M194" s="1" t="n"/>
+      <c r="N194" s="1" t="n"/>
+      <c r="O194" s="1" t="n"/>
+      <c r="P194" s="1" t="n"/>
+      <c r="Q194" s="1" t="n"/>
     </row>
     <row r="195" ht="22" customHeight="1">
       <c r="A195" s="37" t="inlineStr">
         <is>
+          <t>Wert Ihrer Auswahl netto</t>
+        </is>
+      </c>
+      <c r="Q195" s="38">
+        <f>SUM(Q8:Q192)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196" ht="22" customHeight="1">
+      <c r="A196" s="37" t="inlineStr">
+        <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q195" s="38">
-        <f>Q194*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196" ht="26" customHeight="1">
-      <c r="A196" s="39" t="inlineStr">
+      <c r="Q196" s="38">
+        <f>Q195*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197" ht="26" customHeight="1">
+      <c r="A197" s="39" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl brutto</t>
         </is>
       </c>
-      <c r="Q196" s="40">
-        <f>Q194+Q195</f>
-        <v/>
-      </c>
-    </row>
-    <row r="197" ht="22" customHeight="1">
-      <c r="A197" s="37" t="inlineStr">
+      <c r="Q197" s="40">
+        <f>Q195+Q196</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198" ht="22" customHeight="1">
+      <c r="A198" s="37" t="inlineStr">
         <is>
           <t>gewählte Positionen</t>
         </is>
       </c>
-      <c r="Q197" s="41">
-        <f>COUNTIF(N8:N191,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="42" t="inlineStr">
+      <c r="Q198" s="41">
+        <f>COUNTIF(N8:N192,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="42" t="inlineStr">
         <is>
           <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
         </is>
       </c>
     </row>
-    <row r="200" ht="24" customHeight="1">
-      <c r="A200" s="43" t="inlineStr">
+    <row r="201" ht="24" customHeight="1">
+      <c r="A201" s="43" t="inlineStr">
         <is>
           <t>B · GESAMTBESTAND</t>
         </is>
       </c>
-      <c r="B200" s="44" t="n"/>
-      <c r="C200" s="44" t="n"/>
-      <c r="D200" s="44" t="n"/>
-      <c r="E200" s="44" t="n"/>
-      <c r="F200" s="44" t="n"/>
-      <c r="G200" s="44" t="n"/>
-      <c r="H200" s="44" t="n"/>
-      <c r="I200" s="44" t="n"/>
-      <c r="J200" s="44" t="n"/>
-      <c r="K200" s="44" t="n"/>
-      <c r="L200" s="44" t="n"/>
-      <c r="M200" s="44" t="n"/>
-      <c r="N200" s="44" t="n"/>
-      <c r="O200" s="44" t="n"/>
-      <c r="P200" s="44" t="n"/>
-      <c r="Q200" s="44" t="n"/>
-    </row>
-    <row r="201" ht="22" customHeight="1">
-      <c r="A201" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
-        </is>
-      </c>
-      <c r="Q201" s="38">
-        <f>SUMPRODUCT(H8:H191,J8:J191)</f>
-        <v/>
-      </c>
+      <c r="B201" s="44" t="n"/>
+      <c r="C201" s="44" t="n"/>
+      <c r="D201" s="44" t="n"/>
+      <c r="E201" s="44" t="n"/>
+      <c r="F201" s="44" t="n"/>
+      <c r="G201" s="44" t="n"/>
+      <c r="H201" s="44" t="n"/>
+      <c r="I201" s="44" t="n"/>
+      <c r="J201" s="44" t="n"/>
+      <c r="K201" s="44" t="n"/>
+      <c r="L201" s="44" t="n"/>
+      <c r="M201" s="44" t="n"/>
+      <c r="N201" s="44" t="n"/>
+      <c r="O201" s="44" t="n"/>
+      <c r="P201" s="44" t="n"/>
+      <c r="Q201" s="44" t="n"/>
     </row>
     <row r="202" ht="22" customHeight="1">
       <c r="A202" s="37" t="inlineStr">
         <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q202" s="38">
+        <f>SUMPRODUCT(H8:H192,J8:J192)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203" ht="22" customHeight="1">
+      <c r="A203" s="37" t="inlineStr">
+        <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q202" s="38">
-        <f>Q201*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="203" ht="22" customHeight="1">
-      <c r="A203" s="45" t="inlineStr">
+      <c r="Q203" s="38">
+        <f>Q202*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204" ht="22" customHeight="1">
+      <c r="A204" s="45" t="inlineStr">
         <is>
           <t>Gesamtwert brutto</t>
         </is>
       </c>
-      <c r="Q203" s="46">
-        <f>Q201+Q202</f>
-        <v/>
-      </c>
-    </row>
-    <row r="205" ht="24" customHeight="1">
-      <c r="A205" s="47" t="inlineStr">
+      <c r="Q204" s="46">
+        <f>Q202+Q203</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206" ht="24" customHeight="1">
+      <c r="A206" s="47" t="inlineStr">
         <is>
           <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
         </is>
       </c>
-      <c r="B205" s="48" t="n"/>
-      <c r="C205" s="48" t="n"/>
-      <c r="D205" s="48" t="n"/>
-      <c r="E205" s="48" t="n"/>
-      <c r="F205" s="48" t="n"/>
-      <c r="G205" s="48" t="n"/>
-      <c r="H205" s="48" t="n"/>
-      <c r="I205" s="48" t="n"/>
-      <c r="J205" s="48" t="n"/>
-      <c r="K205" s="48" t="n"/>
-      <c r="L205" s="48" t="n"/>
-      <c r="M205" s="48" t="n"/>
-      <c r="N205" s="48" t="n"/>
-      <c r="O205" s="48" t="n"/>
-      <c r="P205" s="48" t="n"/>
-      <c r="Q205" s="48" t="n"/>
-    </row>
-    <row r="206" ht="22" customHeight="1">
-      <c r="A206" s="37" t="inlineStr">
+      <c r="B206" s="48" t="n"/>
+      <c r="C206" s="48" t="n"/>
+      <c r="D206" s="48" t="n"/>
+      <c r="E206" s="48" t="n"/>
+      <c r="F206" s="48" t="n"/>
+      <c r="G206" s="48" t="n"/>
+      <c r="H206" s="48" t="n"/>
+      <c r="I206" s="48" t="n"/>
+      <c r="J206" s="48" t="n"/>
+      <c r="K206" s="48" t="n"/>
+      <c r="L206" s="48" t="n"/>
+      <c r="M206" s="48" t="n"/>
+      <c r="N206" s="48" t="n"/>
+      <c r="O206" s="48" t="n"/>
+      <c r="P206" s="48" t="n"/>
+      <c r="Q206" s="48" t="n"/>
+    </row>
+    <row r="207" ht="22" customHeight="1">
+      <c r="A207" s="37" t="inlineStr">
         <is>
           <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
         </is>
       </c>
-      <c r="Q206" s="38">
-        <f>-Q201*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="207" ht="22" customHeight="1">
-      <c r="A207" s="45" t="inlineStr">
+      <c r="Q207" s="38">
+        <f>-Q202*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208" ht="22" customHeight="1">
+      <c r="A208" s="45" t="inlineStr">
         <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="Q207" s="46">
-        <f>Q201+Q206</f>
-        <v/>
-      </c>
-    </row>
-    <row r="208" ht="22" customHeight="1">
-      <c r="A208" s="37" t="inlineStr">
+      <c r="Q208" s="46">
+        <f>Q202+Q207</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209" ht="22" customHeight="1">
+      <c r="A209" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q208" s="38">
-        <f>Q207*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="209" ht="26" customHeight="1">
-      <c r="A209" s="39" t="inlineStr">
+      <c r="Q209" s="38">
+        <f>Q208*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210" ht="26" customHeight="1">
+      <c r="A210" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q209" s="40">
-        <f>Q207+Q208</f>
-        <v/>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" s="42" t="inlineStr">
+      <c r="Q210" s="40">
+        <f>Q208+Q209</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="49" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="213"/>
     <row r="214"/>
     <row r="215"/>
+    <row r="216"/>
   </sheetData>
-  <autoFilter ref="A7:Q191"/>
+  <autoFilter ref="A7:Q192"/>
   <mergeCells count="26">
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A194:P194"/>
+    <mergeCell ref="A211:Q211"/>
     <mergeCell ref="A203:P203"/>
-    <mergeCell ref="A206:P206"/>
+    <mergeCell ref="A201:Q201"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A209:P209"/>
     <mergeCell ref="L4:Q4"/>
+    <mergeCell ref="A213:Q216"/>
     <mergeCell ref="A202:P202"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A205:Q205"/>
-    <mergeCell ref="A201:P201"/>
-    <mergeCell ref="A193:Q193"/>
-    <mergeCell ref="A198:Q198"/>
     <mergeCell ref="A207:P207"/>
     <mergeCell ref="A197:P197"/>
     <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A210:Q210"/>
     <mergeCell ref="A196:P196"/>
+    <mergeCell ref="A194:Q194"/>
     <mergeCell ref="L2:Q2"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="A208:P208"/>
-    <mergeCell ref="A200:Q200"/>
+    <mergeCell ref="A206:Q206"/>
+    <mergeCell ref="A198:P198"/>
+    <mergeCell ref="A199:Q199"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A212:Q215"/>
+    <mergeCell ref="A210:P210"/>
     <mergeCell ref="A195:P195"/>
+    <mergeCell ref="A204:P204"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q191">
+  <conditionalFormatting sqref="A8:Q192">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N191" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N192" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O191" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O192" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5068,6 +5068,231 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>192</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="187" name="Image 187" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId187"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>193</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="188" name="Image 188" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId188"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>194</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="189" name="Image 189" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId189"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>195</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="190" name="Image 190" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId190"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>196</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="191" name="Image 191" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId191"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>197</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="192" name="Image 192" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId192"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>198</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="193" name="Image 193" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId193"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>199</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="194" name="Image 194" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId194"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>200</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="195" name="Image 195" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId195"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -5360,7 +5585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q216"/>
+  <dimension ref="A1:Q225"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -16684,261 +16909,801 @@
         <v/>
       </c>
     </row>
-    <row r="194" ht="24" customHeight="1">
-      <c r="A194" s="36" t="inlineStr">
+    <row r="193" ht="78" customHeight="1">
+      <c r="A193" s="20" t="n">
+        <v>186</v>
+      </c>
+      <c r="B193" s="21" t="inlineStr">
+        <is>
+          <t>NE02-01</t>
+        </is>
+      </c>
+      <c r="C193" s="22" t="n"/>
+      <c r="D193" s="23" t="inlineStr">
+        <is>
+          <t>Hirsch Metall, stehend
+Figur eines Hirschs aus Metall mit dunkler, teils silbrig durchscheinender Oberfläche, auf länglichem Sockel mit Geweihstück.</t>
+        </is>
+      </c>
+      <c r="E193" s="13" t="n"/>
+      <c r="F193" s="23" t="inlineStr">
+        <is>
+          <t>Küche</t>
+        </is>
+      </c>
+      <c r="G193" s="21" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H193" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I193" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J193" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="K193" s="25">
+        <f>J193*1.19</f>
+        <v/>
+      </c>
+      <c r="L193" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M193" s="23" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N193" s="16" t="n"/>
+      <c r="O193" s="17" t="n"/>
+      <c r="P193" s="18" t="n"/>
+      <c r="Q193" s="26">
+        <f>IF(N193&lt;&gt;"ja","",IF(O193="",H193,O193)*J193)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194" ht="78" customHeight="1">
+      <c r="A194" s="9" t="n">
+        <v>187</v>
+      </c>
+      <c r="B194" s="10" t="inlineStr">
+        <is>
+          <t>NE02-02</t>
+        </is>
+      </c>
+      <c r="C194" s="11" t="n"/>
+      <c r="D194" s="12" t="inlineStr">
+        <is>
+          <t>Barhocker dunkelgrau, Erwachsenenhöhe
+Barhocker mit dunkelgrauer Kunststoffschale auf schwarzem Kufengestell aus Rundstahl, mit Fußstütze.</t>
+        </is>
+      </c>
+      <c r="E194" s="13" t="n"/>
+      <c r="F194" s="12" t="inlineStr">
+        <is>
+          <t>Küche</t>
+        </is>
+      </c>
+      <c r="G194" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H194" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I194" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J194" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="K194" s="15">
+        <f>J194*1.19</f>
+        <v/>
+      </c>
+      <c r="L194" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M194" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N194" s="16" t="n"/>
+      <c r="O194" s="17" t="n"/>
+      <c r="P194" s="18" t="n"/>
+      <c r="Q194" s="19">
+        <f>IF(N194&lt;&gt;"ja","",IF(O194="",H194,O194)*J194)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195" ht="78" customHeight="1">
+      <c r="A195" s="20" t="n">
+        <v>188</v>
+      </c>
+      <c r="B195" s="21" t="inlineStr">
+        <is>
+          <t>NE02-03</t>
+        </is>
+      </c>
+      <c r="C195" s="22" t="n"/>
+      <c r="D195" s="23" t="inlineStr">
+        <is>
+          <t>Wäschekorb schwarz mit Deckel
+Wäschekorb aus Kunststoff in Flechtoptik, schwarz, mit aufklappbarem Deckel.</t>
+        </is>
+      </c>
+      <c r="E195" s="13" t="n"/>
+      <c r="F195" s="23" t="inlineStr">
+        <is>
+          <t>Küche</t>
+        </is>
+      </c>
+      <c r="G195" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H195" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I195" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J195" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="K195" s="25">
+        <f>J195*1.19</f>
+        <v/>
+      </c>
+      <c r="L195" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M195" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N195" s="16" t="n"/>
+      <c r="O195" s="17" t="n"/>
+      <c r="P195" s="18" t="n"/>
+      <c r="Q195" s="26">
+        <f>IF(N195&lt;&gt;"ja","",IF(O195="",H195,O195)*J195)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196" ht="78" customHeight="1">
+      <c r="A196" s="9" t="n">
+        <v>189</v>
+      </c>
+      <c r="B196" s="10" t="inlineStr">
+        <is>
+          <t>NE02-04</t>
+        </is>
+      </c>
+      <c r="C196" s="11" t="n"/>
+      <c r="D196" s="12" t="inlineStr">
+        <is>
+          <t>Mülleimer Kunststoff schwarz, groß
+Runder Abfallbehälter aus schwarzem Kunststoff mit aufgesetztem Schwingdeckel.</t>
+        </is>
+      </c>
+      <c r="E196" s="13" t="n"/>
+      <c r="F196" s="12" t="inlineStr">
+        <is>
+          <t>Küche</t>
+        </is>
+      </c>
+      <c r="G196" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H196" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I196" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J196" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="K196" s="15">
+        <f>J196*1.19</f>
+        <v/>
+      </c>
+      <c r="L196" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M196" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N196" s="16" t="n"/>
+      <c r="O196" s="17" t="n"/>
+      <c r="P196" s="18" t="n"/>
+      <c r="Q196" s="19">
+        <f>IF(N196&lt;&gt;"ja","",IF(O196="",H196,O196)*J196)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197" ht="78" customHeight="1">
+      <c r="A197" s="20" t="n">
+        <v>190</v>
+      </c>
+      <c r="B197" s="21" t="inlineStr">
+        <is>
+          <t>NE02-05</t>
+        </is>
+      </c>
+      <c r="C197" s="22" t="n"/>
+      <c r="D197" s="23" t="inlineStr">
+        <is>
+          <t>IKEA Trinkbecher Kinder, bunt
+Trinkbecher aus Kunststoff für Kinder, IKEA, in Rot, Blau, Pink, Gelb und Weiß. Stapelbar, spülmaschinenfest.</t>
+        </is>
+      </c>
+      <c r="E197" s="13" t="n"/>
+      <c r="F197" s="23" t="inlineStr">
+        <is>
+          <t>Küche</t>
+        </is>
+      </c>
+      <c r="G197" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H197" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="I197" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J197" s="24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K197" s="25">
+        <f>J197*1.19</f>
+        <v/>
+      </c>
+      <c r="L197" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M197" s="23" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N197" s="16" t="n"/>
+      <c r="O197" s="17" t="n"/>
+      <c r="P197" s="18" t="n"/>
+      <c r="Q197" s="26">
+        <f>IF(N197&lt;&gt;"ja","",IF(O197="",H197,O197)*J197)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198" ht="78" customHeight="1">
+      <c r="A198" s="9" t="n">
+        <v>191</v>
+      </c>
+      <c r="B198" s="10" t="inlineStr">
+        <is>
+          <t>NE02-06</t>
+        </is>
+      </c>
+      <c r="C198" s="11" t="n"/>
+      <c r="D198" s="12" t="inlineStr">
+        <is>
+          <t>Trinkbecher Melamin, grün- und grautöne
+Trinkbecher mit facettiertem Fuß in Weiß, Salbeigrün, Graugrün und Mintgrün. Acht der Becher tragen ein Motiv.</t>
+        </is>
+      </c>
+      <c r="E198" s="13" t="n"/>
+      <c r="F198" s="12" t="inlineStr">
+        <is>
+          <t>Küche</t>
+        </is>
+      </c>
+      <c r="G198" s="10" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H198" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="I198" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J198" s="14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K198" s="15">
+        <f>J198*1.19</f>
+        <v/>
+      </c>
+      <c r="L198" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M198" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N198" s="16" t="n"/>
+      <c r="O198" s="17" t="n"/>
+      <c r="P198" s="18" t="n"/>
+      <c r="Q198" s="19">
+        <f>IF(N198&lt;&gt;"ja","",IF(O198="",H198,O198)*J198)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199" ht="78" customHeight="1">
+      <c r="A199" s="20" t="n">
+        <v>192</v>
+      </c>
+      <c r="B199" s="21" t="inlineStr">
+        <is>
+          <t>NE02-07</t>
+        </is>
+      </c>
+      <c r="C199" s="22" t="n"/>
+      <c r="D199" s="23" t="inlineStr">
+        <is>
+          <t>Teller Kunststoff, bunt
+Flache Teller aus Kunststoff in kräftigen Farben: elf kleine bunte, drei große sowie weitere mit Tiermotiv.</t>
+        </is>
+      </c>
+      <c r="E199" s="13" t="n"/>
+      <c r="F199" s="23" t="inlineStr">
+        <is>
+          <t>Küche</t>
+        </is>
+      </c>
+      <c r="G199" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H199" s="21" t="n">
+        <v>22</v>
+      </c>
+      <c r="I199" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J199" s="24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K199" s="25">
+        <f>J199*1.19</f>
+        <v/>
+      </c>
+      <c r="L199" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M199" s="23" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N199" s="16" t="n"/>
+      <c r="O199" s="17" t="n"/>
+      <c r="P199" s="18" t="n"/>
+      <c r="Q199" s="26">
+        <f>IF(N199&lt;&gt;"ja","",IF(O199="",H199,O199)*J199)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200" ht="78" customHeight="1">
+      <c r="A200" s="9" t="n">
+        <v>193</v>
+      </c>
+      <c r="B200" s="10" t="inlineStr">
+        <is>
+          <t>NE02-08</t>
+        </is>
+      </c>
+      <c r="C200" s="11" t="n"/>
+      <c r="D200" s="12" t="inlineStr">
+        <is>
+          <t>Schriftzug „Sterneküche", schwarz
+Großer Wandschriftzug „Sterneküche" in Schreibschrift, schwarz, aus Holz gefräst.</t>
+        </is>
+      </c>
+      <c r="E200" s="13" t="n"/>
+      <c r="F200" s="12" t="inlineStr">
+        <is>
+          <t>Küche</t>
+        </is>
+      </c>
+      <c r="G200" s="10" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H200" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I200" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J200" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K200" s="15">
+        <f>J200*1.19</f>
+        <v/>
+      </c>
+      <c r="L200" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M200" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N200" s="16" t="n"/>
+      <c r="O200" s="17" t="n"/>
+      <c r="P200" s="18" t="n"/>
+      <c r="Q200" s="19">
+        <f>IF(N200&lt;&gt;"ja","",IF(O200="",H200,O200)*J200)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201" ht="78" customHeight="1">
+      <c r="A201" s="20" t="n">
+        <v>194</v>
+      </c>
+      <c r="B201" s="21" t="inlineStr">
+        <is>
+          <t>NE02-09</t>
+        </is>
+      </c>
+      <c r="C201" s="22" t="n"/>
+      <c r="D201" s="23" t="inlineStr">
+        <is>
+          <t>Tablett weiß mit Streifenmuster
+Serviertablett aus Kunststoff, weiß mit Griffausschnitten, Boden mit Streifenmuster – eines in Blautönen, eines in Rottönen.</t>
+        </is>
+      </c>
+      <c r="E201" s="13" t="n"/>
+      <c r="F201" s="23" t="inlineStr">
+        <is>
+          <t>Küche</t>
+        </is>
+      </c>
+      <c r="G201" s="21" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H201" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I201" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J201" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="K201" s="25">
+        <f>J201*1.19</f>
+        <v/>
+      </c>
+      <c r="L201" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M201" s="23" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N201" s="16" t="n"/>
+      <c r="O201" s="17" t="n"/>
+      <c r="P201" s="18" t="n"/>
+      <c r="Q201" s="26">
+        <f>IF(N201&lt;&gt;"ja","",IF(O201="",H201,O201)*J201)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203" ht="24" customHeight="1">
+      <c r="A203" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B194" s="1" t="n"/>
-      <c r="C194" s="1" t="n"/>
-      <c r="D194" s="1" t="n"/>
-      <c r="E194" s="1" t="n"/>
-      <c r="F194" s="1" t="n"/>
-      <c r="G194" s="1" t="n"/>
-      <c r="H194" s="1" t="n"/>
-      <c r="I194" s="1" t="n"/>
-      <c r="J194" s="1" t="n"/>
-      <c r="K194" s="1" t="n"/>
-      <c r="L194" s="1" t="n"/>
-      <c r="M194" s="1" t="n"/>
-      <c r="N194" s="1" t="n"/>
-      <c r="O194" s="1" t="n"/>
-      <c r="P194" s="1" t="n"/>
-      <c r="Q194" s="1" t="n"/>
-    </row>
-    <row r="195" ht="22" customHeight="1">
-      <c r="A195" s="37" t="inlineStr">
+      <c r="B203" s="1" t="n"/>
+      <c r="C203" s="1" t="n"/>
+      <c r="D203" s="1" t="n"/>
+      <c r="E203" s="1" t="n"/>
+      <c r="F203" s="1" t="n"/>
+      <c r="G203" s="1" t="n"/>
+      <c r="H203" s="1" t="n"/>
+      <c r="I203" s="1" t="n"/>
+      <c r="J203" s="1" t="n"/>
+      <c r="K203" s="1" t="n"/>
+      <c r="L203" s="1" t="n"/>
+      <c r="M203" s="1" t="n"/>
+      <c r="N203" s="1" t="n"/>
+      <c r="O203" s="1" t="n"/>
+      <c r="P203" s="1" t="n"/>
+      <c r="Q203" s="1" t="n"/>
+    </row>
+    <row r="204" ht="22" customHeight="1">
+      <c r="A204" s="37" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl netto</t>
         </is>
       </c>
-      <c r="Q195" s="38">
-        <f>SUM(Q8:Q192)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196" ht="22" customHeight="1">
-      <c r="A196" s="37" t="inlineStr">
+      <c r="Q204" s="38">
+        <f>SUM(Q8:Q201)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205" ht="22" customHeight="1">
+      <c r="A205" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q196" s="38">
-        <f>Q195*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="197" ht="26" customHeight="1">
-      <c r="A197" s="39" t="inlineStr">
+      <c r="Q205" s="38">
+        <f>Q204*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206" ht="26" customHeight="1">
+      <c r="A206" s="39" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl brutto</t>
         </is>
       </c>
-      <c r="Q197" s="40">
-        <f>Q195+Q196</f>
-        <v/>
-      </c>
-    </row>
-    <row r="198" ht="22" customHeight="1">
-      <c r="A198" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q198" s="41">
-        <f>COUNTIF(N8:N192,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="201" ht="24" customHeight="1">
-      <c r="A201" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B201" s="44" t="n"/>
-      <c r="C201" s="44" t="n"/>
-      <c r="D201" s="44" t="n"/>
-      <c r="E201" s="44" t="n"/>
-      <c r="F201" s="44" t="n"/>
-      <c r="G201" s="44" t="n"/>
-      <c r="H201" s="44" t="n"/>
-      <c r="I201" s="44" t="n"/>
-      <c r="J201" s="44" t="n"/>
-      <c r="K201" s="44" t="n"/>
-      <c r="L201" s="44" t="n"/>
-      <c r="M201" s="44" t="n"/>
-      <c r="N201" s="44" t="n"/>
-      <c r="O201" s="44" t="n"/>
-      <c r="P201" s="44" t="n"/>
-      <c r="Q201" s="44" t="n"/>
-    </row>
-    <row r="202" ht="22" customHeight="1">
-      <c r="A202" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
-        </is>
-      </c>
-      <c r="Q202" s="38">
-        <f>SUMPRODUCT(H8:H192,J8:J192)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="203" ht="22" customHeight="1">
-      <c r="A203" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q203" s="38">
-        <f>Q202*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="204" ht="22" customHeight="1">
-      <c r="A204" s="45" t="inlineStr">
-        <is>
-          <t>Gesamtwert brutto</t>
-        </is>
-      </c>
-      <c r="Q204" s="46">
-        <f>Q202+Q203</f>
-        <v/>
-      </c>
-    </row>
-    <row r="206" ht="24" customHeight="1">
-      <c r="A206" s="47" t="inlineStr">
-        <is>
-          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B206" s="48" t="n"/>
-      <c r="C206" s="48" t="n"/>
-      <c r="D206" s="48" t="n"/>
-      <c r="E206" s="48" t="n"/>
-      <c r="F206" s="48" t="n"/>
-      <c r="G206" s="48" t="n"/>
-      <c r="H206" s="48" t="n"/>
-      <c r="I206" s="48" t="n"/>
-      <c r="J206" s="48" t="n"/>
-      <c r="K206" s="48" t="n"/>
-      <c r="L206" s="48" t="n"/>
-      <c r="M206" s="48" t="n"/>
-      <c r="N206" s="48" t="n"/>
-      <c r="O206" s="48" t="n"/>
-      <c r="P206" s="48" t="n"/>
-      <c r="Q206" s="48" t="n"/>
+      <c r="Q206" s="40">
+        <f>Q204+Q205</f>
+        <v/>
+      </c>
     </row>
     <row r="207" ht="22" customHeight="1">
       <c r="A207" s="37" t="inlineStr">
         <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q207" s="41">
+        <f>COUNTIF(N8:N201,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="24" customHeight="1">
+      <c r="A210" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B210" s="44" t="n"/>
+      <c r="C210" s="44" t="n"/>
+      <c r="D210" s="44" t="n"/>
+      <c r="E210" s="44" t="n"/>
+      <c r="F210" s="44" t="n"/>
+      <c r="G210" s="44" t="n"/>
+      <c r="H210" s="44" t="n"/>
+      <c r="I210" s="44" t="n"/>
+      <c r="J210" s="44" t="n"/>
+      <c r="K210" s="44" t="n"/>
+      <c r="L210" s="44" t="n"/>
+      <c r="M210" s="44" t="n"/>
+      <c r="N210" s="44" t="n"/>
+      <c r="O210" s="44" t="n"/>
+      <c r="P210" s="44" t="n"/>
+      <c r="Q210" s="44" t="n"/>
+    </row>
+    <row r="211" ht="22" customHeight="1">
+      <c r="A211" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q211" s="38">
+        <f>SUMPRODUCT(H8:H201,J8:J201)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212" ht="22" customHeight="1">
+      <c r="A212" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q212" s="38">
+        <f>Q211*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213" ht="22" customHeight="1">
+      <c r="A213" s="45" t="inlineStr">
+        <is>
+          <t>Gesamtwert brutto</t>
+        </is>
+      </c>
+      <c r="Q213" s="46">
+        <f>Q211+Q212</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215" ht="24" customHeight="1">
+      <c r="A215" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B215" s="48" t="n"/>
+      <c r="C215" s="48" t="n"/>
+      <c r="D215" s="48" t="n"/>
+      <c r="E215" s="48" t="n"/>
+      <c r="F215" s="48" t="n"/>
+      <c r="G215" s="48" t="n"/>
+      <c r="H215" s="48" t="n"/>
+      <c r="I215" s="48" t="n"/>
+      <c r="J215" s="48" t="n"/>
+      <c r="K215" s="48" t="n"/>
+      <c r="L215" s="48" t="n"/>
+      <c r="M215" s="48" t="n"/>
+      <c r="N215" s="48" t="n"/>
+      <c r="O215" s="48" t="n"/>
+      <c r="P215" s="48" t="n"/>
+      <c r="Q215" s="48" t="n"/>
+    </row>
+    <row r="216" ht="22" customHeight="1">
+      <c r="A216" s="37" t="inlineStr">
+        <is>
           <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
         </is>
       </c>
-      <c r="Q207" s="38">
-        <f>-Q202*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="208" ht="22" customHeight="1">
-      <c r="A208" s="45" t="inlineStr">
+      <c r="Q216" s="38">
+        <f>-Q211*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="217" ht="22" customHeight="1">
+      <c r="A217" s="45" t="inlineStr">
         <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="Q208" s="46">
-        <f>Q202+Q207</f>
-        <v/>
-      </c>
-    </row>
-    <row r="209" ht="22" customHeight="1">
-      <c r="A209" s="37" t="inlineStr">
+      <c r="Q217" s="46">
+        <f>Q211+Q216</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218" ht="22" customHeight="1">
+      <c r="A218" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q209" s="38">
-        <f>Q208*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="210" ht="26" customHeight="1">
-      <c r="A210" s="39" t="inlineStr">
+      <c r="Q218" s="38">
+        <f>Q217*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219" ht="26" customHeight="1">
+      <c r="A219" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q210" s="40">
-        <f>Q208+Q209</f>
-        <v/>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="42" t="inlineStr">
+      <c r="Q219" s="40">
+        <f>Q217+Q218</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="213">
-      <c r="A213" s="49" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="214"/>
-    <row r="215"/>
-    <row r="216"/>
+    <row r="223"/>
+    <row r="224"/>
+    <row r="225"/>
   </sheetData>
-  <autoFilter ref="A7:Q192"/>
+  <autoFilter ref="A7:Q201"/>
   <mergeCells count="26">
+    <mergeCell ref="A220:Q220"/>
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A211:Q211"/>
-    <mergeCell ref="A203:P203"/>
-    <mergeCell ref="A201:Q201"/>
+    <mergeCell ref="A219:P219"/>
+    <mergeCell ref="A206:P206"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A209:P209"/>
     <mergeCell ref="L4:Q4"/>
-    <mergeCell ref="A213:Q216"/>
-    <mergeCell ref="A202:P202"/>
     <mergeCell ref="C3:I3"/>
+    <mergeCell ref="A211:P211"/>
+    <mergeCell ref="A208:Q208"/>
+    <mergeCell ref="A216:P216"/>
     <mergeCell ref="A207:P207"/>
-    <mergeCell ref="A197:P197"/>
     <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A196:P196"/>
-    <mergeCell ref="A194:Q194"/>
+    <mergeCell ref="A210:Q210"/>
+    <mergeCell ref="A218:P218"/>
+    <mergeCell ref="A205:P205"/>
+    <mergeCell ref="A203:Q203"/>
+    <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A5:Q5"/>
-    <mergeCell ref="A208:P208"/>
-    <mergeCell ref="A206:Q206"/>
-    <mergeCell ref="A198:P198"/>
-    <mergeCell ref="A199:Q199"/>
+    <mergeCell ref="A212:P212"/>
+    <mergeCell ref="A217:P217"/>
+    <mergeCell ref="A215:Q215"/>
+    <mergeCell ref="A222:Q225"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A210:P210"/>
-    <mergeCell ref="A195:P195"/>
+    <mergeCell ref="A213:P213"/>
     <mergeCell ref="A204:P204"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q192">
+  <conditionalFormatting sqref="A8:Q201">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N192" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O192" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$204</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5293,6 +5293,81 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>201</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="196" name="Image 196" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId196"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>202</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="197" name="Image 197" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId197"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>203</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="198" name="Image 198" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId198"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -5585,7 +5660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q225"/>
+  <dimension ref="A1:Q228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6660,7 +6735,7 @@
         </is>
       </c>
       <c r="H22" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I22" s="10" t="inlineStr">
         <is>
@@ -16877,7 +16952,7 @@
         </is>
       </c>
       <c r="H192" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I192" s="10" t="inlineStr">
         <is>
@@ -17449,261 +17524,441 @@
         <v/>
       </c>
     </row>
-    <row r="203" ht="24" customHeight="1">
-      <c r="A203" s="36" t="inlineStr">
+    <row r="202" ht="78" customHeight="1">
+      <c r="A202" s="9" t="n">
+        <v>195</v>
+      </c>
+      <c r="B202" s="10" t="inlineStr">
+        <is>
+          <t>BA10-09</t>
+        </is>
+      </c>
+      <c r="C202" s="11" t="n"/>
+      <c r="D202" s="12" t="inlineStr">
+        <is>
+          <t>Beistelltisch rund, Tablettplatte Birke
+Runder Beistelltisch: abnehmbare Tablettplatte aus Birke mit umlaufendem Rand, auf einem weißen Gestell aus Rundstahl mit Tragebügel.</t>
+        </is>
+      </c>
+      <c r="E202" s="13" t="n"/>
+      <c r="F202" s="12" t="inlineStr">
+        <is>
+          <t>Ruhe- / Schlafraum</t>
+        </is>
+      </c>
+      <c r="G202" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H202" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I202" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J202" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K202" s="15">
+        <f>J202*1.19</f>
+        <v/>
+      </c>
+      <c r="L202" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M202" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N202" s="16" t="n"/>
+      <c r="O202" s="17" t="n"/>
+      <c r="P202" s="18" t="n"/>
+      <c r="Q202" s="19">
+        <f>IF(N202&lt;&gt;"ja","",IF(O202="",H202,O202)*J202)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203" ht="78" customHeight="1">
+      <c r="A203" s="20" t="n">
+        <v>196</v>
+      </c>
+      <c r="B203" s="21" t="inlineStr">
+        <is>
+          <t>BA10-10</t>
+        </is>
+      </c>
+      <c r="C203" s="22" t="n"/>
+      <c r="D203" s="23" t="inlineStr">
+        <is>
+          <t>Beistelltisch rund, Tablettplatte schwarz
+Runder Beistelltisch mit schwarzer Tablettplatte auf drei schlanken, schwarz lackierten Metallbeinen. Platte mit Gebrauchsspuren.</t>
+        </is>
+      </c>
+      <c r="E203" s="13" t="n"/>
+      <c r="F203" s="23" t="inlineStr">
+        <is>
+          <t>Ruhe- / Schlafraum</t>
+        </is>
+      </c>
+      <c r="G203" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H203" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I203" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J203" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="K203" s="25">
+        <f>J203*1.19</f>
+        <v/>
+      </c>
+      <c r="L203" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M203" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N203" s="16" t="n"/>
+      <c r="O203" s="17" t="n"/>
+      <c r="P203" s="18" t="n"/>
+      <c r="Q203" s="26">
+        <f>IF(N203&lt;&gt;"ja","",IF(O203="",H203,O203)*J203)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204" ht="78" customHeight="1">
+      <c r="A204" s="9" t="n">
+        <v>197</v>
+      </c>
+      <c r="B204" s="10" t="inlineStr">
+        <is>
+          <t>BA10-11</t>
+        </is>
+      </c>
+      <c r="C204" s="11" t="n"/>
+      <c r="D204" s="12" t="inlineStr">
+        <is>
+          <t>Tisch rund, zweiteilig, weiß
+Runder Tisch aus zwei halbrunden weißen Platten mit Multiplex-Kante, auf höhenverstellbaren Rundfüßen aus Chrom. Die Hälften lassen sich einzeln stellen.</t>
+        </is>
+      </c>
+      <c r="E204" s="13" t="n"/>
+      <c r="F204" s="12" t="inlineStr">
+        <is>
+          <t>Ruhe- / Schlafraum</t>
+        </is>
+      </c>
+      <c r="G204" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H204" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I204" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J204" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="K204" s="15">
+        <f>J204*1.19</f>
+        <v/>
+      </c>
+      <c r="L204" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M204" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N204" s="16" t="n"/>
+      <c r="O204" s="17" t="n"/>
+      <c r="P204" s="18" t="n"/>
+      <c r="Q204" s="19">
+        <f>IF(N204&lt;&gt;"ja","",IF(O204="",H204,O204)*J204)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206" ht="24" customHeight="1">
+      <c r="A206" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B203" s="1" t="n"/>
-      <c r="C203" s="1" t="n"/>
-      <c r="D203" s="1" t="n"/>
-      <c r="E203" s="1" t="n"/>
-      <c r="F203" s="1" t="n"/>
-      <c r="G203" s="1" t="n"/>
-      <c r="H203" s="1" t="n"/>
-      <c r="I203" s="1" t="n"/>
-      <c r="J203" s="1" t="n"/>
-      <c r="K203" s="1" t="n"/>
-      <c r="L203" s="1" t="n"/>
-      <c r="M203" s="1" t="n"/>
-      <c r="N203" s="1" t="n"/>
-      <c r="O203" s="1" t="n"/>
-      <c r="P203" s="1" t="n"/>
-      <c r="Q203" s="1" t="n"/>
-    </row>
-    <row r="204" ht="22" customHeight="1">
-      <c r="A204" s="37" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl netto</t>
-        </is>
-      </c>
-      <c r="Q204" s="38">
-        <f>SUM(Q8:Q201)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="205" ht="22" customHeight="1">
-      <c r="A205" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q205" s="38">
-        <f>Q204*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="206" ht="26" customHeight="1">
-      <c r="A206" s="39" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl brutto</t>
-        </is>
-      </c>
-      <c r="Q206" s="40">
-        <f>Q204+Q205</f>
-        <v/>
-      </c>
+      <c r="B206" s="1" t="n"/>
+      <c r="C206" s="1" t="n"/>
+      <c r="D206" s="1" t="n"/>
+      <c r="E206" s="1" t="n"/>
+      <c r="F206" s="1" t="n"/>
+      <c r="G206" s="1" t="n"/>
+      <c r="H206" s="1" t="n"/>
+      <c r="I206" s="1" t="n"/>
+      <c r="J206" s="1" t="n"/>
+      <c r="K206" s="1" t="n"/>
+      <c r="L206" s="1" t="n"/>
+      <c r="M206" s="1" t="n"/>
+      <c r="N206" s="1" t="n"/>
+      <c r="O206" s="1" t="n"/>
+      <c r="P206" s="1" t="n"/>
+      <c r="Q206" s="1" t="n"/>
     </row>
     <row r="207" ht="22" customHeight="1">
       <c r="A207" s="37" t="inlineStr">
         <is>
+          <t>Wert Ihrer Auswahl netto</t>
+        </is>
+      </c>
+      <c r="Q207" s="38">
+        <f>SUM(Q8:Q204)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208" ht="22" customHeight="1">
+      <c r="A208" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q208" s="38">
+        <f>Q207*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209" ht="26" customHeight="1">
+      <c r="A209" s="39" t="inlineStr">
+        <is>
+          <t>Wert Ihrer Auswahl brutto</t>
+        </is>
+      </c>
+      <c r="Q209" s="40">
+        <f>Q207+Q208</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210" ht="22" customHeight="1">
+      <c r="A210" s="37" t="inlineStr">
+        <is>
           <t>gewählte Positionen</t>
         </is>
       </c>
-      <c r="Q207" s="41">
-        <f>COUNTIF(N8:N201,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" s="42" t="inlineStr">
+      <c r="Q210" s="41">
+        <f>COUNTIF(N8:N204,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="42" t="inlineStr">
         <is>
           <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
         </is>
       </c>
     </row>
-    <row r="210" ht="24" customHeight="1">
-      <c r="A210" s="43" t="inlineStr">
+    <row r="213" ht="24" customHeight="1">
+      <c r="A213" s="43" t="inlineStr">
         <is>
           <t>B · GESAMTBESTAND</t>
         </is>
       </c>
-      <c r="B210" s="44" t="n"/>
-      <c r="C210" s="44" t="n"/>
-      <c r="D210" s="44" t="n"/>
-      <c r="E210" s="44" t="n"/>
-      <c r="F210" s="44" t="n"/>
-      <c r="G210" s="44" t="n"/>
-      <c r="H210" s="44" t="n"/>
-      <c r="I210" s="44" t="n"/>
-      <c r="J210" s="44" t="n"/>
-      <c r="K210" s="44" t="n"/>
-      <c r="L210" s="44" t="n"/>
-      <c r="M210" s="44" t="n"/>
-      <c r="N210" s="44" t="n"/>
-      <c r="O210" s="44" t="n"/>
-      <c r="P210" s="44" t="n"/>
-      <c r="Q210" s="44" t="n"/>
-    </row>
-    <row r="211" ht="22" customHeight="1">
-      <c r="A211" s="37" t="inlineStr">
+      <c r="B213" s="44" t="n"/>
+      <c r="C213" s="44" t="n"/>
+      <c r="D213" s="44" t="n"/>
+      <c r="E213" s="44" t="n"/>
+      <c r="F213" s="44" t="n"/>
+      <c r="G213" s="44" t="n"/>
+      <c r="H213" s="44" t="n"/>
+      <c r="I213" s="44" t="n"/>
+      <c r="J213" s="44" t="n"/>
+      <c r="K213" s="44" t="n"/>
+      <c r="L213" s="44" t="n"/>
+      <c r="M213" s="44" t="n"/>
+      <c r="N213" s="44" t="n"/>
+      <c r="O213" s="44" t="n"/>
+      <c r="P213" s="44" t="n"/>
+      <c r="Q213" s="44" t="n"/>
+    </row>
+    <row r="214" ht="22" customHeight="1">
+      <c r="A214" s="37" t="inlineStr">
         <is>
           <t>Gesamtwert aller gelisteten Positionen netto</t>
         </is>
       </c>
-      <c r="Q211" s="38">
-        <f>SUMPRODUCT(H8:H201,J8:J201)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="212" ht="22" customHeight="1">
-      <c r="A212" s="37" t="inlineStr">
+      <c r="Q214" s="38">
+        <f>SUMPRODUCT(H8:H204,J8:J204)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215" ht="22" customHeight="1">
+      <c r="A215" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q212" s="38">
-        <f>Q211*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="213" ht="22" customHeight="1">
-      <c r="A213" s="45" t="inlineStr">
+      <c r="Q215" s="38">
+        <f>Q214*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="216" ht="22" customHeight="1">
+      <c r="A216" s="45" t="inlineStr">
         <is>
           <t>Gesamtwert brutto</t>
         </is>
       </c>
-      <c r="Q213" s="46">
-        <f>Q211+Q212</f>
-        <v/>
-      </c>
-    </row>
-    <row r="215" ht="24" customHeight="1">
-      <c r="A215" s="47" t="inlineStr">
+      <c r="Q216" s="46">
+        <f>Q214+Q215</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218" ht="24" customHeight="1">
+      <c r="A218" s="47" t="inlineStr">
         <is>
           <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
         </is>
       </c>
-      <c r="B215" s="48" t="n"/>
-      <c r="C215" s="48" t="n"/>
-      <c r="D215" s="48" t="n"/>
-      <c r="E215" s="48" t="n"/>
-      <c r="F215" s="48" t="n"/>
-      <c r="G215" s="48" t="n"/>
-      <c r="H215" s="48" t="n"/>
-      <c r="I215" s="48" t="n"/>
-      <c r="J215" s="48" t="n"/>
-      <c r="K215" s="48" t="n"/>
-      <c r="L215" s="48" t="n"/>
-      <c r="M215" s="48" t="n"/>
-      <c r="N215" s="48" t="n"/>
-      <c r="O215" s="48" t="n"/>
-      <c r="P215" s="48" t="n"/>
-      <c r="Q215" s="48" t="n"/>
-    </row>
-    <row r="216" ht="22" customHeight="1">
-      <c r="A216" s="37" t="inlineStr">
+      <c r="B218" s="48" t="n"/>
+      <c r="C218" s="48" t="n"/>
+      <c r="D218" s="48" t="n"/>
+      <c r="E218" s="48" t="n"/>
+      <c r="F218" s="48" t="n"/>
+      <c r="G218" s="48" t="n"/>
+      <c r="H218" s="48" t="n"/>
+      <c r="I218" s="48" t="n"/>
+      <c r="J218" s="48" t="n"/>
+      <c r="K218" s="48" t="n"/>
+      <c r="L218" s="48" t="n"/>
+      <c r="M218" s="48" t="n"/>
+      <c r="N218" s="48" t="n"/>
+      <c r="O218" s="48" t="n"/>
+      <c r="P218" s="48" t="n"/>
+      <c r="Q218" s="48" t="n"/>
+    </row>
+    <row r="219" ht="22" customHeight="1">
+      <c r="A219" s="37" t="inlineStr">
         <is>
           <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
         </is>
       </c>
-      <c r="Q216" s="38">
-        <f>-Q211*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="217" ht="22" customHeight="1">
-      <c r="A217" s="45" t="inlineStr">
+      <c r="Q219" s="38">
+        <f>-Q214*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220" ht="22" customHeight="1">
+      <c r="A220" s="45" t="inlineStr">
         <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="Q217" s="46">
-        <f>Q211+Q216</f>
-        <v/>
-      </c>
-    </row>
-    <row r="218" ht="22" customHeight="1">
-      <c r="A218" s="37" t="inlineStr">
+      <c r="Q220" s="46">
+        <f>Q214+Q219</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221" ht="22" customHeight="1">
+      <c r="A221" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q218" s="38">
-        <f>Q217*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="219" ht="26" customHeight="1">
-      <c r="A219" s="39" t="inlineStr">
+      <c r="Q221" s="38">
+        <f>Q220*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222" ht="26" customHeight="1">
+      <c r="A222" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q219" s="40">
-        <f>Q217+Q218</f>
-        <v/>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" s="42" t="inlineStr">
+      <c r="Q222" s="40">
+        <f>Q220+Q221</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="222">
-      <c r="A222" s="49" t="inlineStr">
+    <row r="225">
+      <c r="A225" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="223"/>
-    <row r="224"/>
-    <row r="225"/>
+    <row r="226"/>
+    <row r="227"/>
+    <row r="228"/>
   </sheetData>
-  <autoFilter ref="A7:Q201"/>
+  <autoFilter ref="A7:Q204"/>
   <mergeCells count="26">
-    <mergeCell ref="A220:Q220"/>
     <mergeCell ref="C1:Q1"/>
+    <mergeCell ref="A211:Q211"/>
     <mergeCell ref="A219:P219"/>
-    <mergeCell ref="A206:P206"/>
+    <mergeCell ref="A215:P215"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A209:P209"/>
     <mergeCell ref="L4:Q4"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A211:P211"/>
-    <mergeCell ref="A208:Q208"/>
+    <mergeCell ref="A220:P220"/>
+    <mergeCell ref="A218:Q218"/>
     <mergeCell ref="A216:P216"/>
+    <mergeCell ref="A222:P222"/>
     <mergeCell ref="A207:P207"/>
+    <mergeCell ref="A223:Q223"/>
     <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A210:Q210"/>
-    <mergeCell ref="A218:P218"/>
-    <mergeCell ref="A205:P205"/>
-    <mergeCell ref="A203:Q203"/>
+    <mergeCell ref="A213:Q213"/>
+    <mergeCell ref="A221:P221"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A212:P212"/>
-    <mergeCell ref="A217:P217"/>
-    <mergeCell ref="A215:Q215"/>
-    <mergeCell ref="A222:Q225"/>
+    <mergeCell ref="A208:P208"/>
+    <mergeCell ref="A206:Q206"/>
+    <mergeCell ref="A214:P214"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A213:P213"/>
-    <mergeCell ref="A204:P204"/>
+    <mergeCell ref="A210:P210"/>
+    <mergeCell ref="A225:Q228"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q201">
+  <conditionalFormatting sqref="A8:Q204">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N204" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O201" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O204" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$211</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5368,6 +5368,181 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>204</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="199" name="Image 199" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId199"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>205</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="200" name="Image 200" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId200"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>206</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="201" name="Image 201" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId201"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>207</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="202" name="Image 202" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId202"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>208</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="203" name="Image 203" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId203"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>209</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="204" name="Image 204" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId204"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>210</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="205" name="Image 205" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId205"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -5660,7 +5835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q228"/>
+  <dimension ref="A1:Q235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -17704,111 +17879,461 @@
         <v/>
       </c>
     </row>
-    <row r="206" ht="24" customHeight="1">
-      <c r="A206" s="36" t="inlineStr">
+    <row r="205" ht="78" customHeight="1">
+      <c r="A205" s="20" t="n">
+        <v>198</v>
+      </c>
+      <c r="B205" s="21" t="inlineStr">
+        <is>
+          <t>BA03-01</t>
+        </is>
+      </c>
+      <c r="C205" s="22" t="n"/>
+      <c r="D205" s="23" t="inlineStr">
+        <is>
+          <t>IKEA Avsiktlig Teppich, schwarz-weiß gepunktet
+Flachgewebter Teppich in Creme mit schwarzen Punktreihen, IKEA Avsiktlig. Flor 100 % Polypropylen auf Jutekette. Etikett auf der Rückseite vorhanden.</t>
+        </is>
+      </c>
+      <c r="E205" s="13" t="inlineStr">
+        <is>
+          <t>133 × 195 cm</t>
+        </is>
+      </c>
+      <c r="F205" s="23" t="inlineStr">
+        <is>
+          <t>Galerie</t>
+        </is>
+      </c>
+      <c r="G205" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H205" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I205" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J205" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="K205" s="25">
+        <f>J205*1.19</f>
+        <v/>
+      </c>
+      <c r="L205" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M205" s="23" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N205" s="16" t="n"/>
+      <c r="O205" s="17" t="n"/>
+      <c r="P205" s="18" t="n"/>
+      <c r="Q205" s="26">
+        <f>IF(N205&lt;&gt;"ja","",IF(O205="",H205,O205)*J205)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206" ht="78" customHeight="1">
+      <c r="A206" s="9" t="n">
+        <v>199</v>
+      </c>
+      <c r="B206" s="35" t="inlineStr">
+        <is>
+          <t>BA03-02</t>
+        </is>
+      </c>
+      <c r="C206" s="11" t="n"/>
+      <c r="D206" s="12" t="inlineStr">
+        <is>
+          <t>Spielküche beige-braun, mehrteilig
+Spielküche aus beschichteter Platte in Creme und Taupe mit Holzarbeitsplatten: Mikrowellenmodul mit Digitalanzeige, Unterschränke mit Kochfeld, Backofen mit Sichtfenster und Spüle, dazu ein Wandregal. Abgerundete Ecken, kindgerechte Höhe.</t>
+        </is>
+      </c>
+      <c r="E206" s="13" t="n"/>
+      <c r="F206" s="12" t="inlineStr">
+        <is>
+          <t>Galerie</t>
+        </is>
+      </c>
+      <c r="G206" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H206" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I206" s="10" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="J206" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="K206" s="15">
+        <f>J206*1.19</f>
+        <v/>
+      </c>
+      <c r="L206" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M206" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N206" s="16" t="n"/>
+      <c r="O206" s="17" t="n"/>
+      <c r="P206" s="18" t="n"/>
+      <c r="Q206" s="19">
+        <f>IF(N206&lt;&gt;"ja","",IF(O206="",H206,O206)*J206)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207" ht="78" customHeight="1">
+      <c r="A207" s="20" t="n">
+        <v>200</v>
+      </c>
+      <c r="B207" s="21" t="inlineStr">
+        <is>
+          <t>BA03-03</t>
+        </is>
+      </c>
+      <c r="C207" s="22" t="n"/>
+      <c r="D207" s="23" t="inlineStr">
+        <is>
+          <t>Sofa grau, 2-Sitzer
+Kleines Zweisitzer-Sofa mit grauem Steppbezug aus Velours und weißem Metallgestell. Bezug abnehmbar.</t>
+        </is>
+      </c>
+      <c r="E207" s="13" t="n"/>
+      <c r="F207" s="23" t="inlineStr">
+        <is>
+          <t>Galerie</t>
+        </is>
+      </c>
+      <c r="G207" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H207" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I207" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J207" s="24" t="n">
+        <v>70</v>
+      </c>
+      <c r="K207" s="25">
+        <f>J207*1.19</f>
+        <v/>
+      </c>
+      <c r="L207" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M207" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N207" s="16" t="n"/>
+      <c r="O207" s="17" t="n"/>
+      <c r="P207" s="18" t="n"/>
+      <c r="Q207" s="26">
+        <f>IF(N207&lt;&gt;"ja","",IF(O207="",H207,O207)*J207)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208" ht="78" customHeight="1">
+      <c r="A208" s="9" t="n">
+        <v>201</v>
+      </c>
+      <c r="B208" s="10" t="inlineStr">
+        <is>
+          <t>BA03-05</t>
+        </is>
+      </c>
+      <c r="C208" s="11" t="n"/>
+      <c r="D208" s="12" t="inlineStr">
+        <is>
+          <t>BRIO Puppenwagen rot gepunktet
+Kombi-Puppenwagen von BRIO: weißes Metallgestell mit Luftreifen, roter Stoffbezug mit weißen Punkten, schwenkbarer Schiebebügel, Ablagekorb unten. Markenetikett am Verdeck.</t>
+        </is>
+      </c>
+      <c r="E208" s="13" t="n"/>
+      <c r="F208" s="12" t="inlineStr">
+        <is>
+          <t>Galerie</t>
+        </is>
+      </c>
+      <c r="G208" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H208" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I208" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J208" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="K208" s="15">
+        <f>J208*1.19</f>
+        <v/>
+      </c>
+      <c r="L208" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M208" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N208" s="16" t="n"/>
+      <c r="O208" s="17" t="n"/>
+      <c r="P208" s="18" t="n"/>
+      <c r="Q208" s="19">
+        <f>IF(N208&lt;&gt;"ja","",IF(O208="",H208,O208)*J208)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209" ht="78" customHeight="1">
+      <c r="A209" s="20" t="n">
+        <v>202</v>
+      </c>
+      <c r="B209" s="21" t="inlineStr">
+        <is>
+          <t>BA03-06</t>
+        </is>
+      </c>
+      <c r="C209" s="22" t="n"/>
+      <c r="D209" s="23" t="inlineStr">
+        <is>
+          <t>Kaufladen weiß mit Aufsatz
+Kaufladen aus Holz, weiß mit grauer Rückwand: Verkaufstheke mit Ablage unten, Aufsatz mit mehreren unterschiedlich großen Fächern.</t>
+        </is>
+      </c>
+      <c r="E209" s="13" t="n"/>
+      <c r="F209" s="23" t="inlineStr">
+        <is>
+          <t>Galerie</t>
+        </is>
+      </c>
+      <c r="G209" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H209" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I209" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J209" s="24" t="n">
+        <v>90</v>
+      </c>
+      <c r="K209" s="25">
+        <f>J209*1.19</f>
+        <v/>
+      </c>
+      <c r="L209" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M209" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N209" s="16" t="n"/>
+      <c r="O209" s="17" t="n"/>
+      <c r="P209" s="18" t="n"/>
+      <c r="Q209" s="26">
+        <f>IF(N209&lt;&gt;"ja","",IF(O209="",H209,O209)*J209)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210" ht="78" customHeight="1">
+      <c r="A210" s="9" t="n">
+        <v>203</v>
+      </c>
+      <c r="B210" s="10" t="inlineStr">
+        <is>
+          <t>BA03-07</t>
+        </is>
+      </c>
+      <c r="C210" s="11" t="n"/>
+      <c r="D210" s="12" t="inlineStr">
+        <is>
+          <t>Schrank weiß, zwei Türen
+Hoher Schrank in Weiß mit zwei Türen und runden Porzellanknöpfen in Rosenform.</t>
+        </is>
+      </c>
+      <c r="E210" s="13" t="n"/>
+      <c r="F210" s="12" t="inlineStr">
+        <is>
+          <t>Galerie</t>
+        </is>
+      </c>
+      <c r="G210" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H210" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I210" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J210" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="K210" s="15">
+        <f>J210*1.19</f>
+        <v/>
+      </c>
+      <c r="L210" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M210" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N210" s="16" t="n"/>
+      <c r="O210" s="17" t="n"/>
+      <c r="P210" s="18" t="n"/>
+      <c r="Q210" s="19">
+        <f>IF(N210&lt;&gt;"ja","",IF(O210="",H210,O210)*J210)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211" ht="78" customHeight="1">
+      <c r="A211" s="20" t="n">
+        <v>204</v>
+      </c>
+      <c r="B211" s="21" t="inlineStr">
+        <is>
+          <t>BA03-04</t>
+        </is>
+      </c>
+      <c r="C211" s="22" t="n"/>
+      <c r="D211" s="23" t="inlineStr">
+        <is>
+          <t>Wandregal Hausform, schwarz
+Wandregale in Hausform aus schwarz lackiertem Holz, zum Aufstellen oder Aufhängen, in unterschiedlichen Größen.</t>
+        </is>
+      </c>
+      <c r="E211" s="13" t="n"/>
+      <c r="F211" s="23" t="inlineStr">
+        <is>
+          <t>Galerie</t>
+        </is>
+      </c>
+      <c r="G211" s="21" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H211" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I211" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J211" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="K211" s="25">
+        <f>J211*1.19</f>
+        <v/>
+      </c>
+      <c r="L211" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M211" s="23" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N211" s="16" t="n"/>
+      <c r="O211" s="17" t="n"/>
+      <c r="P211" s="18" t="n"/>
+      <c r="Q211" s="26">
+        <f>IF(N211&lt;&gt;"ja","",IF(O211="",H211,O211)*J211)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213" ht="24" customHeight="1">
+      <c r="A213" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B206" s="1" t="n"/>
-      <c r="C206" s="1" t="n"/>
-      <c r="D206" s="1" t="n"/>
-      <c r="E206" s="1" t="n"/>
-      <c r="F206" s="1" t="n"/>
-      <c r="G206" s="1" t="n"/>
-      <c r="H206" s="1" t="n"/>
-      <c r="I206" s="1" t="n"/>
-      <c r="J206" s="1" t="n"/>
-      <c r="K206" s="1" t="n"/>
-      <c r="L206" s="1" t="n"/>
-      <c r="M206" s="1" t="n"/>
-      <c r="N206" s="1" t="n"/>
-      <c r="O206" s="1" t="n"/>
-      <c r="P206" s="1" t="n"/>
-      <c r="Q206" s="1" t="n"/>
-    </row>
-    <row r="207" ht="22" customHeight="1">
-      <c r="A207" s="37" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl netto</t>
-        </is>
-      </c>
-      <c r="Q207" s="38">
-        <f>SUM(Q8:Q204)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="208" ht="22" customHeight="1">
-      <c r="A208" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q208" s="38">
-        <f>Q207*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="209" ht="26" customHeight="1">
-      <c r="A209" s="39" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl brutto</t>
-        </is>
-      </c>
-      <c r="Q209" s="40">
-        <f>Q207+Q208</f>
-        <v/>
-      </c>
-    </row>
-    <row r="210" ht="22" customHeight="1">
-      <c r="A210" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q210" s="41">
-        <f>COUNTIF(N8:N204,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="24" customHeight="1">
-      <c r="A213" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B213" s="44" t="n"/>
-      <c r="C213" s="44" t="n"/>
-      <c r="D213" s="44" t="n"/>
-      <c r="E213" s="44" t="n"/>
-      <c r="F213" s="44" t="n"/>
-      <c r="G213" s="44" t="n"/>
-      <c r="H213" s="44" t="n"/>
-      <c r="I213" s="44" t="n"/>
-      <c r="J213" s="44" t="n"/>
-      <c r="K213" s="44" t="n"/>
-      <c r="L213" s="44" t="n"/>
-      <c r="M213" s="44" t="n"/>
-      <c r="N213" s="44" t="n"/>
-      <c r="O213" s="44" t="n"/>
-      <c r="P213" s="44" t="n"/>
-      <c r="Q213" s="44" t="n"/>
+      <c r="B213" s="1" t="n"/>
+      <c r="C213" s="1" t="n"/>
+      <c r="D213" s="1" t="n"/>
+      <c r="E213" s="1" t="n"/>
+      <c r="F213" s="1" t="n"/>
+      <c r="G213" s="1" t="n"/>
+      <c r="H213" s="1" t="n"/>
+      <c r="I213" s="1" t="n"/>
+      <c r="J213" s="1" t="n"/>
+      <c r="K213" s="1" t="n"/>
+      <c r="L213" s="1" t="n"/>
+      <c r="M213" s="1" t="n"/>
+      <c r="N213" s="1" t="n"/>
+      <c r="O213" s="1" t="n"/>
+      <c r="P213" s="1" t="n"/>
+      <c r="Q213" s="1" t="n"/>
     </row>
     <row r="214" ht="22" customHeight="1">
       <c r="A214" s="37" t="inlineStr">
         <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
+          <t>Wert Ihrer Auswahl netto</t>
         </is>
       </c>
       <c r="Q214" s="38">
-        <f>SUMPRODUCT(H8:H204,J8:J204)</f>
+        <f>SUM(Q8:Q211)</f>
         <v/>
       </c>
     </row>
@@ -17823,142 +18348,216 @@
         <v/>
       </c>
     </row>
-    <row r="216" ht="22" customHeight="1">
-      <c r="A216" s="45" t="inlineStr">
-        <is>
-          <t>Gesamtwert brutto</t>
-        </is>
-      </c>
-      <c r="Q216" s="46">
+    <row r="216" ht="26" customHeight="1">
+      <c r="A216" s="39" t="inlineStr">
+        <is>
+          <t>Wert Ihrer Auswahl brutto</t>
+        </is>
+      </c>
+      <c r="Q216" s="40">
         <f>Q214+Q215</f>
         <v/>
       </c>
     </row>
-    <row r="218" ht="24" customHeight="1">
-      <c r="A218" s="47" t="inlineStr">
-        <is>
-          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B218" s="48" t="n"/>
-      <c r="C218" s="48" t="n"/>
-      <c r="D218" s="48" t="n"/>
-      <c r="E218" s="48" t="n"/>
-      <c r="F218" s="48" t="n"/>
-      <c r="G218" s="48" t="n"/>
-      <c r="H218" s="48" t="n"/>
-      <c r="I218" s="48" t="n"/>
-      <c r="J218" s="48" t="n"/>
-      <c r="K218" s="48" t="n"/>
-      <c r="L218" s="48" t="n"/>
-      <c r="M218" s="48" t="n"/>
-      <c r="N218" s="48" t="n"/>
-      <c r="O218" s="48" t="n"/>
-      <c r="P218" s="48" t="n"/>
-      <c r="Q218" s="48" t="n"/>
-    </row>
-    <row r="219" ht="22" customHeight="1">
-      <c r="A219" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
-        </is>
-      </c>
-      <c r="Q219" s="38">
-        <f>-Q214*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="220" ht="22" customHeight="1">
-      <c r="A220" s="45" t="inlineStr">
-        <is>
-          <t>Paketpreis netto</t>
-        </is>
-      </c>
-      <c r="Q220" s="46">
-        <f>Q214+Q219</f>
-        <v/>
-      </c>
+    <row r="217" ht="22" customHeight="1">
+      <c r="A217" s="37" t="inlineStr">
+        <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q217" s="41">
+        <f>COUNTIF(N8:N211,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="24" customHeight="1">
+      <c r="A220" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B220" s="44" t="n"/>
+      <c r="C220" s="44" t="n"/>
+      <c r="D220" s="44" t="n"/>
+      <c r="E220" s="44" t="n"/>
+      <c r="F220" s="44" t="n"/>
+      <c r="G220" s="44" t="n"/>
+      <c r="H220" s="44" t="n"/>
+      <c r="I220" s="44" t="n"/>
+      <c r="J220" s="44" t="n"/>
+      <c r="K220" s="44" t="n"/>
+      <c r="L220" s="44" t="n"/>
+      <c r="M220" s="44" t="n"/>
+      <c r="N220" s="44" t="n"/>
+      <c r="O220" s="44" t="n"/>
+      <c r="P220" s="44" t="n"/>
+      <c r="Q220" s="44" t="n"/>
     </row>
     <row r="221" ht="22" customHeight="1">
       <c r="A221" s="37" t="inlineStr">
         <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q221" s="38">
+        <f>SUMPRODUCT(H8:H211,J8:J211)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222" ht="22" customHeight="1">
+      <c r="A222" s="37" t="inlineStr">
+        <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q221" s="38">
-        <f>Q220*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="222" ht="26" customHeight="1">
-      <c r="A222" s="39" t="inlineStr">
+      <c r="Q222" s="38">
+        <f>Q221*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223" ht="22" customHeight="1">
+      <c r="A223" s="45" t="inlineStr">
+        <is>
+          <t>Gesamtwert brutto</t>
+        </is>
+      </c>
+      <c r="Q223" s="46">
+        <f>Q221+Q222</f>
+        <v/>
+      </c>
+    </row>
+    <row r="225" ht="24" customHeight="1">
+      <c r="A225" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B225" s="48" t="n"/>
+      <c r="C225" s="48" t="n"/>
+      <c r="D225" s="48" t="n"/>
+      <c r="E225" s="48" t="n"/>
+      <c r="F225" s="48" t="n"/>
+      <c r="G225" s="48" t="n"/>
+      <c r="H225" s="48" t="n"/>
+      <c r="I225" s="48" t="n"/>
+      <c r="J225" s="48" t="n"/>
+      <c r="K225" s="48" t="n"/>
+      <c r="L225" s="48" t="n"/>
+      <c r="M225" s="48" t="n"/>
+      <c r="N225" s="48" t="n"/>
+      <c r="O225" s="48" t="n"/>
+      <c r="P225" s="48" t="n"/>
+      <c r="Q225" s="48" t="n"/>
+    </row>
+    <row r="226" ht="22" customHeight="1">
+      <c r="A226" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
+        </is>
+      </c>
+      <c r="Q226" s="38">
+        <f>-Q221*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227" ht="22" customHeight="1">
+      <c r="A227" s="45" t="inlineStr">
+        <is>
+          <t>Paketpreis netto</t>
+        </is>
+      </c>
+      <c r="Q227" s="46">
+        <f>Q221+Q226</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228" ht="22" customHeight="1">
+      <c r="A228" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q228" s="38">
+        <f>Q227*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="229" ht="26" customHeight="1">
+      <c r="A229" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q222" s="40">
-        <f>Q220+Q221</f>
-        <v/>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="42" t="inlineStr">
+      <c r="Q229" s="40">
+        <f>Q227+Q228</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="225">
-      <c r="A225" s="49" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="226"/>
-    <row r="227"/>
-    <row r="228"/>
+    <row r="233"/>
+    <row r="234"/>
+    <row r="235"/>
   </sheetData>
-  <autoFilter ref="A7:Q204"/>
+  <autoFilter ref="A7:Q211"/>
   <mergeCells count="26">
+    <mergeCell ref="A220:Q220"/>
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A211:Q211"/>
-    <mergeCell ref="A219:P219"/>
     <mergeCell ref="A215:P215"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A209:P209"/>
+    <mergeCell ref="A225:Q225"/>
     <mergeCell ref="L4:Q4"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A220:P220"/>
+    <mergeCell ref="A229:P229"/>
     <mergeCell ref="A218:Q218"/>
+    <mergeCell ref="A226:P226"/>
     <mergeCell ref="A216:P216"/>
     <mergeCell ref="A222:P222"/>
-    <mergeCell ref="A207:P207"/>
-    <mergeCell ref="A223:Q223"/>
     <mergeCell ref="C4:I4"/>
+    <mergeCell ref="A228:P228"/>
     <mergeCell ref="A213:Q213"/>
     <mergeCell ref="A221:P221"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A208:P208"/>
-    <mergeCell ref="A206:Q206"/>
+    <mergeCell ref="A227:P227"/>
+    <mergeCell ref="A217:P217"/>
+    <mergeCell ref="A232:Q235"/>
+    <mergeCell ref="A223:P223"/>
     <mergeCell ref="A214:P214"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A210:P210"/>
-    <mergeCell ref="A225:Q228"/>
+    <mergeCell ref="A230:Q230"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q204">
+  <conditionalFormatting sqref="A8:Q211">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N204" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N211" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O204" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O211" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$211</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$216</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5543,6 +5543,131 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>211</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="206" name="Image 206" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId206"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>212</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="207" name="Image 207" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId207"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>213</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="208" name="Image 208" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId208"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>214</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="209" name="Image 209" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId209"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>215</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="210" name="Image 210" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId210"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -5835,7 +5960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q235"/>
+  <dimension ref="A1:Q240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -6128,7 +6253,7 @@
         </is>
       </c>
       <c r="H9" s="21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I9" s="21" t="inlineStr">
         <is>
@@ -13827,7 +13952,7 @@
         </is>
       </c>
       <c r="H137" s="21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I137" s="21" t="inlineStr">
         <is>
@@ -14247,7 +14372,7 @@
         </is>
       </c>
       <c r="H144" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I144" s="10" t="inlineStr">
         <is>
@@ -18303,261 +18428,561 @@
         <v/>
       </c>
     </row>
-    <row r="213" ht="24" customHeight="1">
-      <c r="A213" s="36" t="inlineStr">
+    <row r="212" ht="78" customHeight="1">
+      <c r="A212" s="9" t="n">
+        <v>205</v>
+      </c>
+      <c r="B212" s="10" t="inlineStr">
+        <is>
+          <t>BA04-04</t>
+        </is>
+      </c>
+      <c r="C212" s="11" t="n"/>
+      <c r="D212" s="12" t="inlineStr">
+        <is>
+          <t>Stapelstuhl Kunststoff, weiß
+Stuhl aus weißem Kunststoff in einem Stück, runde Rückenlehne, konische Beine mit Querstrebe, stapelbar. Sitzfläche mit Kratzern.</t>
+        </is>
+      </c>
+      <c r="E212" s="13" t="n"/>
+      <c r="F212" s="12" t="inlineStr">
+        <is>
+          <t>Gruppenraum 4</t>
+        </is>
+      </c>
+      <c r="G212" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H212" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="I212" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J212" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K212" s="15">
+        <f>J212*1.19</f>
+        <v/>
+      </c>
+      <c r="L212" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M212" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N212" s="16" t="n"/>
+      <c r="O212" s="17" t="n"/>
+      <c r="P212" s="18" t="n"/>
+      <c r="Q212" s="19">
+        <f>IF(N212&lt;&gt;"ja","",IF(O212="",H212,O212)*J212)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213" ht="78" customHeight="1">
+      <c r="A213" s="20" t="n">
+        <v>206</v>
+      </c>
+      <c r="B213" s="21" t="inlineStr">
+        <is>
+          <t>BA04-05</t>
+        </is>
+      </c>
+      <c r="C213" s="22" t="n"/>
+      <c r="D213" s="23" t="inlineStr">
+        <is>
+          <t>Kinder-Sessel Bugholz mit Polster
+Sessel in Kindergröße: Gestell aus gebogenem Schichtholz in Birke, Auflage aus cremefarbenem Stoff mit Nackenkissen. Bezug abnehmbar, Stoff fleckig.</t>
+        </is>
+      </c>
+      <c r="E213" s="13" t="n"/>
+      <c r="F213" s="23" t="inlineStr">
+        <is>
+          <t>Gruppenraum 4</t>
+        </is>
+      </c>
+      <c r="G213" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H213" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I213" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J213" s="24" t="n">
+        <v>45</v>
+      </c>
+      <c r="K213" s="25">
+        <f>J213*1.19</f>
+        <v/>
+      </c>
+      <c r="L213" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M213" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N213" s="16" t="n"/>
+      <c r="O213" s="17" t="n"/>
+      <c r="P213" s="18" t="n"/>
+      <c r="Q213" s="26">
+        <f>IF(N213&lt;&gt;"ja","",IF(O213="",H213,O213)*J213)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="214" ht="78" customHeight="1">
+      <c r="A214" s="9" t="n">
+        <v>207</v>
+      </c>
+      <c r="B214" s="10" t="inlineStr">
+        <is>
+          <t>BA04-06</t>
+        </is>
+      </c>
+      <c r="C214" s="11" t="n"/>
+      <c r="D214" s="12" t="inlineStr">
+        <is>
+          <t>Rollwagen weiß, drei Etagen
+Rollwagen aus weiß lackiertem Stahlblech mit drei Wannenböden und vier Rollen.</t>
+        </is>
+      </c>
+      <c r="E214" s="13" t="n"/>
+      <c r="F214" s="12" t="inlineStr">
+        <is>
+          <t>Gruppenraum 4</t>
+        </is>
+      </c>
+      <c r="G214" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H214" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I214" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J214" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="K214" s="15">
+        <f>J214*1.19</f>
+        <v/>
+      </c>
+      <c r="L214" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M214" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N214" s="16" t="n"/>
+      <c r="O214" s="17" t="n"/>
+      <c r="P214" s="18" t="n"/>
+      <c r="Q214" s="19">
+        <f>IF(N214&lt;&gt;"ja","",IF(O214="",H214,O214)*J214)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215" ht="78" customHeight="1">
+      <c r="A215" s="20" t="n">
+        <v>208</v>
+      </c>
+      <c r="B215" s="21" t="inlineStr">
+        <is>
+          <t>BA04-07</t>
+        </is>
+      </c>
+      <c r="C215" s="22" t="n"/>
+      <c r="D215" s="23" t="inlineStr">
+        <is>
+          <t>Beistelltisch Drahtkorb, weiß
+Runder Beistelltisch: weißer Drahtkorb mit abnehmbarer Platte in heller Holzoptik. Der Korb lässt sich als Ablage nutzen.</t>
+        </is>
+      </c>
+      <c r="E215" s="13" t="n"/>
+      <c r="F215" s="23" t="inlineStr">
+        <is>
+          <t>Gruppenraum 4</t>
+        </is>
+      </c>
+      <c r="G215" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H215" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I215" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J215" s="24" t="n">
+        <v>35</v>
+      </c>
+      <c r="K215" s="25">
+        <f>J215*1.19</f>
+        <v/>
+      </c>
+      <c r="L215" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M215" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N215" s="16" t="n"/>
+      <c r="O215" s="17" t="n"/>
+      <c r="P215" s="18" t="n"/>
+      <c r="Q215" s="26">
+        <f>IF(N215&lt;&gt;"ja","",IF(O215="",H215,O215)*J215)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="216" ht="78" customHeight="1">
+      <c r="A216" s="9" t="n">
+        <v>209</v>
+      </c>
+      <c r="B216" s="10" t="inlineStr">
+        <is>
+          <t>BA04-09</t>
+        </is>
+      </c>
+      <c r="C216" s="11" t="n"/>
+      <c r="D216" s="12" t="inlineStr">
+        <is>
+          <t>Kinderschrank weiß, zwei Türen mit Schublade
+Hoher Schrank in Weiß mit zwei Türen und schwarzen Griffmulden, darunter eine Schublade.</t>
+        </is>
+      </c>
+      <c r="E216" s="13" t="n"/>
+      <c r="F216" s="12" t="inlineStr">
+        <is>
+          <t>Gruppenraum 4</t>
+        </is>
+      </c>
+      <c r="G216" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H216" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I216" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J216" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="K216" s="15">
+        <f>J216*1.19</f>
+        <v/>
+      </c>
+      <c r="L216" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M216" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N216" s="16" t="n"/>
+      <c r="O216" s="17" t="n"/>
+      <c r="P216" s="18" t="n"/>
+      <c r="Q216" s="19">
+        <f>IF(N216&lt;&gt;"ja","",IF(O216="",H216,O216)*J216)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218" ht="24" customHeight="1">
+      <c r="A218" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B213" s="1" t="n"/>
-      <c r="C213" s="1" t="n"/>
-      <c r="D213" s="1" t="n"/>
-      <c r="E213" s="1" t="n"/>
-      <c r="F213" s="1" t="n"/>
-      <c r="G213" s="1" t="n"/>
-      <c r="H213" s="1" t="n"/>
-      <c r="I213" s="1" t="n"/>
-      <c r="J213" s="1" t="n"/>
-      <c r="K213" s="1" t="n"/>
-      <c r="L213" s="1" t="n"/>
-      <c r="M213" s="1" t="n"/>
-      <c r="N213" s="1" t="n"/>
-      <c r="O213" s="1" t="n"/>
-      <c r="P213" s="1" t="n"/>
-      <c r="Q213" s="1" t="n"/>
-    </row>
-    <row r="214" ht="22" customHeight="1">
-      <c r="A214" s="37" t="inlineStr">
+      <c r="B218" s="1" t="n"/>
+      <c r="C218" s="1" t="n"/>
+      <c r="D218" s="1" t="n"/>
+      <c r="E218" s="1" t="n"/>
+      <c r="F218" s="1" t="n"/>
+      <c r="G218" s="1" t="n"/>
+      <c r="H218" s="1" t="n"/>
+      <c r="I218" s="1" t="n"/>
+      <c r="J218" s="1" t="n"/>
+      <c r="K218" s="1" t="n"/>
+      <c r="L218" s="1" t="n"/>
+      <c r="M218" s="1" t="n"/>
+      <c r="N218" s="1" t="n"/>
+      <c r="O218" s="1" t="n"/>
+      <c r="P218" s="1" t="n"/>
+      <c r="Q218" s="1" t="n"/>
+    </row>
+    <row r="219" ht="22" customHeight="1">
+      <c r="A219" s="37" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl netto</t>
         </is>
       </c>
-      <c r="Q214" s="38">
-        <f>SUM(Q8:Q211)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="215" ht="22" customHeight="1">
-      <c r="A215" s="37" t="inlineStr">
+      <c r="Q219" s="38">
+        <f>SUM(Q8:Q216)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220" ht="22" customHeight="1">
+      <c r="A220" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q215" s="38">
-        <f>Q214*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="216" ht="26" customHeight="1">
-      <c r="A216" s="39" t="inlineStr">
+      <c r="Q220" s="38">
+        <f>Q219*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221" ht="26" customHeight="1">
+      <c r="A221" s="39" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl brutto</t>
         </is>
       </c>
-      <c r="Q216" s="40">
-        <f>Q214+Q215</f>
-        <v/>
-      </c>
-    </row>
-    <row r="217" ht="22" customHeight="1">
-      <c r="A217" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q217" s="41">
-        <f>COUNTIF(N8:N211,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="220" ht="24" customHeight="1">
-      <c r="A220" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B220" s="44" t="n"/>
-      <c r="C220" s="44" t="n"/>
-      <c r="D220" s="44" t="n"/>
-      <c r="E220" s="44" t="n"/>
-      <c r="F220" s="44" t="n"/>
-      <c r="G220" s="44" t="n"/>
-      <c r="H220" s="44" t="n"/>
-      <c r="I220" s="44" t="n"/>
-      <c r="J220" s="44" t="n"/>
-      <c r="K220" s="44" t="n"/>
-      <c r="L220" s="44" t="n"/>
-      <c r="M220" s="44" t="n"/>
-      <c r="N220" s="44" t="n"/>
-      <c r="O220" s="44" t="n"/>
-      <c r="P220" s="44" t="n"/>
-      <c r="Q220" s="44" t="n"/>
-    </row>
-    <row r="221" ht="22" customHeight="1">
-      <c r="A221" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
-        </is>
-      </c>
-      <c r="Q221" s="38">
-        <f>SUMPRODUCT(H8:H211,J8:J211)</f>
+      <c r="Q221" s="40">
+        <f>Q219+Q220</f>
         <v/>
       </c>
     </row>
     <row r="222" ht="22" customHeight="1">
       <c r="A222" s="37" t="inlineStr">
         <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q222" s="38">
-        <f>Q221*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="223" ht="22" customHeight="1">
-      <c r="A223" s="45" t="inlineStr">
-        <is>
-          <t>Gesamtwert brutto</t>
-        </is>
-      </c>
-      <c r="Q223" s="46">
-        <f>Q221+Q222</f>
-        <v/>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q222" s="41">
+        <f>COUNTIF(N8:N216,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
       </c>
     </row>
     <row r="225" ht="24" customHeight="1">
-      <c r="A225" s="47" t="inlineStr">
-        <is>
-          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B225" s="48" t="n"/>
-      <c r="C225" s="48" t="n"/>
-      <c r="D225" s="48" t="n"/>
-      <c r="E225" s="48" t="n"/>
-      <c r="F225" s="48" t="n"/>
-      <c r="G225" s="48" t="n"/>
-      <c r="H225" s="48" t="n"/>
-      <c r="I225" s="48" t="n"/>
-      <c r="J225" s="48" t="n"/>
-      <c r="K225" s="48" t="n"/>
-      <c r="L225" s="48" t="n"/>
-      <c r="M225" s="48" t="n"/>
-      <c r="N225" s="48" t="n"/>
-      <c r="O225" s="48" t="n"/>
-      <c r="P225" s="48" t="n"/>
-      <c r="Q225" s="48" t="n"/>
+      <c r="A225" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B225" s="44" t="n"/>
+      <c r="C225" s="44" t="n"/>
+      <c r="D225" s="44" t="n"/>
+      <c r="E225" s="44" t="n"/>
+      <c r="F225" s="44" t="n"/>
+      <c r="G225" s="44" t="n"/>
+      <c r="H225" s="44" t="n"/>
+      <c r="I225" s="44" t="n"/>
+      <c r="J225" s="44" t="n"/>
+      <c r="K225" s="44" t="n"/>
+      <c r="L225" s="44" t="n"/>
+      <c r="M225" s="44" t="n"/>
+      <c r="N225" s="44" t="n"/>
+      <c r="O225" s="44" t="n"/>
+      <c r="P225" s="44" t="n"/>
+      <c r="Q225" s="44" t="n"/>
     </row>
     <row r="226" ht="22" customHeight="1">
       <c r="A226" s="37" t="inlineStr">
         <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q226" s="38">
+        <f>SUMPRODUCT(H8:H216,J8:J216)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227" ht="22" customHeight="1">
+      <c r="A227" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q227" s="38">
+        <f>Q226*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228" ht="22" customHeight="1">
+      <c r="A228" s="45" t="inlineStr">
+        <is>
+          <t>Gesamtwert brutto</t>
+        </is>
+      </c>
+      <c r="Q228" s="46">
+        <f>Q226+Q227</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230" ht="24" customHeight="1">
+      <c r="A230" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B230" s="48" t="n"/>
+      <c r="C230" s="48" t="n"/>
+      <c r="D230" s="48" t="n"/>
+      <c r="E230" s="48" t="n"/>
+      <c r="F230" s="48" t="n"/>
+      <c r="G230" s="48" t="n"/>
+      <c r="H230" s="48" t="n"/>
+      <c r="I230" s="48" t="n"/>
+      <c r="J230" s="48" t="n"/>
+      <c r="K230" s="48" t="n"/>
+      <c r="L230" s="48" t="n"/>
+      <c r="M230" s="48" t="n"/>
+      <c r="N230" s="48" t="n"/>
+      <c r="O230" s="48" t="n"/>
+      <c r="P230" s="48" t="n"/>
+      <c r="Q230" s="48" t="n"/>
+    </row>
+    <row r="231" ht="22" customHeight="1">
+      <c r="A231" s="37" t="inlineStr">
+        <is>
           <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
         </is>
       </c>
-      <c r="Q226" s="38">
-        <f>-Q221*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="227" ht="22" customHeight="1">
-      <c r="A227" s="45" t="inlineStr">
+      <c r="Q231" s="38">
+        <f>-Q226*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="232" ht="22" customHeight="1">
+      <c r="A232" s="45" t="inlineStr">
         <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="Q227" s="46">
-        <f>Q221+Q226</f>
-        <v/>
-      </c>
-    </row>
-    <row r="228" ht="22" customHeight="1">
-      <c r="A228" s="37" t="inlineStr">
+      <c r="Q232" s="46">
+        <f>Q226+Q231</f>
+        <v/>
+      </c>
+    </row>
+    <row r="233" ht="22" customHeight="1">
+      <c r="A233" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q228" s="38">
-        <f>Q227*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="229" ht="26" customHeight="1">
-      <c r="A229" s="39" t="inlineStr">
+      <c r="Q233" s="38">
+        <f>Q232*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234" ht="26" customHeight="1">
+      <c r="A234" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q229" s="40">
-        <f>Q227+Q228</f>
-        <v/>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" s="42" t="inlineStr">
+      <c r="Q234" s="40">
+        <f>Q232+Q233</f>
+        <v/>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="232">
-      <c r="A232" s="49" t="inlineStr">
+    <row r="237">
+      <c r="A237" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="233"/>
-    <row r="234"/>
-    <row r="235"/>
+    <row r="238"/>
+    <row r="239"/>
+    <row r="240"/>
   </sheetData>
-  <autoFilter ref="A7:Q211"/>
+  <autoFilter ref="A7:Q216"/>
   <mergeCells count="26">
-    <mergeCell ref="A220:Q220"/>
+    <mergeCell ref="A237:Q240"/>
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A215:P215"/>
+    <mergeCell ref="A234:P234"/>
+    <mergeCell ref="A219:P219"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A225:Q225"/>
+    <mergeCell ref="A231:P231"/>
     <mergeCell ref="L4:Q4"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A229:P229"/>
+    <mergeCell ref="A220:P220"/>
     <mergeCell ref="A218:Q218"/>
+    <mergeCell ref="A232:P232"/>
     <mergeCell ref="A226:P226"/>
-    <mergeCell ref="A216:P216"/>
     <mergeCell ref="A222:P222"/>
+    <mergeCell ref="A223:Q223"/>
     <mergeCell ref="C4:I4"/>
     <mergeCell ref="A228:P228"/>
-    <mergeCell ref="A213:Q213"/>
+    <mergeCell ref="A235:Q235"/>
+    <mergeCell ref="A227:P227"/>
     <mergeCell ref="A221:P221"/>
+    <mergeCell ref="L2:Q2"/>
     <mergeCell ref="A5:Q5"/>
-    <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A227:P227"/>
-    <mergeCell ref="A217:P217"/>
-    <mergeCell ref="A232:Q235"/>
-    <mergeCell ref="A223:P223"/>
-    <mergeCell ref="A214:P214"/>
+    <mergeCell ref="A233:P233"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
     <mergeCell ref="A230:Q230"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q211">
+  <conditionalFormatting sqref="A8:Q216">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N211" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N216" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O211" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O216" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$225</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5650,14 +5650,189 @@
       <row>215</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="210" name="Image 210" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId210"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>216</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="211" name="Image 211" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId211"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>217</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="212" name="Image 212" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId212"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>218</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="213" name="Image 213" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId213"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>220</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="210" name="Image 210" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId210"/>
+        <cNvPr id="214" name="Image 214" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId214"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>221</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="215" name="Image 215" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId215"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>222</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="216" name="Image 216" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId216"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>223</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="217" name="Image 217" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId217"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -5960,7 +6135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q240"/>
+  <dimension ref="A1:Q249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -17116,8 +17291,8 @@
       <c r="C190" s="11" t="n"/>
       <c r="D190" s="12" t="inlineStr">
         <is>
-          <t>Kinderschrank weiß mit Handabdrücken
-Hoher Schrank in Weiß mit Türen und Schubladen, Griffmulden. Auf den Fronten kleben Aufkleber mit Kinderhandabdrücken in Schwarz und Rot; sie lassen sich abziehen.</t>
+          <t>IKEA Kinderschrank weiß, zwei Türen
+Hoher Schrank von IKEA in Weiß mit zwei Türen und schwarzen Griffmulden, darunter Schubladen. Auf zwei der Schränke kleben Aufkleber mit Kinderhandabdrücken; sie lassen sich abziehen.</t>
         </is>
       </c>
       <c r="E190" s="13" t="n"/>
@@ -17132,7 +17307,7 @@
         </is>
       </c>
       <c r="H190" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I190" s="10" t="inlineStr">
         <is>
@@ -18440,8 +18615,8 @@
       <c r="C212" s="11" t="n"/>
       <c r="D212" s="12" t="inlineStr">
         <is>
-          <t>Stapelstuhl Kunststoff, weiß
-Stuhl aus weißem Kunststoff in einem Stück, runde Rückenlehne, konische Beine mit Querstrebe, stapelbar. Sitzfläche mit Kratzern.</t>
+          <t>Stapelstuhl Kunststoff weiß, Erwachsenengröße
+Stuhl aus weißem Kunststoff in einem Stück, runde Rückenlehne, konische Beine mit Querstrebe, stapelbar. Erwachsenengröße. Sitzfläche mit Kratzern.</t>
         </is>
       </c>
       <c r="E212" s="13" t="n"/>
@@ -18464,7 +18639,7 @@
         </is>
       </c>
       <c r="J212" s="14" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K212" s="15">
         <f>J212*1.19</f>
@@ -18674,20 +18849,20 @@
       </c>
       <c r="B216" s="10" t="inlineStr">
         <is>
-          <t>BA04-09</t>
+          <t>BA05-01</t>
         </is>
       </c>
       <c r="C216" s="11" t="n"/>
       <c r="D216" s="12" t="inlineStr">
         <is>
-          <t>Kinderschrank weiß, zwei Türen mit Schublade
-Hoher Schrank in Weiß mit zwei Türen und schwarzen Griffmulden, darunter eine Schublade.</t>
+          <t>Rollkasten mit großen Kunststoff-Bausteinen
+Flacher Kasten auf Rollen, Front in Weiß, Grün oder Grau, gefüllt mit großen Kunststoff-Bausteinen in Rot, Blau, Gelb und Grün.</t>
         </is>
       </c>
       <c r="E216" s="13" t="n"/>
       <c r="F216" s="12" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Turnraum</t>
         </is>
       </c>
       <c r="G216" s="10" t="inlineStr">
@@ -18696,7 +18871,7 @@
         </is>
       </c>
       <c r="H216" s="10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I216" s="10" t="inlineStr">
         <is>
@@ -18704,7 +18879,7 @@
         </is>
       </c>
       <c r="J216" s="14" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="K216" s="15">
         <f>J216*1.19</f>
@@ -18728,261 +18903,801 @@
         <v/>
       </c>
     </row>
-    <row r="218" ht="24" customHeight="1">
-      <c r="A218" s="36" t="inlineStr">
+    <row r="217" ht="78" customHeight="1">
+      <c r="A217" s="20" t="n">
+        <v>210</v>
+      </c>
+      <c r="B217" s="21" t="inlineStr">
+        <is>
+          <t>BA05-02</t>
+        </is>
+      </c>
+      <c r="C217" s="22" t="n"/>
+      <c r="D217" s="23" t="inlineStr">
+        <is>
+          <t>BENZ Turnbank
+Turnbank aus Holz mit Schmalseite zum Umdrehen, rutschhemmender Belag, Aufhängehaken an einem Ende. Aufdruck: BENZ Geräte.</t>
+        </is>
+      </c>
+      <c r="E217" s="13" t="n"/>
+      <c r="F217" s="23" t="inlineStr">
+        <is>
+          <t>Turnraum</t>
+        </is>
+      </c>
+      <c r="G217" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H217" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I217" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J217" s="24" t="n">
+        <v>140</v>
+      </c>
+      <c r="K217" s="25">
+        <f>J217*1.19</f>
+        <v/>
+      </c>
+      <c r="L217" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M217" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N217" s="16" t="n"/>
+      <c r="O217" s="17" t="n"/>
+      <c r="P217" s="18" t="n"/>
+      <c r="Q217" s="26">
+        <f>IF(N217&lt;&gt;"ja","",IF(O217="",H217,O217)*J217)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218" ht="78" customHeight="1">
+      <c r="A218" s="9" t="n">
+        <v>211</v>
+      </c>
+      <c r="B218" s="10" t="inlineStr">
+        <is>
+          <t>BA05-03</t>
+        </is>
+      </c>
+      <c r="C218" s="11" t="n"/>
+      <c r="D218" s="12" t="inlineStr">
+        <is>
+          <t>Trampolin mit Haltestange
+Rundes Fitness-Trampolin mit gepolstertem Randschutz in Rot und abnehmbarer Haltestange. Aufdruck auf dem Sprungtuch: ANCHEER. Der Randschutz ist an mehreren Stellen eingerissen.</t>
+        </is>
+      </c>
+      <c r="E218" s="13" t="n"/>
+      <c r="F218" s="12" t="inlineStr">
+        <is>
+          <t>Turnraum</t>
+        </is>
+      </c>
+      <c r="G218" s="10" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="H218" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I218" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J218" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K218" s="15">
+        <f>J218*1.19</f>
+        <v/>
+      </c>
+      <c r="L218" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M218" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N218" s="16" t="n"/>
+      <c r="O218" s="17" t="n"/>
+      <c r="P218" s="18" t="n"/>
+      <c r="Q218" s="19">
+        <f>IF(N218&lt;&gt;"ja","",IF(O218="",H218,O218)*J218)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219" ht="78" customHeight="1">
+      <c r="A219" s="20" t="n">
+        <v>212</v>
+      </c>
+      <c r="B219" s="35" t="inlineStr">
+        <is>
+          <t>BA05-04</t>
+        </is>
+      </c>
+      <c r="C219" s="22" t="n"/>
+      <c r="D219" s="23" t="inlineStr">
+        <is>
+          <t>Spielhochbett mit Bällebad und Rutsche
+Großes Spielhochbett aus weiß beschichteter Platte: zwei Liegeflächen oben mit Absturzsicherung, Leiter, Rutsche, runde Bullaugen und darunter ein eingebautes Bällebad einschließlich der Bälle.</t>
+        </is>
+      </c>
+      <c r="E219" s="13" t="n"/>
+      <c r="F219" s="23" t="inlineStr">
+        <is>
+          <t>Turnraum</t>
+        </is>
+      </c>
+      <c r="G219" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H219" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I219" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J219" s="24" t="n">
+        <v>750</v>
+      </c>
+      <c r="K219" s="25">
+        <f>J219*1.19</f>
+        <v/>
+      </c>
+      <c r="L219" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M219" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N219" s="16" t="n"/>
+      <c r="O219" s="17" t="n"/>
+      <c r="P219" s="18" t="n"/>
+      <c r="Q219" s="26">
+        <f>IF(N219&lt;&gt;"ja","",IF(O219="",H219,O219)*J219)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220" ht="78" customHeight="1">
+      <c r="A220" s="9" t="n">
+        <v>213</v>
+      </c>
+      <c r="B220" s="10" t="inlineStr">
+        <is>
+          <t>BA05-05</t>
+        </is>
+      </c>
+      <c r="C220" s="11" t="n"/>
+      <c r="D220" s="12" t="inlineStr">
+        <is>
+          <t>Sprossenwand einzeln
+Sprossenwand aus Massivholz zur Wandmontage, mit Querholmen über die volle Breite.</t>
+        </is>
+      </c>
+      <c r="E220" s="13" t="n"/>
+      <c r="F220" s="12" t="inlineStr">
+        <is>
+          <t>Turnraum</t>
+        </is>
+      </c>
+      <c r="G220" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H220" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I220" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J220" s="14" t="n">
+        <v>100</v>
+      </c>
+      <c r="K220" s="15">
+        <f>J220*1.19</f>
+        <v/>
+      </c>
+      <c r="L220" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M220" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N220" s="16" t="n"/>
+      <c r="O220" s="17" t="n"/>
+      <c r="P220" s="18" t="n"/>
+      <c r="Q220" s="19">
+        <f>IF(N220&lt;&gt;"ja","",IF(O220="",H220,O220)*J220)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221" ht="78" customHeight="1">
+      <c r="A221" s="20" t="n">
+        <v>214</v>
+      </c>
+      <c r="B221" s="35" t="inlineStr">
+        <is>
+          <t>BA05-06</t>
+        </is>
+      </c>
+      <c r="C221" s="22" t="n"/>
+      <c r="D221" s="23" t="inlineStr">
+        <is>
+          <t>Doppelsprossenwand
+Breite Sprossenwand aus Massivholz zur Wandmontage, zwei Felder nebeneinander mit durchgehenden Querholmen und oberer Ausleger-Leiste.</t>
+        </is>
+      </c>
+      <c r="E221" s="13" t="n"/>
+      <c r="F221" s="23" t="inlineStr">
+        <is>
+          <t>Turnraum</t>
+        </is>
+      </c>
+      <c r="G221" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H221" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I221" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J221" s="24" t="n">
+        <v>180</v>
+      </c>
+      <c r="K221" s="25">
+        <f>J221*1.19</f>
+        <v/>
+      </c>
+      <c r="L221" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M221" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N221" s="16" t="n"/>
+      <c r="O221" s="17" t="n"/>
+      <c r="P221" s="18" t="n"/>
+      <c r="Q221" s="26">
+        <f>IF(N221&lt;&gt;"ja","",IF(O221="",H221,O221)*J221)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222" ht="78" customHeight="1">
+      <c r="A222" s="9" t="n">
+        <v>215</v>
+      </c>
+      <c r="B222" s="10" t="inlineStr">
+        <is>
+          <t>BA05-07</t>
+        </is>
+      </c>
+      <c r="C222" s="11" t="n"/>
+      <c r="D222" s="12" t="inlineStr">
+        <is>
+          <t>Treppenturngerät gepolstert
+Turngerät aus Schaumstoff mit Kunstlederbezug in Creme und Grau: Treppenelement mit drei Stufen und passende Rampe, zusammensteckbar.</t>
+        </is>
+      </c>
+      <c r="E222" s="13" t="n"/>
+      <c r="F222" s="12" t="inlineStr">
+        <is>
+          <t>Turnraum</t>
+        </is>
+      </c>
+      <c r="G222" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H222" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I222" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J222" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="K222" s="15">
+        <f>J222*1.19</f>
+        <v/>
+      </c>
+      <c r="L222" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M222" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N222" s="16" t="n"/>
+      <c r="O222" s="17" t="n"/>
+      <c r="P222" s="18" t="n"/>
+      <c r="Q222" s="19">
+        <f>IF(N222&lt;&gt;"ja","",IF(O222="",H222,O222)*J222)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223" ht="78" customHeight="1">
+      <c r="A223" s="20" t="n">
+        <v>216</v>
+      </c>
+      <c r="B223" s="21" t="inlineStr">
+        <is>
+          <t>BA05-08</t>
+        </is>
+      </c>
+      <c r="C223" s="22" t="n"/>
+      <c r="D223" s="23" t="inlineStr">
+        <is>
+          <t>Rody Hüpfpferd rot
+Hüpfpferd Rody aus rotem Gummi mit gelbem Sattelaufdruck und weißen Punkten, aufblasbar. Markenaufdruck am Bauch.</t>
+        </is>
+      </c>
+      <c r="E223" s="13" t="n"/>
+      <c r="F223" s="23" t="inlineStr">
+        <is>
+          <t>Turnraum</t>
+        </is>
+      </c>
+      <c r="G223" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H223" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I223" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J223" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="K223" s="25">
+        <f>J223*1.19</f>
+        <v/>
+      </c>
+      <c r="L223" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M223" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N223" s="16" t="n"/>
+      <c r="O223" s="17" t="n"/>
+      <c r="P223" s="18" t="n"/>
+      <c r="Q223" s="26">
+        <f>IF(N223&lt;&gt;"ja","",IF(O223="",H223,O223)*J223)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="224" ht="78" customHeight="1">
+      <c r="A224" s="9" t="n">
+        <v>217</v>
+      </c>
+      <c r="B224" s="10" t="inlineStr">
+        <is>
+          <t>BA05-09</t>
+        </is>
+      </c>
+      <c r="C224" s="11" t="n"/>
+      <c r="D224" s="12" t="inlineStr">
+        <is>
+          <t>Softbausteine gepolstert, groß
+Große Turn- und Bauelemente aus Schaumstoff mit Kunstlederbezug in Rot, Blau, Grün und Hellgrün: Treppen, Rampen, Wellen, Quader und Keile.</t>
+        </is>
+      </c>
+      <c r="E224" s="13" t="n"/>
+      <c r="F224" s="12" t="inlineStr">
+        <is>
+          <t>Turnraum</t>
+        </is>
+      </c>
+      <c r="G224" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H224" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="I224" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J224" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="K224" s="15">
+        <f>J224*1.19</f>
+        <v/>
+      </c>
+      <c r="L224" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M224" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N224" s="16" t="n"/>
+      <c r="O224" s="17" t="n"/>
+      <c r="P224" s="18" t="n"/>
+      <c r="Q224" s="19">
+        <f>IF(N224&lt;&gt;"ja","",IF(O224="",H224,O224)*J224)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="225" ht="78" customHeight="1">
+      <c r="A225" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="B225" s="21" t="inlineStr">
+        <is>
+          <t>BA05-10</t>
+        </is>
+      </c>
+      <c r="C225" s="22" t="n"/>
+      <c r="D225" s="23" t="inlineStr">
+        <is>
+          <t>Wandschutz grün, gepolstert
+Gepolsterter Wand- und Säulenschutz mit grünem Kunstlederbezug und grauer Oberseite.</t>
+        </is>
+      </c>
+      <c r="E225" s="13" t="n"/>
+      <c r="F225" s="23" t="inlineStr">
+        <is>
+          <t>Turnraum</t>
+        </is>
+      </c>
+      <c r="G225" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H225" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I225" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J225" s="24" t="n">
+        <v>35</v>
+      </c>
+      <c r="K225" s="25">
+        <f>J225*1.19</f>
+        <v/>
+      </c>
+      <c r="L225" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M225" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N225" s="16" t="n"/>
+      <c r="O225" s="17" t="n"/>
+      <c r="P225" s="18" t="n"/>
+      <c r="Q225" s="26">
+        <f>IF(N225&lt;&gt;"ja","",IF(O225="",H225,O225)*J225)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227" ht="24" customHeight="1">
+      <c r="A227" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B218" s="1" t="n"/>
-      <c r="C218" s="1" t="n"/>
-      <c r="D218" s="1" t="n"/>
-      <c r="E218" s="1" t="n"/>
-      <c r="F218" s="1" t="n"/>
-      <c r="G218" s="1" t="n"/>
-      <c r="H218" s="1" t="n"/>
-      <c r="I218" s="1" t="n"/>
-      <c r="J218" s="1" t="n"/>
-      <c r="K218" s="1" t="n"/>
-      <c r="L218" s="1" t="n"/>
-      <c r="M218" s="1" t="n"/>
-      <c r="N218" s="1" t="n"/>
-      <c r="O218" s="1" t="n"/>
-      <c r="P218" s="1" t="n"/>
-      <c r="Q218" s="1" t="n"/>
-    </row>
-    <row r="219" ht="22" customHeight="1">
-      <c r="A219" s="37" t="inlineStr">
+      <c r="B227" s="1" t="n"/>
+      <c r="C227" s="1" t="n"/>
+      <c r="D227" s="1" t="n"/>
+      <c r="E227" s="1" t="n"/>
+      <c r="F227" s="1" t="n"/>
+      <c r="G227" s="1" t="n"/>
+      <c r="H227" s="1" t="n"/>
+      <c r="I227" s="1" t="n"/>
+      <c r="J227" s="1" t="n"/>
+      <c r="K227" s="1" t="n"/>
+      <c r="L227" s="1" t="n"/>
+      <c r="M227" s="1" t="n"/>
+      <c r="N227" s="1" t="n"/>
+      <c r="O227" s="1" t="n"/>
+      <c r="P227" s="1" t="n"/>
+      <c r="Q227" s="1" t="n"/>
+    </row>
+    <row r="228" ht="22" customHeight="1">
+      <c r="A228" s="37" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl netto</t>
         </is>
       </c>
-      <c r="Q219" s="38">
-        <f>SUM(Q8:Q216)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="220" ht="22" customHeight="1">
-      <c r="A220" s="37" t="inlineStr">
+      <c r="Q228" s="38">
+        <f>SUM(Q8:Q225)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="229" ht="22" customHeight="1">
+      <c r="A229" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q220" s="38">
-        <f>Q219*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="221" ht="26" customHeight="1">
-      <c r="A221" s="39" t="inlineStr">
+      <c r="Q229" s="38">
+        <f>Q228*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230" ht="26" customHeight="1">
+      <c r="A230" s="39" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl brutto</t>
         </is>
       </c>
-      <c r="Q221" s="40">
-        <f>Q219+Q220</f>
-        <v/>
-      </c>
-    </row>
-    <row r="222" ht="22" customHeight="1">
-      <c r="A222" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q222" s="41">
-        <f>COUNTIF(N8:N216,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="225" ht="24" customHeight="1">
-      <c r="A225" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B225" s="44" t="n"/>
-      <c r="C225" s="44" t="n"/>
-      <c r="D225" s="44" t="n"/>
-      <c r="E225" s="44" t="n"/>
-      <c r="F225" s="44" t="n"/>
-      <c r="G225" s="44" t="n"/>
-      <c r="H225" s="44" t="n"/>
-      <c r="I225" s="44" t="n"/>
-      <c r="J225" s="44" t="n"/>
-      <c r="K225" s="44" t="n"/>
-      <c r="L225" s="44" t="n"/>
-      <c r="M225" s="44" t="n"/>
-      <c r="N225" s="44" t="n"/>
-      <c r="O225" s="44" t="n"/>
-      <c r="P225" s="44" t="n"/>
-      <c r="Q225" s="44" t="n"/>
-    </row>
-    <row r="226" ht="22" customHeight="1">
-      <c r="A226" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
-        </is>
-      </c>
-      <c r="Q226" s="38">
-        <f>SUMPRODUCT(H8:H216,J8:J216)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="227" ht="22" customHeight="1">
-      <c r="A227" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q227" s="38">
-        <f>Q226*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="228" ht="22" customHeight="1">
-      <c r="A228" s="45" t="inlineStr">
-        <is>
-          <t>Gesamtwert brutto</t>
-        </is>
-      </c>
-      <c r="Q228" s="46">
-        <f>Q226+Q227</f>
-        <v/>
-      </c>
-    </row>
-    <row r="230" ht="24" customHeight="1">
-      <c r="A230" s="47" t="inlineStr">
-        <is>
-          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B230" s="48" t="n"/>
-      <c r="C230" s="48" t="n"/>
-      <c r="D230" s="48" t="n"/>
-      <c r="E230" s="48" t="n"/>
-      <c r="F230" s="48" t="n"/>
-      <c r="G230" s="48" t="n"/>
-      <c r="H230" s="48" t="n"/>
-      <c r="I230" s="48" t="n"/>
-      <c r="J230" s="48" t="n"/>
-      <c r="K230" s="48" t="n"/>
-      <c r="L230" s="48" t="n"/>
-      <c r="M230" s="48" t="n"/>
-      <c r="N230" s="48" t="n"/>
-      <c r="O230" s="48" t="n"/>
-      <c r="P230" s="48" t="n"/>
-      <c r="Q230" s="48" t="n"/>
+      <c r="Q230" s="40">
+        <f>Q228+Q229</f>
+        <v/>
+      </c>
     </row>
     <row r="231" ht="22" customHeight="1">
       <c r="A231" s="37" t="inlineStr">
         <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q231" s="41">
+        <f>COUNTIF(N8:N225,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="24" customHeight="1">
+      <c r="A234" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B234" s="44" t="n"/>
+      <c r="C234" s="44" t="n"/>
+      <c r="D234" s="44" t="n"/>
+      <c r="E234" s="44" t="n"/>
+      <c r="F234" s="44" t="n"/>
+      <c r="G234" s="44" t="n"/>
+      <c r="H234" s="44" t="n"/>
+      <c r="I234" s="44" t="n"/>
+      <c r="J234" s="44" t="n"/>
+      <c r="K234" s="44" t="n"/>
+      <c r="L234" s="44" t="n"/>
+      <c r="M234" s="44" t="n"/>
+      <c r="N234" s="44" t="n"/>
+      <c r="O234" s="44" t="n"/>
+      <c r="P234" s="44" t="n"/>
+      <c r="Q234" s="44" t="n"/>
+    </row>
+    <row r="235" ht="22" customHeight="1">
+      <c r="A235" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q235" s="38">
+        <f>SUMPRODUCT(H8:H225,J8:J225)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="236" ht="22" customHeight="1">
+      <c r="A236" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q236" s="38">
+        <f>Q235*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="237" ht="22" customHeight="1">
+      <c r="A237" s="45" t="inlineStr">
+        <is>
+          <t>Gesamtwert brutto</t>
+        </is>
+      </c>
+      <c r="Q237" s="46">
+        <f>Q235+Q236</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239" ht="24" customHeight="1">
+      <c r="A239" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B239" s="48" t="n"/>
+      <c r="C239" s="48" t="n"/>
+      <c r="D239" s="48" t="n"/>
+      <c r="E239" s="48" t="n"/>
+      <c r="F239" s="48" t="n"/>
+      <c r="G239" s="48" t="n"/>
+      <c r="H239" s="48" t="n"/>
+      <c r="I239" s="48" t="n"/>
+      <c r="J239" s="48" t="n"/>
+      <c r="K239" s="48" t="n"/>
+      <c r="L239" s="48" t="n"/>
+      <c r="M239" s="48" t="n"/>
+      <c r="N239" s="48" t="n"/>
+      <c r="O239" s="48" t="n"/>
+      <c r="P239" s="48" t="n"/>
+      <c r="Q239" s="48" t="n"/>
+    </row>
+    <row r="240" ht="22" customHeight="1">
+      <c r="A240" s="37" t="inlineStr">
+        <is>
           <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
         </is>
       </c>
-      <c r="Q231" s="38">
-        <f>-Q226*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="232" ht="22" customHeight="1">
-      <c r="A232" s="45" t="inlineStr">
+      <c r="Q240" s="38">
+        <f>-Q235*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241" ht="22" customHeight="1">
+      <c r="A241" s="45" t="inlineStr">
         <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="Q232" s="46">
-        <f>Q226+Q231</f>
-        <v/>
-      </c>
-    </row>
-    <row r="233" ht="22" customHeight="1">
-      <c r="A233" s="37" t="inlineStr">
+      <c r="Q241" s="46">
+        <f>Q235+Q240</f>
+        <v/>
+      </c>
+    </row>
+    <row r="242" ht="22" customHeight="1">
+      <c r="A242" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q233" s="38">
-        <f>Q232*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="234" ht="26" customHeight="1">
-      <c r="A234" s="39" t="inlineStr">
+      <c r="Q242" s="38">
+        <f>Q241*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243" ht="26" customHeight="1">
+      <c r="A243" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q234" s="40">
-        <f>Q232+Q233</f>
-        <v/>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" s="42" t="inlineStr">
+      <c r="Q243" s="40">
+        <f>Q241+Q242</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="49" t="inlineStr">
+    <row r="246">
+      <c r="A246" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
+    <row r="247"/>
+    <row r="248"/>
+    <row r="249"/>
   </sheetData>
-  <autoFilter ref="A7:Q216"/>
+  <autoFilter ref="A7:Q225"/>
   <mergeCells count="26">
-    <mergeCell ref="A237:Q240"/>
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A234:P234"/>
-    <mergeCell ref="A219:P219"/>
+    <mergeCell ref="A246:Q249"/>
+    <mergeCell ref="A232:Q232"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A225:Q225"/>
+    <mergeCell ref="A240:P240"/>
     <mergeCell ref="A231:P231"/>
     <mergeCell ref="L4:Q4"/>
+    <mergeCell ref="A230:P230"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A220:P220"/>
-    <mergeCell ref="A218:Q218"/>
-    <mergeCell ref="A232:P232"/>
-    <mergeCell ref="A226:P226"/>
-    <mergeCell ref="A222:P222"/>
-    <mergeCell ref="A223:Q223"/>
+    <mergeCell ref="A229:P229"/>
+    <mergeCell ref="A227:Q227"/>
+    <mergeCell ref="A241:P241"/>
+    <mergeCell ref="A239:Q239"/>
     <mergeCell ref="C4:I4"/>
+    <mergeCell ref="A237:P237"/>
     <mergeCell ref="A228:P228"/>
-    <mergeCell ref="A235:Q235"/>
-    <mergeCell ref="A227:P227"/>
-    <mergeCell ref="A221:P221"/>
+    <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A5:Q5"/>
-    <mergeCell ref="A233:P233"/>
+    <mergeCell ref="A243:P243"/>
+    <mergeCell ref="A234:Q234"/>
+    <mergeCell ref="A244:Q244"/>
+    <mergeCell ref="A236:P236"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A230:Q230"/>
+    <mergeCell ref="A235:P235"/>
+    <mergeCell ref="A242:P242"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q216">
+  <conditionalFormatting sqref="A8:Q225">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N216" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N225" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O216" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O225" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -5747,17 +5747,42 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
+      <row>219</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="214" name="Image 214" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId214"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
       <row>220</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="214" name="Image 214" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId214"/>
+        <cNvPr id="215" name="Image 215" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId215"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -5778,11 +5803,11 @@
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="215" name="Image 215" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId215"/>
+        <cNvPr id="216" name="Image 216" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId216"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -5803,11 +5828,11 @@
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="216" name="Image 216" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId216"/>
+        <cNvPr id="217" name="Image 217" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId217"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -5828,11 +5853,36 @@
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="217" name="Image 217" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId217"/>
+        <cNvPr id="218" name="Image 218" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId218"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>224</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="219" name="Image 219" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId219"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -19096,7 +19146,7 @@
       <c r="D220" s="12" t="inlineStr">
         <is>
           <t>Sprossenwand einzeln
-Sprossenwand aus Massivholz zur Wandmontage, mit Querholmen über die volle Breite.</t>
+Sprossenwand aus Massivholz zur Wandmontage: zwei kräftige Holme mit durchgehenden Rundsprossen, oben eine ausladende Aufhängeleiste.</t>
         </is>
       </c>
       <c r="E220" s="13" t="n"/>
@@ -19395,8 +19445,8 @@
       <c r="C225" s="22" t="n"/>
       <c r="D225" s="23" t="inlineStr">
         <is>
-          <t>Wandschutz grün, gepolstert
-Gepolsterter Wand- und Säulenschutz mit grünem Kunstlederbezug und grauer Oberseite.</t>
+          <t>Polstersäule grün, Raumteiler
+Standsäule aus Schaumstoff mit Kunstlederbezug: Mantel in Limettengrün, Oberseiten in Grau, mehrere Lappen ergeben im Querschnitt eine Blütenform. Als Wand- und Säulenschutz oder als Raumteiler nutzbar.</t>
         </is>
       </c>
       <c r="E225" s="13" t="n"/>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$225</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$236</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5893,6 +5893,231 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>225</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="220" name="Image 220" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId220"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>226</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="221" name="Image 221" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId221"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>227</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="222" name="Image 222" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId222"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>228</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="223" name="Image 223" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId223"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>229</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="224" name="Image 224" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId224"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>230</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="225" name="Image 225" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId225"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>231</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="226" name="Image 226" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId226"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>233</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="227" name="Image 227" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId227"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>234</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="228" name="Image 228" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId228"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -6185,7 +6410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q249"/>
+  <dimension ref="A1:Q260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -14417,7 +14642,7 @@
         </is>
       </c>
       <c r="H141" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I141" s="21" t="inlineStr">
         <is>
@@ -19325,8 +19550,8 @@
       <c r="C223" s="22" t="n"/>
       <c r="D223" s="23" t="inlineStr">
         <is>
-          <t>Rody Hüpfpferd rot
-Hüpfpferd Rody aus rotem Gummi mit gelbem Sattelaufdruck und weißen Punkten, aufblasbar. Markenaufdruck am Bauch.</t>
+          <t>Rody Hüpfpferd, rot und grün
+Hüpfpferd Rody aus Gummi mit weißen Punkten, aufblasbar. Markenaufdruck am Bauch. Eines in Rot mit gelbem Sattel, zwei in Grün mit blauem Sattel.</t>
         </is>
       </c>
       <c r="E223" s="13" t="n"/>
@@ -19341,7 +19566,7 @@
         </is>
       </c>
       <c r="H223" s="21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I223" s="21" t="inlineStr">
         <is>
@@ -19493,261 +19718,921 @@
         <v/>
       </c>
     </row>
-    <row r="227" ht="24" customHeight="1">
-      <c r="A227" s="36" t="inlineStr">
+    <row r="226" ht="78" customHeight="1">
+      <c r="A226" s="9" t="n">
+        <v>219</v>
+      </c>
+      <c r="B226" s="10" t="inlineStr">
+        <is>
+          <t>BA06-02</t>
+        </is>
+      </c>
+      <c r="C226" s="11" t="n"/>
+      <c r="D226" s="12" t="inlineStr">
+        <is>
+          <t>BMW Baby Racer Rutscherauto
+Rutscherauto in Sportwagenform, Karosserie blau mit rotem Sitz, Lenkrad mit Hupe, verchromte Felgen. BMW-Emblem an der Front. Lack stark zerkratzt.</t>
+        </is>
+      </c>
+      <c r="E226" s="13" t="n"/>
+      <c r="F226" s="12" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="G226" s="10" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="H226" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I226" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J226" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="K226" s="15">
+        <f>J226*1.19</f>
+        <v/>
+      </c>
+      <c r="L226" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M226" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N226" s="16" t="n"/>
+      <c r="O226" s="17" t="n"/>
+      <c r="P226" s="18" t="n"/>
+      <c r="Q226" s="19">
+        <f>IF(N226&lt;&gt;"ja","",IF(O226="",H226,O226)*J226)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227" ht="78" customHeight="1">
+      <c r="A227" s="20" t="n">
+        <v>220</v>
+      </c>
+      <c r="B227" s="21" t="inlineStr">
+        <is>
+          <t>BA06-03</t>
+        </is>
+      </c>
+      <c r="C227" s="22" t="n"/>
+      <c r="D227" s="23" t="inlineStr">
+        <is>
+          <t>BIG Bobby Quad
+Quad-Rutscherfahrzeug aus Kunststoff in Schwarz mit limettengrünen Felgen und Lenkergriffen, Stollenreifen. Aufdruck: bobby quad, BIG.</t>
+        </is>
+      </c>
+      <c r="E227" s="13" t="n"/>
+      <c r="F227" s="23" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="G227" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H227" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I227" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J227" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="K227" s="25">
+        <f>J227*1.19</f>
+        <v/>
+      </c>
+      <c r="L227" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M227" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N227" s="16" t="n"/>
+      <c r="O227" s="17" t="n"/>
+      <c r="P227" s="18" t="n"/>
+      <c r="Q227" s="26">
+        <f>IF(N227&lt;&gt;"ja","",IF(O227="",H227,O227)*J227)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228" ht="78" customHeight="1">
+      <c r="A228" s="9" t="n">
+        <v>221</v>
+      </c>
+      <c r="B228" s="10" t="inlineStr">
+        <is>
+          <t>BA06-04</t>
+        </is>
+      </c>
+      <c r="C228" s="11" t="n"/>
+      <c r="D228" s="12" t="inlineStr">
+        <is>
+          <t>Holz-Dreirad mit Kuhkopf
+Rutschfahrzeug aus Massivholz mit vier Rädern, ovalem Sitz und Lehne, vorn ein Kuhkopf mit Stoffohren und gemaltem Gesicht.</t>
+        </is>
+      </c>
+      <c r="E228" s="13" t="n"/>
+      <c r="F228" s="12" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="G228" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H228" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I228" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J228" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K228" s="15">
+        <f>J228*1.19</f>
+        <v/>
+      </c>
+      <c r="L228" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M228" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N228" s="16" t="n"/>
+      <c r="O228" s="17" t="n"/>
+      <c r="P228" s="18" t="n"/>
+      <c r="Q228" s="19">
+        <f>IF(N228&lt;&gt;"ja","",IF(O228="",H228,O228)*J228)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="229" ht="78" customHeight="1">
+      <c r="A229" s="20" t="n">
+        <v>222</v>
+      </c>
+      <c r="B229" s="21" t="inlineStr">
+        <is>
+          <t>BA06-05</t>
+        </is>
+      </c>
+      <c r="C229" s="22" t="n"/>
+      <c r="D229" s="23" t="inlineStr">
+        <is>
+          <t>Schaukel- und Rutschtier aus Formholz
+Fahrzeug aus weiß lackiertem Formholz mit Naturholz-Lehne, vier kleinen Rollen und schwarzen Griffen. Lack an vielen Stellen abgeplatzt.</t>
+        </is>
+      </c>
+      <c r="E229" s="13" t="n"/>
+      <c r="F229" s="23" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="G229" s="21" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="H229" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I229" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J229" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="K229" s="25">
+        <f>J229*1.19</f>
+        <v/>
+      </c>
+      <c r="L229" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M229" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N229" s="16" t="n"/>
+      <c r="O229" s="17" t="n"/>
+      <c r="P229" s="18" t="n"/>
+      <c r="Q229" s="26">
+        <f>IF(N229&lt;&gt;"ja","",IF(O229="",H229,O229)*J229)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230" ht="78" customHeight="1">
+      <c r="A230" s="9" t="n">
+        <v>223</v>
+      </c>
+      <c r="B230" s="10" t="inlineStr">
+        <is>
+          <t>BA06-06</t>
+        </is>
+      </c>
+      <c r="C230" s="11" t="n"/>
+      <c r="D230" s="12" t="inlineStr">
+        <is>
+          <t>BIG Bobby Car Feuerwehr
+Rutscherauto als Feuerwehrfahrzeug aus rotem Kunststoff mit Blaulicht, drehbarem Wasserwerfer und Stollenreifen. Aufdruck: BIG.</t>
+        </is>
+      </c>
+      <c r="E230" s="13" t="n"/>
+      <c r="F230" s="12" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="G230" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H230" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I230" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J230" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="K230" s="15">
+        <f>J230*1.19</f>
+        <v/>
+      </c>
+      <c r="L230" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M230" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N230" s="16" t="n"/>
+      <c r="O230" s="17" t="n"/>
+      <c r="P230" s="18" t="n"/>
+      <c r="Q230" s="19">
+        <f>IF(N230&lt;&gt;"ja","",IF(O230="",H230,O230)*J230)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231" ht="78" customHeight="1">
+      <c r="A231" s="20" t="n">
+        <v>224</v>
+      </c>
+      <c r="B231" s="21" t="inlineStr">
+        <is>
+          <t>BA06-07</t>
+        </is>
+      </c>
+      <c r="C231" s="22" t="n"/>
+      <c r="D231" s="23" t="inlineStr">
+        <is>
+          <t>Klettergerüst Holz
+Klettergerüst aus Buche massiv mit Rundsprossen und seitlichen Wangen, zusammenklappbar.</t>
+        </is>
+      </c>
+      <c r="E231" s="13" t="n"/>
+      <c r="F231" s="23" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="G231" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H231" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I231" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J231" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="K231" s="25">
+        <f>J231*1.19</f>
+        <v/>
+      </c>
+      <c r="L231" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M231" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N231" s="16" t="n"/>
+      <c r="O231" s="17" t="n"/>
+      <c r="P231" s="18" t="n"/>
+      <c r="Q231" s="26">
+        <f>IF(N231&lt;&gt;"ja","",IF(O231="",H231,O231)*J231)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="232" ht="78" customHeight="1">
+      <c r="A232" s="9" t="n">
+        <v>225</v>
+      </c>
+      <c r="B232" s="10" t="inlineStr">
+        <is>
+          <t>BA06-08</t>
+        </is>
+      </c>
+      <c r="C232" s="11" t="n"/>
+      <c r="D232" s="12" t="inlineStr">
+        <is>
+          <t>Klettergerüst grün mit Rutschbrett
+Klettergerüst mit grün lackiertem Metallrahmen, Rundsprossen aus Holz und einem Rutschbrett mit dunkler Lauffläche.</t>
+        </is>
+      </c>
+      <c r="E232" s="13" t="n"/>
+      <c r="F232" s="12" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="G232" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H232" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I232" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J232" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="K232" s="15">
+        <f>J232*1.19</f>
+        <v/>
+      </c>
+      <c r="L232" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M232" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N232" s="16" t="n"/>
+      <c r="O232" s="17" t="n"/>
+      <c r="P232" s="18" t="n"/>
+      <c r="Q232" s="19">
+        <f>IF(N232&lt;&gt;"ja","",IF(O232="",H232,O232)*J232)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="233" ht="78" customHeight="1">
+      <c r="A233" s="20" t="n">
+        <v>226</v>
+      </c>
+      <c r="B233" s="21" t="inlineStr">
+        <is>
+          <t>BA06-09</t>
+        </is>
+      </c>
+      <c r="C233" s="22" t="n"/>
+      <c r="D233" s="23" t="inlineStr">
+        <is>
+          <t>Holz-Lastwagen zum Rutschen
+Rutschfahrzeug aus Massivholz in Lastwagenform mit offener Ladefläche, Holzlenkrad und roten Rädern.</t>
+        </is>
+      </c>
+      <c r="E233" s="13" t="n"/>
+      <c r="F233" s="23" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="G233" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H233" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I233" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J233" s="24" t="n">
+        <v>40</v>
+      </c>
+      <c r="K233" s="25">
+        <f>J233*1.19</f>
+        <v/>
+      </c>
+      <c r="L233" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M233" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N233" s="16" t="n"/>
+      <c r="O233" s="17" t="n"/>
+      <c r="P233" s="18" t="n"/>
+      <c r="Q233" s="26">
+        <f>IF(N233&lt;&gt;"ja","",IF(O233="",H233,O233)*J233)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234" ht="78" customHeight="1">
+      <c r="A234" s="9" t="n">
+        <v>227</v>
+      </c>
+      <c r="B234" s="10" t="inlineStr">
+        <is>
+          <t>BA06-10</t>
+        </is>
+      </c>
+      <c r="C234" s="11" t="n"/>
+      <c r="D234" s="12" t="inlineStr">
+        <is>
+          <t>Feuerwehrhaus aus Holz
+Spiel-Feuerwehrhaus aus Holz mit rot lackierten Wänden, dunklem Dach, aufklappbarem Tor und Zwischenboden. Aufdruck: FIRE STATION. Farbe stark abgegriffen.</t>
+        </is>
+      </c>
+      <c r="E234" s="13" t="n"/>
+      <c r="F234" s="12" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="G234" s="10" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="H234" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I234" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J234" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="K234" s="15">
+        <f>J234*1.19</f>
+        <v/>
+      </c>
+      <c r="L234" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M234" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N234" s="16" t="n"/>
+      <c r="O234" s="17" t="n"/>
+      <c r="P234" s="18" t="n"/>
+      <c r="Q234" s="19">
+        <f>IF(N234&lt;&gt;"ja","",IF(O234="",H234,O234)*J234)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="235" ht="78" customHeight="1">
+      <c r="A235" s="20" t="n">
+        <v>228</v>
+      </c>
+      <c r="B235" s="21" t="inlineStr">
+        <is>
+          <t>BA06-11</t>
+        </is>
+      </c>
+      <c r="C235" s="22" t="n"/>
+      <c r="D235" s="23" t="inlineStr">
+        <is>
+          <t>Sitzschaukel Kunststoff mit Seilen
+Babyschaukel aus Kunststoff: Sitzschale in Violett mit limettengrünem Sicherheitsbügel, Aufhängung über weiße Seile.</t>
+        </is>
+      </c>
+      <c r="E235" s="13" t="n"/>
+      <c r="F235" s="23" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="G235" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H235" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I235" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J235" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="K235" s="25">
+        <f>J235*1.19</f>
+        <v/>
+      </c>
+      <c r="L235" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M235" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N235" s="16" t="n"/>
+      <c r="O235" s="17" t="n"/>
+      <c r="P235" s="18" t="n"/>
+      <c r="Q235" s="26">
+        <f>IF(N235&lt;&gt;"ja","",IF(O235="",H235,O235)*J235)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="236" ht="78" customHeight="1">
+      <c r="A236" s="9" t="n">
+        <v>229</v>
+      </c>
+      <c r="B236" s="10" t="inlineStr">
+        <is>
+          <t>BA06-12</t>
+        </is>
+      </c>
+      <c r="C236" s="11" t="n"/>
+      <c r="D236" s="12" t="inlineStr">
+        <is>
+          <t>Spieltunnel grün
+Spieltunnel aus grünem Stoff mit roten Ringen, etwa 180 cm lang und 45 cm Durchmesser, zusammenfaltbar, mit Originalkarton.</t>
+        </is>
+      </c>
+      <c r="E236" s="13" t="n"/>
+      <c r="F236" s="12" t="inlineStr">
+        <is>
+          <t>Material / Turnraum</t>
+        </is>
+      </c>
+      <c r="G236" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H236" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I236" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J236" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="K236" s="15">
+        <f>J236*1.19</f>
+        <v/>
+      </c>
+      <c r="L236" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M236" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N236" s="16" t="n"/>
+      <c r="O236" s="17" t="n"/>
+      <c r="P236" s="18" t="n"/>
+      <c r="Q236" s="19">
+        <f>IF(N236&lt;&gt;"ja","",IF(O236="",H236,O236)*J236)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238" ht="24" customHeight="1">
+      <c r="A238" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B227" s="1" t="n"/>
-      <c r="C227" s="1" t="n"/>
-      <c r="D227" s="1" t="n"/>
-      <c r="E227" s="1" t="n"/>
-      <c r="F227" s="1" t="n"/>
-      <c r="G227" s="1" t="n"/>
-      <c r="H227" s="1" t="n"/>
-      <c r="I227" s="1" t="n"/>
-      <c r="J227" s="1" t="n"/>
-      <c r="K227" s="1" t="n"/>
-      <c r="L227" s="1" t="n"/>
-      <c r="M227" s="1" t="n"/>
-      <c r="N227" s="1" t="n"/>
-      <c r="O227" s="1" t="n"/>
-      <c r="P227" s="1" t="n"/>
-      <c r="Q227" s="1" t="n"/>
-    </row>
-    <row r="228" ht="22" customHeight="1">
-      <c r="A228" s="37" t="inlineStr">
+      <c r="B238" s="1" t="n"/>
+      <c r="C238" s="1" t="n"/>
+      <c r="D238" s="1" t="n"/>
+      <c r="E238" s="1" t="n"/>
+      <c r="F238" s="1" t="n"/>
+      <c r="G238" s="1" t="n"/>
+      <c r="H238" s="1" t="n"/>
+      <c r="I238" s="1" t="n"/>
+      <c r="J238" s="1" t="n"/>
+      <c r="K238" s="1" t="n"/>
+      <c r="L238" s="1" t="n"/>
+      <c r="M238" s="1" t="n"/>
+      <c r="N238" s="1" t="n"/>
+      <c r="O238" s="1" t="n"/>
+      <c r="P238" s="1" t="n"/>
+      <c r="Q238" s="1" t="n"/>
+    </row>
+    <row r="239" ht="22" customHeight="1">
+      <c r="A239" s="37" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl netto</t>
         </is>
       </c>
-      <c r="Q228" s="38">
-        <f>SUM(Q8:Q225)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="229" ht="22" customHeight="1">
-      <c r="A229" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q229" s="38">
-        <f>Q228*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="230" ht="26" customHeight="1">
-      <c r="A230" s="39" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl brutto</t>
-        </is>
-      </c>
-      <c r="Q230" s="40">
-        <f>Q228+Q229</f>
-        <v/>
-      </c>
-    </row>
-    <row r="231" ht="22" customHeight="1">
-      <c r="A231" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q231" s="41">
-        <f>COUNTIF(N8:N225,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="234" ht="24" customHeight="1">
-      <c r="A234" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B234" s="44" t="n"/>
-      <c r="C234" s="44" t="n"/>
-      <c r="D234" s="44" t="n"/>
-      <c r="E234" s="44" t="n"/>
-      <c r="F234" s="44" t="n"/>
-      <c r="G234" s="44" t="n"/>
-      <c r="H234" s="44" t="n"/>
-      <c r="I234" s="44" t="n"/>
-      <c r="J234" s="44" t="n"/>
-      <c r="K234" s="44" t="n"/>
-      <c r="L234" s="44" t="n"/>
-      <c r="M234" s="44" t="n"/>
-      <c r="N234" s="44" t="n"/>
-      <c r="O234" s="44" t="n"/>
-      <c r="P234" s="44" t="n"/>
-      <c r="Q234" s="44" t="n"/>
-    </row>
-    <row r="235" ht="22" customHeight="1">
-      <c r="A235" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
-        </is>
-      </c>
-      <c r="Q235" s="38">
-        <f>SUMPRODUCT(H8:H225,J8:J225)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="236" ht="22" customHeight="1">
-      <c r="A236" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q236" s="38">
-        <f>Q235*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="237" ht="22" customHeight="1">
-      <c r="A237" s="45" t="inlineStr">
-        <is>
-          <t>Gesamtwert brutto</t>
-        </is>
-      </c>
-      <c r="Q237" s="46">
-        <f>Q235+Q236</f>
-        <v/>
-      </c>
-    </row>
-    <row r="239" ht="24" customHeight="1">
-      <c r="A239" s="47" t="inlineStr">
-        <is>
-          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B239" s="48" t="n"/>
-      <c r="C239" s="48" t="n"/>
-      <c r="D239" s="48" t="n"/>
-      <c r="E239" s="48" t="n"/>
-      <c r="F239" s="48" t="n"/>
-      <c r="G239" s="48" t="n"/>
-      <c r="H239" s="48" t="n"/>
-      <c r="I239" s="48" t="n"/>
-      <c r="J239" s="48" t="n"/>
-      <c r="K239" s="48" t="n"/>
-      <c r="L239" s="48" t="n"/>
-      <c r="M239" s="48" t="n"/>
-      <c r="N239" s="48" t="n"/>
-      <c r="O239" s="48" t="n"/>
-      <c r="P239" s="48" t="n"/>
-      <c r="Q239" s="48" t="n"/>
+      <c r="Q239" s="38">
+        <f>SUM(Q8:Q236)</f>
+        <v/>
+      </c>
     </row>
     <row r="240" ht="22" customHeight="1">
       <c r="A240" s="37" t="inlineStr">
         <is>
-          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
+          <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
       <c r="Q240" s="38">
-        <f>-Q235*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="241" ht="22" customHeight="1">
-      <c r="A241" s="45" t="inlineStr">
-        <is>
-          <t>Paketpreis netto</t>
-        </is>
-      </c>
-      <c r="Q241" s="46">
-        <f>Q235+Q240</f>
+        <f>Q239*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241" ht="26" customHeight="1">
+      <c r="A241" s="39" t="inlineStr">
+        <is>
+          <t>Wert Ihrer Auswahl brutto</t>
+        </is>
+      </c>
+      <c r="Q241" s="40">
+        <f>Q239+Q240</f>
         <v/>
       </c>
     </row>
     <row r="242" ht="22" customHeight="1">
       <c r="A242" s="37" t="inlineStr">
         <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q242" s="41">
+        <f>COUNTIF(N8:N236,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="24" customHeight="1">
+      <c r="A245" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B245" s="44" t="n"/>
+      <c r="C245" s="44" t="n"/>
+      <c r="D245" s="44" t="n"/>
+      <c r="E245" s="44" t="n"/>
+      <c r="F245" s="44" t="n"/>
+      <c r="G245" s="44" t="n"/>
+      <c r="H245" s="44" t="n"/>
+      <c r="I245" s="44" t="n"/>
+      <c r="J245" s="44" t="n"/>
+      <c r="K245" s="44" t="n"/>
+      <c r="L245" s="44" t="n"/>
+      <c r="M245" s="44" t="n"/>
+      <c r="N245" s="44" t="n"/>
+      <c r="O245" s="44" t="n"/>
+      <c r="P245" s="44" t="n"/>
+      <c r="Q245" s="44" t="n"/>
+    </row>
+    <row r="246" ht="22" customHeight="1">
+      <c r="A246" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q246" s="38">
+        <f>SUMPRODUCT(H8:H236,J8:J236)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247" ht="22" customHeight="1">
+      <c r="A247" s="37" t="inlineStr">
+        <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q242" s="38">
-        <f>Q241*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="243" ht="26" customHeight="1">
-      <c r="A243" s="39" t="inlineStr">
+      <c r="Q247" s="38">
+        <f>Q246*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248" ht="22" customHeight="1">
+      <c r="A248" s="45" t="inlineStr">
+        <is>
+          <t>Gesamtwert brutto</t>
+        </is>
+      </c>
+      <c r="Q248" s="46">
+        <f>Q246+Q247</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250" ht="24" customHeight="1">
+      <c r="A250" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B250" s="48" t="n"/>
+      <c r="C250" s="48" t="n"/>
+      <c r="D250" s="48" t="n"/>
+      <c r="E250" s="48" t="n"/>
+      <c r="F250" s="48" t="n"/>
+      <c r="G250" s="48" t="n"/>
+      <c r="H250" s="48" t="n"/>
+      <c r="I250" s="48" t="n"/>
+      <c r="J250" s="48" t="n"/>
+      <c r="K250" s="48" t="n"/>
+      <c r="L250" s="48" t="n"/>
+      <c r="M250" s="48" t="n"/>
+      <c r="N250" s="48" t="n"/>
+      <c r="O250" s="48" t="n"/>
+      <c r="P250" s="48" t="n"/>
+      <c r="Q250" s="48" t="n"/>
+    </row>
+    <row r="251" ht="22" customHeight="1">
+      <c r="A251" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
+        </is>
+      </c>
+      <c r="Q251" s="38">
+        <f>-Q246*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="252" ht="22" customHeight="1">
+      <c r="A252" s="45" t="inlineStr">
+        <is>
+          <t>Paketpreis netto</t>
+        </is>
+      </c>
+      <c r="Q252" s="46">
+        <f>Q246+Q251</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253" ht="22" customHeight="1">
+      <c r="A253" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q253" s="38">
+        <f>Q252*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="254" ht="26" customHeight="1">
+      <c r="A254" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q243" s="40">
-        <f>Q241+Q242</f>
-        <v/>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="42" t="inlineStr">
+      <c r="Q254" s="40">
+        <f>Q252+Q253</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="A246" s="49" t="inlineStr">
+    <row r="257">
+      <c r="A257" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="247"/>
-    <row r="248"/>
-    <row r="249"/>
+    <row r="258"/>
+    <row r="259"/>
+    <row r="260"/>
   </sheetData>
-  <autoFilter ref="A7:Q225"/>
+  <autoFilter ref="A7:Q236"/>
   <mergeCells count="26">
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A246:Q249"/>
-    <mergeCell ref="A232:Q232"/>
+    <mergeCell ref="A247:P247"/>
+    <mergeCell ref="A245:Q245"/>
+    <mergeCell ref="A254:P254"/>
+    <mergeCell ref="A253:P253"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A240:P240"/>
-    <mergeCell ref="A231:P231"/>
     <mergeCell ref="L4:Q4"/>
-    <mergeCell ref="A230:P230"/>
+    <mergeCell ref="A250:Q250"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A229:P229"/>
-    <mergeCell ref="A227:Q227"/>
+    <mergeCell ref="A243:Q243"/>
+    <mergeCell ref="A255:Q255"/>
+    <mergeCell ref="A238:Q238"/>
     <mergeCell ref="A241:P241"/>
-    <mergeCell ref="A239:Q239"/>
     <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A237:P237"/>
-    <mergeCell ref="A228:P228"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A243:P243"/>
-    <mergeCell ref="A234:Q234"/>
-    <mergeCell ref="A244:Q244"/>
-    <mergeCell ref="A236:P236"/>
+    <mergeCell ref="A252:P252"/>
+    <mergeCell ref="A246:P246"/>
+    <mergeCell ref="A257:Q260"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A235:P235"/>
+    <mergeCell ref="A248:P248"/>
+    <mergeCell ref="A239:P239"/>
+    <mergeCell ref="A251:P251"/>
     <mergeCell ref="A242:P242"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q225">
+  <conditionalFormatting sqref="A8:Q236">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N225" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O225" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -6072,17 +6072,42 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
+      <row>232</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="227" name="Image 227" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId227"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
       <row>233</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="227" name="Image 227" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId227"/>
+        <cNvPr id="228" name="Image 228" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId228"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -6103,11 +6128,36 @@
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="228" name="Image 228" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId228"/>
+        <cNvPr id="229" name="Image 229" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId229"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>235</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="230" name="Image 230" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId230"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -20151,7 +20201,7 @@
       <c r="D233" s="23" t="inlineStr">
         <is>
           <t>Holz-Lastwagen zum Rutschen
-Rutschfahrzeug aus Massivholz in Lastwagenform mit offener Ladefläche, Holzlenkrad und roten Rädern.</t>
+Rutschfahrzeug aus Massivholz in Lastwagenform: offene Ladefläche mit Bordwänden, gepolsterter Sitz vor dem Führerhaus, Holzlenkrad und vier Gummiräder mit roten Felgen.</t>
         </is>
       </c>
       <c r="E233" s="13" t="n"/>
@@ -20330,8 +20380,8 @@
       <c r="C236" s="11" t="n"/>
       <c r="D236" s="12" t="inlineStr">
         <is>
-          <t>Spieltunnel grün
-Spieltunnel aus grünem Stoff mit roten Ringen, etwa 180 cm lang und 45 cm Durchmesser, zusammenfaltbar, mit Originalkarton.</t>
+          <t>Spieltunnel grün, 180 cm
+Spieltunnel aus grünem Stoff mit roten Ringen, etwa 180 cm lang bei 45 cm Durchmesser. Faltbar, mit Originalkarton.</t>
         </is>
       </c>
       <c r="E236" s="13" t="n"/>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$236</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$241</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -6168,6 +6168,131 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>236</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="231" name="Image 231" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId231"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>237</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="232" name="Image 232" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId232"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>238</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="233" name="Image 233" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId233"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>239</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="234" name="Image 234" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId234"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>240</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="235" name="Image 235" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId235"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -6460,7 +6585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q260"/>
+  <dimension ref="A1:Q265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -19136,7 +19261,7 @@
         </is>
       </c>
       <c r="H215" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I215" s="21" t="inlineStr">
         <is>
@@ -20428,261 +20553,561 @@
         <v/>
       </c>
     </row>
-    <row r="238" ht="24" customHeight="1">
-      <c r="A238" s="36" t="inlineStr">
+    <row r="237" ht="78" customHeight="1">
+      <c r="A237" s="20" t="n">
+        <v>230</v>
+      </c>
+      <c r="B237" s="21" t="inlineStr">
+        <is>
+          <t>BA07-01</t>
+        </is>
+      </c>
+      <c r="C237" s="22" t="n"/>
+      <c r="D237" s="23" t="inlineStr">
+        <is>
+          <t>Kissen in Wolkenform, hellblau
+Dekokissen in Wolkenform aus hellblauem Samtstoff, mit aufgestickten Augen, Lächeln und rosa Wangen.</t>
+        </is>
+      </c>
+      <c r="E237" s="13" t="n"/>
+      <c r="F237" s="23" t="inlineStr">
+        <is>
+          <t>Klassenzimmer</t>
+        </is>
+      </c>
+      <c r="G237" s="21" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H237" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I237" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J237" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="K237" s="25">
+        <f>J237*1.19</f>
+        <v/>
+      </c>
+      <c r="L237" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M237" s="23" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N237" s="16" t="n"/>
+      <c r="O237" s="17" t="n"/>
+      <c r="P237" s="18" t="n"/>
+      <c r="Q237" s="26">
+        <f>IF(N237&lt;&gt;"ja","",IF(O237="",H237,O237)*J237)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238" ht="78" customHeight="1">
+      <c r="A238" s="9" t="n">
+        <v>231</v>
+      </c>
+      <c r="B238" s="10" t="inlineStr">
+        <is>
+          <t>BA07-02</t>
+        </is>
+      </c>
+      <c r="C238" s="11" t="n"/>
+      <c r="D238" s="12" t="inlineStr">
+        <is>
+          <t>Wandleuchte rund mit Holzrand
+Runde Wandleuchte: Rahmen aus gebogenem Schichtholz mit satinierter Scheibe, flache Bauform, Zuleitung sichtbar verlegt. Zwei verschiedene Durchmesser.</t>
+        </is>
+      </c>
+      <c r="E238" s="13" t="n"/>
+      <c r="F238" s="12" t="inlineStr">
+        <is>
+          <t>Klassenzimmer</t>
+        </is>
+      </c>
+      <c r="G238" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H238" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I238" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J238" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="K238" s="15">
+        <f>J238*1.19</f>
+        <v/>
+      </c>
+      <c r="L238" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M238" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N238" s="16" t="n"/>
+      <c r="O238" s="17" t="n"/>
+      <c r="P238" s="18" t="n"/>
+      <c r="Q238" s="19">
+        <f>IF(N238&lt;&gt;"ja","",IF(O238="",H238,O238)*J238)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239" ht="78" customHeight="1">
+      <c r="A239" s="20" t="n">
+        <v>232</v>
+      </c>
+      <c r="B239" s="21" t="inlineStr">
+        <is>
+          <t>BA07-03</t>
+        </is>
+      </c>
+      <c r="C239" s="22" t="n"/>
+      <c r="D239" s="23" t="inlineStr">
+        <is>
+          <t>Standregal grau mit Wolkenaufsatz
+Schmales Standregal in Grau mit drei Ablagen und vorderen Haltelleisten, oben ein ausgesägter Wolkenaufsatz, auf schrägen Holzbeinen. Als Bücherregal genutzt.</t>
+        </is>
+      </c>
+      <c r="E239" s="13" t="n"/>
+      <c r="F239" s="23" t="inlineStr">
+        <is>
+          <t>Klassenzimmer</t>
+        </is>
+      </c>
+      <c r="G239" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H239" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I239" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J239" s="24" t="n">
+        <v>45</v>
+      </c>
+      <c r="K239" s="25">
+        <f>J239*1.19</f>
+        <v/>
+      </c>
+      <c r="L239" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M239" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N239" s="16" t="n"/>
+      <c r="O239" s="17" t="n"/>
+      <c r="P239" s="18" t="n"/>
+      <c r="Q239" s="26">
+        <f>IF(N239&lt;&gt;"ja","",IF(O239="",H239,O239)*J239)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="240" ht="78" customHeight="1">
+      <c r="A240" s="9" t="n">
+        <v>233</v>
+      </c>
+      <c r="B240" s="10" t="inlineStr">
+        <is>
+          <t>BA07-05</t>
+        </is>
+      </c>
+      <c r="C240" s="11" t="n"/>
+      <c r="D240" s="12" t="inlineStr">
+        <is>
+          <t>Tisch weiß, lang, auf schwarzen Beinen
+Langer Tisch mit weißer Platte auf vier schwarzen Rundbeinen mit Gleitern. Als Arbeits- und Ablagefläche genutzt.</t>
+        </is>
+      </c>
+      <c r="E240" s="13" t="n"/>
+      <c r="F240" s="12" t="inlineStr">
+        <is>
+          <t>Klassenzimmer</t>
+        </is>
+      </c>
+      <c r="G240" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H240" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I240" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J240" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="K240" s="15">
+        <f>J240*1.19</f>
+        <v/>
+      </c>
+      <c r="L240" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M240" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N240" s="16" t="n"/>
+      <c r="O240" s="17" t="n"/>
+      <c r="P240" s="18" t="n"/>
+      <c r="Q240" s="19">
+        <f>IF(N240&lt;&gt;"ja","",IF(O240="",H240,O240)*J240)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241" ht="78" customHeight="1">
+      <c r="A241" s="20" t="n">
+        <v>234</v>
+      </c>
+      <c r="B241" s="21" t="inlineStr">
+        <is>
+          <t>BA07-06</t>
+        </is>
+      </c>
+      <c r="C241" s="22" t="n"/>
+      <c r="D241" s="23" t="inlineStr">
+        <is>
+          <t>Regal creme, 16 Fächer, auf Metallbeinen
+Großes Regal in Creme mit sechzehn Fächern in vier Reihen, auf schräg gestellten schwarzen Metallbeinen.</t>
+        </is>
+      </c>
+      <c r="E241" s="13" t="n"/>
+      <c r="F241" s="23" t="inlineStr">
+        <is>
+          <t>Klassenzimmer</t>
+        </is>
+      </c>
+      <c r="G241" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H241" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I241" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J241" s="24" t="n">
+        <v>90</v>
+      </c>
+      <c r="K241" s="25">
+        <f>J241*1.19</f>
+        <v/>
+      </c>
+      <c r="L241" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M241" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N241" s="16" t="n"/>
+      <c r="O241" s="17" t="n"/>
+      <c r="P241" s="18" t="n"/>
+      <c r="Q241" s="26">
+        <f>IF(N241&lt;&gt;"ja","",IF(O241="",H241,O241)*J241)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243" ht="24" customHeight="1">
+      <c r="A243" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B238" s="1" t="n"/>
-      <c r="C238" s="1" t="n"/>
-      <c r="D238" s="1" t="n"/>
-      <c r="E238" s="1" t="n"/>
-      <c r="F238" s="1" t="n"/>
-      <c r="G238" s="1" t="n"/>
-      <c r="H238" s="1" t="n"/>
-      <c r="I238" s="1" t="n"/>
-      <c r="J238" s="1" t="n"/>
-      <c r="K238" s="1" t="n"/>
-      <c r="L238" s="1" t="n"/>
-      <c r="M238" s="1" t="n"/>
-      <c r="N238" s="1" t="n"/>
-      <c r="O238" s="1" t="n"/>
-      <c r="P238" s="1" t="n"/>
-      <c r="Q238" s="1" t="n"/>
-    </row>
-    <row r="239" ht="22" customHeight="1">
-      <c r="A239" s="37" t="inlineStr">
+      <c r="B243" s="1" t="n"/>
+      <c r="C243" s="1" t="n"/>
+      <c r="D243" s="1" t="n"/>
+      <c r="E243" s="1" t="n"/>
+      <c r="F243" s="1" t="n"/>
+      <c r="G243" s="1" t="n"/>
+      <c r="H243" s="1" t="n"/>
+      <c r="I243" s="1" t="n"/>
+      <c r="J243" s="1" t="n"/>
+      <c r="K243" s="1" t="n"/>
+      <c r="L243" s="1" t="n"/>
+      <c r="M243" s="1" t="n"/>
+      <c r="N243" s="1" t="n"/>
+      <c r="O243" s="1" t="n"/>
+      <c r="P243" s="1" t="n"/>
+      <c r="Q243" s="1" t="n"/>
+    </row>
+    <row r="244" ht="22" customHeight="1">
+      <c r="A244" s="37" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl netto</t>
         </is>
       </c>
-      <c r="Q239" s="38">
-        <f>SUM(Q8:Q236)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="240" ht="22" customHeight="1">
-      <c r="A240" s="37" t="inlineStr">
+      <c r="Q244" s="38">
+        <f>SUM(Q8:Q241)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245" ht="22" customHeight="1">
+      <c r="A245" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q240" s="38">
-        <f>Q239*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="241" ht="26" customHeight="1">
-      <c r="A241" s="39" t="inlineStr">
+      <c r="Q245" s="38">
+        <f>Q244*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246" ht="26" customHeight="1">
+      <c r="A246" s="39" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl brutto</t>
         </is>
       </c>
-      <c r="Q241" s="40">
-        <f>Q239+Q240</f>
-        <v/>
-      </c>
-    </row>
-    <row r="242" ht="22" customHeight="1">
-      <c r="A242" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q242" s="41">
-        <f>COUNTIF(N8:N236,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="245" ht="24" customHeight="1">
-      <c r="A245" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B245" s="44" t="n"/>
-      <c r="C245" s="44" t="n"/>
-      <c r="D245" s="44" t="n"/>
-      <c r="E245" s="44" t="n"/>
-      <c r="F245" s="44" t="n"/>
-      <c r="G245" s="44" t="n"/>
-      <c r="H245" s="44" t="n"/>
-      <c r="I245" s="44" t="n"/>
-      <c r="J245" s="44" t="n"/>
-      <c r="K245" s="44" t="n"/>
-      <c r="L245" s="44" t="n"/>
-      <c r="M245" s="44" t="n"/>
-      <c r="N245" s="44" t="n"/>
-      <c r="O245" s="44" t="n"/>
-      <c r="P245" s="44" t="n"/>
-      <c r="Q245" s="44" t="n"/>
-    </row>
-    <row r="246" ht="22" customHeight="1">
-      <c r="A246" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
-        </is>
-      </c>
-      <c r="Q246" s="38">
-        <f>SUMPRODUCT(H8:H236,J8:J236)</f>
+      <c r="Q246" s="40">
+        <f>Q244+Q245</f>
         <v/>
       </c>
     </row>
     <row r="247" ht="22" customHeight="1">
       <c r="A247" s="37" t="inlineStr">
         <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q247" s="38">
-        <f>Q246*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="248" ht="22" customHeight="1">
-      <c r="A248" s="45" t="inlineStr">
-        <is>
-          <t>Gesamtwert brutto</t>
-        </is>
-      </c>
-      <c r="Q248" s="46">
-        <f>Q246+Q247</f>
-        <v/>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q247" s="41">
+        <f>COUNTIF(N8:N241,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
       </c>
     </row>
     <row r="250" ht="24" customHeight="1">
-      <c r="A250" s="47" t="inlineStr">
-        <is>
-          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B250" s="48" t="n"/>
-      <c r="C250" s="48" t="n"/>
-      <c r="D250" s="48" t="n"/>
-      <c r="E250" s="48" t="n"/>
-      <c r="F250" s="48" t="n"/>
-      <c r="G250" s="48" t="n"/>
-      <c r="H250" s="48" t="n"/>
-      <c r="I250" s="48" t="n"/>
-      <c r="J250" s="48" t="n"/>
-      <c r="K250" s="48" t="n"/>
-      <c r="L250" s="48" t="n"/>
-      <c r="M250" s="48" t="n"/>
-      <c r="N250" s="48" t="n"/>
-      <c r="O250" s="48" t="n"/>
-      <c r="P250" s="48" t="n"/>
-      <c r="Q250" s="48" t="n"/>
+      <c r="A250" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B250" s="44" t="n"/>
+      <c r="C250" s="44" t="n"/>
+      <c r="D250" s="44" t="n"/>
+      <c r="E250" s="44" t="n"/>
+      <c r="F250" s="44" t="n"/>
+      <c r="G250" s="44" t="n"/>
+      <c r="H250" s="44" t="n"/>
+      <c r="I250" s="44" t="n"/>
+      <c r="J250" s="44" t="n"/>
+      <c r="K250" s="44" t="n"/>
+      <c r="L250" s="44" t="n"/>
+      <c r="M250" s="44" t="n"/>
+      <c r="N250" s="44" t="n"/>
+      <c r="O250" s="44" t="n"/>
+      <c r="P250" s="44" t="n"/>
+      <c r="Q250" s="44" t="n"/>
     </row>
     <row r="251" ht="22" customHeight="1">
       <c r="A251" s="37" t="inlineStr">
         <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q251" s="38">
+        <f>SUMPRODUCT(H8:H241,J8:J241)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="252" ht="22" customHeight="1">
+      <c r="A252" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q252" s="38">
+        <f>Q251*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253" ht="22" customHeight="1">
+      <c r="A253" s="45" t="inlineStr">
+        <is>
+          <t>Gesamtwert brutto</t>
+        </is>
+      </c>
+      <c r="Q253" s="46">
+        <f>Q251+Q252</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255" ht="24" customHeight="1">
+      <c r="A255" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B255" s="48" t="n"/>
+      <c r="C255" s="48" t="n"/>
+      <c r="D255" s="48" t="n"/>
+      <c r="E255" s="48" t="n"/>
+      <c r="F255" s="48" t="n"/>
+      <c r="G255" s="48" t="n"/>
+      <c r="H255" s="48" t="n"/>
+      <c r="I255" s="48" t="n"/>
+      <c r="J255" s="48" t="n"/>
+      <c r="K255" s="48" t="n"/>
+      <c r="L255" s="48" t="n"/>
+      <c r="M255" s="48" t="n"/>
+      <c r="N255" s="48" t="n"/>
+      <c r="O255" s="48" t="n"/>
+      <c r="P255" s="48" t="n"/>
+      <c r="Q255" s="48" t="n"/>
+    </row>
+    <row r="256" ht="22" customHeight="1">
+      <c r="A256" s="37" t="inlineStr">
+        <is>
           <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
         </is>
       </c>
-      <c r="Q251" s="38">
-        <f>-Q246*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="252" ht="22" customHeight="1">
-      <c r="A252" s="45" t="inlineStr">
+      <c r="Q256" s="38">
+        <f>-Q251*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="257" ht="22" customHeight="1">
+      <c r="A257" s="45" t="inlineStr">
         <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="Q252" s="46">
-        <f>Q246+Q251</f>
-        <v/>
-      </c>
-    </row>
-    <row r="253" ht="22" customHeight="1">
-      <c r="A253" s="37" t="inlineStr">
+      <c r="Q257" s="46">
+        <f>Q251+Q256</f>
+        <v/>
+      </c>
+    </row>
+    <row r="258" ht="22" customHeight="1">
+      <c r="A258" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q253" s="38">
-        <f>Q252*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="254" ht="26" customHeight="1">
-      <c r="A254" s="39" t="inlineStr">
+      <c r="Q258" s="38">
+        <f>Q257*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="259" ht="26" customHeight="1">
+      <c r="A259" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q254" s="40">
-        <f>Q252+Q253</f>
-        <v/>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="42" t="inlineStr">
+      <c r="Q259" s="40">
+        <f>Q257+Q258</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="49" t="inlineStr">
+    <row r="262">
+      <c r="A262" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="258"/>
-    <row r="259"/>
-    <row r="260"/>
+    <row r="263"/>
+    <row r="264"/>
+    <row r="265"/>
   </sheetData>
-  <autoFilter ref="A7:Q236"/>
+  <autoFilter ref="A7:Q241"/>
   <mergeCells count="26">
     <mergeCell ref="C1:Q1"/>
     <mergeCell ref="A247:P247"/>
-    <mergeCell ref="A245:Q245"/>
-    <mergeCell ref="A254:P254"/>
+    <mergeCell ref="A259:P259"/>
     <mergeCell ref="A253:P253"/>
+    <mergeCell ref="A244:P244"/>
+    <mergeCell ref="A260:Q260"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A240:P240"/>
     <mergeCell ref="L4:Q4"/>
     <mergeCell ref="A250:Q250"/>
     <mergeCell ref="C3:I3"/>
+    <mergeCell ref="A245:P245"/>
+    <mergeCell ref="A262:Q265"/>
+    <mergeCell ref="A258:P258"/>
     <mergeCell ref="A243:Q243"/>
     <mergeCell ref="A255:Q255"/>
-    <mergeCell ref="A238:Q238"/>
-    <mergeCell ref="A241:P241"/>
+    <mergeCell ref="A257:P257"/>
     <mergeCell ref="C4:I4"/>
+    <mergeCell ref="A248:Q248"/>
+    <mergeCell ref="A256:P256"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
     <mergeCell ref="A252:P252"/>
     <mergeCell ref="A246:P246"/>
-    <mergeCell ref="A257:Q260"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A248:P248"/>
-    <mergeCell ref="A239:P239"/>
     <mergeCell ref="A251:P251"/>
-    <mergeCell ref="A242:P242"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q236">
+  <conditionalFormatting sqref="A8:Q241">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N241" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O236" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O241" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$241</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$249</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -6293,6 +6293,206 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>241</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="236" name="Image 236" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId236"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>242</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="237" name="Image 237" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId237"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>243</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="238" name="Image 238" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId238"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>244</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="239" name="Image 239" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId239"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>245</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="240" name="Image 240" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId240"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>246</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="241" name="Image 241" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId241"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>247</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="242" name="Image 242" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId242"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>248</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="243" name="Image 243" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId243"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -6585,7 +6785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q265"/>
+  <dimension ref="A1:Q273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -20853,261 +21053,741 @@
         <v/>
       </c>
     </row>
-    <row r="243" ht="24" customHeight="1">
-      <c r="A243" s="36" t="inlineStr">
+    <row r="242" ht="78" customHeight="1">
+      <c r="A242" s="9" t="n">
+        <v>235</v>
+      </c>
+      <c r="B242" s="10" t="inlineStr">
+        <is>
+          <t>BA08-05</t>
+        </is>
+      </c>
+      <c r="C242" s="11" t="n"/>
+      <c r="D242" s="12" t="inlineStr">
+        <is>
+          <t>Acrylbild schwarz-weiß, Kreise mit Punkten
+Acryl auf Leinwand, großes Quadrat: mit breitem Pinsel gezogene Kreise, darin je mehrere gemalte Punkte – die Anmutung von Würfeln. Eigenarbeit einer Privatperson, nicht signiert.</t>
+        </is>
+      </c>
+      <c r="E242" s="13" t="n"/>
+      <c r="F242" s="12" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="G242" s="10" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H242" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I242" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J242" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="K242" s="15">
+        <f>J242*1.19</f>
+        <v/>
+      </c>
+      <c r="L242" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M242" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N242" s="16" t="n"/>
+      <c r="O242" s="17" t="n"/>
+      <c r="P242" s="18" t="n"/>
+      <c r="Q242" s="19">
+        <f>IF(N242&lt;&gt;"ja","",IF(O242="",H242,O242)*J242)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243" ht="78" customHeight="1">
+      <c r="A243" s="20" t="n">
+        <v>236</v>
+      </c>
+      <c r="B243" s="21" t="inlineStr">
+        <is>
+          <t>BA08-06</t>
+        </is>
+      </c>
+      <c r="C243" s="22" t="n"/>
+      <c r="D243" s="23" t="inlineStr">
+        <is>
+          <t>VS Schalenstuhl grau, Vierfußgestell
+Schalenstuhl von VS (Vereinigte Spezialmöbelfabriken): graue Kunststoffschale mit Rautenstruktur und Griffloch in der Lehne, auf grauem Vierfußgestell aus Rohr. Farbspritzer aus dem Atelierbetrieb auf Sitz und Lehne.</t>
+        </is>
+      </c>
+      <c r="E243" s="13" t="n"/>
+      <c r="F243" s="23" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="G243" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H243" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="I243" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J243" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="K243" s="25">
+        <f>J243*1.19</f>
+        <v/>
+      </c>
+      <c r="L243" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M243" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N243" s="16" t="n"/>
+      <c r="O243" s="17" t="n"/>
+      <c r="P243" s="18" t="n"/>
+      <c r="Q243" s="26">
+        <f>IF(N243&lt;&gt;"ja","",IF(O243="",H243,O243)*J243)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244" ht="78" customHeight="1">
+      <c r="A244" s="9" t="n">
+        <v>237</v>
+      </c>
+      <c r="B244" s="10" t="inlineStr">
+        <is>
+          <t>BA08-07</t>
+        </is>
+      </c>
+      <c r="C244" s="11" t="n"/>
+      <c r="D244" s="12" t="inlineStr">
+        <is>
+          <t>Konvolut Feinkrepp-Papier
+Rollen Feinkrepp von Marpa Jansen, je 50 × 250 cm, in Blau, Grün, Gelb, Rot, Orange und Braun. Teils angebrochen, dazu ein Beutel mit zugeschnittenen Schnipseln.</t>
+        </is>
+      </c>
+      <c r="E244" s="13" t="n"/>
+      <c r="F244" s="12" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="G244" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H244" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I244" s="10" t="inlineStr">
+        <is>
+          <t>Konvolut</t>
+        </is>
+      </c>
+      <c r="J244" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="K244" s="15">
+        <f>J244*1.19</f>
+        <v/>
+      </c>
+      <c r="L244" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M244" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N244" s="16" t="n"/>
+      <c r="O244" s="17" t="n"/>
+      <c r="P244" s="18" t="n"/>
+      <c r="Q244" s="19">
+        <f>IF(N244&lt;&gt;"ja","",IF(O244="",H244,O244)*J244)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245" ht="78" customHeight="1">
+      <c r="A245" s="20" t="n">
+        <v>238</v>
+      </c>
+      <c r="B245" s="21" t="inlineStr">
+        <is>
+          <t>BA08-08</t>
+        </is>
+      </c>
+      <c r="C245" s="22" t="n"/>
+      <c r="D245" s="23" t="inlineStr">
+        <is>
+          <t>Deko-Pilze auf Holzfuß
+Dekopilze mit gedrechseltem Fuß aus Massivholz: zwei mit gehämmerter Metallkappe in Silberoptik, einer mit Kappe in Betonoptik.</t>
+        </is>
+      </c>
+      <c r="E245" s="13" t="n"/>
+      <c r="F245" s="23" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="G245" s="21" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H245" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I245" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J245" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="K245" s="25">
+        <f>J245*1.19</f>
+        <v/>
+      </c>
+      <c r="L245" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M245" s="23" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N245" s="16" t="n"/>
+      <c r="O245" s="17" t="n"/>
+      <c r="P245" s="18" t="n"/>
+      <c r="Q245" s="26">
+        <f>IF(N245&lt;&gt;"ja","",IF(O245="",H245,O245)*J245)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246" ht="78" customHeight="1">
+      <c r="A246" s="9" t="n">
+        <v>239</v>
+      </c>
+      <c r="B246" s="10" t="inlineStr">
+        <is>
+          <t>BA08-09</t>
+        </is>
+      </c>
+      <c r="C246" s="11" t="n"/>
+      <c r="D246" s="12" t="inlineStr">
+        <is>
+          <t>Bastelscheren im Betzold-Holzblock
+Kinder-Bastelscheren mit Kunststoffgriffen in gemischten Farben, dazu ein Holzblock mit Steckbohrungen von Betzold als Ablage.</t>
+        </is>
+      </c>
+      <c r="E246" s="13" t="n"/>
+      <c r="F246" s="12" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="G246" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H246" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="I246" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J246" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="K246" s="15">
+        <f>J246*1.19</f>
+        <v/>
+      </c>
+      <c r="L246" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M246" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N246" s="16" t="n"/>
+      <c r="O246" s="17" t="n"/>
+      <c r="P246" s="18" t="n"/>
+      <c r="Q246" s="19">
+        <f>IF(N246&lt;&gt;"ja","",IF(O246="",H246,O246)*J246)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247" ht="78" customHeight="1">
+      <c r="A247" s="20" t="n">
+        <v>240</v>
+      </c>
+      <c r="B247" s="21" t="inlineStr">
+        <is>
+          <t>BA08-10</t>
+        </is>
+      </c>
+      <c r="C247" s="22" t="n"/>
+      <c r="D247" s="23" t="inlineStr">
+        <is>
+          <t>Kunstpflanze Gras im weißen Topf
+Künstliches Ziergras mit gedrehten Halmen in einem weißen Übertopf aus Metall mit durchbrochenem Spitzenrand.</t>
+        </is>
+      </c>
+      <c r="E247" s="13" t="n"/>
+      <c r="F247" s="23" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="G247" s="21" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H247" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I247" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J247" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="K247" s="25">
+        <f>J247*1.19</f>
+        <v/>
+      </c>
+      <c r="L247" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M247" s="23" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N247" s="16" t="n"/>
+      <c r="O247" s="17" t="n"/>
+      <c r="P247" s="18" t="n"/>
+      <c r="Q247" s="26">
+        <f>IF(N247&lt;&gt;"ja","",IF(O247="",H247,O247)*J247)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248" ht="78" customHeight="1">
+      <c r="A248" s="9" t="n">
+        <v>241</v>
+      </c>
+      <c r="B248" s="10" t="inlineStr">
+        <is>
+          <t>BA08-11</t>
+        </is>
+      </c>
+      <c r="C248" s="11" t="n"/>
+      <c r="D248" s="12" t="inlineStr">
+        <is>
+          <t>Bilderrahmen mit Zeichenwerkzeug
+Zwei schwarze Rahmen hinter Glas, gepunkteter Hintergrund: einer mit Bleistift, Lineal und gefaltetem Papier, einer mit sechs Pinseln in verschiedenen Breiten. Passend für ein Atelier oder Arbeitszimmer.</t>
+        </is>
+      </c>
+      <c r="E248" s="13" t="n"/>
+      <c r="F248" s="12" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="G248" s="10" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H248" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I248" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J248" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K248" s="15">
+        <f>J248*1.19</f>
+        <v/>
+      </c>
+      <c r="L248" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M248" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N248" s="16" t="n"/>
+      <c r="O248" s="17" t="n"/>
+      <c r="P248" s="18" t="n"/>
+      <c r="Q248" s="19">
+        <f>IF(N248&lt;&gt;"ja","",IF(O248="",H248,O248)*J248)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="249" ht="78" customHeight="1">
+      <c r="A249" s="20" t="n">
+        <v>242</v>
+      </c>
+      <c r="B249" s="21" t="inlineStr">
+        <is>
+          <t>BA08-12</t>
+        </is>
+      </c>
+      <c r="C249" s="22" t="n"/>
+      <c r="D249" s="23" t="inlineStr">
+        <is>
+          <t>Wandregalbrett weiß
+Schmales weißes Wandregalbrett mit vorderer Kante, zum Anschrauben.</t>
+        </is>
+      </c>
+      <c r="E249" s="13" t="n"/>
+      <c r="F249" s="23" t="inlineStr">
+        <is>
+          <t>Atelier</t>
+        </is>
+      </c>
+      <c r="G249" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H249" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I249" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J249" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="K249" s="25">
+        <f>J249*1.19</f>
+        <v/>
+      </c>
+      <c r="L249" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M249" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N249" s="16" t="n"/>
+      <c r="O249" s="17" t="n"/>
+      <c r="P249" s="18" t="n"/>
+      <c r="Q249" s="26">
+        <f>IF(N249&lt;&gt;"ja","",IF(O249="",H249,O249)*J249)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251" ht="24" customHeight="1">
+      <c r="A251" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B243" s="1" t="n"/>
-      <c r="C243" s="1" t="n"/>
-      <c r="D243" s="1" t="n"/>
-      <c r="E243" s="1" t="n"/>
-      <c r="F243" s="1" t="n"/>
-      <c r="G243" s="1" t="n"/>
-      <c r="H243" s="1" t="n"/>
-      <c r="I243" s="1" t="n"/>
-      <c r="J243" s="1" t="n"/>
-      <c r="K243" s="1" t="n"/>
-      <c r="L243" s="1" t="n"/>
-      <c r="M243" s="1" t="n"/>
-      <c r="N243" s="1" t="n"/>
-      <c r="O243" s="1" t="n"/>
-      <c r="P243" s="1" t="n"/>
-      <c r="Q243" s="1" t="n"/>
-    </row>
-    <row r="244" ht="22" customHeight="1">
-      <c r="A244" s="37" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl netto</t>
-        </is>
-      </c>
-      <c r="Q244" s="38">
-        <f>SUM(Q8:Q241)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="245" ht="22" customHeight="1">
-      <c r="A245" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q245" s="38">
-        <f>Q244*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="246" ht="26" customHeight="1">
-      <c r="A246" s="39" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl brutto</t>
-        </is>
-      </c>
-      <c r="Q246" s="40">
-        <f>Q244+Q245</f>
-        <v/>
-      </c>
-    </row>
-    <row r="247" ht="22" customHeight="1">
-      <c r="A247" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q247" s="41">
-        <f>COUNTIF(N8:N241,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="250" ht="24" customHeight="1">
-      <c r="A250" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B250" s="44" t="n"/>
-      <c r="C250" s="44" t="n"/>
-      <c r="D250" s="44" t="n"/>
-      <c r="E250" s="44" t="n"/>
-      <c r="F250" s="44" t="n"/>
-      <c r="G250" s="44" t="n"/>
-      <c r="H250" s="44" t="n"/>
-      <c r="I250" s="44" t="n"/>
-      <c r="J250" s="44" t="n"/>
-      <c r="K250" s="44" t="n"/>
-      <c r="L250" s="44" t="n"/>
-      <c r="M250" s="44" t="n"/>
-      <c r="N250" s="44" t="n"/>
-      <c r="O250" s="44" t="n"/>
-      <c r="P250" s="44" t="n"/>
-      <c r="Q250" s="44" t="n"/>
-    </row>
-    <row r="251" ht="22" customHeight="1">
-      <c r="A251" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
-        </is>
-      </c>
-      <c r="Q251" s="38">
-        <f>SUMPRODUCT(H8:H241,J8:J241)</f>
-        <v/>
-      </c>
+      <c r="B251" s="1" t="n"/>
+      <c r="C251" s="1" t="n"/>
+      <c r="D251" s="1" t="n"/>
+      <c r="E251" s="1" t="n"/>
+      <c r="F251" s="1" t="n"/>
+      <c r="G251" s="1" t="n"/>
+      <c r="H251" s="1" t="n"/>
+      <c r="I251" s="1" t="n"/>
+      <c r="J251" s="1" t="n"/>
+      <c r="K251" s="1" t="n"/>
+      <c r="L251" s="1" t="n"/>
+      <c r="M251" s="1" t="n"/>
+      <c r="N251" s="1" t="n"/>
+      <c r="O251" s="1" t="n"/>
+      <c r="P251" s="1" t="n"/>
+      <c r="Q251" s="1" t="n"/>
     </row>
     <row r="252" ht="22" customHeight="1">
       <c r="A252" s="37" t="inlineStr">
         <is>
+          <t>Wert Ihrer Auswahl netto</t>
+        </is>
+      </c>
+      <c r="Q252" s="38">
+        <f>SUM(Q8:Q249)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253" ht="22" customHeight="1">
+      <c r="A253" s="37" t="inlineStr">
+        <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q252" s="38">
-        <f>Q251*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="253" ht="22" customHeight="1">
-      <c r="A253" s="45" t="inlineStr">
+      <c r="Q253" s="38">
+        <f>Q252*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="254" ht="26" customHeight="1">
+      <c r="A254" s="39" t="inlineStr">
+        <is>
+          <t>Wert Ihrer Auswahl brutto</t>
+        </is>
+      </c>
+      <c r="Q254" s="40">
+        <f>Q252+Q253</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255" ht="22" customHeight="1">
+      <c r="A255" s="37" t="inlineStr">
+        <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q255" s="41">
+        <f>COUNTIF(N8:N249,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="24" customHeight="1">
+      <c r="A258" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B258" s="44" t="n"/>
+      <c r="C258" s="44" t="n"/>
+      <c r="D258" s="44" t="n"/>
+      <c r="E258" s="44" t="n"/>
+      <c r="F258" s="44" t="n"/>
+      <c r="G258" s="44" t="n"/>
+      <c r="H258" s="44" t="n"/>
+      <c r="I258" s="44" t="n"/>
+      <c r="J258" s="44" t="n"/>
+      <c r="K258" s="44" t="n"/>
+      <c r="L258" s="44" t="n"/>
+      <c r="M258" s="44" t="n"/>
+      <c r="N258" s="44" t="n"/>
+      <c r="O258" s="44" t="n"/>
+      <c r="P258" s="44" t="n"/>
+      <c r="Q258" s="44" t="n"/>
+    </row>
+    <row r="259" ht="22" customHeight="1">
+      <c r="A259" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q259" s="38">
+        <f>SUMPRODUCT(H8:H249,J8:J249)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260" ht="22" customHeight="1">
+      <c r="A260" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q260" s="38">
+        <f>Q259*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="261" ht="22" customHeight="1">
+      <c r="A261" s="45" t="inlineStr">
         <is>
           <t>Gesamtwert brutto</t>
         </is>
       </c>
-      <c r="Q253" s="46">
-        <f>Q251+Q252</f>
-        <v/>
-      </c>
-    </row>
-    <row r="255" ht="24" customHeight="1">
-      <c r="A255" s="47" t="inlineStr">
+      <c r="Q261" s="46">
+        <f>Q259+Q260</f>
+        <v/>
+      </c>
+    </row>
+    <row r="263" ht="24" customHeight="1">
+      <c r="A263" s="47" t="inlineStr">
         <is>
           <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
         </is>
       </c>
-      <c r="B255" s="48" t="n"/>
-      <c r="C255" s="48" t="n"/>
-      <c r="D255" s="48" t="n"/>
-      <c r="E255" s="48" t="n"/>
-      <c r="F255" s="48" t="n"/>
-      <c r="G255" s="48" t="n"/>
-      <c r="H255" s="48" t="n"/>
-      <c r="I255" s="48" t="n"/>
-      <c r="J255" s="48" t="n"/>
-      <c r="K255" s="48" t="n"/>
-      <c r="L255" s="48" t="n"/>
-      <c r="M255" s="48" t="n"/>
-      <c r="N255" s="48" t="n"/>
-      <c r="O255" s="48" t="n"/>
-      <c r="P255" s="48" t="n"/>
-      <c r="Q255" s="48" t="n"/>
-    </row>
-    <row r="256" ht="22" customHeight="1">
-      <c r="A256" s="37" t="inlineStr">
+      <c r="B263" s="48" t="n"/>
+      <c r="C263" s="48" t="n"/>
+      <c r="D263" s="48" t="n"/>
+      <c r="E263" s="48" t="n"/>
+      <c r="F263" s="48" t="n"/>
+      <c r="G263" s="48" t="n"/>
+      <c r="H263" s="48" t="n"/>
+      <c r="I263" s="48" t="n"/>
+      <c r="J263" s="48" t="n"/>
+      <c r="K263" s="48" t="n"/>
+      <c r="L263" s="48" t="n"/>
+      <c r="M263" s="48" t="n"/>
+      <c r="N263" s="48" t="n"/>
+      <c r="O263" s="48" t="n"/>
+      <c r="P263" s="48" t="n"/>
+      <c r="Q263" s="48" t="n"/>
+    </row>
+    <row r="264" ht="22" customHeight="1">
+      <c r="A264" s="37" t="inlineStr">
         <is>
           <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
         </is>
       </c>
-      <c r="Q256" s="38">
-        <f>-Q251*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="257" ht="22" customHeight="1">
-      <c r="A257" s="45" t="inlineStr">
+      <c r="Q264" s="38">
+        <f>-Q259*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="265" ht="22" customHeight="1">
+      <c r="A265" s="45" t="inlineStr">
         <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="Q257" s="46">
-        <f>Q251+Q256</f>
-        <v/>
-      </c>
-    </row>
-    <row r="258" ht="22" customHeight="1">
-      <c r="A258" s="37" t="inlineStr">
+      <c r="Q265" s="46">
+        <f>Q259+Q264</f>
+        <v/>
+      </c>
+    </row>
+    <row r="266" ht="22" customHeight="1">
+      <c r="A266" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q258" s="38">
-        <f>Q257*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="259" ht="26" customHeight="1">
-      <c r="A259" s="39" t="inlineStr">
+      <c r="Q266" s="38">
+        <f>Q265*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="267" ht="26" customHeight="1">
+      <c r="A267" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q259" s="40">
-        <f>Q257+Q258</f>
-        <v/>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="42" t="inlineStr">
+      <c r="Q267" s="40">
+        <f>Q265+Q266</f>
+        <v/>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="262">
-      <c r="A262" s="49" t="inlineStr">
+    <row r="270">
+      <c r="A270" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="263"/>
-    <row r="264"/>
-    <row r="265"/>
+    <row r="271"/>
+    <row r="272"/>
+    <row r="273"/>
   </sheetData>
-  <autoFilter ref="A7:Q241"/>
+  <autoFilter ref="A7:Q249"/>
   <mergeCells count="26">
+    <mergeCell ref="A258:Q258"/>
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A247:P247"/>
+    <mergeCell ref="A254:P254"/>
     <mergeCell ref="A259:P259"/>
     <mergeCell ref="A253:P253"/>
-    <mergeCell ref="A244:P244"/>
-    <mergeCell ref="A260:Q260"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="L4:Q4"/>
-    <mergeCell ref="A250:Q250"/>
+    <mergeCell ref="A265:P265"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A245:P245"/>
-    <mergeCell ref="A262:Q265"/>
-    <mergeCell ref="A258:P258"/>
-    <mergeCell ref="A243:Q243"/>
-    <mergeCell ref="A255:Q255"/>
-    <mergeCell ref="A257:P257"/>
+    <mergeCell ref="A256:Q256"/>
+    <mergeCell ref="A261:P261"/>
+    <mergeCell ref="A268:Q268"/>
+    <mergeCell ref="A266:P266"/>
+    <mergeCell ref="A260:P260"/>
     <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A248:Q248"/>
-    <mergeCell ref="A256:P256"/>
+    <mergeCell ref="A270:Q273"/>
+    <mergeCell ref="A251:Q251"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="A263:Q263"/>
     <mergeCell ref="A252:P252"/>
-    <mergeCell ref="A246:P246"/>
+    <mergeCell ref="A255:P255"/>
+    <mergeCell ref="A264:P264"/>
+    <mergeCell ref="A267:P267"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A251:P251"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q241">
+  <conditionalFormatting sqref="A8:Q249">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N241" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N249" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O241" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O249" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$249</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$255</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -6493,6 +6493,156 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>249</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="244" name="Image 244" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId244"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>250</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="245" name="Image 245" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId245"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>251</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="246" name="Image 246" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId246"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>252</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="247" name="Image 247" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId247"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>253</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="248" name="Image 248" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId248"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>254</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="249" name="Image 249" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId249"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -6785,7 +6935,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q273"/>
+  <dimension ref="A1:Q279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -14777,7 +14927,7 @@
         </is>
       </c>
       <c r="H137" s="21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I137" s="21" t="inlineStr">
         <is>
@@ -21533,178 +21683,471 @@
         <v/>
       </c>
     </row>
-    <row r="251" ht="24" customHeight="1">
-      <c r="A251" s="36" t="inlineStr">
+    <row r="250" ht="78" customHeight="1">
+      <c r="A250" s="9" t="n">
+        <v>243</v>
+      </c>
+      <c r="B250" s="35" t="inlineStr">
+        <is>
+          <t>BU01-01</t>
+        </is>
+      </c>
+      <c r="C250" s="11" t="n"/>
+      <c r="D250" s="12" t="inlineStr">
+        <is>
+          <t>Hausbett Buche massiv
+Kinderbett in Hausform aus massiver Buche, natur geölt, mit Dachgiebel und umlaufendem Rahmen. Einschließlich Matratze.</t>
+        </is>
+      </c>
+      <c r="E250" s="13" t="n"/>
+      <c r="F250" s="12" t="inlineStr">
+        <is>
+          <t>Flur 1</t>
+        </is>
+      </c>
+      <c r="G250" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H250" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I250" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J250" s="14" t="n">
+        <v>220</v>
+      </c>
+      <c r="K250" s="15">
+        <f>J250*1.19</f>
+        <v/>
+      </c>
+      <c r="L250" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M250" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N250" s="16" t="n"/>
+      <c r="O250" s="17" t="n"/>
+      <c r="P250" s="18" t="n"/>
+      <c r="Q250" s="19">
+        <f>IF(N250&lt;&gt;"ja","",IF(O250="",H250,O250)*J250)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251" ht="78" customHeight="1">
+      <c r="A251" s="20" t="n">
+        <v>244</v>
+      </c>
+      <c r="B251" s="21" t="inlineStr">
+        <is>
+          <t>BU01-02</t>
+        </is>
+      </c>
+      <c r="C251" s="22" t="n"/>
+      <c r="D251" s="23" t="inlineStr">
+        <is>
+          <t>Spielküche klein mit Mikrowelle
+Kleine Spielküche aus Birke-Multiplex mit weißen Fronten: Aufsatz mit Mikrowelle und zwei offenen Fächern, Arbeitsplatte mit Kochfeld, Spülbecken und Wasserhahn, darunter Backofen mit Sichtfenster und ein Schrank.</t>
+        </is>
+      </c>
+      <c r="E251" s="13" t="n"/>
+      <c r="F251" s="23" t="inlineStr">
+        <is>
+          <t>Flur 1</t>
+        </is>
+      </c>
+      <c r="G251" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H251" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I251" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J251" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="K251" s="25">
+        <f>J251*1.19</f>
+        <v/>
+      </c>
+      <c r="L251" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M251" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N251" s="16" t="n"/>
+      <c r="O251" s="17" t="n"/>
+      <c r="P251" s="18" t="n"/>
+      <c r="Q251" s="26">
+        <f>IF(N251&lt;&gt;"ja","",IF(O251="",H251,O251)*J251)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="252" ht="78" customHeight="1">
+      <c r="A252" s="9" t="n">
+        <v>245</v>
+      </c>
+      <c r="B252" s="10" t="inlineStr">
+        <is>
+          <t>BU01-04</t>
+        </is>
+      </c>
+      <c r="C252" s="11" t="n"/>
+      <c r="D252" s="12" t="inlineStr">
+        <is>
+          <t>Gestell Kiefer mit sechs Wannen
+Gestell aus Kiefer massiv mit sechs weißen Kunststoffwannen in zwei Reihen, als Spielzeugaufbewahrung genutzt.</t>
+        </is>
+      </c>
+      <c r="E252" s="13" t="n"/>
+      <c r="F252" s="12" t="inlineStr">
+        <is>
+          <t>Flur 1</t>
+        </is>
+      </c>
+      <c r="G252" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H252" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I252" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J252" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="K252" s="15">
+        <f>J252*1.19</f>
+        <v/>
+      </c>
+      <c r="L252" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M252" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N252" s="16" t="n"/>
+      <c r="O252" s="17" t="n"/>
+      <c r="P252" s="18" t="n"/>
+      <c r="Q252" s="19">
+        <f>IF(N252&lt;&gt;"ja","",IF(O252="",H252,O252)*J252)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253" ht="78" customHeight="1">
+      <c r="A253" s="20" t="n">
+        <v>246</v>
+      </c>
+      <c r="B253" s="21" t="inlineStr">
+        <is>
+          <t>BU01-05</t>
+        </is>
+      </c>
+      <c r="C253" s="22" t="n"/>
+      <c r="D253" s="23" t="inlineStr">
+        <is>
+          <t>IKEA Småstad Kindertisch weiß
+Niedriger Kindertisch von IKEA in Weiß mit Seitenwangen, Etikett an der Unterseite: Småstad, 804.335.42. Die Platte ist stark verkratzt und mit einer Schutzfolie belegt.</t>
+        </is>
+      </c>
+      <c r="E253" s="13" t="n"/>
+      <c r="F253" s="23" t="inlineStr">
+        <is>
+          <t>Flur 1</t>
+        </is>
+      </c>
+      <c r="G253" s="21" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="H253" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I253" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J253" s="24" t="n">
+        <v>35</v>
+      </c>
+      <c r="K253" s="25">
+        <f>J253*1.19</f>
+        <v/>
+      </c>
+      <c r="L253" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M253" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N253" s="16" t="n"/>
+      <c r="O253" s="17" t="n"/>
+      <c r="P253" s="18" t="n"/>
+      <c r="Q253" s="26">
+        <f>IF(N253&lt;&gt;"ja","",IF(O253="",H253,O253)*J253)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="254" ht="78" customHeight="1">
+      <c r="A254" s="9" t="n">
+        <v>247</v>
+      </c>
+      <c r="B254" s="10" t="inlineStr">
+        <is>
+          <t>BU01-06</t>
+        </is>
+      </c>
+      <c r="C254" s="11" t="n"/>
+      <c r="D254" s="12" t="inlineStr">
+        <is>
+          <t>Wanddeko Lama, Steckwand
+Wandelement in Lamaform aus weiß lackiertem Holz mit grauen Ohren, Gesicht und Füßen, durchgehend gelocht zum Einstecken von Haken oder Stäben.</t>
+        </is>
+      </c>
+      <c r="E254" s="13" t="n"/>
+      <c r="F254" s="12" t="inlineStr">
+        <is>
+          <t>Flur 1</t>
+        </is>
+      </c>
+      <c r="G254" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H254" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I254" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J254" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K254" s="15">
+        <f>J254*1.19</f>
+        <v/>
+      </c>
+      <c r="L254" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M254" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N254" s="16" t="n"/>
+      <c r="O254" s="17" t="n"/>
+      <c r="P254" s="18" t="n"/>
+      <c r="Q254" s="19">
+        <f>IF(N254&lt;&gt;"ja","",IF(O254="",H254,O254)*J254)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255" ht="78" customHeight="1">
+      <c r="A255" s="20" t="n">
+        <v>248</v>
+      </c>
+      <c r="B255" s="21" t="inlineStr">
+        <is>
+          <t>BU01-07</t>
+        </is>
+      </c>
+      <c r="C255" s="22" t="n"/>
+      <c r="D255" s="23" t="inlineStr">
+        <is>
+          <t>IKEA Grua Wandspiegel, schwarzer Rahmen
+Wandspiegel mit schmalem schwarzem Rahmen und abgerundeten Ecken. Etikett auf der Rückseite: Grua, IKEA.</t>
+        </is>
+      </c>
+      <c r="E255" s="13" t="n"/>
+      <c r="F255" s="23" t="inlineStr">
+        <is>
+          <t>Flur 1</t>
+        </is>
+      </c>
+      <c r="G255" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H255" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I255" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J255" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="K255" s="25">
+        <f>J255*1.19</f>
+        <v/>
+      </c>
+      <c r="L255" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M255" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N255" s="16" t="n"/>
+      <c r="O255" s="17" t="n"/>
+      <c r="P255" s="18" t="n"/>
+      <c r="Q255" s="26">
+        <f>IF(N255&lt;&gt;"ja","",IF(O255="",H255,O255)*J255)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="257" ht="24" customHeight="1">
+      <c r="A257" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B251" s="1" t="n"/>
-      <c r="C251" s="1" t="n"/>
-      <c r="D251" s="1" t="n"/>
-      <c r="E251" s="1" t="n"/>
-      <c r="F251" s="1" t="n"/>
-      <c r="G251" s="1" t="n"/>
-      <c r="H251" s="1" t="n"/>
-      <c r="I251" s="1" t="n"/>
-      <c r="J251" s="1" t="n"/>
-      <c r="K251" s="1" t="n"/>
-      <c r="L251" s="1" t="n"/>
-      <c r="M251" s="1" t="n"/>
-      <c r="N251" s="1" t="n"/>
-      <c r="O251" s="1" t="n"/>
-      <c r="P251" s="1" t="n"/>
-      <c r="Q251" s="1" t="n"/>
-    </row>
-    <row r="252" ht="22" customHeight="1">
-      <c r="A252" s="37" t="inlineStr">
+      <c r="B257" s="1" t="n"/>
+      <c r="C257" s="1" t="n"/>
+      <c r="D257" s="1" t="n"/>
+      <c r="E257" s="1" t="n"/>
+      <c r="F257" s="1" t="n"/>
+      <c r="G257" s="1" t="n"/>
+      <c r="H257" s="1" t="n"/>
+      <c r="I257" s="1" t="n"/>
+      <c r="J257" s="1" t="n"/>
+      <c r="K257" s="1" t="n"/>
+      <c r="L257" s="1" t="n"/>
+      <c r="M257" s="1" t="n"/>
+      <c r="N257" s="1" t="n"/>
+      <c r="O257" s="1" t="n"/>
+      <c r="P257" s="1" t="n"/>
+      <c r="Q257" s="1" t="n"/>
+    </row>
+    <row r="258" ht="22" customHeight="1">
+      <c r="A258" s="37" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl netto</t>
         </is>
       </c>
-      <c r="Q252" s="38">
-        <f>SUM(Q8:Q249)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="253" ht="22" customHeight="1">
-      <c r="A253" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q253" s="38">
-        <f>Q252*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="254" ht="26" customHeight="1">
-      <c r="A254" s="39" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl brutto</t>
-        </is>
-      </c>
-      <c r="Q254" s="40">
-        <f>Q252+Q253</f>
-        <v/>
-      </c>
-    </row>
-    <row r="255" ht="22" customHeight="1">
-      <c r="A255" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q255" s="41">
-        <f>COUNTIF(N8:N249,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="258" ht="24" customHeight="1">
-      <c r="A258" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B258" s="44" t="n"/>
-      <c r="C258" s="44" t="n"/>
-      <c r="D258" s="44" t="n"/>
-      <c r="E258" s="44" t="n"/>
-      <c r="F258" s="44" t="n"/>
-      <c r="G258" s="44" t="n"/>
-      <c r="H258" s="44" t="n"/>
-      <c r="I258" s="44" t="n"/>
-      <c r="J258" s="44" t="n"/>
-      <c r="K258" s="44" t="n"/>
-      <c r="L258" s="44" t="n"/>
-      <c r="M258" s="44" t="n"/>
-      <c r="N258" s="44" t="n"/>
-      <c r="O258" s="44" t="n"/>
-      <c r="P258" s="44" t="n"/>
-      <c r="Q258" s="44" t="n"/>
+      <c r="Q258" s="38">
+        <f>SUM(Q8:Q255)</f>
+        <v/>
+      </c>
     </row>
     <row r="259" ht="22" customHeight="1">
       <c r="A259" s="37" t="inlineStr">
         <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q259" s="38">
+        <f>Q258*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260" ht="26" customHeight="1">
+      <c r="A260" s="39" t="inlineStr">
+        <is>
+          <t>Wert Ihrer Auswahl brutto</t>
+        </is>
+      </c>
+      <c r="Q260" s="40">
+        <f>Q258+Q259</f>
+        <v/>
+      </c>
+    </row>
+    <row r="261" ht="22" customHeight="1">
+      <c r="A261" s="37" t="inlineStr">
+        <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q261" s="41">
+        <f>COUNTIF(N8:N255,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="24" customHeight="1">
+      <c r="A264" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B264" s="44" t="n"/>
+      <c r="C264" s="44" t="n"/>
+      <c r="D264" s="44" t="n"/>
+      <c r="E264" s="44" t="n"/>
+      <c r="F264" s="44" t="n"/>
+      <c r="G264" s="44" t="n"/>
+      <c r="H264" s="44" t="n"/>
+      <c r="I264" s="44" t="n"/>
+      <c r="J264" s="44" t="n"/>
+      <c r="K264" s="44" t="n"/>
+      <c r="L264" s="44" t="n"/>
+      <c r="M264" s="44" t="n"/>
+      <c r="N264" s="44" t="n"/>
+      <c r="O264" s="44" t="n"/>
+      <c r="P264" s="44" t="n"/>
+      <c r="Q264" s="44" t="n"/>
+    </row>
+    <row r="265" ht="22" customHeight="1">
+      <c r="A265" s="37" t="inlineStr">
+        <is>
           <t>Gesamtwert aller gelisteten Positionen netto</t>
         </is>
       </c>
-      <c r="Q259" s="38">
-        <f>SUMPRODUCT(H8:H249,J8:J249)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="260" ht="22" customHeight="1">
-      <c r="A260" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q260" s="38">
-        <f>Q259*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="261" ht="22" customHeight="1">
-      <c r="A261" s="45" t="inlineStr">
-        <is>
-          <t>Gesamtwert brutto</t>
-        </is>
-      </c>
-      <c r="Q261" s="46">
-        <f>Q259+Q260</f>
-        <v/>
-      </c>
-    </row>
-    <row r="263" ht="24" customHeight="1">
-      <c r="A263" s="47" t="inlineStr">
-        <is>
-          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B263" s="48" t="n"/>
-      <c r="C263" s="48" t="n"/>
-      <c r="D263" s="48" t="n"/>
-      <c r="E263" s="48" t="n"/>
-      <c r="F263" s="48" t="n"/>
-      <c r="G263" s="48" t="n"/>
-      <c r="H263" s="48" t="n"/>
-      <c r="I263" s="48" t="n"/>
-      <c r="J263" s="48" t="n"/>
-      <c r="K263" s="48" t="n"/>
-      <c r="L263" s="48" t="n"/>
-      <c r="M263" s="48" t="n"/>
-      <c r="N263" s="48" t="n"/>
-      <c r="O263" s="48" t="n"/>
-      <c r="P263" s="48" t="n"/>
-      <c r="Q263" s="48" t="n"/>
-    </row>
-    <row r="264" ht="22" customHeight="1">
-      <c r="A264" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
-        </is>
-      </c>
-      <c r="Q264" s="38">
-        <f>-Q259*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="265" ht="22" customHeight="1">
-      <c r="A265" s="45" t="inlineStr">
-        <is>
-          <t>Paketpreis netto</t>
-        </is>
-      </c>
-      <c r="Q265" s="46">
-        <f>Q259+Q264</f>
+      <c r="Q265" s="38">
+        <f>SUMPRODUCT(H8:H255,J8:J255)</f>
         <v/>
       </c>
     </row>
@@ -21719,75 +22162,142 @@
         <v/>
       </c>
     </row>
-    <row r="267" ht="26" customHeight="1">
-      <c r="A267" s="39" t="inlineStr">
+    <row r="267" ht="22" customHeight="1">
+      <c r="A267" s="45" t="inlineStr">
+        <is>
+          <t>Gesamtwert brutto</t>
+        </is>
+      </c>
+      <c r="Q267" s="46">
+        <f>Q265+Q266</f>
+        <v/>
+      </c>
+    </row>
+    <row r="269" ht="24" customHeight="1">
+      <c r="A269" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B269" s="48" t="n"/>
+      <c r="C269" s="48" t="n"/>
+      <c r="D269" s="48" t="n"/>
+      <c r="E269" s="48" t="n"/>
+      <c r="F269" s="48" t="n"/>
+      <c r="G269" s="48" t="n"/>
+      <c r="H269" s="48" t="n"/>
+      <c r="I269" s="48" t="n"/>
+      <c r="J269" s="48" t="n"/>
+      <c r="K269" s="48" t="n"/>
+      <c r="L269" s="48" t="n"/>
+      <c r="M269" s="48" t="n"/>
+      <c r="N269" s="48" t="n"/>
+      <c r="O269" s="48" t="n"/>
+      <c r="P269" s="48" t="n"/>
+      <c r="Q269" s="48" t="n"/>
+    </row>
+    <row r="270" ht="22" customHeight="1">
+      <c r="A270" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
+        </is>
+      </c>
+      <c r="Q270" s="38">
+        <f>-Q265*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="271" ht="22" customHeight="1">
+      <c r="A271" s="45" t="inlineStr">
+        <is>
+          <t>Paketpreis netto</t>
+        </is>
+      </c>
+      <c r="Q271" s="46">
+        <f>Q265+Q270</f>
+        <v/>
+      </c>
+    </row>
+    <row r="272" ht="22" customHeight="1">
+      <c r="A272" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q272" s="38">
+        <f>Q271*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="273" ht="26" customHeight="1">
+      <c r="A273" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q267" s="40">
-        <f>Q265+Q266</f>
-        <v/>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="42" t="inlineStr">
+      <c r="Q273" s="40">
+        <f>Q271+Q272</f>
+        <v/>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" s="49" t="inlineStr">
+    <row r="276">
+      <c r="A276" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="271"/>
-    <row r="272"/>
-    <row r="273"/>
+    <row r="277"/>
+    <row r="278"/>
+    <row r="279"/>
   </sheetData>
-  <autoFilter ref="A7:Q249"/>
+  <autoFilter ref="A7:Q255"/>
   <mergeCells count="26">
-    <mergeCell ref="A258:Q258"/>
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A254:P254"/>
     <mergeCell ref="A259:P259"/>
-    <mergeCell ref="A253:P253"/>
+    <mergeCell ref="A257:Q257"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="L4:Q4"/>
     <mergeCell ref="A265:P265"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A256:Q256"/>
+    <mergeCell ref="A258:P258"/>
     <mergeCell ref="A261:P261"/>
-    <mergeCell ref="A268:Q268"/>
+    <mergeCell ref="A270:P270"/>
     <mergeCell ref="A266:P266"/>
+    <mergeCell ref="A264:Q264"/>
     <mergeCell ref="A260:P260"/>
     <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A270:Q273"/>
-    <mergeCell ref="A251:Q251"/>
+    <mergeCell ref="A271:P271"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A263:Q263"/>
-    <mergeCell ref="A252:P252"/>
-    <mergeCell ref="A255:P255"/>
-    <mergeCell ref="A264:P264"/>
+    <mergeCell ref="A269:Q269"/>
+    <mergeCell ref="A262:Q262"/>
+    <mergeCell ref="A276:Q279"/>
+    <mergeCell ref="A273:P273"/>
     <mergeCell ref="A267:P267"/>
+    <mergeCell ref="A274:Q274"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
+    <mergeCell ref="A272:P272"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q249">
+  <conditionalFormatting sqref="A8:Q255">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N249" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N255" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O249" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O255" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$255</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$269</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -6643,6 +6643,356 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>255</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="250" name="Image 250" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId250"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>256</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="251" name="Image 251" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId251"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>257</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="252" name="Image 252" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId252"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>258</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="253" name="Image 253" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId253"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>259</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="254" name="Image 254" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId254"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>260</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="255" name="Image 255" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId255"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>261</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="256" name="Image 256" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId256"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>262</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="257" name="Image 257" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId257"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>263</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="258" name="Image 258" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId258"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>264</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="259" name="Image 259" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId259"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>265</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="260" name="Image 260" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId260"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>266</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="261" name="Image 261" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId261"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>267</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="262" name="Image 262" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId262"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>268</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="263" name="Image 263" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId263"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -6935,7 +7285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q279"/>
+  <dimension ref="A1:Q293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13007,7 +13357,7 @@
         </is>
       </c>
       <c r="H105" s="21" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="I105" s="21" t="inlineStr">
         <is>
@@ -14927,7 +15277,7 @@
         </is>
       </c>
       <c r="H137" s="21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I137" s="21" t="inlineStr">
         <is>
@@ -14987,7 +15337,7 @@
         </is>
       </c>
       <c r="H138" s="10" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I138" s="10" t="inlineStr">
         <is>
@@ -21651,7 +22001,7 @@
         </is>
       </c>
       <c r="H249" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I249" s="21" t="inlineStr">
         <is>
@@ -21951,7 +22301,7 @@
         </is>
       </c>
       <c r="H254" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I254" s="10" t="inlineStr">
         <is>
@@ -22043,261 +22393,1105 @@
         <v/>
       </c>
     </row>
-    <row r="257" ht="24" customHeight="1">
-      <c r="A257" s="36" t="inlineStr">
+    <row r="256" ht="78" customHeight="1">
+      <c r="A256" s="9" t="n">
+        <v>249</v>
+      </c>
+      <c r="B256" s="35" t="inlineStr">
+        <is>
+          <t>BU02-01</t>
+        </is>
+      </c>
+      <c r="C256" s="11" t="n"/>
+      <c r="D256" s="12" t="inlineStr">
+        <is>
+          <t>Hausbett Holz natur mit Stoffdach
+Bodenbett in Hausform aus hellem Massivholz mit vier Pfosten und aufgelegtem Stoffdach in Creme mit schwarzer Zackenkante und aufgesticktem Wolkenmotiv. Einschließlich Matratze.</t>
+        </is>
+      </c>
+      <c r="E256" s="13" t="n"/>
+      <c r="F256" s="12" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G256" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H256" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I256" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J256" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="K256" s="15">
+        <f>J256*1.19</f>
+        <v/>
+      </c>
+      <c r="L256" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M256" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N256" s="16" t="n"/>
+      <c r="O256" s="17" t="n"/>
+      <c r="P256" s="18" t="n"/>
+      <c r="Q256" s="19">
+        <f>IF(N256&lt;&gt;"ja","",IF(O256="",H256,O256)*J256)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="257" ht="78" customHeight="1">
+      <c r="A257" s="20" t="n">
+        <v>250</v>
+      </c>
+      <c r="B257" s="21" t="inlineStr">
+        <is>
+          <t>BU02-02</t>
+        </is>
+      </c>
+      <c r="C257" s="22" t="n"/>
+      <c r="D257" s="23" t="inlineStr">
+        <is>
+          <t>Nachtlicht Marienkäfer, schwarz
+Steckdosen-Nachtlicht in Marienkäferform aus schwarzem Kunststoff mit geprägten Punkten und Fühlern.</t>
+        </is>
+      </c>
+      <c r="E257" s="13" t="n"/>
+      <c r="F257" s="23" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G257" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H257" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I257" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J257" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="K257" s="25">
+        <f>J257*1.19</f>
+        <v/>
+      </c>
+      <c r="L257" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M257" s="23" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N257" s="16" t="n"/>
+      <c r="O257" s="17" t="n"/>
+      <c r="P257" s="18" t="n"/>
+      <c r="Q257" s="26">
+        <f>IF(N257&lt;&gt;"ja","",IF(O257="",H257,O257)*J257)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="258" ht="78" customHeight="1">
+      <c r="A258" s="9" t="n">
+        <v>251</v>
+      </c>
+      <c r="B258" s="35" t="inlineStr">
+        <is>
+          <t>BU02-03</t>
+        </is>
+      </c>
+      <c r="C258" s="11" t="n"/>
+      <c r="D258" s="12" t="inlineStr">
+        <is>
+          <t>Kindertisch weiß, oval, aus vier Segmenten
+Vier Tischsegmente mit weißer Platte und Multiplex-Kante auf verchromten Rundfüßen in Kinderhöhe: zwei halbrunde Endstücke und zwei Mittelstücke. Zusammengestellt ergeben sie einen großen ovalen Gruppentisch, einzeln sind sie frei kombinierbar.</t>
+        </is>
+      </c>
+      <c r="E258" s="13" t="n"/>
+      <c r="F258" s="12" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G258" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H258" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I258" s="10" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="J258" s="14" t="n">
+        <v>160</v>
+      </c>
+      <c r="K258" s="15">
+        <f>J258*1.19</f>
+        <v/>
+      </c>
+      <c r="L258" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M258" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N258" s="16" t="n"/>
+      <c r="O258" s="17" t="n"/>
+      <c r="P258" s="18" t="n"/>
+      <c r="Q258" s="19">
+        <f>IF(N258&lt;&gt;"ja","",IF(O258="",H258,O258)*J258)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="259" ht="78" customHeight="1">
+      <c r="A259" s="20" t="n">
+        <v>252</v>
+      </c>
+      <c r="B259" s="21" t="inlineStr">
+        <is>
+          <t>BU02-05</t>
+        </is>
+      </c>
+      <c r="C259" s="22" t="n"/>
+      <c r="D259" s="23" t="inlineStr">
+        <is>
+          <t>IKEA Duktig Spielküche mit Mikrowelle
+Spielküche von IKEA aus Birkenholz mit weißen Fronten: Aufsatz mit Mikrowelle und offenen Fächern, Arbeitsplatte mit Kochfeld, Spülbecken und Wasserhahn, darunter Backofen mit Sichtfenster und ein Schrank.</t>
+        </is>
+      </c>
+      <c r="E259" s="13" t="n"/>
+      <c r="F259" s="23" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G259" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H259" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I259" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J259" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="K259" s="25">
+        <f>J259*1.19</f>
+        <v/>
+      </c>
+      <c r="L259" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M259" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N259" s="16" t="n"/>
+      <c r="O259" s="17" t="n"/>
+      <c r="P259" s="18" t="n"/>
+      <c r="Q259" s="26">
+        <f>IF(N259&lt;&gt;"ja","",IF(O259="",H259,O259)*J259)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260" ht="78" customHeight="1">
+      <c r="A260" s="9" t="n">
+        <v>253</v>
+      </c>
+      <c r="B260" s="10" t="inlineStr">
+        <is>
+          <t>BU02-06</t>
+        </is>
+      </c>
+      <c r="C260" s="11" t="n"/>
+      <c r="D260" s="12" t="inlineStr">
+        <is>
+          <t>Kinder-Putzständer, fünfteilig
+Ständer aus Holz und Metall in Weiß mit Ablagekasten und aufgehängtem Kinder-Reinigungsgerät: Besen, Schrubber, Kehrblech und Staubwedel.</t>
+        </is>
+      </c>
+      <c r="E260" s="13" t="n"/>
+      <c r="F260" s="12" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G260" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H260" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I260" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J260" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K260" s="15">
+        <f>J260*1.19</f>
+        <v/>
+      </c>
+      <c r="L260" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M260" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N260" s="16" t="n"/>
+      <c r="O260" s="17" t="n"/>
+      <c r="P260" s="18" t="n"/>
+      <c r="Q260" s="19">
+        <f>IF(N260&lt;&gt;"ja","",IF(O260="",H260,O260)*J260)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="261" ht="78" customHeight="1">
+      <c r="A261" s="20" t="n">
+        <v>254</v>
+      </c>
+      <c r="B261" s="21" t="inlineStr">
+        <is>
+          <t>BU02-09</t>
+        </is>
+      </c>
+      <c r="C261" s="22" t="n"/>
+      <c r="D261" s="23" t="inlineStr">
+        <is>
+          <t>Acrylbild Herz auf Strahlenkranz
+Acryl auf Leinwand im Hochformat: breite Pinselstriche in Pink, Magenta und Grau strahlenförmig um ein ausgespartes weißes Herz. Eigenarbeit einer Privatperson, nicht signiert.</t>
+        </is>
+      </c>
+      <c r="E261" s="13" t="n"/>
+      <c r="F261" s="23" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G261" s="21" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H261" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I261" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J261" s="24" t="n">
+        <v>80</v>
+      </c>
+      <c r="K261" s="25">
+        <f>J261*1.19</f>
+        <v/>
+      </c>
+      <c r="L261" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M261" s="23" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N261" s="16" t="n"/>
+      <c r="O261" s="17" t="n"/>
+      <c r="P261" s="18" t="n"/>
+      <c r="Q261" s="26">
+        <f>IF(N261&lt;&gt;"ja","",IF(O261="",H261,O261)*J261)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="262" ht="78" customHeight="1">
+      <c r="A262" s="9" t="n">
+        <v>255</v>
+      </c>
+      <c r="B262" s="10" t="inlineStr">
+        <is>
+          <t>BU02-10</t>
+        </is>
+      </c>
+      <c r="C262" s="11" t="n"/>
+      <c r="D262" s="12" t="inlineStr">
+        <is>
+          <t>Spieltisch Kiefer mit herausnehmbaren Platten
+Kindertisch aus Kiefer massiv mit zwei herausnehmbaren weißen Platten. Darunter liegen Wannen, sodass der Tisch als Spiel- und Materialtisch genutzt werden kann. Die Platten sind an den Kanten großflächig abgeplatzt.</t>
+        </is>
+      </c>
+      <c r="E262" s="13" t="n"/>
+      <c r="F262" s="12" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G262" s="10" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="H262" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I262" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J262" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="K262" s="15">
+        <f>J262*1.19</f>
+        <v/>
+      </c>
+      <c r="L262" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M262" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N262" s="16" t="n"/>
+      <c r="O262" s="17" t="n"/>
+      <c r="P262" s="18" t="n"/>
+      <c r="Q262" s="19">
+        <f>IF(N262&lt;&gt;"ja","",IF(O262="",H262,O262)*J262)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="263" ht="78" customHeight="1">
+      <c r="A263" s="20" t="n">
+        <v>256</v>
+      </c>
+      <c r="B263" s="21" t="inlineStr">
+        <is>
+          <t>BU02-12</t>
+        </is>
+      </c>
+      <c r="C263" s="22" t="n"/>
+      <c r="D263" s="23" t="inlineStr">
+        <is>
+          <t>Wandregal weiß mit drei Wannen, geschwungen
+Weißes Wandelement mit geschwungener Front, drei Fächern und drei eingeschobenen Kunststoffwannen.</t>
+        </is>
+      </c>
+      <c r="E263" s="13" t="n"/>
+      <c r="F263" s="23" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G263" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H263" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I263" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J263" s="24" t="n">
+        <v>35</v>
+      </c>
+      <c r="K263" s="25">
+        <f>J263*1.19</f>
+        <v/>
+      </c>
+      <c r="L263" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M263" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N263" s="16" t="n"/>
+      <c r="O263" s="17" t="n"/>
+      <c r="P263" s="18" t="n"/>
+      <c r="Q263" s="26">
+        <f>IF(N263&lt;&gt;"ja","",IF(O263="",H263,O263)*J263)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="264" ht="78" customHeight="1">
+      <c r="A264" s="9" t="n">
+        <v>257</v>
+      </c>
+      <c r="B264" s="10" t="inlineStr">
+        <is>
+          <t>BU02-14</t>
+        </is>
+      </c>
+      <c r="C264" s="11" t="n"/>
+      <c r="D264" s="12" t="inlineStr">
+        <is>
+          <t>Kinderschrank graugrün, zwei Türen
+Hoher Kinderschrank von IKEA mit zwei graugrünen Türen und schwarzen Griffmulden, darunter eine Schublade.</t>
+        </is>
+      </c>
+      <c r="E264" s="13" t="n"/>
+      <c r="F264" s="12" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G264" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H264" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I264" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J264" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="K264" s="15">
+        <f>J264*1.19</f>
+        <v/>
+      </c>
+      <c r="L264" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M264" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N264" s="16" t="n"/>
+      <c r="O264" s="17" t="n"/>
+      <c r="P264" s="18" t="n"/>
+      <c r="Q264" s="19">
+        <f>IF(N264&lt;&gt;"ja","",IF(O264="",H264,O264)*J264)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="265" ht="78" customHeight="1">
+      <c r="A265" s="20" t="n">
+        <v>258</v>
+      </c>
+      <c r="B265" s="21" t="inlineStr">
+        <is>
+          <t>BU02-15</t>
+        </is>
+      </c>
+      <c r="C265" s="22" t="n"/>
+      <c r="D265" s="23" t="inlineStr">
+        <is>
+          <t>Bodensitzkissen beige, selbststehend
+Selbststehendes Bodensitzkissen aus beigem Leinenstoff mit gesteppten Feldern, Rückenlehne und langer Sitzfläche. Die Lehne lässt sich flach ausklappen.</t>
+        </is>
+      </c>
+      <c r="E265" s="13" t="n"/>
+      <c r="F265" s="23" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G265" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H265" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I265" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J265" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="K265" s="25">
+        <f>J265*1.19</f>
+        <v/>
+      </c>
+      <c r="L265" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M265" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N265" s="16" t="n"/>
+      <c r="O265" s="17" t="n"/>
+      <c r="P265" s="18" t="n"/>
+      <c r="Q265" s="26">
+        <f>IF(N265&lt;&gt;"ja","",IF(O265="",H265,O265)*J265)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="266" ht="78" customHeight="1">
+      <c r="A266" s="9" t="n">
+        <v>259</v>
+      </c>
+      <c r="B266" s="10" t="inlineStr">
+        <is>
+          <t>BU02-16</t>
+        </is>
+      </c>
+      <c r="C266" s="11" t="n"/>
+      <c r="D266" s="12" t="inlineStr">
+        <is>
+          <t>Servierwagen Metall schwarz, drei Ebenen
+Rollwagen aus schwarz lackiertem Metall mit drei Ablageebenen und Lochblechböden, auf vier Rollen.</t>
+        </is>
+      </c>
+      <c r="E266" s="13" t="n"/>
+      <c r="F266" s="12" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G266" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H266" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I266" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J266" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="K266" s="15">
+        <f>J266*1.19</f>
+        <v/>
+      </c>
+      <c r="L266" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M266" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N266" s="16" t="n"/>
+      <c r="O266" s="17" t="n"/>
+      <c r="P266" s="18" t="n"/>
+      <c r="Q266" s="19">
+        <f>IF(N266&lt;&gt;"ja","",IF(O266="",H266,O266)*J266)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="267" ht="78" customHeight="1">
+      <c r="A267" s="20" t="n">
+        <v>260</v>
+      </c>
+      <c r="B267" s="21" t="inlineStr">
+        <is>
+          <t>BU02-17</t>
+        </is>
+      </c>
+      <c r="C267" s="22" t="n"/>
+      <c r="D267" s="23" t="inlineStr">
+        <is>
+          <t>Kommode weiß, drei Schubladen
+Kommode in Weiß mit drei breiten Schubladen und mittig ausgeschnittenen Griffmulden, auf umlaufendem Sockel.</t>
+        </is>
+      </c>
+      <c r="E267" s="13" t="n"/>
+      <c r="F267" s="23" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G267" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H267" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I267" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J267" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="K267" s="25">
+        <f>J267*1.19</f>
+        <v/>
+      </c>
+      <c r="L267" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M267" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N267" s="16" t="n"/>
+      <c r="O267" s="17" t="n"/>
+      <c r="P267" s="18" t="n"/>
+      <c r="Q267" s="26">
+        <f>IF(N267&lt;&gt;"ja","",IF(O267="",H267,O267)*J267)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="268" ht="78" customHeight="1">
+      <c r="A268" s="9" t="n">
+        <v>261</v>
+      </c>
+      <c r="B268" s="10" t="inlineStr">
+        <is>
+          <t>BU02-18</t>
+        </is>
+      </c>
+      <c r="C268" s="11" t="n"/>
+      <c r="D268" s="12" t="inlineStr">
+        <is>
+          <t>Hochflorteppich grau
+Hochflorteppich in Grau, rechteckig. Etikett auf der Rückseite vorhanden, Maßangabe 160 × 230 cm.</t>
+        </is>
+      </c>
+      <c r="E268" s="13" t="inlineStr">
+        <is>
+          <t>160 × 230 cm</t>
+        </is>
+      </c>
+      <c r="F268" s="12" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G268" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H268" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I268" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J268" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="K268" s="15">
+        <f>J268*1.19</f>
+        <v/>
+      </c>
+      <c r="L268" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M268" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N268" s="16" t="n"/>
+      <c r="O268" s="17" t="n"/>
+      <c r="P268" s="18" t="n"/>
+      <c r="Q268" s="19">
+        <f>IF(N268&lt;&gt;"ja","",IF(O268="",H268,O268)*J268)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="269" ht="78" customHeight="1">
+      <c r="A269" s="20" t="n">
+        <v>262</v>
+      </c>
+      <c r="B269" s="21" t="inlineStr">
+        <is>
+          <t>BU02-19</t>
+        </is>
+      </c>
+      <c r="C269" s="22" t="n"/>
+      <c r="D269" s="23" t="inlineStr">
+        <is>
+          <t>Spielmöbel Kiefer, dreiteilig
+Dreiteilige Kombination aus Kiefer massiv: Wandregal mit zwei Kunststoffwannen, niedrige Werkbank mit offenem Unterbau und zwei Wannen sowie ein hohes Seitenteil mit Wanne.</t>
+        </is>
+      </c>
+      <c r="E269" s="13" t="n"/>
+      <c r="F269" s="23" t="inlineStr">
+        <is>
+          <t>Flur 2</t>
+        </is>
+      </c>
+      <c r="G269" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H269" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I269" s="21" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="J269" s="24" t="n">
+        <v>90</v>
+      </c>
+      <c r="K269" s="25">
+        <f>J269*1.19</f>
+        <v/>
+      </c>
+      <c r="L269" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M269" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N269" s="16" t="n"/>
+      <c r="O269" s="17" t="n"/>
+      <c r="P269" s="18" t="n"/>
+      <c r="Q269" s="26">
+        <f>IF(N269&lt;&gt;"ja","",IF(O269="",H269,O269)*J269)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="271" ht="24" customHeight="1">
+      <c r="A271" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B257" s="1" t="n"/>
-      <c r="C257" s="1" t="n"/>
-      <c r="D257" s="1" t="n"/>
-      <c r="E257" s="1" t="n"/>
-      <c r="F257" s="1" t="n"/>
-      <c r="G257" s="1" t="n"/>
-      <c r="H257" s="1" t="n"/>
-      <c r="I257" s="1" t="n"/>
-      <c r="J257" s="1" t="n"/>
-      <c r="K257" s="1" t="n"/>
-      <c r="L257" s="1" t="n"/>
-      <c r="M257" s="1" t="n"/>
-      <c r="N257" s="1" t="n"/>
-      <c r="O257" s="1" t="n"/>
-      <c r="P257" s="1" t="n"/>
-      <c r="Q257" s="1" t="n"/>
-    </row>
-    <row r="258" ht="22" customHeight="1">
-      <c r="A258" s="37" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl netto</t>
-        </is>
-      </c>
-      <c r="Q258" s="38">
-        <f>SUM(Q8:Q255)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="259" ht="22" customHeight="1">
-      <c r="A259" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q259" s="38">
-        <f>Q258*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="260" ht="26" customHeight="1">
-      <c r="A260" s="39" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl brutto</t>
-        </is>
-      </c>
-      <c r="Q260" s="40">
-        <f>Q258+Q259</f>
-        <v/>
-      </c>
-    </row>
-    <row r="261" ht="22" customHeight="1">
-      <c r="A261" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q261" s="41">
-        <f>COUNTIF(N8:N255,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="264" ht="24" customHeight="1">
-      <c r="A264" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B264" s="44" t="n"/>
-      <c r="C264" s="44" t="n"/>
-      <c r="D264" s="44" t="n"/>
-      <c r="E264" s="44" t="n"/>
-      <c r="F264" s="44" t="n"/>
-      <c r="G264" s="44" t="n"/>
-      <c r="H264" s="44" t="n"/>
-      <c r="I264" s="44" t="n"/>
-      <c r="J264" s="44" t="n"/>
-      <c r="K264" s="44" t="n"/>
-      <c r="L264" s="44" t="n"/>
-      <c r="M264" s="44" t="n"/>
-      <c r="N264" s="44" t="n"/>
-      <c r="O264" s="44" t="n"/>
-      <c r="P264" s="44" t="n"/>
-      <c r="Q264" s="44" t="n"/>
-    </row>
-    <row r="265" ht="22" customHeight="1">
-      <c r="A265" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
-        </is>
-      </c>
-      <c r="Q265" s="38">
-        <f>SUMPRODUCT(H8:H255,J8:J255)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="266" ht="22" customHeight="1">
-      <c r="A266" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q266" s="38">
-        <f>Q265*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="267" ht="22" customHeight="1">
-      <c r="A267" s="45" t="inlineStr">
-        <is>
-          <t>Gesamtwert brutto</t>
-        </is>
-      </c>
-      <c r="Q267" s="46">
-        <f>Q265+Q266</f>
-        <v/>
-      </c>
-    </row>
-    <row r="269" ht="24" customHeight="1">
-      <c r="A269" s="47" t="inlineStr">
-        <is>
-          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B269" s="48" t="n"/>
-      <c r="C269" s="48" t="n"/>
-      <c r="D269" s="48" t="n"/>
-      <c r="E269" s="48" t="n"/>
-      <c r="F269" s="48" t="n"/>
-      <c r="G269" s="48" t="n"/>
-      <c r="H269" s="48" t="n"/>
-      <c r="I269" s="48" t="n"/>
-      <c r="J269" s="48" t="n"/>
-      <c r="K269" s="48" t="n"/>
-      <c r="L269" s="48" t="n"/>
-      <c r="M269" s="48" t="n"/>
-      <c r="N269" s="48" t="n"/>
-      <c r="O269" s="48" t="n"/>
-      <c r="P269" s="48" t="n"/>
-      <c r="Q269" s="48" t="n"/>
-    </row>
-    <row r="270" ht="22" customHeight="1">
-      <c r="A270" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
-        </is>
-      </c>
-      <c r="Q270" s="38">
-        <f>-Q265*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="271" ht="22" customHeight="1">
-      <c r="A271" s="45" t="inlineStr">
-        <is>
-          <t>Paketpreis netto</t>
-        </is>
-      </c>
-      <c r="Q271" s="46">
-        <f>Q265+Q270</f>
-        <v/>
-      </c>
+      <c r="B271" s="1" t="n"/>
+      <c r="C271" s="1" t="n"/>
+      <c r="D271" s="1" t="n"/>
+      <c r="E271" s="1" t="n"/>
+      <c r="F271" s="1" t="n"/>
+      <c r="G271" s="1" t="n"/>
+      <c r="H271" s="1" t="n"/>
+      <c r="I271" s="1" t="n"/>
+      <c r="J271" s="1" t="n"/>
+      <c r="K271" s="1" t="n"/>
+      <c r="L271" s="1" t="n"/>
+      <c r="M271" s="1" t="n"/>
+      <c r="N271" s="1" t="n"/>
+      <c r="O271" s="1" t="n"/>
+      <c r="P271" s="1" t="n"/>
+      <c r="Q271" s="1" t="n"/>
     </row>
     <row r="272" ht="22" customHeight="1">
       <c r="A272" s="37" t="inlineStr">
         <is>
+          <t>Wert Ihrer Auswahl netto</t>
+        </is>
+      </c>
+      <c r="Q272" s="38">
+        <f>SUM(Q8:Q269)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="273" ht="22" customHeight="1">
+      <c r="A273" s="37" t="inlineStr">
+        <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q272" s="38">
-        <f>Q271*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="273" ht="26" customHeight="1">
-      <c r="A273" s="39" t="inlineStr">
+      <c r="Q273" s="38">
+        <f>Q272*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="274" ht="26" customHeight="1">
+      <c r="A274" s="39" t="inlineStr">
+        <is>
+          <t>Wert Ihrer Auswahl brutto</t>
+        </is>
+      </c>
+      <c r="Q274" s="40">
+        <f>Q272+Q273</f>
+        <v/>
+      </c>
+    </row>
+    <row r="275" ht="22" customHeight="1">
+      <c r="A275" s="37" t="inlineStr">
+        <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q275" s="41">
+        <f>COUNTIF(N8:N269,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="24" customHeight="1">
+      <c r="A278" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B278" s="44" t="n"/>
+      <c r="C278" s="44" t="n"/>
+      <c r="D278" s="44" t="n"/>
+      <c r="E278" s="44" t="n"/>
+      <c r="F278" s="44" t="n"/>
+      <c r="G278" s="44" t="n"/>
+      <c r="H278" s="44" t="n"/>
+      <c r="I278" s="44" t="n"/>
+      <c r="J278" s="44" t="n"/>
+      <c r="K278" s="44" t="n"/>
+      <c r="L278" s="44" t="n"/>
+      <c r="M278" s="44" t="n"/>
+      <c r="N278" s="44" t="n"/>
+      <c r="O278" s="44" t="n"/>
+      <c r="P278" s="44" t="n"/>
+      <c r="Q278" s="44" t="n"/>
+    </row>
+    <row r="279" ht="22" customHeight="1">
+      <c r="A279" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q279" s="38">
+        <f>SUMPRODUCT(H8:H269,J8:J269)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="280" ht="22" customHeight="1">
+      <c r="A280" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q280" s="38">
+        <f>Q279*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="281" ht="22" customHeight="1">
+      <c r="A281" s="45" t="inlineStr">
+        <is>
+          <t>Gesamtwert brutto</t>
+        </is>
+      </c>
+      <c r="Q281" s="46">
+        <f>Q279+Q280</f>
+        <v/>
+      </c>
+    </row>
+    <row r="283" ht="24" customHeight="1">
+      <c r="A283" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B283" s="48" t="n"/>
+      <c r="C283" s="48" t="n"/>
+      <c r="D283" s="48" t="n"/>
+      <c r="E283" s="48" t="n"/>
+      <c r="F283" s="48" t="n"/>
+      <c r="G283" s="48" t="n"/>
+      <c r="H283" s="48" t="n"/>
+      <c r="I283" s="48" t="n"/>
+      <c r="J283" s="48" t="n"/>
+      <c r="K283" s="48" t="n"/>
+      <c r="L283" s="48" t="n"/>
+      <c r="M283" s="48" t="n"/>
+      <c r="N283" s="48" t="n"/>
+      <c r="O283" s="48" t="n"/>
+      <c r="P283" s="48" t="n"/>
+      <c r="Q283" s="48" t="n"/>
+    </row>
+    <row r="284" ht="22" customHeight="1">
+      <c r="A284" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
+        </is>
+      </c>
+      <c r="Q284" s="38">
+        <f>-Q279*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="285" ht="22" customHeight="1">
+      <c r="A285" s="45" t="inlineStr">
+        <is>
+          <t>Paketpreis netto</t>
+        </is>
+      </c>
+      <c r="Q285" s="46">
+        <f>Q279+Q284</f>
+        <v/>
+      </c>
+    </row>
+    <row r="286" ht="22" customHeight="1">
+      <c r="A286" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q286" s="38">
+        <f>Q285*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="287" ht="26" customHeight="1">
+      <c r="A287" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q273" s="40">
-        <f>Q271+Q272</f>
-        <v/>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" s="42" t="inlineStr">
+      <c r="Q287" s="40">
+        <f>Q285+Q286</f>
+        <v/>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" s="49" t="inlineStr">
+    <row r="290">
+      <c r="A290" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="277"/>
-    <row r="278"/>
-    <row r="279"/>
+    <row r="291"/>
+    <row r="292"/>
+    <row r="293"/>
   </sheetData>
-  <autoFilter ref="A7:Q255"/>
+  <autoFilter ref="A7:Q269"/>
   <mergeCells count="26">
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A259:P259"/>
-    <mergeCell ref="A257:Q257"/>
+    <mergeCell ref="A276:Q276"/>
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A280:P280"/>
+    <mergeCell ref="A274:P274"/>
     <mergeCell ref="L4:Q4"/>
-    <mergeCell ref="A265:P265"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A258:P258"/>
-    <mergeCell ref="A261:P261"/>
-    <mergeCell ref="A270:P270"/>
-    <mergeCell ref="A266:P266"/>
-    <mergeCell ref="A264:Q264"/>
-    <mergeCell ref="A260:P260"/>
+    <mergeCell ref="A271:Q271"/>
+    <mergeCell ref="A283:Q283"/>
+    <mergeCell ref="A279:P279"/>
+    <mergeCell ref="A275:P275"/>
+    <mergeCell ref="A284:P284"/>
+    <mergeCell ref="A287:P287"/>
     <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A271:P271"/>
+    <mergeCell ref="A281:P281"/>
+    <mergeCell ref="A290:Q293"/>
+    <mergeCell ref="A278:Q278"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A269:Q269"/>
-    <mergeCell ref="A262:Q262"/>
-    <mergeCell ref="A276:Q279"/>
+    <mergeCell ref="A286:P286"/>
     <mergeCell ref="A273:P273"/>
-    <mergeCell ref="A267:P267"/>
-    <mergeCell ref="A274:Q274"/>
+    <mergeCell ref="A285:P285"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
     <mergeCell ref="A272:P272"/>
+    <mergeCell ref="A288:Q288"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q255">
+  <conditionalFormatting sqref="A8:Q269">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N255" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N269" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O255" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O269" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$269</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$276</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -6900,89 +6900,264 @@
       <row>265</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="260" name="Image 260" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId260"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>266</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="261" name="Image 261" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId261"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>267</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="260" name="Image 260" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId260"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>266</row>
+        <cNvPr id="262" name="Image 262" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId262"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>268</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="263" name="Image 263" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId263"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>269</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="264" name="Image 264" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId264"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>270</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="261" name="Image 261" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId261"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>267</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="262" name="Image 262" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId262"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>268</row>
+        <cNvPr id="265" name="Image 265" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId265"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>271</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="263" name="Image 263" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId263"/>
+        <cNvPr id="266" name="Image 266" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId266"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>272</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="267" name="Image 267" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId267"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>273</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="268" name="Image 268" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId268"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>274</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="269" name="Image 269" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId269"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>275</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="270" name="Image 270" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId270"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -7285,7 +7460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q293"/>
+  <dimension ref="A1:Q300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -18457,7 +18632,7 @@
         </is>
       </c>
       <c r="H190" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I190" s="10" t="inlineStr">
         <is>
@@ -22879,14 +23054,14 @@
       </c>
       <c r="B264" s="10" t="inlineStr">
         <is>
-          <t>BU02-14</t>
+          <t>BU02-15</t>
         </is>
       </c>
       <c r="C264" s="11" t="n"/>
       <c r="D264" s="12" t="inlineStr">
         <is>
-          <t>Kinderschrank graugrün, zwei Türen
-Hoher Kinderschrank von IKEA mit zwei graugrünen Türen und schwarzen Griffmulden, darunter eine Schublade.</t>
+          <t>Bodensitzkissen beige, selbststehend
+Selbststehendes Bodensitzkissen aus beigem Leinenstoff mit gesteppten Feldern, Rückenlehne und langer Sitzfläche. Die Lehne lässt sich flach ausklappen.</t>
         </is>
       </c>
       <c r="E264" s="13" t="n"/>
@@ -22909,7 +23084,7 @@
         </is>
       </c>
       <c r="J264" s="14" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="K264" s="15">
         <f>J264*1.19</f>
@@ -22939,14 +23114,14 @@
       </c>
       <c r="B265" s="21" t="inlineStr">
         <is>
-          <t>BU02-15</t>
+          <t>BU02-16</t>
         </is>
       </c>
       <c r="C265" s="22" t="n"/>
       <c r="D265" s="23" t="inlineStr">
         <is>
-          <t>Bodensitzkissen beige, selbststehend
-Selbststehendes Bodensitzkissen aus beigem Leinenstoff mit gesteppten Feldern, Rückenlehne und langer Sitzfläche. Die Lehne lässt sich flach ausklappen.</t>
+          <t>Servierwagen Metall schwarz, drei Ebenen
+Rollwagen aus schwarz lackiertem Metall mit drei Ablageebenen und Lochblechböden, auf vier Rollen.</t>
         </is>
       </c>
       <c r="E265" s="13" t="n"/>
@@ -22961,7 +23136,7 @@
         </is>
       </c>
       <c r="H265" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I265" s="21" t="inlineStr">
         <is>
@@ -22969,7 +23144,7 @@
         </is>
       </c>
       <c r="J265" s="24" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K265" s="25">
         <f>J265*1.19</f>
@@ -22999,14 +23174,14 @@
       </c>
       <c r="B266" s="10" t="inlineStr">
         <is>
-          <t>BU02-16</t>
+          <t>BU02-17</t>
         </is>
       </c>
       <c r="C266" s="11" t="n"/>
       <c r="D266" s="12" t="inlineStr">
         <is>
-          <t>Servierwagen Metall schwarz, drei Ebenen
-Rollwagen aus schwarz lackiertem Metall mit drei Ablageebenen und Lochblechböden, auf vier Rollen.</t>
+          <t>Kommode weiß, drei Schubladen
+Kommode in Weiß mit drei breiten Schubladen und mittig ausgeschnittenen Griffmulden, auf umlaufendem Sockel.</t>
         </is>
       </c>
       <c r="E266" s="13" t="n"/>
@@ -23029,7 +23204,7 @@
         </is>
       </c>
       <c r="J266" s="14" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K266" s="15">
         <f>J266*1.19</f>
@@ -23059,17 +23234,21 @@
       </c>
       <c r="B267" s="21" t="inlineStr">
         <is>
-          <t>BU02-17</t>
+          <t>BU02-18</t>
         </is>
       </c>
       <c r="C267" s="22" t="n"/>
       <c r="D267" s="23" t="inlineStr">
         <is>
-          <t>Kommode weiß, drei Schubladen
-Kommode in Weiß mit drei breiten Schubladen und mittig ausgeschnittenen Griffmulden, auf umlaufendem Sockel.</t>
-        </is>
-      </c>
-      <c r="E267" s="13" t="n"/>
+          <t>Hochflorteppich grau
+Hochflorteppich in Grau, rechteckig. Maße laut Etikett auf der Rückseite: 160 × 230 cm.</t>
+        </is>
+      </c>
+      <c r="E267" s="13" t="inlineStr">
+        <is>
+          <t>160 × 230 cm</t>
+        </is>
+      </c>
       <c r="F267" s="23" t="inlineStr">
         <is>
           <t>Flur 2</t>
@@ -23089,7 +23268,7 @@
         </is>
       </c>
       <c r="J267" s="24" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K267" s="25">
         <f>J267*1.19</f>
@@ -23102,7 +23281,7 @@
       </c>
       <c r="M267" s="23" t="inlineStr">
         <is>
-          <t>nur Abholung</t>
+          <t>Versand möglich</t>
         </is>
       </c>
       <c r="N267" s="16" t="n"/>
@@ -23119,21 +23298,17 @@
       </c>
       <c r="B268" s="10" t="inlineStr">
         <is>
-          <t>BU02-18</t>
+          <t>BU02-19</t>
         </is>
       </c>
       <c r="C268" s="11" t="n"/>
       <c r="D268" s="12" t="inlineStr">
         <is>
-          <t>Hochflorteppich grau
-Hochflorteppich in Grau, rechteckig. Etikett auf der Rückseite vorhanden, Maßangabe 160 × 230 cm.</t>
-        </is>
-      </c>
-      <c r="E268" s="13" t="inlineStr">
-        <is>
-          <t>160 × 230 cm</t>
-        </is>
-      </c>
+          <t>Spielmöbel Kiefer, dreiteilig
+Dreiteilige Kombination aus Kiefer massiv: Wandregal mit zwei Kunststoffwannen, niedrige Werkbank mit offenem Unterbau und zwei Wannen sowie ein hohes Seitenteil mit Wanne.</t>
+        </is>
+      </c>
+      <c r="E268" s="13" t="n"/>
       <c r="F268" s="12" t="inlineStr">
         <is>
           <t>Flur 2</t>
@@ -23149,11 +23324,11 @@
       </c>
       <c r="I268" s="10" t="inlineStr">
         <is>
-          <t>Stück</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="J268" s="14" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="K268" s="15">
         <f>J268*1.19</f>
@@ -23166,7 +23341,7 @@
       </c>
       <c r="M268" s="12" t="inlineStr">
         <is>
-          <t>Versand möglich</t>
+          <t>nur Abholung</t>
         </is>
       </c>
       <c r="N268" s="16" t="n"/>
@@ -23183,20 +23358,20 @@
       </c>
       <c r="B269" s="21" t="inlineStr">
         <is>
-          <t>BU02-19</t>
+          <t>BU03-01</t>
         </is>
       </c>
       <c r="C269" s="22" t="n"/>
       <c r="D269" s="23" t="inlineStr">
         <is>
-          <t>Spielmöbel Kiefer, dreiteilig
-Dreiteilige Kombination aus Kiefer massiv: Wandregal mit zwei Kunststoffwannen, niedrige Werkbank mit offenem Unterbau und zwei Wannen sowie ein hohes Seitenteil mit Wanne.</t>
+          <t>Pinnwand Holz mit Klammerleinen
+Großes Wandelement aus hellem Massivholz mit vier waagerechten Bändern und Holzklammern zum Aufhängen von Bildern und Bastelarbeiten. Zwei zusätzliche Querbretter als Ablage.</t>
         </is>
       </c>
       <c r="E269" s="13" t="n"/>
       <c r="F269" s="23" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur 3</t>
         </is>
       </c>
       <c r="G269" s="21" t="inlineStr">
@@ -23209,11 +23384,11 @@
       </c>
       <c r="I269" s="21" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Stück</t>
         </is>
       </c>
       <c r="J269" s="24" t="n">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="K269" s="25">
         <f>J269*1.19</f>
@@ -23237,111 +23412,457 @@
         <v/>
       </c>
     </row>
-    <row r="271" ht="24" customHeight="1">
-      <c r="A271" s="36" t="inlineStr">
+    <row r="270" ht="78" customHeight="1">
+      <c r="A270" s="9" t="n">
+        <v>263</v>
+      </c>
+      <c r="B270" s="10" t="inlineStr">
+        <is>
+          <t>BU03-02</t>
+        </is>
+      </c>
+      <c r="C270" s="11" t="n"/>
+      <c r="D270" s="12" t="inlineStr">
+        <is>
+          <t>Schwingspiegel, geschwungene Form
+Hoher Wandspiegel mit geschwungener Außenkante ohne Rahmen, zum Anschrauben.</t>
+        </is>
+      </c>
+      <c r="E270" s="13" t="n"/>
+      <c r="F270" s="12" t="inlineStr">
+        <is>
+          <t>Flur 3</t>
+        </is>
+      </c>
+      <c r="G270" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H270" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I270" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J270" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K270" s="15">
+        <f>J270*1.19</f>
+        <v/>
+      </c>
+      <c r="L270" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M270" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N270" s="16" t="n"/>
+      <c r="O270" s="17" t="n"/>
+      <c r="P270" s="18" t="n"/>
+      <c r="Q270" s="19">
+        <f>IF(N270&lt;&gt;"ja","",IF(O270="",H270,O270)*J270)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="271" ht="78" customHeight="1">
+      <c r="A271" s="20" t="n">
+        <v>264</v>
+      </c>
+      <c r="B271" s="21" t="inlineStr">
+        <is>
+          <t>BU03-03</t>
+        </is>
+      </c>
+      <c r="C271" s="22" t="n"/>
+      <c r="D271" s="23" t="inlineStr">
+        <is>
+          <t>Schuhregal schwarz mit Chromstangen
+Niedriges Schuhregal aus schwarz lackiertem Holz mit schwarzer Deckplatte und drei Ebenen aus verchromten Rundstangen, auch als Sitzbank nutzbar.</t>
+        </is>
+      </c>
+      <c r="E271" s="13" t="n"/>
+      <c r="F271" s="23" t="inlineStr">
+        <is>
+          <t>Flur 3</t>
+        </is>
+      </c>
+      <c r="G271" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H271" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I271" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J271" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="K271" s="25">
+        <f>J271*1.19</f>
+        <v/>
+      </c>
+      <c r="L271" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M271" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N271" s="16" t="n"/>
+      <c r="O271" s="17" t="n"/>
+      <c r="P271" s="18" t="n"/>
+      <c r="Q271" s="26">
+        <f>IF(N271&lt;&gt;"ja","",IF(O271="",H271,O271)*J271)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="272" ht="78" customHeight="1">
+      <c r="A272" s="9" t="n">
+        <v>265</v>
+      </c>
+      <c r="B272" s="10" t="inlineStr">
+        <is>
+          <t>BU03-04</t>
+        </is>
+      </c>
+      <c r="C272" s="11" t="n"/>
+      <c r="D272" s="12" t="inlineStr">
+        <is>
+          <t>Metallregal weiß, vier Böden
+Offenes Regal mit weißem Metallgestell, Kreuzstrebe auf der Rückseite und vier weißen Böden.</t>
+        </is>
+      </c>
+      <c r="E272" s="13" t="n"/>
+      <c r="F272" s="12" t="inlineStr">
+        <is>
+          <t>Flur 3</t>
+        </is>
+      </c>
+      <c r="G272" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H272" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I272" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J272" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K272" s="15">
+        <f>J272*1.19</f>
+        <v/>
+      </c>
+      <c r="L272" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M272" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N272" s="16" t="n"/>
+      <c r="O272" s="17" t="n"/>
+      <c r="P272" s="18" t="n"/>
+      <c r="Q272" s="19">
+        <f>IF(N272&lt;&gt;"ja","",IF(O272="",H272,O272)*J272)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="273" ht="78" customHeight="1">
+      <c r="A273" s="20" t="n">
+        <v>266</v>
+      </c>
+      <c r="B273" s="21" t="inlineStr">
+        <is>
+          <t>BU03-05</t>
+        </is>
+      </c>
+      <c r="C273" s="22" t="n"/>
+      <c r="D273" s="23" t="inlineStr">
+        <is>
+          <t>Schuhschrank weiß mit Klappfächern
+Schmaler Schuhschrank in Weiß mit zwei Klappfächern und schwarzen Knöpfen. Die Schuhablagen sind innen verschmutzt und an den Kanten abgestoßen.</t>
+        </is>
+      </c>
+      <c r="E273" s="13" t="n"/>
+      <c r="F273" s="23" t="inlineStr">
+        <is>
+          <t>Flur 3</t>
+        </is>
+      </c>
+      <c r="G273" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H273" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I273" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J273" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="K273" s="25">
+        <f>J273*1.19</f>
+        <v/>
+      </c>
+      <c r="L273" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M273" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N273" s="16" t="n"/>
+      <c r="O273" s="17" t="n"/>
+      <c r="P273" s="18" t="n"/>
+      <c r="Q273" s="26">
+        <f>IF(N273&lt;&gt;"ja","",IF(O273="",H273,O273)*J273)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="274" ht="78" customHeight="1">
+      <c r="A274" s="9" t="n">
+        <v>267</v>
+      </c>
+      <c r="B274" s="10" t="inlineStr">
+        <is>
+          <t>BU03-06</t>
+        </is>
+      </c>
+      <c r="C274" s="11" t="n"/>
+      <c r="D274" s="12" t="inlineStr">
+        <is>
+          <t>Wäschekorb anthrazit mit Deckel, hoch
+Hoher Wäschekorb aus Kunststoff in Flechtoptik, anthrazit, nach unten verjüngt, mit aufklappbarem Deckel und Griffloch.</t>
+        </is>
+      </c>
+      <c r="E274" s="13" t="n"/>
+      <c r="F274" s="12" t="inlineStr">
+        <is>
+          <t>Flur 3</t>
+        </is>
+      </c>
+      <c r="G274" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H274" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I274" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J274" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="K274" s="15">
+        <f>J274*1.19</f>
+        <v/>
+      </c>
+      <c r="L274" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M274" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N274" s="16" t="n"/>
+      <c r="O274" s="17" t="n"/>
+      <c r="P274" s="18" t="n"/>
+      <c r="Q274" s="19">
+        <f>IF(N274&lt;&gt;"ja","",IF(O274="",H274,O274)*J274)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="275" ht="78" customHeight="1">
+      <c r="A275" s="20" t="n">
+        <v>268</v>
+      </c>
+      <c r="B275" s="21" t="inlineStr">
+        <is>
+          <t>BU03-07</t>
+        </is>
+      </c>
+      <c r="C275" s="22" t="n"/>
+      <c r="D275" s="23" t="inlineStr">
+        <is>
+          <t>Tischleuchte Holzgestell mit Stoffschirm
+Tischleuchte mit dreieckigem Gestell aus hellem Holz und zylindrischem Stoffschirm in Hellgrau, mit Schnurschalter.</t>
+        </is>
+      </c>
+      <c r="E275" s="13" t="n"/>
+      <c r="F275" s="23" t="inlineStr">
+        <is>
+          <t>Flur 3</t>
+        </is>
+      </c>
+      <c r="G275" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H275" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I275" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J275" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="K275" s="25">
+        <f>J275*1.19</f>
+        <v/>
+      </c>
+      <c r="L275" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M275" s="23" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N275" s="16" t="n"/>
+      <c r="O275" s="17" t="n"/>
+      <c r="P275" s="18" t="n"/>
+      <c r="Q275" s="26">
+        <f>IF(N275&lt;&gt;"ja","",IF(O275="",H275,O275)*J275)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="276" ht="78" customHeight="1">
+      <c r="A276" s="9" t="n">
+        <v>269</v>
+      </c>
+      <c r="B276" s="10" t="inlineStr">
+        <is>
+          <t>BU03-08</t>
+        </is>
+      </c>
+      <c r="C276" s="11" t="n"/>
+      <c r="D276" s="12" t="inlineStr">
+        <is>
+          <t>Beistelltisch rund türkis mit Hairpin-Beinen
+Kleiner runder Beistelltisch mit türkis lackierter Holzplatte auf drei schwarzen Hairpin-Beinen aus Rundstahl. Die Platte ist leicht verkratzt.</t>
+        </is>
+      </c>
+      <c r="E276" s="13" t="n"/>
+      <c r="F276" s="12" t="inlineStr">
+        <is>
+          <t>Flur 3</t>
+        </is>
+      </c>
+      <c r="G276" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H276" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I276" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J276" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K276" s="15">
+        <f>J276*1.19</f>
+        <v/>
+      </c>
+      <c r="L276" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M276" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N276" s="16" t="n"/>
+      <c r="O276" s="17" t="n"/>
+      <c r="P276" s="18" t="n"/>
+      <c r="Q276" s="19">
+        <f>IF(N276&lt;&gt;"ja","",IF(O276="",H276,O276)*J276)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="278" ht="24" customHeight="1">
+      <c r="A278" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B271" s="1" t="n"/>
-      <c r="C271" s="1" t="n"/>
-      <c r="D271" s="1" t="n"/>
-      <c r="E271" s="1" t="n"/>
-      <c r="F271" s="1" t="n"/>
-      <c r="G271" s="1" t="n"/>
-      <c r="H271" s="1" t="n"/>
-      <c r="I271" s="1" t="n"/>
-      <c r="J271" s="1" t="n"/>
-      <c r="K271" s="1" t="n"/>
-      <c r="L271" s="1" t="n"/>
-      <c r="M271" s="1" t="n"/>
-      <c r="N271" s="1" t="n"/>
-      <c r="O271" s="1" t="n"/>
-      <c r="P271" s="1" t="n"/>
-      <c r="Q271" s="1" t="n"/>
-    </row>
-    <row r="272" ht="22" customHeight="1">
-      <c r="A272" s="37" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl netto</t>
-        </is>
-      </c>
-      <c r="Q272" s="38">
-        <f>SUM(Q8:Q269)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="273" ht="22" customHeight="1">
-      <c r="A273" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q273" s="38">
-        <f>Q272*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="274" ht="26" customHeight="1">
-      <c r="A274" s="39" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl brutto</t>
-        </is>
-      </c>
-      <c r="Q274" s="40">
-        <f>Q272+Q273</f>
-        <v/>
-      </c>
-    </row>
-    <row r="275" ht="22" customHeight="1">
-      <c r="A275" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q275" s="41">
-        <f>COUNTIF(N8:N269,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="278" ht="24" customHeight="1">
-      <c r="A278" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B278" s="44" t="n"/>
-      <c r="C278" s="44" t="n"/>
-      <c r="D278" s="44" t="n"/>
-      <c r="E278" s="44" t="n"/>
-      <c r="F278" s="44" t="n"/>
-      <c r="G278" s="44" t="n"/>
-      <c r="H278" s="44" t="n"/>
-      <c r="I278" s="44" t="n"/>
-      <c r="J278" s="44" t="n"/>
-      <c r="K278" s="44" t="n"/>
-      <c r="L278" s="44" t="n"/>
-      <c r="M278" s="44" t="n"/>
-      <c r="N278" s="44" t="n"/>
-      <c r="O278" s="44" t="n"/>
-      <c r="P278" s="44" t="n"/>
-      <c r="Q278" s="44" t="n"/>
+      <c r="B278" s="1" t="n"/>
+      <c r="C278" s="1" t="n"/>
+      <c r="D278" s="1" t="n"/>
+      <c r="E278" s="1" t="n"/>
+      <c r="F278" s="1" t="n"/>
+      <c r="G278" s="1" t="n"/>
+      <c r="H278" s="1" t="n"/>
+      <c r="I278" s="1" t="n"/>
+      <c r="J278" s="1" t="n"/>
+      <c r="K278" s="1" t="n"/>
+      <c r="L278" s="1" t="n"/>
+      <c r="M278" s="1" t="n"/>
+      <c r="N278" s="1" t="n"/>
+      <c r="O278" s="1" t="n"/>
+      <c r="P278" s="1" t="n"/>
+      <c r="Q278" s="1" t="n"/>
     </row>
     <row r="279" ht="22" customHeight="1">
       <c r="A279" s="37" t="inlineStr">
         <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
+          <t>Wert Ihrer Auswahl netto</t>
         </is>
       </c>
       <c r="Q279" s="38">
-        <f>SUMPRODUCT(H8:H269,J8:J269)</f>
+        <f>SUM(Q8:Q276)</f>
         <v/>
       </c>
     </row>
@@ -23356,142 +23877,216 @@
         <v/>
       </c>
     </row>
-    <row r="281" ht="22" customHeight="1">
-      <c r="A281" s="45" t="inlineStr">
-        <is>
-          <t>Gesamtwert brutto</t>
-        </is>
-      </c>
-      <c r="Q281" s="46">
+    <row r="281" ht="26" customHeight="1">
+      <c r="A281" s="39" t="inlineStr">
+        <is>
+          <t>Wert Ihrer Auswahl brutto</t>
+        </is>
+      </c>
+      <c r="Q281" s="40">
         <f>Q279+Q280</f>
         <v/>
       </c>
     </row>
-    <row r="283" ht="24" customHeight="1">
-      <c r="A283" s="47" t="inlineStr">
-        <is>
-          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B283" s="48" t="n"/>
-      <c r="C283" s="48" t="n"/>
-      <c r="D283" s="48" t="n"/>
-      <c r="E283" s="48" t="n"/>
-      <c r="F283" s="48" t="n"/>
-      <c r="G283" s="48" t="n"/>
-      <c r="H283" s="48" t="n"/>
-      <c r="I283" s="48" t="n"/>
-      <c r="J283" s="48" t="n"/>
-      <c r="K283" s="48" t="n"/>
-      <c r="L283" s="48" t="n"/>
-      <c r="M283" s="48" t="n"/>
-      <c r="N283" s="48" t="n"/>
-      <c r="O283" s="48" t="n"/>
-      <c r="P283" s="48" t="n"/>
-      <c r="Q283" s="48" t="n"/>
-    </row>
-    <row r="284" ht="22" customHeight="1">
-      <c r="A284" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
-        </is>
-      </c>
-      <c r="Q284" s="38">
-        <f>-Q279*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="285" ht="22" customHeight="1">
-      <c r="A285" s="45" t="inlineStr">
-        <is>
-          <t>Paketpreis netto</t>
-        </is>
-      </c>
-      <c r="Q285" s="46">
-        <f>Q279+Q284</f>
-        <v/>
-      </c>
+    <row r="282" ht="22" customHeight="1">
+      <c r="A282" s="37" t="inlineStr">
+        <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q282" s="41">
+        <f>COUNTIF(N8:N276,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="24" customHeight="1">
+      <c r="A285" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B285" s="44" t="n"/>
+      <c r="C285" s="44" t="n"/>
+      <c r="D285" s="44" t="n"/>
+      <c r="E285" s="44" t="n"/>
+      <c r="F285" s="44" t="n"/>
+      <c r="G285" s="44" t="n"/>
+      <c r="H285" s="44" t="n"/>
+      <c r="I285" s="44" t="n"/>
+      <c r="J285" s="44" t="n"/>
+      <c r="K285" s="44" t="n"/>
+      <c r="L285" s="44" t="n"/>
+      <c r="M285" s="44" t="n"/>
+      <c r="N285" s="44" t="n"/>
+      <c r="O285" s="44" t="n"/>
+      <c r="P285" s="44" t="n"/>
+      <c r="Q285" s="44" t="n"/>
     </row>
     <row r="286" ht="22" customHeight="1">
       <c r="A286" s="37" t="inlineStr">
         <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q286" s="38">
+        <f>SUMPRODUCT(H8:H276,J8:J276)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="287" ht="22" customHeight="1">
+      <c r="A287" s="37" t="inlineStr">
+        <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q286" s="38">
-        <f>Q285*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="287" ht="26" customHeight="1">
-      <c r="A287" s="39" t="inlineStr">
+      <c r="Q287" s="38">
+        <f>Q286*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="288" ht="22" customHeight="1">
+      <c r="A288" s="45" t="inlineStr">
+        <is>
+          <t>Gesamtwert brutto</t>
+        </is>
+      </c>
+      <c r="Q288" s="46">
+        <f>Q286+Q287</f>
+        <v/>
+      </c>
+    </row>
+    <row r="290" ht="24" customHeight="1">
+      <c r="A290" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B290" s="48" t="n"/>
+      <c r="C290" s="48" t="n"/>
+      <c r="D290" s="48" t="n"/>
+      <c r="E290" s="48" t="n"/>
+      <c r="F290" s="48" t="n"/>
+      <c r="G290" s="48" t="n"/>
+      <c r="H290" s="48" t="n"/>
+      <c r="I290" s="48" t="n"/>
+      <c r="J290" s="48" t="n"/>
+      <c r="K290" s="48" t="n"/>
+      <c r="L290" s="48" t="n"/>
+      <c r="M290" s="48" t="n"/>
+      <c r="N290" s="48" t="n"/>
+      <c r="O290" s="48" t="n"/>
+      <c r="P290" s="48" t="n"/>
+      <c r="Q290" s="48" t="n"/>
+    </row>
+    <row r="291" ht="22" customHeight="1">
+      <c r="A291" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
+        </is>
+      </c>
+      <c r="Q291" s="38">
+        <f>-Q286*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="292" ht="22" customHeight="1">
+      <c r="A292" s="45" t="inlineStr">
+        <is>
+          <t>Paketpreis netto</t>
+        </is>
+      </c>
+      <c r="Q292" s="46">
+        <f>Q286+Q291</f>
+        <v/>
+      </c>
+    </row>
+    <row r="293" ht="22" customHeight="1">
+      <c r="A293" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q293" s="38">
+        <f>Q292*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="294" ht="26" customHeight="1">
+      <c r="A294" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q287" s="40">
-        <f>Q285+Q286</f>
-        <v/>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" s="42" t="inlineStr">
+      <c r="Q294" s="40">
+        <f>Q292+Q293</f>
+        <v/>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="290">
-      <c r="A290" s="49" t="inlineStr">
+    <row r="297">
+      <c r="A297" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="291"/>
-    <row r="292"/>
-    <row r="293"/>
+    <row r="298"/>
+    <row r="299"/>
+    <row r="300"/>
   </sheetData>
-  <autoFilter ref="A7:Q269"/>
+  <autoFilter ref="A7:Q276"/>
   <mergeCells count="26">
+    <mergeCell ref="A295:Q295"/>
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A276:Q276"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A280:P280"/>
-    <mergeCell ref="A274:P274"/>
     <mergeCell ref="L4:Q4"/>
+    <mergeCell ref="A293:P293"/>
+    <mergeCell ref="A288:P288"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A271:Q271"/>
+    <mergeCell ref="A297:Q300"/>
     <mergeCell ref="A283:Q283"/>
     <mergeCell ref="A279:P279"/>
-    <mergeCell ref="A275:P275"/>
-    <mergeCell ref="A284:P284"/>
+    <mergeCell ref="A291:P291"/>
     <mergeCell ref="A287:P287"/>
+    <mergeCell ref="A285:Q285"/>
     <mergeCell ref="C4:I4"/>
     <mergeCell ref="A281:P281"/>
-    <mergeCell ref="A290:Q293"/>
     <mergeCell ref="A278:Q278"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
+    <mergeCell ref="A292:P292"/>
+    <mergeCell ref="A290:Q290"/>
     <mergeCell ref="A286:P286"/>
-    <mergeCell ref="A273:P273"/>
-    <mergeCell ref="A285:P285"/>
+    <mergeCell ref="A282:P282"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A272:P272"/>
-    <mergeCell ref="A288:Q288"/>
+    <mergeCell ref="A294:P294"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q269">
+  <conditionalFormatting sqref="A8:Q276">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N269" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N276" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O269" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O276" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$276</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$284</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7168,6 +7168,206 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>276</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="271" name="Image 271" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId271"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>277</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="272" name="Image 272" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId272"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>278</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="273" name="Image 273" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId273"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>279</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="274" name="Image 274" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId274"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>280</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="275" name="Image 275" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId275"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>281</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="276" name="Image 276" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId276"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>282</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="277" name="Image 277" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId277"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>283</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="278" name="Image 278" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId278"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -7460,7 +7660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q300"/>
+  <dimension ref="A1:Q308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9657,7 +9857,7 @@
       </c>
       <c r="B41" s="21" t="inlineStr">
         <is>
-          <t>BU04-05</t>
+          <t>BU04-16</t>
         </is>
       </c>
       <c r="C41" s="22" t="n"/>
@@ -15257,7 +15457,7 @@
       <c r="D134" s="12" t="inlineStr">
         <is>
           <t>IKEA Kinderhochstuhl mit Gurt
-Kinderhochstuhl von IKEA: weiße Kunststoffschale, graue Stahlbeine, Sicherheitsgurt. Ohne Esstablett.</t>
+Kinderhochstuhl von IKEA: weiße Kunststoffschale, graue Stahlbeine, Sicherheitsgurt. Ein Teil der Stühle hat ein Esstablett.</t>
         </is>
       </c>
       <c r="E134" s="13" t="n"/>
@@ -15272,7 +15472,7 @@
         </is>
       </c>
       <c r="H134" s="10" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I134" s="10" t="inlineStr">
         <is>
@@ -18632,7 +18832,7 @@
         </is>
       </c>
       <c r="H190" s="10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I190" s="10" t="inlineStr">
         <is>
@@ -23320,7 +23520,7 @@
         </is>
       </c>
       <c r="H268" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I268" s="10" t="inlineStr">
         <is>
@@ -23832,261 +24032,741 @@
         <v/>
       </c>
     </row>
-    <row r="278" ht="24" customHeight="1">
-      <c r="A278" s="36" t="inlineStr">
+    <row r="277" ht="78" customHeight="1">
+      <c r="A277" s="20" t="n">
+        <v>270</v>
+      </c>
+      <c r="B277" s="21" t="inlineStr">
+        <is>
+          <t>BU04-06</t>
+        </is>
+      </c>
+      <c r="C277" s="22" t="n"/>
+      <c r="D277" s="23" t="inlineStr">
+        <is>
+          <t>Kindertisch weiß, lang, zweiteilig
+Langer Kindertisch aus zwei aneinandergestellten Platten in Weiß mit cremefarbener Kante, auf cremefarbenen Vierkantfüßen aus Metall mit Gleitern. Die Platten sind an den Kanten abgestoßen.</t>
+        </is>
+      </c>
+      <c r="E277" s="13" t="n"/>
+      <c r="F277" s="23" t="inlineStr">
+        <is>
+          <t>Gruppenraum</t>
+        </is>
+      </c>
+      <c r="G277" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H277" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I277" s="21" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="J277" s="24" t="n">
+        <v>90</v>
+      </c>
+      <c r="K277" s="25">
+        <f>J277*1.19</f>
+        <v/>
+      </c>
+      <c r="L277" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M277" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N277" s="16" t="n"/>
+      <c r="O277" s="17" t="n"/>
+      <c r="P277" s="18" t="n"/>
+      <c r="Q277" s="26">
+        <f>IF(N277&lt;&gt;"ja","",IF(O277="",H277,O277)*J277)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="278" ht="78" customHeight="1">
+      <c r="A278" s="9" t="n">
+        <v>271</v>
+      </c>
+      <c r="B278" s="10" t="inlineStr">
+        <is>
+          <t>BU04-07</t>
+        </is>
+      </c>
+      <c r="C278" s="11" t="n"/>
+      <c r="D278" s="12" t="inlineStr">
+        <is>
+          <t>Gemälde Schwarzwaldfrau mit Planeten
+Acryl auf Leinwand im Hochformat: Frau in Schwarzwälder Tracht mit Bollenhut, umgeben von gemalten Planeten und Sternen. Eigenarbeit einer Privatperson, nicht signiert.</t>
+        </is>
+      </c>
+      <c r="E278" s="13" t="n"/>
+      <c r="F278" s="12" t="inlineStr">
+        <is>
+          <t>Gruppenraum</t>
+        </is>
+      </c>
+      <c r="G278" s="10" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H278" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I278" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J278" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="K278" s="15">
+        <f>J278*1.19</f>
+        <v/>
+      </c>
+      <c r="L278" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M278" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N278" s="16" t="n"/>
+      <c r="O278" s="17" t="n"/>
+      <c r="P278" s="18" t="n"/>
+      <c r="Q278" s="19">
+        <f>IF(N278&lt;&gt;"ja","",IF(O278="",H278,O278)*J278)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="279" ht="78" customHeight="1">
+      <c r="A279" s="20" t="n">
+        <v>272</v>
+      </c>
+      <c r="B279" s="21" t="inlineStr">
+        <is>
+          <t>BU04-08</t>
+        </is>
+      </c>
+      <c r="C279" s="22" t="n"/>
+      <c r="D279" s="23" t="inlineStr">
+        <is>
+          <t>Garderobenständer bunt, Stangenform
+Stehender Garderobenständer: weiße Rundstange mit farbig lackierten Ringen in Grün, Blau, Rot, Orange und Gelb und passenden Haken in mehreren Höhen, auf Tellerfuß.</t>
+        </is>
+      </c>
+      <c r="E279" s="13" t="n"/>
+      <c r="F279" s="23" t="inlineStr">
+        <is>
+          <t>Gruppenraum</t>
+        </is>
+      </c>
+      <c r="G279" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H279" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I279" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J279" s="24" t="n">
+        <v>35</v>
+      </c>
+      <c r="K279" s="25">
+        <f>J279*1.19</f>
+        <v/>
+      </c>
+      <c r="L279" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M279" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N279" s="16" t="n"/>
+      <c r="O279" s="17" t="n"/>
+      <c r="P279" s="18" t="n"/>
+      <c r="Q279" s="26">
+        <f>IF(N279&lt;&gt;"ja","",IF(O279="",H279,O279)*J279)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="280" ht="78" customHeight="1">
+      <c r="A280" s="9" t="n">
+        <v>273</v>
+      </c>
+      <c r="B280" s="35" t="inlineStr">
+        <is>
+          <t>BU04-10</t>
+        </is>
+      </c>
+      <c r="C280" s="11" t="n"/>
+      <c r="D280" s="12" t="inlineStr">
+        <is>
+          <t>Kindertisch weiß aus fünf Segmenten
+Fünf Tischsegmente mit weißer Platte, Multiplex-Kante und verchromten Rundfüßen in Kinderhöhe. Zusammengestellt ergeben sie einen großen Gruppentisch, einzeln sind sie frei kombinierbar.</t>
+        </is>
+      </c>
+      <c r="E280" s="13" t="n"/>
+      <c r="F280" s="12" t="inlineStr">
+        <is>
+          <t>Gruppenraum</t>
+        </is>
+      </c>
+      <c r="G280" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H280" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I280" s="10" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="J280" s="14" t="n">
+        <v>190</v>
+      </c>
+      <c r="K280" s="15">
+        <f>J280*1.19</f>
+        <v/>
+      </c>
+      <c r="L280" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M280" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N280" s="16" t="n"/>
+      <c r="O280" s="17" t="n"/>
+      <c r="P280" s="18" t="n"/>
+      <c r="Q280" s="19">
+        <f>IF(N280&lt;&gt;"ja","",IF(O280="",H280,O280)*J280)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="281" ht="78" customHeight="1">
+      <c r="A281" s="20" t="n">
+        <v>274</v>
+      </c>
+      <c r="B281" s="21" t="inlineStr">
+        <is>
+          <t>BU04-11</t>
+        </is>
+      </c>
+      <c r="C281" s="22" t="n"/>
+      <c r="D281" s="23" t="inlineStr">
+        <is>
+          <t>Regal weiß, vier Böden
+Offenes Regal in Weiß mit vier Böden, eines der beiden Regale hat zusätzlich zwei Schubladen. Böden und Kanten sind großflächig verschmutzt und abgestoßen.</t>
+        </is>
+      </c>
+      <c r="E281" s="13" t="n"/>
+      <c r="F281" s="23" t="inlineStr">
+        <is>
+          <t>Gruppenraum</t>
+        </is>
+      </c>
+      <c r="G281" s="21" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="H281" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I281" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J281" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="K281" s="25">
+        <f>J281*1.19</f>
+        <v/>
+      </c>
+      <c r="L281" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M281" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N281" s="16" t="n"/>
+      <c r="O281" s="17" t="n"/>
+      <c r="P281" s="18" t="n"/>
+      <c r="Q281" s="26">
+        <f>IF(N281&lt;&gt;"ja","",IF(O281="",H281,O281)*J281)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="282" ht="78" customHeight="1">
+      <c r="A282" s="9" t="n">
+        <v>275</v>
+      </c>
+      <c r="B282" s="10" t="inlineStr">
+        <is>
+          <t>BU04-13</t>
+        </is>
+      </c>
+      <c r="C282" s="11" t="n"/>
+      <c r="D282" s="12" t="inlineStr">
+        <is>
+          <t>Servierwagen Metall grau, drei Ebenen
+Rollwagen aus dunkelgrau lackiertem Metall mit drei Ablageebenen und Lochblechböden, auf vier Rollen.</t>
+        </is>
+      </c>
+      <c r="E282" s="13" t="n"/>
+      <c r="F282" s="12" t="inlineStr">
+        <is>
+          <t>Gruppenraum</t>
+        </is>
+      </c>
+      <c r="G282" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H282" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I282" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J282" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="K282" s="15">
+        <f>J282*1.19</f>
+        <v/>
+      </c>
+      <c r="L282" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M282" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N282" s="16" t="n"/>
+      <c r="O282" s="17" t="n"/>
+      <c r="P282" s="18" t="n"/>
+      <c r="Q282" s="19">
+        <f>IF(N282&lt;&gt;"ja","",IF(O282="",H282,O282)*J282)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="283" ht="78" customHeight="1">
+      <c r="A283" s="20" t="n">
+        <v>276</v>
+      </c>
+      <c r="B283" s="21" t="inlineStr">
+        <is>
+          <t>BU04-14</t>
+        </is>
+      </c>
+      <c r="C283" s="22" t="n"/>
+      <c r="D283" s="23" t="inlineStr">
+        <is>
+          <t>Bücherregal creme mit Wolkenaufsatz
+Stehendes Bücherregal aus Holz, creme lackiert, mit geschwungenem Wolkenaufsatz und drei Ablagen mit vorderer Haltelatte für nach vorn zeigende Bilderbücher.</t>
+        </is>
+      </c>
+      <c r="E283" s="13" t="n"/>
+      <c r="F283" s="23" t="inlineStr">
+        <is>
+          <t>Gruppenraum</t>
+        </is>
+      </c>
+      <c r="G283" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H283" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I283" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J283" s="24" t="n">
+        <v>45</v>
+      </c>
+      <c r="K283" s="25">
+        <f>J283*1.19</f>
+        <v/>
+      </c>
+      <c r="L283" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M283" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N283" s="16" t="n"/>
+      <c r="O283" s="17" t="n"/>
+      <c r="P283" s="18" t="n"/>
+      <c r="Q283" s="26">
+        <f>IF(N283&lt;&gt;"ja","",IF(O283="",H283,O283)*J283)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="284" ht="78" customHeight="1">
+      <c r="A284" s="9" t="n">
+        <v>277</v>
+      </c>
+      <c r="B284" s="10" t="inlineStr">
+        <is>
+          <t>BU04-15</t>
+        </is>
+      </c>
+      <c r="C284" s="11" t="n"/>
+      <c r="D284" s="12" t="inlineStr">
+        <is>
+          <t>Acrylbilder Roboter, schwarz-weiß
+Zwei Bilder auf Leinwand im Quadrat: Roboterfiguren mit breitem Pinsel in Schwarz auf weißem Grund. Eigenarbeit einer Privatperson, nicht signiert.</t>
+        </is>
+      </c>
+      <c r="E284" s="13" t="n"/>
+      <c r="F284" s="12" t="inlineStr">
+        <is>
+          <t>Gruppenraum</t>
+        </is>
+      </c>
+      <c r="G284" s="10" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H284" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I284" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J284" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="K284" s="15">
+        <f>J284*1.19</f>
+        <v/>
+      </c>
+      <c r="L284" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M284" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N284" s="16" t="n"/>
+      <c r="O284" s="17" t="n"/>
+      <c r="P284" s="18" t="n"/>
+      <c r="Q284" s="19">
+        <f>IF(N284&lt;&gt;"ja","",IF(O284="",H284,O284)*J284)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="286" ht="24" customHeight="1">
+      <c r="A286" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B278" s="1" t="n"/>
-      <c r="C278" s="1" t="n"/>
-      <c r="D278" s="1" t="n"/>
-      <c r="E278" s="1" t="n"/>
-      <c r="F278" s="1" t="n"/>
-      <c r="G278" s="1" t="n"/>
-      <c r="H278" s="1" t="n"/>
-      <c r="I278" s="1" t="n"/>
-      <c r="J278" s="1" t="n"/>
-      <c r="K278" s="1" t="n"/>
-      <c r="L278" s="1" t="n"/>
-      <c r="M278" s="1" t="n"/>
-      <c r="N278" s="1" t="n"/>
-      <c r="O278" s="1" t="n"/>
-      <c r="P278" s="1" t="n"/>
-      <c r="Q278" s="1" t="n"/>
-    </row>
-    <row r="279" ht="22" customHeight="1">
-      <c r="A279" s="37" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl netto</t>
-        </is>
-      </c>
-      <c r="Q279" s="38">
-        <f>SUM(Q8:Q276)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="280" ht="22" customHeight="1">
-      <c r="A280" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q280" s="38">
-        <f>Q279*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="281" ht="26" customHeight="1">
-      <c r="A281" s="39" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl brutto</t>
-        </is>
-      </c>
-      <c r="Q281" s="40">
-        <f>Q279+Q280</f>
-        <v/>
-      </c>
-    </row>
-    <row r="282" ht="22" customHeight="1">
-      <c r="A282" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q282" s="41">
-        <f>COUNTIF(N8:N276,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="283">
-      <c r="A283" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="285" ht="24" customHeight="1">
-      <c r="A285" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B285" s="44" t="n"/>
-      <c r="C285" s="44" t="n"/>
-      <c r="D285" s="44" t="n"/>
-      <c r="E285" s="44" t="n"/>
-      <c r="F285" s="44" t="n"/>
-      <c r="G285" s="44" t="n"/>
-      <c r="H285" s="44" t="n"/>
-      <c r="I285" s="44" t="n"/>
-      <c r="J285" s="44" t="n"/>
-      <c r="K285" s="44" t="n"/>
-      <c r="L285" s="44" t="n"/>
-      <c r="M285" s="44" t="n"/>
-      <c r="N285" s="44" t="n"/>
-      <c r="O285" s="44" t="n"/>
-      <c r="P285" s="44" t="n"/>
-      <c r="Q285" s="44" t="n"/>
-    </row>
-    <row r="286" ht="22" customHeight="1">
-      <c r="A286" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
-        </is>
-      </c>
-      <c r="Q286" s="38">
-        <f>SUMPRODUCT(H8:H276,J8:J276)</f>
-        <v/>
-      </c>
+      <c r="B286" s="1" t="n"/>
+      <c r="C286" s="1" t="n"/>
+      <c r="D286" s="1" t="n"/>
+      <c r="E286" s="1" t="n"/>
+      <c r="F286" s="1" t="n"/>
+      <c r="G286" s="1" t="n"/>
+      <c r="H286" s="1" t="n"/>
+      <c r="I286" s="1" t="n"/>
+      <c r="J286" s="1" t="n"/>
+      <c r="K286" s="1" t="n"/>
+      <c r="L286" s="1" t="n"/>
+      <c r="M286" s="1" t="n"/>
+      <c r="N286" s="1" t="n"/>
+      <c r="O286" s="1" t="n"/>
+      <c r="P286" s="1" t="n"/>
+      <c r="Q286" s="1" t="n"/>
     </row>
     <row r="287" ht="22" customHeight="1">
       <c r="A287" s="37" t="inlineStr">
         <is>
+          <t>Wert Ihrer Auswahl netto</t>
+        </is>
+      </c>
+      <c r="Q287" s="38">
+        <f>SUM(Q8:Q284)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="288" ht="22" customHeight="1">
+      <c r="A288" s="37" t="inlineStr">
+        <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q287" s="38">
-        <f>Q286*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="288" ht="22" customHeight="1">
-      <c r="A288" s="45" t="inlineStr">
+      <c r="Q288" s="38">
+        <f>Q287*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="289" ht="26" customHeight="1">
+      <c r="A289" s="39" t="inlineStr">
+        <is>
+          <t>Wert Ihrer Auswahl brutto</t>
+        </is>
+      </c>
+      <c r="Q289" s="40">
+        <f>Q287+Q288</f>
+        <v/>
+      </c>
+    </row>
+    <row r="290" ht="22" customHeight="1">
+      <c r="A290" s="37" t="inlineStr">
+        <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q290" s="41">
+        <f>COUNTIF(N8:N284,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="24" customHeight="1">
+      <c r="A293" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B293" s="44" t="n"/>
+      <c r="C293" s="44" t="n"/>
+      <c r="D293" s="44" t="n"/>
+      <c r="E293" s="44" t="n"/>
+      <c r="F293" s="44" t="n"/>
+      <c r="G293" s="44" t="n"/>
+      <c r="H293" s="44" t="n"/>
+      <c r="I293" s="44" t="n"/>
+      <c r="J293" s="44" t="n"/>
+      <c r="K293" s="44" t="n"/>
+      <c r="L293" s="44" t="n"/>
+      <c r="M293" s="44" t="n"/>
+      <c r="N293" s="44" t="n"/>
+      <c r="O293" s="44" t="n"/>
+      <c r="P293" s="44" t="n"/>
+      <c r="Q293" s="44" t="n"/>
+    </row>
+    <row r="294" ht="22" customHeight="1">
+      <c r="A294" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q294" s="38">
+        <f>SUMPRODUCT(H8:H284,J8:J284)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="295" ht="22" customHeight="1">
+      <c r="A295" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q295" s="38">
+        <f>Q294*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="296" ht="22" customHeight="1">
+      <c r="A296" s="45" t="inlineStr">
         <is>
           <t>Gesamtwert brutto</t>
         </is>
       </c>
-      <c r="Q288" s="46">
-        <f>Q286+Q287</f>
-        <v/>
-      </c>
-    </row>
-    <row r="290" ht="24" customHeight="1">
-      <c r="A290" s="47" t="inlineStr">
+      <c r="Q296" s="46">
+        <f>Q294+Q295</f>
+        <v/>
+      </c>
+    </row>
+    <row r="298" ht="24" customHeight="1">
+      <c r="A298" s="47" t="inlineStr">
         <is>
           <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
         </is>
       </c>
-      <c r="B290" s="48" t="n"/>
-      <c r="C290" s="48" t="n"/>
-      <c r="D290" s="48" t="n"/>
-      <c r="E290" s="48" t="n"/>
-      <c r="F290" s="48" t="n"/>
-      <c r="G290" s="48" t="n"/>
-      <c r="H290" s="48" t="n"/>
-      <c r="I290" s="48" t="n"/>
-      <c r="J290" s="48" t="n"/>
-      <c r="K290" s="48" t="n"/>
-      <c r="L290" s="48" t="n"/>
-      <c r="M290" s="48" t="n"/>
-      <c r="N290" s="48" t="n"/>
-      <c r="O290" s="48" t="n"/>
-      <c r="P290" s="48" t="n"/>
-      <c r="Q290" s="48" t="n"/>
-    </row>
-    <row r="291" ht="22" customHeight="1">
-      <c r="A291" s="37" t="inlineStr">
+      <c r="B298" s="48" t="n"/>
+      <c r="C298" s="48" t="n"/>
+      <c r="D298" s="48" t="n"/>
+      <c r="E298" s="48" t="n"/>
+      <c r="F298" s="48" t="n"/>
+      <c r="G298" s="48" t="n"/>
+      <c r="H298" s="48" t="n"/>
+      <c r="I298" s="48" t="n"/>
+      <c r="J298" s="48" t="n"/>
+      <c r="K298" s="48" t="n"/>
+      <c r="L298" s="48" t="n"/>
+      <c r="M298" s="48" t="n"/>
+      <c r="N298" s="48" t="n"/>
+      <c r="O298" s="48" t="n"/>
+      <c r="P298" s="48" t="n"/>
+      <c r="Q298" s="48" t="n"/>
+    </row>
+    <row r="299" ht="22" customHeight="1">
+      <c r="A299" s="37" t="inlineStr">
         <is>
           <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
         </is>
       </c>
-      <c r="Q291" s="38">
-        <f>-Q286*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="292" ht="22" customHeight="1">
-      <c r="A292" s="45" t="inlineStr">
+      <c r="Q299" s="38">
+        <f>-Q294*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="300" ht="22" customHeight="1">
+      <c r="A300" s="45" t="inlineStr">
         <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="Q292" s="46">
-        <f>Q286+Q291</f>
-        <v/>
-      </c>
-    </row>
-    <row r="293" ht="22" customHeight="1">
-      <c r="A293" s="37" t="inlineStr">
+      <c r="Q300" s="46">
+        <f>Q294+Q299</f>
+        <v/>
+      </c>
+    </row>
+    <row r="301" ht="22" customHeight="1">
+      <c r="A301" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q293" s="38">
-        <f>Q292*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="294" ht="26" customHeight="1">
-      <c r="A294" s="39" t="inlineStr">
+      <c r="Q301" s="38">
+        <f>Q300*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="302" ht="26" customHeight="1">
+      <c r="A302" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q294" s="40">
-        <f>Q292+Q293</f>
-        <v/>
-      </c>
-    </row>
-    <row r="295">
-      <c r="A295" s="42" t="inlineStr">
+      <c r="Q302" s="40">
+        <f>Q300+Q301</f>
+        <v/>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="297">
-      <c r="A297" s="49" t="inlineStr">
+    <row r="305">
+      <c r="A305" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="298"/>
-    <row r="299"/>
-    <row r="300"/>
+    <row r="306"/>
+    <row r="307"/>
+    <row r="308"/>
   </sheetData>
-  <autoFilter ref="A7:Q276"/>
+  <autoFilter ref="A7:Q284"/>
   <mergeCells count="26">
-    <mergeCell ref="A295:Q295"/>
     <mergeCell ref="C1:Q1"/>
+    <mergeCell ref="A290:P290"/>
+    <mergeCell ref="A305:Q308"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A280:P280"/>
+    <mergeCell ref="A291:Q291"/>
     <mergeCell ref="L4:Q4"/>
-    <mergeCell ref="A293:P293"/>
+    <mergeCell ref="A299:P299"/>
     <mergeCell ref="A288:P288"/>
+    <mergeCell ref="A295:P295"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A297:Q300"/>
-    <mergeCell ref="A283:Q283"/>
-    <mergeCell ref="A279:P279"/>
-    <mergeCell ref="A291:P291"/>
+    <mergeCell ref="A289:P289"/>
+    <mergeCell ref="A286:Q286"/>
+    <mergeCell ref="A300:P300"/>
+    <mergeCell ref="A296:P296"/>
     <mergeCell ref="A287:P287"/>
-    <mergeCell ref="A285:Q285"/>
     <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A281:P281"/>
-    <mergeCell ref="A278:Q278"/>
+    <mergeCell ref="A298:Q298"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A292:P292"/>
-    <mergeCell ref="A290:Q290"/>
-    <mergeCell ref="A286:P286"/>
-    <mergeCell ref="A282:P282"/>
+    <mergeCell ref="A303:Q303"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
     <mergeCell ref="A294:P294"/>
+    <mergeCell ref="A301:P301"/>
+    <mergeCell ref="A302:P302"/>
+    <mergeCell ref="A293:Q293"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q276">
+  <conditionalFormatting sqref="A8:Q284">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N276" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N284" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O276" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O284" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$284</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$293</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7368,6 +7368,231 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>284</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="279" name="Image 279" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId279"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>285</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="280" name="Image 280" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId280"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>286</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="281" name="Image 281" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId281"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>287</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="282" name="Image 282" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId282"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>288</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="283" name="Image 283" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId283"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>289</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="284" name="Image 284" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId284"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>290</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="285" name="Image 285" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId285"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>291</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="286" name="Image 286" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId286"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>292</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="287" name="Image 287" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId287"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -7660,7 +7885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q308"/>
+  <dimension ref="A1:Q317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -22001,7 +22226,7 @@
       <c r="D243" s="23" t="inlineStr">
         <is>
           <t>VS Schalenstuhl grau, Vierfußgestell
-Schalenstuhl von VS (Vereinigte Spezialmöbelfabriken): graue Kunststoffschale mit Rautenstruktur und Griffloch in der Lehne, auf grauem Vierfußgestell aus Rohr. Farbspritzer aus dem Atelierbetrieb auf Sitz und Lehne.</t>
+Schalenstuhl von VS (Vereinigte Spezialmöbelfabriken): graue Kunststoffschale mit Rautenstruktur und Griffloch in der Lehne, auf grauem Vierfußgestell aus Rohr. Auf den Stühlen aus dem Atelier sind Farbspritzer.</t>
         </is>
       </c>
       <c r="E243" s="13" t="n"/>
@@ -22016,7 +22241,7 @@
         </is>
       </c>
       <c r="H243" s="21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I243" s="21" t="inlineStr">
         <is>
@@ -24512,261 +24737,801 @@
         <v/>
       </c>
     </row>
-    <row r="286" ht="24" customHeight="1">
-      <c r="A286" s="36" t="inlineStr">
+    <row r="285" ht="78" customHeight="1">
+      <c r="A285" s="20" t="n">
+        <v>278</v>
+      </c>
+      <c r="B285" s="35" t="inlineStr">
+        <is>
+          <t>BU05-01</t>
+        </is>
+      </c>
+      <c r="C285" s="22" t="n"/>
+      <c r="D285" s="23" t="inlineStr">
+        <is>
+          <t>Spielhaus weiß mit Hochebene und Bett
+Große Spielhaus-Konstruktion in Weiß: obere Spielebene mit Brüstung, grüner Tafel und Ablagefach, darunter eine Liegefläche mit Matratze. Eine Seitenwand trägt eine goldene Krone als Aufkleber.</t>
+        </is>
+      </c>
+      <c r="E285" s="13" t="n"/>
+      <c r="F285" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum</t>
+        </is>
+      </c>
+      <c r="G285" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H285" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I285" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J285" s="24" t="n">
+        <v>450</v>
+      </c>
+      <c r="K285" s="25">
+        <f>J285*1.19</f>
+        <v/>
+      </c>
+      <c r="L285" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M285" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N285" s="16" t="n"/>
+      <c r="O285" s="17" t="n"/>
+      <c r="P285" s="18" t="n"/>
+      <c r="Q285" s="26">
+        <f>IF(N285&lt;&gt;"ja","",IF(O285="",H285,O285)*J285)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="286" ht="78" customHeight="1">
+      <c r="A286" s="9" t="n">
+        <v>279</v>
+      </c>
+      <c r="B286" s="35" t="inlineStr">
+        <is>
+          <t>BU05-02</t>
+        </is>
+      </c>
+      <c r="C286" s="11" t="n"/>
+      <c r="D286" s="12" t="inlineStr">
+        <is>
+          <t>Wesco Spielküche, vier Module mit Mikrowelle
+Spielküche von Wesco aus Birke-Multiplex: offenes Regalmodul, Backofenmodul mit Klappe, Spülenmodul mit Becken und Kochfeldmodul, dazu eine aufgesetzte Spielmikrowelle. Fronten mit aufgedruckten Bedienfeldern, Rückwände mit Fliesenmuster.</t>
+        </is>
+      </c>
+      <c r="E286" s="13" t="n"/>
+      <c r="F286" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum</t>
+        </is>
+      </c>
+      <c r="G286" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H286" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I286" s="10" t="inlineStr">
+        <is>
+          <t>Set</t>
+        </is>
+      </c>
+      <c r="J286" s="14" t="n">
+        <v>550</v>
+      </c>
+      <c r="K286" s="15">
+        <f>J286*1.19</f>
+        <v/>
+      </c>
+      <c r="L286" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M286" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N286" s="16" t="n"/>
+      <c r="O286" s="17" t="n"/>
+      <c r="P286" s="18" t="n"/>
+      <c r="Q286" s="19">
+        <f>IF(N286&lt;&gt;"ja","",IF(O286="",H286,O286)*J286)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="287" ht="78" customHeight="1">
+      <c r="A287" s="20" t="n">
+        <v>280</v>
+      </c>
+      <c r="B287" s="21" t="inlineStr">
+        <is>
+          <t>BU05-03</t>
+        </is>
+      </c>
+      <c r="C287" s="22" t="n"/>
+      <c r="D287" s="23" t="inlineStr">
+        <is>
+          <t>Treppenregal weiß mit Wannen
+Weißes Regal in Treppenform: zwei hohe Fächer mit eingeschobenen Kunststoffwannen, dazu eine niedrigere Stufe mit Ablage und Wanne, die als Sitzfläche dient.</t>
+        </is>
+      </c>
+      <c r="E287" s="13" t="n"/>
+      <c r="F287" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum</t>
+        </is>
+      </c>
+      <c r="G287" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H287" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I287" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J287" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="K287" s="25">
+        <f>J287*1.19</f>
+        <v/>
+      </c>
+      <c r="L287" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M287" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N287" s="16" t="n"/>
+      <c r="O287" s="17" t="n"/>
+      <c r="P287" s="18" t="n"/>
+      <c r="Q287" s="26">
+        <f>IF(N287&lt;&gt;"ja","",IF(O287="",H287,O287)*J287)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="288" ht="78" customHeight="1">
+      <c r="A288" s="9" t="n">
+        <v>281</v>
+      </c>
+      <c r="B288" s="10" t="inlineStr">
+        <is>
+          <t>BU05-04</t>
+        </is>
+      </c>
+      <c r="C288" s="11" t="n"/>
+      <c r="D288" s="12" t="inlineStr">
+        <is>
+          <t>Schaukeltier Storch
+Plüsch-Schaukeltier in Storchenform: weißer Körper mit rotem Schnabel, gelber Zipfelmütze mit Bommeln und rot-weiß gepunktetem Sattel mit Haltegriff, auf hellen Holzkufen.</t>
+        </is>
+      </c>
+      <c r="E288" s="13" t="n"/>
+      <c r="F288" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum</t>
+        </is>
+      </c>
+      <c r="G288" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H288" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I288" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J288" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="K288" s="15">
+        <f>J288*1.19</f>
+        <v/>
+      </c>
+      <c r="L288" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M288" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N288" s="16" t="n"/>
+      <c r="O288" s="17" t="n"/>
+      <c r="P288" s="18" t="n"/>
+      <c r="Q288" s="19">
+        <f>IF(N288&lt;&gt;"ja","",IF(O288="",H288,O288)*J288)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="289" ht="78" customHeight="1">
+      <c r="A289" s="20" t="n">
+        <v>282</v>
+      </c>
+      <c r="B289" s="21" t="inlineStr">
+        <is>
+          <t>BU05-05</t>
+        </is>
+      </c>
+      <c r="C289" s="22" t="n"/>
+      <c r="D289" s="23" t="inlineStr">
+        <is>
+          <t>Kindersessel Teddyfell beige
+Kindersessel aus beigem Teddyfell mit runder Lehne, zwei aufgesetzten Ohren und breiten Armlehnen. Am Rücken ein Tragegriff; das Band am Griff ist eingerissen.</t>
+        </is>
+      </c>
+      <c r="E289" s="13" t="n"/>
+      <c r="F289" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum</t>
+        </is>
+      </c>
+      <c r="G289" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H289" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I289" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J289" s="24" t="n">
+        <v>45</v>
+      </c>
+      <c r="K289" s="25">
+        <f>J289*1.19</f>
+        <v/>
+      </c>
+      <c r="L289" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M289" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N289" s="16" t="n"/>
+      <c r="O289" s="17" t="n"/>
+      <c r="P289" s="18" t="n"/>
+      <c r="Q289" s="26">
+        <f>IF(N289&lt;&gt;"ja","",IF(O289="",H289,O289)*J289)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="290" ht="78" customHeight="1">
+      <c r="A290" s="9" t="n">
+        <v>283</v>
+      </c>
+      <c r="B290" s="10" t="inlineStr">
+        <is>
+          <t>BU05-06</t>
+        </is>
+      </c>
+      <c r="C290" s="11" t="n"/>
+      <c r="D290" s="12" t="inlineStr">
+        <is>
+          <t>Sitzbank gepolstert, hellgrau
+Niedrige gepolsterte Sitzbank in Kinderhöhe mit hellgrauem Chenillebezug und flacher Rückenlehne, ohne Armlehnen. Der Bezug ist an mehreren Stellen fleckig.</t>
+        </is>
+      </c>
+      <c r="E290" s="13" t="n"/>
+      <c r="F290" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum</t>
+        </is>
+      </c>
+      <c r="G290" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H290" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I290" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J290" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="K290" s="15">
+        <f>J290*1.19</f>
+        <v/>
+      </c>
+      <c r="L290" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M290" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N290" s="16" t="n"/>
+      <c r="O290" s="17" t="n"/>
+      <c r="P290" s="18" t="n"/>
+      <c r="Q290" s="19">
+        <f>IF(N290&lt;&gt;"ja","",IF(O290="",H290,O290)*J290)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="291" ht="78" customHeight="1">
+      <c r="A291" s="20" t="n">
+        <v>284</v>
+      </c>
+      <c r="B291" s="21" t="inlineStr">
+        <is>
+          <t>BU05-07</t>
+        </is>
+      </c>
+      <c r="C291" s="22" t="n"/>
+      <c r="D291" s="23" t="inlineStr">
+        <is>
+          <t>Puppenwagen rosa mit Tragetasche
+Puppen-Sportwagen mit rosa-weiß gestreiftem Bezug, blauem Verdeck und höhenverstellbarem Schiebegriff, dazu eine passende Tragetasche. Der Griff ist an mehreren Stellen aufgerissen.</t>
+        </is>
+      </c>
+      <c r="E291" s="13" t="n"/>
+      <c r="F291" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum</t>
+        </is>
+      </c>
+      <c r="G291" s="21" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="H291" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I291" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J291" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="K291" s="25">
+        <f>J291*1.19</f>
+        <v/>
+      </c>
+      <c r="L291" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M291" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N291" s="16" t="n"/>
+      <c r="O291" s="17" t="n"/>
+      <c r="P291" s="18" t="n"/>
+      <c r="Q291" s="26">
+        <f>IF(N291&lt;&gt;"ja","",IF(O291="",H291,O291)*J291)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="292" ht="78" customHeight="1">
+      <c r="A292" s="9" t="n">
+        <v>285</v>
+      </c>
+      <c r="B292" s="10" t="inlineStr">
+        <is>
+          <t>BU05-09</t>
+        </is>
+      </c>
+      <c r="C292" s="11" t="n"/>
+      <c r="D292" s="12" t="inlineStr">
+        <is>
+          <t>Puppenwagen Holz mit Gummirädern
+Puppen- und Lauflernwagen aus Birke-Multiplex mit hohem Schiebebügel und vier schwarzen Gummirädern. Herstellerangabe laut Erfassungsblatt der Einrichtung: Wesco.</t>
+        </is>
+      </c>
+      <c r="E292" s="13" t="n"/>
+      <c r="F292" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum</t>
+        </is>
+      </c>
+      <c r="G292" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H292" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I292" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J292" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="K292" s="15">
+        <f>J292*1.19</f>
+        <v/>
+      </c>
+      <c r="L292" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M292" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N292" s="16" t="n"/>
+      <c r="O292" s="17" t="n"/>
+      <c r="P292" s="18" t="n"/>
+      <c r="Q292" s="19">
+        <f>IF(N292&lt;&gt;"ja","",IF(O292="",H292,O292)*J292)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="293" ht="78" customHeight="1">
+      <c r="A293" s="20" t="n">
+        <v>286</v>
+      </c>
+      <c r="B293" s="21" t="inlineStr">
+        <is>
+          <t>BU05-10</t>
+        </is>
+      </c>
+      <c r="C293" s="22" t="n"/>
+      <c r="D293" s="23" t="inlineStr">
+        <is>
+          <t>Wesco Rutschfahrzeug mit Spielelementen
+Rutschfahrzeug aus Birke-Multiplex mit gepolsterter Sitzfläche, Steckformen im Sitz, Rückenlehne mit rundem Spiegel und seitlichen Zahnrädern zum Drehen, auf vier Gummirädern. Logo auf der Frontblende: wesco.</t>
+        </is>
+      </c>
+      <c r="E293" s="13" t="n"/>
+      <c r="F293" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum</t>
+        </is>
+      </c>
+      <c r="G293" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H293" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I293" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J293" s="24" t="n">
+        <v>90</v>
+      </c>
+      <c r="K293" s="25">
+        <f>J293*1.19</f>
+        <v/>
+      </c>
+      <c r="L293" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M293" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N293" s="16" t="n"/>
+      <c r="O293" s="17" t="n"/>
+      <c r="P293" s="18" t="n"/>
+      <c r="Q293" s="26">
+        <f>IF(N293&lt;&gt;"ja","",IF(O293="",H293,O293)*J293)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="295" ht="24" customHeight="1">
+      <c r="A295" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B286" s="1" t="n"/>
-      <c r="C286" s="1" t="n"/>
-      <c r="D286" s="1" t="n"/>
-      <c r="E286" s="1" t="n"/>
-      <c r="F286" s="1" t="n"/>
-      <c r="G286" s="1" t="n"/>
-      <c r="H286" s="1" t="n"/>
-      <c r="I286" s="1" t="n"/>
-      <c r="J286" s="1" t="n"/>
-      <c r="K286" s="1" t="n"/>
-      <c r="L286" s="1" t="n"/>
-      <c r="M286" s="1" t="n"/>
-      <c r="N286" s="1" t="n"/>
-      <c r="O286" s="1" t="n"/>
-      <c r="P286" s="1" t="n"/>
-      <c r="Q286" s="1" t="n"/>
-    </row>
-    <row r="287" ht="22" customHeight="1">
-      <c r="A287" s="37" t="inlineStr">
+      <c r="B295" s="1" t="n"/>
+      <c r="C295" s="1" t="n"/>
+      <c r="D295" s="1" t="n"/>
+      <c r="E295" s="1" t="n"/>
+      <c r="F295" s="1" t="n"/>
+      <c r="G295" s="1" t="n"/>
+      <c r="H295" s="1" t="n"/>
+      <c r="I295" s="1" t="n"/>
+      <c r="J295" s="1" t="n"/>
+      <c r="K295" s="1" t="n"/>
+      <c r="L295" s="1" t="n"/>
+      <c r="M295" s="1" t="n"/>
+      <c r="N295" s="1" t="n"/>
+      <c r="O295" s="1" t="n"/>
+      <c r="P295" s="1" t="n"/>
+      <c r="Q295" s="1" t="n"/>
+    </row>
+    <row r="296" ht="22" customHeight="1">
+      <c r="A296" s="37" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl netto</t>
         </is>
       </c>
-      <c r="Q287" s="38">
-        <f>SUM(Q8:Q284)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="288" ht="22" customHeight="1">
-      <c r="A288" s="37" t="inlineStr">
+      <c r="Q296" s="38">
+        <f>SUM(Q8:Q293)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="297" ht="22" customHeight="1">
+      <c r="A297" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q288" s="38">
-        <f>Q287*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="289" ht="26" customHeight="1">
-      <c r="A289" s="39" t="inlineStr">
+      <c r="Q297" s="38">
+        <f>Q296*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="298" ht="26" customHeight="1">
+      <c r="A298" s="39" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl brutto</t>
         </is>
       </c>
-      <c r="Q289" s="40">
-        <f>Q287+Q288</f>
-        <v/>
-      </c>
-    </row>
-    <row r="290" ht="22" customHeight="1">
-      <c r="A290" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q290" s="41">
-        <f>COUNTIF(N8:N284,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="293" ht="24" customHeight="1">
-      <c r="A293" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B293" s="44" t="n"/>
-      <c r="C293" s="44" t="n"/>
-      <c r="D293" s="44" t="n"/>
-      <c r="E293" s="44" t="n"/>
-      <c r="F293" s="44" t="n"/>
-      <c r="G293" s="44" t="n"/>
-      <c r="H293" s="44" t="n"/>
-      <c r="I293" s="44" t="n"/>
-      <c r="J293" s="44" t="n"/>
-      <c r="K293" s="44" t="n"/>
-      <c r="L293" s="44" t="n"/>
-      <c r="M293" s="44" t="n"/>
-      <c r="N293" s="44" t="n"/>
-      <c r="O293" s="44" t="n"/>
-      <c r="P293" s="44" t="n"/>
-      <c r="Q293" s="44" t="n"/>
-    </row>
-    <row r="294" ht="22" customHeight="1">
-      <c r="A294" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
-        </is>
-      </c>
-      <c r="Q294" s="38">
-        <f>SUMPRODUCT(H8:H284,J8:J284)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="295" ht="22" customHeight="1">
-      <c r="A295" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q295" s="38">
-        <f>Q294*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="296" ht="22" customHeight="1">
-      <c r="A296" s="45" t="inlineStr">
-        <is>
-          <t>Gesamtwert brutto</t>
-        </is>
-      </c>
-      <c r="Q296" s="46">
-        <f>Q294+Q295</f>
-        <v/>
-      </c>
-    </row>
-    <row r="298" ht="24" customHeight="1">
-      <c r="A298" s="47" t="inlineStr">
-        <is>
-          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B298" s="48" t="n"/>
-      <c r="C298" s="48" t="n"/>
-      <c r="D298" s="48" t="n"/>
-      <c r="E298" s="48" t="n"/>
-      <c r="F298" s="48" t="n"/>
-      <c r="G298" s="48" t="n"/>
-      <c r="H298" s="48" t="n"/>
-      <c r="I298" s="48" t="n"/>
-      <c r="J298" s="48" t="n"/>
-      <c r="K298" s="48" t="n"/>
-      <c r="L298" s="48" t="n"/>
-      <c r="M298" s="48" t="n"/>
-      <c r="N298" s="48" t="n"/>
-      <c r="O298" s="48" t="n"/>
-      <c r="P298" s="48" t="n"/>
-      <c r="Q298" s="48" t="n"/>
+      <c r="Q298" s="40">
+        <f>Q296+Q297</f>
+        <v/>
+      </c>
     </row>
     <row r="299" ht="22" customHeight="1">
       <c r="A299" s="37" t="inlineStr">
         <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q299" s="41">
+        <f>COUNTIF(N8:N293,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="24" customHeight="1">
+      <c r="A302" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B302" s="44" t="n"/>
+      <c r="C302" s="44" t="n"/>
+      <c r="D302" s="44" t="n"/>
+      <c r="E302" s="44" t="n"/>
+      <c r="F302" s="44" t="n"/>
+      <c r="G302" s="44" t="n"/>
+      <c r="H302" s="44" t="n"/>
+      <c r="I302" s="44" t="n"/>
+      <c r="J302" s="44" t="n"/>
+      <c r="K302" s="44" t="n"/>
+      <c r="L302" s="44" t="n"/>
+      <c r="M302" s="44" t="n"/>
+      <c r="N302" s="44" t="n"/>
+      <c r="O302" s="44" t="n"/>
+      <c r="P302" s="44" t="n"/>
+      <c r="Q302" s="44" t="n"/>
+    </row>
+    <row r="303" ht="22" customHeight="1">
+      <c r="A303" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q303" s="38">
+        <f>SUMPRODUCT(H8:H293,J8:J293)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="304" ht="22" customHeight="1">
+      <c r="A304" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q304" s="38">
+        <f>Q303*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="305" ht="22" customHeight="1">
+      <c r="A305" s="45" t="inlineStr">
+        <is>
+          <t>Gesamtwert brutto</t>
+        </is>
+      </c>
+      <c r="Q305" s="46">
+        <f>Q303+Q304</f>
+        <v/>
+      </c>
+    </row>
+    <row r="307" ht="24" customHeight="1">
+      <c r="A307" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B307" s="48" t="n"/>
+      <c r="C307" s="48" t="n"/>
+      <c r="D307" s="48" t="n"/>
+      <c r="E307" s="48" t="n"/>
+      <c r="F307" s="48" t="n"/>
+      <c r="G307" s="48" t="n"/>
+      <c r="H307" s="48" t="n"/>
+      <c r="I307" s="48" t="n"/>
+      <c r="J307" s="48" t="n"/>
+      <c r="K307" s="48" t="n"/>
+      <c r="L307" s="48" t="n"/>
+      <c r="M307" s="48" t="n"/>
+      <c r="N307" s="48" t="n"/>
+      <c r="O307" s="48" t="n"/>
+      <c r="P307" s="48" t="n"/>
+      <c r="Q307" s="48" t="n"/>
+    </row>
+    <row r="308" ht="22" customHeight="1">
+      <c r="A308" s="37" t="inlineStr">
+        <is>
           <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
         </is>
       </c>
-      <c r="Q299" s="38">
-        <f>-Q294*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="300" ht="22" customHeight="1">
-      <c r="A300" s="45" t="inlineStr">
+      <c r="Q308" s="38">
+        <f>-Q303*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="309" ht="22" customHeight="1">
+      <c r="A309" s="45" t="inlineStr">
         <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="Q300" s="46">
-        <f>Q294+Q299</f>
-        <v/>
-      </c>
-    </row>
-    <row r="301" ht="22" customHeight="1">
-      <c r="A301" s="37" t="inlineStr">
+      <c r="Q309" s="46">
+        <f>Q303+Q308</f>
+        <v/>
+      </c>
+    </row>
+    <row r="310" ht="22" customHeight="1">
+      <c r="A310" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q301" s="38">
-        <f>Q300*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="302" ht="26" customHeight="1">
-      <c r="A302" s="39" t="inlineStr">
+      <c r="Q310" s="38">
+        <f>Q309*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="311" ht="26" customHeight="1">
+      <c r="A311" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q302" s="40">
-        <f>Q300+Q301</f>
-        <v/>
-      </c>
-    </row>
-    <row r="303">
-      <c r="A303" s="42" t="inlineStr">
+      <c r="Q311" s="40">
+        <f>Q309+Q310</f>
+        <v/>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="305">
-      <c r="A305" s="49" t="inlineStr">
+    <row r="314">
+      <c r="A314" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="306"/>
-    <row r="307"/>
-    <row r="308"/>
+    <row r="315"/>
+    <row r="316"/>
+    <row r="317"/>
   </sheetData>
-  <autoFilter ref="A7:Q284"/>
+  <autoFilter ref="A7:Q293"/>
   <mergeCells count="26">
+    <mergeCell ref="A295:Q295"/>
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A290:P290"/>
-    <mergeCell ref="A305:Q308"/>
+    <mergeCell ref="A309:P309"/>
+    <mergeCell ref="A298:P298"/>
+    <mergeCell ref="A303:P303"/>
+    <mergeCell ref="A311:P311"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A291:Q291"/>
+    <mergeCell ref="A300:Q300"/>
     <mergeCell ref="L4:Q4"/>
     <mergeCell ref="A299:P299"/>
-    <mergeCell ref="A288:P288"/>
-    <mergeCell ref="A295:P295"/>
+    <mergeCell ref="A308:P308"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A289:P289"/>
-    <mergeCell ref="A286:Q286"/>
-    <mergeCell ref="A300:P300"/>
+    <mergeCell ref="A304:P304"/>
+    <mergeCell ref="A310:P310"/>
     <mergeCell ref="A296:P296"/>
-    <mergeCell ref="A287:P287"/>
     <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A298:Q298"/>
+    <mergeCell ref="A314:Q317"/>
+    <mergeCell ref="A302:Q302"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A303:Q303"/>
+    <mergeCell ref="A305:P305"/>
+    <mergeCell ref="A307:Q307"/>
+    <mergeCell ref="A312:Q312"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A294:P294"/>
-    <mergeCell ref="A301:P301"/>
-    <mergeCell ref="A302:P302"/>
-    <mergeCell ref="A293:Q293"/>
+    <mergeCell ref="A297:P297"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q284">
+  <conditionalFormatting sqref="A8:Q293">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N284" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N293" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O284" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O293" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$293</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$301</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5225,2364 +5225,2564 @@
       <row>198</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="193" name="Image 193" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId193"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>199</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="194" name="Image 194" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId194"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>200</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="195" name="Image 195" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId195"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>201</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="193" name="Image 193" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId193"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>199</row>
+        <cNvPr id="196" name="Image 196" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId196"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>202</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="197" name="Image 197" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId197"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>203</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="194" name="Image 194" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId194"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>200</row>
+        <cNvPr id="198" name="Image 198" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId198"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>204</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="199" name="Image 199" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId199"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>205</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="200" name="Image 200" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId200"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>206</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="195" name="Image 195" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId195"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>201</row>
+        <cNvPr id="201" name="Image 201" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId201"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>207</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="196" name="Image 196" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId196"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>202</row>
+        <cNvPr id="202" name="Image 202" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId202"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>208</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="203" name="Image 203" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId203"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>209</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="197" name="Image 197" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId197"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>203</row>
+        <cNvPr id="204" name="Image 204" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId204"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>210</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="205" name="Image 205" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId205"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>211</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="206" name="Image 206" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId206"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>212</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="207" name="Image 207" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId207"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>213</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="198" name="Image 198" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId198"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>204</row>
+        <cNvPr id="208" name="Image 208" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId208"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>214</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="209" name="Image 209" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId209"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>215</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="210" name="Image 210" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId210"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>216</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="211" name="Image 211" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId211"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>217</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="199" name="Image 199" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId199"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>205</row>
+        <cNvPr id="212" name="Image 212" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId212"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>218</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="213" name="Image 213" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId213"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>219</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="214" name="Image 214" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId214"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>220</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="200" name="Image 200" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId200"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>206</row>
+        <cNvPr id="215" name="Image 215" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId215"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>221</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="201" name="Image 201" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId201"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>207</row>
+        <cNvPr id="216" name="Image 216" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId216"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>222</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="217" name="Image 217" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId217"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>223</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="202" name="Image 202" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId202"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>208</row>
+        <cNvPr id="218" name="Image 218" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId218"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>224</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="219" name="Image 219" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId219"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>225</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="220" name="Image 220" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId220"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>226</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="221" name="Image 221" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId221"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>227</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="222" name="Image 222" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId222"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>228</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="203" name="Image 203" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId203"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>209</row>
+        <cNvPr id="223" name="Image 223" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId223"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>229</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="204" name="Image 204" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId204"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>210</row>
+        <cNvPr id="224" name="Image 224" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId224"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>230</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="205" name="Image 205" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId205"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>211</row>
+        <cNvPr id="225" name="Image 225" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId225"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>231</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="226" name="Image 226" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId226"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>232</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="206" name="Image 206" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId206"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>212</row>
+        <cNvPr id="227" name="Image 227" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId227"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>233</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="228" name="Image 228" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId228"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>234</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="229" name="Image 229" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId229"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>235</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="230" name="Image 230" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId230"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>236</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="207" name="Image 207" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId207"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>213</row>
+        <cNvPr id="231" name="Image 231" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId231"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>237</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="232" name="Image 232" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId232"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>238</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="208" name="Image 208" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId208"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>214</row>
+        <cNvPr id="233" name="Image 233" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId233"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>239</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="234" name="Image 234" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId234"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>240</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="209" name="Image 209" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId209"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>215</row>
+        <cNvPr id="235" name="Image 235" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId235"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>241</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="210" name="Image 210" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId210"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>216</row>
+        <cNvPr id="236" name="Image 236" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId236"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>242</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="211" name="Image 211" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId211"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>217</row>
+        <cNvPr id="237" name="Image 237" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId237"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>243</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="212" name="Image 212" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId212"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>218</row>
+        <cNvPr id="238" name="Image 238" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId238"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>244</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="213" name="Image 213" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId213"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>219</row>
+        <cNvPr id="239" name="Image 239" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId239"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>245</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="240" name="Image 240" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId240"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>246</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="241" name="Image 241" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId241"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>247</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="242" name="Image 242" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId242"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>248</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="214" name="Image 214" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId214"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>220</row>
+        <cNvPr id="243" name="Image 243" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId243"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>249</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="244" name="Image 244" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId244"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>250</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="245" name="Image 245" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId245"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>251</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="215" name="Image 215" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId215"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>221</row>
+        <cNvPr id="246" name="Image 246" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId246"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>252</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="216" name="Image 216" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId216"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>222</row>
+        <cNvPr id="247" name="Image 247" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId247"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>253</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="217" name="Image 217" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId217"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>223</row>
+        <cNvPr id="248" name="Image 248" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId248"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>254</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="249" name="Image 249" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId249"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>255</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="250" name="Image 250" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId250"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>256</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="251" name="Image 251" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId251"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>257</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="252" name="Image 252" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId252"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>258</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="253" name="Image 253" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId253"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>259</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="254" name="Image 254" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId254"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>260</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="218" name="Image 218" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId218"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>224</row>
+        <cNvPr id="255" name="Image 255" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId255"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>261</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="219" name="Image 219" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId219"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>225</row>
+        <cNvPr id="256" name="Image 256" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId256"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>262</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="257" name="Image 257" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId257"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>263</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="220" name="Image 220" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId220"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>226</row>
+        <cNvPr id="258" name="Image 258" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId258"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>264</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="221" name="Image 221" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId221"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>227</row>
+        <cNvPr id="259" name="Image 259" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId259"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>265</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="260" name="Image 260" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId260"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>266</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="261" name="Image 261" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId261"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>267</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="262" name="Image 262" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId262"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>268</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="222" name="Image 222" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId222"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>228</row>
+        <cNvPr id="263" name="Image 263" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId263"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>269</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="264" name="Image 264" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId264"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>270</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="265" name="Image 265" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId265"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>271</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="266" name="Image 266" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId266"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>272</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="267" name="Image 267" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId267"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>273</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="268" name="Image 268" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId268"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>274</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="223" name="Image 223" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId223"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>229</row>
+        <cNvPr id="269" name="Image 269" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId269"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>275</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="270" name="Image 270" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId270"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>276</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="271" name="Image 271" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId271"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>277</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="272" name="Image 272" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId272"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>278</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="273" name="Image 273" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId273"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>279</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="274" name="Image 274" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId274"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>280</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="275" name="Image 275" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId275"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>281</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="224" name="Image 224" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId224"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>230</row>
+        <cNvPr id="276" name="Image 276" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId276"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>282</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="277" name="Image 277" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId277"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>283</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="278" name="Image 278" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId278"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>284</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="279" name="Image 279" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId279"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>285</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="280" name="Image 280" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId280"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>286</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="225" name="Image 225" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId225"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>231</row>
+        <cNvPr id="281" name="Image 281" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId281"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>287</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="282" name="Image 282" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId282"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>288</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="226" name="Image 226" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId226"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>232</row>
+        <cNvPr id="283" name="Image 283" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId283"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>289</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="227" name="Image 227" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId227"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>233</row>
+        <cNvPr id="284" name="Image 284" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId284"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>290</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="228" name="Image 228" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId228"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>234</row>
+        <cNvPr id="285" name="Image 285" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId285"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>291</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="704850" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="229" name="Image 229" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId229"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>235</row>
+        <cNvPr id="286" name="Image 286" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId286"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>292</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="287" name="Image 287" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId287"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>293</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="230" name="Image 230" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId230"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>236</row>
+        <cNvPr id="288" name="Image 288" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId288"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>294</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="289" name="Image 289" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId289"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>295</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="290" name="Image 290" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId290"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>296</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="291" name="Image 291" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId291"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>297</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="231" name="Image 231" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId231"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>237</row>
+        <cNvPr id="292" name="Image 292" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId292"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>298</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="293" name="Image 293" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId293"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>299</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="294" name="Image 294" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId294"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>300</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1257300" cy="942975"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="232" name="Image 232" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId232"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>238</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="233" name="Image 233" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId233"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>239</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="234" name="Image 234" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId234"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>240</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="235" name="Image 235" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId235"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>241</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="236" name="Image 236" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId236"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>242</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="237" name="Image 237" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId237"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>243</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="238" name="Image 238" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId238"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>244</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="239" name="Image 239" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId239"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>245</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="240" name="Image 240" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId240"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>246</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="241" name="Image 241" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId241"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>247</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="242" name="Image 242" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId242"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>248</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="243" name="Image 243" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId243"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>249</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="244" name="Image 244" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId244"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>250</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="245" name="Image 245" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId245"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>251</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="246" name="Image 246" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId246"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>252</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="247" name="Image 247" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId247"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>253</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="248" name="Image 248" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId248"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>254</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="249" name="Image 249" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId249"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>255</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="250" name="Image 250" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId250"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>256</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="251" name="Image 251" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId251"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>257</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="252" name="Image 252" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId252"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>258</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="253" name="Image 253" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId253"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>259</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="254" name="Image 254" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId254"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>260</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="255" name="Image 255" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId255"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>261</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="256" name="Image 256" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId256"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>262</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="257" name="Image 257" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId257"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>263</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="258" name="Image 258" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId258"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>264</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="259" name="Image 259" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId259"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>265</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="260" name="Image 260" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId260"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>266</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="261" name="Image 261" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId261"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>267</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="262" name="Image 262" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId262"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>268</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="263" name="Image 263" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId263"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>269</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="264" name="Image 264" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId264"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>270</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="265" name="Image 265" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId265"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>271</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="266" name="Image 266" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId266"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>272</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="267" name="Image 267" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId267"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>273</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="268" name="Image 268" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId268"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>274</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="269" name="Image 269" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId269"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>275</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="270" name="Image 270" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId270"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>276</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="271" name="Image 271" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId271"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>277</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="272" name="Image 272" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId272"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>278</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="273" name="Image 273" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId273"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>279</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="274" name="Image 274" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId274"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>280</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="275" name="Image 275" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId275"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>281</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="276" name="Image 276" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId276"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>282</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="277" name="Image 277" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId277"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>283</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="278" name="Image 278" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId278"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>284</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="279" name="Image 279" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId279"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>285</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="280" name="Image 280" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId280"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>286</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="281" name="Image 281" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId281"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>287</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="282" name="Image 282" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId282"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>288</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="283" name="Image 283" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId283"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>289</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="284" name="Image 284" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId284"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>290</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="704850" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="285" name="Image 285" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId285"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>291</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="286" name="Image 286" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId286"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>292</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1257300" cy="942975"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="287" name="Image 287" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId287"/>
+        <cNvPr id="295" name="Image 295" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId295"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -7885,7 +8085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q317"/>
+  <dimension ref="A1:Q325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -19461,8 +19661,8 @@
       <c r="C197" s="22" t="n"/>
       <c r="D197" s="23" t="inlineStr">
         <is>
-          <t>IKEA Trinkbecher Kinder, bunt
-Trinkbecher aus Kunststoff für Kinder, IKEA, in Rot, Blau, Pink, Gelb und Weiß. Stapelbar, spülmaschinenfest.</t>
+          <t>Geschirr-Konvolut Kinder: 134 Becher und 49 Teller
+Komplettes Kindergeschirr aus zwei Küchen. 134 Trinkbecher aus Kunststoff und Melamin: 73 bunte von IKEA in Rot, Blau, Pink, Gelb und Weiß, 44 mit facettiertem Fuß in Weiß, Salbei-, Grau- und Mintgrün (acht davon mit Motiv) und 17 rote. Dazu 49 flache Teller: bunte Kunststoffteller in kräftigen Farben in zwei Größen sowie Teller mit Tiermotiv. Alles stapelbar und spülmaschinenfest.</t>
         </is>
       </c>
       <c r="E197" s="13" t="n"/>
@@ -19477,15 +19677,15 @@
         </is>
       </c>
       <c r="H197" s="21" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="I197" s="21" t="inlineStr">
         <is>
-          <t>Stück</t>
+          <t>Konvolut</t>
         </is>
       </c>
       <c r="J197" s="24" t="n">
-        <v>0.5</v>
+        <v>150</v>
       </c>
       <c r="K197" s="25">
         <f>J197*1.19</f>
@@ -19515,14 +19715,14 @@
       </c>
       <c r="B198" s="10" t="inlineStr">
         <is>
-          <t>NE02-06</t>
+          <t>NE02-08</t>
         </is>
       </c>
       <c r="C198" s="11" t="n"/>
       <c r="D198" s="12" t="inlineStr">
         <is>
-          <t>Trinkbecher Melamin, grün- und grautöne
-Trinkbecher mit facettiertem Fuß in Weiß, Salbeigrün, Graugrün und Mintgrün. Acht der Becher tragen ein Motiv.</t>
+          <t>Schriftzug „Sterneküche", schwarz
+Großer Wandschriftzug „Sterneküche" in Schreibschrift, schwarz, aus Holz gefräst.</t>
         </is>
       </c>
       <c r="E198" s="13" t="n"/>
@@ -19537,7 +19737,7 @@
         </is>
       </c>
       <c r="H198" s="10" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I198" s="10" t="inlineStr">
         <is>
@@ -19545,7 +19745,7 @@
         </is>
       </c>
       <c r="J198" s="14" t="n">
-        <v>1.5</v>
+        <v>35</v>
       </c>
       <c r="K198" s="15">
         <f>J198*1.19</f>
@@ -19575,14 +19775,14 @@
       </c>
       <c r="B199" s="21" t="inlineStr">
         <is>
-          <t>NE02-07</t>
+          <t>NE02-09</t>
         </is>
       </c>
       <c r="C199" s="22" t="n"/>
       <c r="D199" s="23" t="inlineStr">
         <is>
-          <t>Teller Kunststoff, bunt
-Flache Teller aus Kunststoff in kräftigen Farben: elf kleine bunte, drei große sowie weitere mit Tiermotiv.</t>
+          <t>Tablett weiß mit Streifenmuster
+Serviertablett aus Kunststoff, weiß mit Griffausschnitten, Boden mit Streifenmuster – eines in Blautönen, eines in Rottönen.</t>
         </is>
       </c>
       <c r="E199" s="13" t="n"/>
@@ -19593,11 +19793,11 @@
       </c>
       <c r="G199" s="21" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H199" s="21" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="I199" s="21" t="inlineStr">
         <is>
@@ -19605,7 +19805,7 @@
         </is>
       </c>
       <c r="J199" s="24" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="K199" s="25">
         <f>J199*1.19</f>
@@ -19635,25 +19835,25 @@
       </c>
       <c r="B200" s="10" t="inlineStr">
         <is>
-          <t>NE02-08</t>
+          <t>BA10-09</t>
         </is>
       </c>
       <c r="C200" s="11" t="n"/>
       <c r="D200" s="12" t="inlineStr">
         <is>
-          <t>Schriftzug „Sterneküche", schwarz
-Großer Wandschriftzug „Sterneküche" in Schreibschrift, schwarz, aus Holz gefräst.</t>
+          <t>Beistelltisch rund, Tablettplatte Birke
+Runder Beistelltisch: abnehmbare Tablettplatte aus Birke mit umlaufendem Rand, auf einem weißen Gestell aus Rundstahl mit Tragebügel.</t>
         </is>
       </c>
       <c r="E200" s="13" t="n"/>
       <c r="F200" s="12" t="inlineStr">
         <is>
-          <t>Küche</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="G200" s="10" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H200" s="10" t="n">
@@ -19678,7 +19878,7 @@
       </c>
       <c r="M200" s="12" t="inlineStr">
         <is>
-          <t>Versand möglich</t>
+          <t>nur Abholung</t>
         </is>
       </c>
       <c r="N200" s="16" t="n"/>
@@ -19695,29 +19895,29 @@
       </c>
       <c r="B201" s="21" t="inlineStr">
         <is>
-          <t>NE02-09</t>
+          <t>BA10-10</t>
         </is>
       </c>
       <c r="C201" s="22" t="n"/>
       <c r="D201" s="23" t="inlineStr">
         <is>
-          <t>Tablett weiß mit Streifenmuster
-Serviertablett aus Kunststoff, weiß mit Griffausschnitten, Boden mit Streifenmuster – eines in Blautönen, eines in Rottönen.</t>
+          <t>Beistelltisch rund, Tablettplatte schwarz
+Runder Beistelltisch mit schwarzer Tablettplatte auf drei schlanken, schwarz lackierten Metallbeinen. Platte mit Gebrauchsspuren.</t>
         </is>
       </c>
       <c r="E201" s="13" t="n"/>
       <c r="F201" s="23" t="inlineStr">
         <is>
-          <t>Küche</t>
+          <t>Ruhe- / Schlafraum</t>
         </is>
       </c>
       <c r="G201" s="21" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H201" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I201" s="21" t="inlineStr">
         <is>
@@ -19725,7 +19925,7 @@
         </is>
       </c>
       <c r="J201" s="24" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="K201" s="25">
         <f>J201*1.19</f>
@@ -19738,7 +19938,7 @@
       </c>
       <c r="M201" s="23" t="inlineStr">
         <is>
-          <t>Versand möglich</t>
+          <t>nur Abholung</t>
         </is>
       </c>
       <c r="N201" s="16" t="n"/>
@@ -19755,14 +19955,14 @@
       </c>
       <c r="B202" s="10" t="inlineStr">
         <is>
-          <t>BA10-09</t>
+          <t>BA10-11</t>
         </is>
       </c>
       <c r="C202" s="11" t="n"/>
       <c r="D202" s="12" t="inlineStr">
         <is>
-          <t>Beistelltisch rund, Tablettplatte Birke
-Runder Beistelltisch: abnehmbare Tablettplatte aus Birke mit umlaufendem Rand, auf einem weißen Gestell aus Rundstahl mit Tragebügel.</t>
+          <t>Tisch rund, zweiteilig, weiß
+Runder Tisch aus zwei halbrunden weißen Platten mit Multiplex-Kante, auf höhenverstellbaren Rundfüßen aus Chrom. Die Hälften lassen sich einzeln stellen.</t>
         </is>
       </c>
       <c r="E202" s="13" t="n"/>
@@ -19785,7 +19985,7 @@
         </is>
       </c>
       <c r="J202" s="14" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="K202" s="15">
         <f>J202*1.19</f>
@@ -19815,20 +20015,24 @@
       </c>
       <c r="B203" s="21" t="inlineStr">
         <is>
-          <t>BA10-10</t>
+          <t>BA03-01</t>
         </is>
       </c>
       <c r="C203" s="22" t="n"/>
       <c r="D203" s="23" t="inlineStr">
         <is>
-          <t>Beistelltisch rund, Tablettplatte schwarz
-Runder Beistelltisch mit schwarzer Tablettplatte auf drei schlanken, schwarz lackierten Metallbeinen. Platte mit Gebrauchsspuren.</t>
-        </is>
-      </c>
-      <c r="E203" s="13" t="n"/>
+          <t>IKEA Avsiktlig Teppich, schwarz-weiß gepunktet
+Flachgewebter Teppich in Creme mit schwarzen Punktreihen, IKEA Avsiktlig. Flor 100 % Polypropylen auf Jutekette. Etikett auf der Rückseite vorhanden.</t>
+        </is>
+      </c>
+      <c r="E203" s="13" t="inlineStr">
+        <is>
+          <t>133 × 195 cm</t>
+        </is>
+      </c>
       <c r="F203" s="23" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Galerie</t>
         </is>
       </c>
       <c r="G203" s="21" t="inlineStr">
@@ -19845,7 +20049,7 @@
         </is>
       </c>
       <c r="J203" s="24" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K203" s="25">
         <f>J203*1.19</f>
@@ -19858,7 +20062,7 @@
       </c>
       <c r="M203" s="23" t="inlineStr">
         <is>
-          <t>nur Abholung</t>
+          <t>Versand möglich</t>
         </is>
       </c>
       <c r="N203" s="16" t="n"/>
@@ -19873,22 +20077,22 @@
       <c r="A204" s="9" t="n">
         <v>197</v>
       </c>
-      <c r="B204" s="10" t="inlineStr">
-        <is>
-          <t>BA10-11</t>
+      <c r="B204" s="35" t="inlineStr">
+        <is>
+          <t>BA03-02</t>
         </is>
       </c>
       <c r="C204" s="11" t="n"/>
       <c r="D204" s="12" t="inlineStr">
         <is>
-          <t>Tisch rund, zweiteilig, weiß
-Runder Tisch aus zwei halbrunden weißen Platten mit Multiplex-Kante, auf höhenverstellbaren Rundfüßen aus Chrom. Die Hälften lassen sich einzeln stellen.</t>
+          <t>Spielküche beige-braun, mehrteilig
+Spielküche aus beschichteter Platte in Creme und Taupe mit Holzarbeitsplatten: Mikrowellenmodul mit Digitalanzeige, Unterschränke mit Kochfeld, Backofen mit Sichtfenster und Spüle, dazu ein Wandregal. Abgerundete Ecken, kindgerechte Höhe.</t>
         </is>
       </c>
       <c r="E204" s="13" t="n"/>
       <c r="F204" s="12" t="inlineStr">
         <is>
-          <t>Ruhe- / Schlafraum</t>
+          <t>Galerie</t>
         </is>
       </c>
       <c r="G204" s="10" t="inlineStr">
@@ -19901,11 +20105,11 @@
       </c>
       <c r="I204" s="10" t="inlineStr">
         <is>
-          <t>Stück</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="J204" s="14" t="n">
-        <v>90</v>
+        <v>250</v>
       </c>
       <c r="K204" s="15">
         <f>J204*1.19</f>
@@ -19935,21 +20139,17 @@
       </c>
       <c r="B205" s="21" t="inlineStr">
         <is>
-          <t>BA03-01</t>
+          <t>BA03-03</t>
         </is>
       </c>
       <c r="C205" s="22" t="n"/>
       <c r="D205" s="23" t="inlineStr">
         <is>
-          <t>IKEA Avsiktlig Teppich, schwarz-weiß gepunktet
-Flachgewebter Teppich in Creme mit schwarzen Punktreihen, IKEA Avsiktlig. Flor 100 % Polypropylen auf Jutekette. Etikett auf der Rückseite vorhanden.</t>
-        </is>
-      </c>
-      <c r="E205" s="13" t="inlineStr">
-        <is>
-          <t>133 × 195 cm</t>
-        </is>
-      </c>
+          <t>Sofa grau, 2-Sitzer
+Kleines Zweisitzer-Sofa mit grauem Steppbezug aus Velours und weißem Metallgestell. Bezug abnehmbar.</t>
+        </is>
+      </c>
+      <c r="E205" s="13" t="n"/>
       <c r="F205" s="23" t="inlineStr">
         <is>
           <t>Galerie</t>
@@ -19969,7 +20169,7 @@
         </is>
       </c>
       <c r="J205" s="24" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="K205" s="25">
         <f>J205*1.19</f>
@@ -19982,7 +20182,7 @@
       </c>
       <c r="M205" s="23" t="inlineStr">
         <is>
-          <t>Versand möglich</t>
+          <t>nur Abholung</t>
         </is>
       </c>
       <c r="N205" s="16" t="n"/>
@@ -19997,16 +20197,16 @@
       <c r="A206" s="9" t="n">
         <v>199</v>
       </c>
-      <c r="B206" s="35" t="inlineStr">
-        <is>
-          <t>BA03-02</t>
+      <c r="B206" s="10" t="inlineStr">
+        <is>
+          <t>BA03-05</t>
         </is>
       </c>
       <c r="C206" s="11" t="n"/>
       <c r="D206" s="12" t="inlineStr">
         <is>
-          <t>Spielküche beige-braun, mehrteilig
-Spielküche aus beschichteter Platte in Creme und Taupe mit Holzarbeitsplatten: Mikrowellenmodul mit Digitalanzeige, Unterschränke mit Kochfeld, Backofen mit Sichtfenster und Spüle, dazu ein Wandregal. Abgerundete Ecken, kindgerechte Höhe.</t>
+          <t>BRIO Puppenwagen rot gepunktet
+Kombi-Puppenwagen von BRIO: weißes Metallgestell mit Luftreifen, roter Stoffbezug mit weißen Punkten, schwenkbarer Schiebebügel, Ablagekorb unten. Markenetikett am Verdeck.</t>
         </is>
       </c>
       <c r="E206" s="13" t="n"/>
@@ -20025,11 +20225,11 @@
       </c>
       <c r="I206" s="10" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Stück</t>
         </is>
       </c>
       <c r="J206" s="14" t="n">
-        <v>250</v>
+        <v>45</v>
       </c>
       <c r="K206" s="15">
         <f>J206*1.19</f>
@@ -20059,14 +20259,14 @@
       </c>
       <c r="B207" s="21" t="inlineStr">
         <is>
-          <t>BA03-03</t>
+          <t>BA03-06</t>
         </is>
       </c>
       <c r="C207" s="22" t="n"/>
       <c r="D207" s="23" t="inlineStr">
         <is>
-          <t>Sofa grau, 2-Sitzer
-Kleines Zweisitzer-Sofa mit grauem Steppbezug aus Velours und weißem Metallgestell. Bezug abnehmbar.</t>
+          <t>Kaufladen weiß mit Aufsatz
+Kaufladen aus Holz, weiß mit grauer Rückwand: Verkaufstheke mit Ablage unten, Aufsatz mit mehreren unterschiedlich großen Fächern.</t>
         </is>
       </c>
       <c r="E207" s="13" t="n"/>
@@ -20089,7 +20289,7 @@
         </is>
       </c>
       <c r="J207" s="24" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="K207" s="25">
         <f>J207*1.19</f>
@@ -20119,14 +20319,14 @@
       </c>
       <c r="B208" s="10" t="inlineStr">
         <is>
-          <t>BA03-05</t>
+          <t>BA03-07</t>
         </is>
       </c>
       <c r="C208" s="11" t="n"/>
       <c r="D208" s="12" t="inlineStr">
         <is>
-          <t>BRIO Puppenwagen rot gepunktet
-Kombi-Puppenwagen von BRIO: weißes Metallgestell mit Luftreifen, roter Stoffbezug mit weißen Punkten, schwenkbarer Schiebebügel, Ablagekorb unten. Markenetikett am Verdeck.</t>
+          <t>Schrank weiß, zwei Türen
+Hoher Schrank in Weiß mit zwei Türen und runden Porzellanknöpfen in Rosenform.</t>
         </is>
       </c>
       <c r="E208" s="13" t="n"/>
@@ -20149,7 +20349,7 @@
         </is>
       </c>
       <c r="J208" s="14" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="K208" s="15">
         <f>J208*1.19</f>
@@ -20179,14 +20379,14 @@
       </c>
       <c r="B209" s="21" t="inlineStr">
         <is>
-          <t>BA03-06</t>
+          <t>BA03-04</t>
         </is>
       </c>
       <c r="C209" s="22" t="n"/>
       <c r="D209" s="23" t="inlineStr">
         <is>
-          <t>Kaufladen weiß mit Aufsatz
-Kaufladen aus Holz, weiß mit grauer Rückwand: Verkaufstheke mit Ablage unten, Aufsatz mit mehreren unterschiedlich großen Fächern.</t>
+          <t>Wandregal Hausform, schwarz
+Wandregale in Hausform aus schwarz lackiertem Holz, zum Aufstellen oder Aufhängen, in unterschiedlichen Größen.</t>
         </is>
       </c>
       <c r="E209" s="13" t="n"/>
@@ -20197,11 +20397,11 @@
       </c>
       <c r="G209" s="21" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H209" s="21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I209" s="21" t="inlineStr">
         <is>
@@ -20209,7 +20409,7 @@
         </is>
       </c>
       <c r="J209" s="24" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="K209" s="25">
         <f>J209*1.19</f>
@@ -20222,7 +20422,7 @@
       </c>
       <c r="M209" s="23" t="inlineStr">
         <is>
-          <t>nur Abholung</t>
+          <t>Versand möglich</t>
         </is>
       </c>
       <c r="N209" s="16" t="n"/>
@@ -20239,20 +20439,20 @@
       </c>
       <c r="B210" s="10" t="inlineStr">
         <is>
-          <t>BA03-07</t>
+          <t>BA04-04</t>
         </is>
       </c>
       <c r="C210" s="11" t="n"/>
       <c r="D210" s="12" t="inlineStr">
         <is>
-          <t>Schrank weiß, zwei Türen
-Hoher Schrank in Weiß mit zwei Türen und runden Porzellanknöpfen in Rosenform.</t>
+          <t>Stapelstuhl Kunststoff weiß, Erwachsenengröße
+Stuhl aus weißem Kunststoff in einem Stück, runde Rückenlehne, konische Beine mit Querstrebe, stapelbar. Erwachsenengröße. Sitzfläche mit Kratzern.</t>
         </is>
       </c>
       <c r="E210" s="13" t="n"/>
       <c r="F210" s="12" t="inlineStr">
         <is>
-          <t>Galerie</t>
+          <t>Gruppenraum 4</t>
         </is>
       </c>
       <c r="G210" s="10" t="inlineStr">
@@ -20261,7 +20461,7 @@
         </is>
       </c>
       <c r="H210" s="10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I210" s="10" t="inlineStr">
         <is>
@@ -20269,7 +20469,7 @@
         </is>
       </c>
       <c r="J210" s="14" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="K210" s="15">
         <f>J210*1.19</f>
@@ -20299,29 +20499,29 @@
       </c>
       <c r="B211" s="21" t="inlineStr">
         <is>
-          <t>BA03-04</t>
+          <t>BA04-05</t>
         </is>
       </c>
       <c r="C211" s="22" t="n"/>
       <c r="D211" s="23" t="inlineStr">
         <is>
-          <t>Wandregal Hausform, schwarz
-Wandregale in Hausform aus schwarz lackiertem Holz, zum Aufstellen oder Aufhängen, in unterschiedlichen Größen.</t>
+          <t>Kinder-Sessel Bugholz mit Polster
+Sessel in Kindergröße: Gestell aus gebogenem Schichtholz in Birke, Auflage aus cremefarbenem Stoff mit Nackenkissen. Bezug abnehmbar, Stoff fleckig.</t>
         </is>
       </c>
       <c r="E211" s="13" t="n"/>
       <c r="F211" s="23" t="inlineStr">
         <is>
-          <t>Galerie</t>
+          <t>Gruppenraum 4</t>
         </is>
       </c>
       <c r="G211" s="21" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H211" s="21" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I211" s="21" t="inlineStr">
         <is>
@@ -20329,7 +20529,7 @@
         </is>
       </c>
       <c r="J211" s="24" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="K211" s="25">
         <f>J211*1.19</f>
@@ -20342,7 +20542,7 @@
       </c>
       <c r="M211" s="23" t="inlineStr">
         <is>
-          <t>Versand möglich</t>
+          <t>nur Abholung</t>
         </is>
       </c>
       <c r="N211" s="16" t="n"/>
@@ -20359,14 +20559,14 @@
       </c>
       <c r="B212" s="10" t="inlineStr">
         <is>
-          <t>BA04-04</t>
+          <t>BA04-06</t>
         </is>
       </c>
       <c r="C212" s="11" t="n"/>
       <c r="D212" s="12" t="inlineStr">
         <is>
-          <t>Stapelstuhl Kunststoff weiß, Erwachsenengröße
-Stuhl aus weißem Kunststoff in einem Stück, runde Rückenlehne, konische Beine mit Querstrebe, stapelbar. Erwachsenengröße. Sitzfläche mit Kratzern.</t>
+          <t>Rollwagen weiß, drei Etagen
+Rollwagen aus weiß lackiertem Stahlblech mit drei Wannenböden und vier Rollen.</t>
         </is>
       </c>
       <c r="E212" s="13" t="n"/>
@@ -20381,7 +20581,7 @@
         </is>
       </c>
       <c r="H212" s="10" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I212" s="10" t="inlineStr">
         <is>
@@ -20419,14 +20619,14 @@
       </c>
       <c r="B213" s="21" t="inlineStr">
         <is>
-          <t>BA04-05</t>
+          <t>BA04-07</t>
         </is>
       </c>
       <c r="C213" s="22" t="n"/>
       <c r="D213" s="23" t="inlineStr">
         <is>
-          <t>Kinder-Sessel Bugholz mit Polster
-Sessel in Kindergröße: Gestell aus gebogenem Schichtholz in Birke, Auflage aus cremefarbenem Stoff mit Nackenkissen. Bezug abnehmbar, Stoff fleckig.</t>
+          <t>Beistelltisch Drahtkorb, weiß
+Runder Beistelltisch: weißer Drahtkorb mit abnehmbarer Platte in heller Holzoptik. Der Korb lässt sich als Ablage nutzen.</t>
         </is>
       </c>
       <c r="E213" s="13" t="n"/>
@@ -20441,7 +20641,7 @@
         </is>
       </c>
       <c r="H213" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I213" s="21" t="inlineStr">
         <is>
@@ -20449,7 +20649,7 @@
         </is>
       </c>
       <c r="J213" s="24" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="K213" s="25">
         <f>J213*1.19</f>
@@ -20479,20 +20679,20 @@
       </c>
       <c r="B214" s="10" t="inlineStr">
         <is>
-          <t>BA04-06</t>
+          <t>BA05-01</t>
         </is>
       </c>
       <c r="C214" s="11" t="n"/>
       <c r="D214" s="12" t="inlineStr">
         <is>
-          <t>Rollwagen weiß, drei Etagen
-Rollwagen aus weiß lackiertem Stahlblech mit drei Wannenböden und vier Rollen.</t>
+          <t>Rollkasten mit großen Kunststoff-Bausteinen
+Flacher Kasten auf Rollen, Front in Weiß, Grün oder Grau, gefüllt mit großen Kunststoff-Bausteinen in Rot, Blau, Gelb und Grün.</t>
         </is>
       </c>
       <c r="E214" s="13" t="n"/>
       <c r="F214" s="12" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Turnraum</t>
         </is>
       </c>
       <c r="G214" s="10" t="inlineStr">
@@ -20501,7 +20701,7 @@
         </is>
       </c>
       <c r="H214" s="10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I214" s="10" t="inlineStr">
         <is>
@@ -20509,7 +20709,7 @@
         </is>
       </c>
       <c r="J214" s="14" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K214" s="15">
         <f>J214*1.19</f>
@@ -20539,20 +20739,20 @@
       </c>
       <c r="B215" s="21" t="inlineStr">
         <is>
-          <t>BA04-07</t>
+          <t>BA05-02</t>
         </is>
       </c>
       <c r="C215" s="22" t="n"/>
       <c r="D215" s="23" t="inlineStr">
         <is>
-          <t>Beistelltisch Drahtkorb, weiß
-Runder Beistelltisch: weißer Drahtkorb mit abnehmbarer Platte in heller Holzoptik. Der Korb lässt sich als Ablage nutzen.</t>
+          <t>BENZ Turnbank
+Turnbank aus Holz mit Schmalseite zum Umdrehen, rutschhemmender Belag, Aufhängehaken an einem Ende. Aufdruck: BENZ Geräte.</t>
         </is>
       </c>
       <c r="E215" s="13" t="n"/>
       <c r="F215" s="23" t="inlineStr">
         <is>
-          <t>Gruppenraum 4</t>
+          <t>Turnraum</t>
         </is>
       </c>
       <c r="G215" s="21" t="inlineStr">
@@ -20569,7 +20769,7 @@
         </is>
       </c>
       <c r="J215" s="24" t="n">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="K215" s="25">
         <f>J215*1.19</f>
@@ -20599,14 +20799,14 @@
       </c>
       <c r="B216" s="10" t="inlineStr">
         <is>
-          <t>BA05-01</t>
+          <t>BA05-03</t>
         </is>
       </c>
       <c r="C216" s="11" t="n"/>
       <c r="D216" s="12" t="inlineStr">
         <is>
-          <t>Rollkasten mit großen Kunststoff-Bausteinen
-Flacher Kasten auf Rollen, Front in Weiß, Grün oder Grau, gefüllt mit großen Kunststoff-Bausteinen in Rot, Blau, Gelb und Grün.</t>
+          <t>Trampolin mit Haltestange
+Rundes Fitness-Trampolin mit gepolstertem Randschutz in Rot und abnehmbarer Haltestange. Aufdruck auf dem Sprungtuch: ANCHEER. Der Randschutz ist an mehreren Stellen eingerissen.</t>
         </is>
       </c>
       <c r="E216" s="13" t="n"/>
@@ -20617,11 +20817,11 @@
       </c>
       <c r="G216" s="10" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>stark gebraucht</t>
         </is>
       </c>
       <c r="H216" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I216" s="10" t="inlineStr">
         <is>
@@ -20657,16 +20857,16 @@
       <c r="A217" s="20" t="n">
         <v>210</v>
       </c>
-      <c r="B217" s="21" t="inlineStr">
-        <is>
-          <t>BA05-02</t>
+      <c r="B217" s="35" t="inlineStr">
+        <is>
+          <t>BA05-04</t>
         </is>
       </c>
       <c r="C217" s="22" t="n"/>
       <c r="D217" s="23" t="inlineStr">
         <is>
-          <t>BENZ Turnbank
-Turnbank aus Holz mit Schmalseite zum Umdrehen, rutschhemmender Belag, Aufhängehaken an einem Ende. Aufdruck: BENZ Geräte.</t>
+          <t>Spielhochbett mit Bällebad und Rutsche
+Großes Spielhochbett aus weiß beschichteter Platte: zwei Liegeflächen oben mit Absturzsicherung, Leiter, Rutsche, runde Bullaugen und darunter ein eingebautes Bällebad einschließlich der Bälle.</t>
         </is>
       </c>
       <c r="E217" s="13" t="n"/>
@@ -20681,7 +20881,7 @@
         </is>
       </c>
       <c r="H217" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I217" s="21" t="inlineStr">
         <is>
@@ -20689,7 +20889,7 @@
         </is>
       </c>
       <c r="J217" s="24" t="n">
-        <v>140</v>
+        <v>750</v>
       </c>
       <c r="K217" s="25">
         <f>J217*1.19</f>
@@ -20719,14 +20919,14 @@
       </c>
       <c r="B218" s="10" t="inlineStr">
         <is>
-          <t>BA05-03</t>
+          <t>BA05-05</t>
         </is>
       </c>
       <c r="C218" s="11" t="n"/>
       <c r="D218" s="12" t="inlineStr">
         <is>
-          <t>Trampolin mit Haltestange
-Rundes Fitness-Trampolin mit gepolstertem Randschutz in Rot und abnehmbarer Haltestange. Aufdruck auf dem Sprungtuch: ANCHEER. Der Randschutz ist an mehreren Stellen eingerissen.</t>
+          <t>Sprossenwand einzeln
+Sprossenwand aus Massivholz zur Wandmontage: zwei kräftige Holme mit durchgehenden Rundsprossen, oben eine ausladende Aufhängeleiste.</t>
         </is>
       </c>
       <c r="E218" s="13" t="n"/>
@@ -20737,11 +20937,11 @@
       </c>
       <c r="G218" s="10" t="inlineStr">
         <is>
-          <t>stark gebraucht</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H218" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I218" s="10" t="inlineStr">
         <is>
@@ -20749,7 +20949,7 @@
         </is>
       </c>
       <c r="J218" s="14" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="K218" s="15">
         <f>J218*1.19</f>
@@ -20779,14 +20979,14 @@
       </c>
       <c r="B219" s="35" t="inlineStr">
         <is>
-          <t>BA05-04</t>
+          <t>BA05-06</t>
         </is>
       </c>
       <c r="C219" s="22" t="n"/>
       <c r="D219" s="23" t="inlineStr">
         <is>
-          <t>Spielhochbett mit Bällebad und Rutsche
-Großes Spielhochbett aus weiß beschichteter Platte: zwei Liegeflächen oben mit Absturzsicherung, Leiter, Rutsche, runde Bullaugen und darunter ein eingebautes Bällebad einschließlich der Bälle.</t>
+          <t>Doppelsprossenwand
+Breite Sprossenwand aus Massivholz zur Wandmontage, zwei Felder nebeneinander mit durchgehenden Querholmen und oberer Ausleger-Leiste.</t>
         </is>
       </c>
       <c r="E219" s="13" t="n"/>
@@ -20809,7 +21009,7 @@
         </is>
       </c>
       <c r="J219" s="24" t="n">
-        <v>750</v>
+        <v>180</v>
       </c>
       <c r="K219" s="25">
         <f>J219*1.19</f>
@@ -20839,14 +21039,14 @@
       </c>
       <c r="B220" s="10" t="inlineStr">
         <is>
-          <t>BA05-05</t>
+          <t>BA05-07</t>
         </is>
       </c>
       <c r="C220" s="11" t="n"/>
       <c r="D220" s="12" t="inlineStr">
         <is>
-          <t>Sprossenwand einzeln
-Sprossenwand aus Massivholz zur Wandmontage: zwei kräftige Holme mit durchgehenden Rundsprossen, oben eine ausladende Aufhängeleiste.</t>
+          <t>Treppenturngerät gepolstert
+Turngerät aus Schaumstoff mit Kunstlederbezug in Creme und Grau: Treppenelement mit drei Stufen und passende Rampe, zusammensteckbar.</t>
         </is>
       </c>
       <c r="E220" s="13" t="n"/>
@@ -20861,7 +21061,7 @@
         </is>
       </c>
       <c r="H220" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I220" s="10" t="inlineStr">
         <is>
@@ -20869,7 +21069,7 @@
         </is>
       </c>
       <c r="J220" s="14" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K220" s="15">
         <f>J220*1.19</f>
@@ -20897,16 +21097,16 @@
       <c r="A221" s="20" t="n">
         <v>214</v>
       </c>
-      <c r="B221" s="35" t="inlineStr">
-        <is>
-          <t>BA05-06</t>
+      <c r="B221" s="21" t="inlineStr">
+        <is>
+          <t>BA05-08</t>
         </is>
       </c>
       <c r="C221" s="22" t="n"/>
       <c r="D221" s="23" t="inlineStr">
         <is>
-          <t>Doppelsprossenwand
-Breite Sprossenwand aus Massivholz zur Wandmontage, zwei Felder nebeneinander mit durchgehenden Querholmen und oberer Ausleger-Leiste.</t>
+          <t>Rody Hüpfpferd, rot und grün
+Hüpfpferd Rody aus Gummi mit weißen Punkten, aufblasbar. Markenaufdruck am Bauch. Eines in Rot mit gelbem Sattel, zwei in Grün mit blauem Sattel.</t>
         </is>
       </c>
       <c r="E221" s="13" t="n"/>
@@ -20921,7 +21121,7 @@
         </is>
       </c>
       <c r="H221" s="21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I221" s="21" t="inlineStr">
         <is>
@@ -20929,7 +21129,7 @@
         </is>
       </c>
       <c r="J221" s="24" t="n">
-        <v>180</v>
+        <v>20</v>
       </c>
       <c r="K221" s="25">
         <f>J221*1.19</f>
@@ -20959,14 +21159,14 @@
       </c>
       <c r="B222" s="10" t="inlineStr">
         <is>
-          <t>BA05-07</t>
+          <t>BA05-09</t>
         </is>
       </c>
       <c r="C222" s="11" t="n"/>
       <c r="D222" s="12" t="inlineStr">
         <is>
-          <t>Treppenturngerät gepolstert
-Turngerät aus Schaumstoff mit Kunstlederbezug in Creme und Grau: Treppenelement mit drei Stufen und passende Rampe, zusammensteckbar.</t>
+          <t>Softbausteine gepolstert, groß
+Große Turn- und Bauelemente aus Schaumstoff mit Kunstlederbezug in Rot, Blau, Grün und Hellgrün: Treppen, Rampen, Wellen, Quader und Keile.</t>
         </is>
       </c>
       <c r="E222" s="13" t="n"/>
@@ -20981,7 +21181,7 @@
         </is>
       </c>
       <c r="H222" s="10" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="I222" s="10" t="inlineStr">
         <is>
@@ -20989,7 +21189,7 @@
         </is>
       </c>
       <c r="J222" s="14" t="n">
-        <v>150</v>
+        <v>45</v>
       </c>
       <c r="K222" s="15">
         <f>J222*1.19</f>
@@ -21019,14 +21219,14 @@
       </c>
       <c r="B223" s="21" t="inlineStr">
         <is>
-          <t>BA05-08</t>
+          <t>BA05-10</t>
         </is>
       </c>
       <c r="C223" s="22" t="n"/>
       <c r="D223" s="23" t="inlineStr">
         <is>
-          <t>Rody Hüpfpferd, rot und grün
-Hüpfpferd Rody aus Gummi mit weißen Punkten, aufblasbar. Markenaufdruck am Bauch. Eines in Rot mit gelbem Sattel, zwei in Grün mit blauem Sattel.</t>
+          <t>Polstersäule grün, Raumteiler
+Standsäule aus Schaumstoff mit Kunstlederbezug: Mantel in Limettengrün, Oberseiten in Grau, mehrere Lappen ergeben im Querschnitt eine Blütenform. Als Wand- und Säulenschutz oder als Raumteiler nutzbar.</t>
         </is>
       </c>
       <c r="E223" s="13" t="n"/>
@@ -21041,7 +21241,7 @@
         </is>
       </c>
       <c r="H223" s="21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I223" s="21" t="inlineStr">
         <is>
@@ -21049,7 +21249,7 @@
         </is>
       </c>
       <c r="J223" s="24" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K223" s="25">
         <f>J223*1.19</f>
@@ -21079,29 +21279,29 @@
       </c>
       <c r="B224" s="10" t="inlineStr">
         <is>
-          <t>BA05-09</t>
+          <t>BA06-02</t>
         </is>
       </c>
       <c r="C224" s="11" t="n"/>
       <c r="D224" s="12" t="inlineStr">
         <is>
-          <t>Softbausteine gepolstert, groß
-Große Turn- und Bauelemente aus Schaumstoff mit Kunstlederbezug in Rot, Blau, Grün und Hellgrün: Treppen, Rampen, Wellen, Quader und Keile.</t>
+          <t>BMW Baby Racer Rutscherauto
+Rutscherauto in Sportwagenform, Karosserie blau mit rotem Sitz, Lenkrad mit Hupe, verchromte Felgen. BMW-Emblem an der Front. Lack stark zerkratzt.</t>
         </is>
       </c>
       <c r="E224" s="13" t="n"/>
       <c r="F224" s="12" t="inlineStr">
         <is>
-          <t>Turnraum</t>
+          <t>Material / Turnraum</t>
         </is>
       </c>
       <c r="G224" s="10" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>stark gebraucht</t>
         </is>
       </c>
       <c r="H224" s="10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I224" s="10" t="inlineStr">
         <is>
@@ -21109,7 +21309,7 @@
         </is>
       </c>
       <c r="J224" s="14" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="K224" s="15">
         <f>J224*1.19</f>
@@ -21139,20 +21339,20 @@
       </c>
       <c r="B225" s="21" t="inlineStr">
         <is>
-          <t>BA05-10</t>
+          <t>BA06-03</t>
         </is>
       </c>
       <c r="C225" s="22" t="n"/>
       <c r="D225" s="23" t="inlineStr">
         <is>
-          <t>Polstersäule grün, Raumteiler
-Standsäule aus Schaumstoff mit Kunstlederbezug: Mantel in Limettengrün, Oberseiten in Grau, mehrere Lappen ergeben im Querschnitt eine Blütenform. Als Wand- und Säulenschutz oder als Raumteiler nutzbar.</t>
+          <t>BIG Bobby Quad
+Quad-Rutscherfahrzeug aus Kunststoff in Schwarz mit limettengrünen Felgen und Lenkergriffen, Stollenreifen. Aufdruck: bobby quad, BIG.</t>
         </is>
       </c>
       <c r="E225" s="13" t="n"/>
       <c r="F225" s="23" t="inlineStr">
         <is>
-          <t>Turnraum</t>
+          <t>Material / Turnraum</t>
         </is>
       </c>
       <c r="G225" s="21" t="inlineStr">
@@ -21161,7 +21361,7 @@
         </is>
       </c>
       <c r="H225" s="21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I225" s="21" t="inlineStr">
         <is>
@@ -21169,7 +21369,7 @@
         </is>
       </c>
       <c r="J225" s="24" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K225" s="25">
         <f>J225*1.19</f>
@@ -21199,14 +21399,14 @@
       </c>
       <c r="B226" s="10" t="inlineStr">
         <is>
-          <t>BA06-02</t>
+          <t>BA06-04</t>
         </is>
       </c>
       <c r="C226" s="11" t="n"/>
       <c r="D226" s="12" t="inlineStr">
         <is>
-          <t>BMW Baby Racer Rutscherauto
-Rutscherauto in Sportwagenform, Karosserie blau mit rotem Sitz, Lenkrad mit Hupe, verchromte Felgen. BMW-Emblem an der Front. Lack stark zerkratzt.</t>
+          <t>Holz-Dreirad mit Kuhkopf
+Rutschfahrzeug aus Massivholz mit vier Rädern, ovalem Sitz und Lehne, vorn ein Kuhkopf mit Stoffohren und gemaltem Gesicht.</t>
         </is>
       </c>
       <c r="E226" s="13" t="n"/>
@@ -21217,7 +21417,7 @@
       </c>
       <c r="G226" s="10" t="inlineStr">
         <is>
-          <t>stark gebraucht</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H226" s="10" t="n">
@@ -21229,7 +21429,7 @@
         </is>
       </c>
       <c r="J226" s="14" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="K226" s="15">
         <f>J226*1.19</f>
@@ -21259,14 +21459,14 @@
       </c>
       <c r="B227" s="21" t="inlineStr">
         <is>
-          <t>BA06-03</t>
+          <t>BA06-05</t>
         </is>
       </c>
       <c r="C227" s="22" t="n"/>
       <c r="D227" s="23" t="inlineStr">
         <is>
-          <t>BIG Bobby Quad
-Quad-Rutscherfahrzeug aus Kunststoff in Schwarz mit limettengrünen Felgen und Lenkergriffen, Stollenreifen. Aufdruck: bobby quad, BIG.</t>
+          <t>Schaukel- und Rutschtier aus Formholz
+Fahrzeug aus weiß lackiertem Formholz mit Naturholz-Lehne, vier kleinen Rollen und schwarzen Griffen. Lack an vielen Stellen abgeplatzt.</t>
         </is>
       </c>
       <c r="E227" s="13" t="n"/>
@@ -21277,11 +21477,11 @@
       </c>
       <c r="G227" s="21" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>stark gebraucht</t>
         </is>
       </c>
       <c r="H227" s="21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I227" s="21" t="inlineStr">
         <is>
@@ -21289,7 +21489,7 @@
         </is>
       </c>
       <c r="J227" s="24" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K227" s="25">
         <f>J227*1.19</f>
@@ -21319,14 +21519,14 @@
       </c>
       <c r="B228" s="10" t="inlineStr">
         <is>
-          <t>BA06-04</t>
+          <t>BA06-06</t>
         </is>
       </c>
       <c r="C228" s="11" t="n"/>
       <c r="D228" s="12" t="inlineStr">
         <is>
-          <t>Holz-Dreirad mit Kuhkopf
-Rutschfahrzeug aus Massivholz mit vier Rädern, ovalem Sitz und Lehne, vorn ein Kuhkopf mit Stoffohren und gemaltem Gesicht.</t>
+          <t>BIG Bobby Car Feuerwehr
+Rutscherauto als Feuerwehrfahrzeug aus rotem Kunststoff mit Blaulicht, drehbarem Wasserwerfer und Stollenreifen. Aufdruck: BIG.</t>
         </is>
       </c>
       <c r="E228" s="13" t="n"/>
@@ -21341,7 +21541,7 @@
         </is>
       </c>
       <c r="H228" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I228" s="10" t="inlineStr">
         <is>
@@ -21349,7 +21549,7 @@
         </is>
       </c>
       <c r="J228" s="14" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K228" s="15">
         <f>J228*1.19</f>
@@ -21379,14 +21579,14 @@
       </c>
       <c r="B229" s="21" t="inlineStr">
         <is>
-          <t>BA06-05</t>
+          <t>BA06-07</t>
         </is>
       </c>
       <c r="C229" s="22" t="n"/>
       <c r="D229" s="23" t="inlineStr">
         <is>
-          <t>Schaukel- und Rutschtier aus Formholz
-Fahrzeug aus weiß lackiertem Formholz mit Naturholz-Lehne, vier kleinen Rollen und schwarzen Griffen. Lack an vielen Stellen abgeplatzt.</t>
+          <t>Klettergerüst Holz
+Klettergerüst aus Buche massiv mit Rundsprossen und seitlichen Wangen, zusammenklappbar.</t>
         </is>
       </c>
       <c r="E229" s="13" t="n"/>
@@ -21397,11 +21597,11 @@
       </c>
       <c r="G229" s="21" t="inlineStr">
         <is>
-          <t>stark gebraucht</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H229" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I229" s="21" t="inlineStr">
         <is>
@@ -21409,7 +21609,7 @@
         </is>
       </c>
       <c r="J229" s="24" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K229" s="25">
         <f>J229*1.19</f>
@@ -21439,14 +21639,14 @@
       </c>
       <c r="B230" s="10" t="inlineStr">
         <is>
-          <t>BA06-06</t>
+          <t>BA06-08</t>
         </is>
       </c>
       <c r="C230" s="11" t="n"/>
       <c r="D230" s="12" t="inlineStr">
         <is>
-          <t>BIG Bobby Car Feuerwehr
-Rutscherauto als Feuerwehrfahrzeug aus rotem Kunststoff mit Blaulicht, drehbarem Wasserwerfer und Stollenreifen. Aufdruck: BIG.</t>
+          <t>Klettergerüst grün mit Rutschbrett
+Klettergerüst mit grün lackiertem Metallrahmen, Rundsprossen aus Holz und einem Rutschbrett mit dunkler Lauffläche.</t>
         </is>
       </c>
       <c r="E230" s="13" t="n"/>
@@ -21461,7 +21661,7 @@
         </is>
       </c>
       <c r="H230" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I230" s="10" t="inlineStr">
         <is>
@@ -21469,7 +21669,7 @@
         </is>
       </c>
       <c r="J230" s="14" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="K230" s="15">
         <f>J230*1.19</f>
@@ -21499,14 +21699,14 @@
       </c>
       <c r="B231" s="21" t="inlineStr">
         <is>
-          <t>BA06-07</t>
+          <t>BA06-09</t>
         </is>
       </c>
       <c r="C231" s="22" t="n"/>
       <c r="D231" s="23" t="inlineStr">
         <is>
-          <t>Klettergerüst Holz
-Klettergerüst aus Buche massiv mit Rundsprossen und seitlichen Wangen, zusammenklappbar.</t>
+          <t>Holz-Lastwagen zum Rutschen
+Rutschfahrzeug aus Massivholz in Lastwagenform: offene Ladefläche mit Bordwänden, gepolsterter Sitz vor dem Führerhaus, Holzlenkrad und vier Gummiräder mit roten Felgen.</t>
         </is>
       </c>
       <c r="E231" s="13" t="n"/>
@@ -21521,7 +21721,7 @@
         </is>
       </c>
       <c r="H231" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I231" s="21" t="inlineStr">
         <is>
@@ -21529,7 +21729,7 @@
         </is>
       </c>
       <c r="J231" s="24" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="K231" s="25">
         <f>J231*1.19</f>
@@ -21559,14 +21759,14 @@
       </c>
       <c r="B232" s="10" t="inlineStr">
         <is>
-          <t>BA06-08</t>
+          <t>BA06-10</t>
         </is>
       </c>
       <c r="C232" s="11" t="n"/>
       <c r="D232" s="12" t="inlineStr">
         <is>
-          <t>Klettergerüst grün mit Rutschbrett
-Klettergerüst mit grün lackiertem Metallrahmen, Rundsprossen aus Holz und einem Rutschbrett mit dunkler Lauffläche.</t>
+          <t>Feuerwehrhaus aus Holz
+Spiel-Feuerwehrhaus aus Holz mit rot lackierten Wänden, dunklem Dach, aufklappbarem Tor und Zwischenboden. Aufdruck: FIRE STATION. Farbe stark abgegriffen.</t>
         </is>
       </c>
       <c r="E232" s="13" t="n"/>
@@ -21577,11 +21777,11 @@
       </c>
       <c r="G232" s="10" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>stark gebraucht</t>
         </is>
       </c>
       <c r="H232" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I232" s="10" t="inlineStr">
         <is>
@@ -21589,7 +21789,7 @@
         </is>
       </c>
       <c r="J232" s="14" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
       <c r="K232" s="15">
         <f>J232*1.19</f>
@@ -21619,14 +21819,14 @@
       </c>
       <c r="B233" s="21" t="inlineStr">
         <is>
-          <t>BA06-09</t>
+          <t>BA06-11</t>
         </is>
       </c>
       <c r="C233" s="22" t="n"/>
       <c r="D233" s="23" t="inlineStr">
         <is>
-          <t>Holz-Lastwagen zum Rutschen
-Rutschfahrzeug aus Massivholz in Lastwagenform: offene Ladefläche mit Bordwänden, gepolsterter Sitz vor dem Führerhaus, Holzlenkrad und vier Gummiräder mit roten Felgen.</t>
+          <t>Sitzschaukel Kunststoff mit Seilen
+Babyschaukel aus Kunststoff: Sitzschale in Violett mit limettengrünem Sicherheitsbügel, Aufhängung über weiße Seile.</t>
         </is>
       </c>
       <c r="E233" s="13" t="n"/>
@@ -21649,7 +21849,7 @@
         </is>
       </c>
       <c r="J233" s="24" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="K233" s="25">
         <f>J233*1.19</f>
@@ -21679,14 +21879,14 @@
       </c>
       <c r="B234" s="10" t="inlineStr">
         <is>
-          <t>BA06-10</t>
+          <t>BA06-12</t>
         </is>
       </c>
       <c r="C234" s="11" t="n"/>
       <c r="D234" s="12" t="inlineStr">
         <is>
-          <t>Feuerwehrhaus aus Holz
-Spiel-Feuerwehrhaus aus Holz mit rot lackierten Wänden, dunklem Dach, aufklappbarem Tor und Zwischenboden. Aufdruck: FIRE STATION. Farbe stark abgegriffen.</t>
+          <t>Spieltunnel grün, 180 cm
+Spieltunnel aus grünem Stoff mit roten Ringen, etwa 180 cm lang bei 45 cm Durchmesser. Faltbar, mit Originalkarton.</t>
         </is>
       </c>
       <c r="E234" s="13" t="n"/>
@@ -21697,7 +21897,7 @@
       </c>
       <c r="G234" s="10" t="inlineStr">
         <is>
-          <t>stark gebraucht</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H234" s="10" t="n">
@@ -21709,7 +21909,7 @@
         </is>
       </c>
       <c r="J234" s="14" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K234" s="15">
         <f>J234*1.19</f>
@@ -21739,29 +21939,29 @@
       </c>
       <c r="B235" s="21" t="inlineStr">
         <is>
-          <t>BA06-11</t>
+          <t>BA07-01</t>
         </is>
       </c>
       <c r="C235" s="22" t="n"/>
       <c r="D235" s="23" t="inlineStr">
         <is>
-          <t>Sitzschaukel Kunststoff mit Seilen
-Babyschaukel aus Kunststoff: Sitzschale in Violett mit limettengrünem Sicherheitsbügel, Aufhängung über weiße Seile.</t>
+          <t>Kissen in Wolkenform, hellblau
+Dekokissen in Wolkenform aus hellblauem Samtstoff, mit aufgestickten Augen, Lächeln und rosa Wangen.</t>
         </is>
       </c>
       <c r="E235" s="13" t="n"/>
       <c r="F235" s="23" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Klassenzimmer</t>
         </is>
       </c>
       <c r="G235" s="21" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H235" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I235" s="21" t="inlineStr">
         <is>
@@ -21769,7 +21969,7 @@
         </is>
       </c>
       <c r="J235" s="24" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K235" s="25">
         <f>J235*1.19</f>
@@ -21782,7 +21982,7 @@
       </c>
       <c r="M235" s="23" t="inlineStr">
         <is>
-          <t>nur Abholung</t>
+          <t>Versand möglich</t>
         </is>
       </c>
       <c r="N235" s="16" t="n"/>
@@ -21799,20 +21999,20 @@
       </c>
       <c r="B236" s="10" t="inlineStr">
         <is>
-          <t>BA06-12</t>
+          <t>BA07-02</t>
         </is>
       </c>
       <c r="C236" s="11" t="n"/>
       <c r="D236" s="12" t="inlineStr">
         <is>
-          <t>Spieltunnel grün, 180 cm
-Spieltunnel aus grünem Stoff mit roten Ringen, etwa 180 cm lang bei 45 cm Durchmesser. Faltbar, mit Originalkarton.</t>
+          <t>Wandleuchte rund mit Holzrand
+Runde Wandleuchte: Rahmen aus gebogenem Schichtholz mit satinierter Scheibe, flache Bauform, Zuleitung sichtbar verlegt. Zwei verschiedene Durchmesser.</t>
         </is>
       </c>
       <c r="E236" s="13" t="n"/>
       <c r="F236" s="12" t="inlineStr">
         <is>
-          <t>Material / Turnraum</t>
+          <t>Klassenzimmer</t>
         </is>
       </c>
       <c r="G236" s="10" t="inlineStr">
@@ -21821,7 +22021,7 @@
         </is>
       </c>
       <c r="H236" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I236" s="10" t="inlineStr">
         <is>
@@ -21829,7 +22029,7 @@
         </is>
       </c>
       <c r="J236" s="14" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="K236" s="15">
         <f>J236*1.19</f>
@@ -21859,14 +22059,14 @@
       </c>
       <c r="B237" s="21" t="inlineStr">
         <is>
-          <t>BA07-01</t>
+          <t>BA07-03</t>
         </is>
       </c>
       <c r="C237" s="22" t="n"/>
       <c r="D237" s="23" t="inlineStr">
         <is>
-          <t>Kissen in Wolkenform, hellblau
-Dekokissen in Wolkenform aus hellblauem Samtstoff, mit aufgestickten Augen, Lächeln und rosa Wangen.</t>
+          <t>Standregal grau mit Wolkenaufsatz
+Schmales Standregal in Grau mit drei Ablagen und vorderen Haltelleisten, oben ein ausgesägter Wolkenaufsatz, auf schrägen Holzbeinen. Als Bücherregal genutzt.</t>
         </is>
       </c>
       <c r="E237" s="13" t="n"/>
@@ -21877,11 +22077,11 @@
       </c>
       <c r="G237" s="21" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H237" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I237" s="21" t="inlineStr">
         <is>
@@ -21889,7 +22089,7 @@
         </is>
       </c>
       <c r="J237" s="24" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="K237" s="25">
         <f>J237*1.19</f>
@@ -21902,7 +22102,7 @@
       </c>
       <c r="M237" s="23" t="inlineStr">
         <is>
-          <t>Versand möglich</t>
+          <t>nur Abholung</t>
         </is>
       </c>
       <c r="N237" s="16" t="n"/>
@@ -21919,14 +22119,14 @@
       </c>
       <c r="B238" s="10" t="inlineStr">
         <is>
-          <t>BA07-02</t>
+          <t>BA07-05</t>
         </is>
       </c>
       <c r="C238" s="11" t="n"/>
       <c r="D238" s="12" t="inlineStr">
         <is>
-          <t>Wandleuchte rund mit Holzrand
-Runde Wandleuchte: Rahmen aus gebogenem Schichtholz mit satinierter Scheibe, flache Bauform, Zuleitung sichtbar verlegt. Zwei verschiedene Durchmesser.</t>
+          <t>Tisch weiß, lang, auf schwarzen Beinen
+Langer Tisch mit weißer Platte auf vier schwarzen Rundbeinen mit Gleitern. Als Arbeits- und Ablagefläche genutzt.</t>
         </is>
       </c>
       <c r="E238" s="13" t="n"/>
@@ -21941,7 +22141,7 @@
         </is>
       </c>
       <c r="H238" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I238" s="10" t="inlineStr">
         <is>
@@ -21949,7 +22149,7 @@
         </is>
       </c>
       <c r="J238" s="14" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="K238" s="15">
         <f>J238*1.19</f>
@@ -21979,14 +22179,14 @@
       </c>
       <c r="B239" s="21" t="inlineStr">
         <is>
-          <t>BA07-03</t>
+          <t>BA07-06</t>
         </is>
       </c>
       <c r="C239" s="22" t="n"/>
       <c r="D239" s="23" t="inlineStr">
         <is>
-          <t>Standregal grau mit Wolkenaufsatz
-Schmales Standregal in Grau mit drei Ablagen und vorderen Haltelleisten, oben ein ausgesägter Wolkenaufsatz, auf schrägen Holzbeinen. Als Bücherregal genutzt.</t>
+          <t>Regal creme, 16 Fächer, auf Metallbeinen
+Großes Regal in Creme mit sechzehn Fächern in vier Reihen, auf schräg gestellten schwarzen Metallbeinen.</t>
         </is>
       </c>
       <c r="E239" s="13" t="n"/>
@@ -22009,7 +22209,7 @@
         </is>
       </c>
       <c r="J239" s="24" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="K239" s="25">
         <f>J239*1.19</f>
@@ -22039,25 +22239,25 @@
       </c>
       <c r="B240" s="10" t="inlineStr">
         <is>
-          <t>BA07-05</t>
+          <t>BA08-05</t>
         </is>
       </c>
       <c r="C240" s="11" t="n"/>
       <c r="D240" s="12" t="inlineStr">
         <is>
-          <t>Tisch weiß, lang, auf schwarzen Beinen
-Langer Tisch mit weißer Platte auf vier schwarzen Rundbeinen mit Gleitern. Als Arbeits- und Ablagefläche genutzt.</t>
+          <t>Acrylbild schwarz-weiß, Kreise mit Punkten
+Acryl auf Leinwand, großes Quadrat: mit breitem Pinsel gezogene Kreise, darin je mehrere gemalte Punkte – die Anmutung von Würfeln. Eigenarbeit einer Privatperson, nicht signiert.</t>
         </is>
       </c>
       <c r="E240" s="13" t="n"/>
       <c r="F240" s="12" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Atelier</t>
         </is>
       </c>
       <c r="G240" s="10" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H240" s="10" t="n">
@@ -22069,7 +22269,7 @@
         </is>
       </c>
       <c r="J240" s="14" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="K240" s="15">
         <f>J240*1.19</f>
@@ -22082,7 +22282,7 @@
       </c>
       <c r="M240" s="12" t="inlineStr">
         <is>
-          <t>nur Abholung</t>
+          <t>Versand möglich</t>
         </is>
       </c>
       <c r="N240" s="16" t="n"/>
@@ -22099,20 +22299,20 @@
       </c>
       <c r="B241" s="21" t="inlineStr">
         <is>
-          <t>BA07-06</t>
+          <t>BA08-06</t>
         </is>
       </c>
       <c r="C241" s="22" t="n"/>
       <c r="D241" s="23" t="inlineStr">
         <is>
-          <t>Regal creme, 16 Fächer, auf Metallbeinen
-Großes Regal in Creme mit sechzehn Fächern in vier Reihen, auf schräg gestellten schwarzen Metallbeinen.</t>
+          <t>VS Schalenstuhl grau, Vierfußgestell
+Schalenstuhl von VS (Vereinigte Spezialmöbelfabriken): graue Kunststoffschale mit Rautenstruktur und Griffloch in der Lehne, auf grauem Vierfußgestell aus Rohr. Auf den Stühlen aus dem Atelier sind Farbspritzer.</t>
         </is>
       </c>
       <c r="E241" s="13" t="n"/>
       <c r="F241" s="23" t="inlineStr">
         <is>
-          <t>Klassenzimmer</t>
+          <t>Atelier</t>
         </is>
       </c>
       <c r="G241" s="21" t="inlineStr">
@@ -22121,7 +22321,7 @@
         </is>
       </c>
       <c r="H241" s="21" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I241" s="21" t="inlineStr">
         <is>
@@ -22129,7 +22329,7 @@
         </is>
       </c>
       <c r="J241" s="24" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="K241" s="25">
         <f>J241*1.19</f>
@@ -22159,14 +22359,14 @@
       </c>
       <c r="B242" s="10" t="inlineStr">
         <is>
-          <t>BA08-05</t>
+          <t>BA08-07</t>
         </is>
       </c>
       <c r="C242" s="11" t="n"/>
       <c r="D242" s="12" t="inlineStr">
         <is>
-          <t>Acrylbild schwarz-weiß, Kreise mit Punkten
-Acryl auf Leinwand, großes Quadrat: mit breitem Pinsel gezogene Kreise, darin je mehrere gemalte Punkte – die Anmutung von Würfeln. Eigenarbeit einer Privatperson, nicht signiert.</t>
+          <t>Konvolut Feinkrepp-Papier
+Rollen Feinkrepp von Marpa Jansen, je 50 × 250 cm, in Blau, Grün, Gelb, Rot, Orange und Braun. Teils angebrochen, dazu ein Beutel mit zugeschnittenen Schnipseln.</t>
         </is>
       </c>
       <c r="E242" s="13" t="n"/>
@@ -22177,7 +22377,7 @@
       </c>
       <c r="G242" s="10" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H242" s="10" t="n">
@@ -22185,11 +22385,11 @@
       </c>
       <c r="I242" s="10" t="inlineStr">
         <is>
-          <t>Stück</t>
+          <t>Konvolut</t>
         </is>
       </c>
       <c r="J242" s="14" t="n">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="K242" s="15">
         <f>J242*1.19</f>
@@ -22202,7 +22402,7 @@
       </c>
       <c r="M242" s="12" t="inlineStr">
         <is>
-          <t>Versand möglich</t>
+          <t>nur Abholung</t>
         </is>
       </c>
       <c r="N242" s="16" t="n"/>
@@ -22219,14 +22419,14 @@
       </c>
       <c r="B243" s="21" t="inlineStr">
         <is>
-          <t>BA08-06</t>
+          <t>BA08-08</t>
         </is>
       </c>
       <c r="C243" s="22" t="n"/>
       <c r="D243" s="23" t="inlineStr">
         <is>
-          <t>VS Schalenstuhl grau, Vierfußgestell
-Schalenstuhl von VS (Vereinigte Spezialmöbelfabriken): graue Kunststoffschale mit Rautenstruktur und Griffloch in der Lehne, auf grauem Vierfußgestell aus Rohr. Auf den Stühlen aus dem Atelier sind Farbspritzer.</t>
+          <t>Deko-Pilze auf Holzfuß
+Dekopilze mit gedrechseltem Fuß aus Massivholz: zwei mit gehämmerter Metallkappe in Silberoptik, einer mit Kappe in Betonoptik.</t>
         </is>
       </c>
       <c r="E243" s="13" t="n"/>
@@ -22237,11 +22437,11 @@
       </c>
       <c r="G243" s="21" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H243" s="21" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I243" s="21" t="inlineStr">
         <is>
@@ -22249,7 +22449,7 @@
         </is>
       </c>
       <c r="J243" s="24" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="K243" s="25">
         <f>J243*1.19</f>
@@ -22262,7 +22462,7 @@
       </c>
       <c r="M243" s="23" t="inlineStr">
         <is>
-          <t>nur Abholung</t>
+          <t>Versand möglich</t>
         </is>
       </c>
       <c r="N243" s="16" t="n"/>
@@ -22279,14 +22479,14 @@
       </c>
       <c r="B244" s="10" t="inlineStr">
         <is>
-          <t>BA08-07</t>
+          <t>BA08-09</t>
         </is>
       </c>
       <c r="C244" s="11" t="n"/>
       <c r="D244" s="12" t="inlineStr">
         <is>
-          <t>Konvolut Feinkrepp-Papier
-Rollen Feinkrepp von Marpa Jansen, je 50 × 250 cm, in Blau, Grün, Gelb, Rot, Orange und Braun. Teils angebrochen, dazu ein Beutel mit zugeschnittenen Schnipseln.</t>
+          <t>Bastelscheren im Betzold-Holzblock
+Kinder-Bastelscheren mit Kunststoffgriffen in gemischten Farben, dazu ein Holzblock mit Steckbohrungen von Betzold als Ablage.</t>
         </is>
       </c>
       <c r="E244" s="13" t="n"/>
@@ -22301,15 +22501,15 @@
         </is>
       </c>
       <c r="H244" s="10" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I244" s="10" t="inlineStr">
         <is>
-          <t>Konvolut</t>
+          <t>Stück</t>
         </is>
       </c>
       <c r="J244" s="14" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="K244" s="15">
         <f>J244*1.19</f>
@@ -22339,14 +22539,14 @@
       </c>
       <c r="B245" s="21" t="inlineStr">
         <is>
-          <t>BA08-08</t>
+          <t>BA08-10</t>
         </is>
       </c>
       <c r="C245" s="22" t="n"/>
       <c r="D245" s="23" t="inlineStr">
         <is>
-          <t>Deko-Pilze auf Holzfuß
-Dekopilze mit gedrechseltem Fuß aus Massivholz: zwei mit gehämmerter Metallkappe in Silberoptik, einer mit Kappe in Betonoptik.</t>
+          <t>Kunstpflanze Gras im weißen Topf
+Künstliches Ziergras mit gedrehten Halmen in einem weißen Übertopf aus Metall mit durchbrochenem Spitzenrand.</t>
         </is>
       </c>
       <c r="E245" s="13" t="n"/>
@@ -22361,7 +22561,7 @@
         </is>
       </c>
       <c r="H245" s="21" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I245" s="21" t="inlineStr">
         <is>
@@ -22369,7 +22569,7 @@
         </is>
       </c>
       <c r="J245" s="24" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K245" s="25">
         <f>J245*1.19</f>
@@ -22399,14 +22599,14 @@
       </c>
       <c r="B246" s="10" t="inlineStr">
         <is>
-          <t>BA08-09</t>
+          <t>BA08-11</t>
         </is>
       </c>
       <c r="C246" s="11" t="n"/>
       <c r="D246" s="12" t="inlineStr">
         <is>
-          <t>Bastelscheren im Betzold-Holzblock
-Kinder-Bastelscheren mit Kunststoffgriffen in gemischten Farben, dazu ein Holzblock mit Steckbohrungen von Betzold als Ablage.</t>
+          <t>Bilderrahmen mit Zeichenwerkzeug
+Zwei schwarze Rahmen hinter Glas, gepunkteter Hintergrund: einer mit Bleistift, Lineal und gefaltetem Papier, einer mit sechs Pinseln in verschiedenen Breiten. Passend für ein Atelier oder Arbeitszimmer.</t>
         </is>
       </c>
       <c r="E246" s="13" t="n"/>
@@ -22417,11 +22617,11 @@
       </c>
       <c r="G246" s="10" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H246" s="10" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="I246" s="10" t="inlineStr">
         <is>
@@ -22429,7 +22629,7 @@
         </is>
       </c>
       <c r="J246" s="14" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="K246" s="15">
         <f>J246*1.19</f>
@@ -22442,7 +22642,7 @@
       </c>
       <c r="M246" s="12" t="inlineStr">
         <is>
-          <t>nur Abholung</t>
+          <t>Versand möglich</t>
         </is>
       </c>
       <c r="N246" s="16" t="n"/>
@@ -22459,14 +22659,14 @@
       </c>
       <c r="B247" s="21" t="inlineStr">
         <is>
-          <t>BA08-10</t>
+          <t>BA08-12</t>
         </is>
       </c>
       <c r="C247" s="22" t="n"/>
       <c r="D247" s="23" t="inlineStr">
         <is>
-          <t>Kunstpflanze Gras im weißen Topf
-Künstliches Ziergras mit gedrehten Halmen in einem weißen Übertopf aus Metall mit durchbrochenem Spitzenrand.</t>
+          <t>Wandregalbrett weiß
+Schmales weißes Wandregalbrett mit vorderer Kante, zum Anschrauben.</t>
         </is>
       </c>
       <c r="E247" s="13" t="n"/>
@@ -22477,11 +22677,11 @@
       </c>
       <c r="G247" s="21" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H247" s="21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I247" s="21" t="inlineStr">
         <is>
@@ -22502,7 +22702,7 @@
       </c>
       <c r="M247" s="23" t="inlineStr">
         <is>
-          <t>Versand möglich</t>
+          <t>nur Abholung</t>
         </is>
       </c>
       <c r="N247" s="16" t="n"/>
@@ -22517,31 +22717,31 @@
       <c r="A248" s="9" t="n">
         <v>241</v>
       </c>
-      <c r="B248" s="10" t="inlineStr">
-        <is>
-          <t>BA08-11</t>
+      <c r="B248" s="35" t="inlineStr">
+        <is>
+          <t>BU01-01</t>
         </is>
       </c>
       <c r="C248" s="11" t="n"/>
       <c r="D248" s="12" t="inlineStr">
         <is>
-          <t>Bilderrahmen mit Zeichenwerkzeug
-Zwei schwarze Rahmen hinter Glas, gepunkteter Hintergrund: einer mit Bleistift, Lineal und gefaltetem Papier, einer mit sechs Pinseln in verschiedenen Breiten. Passend für ein Atelier oder Arbeitszimmer.</t>
+          <t>Hausbett Buche massiv
+Kinderbett in Hausform aus massiver Buche, natur geölt, mit Dachgiebel und umlaufendem Rahmen. Einschließlich Matratze.</t>
         </is>
       </c>
       <c r="E248" s="13" t="n"/>
       <c r="F248" s="12" t="inlineStr">
         <is>
-          <t>Atelier</t>
+          <t>Flur 1</t>
         </is>
       </c>
       <c r="G248" s="10" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H248" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I248" s="10" t="inlineStr">
         <is>
@@ -22549,7 +22749,7 @@
         </is>
       </c>
       <c r="J248" s="14" t="n">
-        <v>25</v>
+        <v>220</v>
       </c>
       <c r="K248" s="15">
         <f>J248*1.19</f>
@@ -22562,7 +22762,7 @@
       </c>
       <c r="M248" s="12" t="inlineStr">
         <is>
-          <t>Versand möglich</t>
+          <t>nur Abholung</t>
         </is>
       </c>
       <c r="N248" s="16" t="n"/>
@@ -22579,20 +22779,20 @@
       </c>
       <c r="B249" s="21" t="inlineStr">
         <is>
-          <t>BA08-12</t>
+          <t>BU01-02</t>
         </is>
       </c>
       <c r="C249" s="22" t="n"/>
       <c r="D249" s="23" t="inlineStr">
         <is>
-          <t>Wandregalbrett weiß
-Schmales weißes Wandregalbrett mit vorderer Kante, zum Anschrauben.</t>
+          <t>Spielküche klein mit Mikrowelle
+Kleine Spielküche aus Birke-Multiplex mit weißen Fronten: Aufsatz mit Mikrowelle und zwei offenen Fächern, Arbeitsplatte mit Kochfeld, Spülbecken und Wasserhahn, darunter Backofen mit Sichtfenster und ein Schrank.</t>
         </is>
       </c>
       <c r="E249" s="13" t="n"/>
       <c r="F249" s="23" t="inlineStr">
         <is>
-          <t>Atelier</t>
+          <t>Flur 1</t>
         </is>
       </c>
       <c r="G249" s="21" t="inlineStr">
@@ -22601,7 +22801,7 @@
         </is>
       </c>
       <c r="H249" s="21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I249" s="21" t="inlineStr">
         <is>
@@ -22609,7 +22809,7 @@
         </is>
       </c>
       <c r="J249" s="24" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K249" s="25">
         <f>J249*1.19</f>
@@ -22637,16 +22837,16 @@
       <c r="A250" s="9" t="n">
         <v>243</v>
       </c>
-      <c r="B250" s="35" t="inlineStr">
-        <is>
-          <t>BU01-01</t>
+      <c r="B250" s="10" t="inlineStr">
+        <is>
+          <t>BU01-04</t>
         </is>
       </c>
       <c r="C250" s="11" t="n"/>
       <c r="D250" s="12" t="inlineStr">
         <is>
-          <t>Hausbett Buche massiv
-Kinderbett in Hausform aus massiver Buche, natur geölt, mit Dachgiebel und umlaufendem Rahmen. Einschließlich Matratze.</t>
+          <t>Gestell Kiefer mit sechs Wannen
+Gestell aus Kiefer massiv mit sechs weißen Kunststoffwannen in zwei Reihen, als Spielzeugaufbewahrung genutzt.</t>
         </is>
       </c>
       <c r="E250" s="13" t="n"/>
@@ -22669,7 +22869,7 @@
         </is>
       </c>
       <c r="J250" s="14" t="n">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="K250" s="15">
         <f>J250*1.19</f>
@@ -22699,14 +22899,14 @@
       </c>
       <c r="B251" s="21" t="inlineStr">
         <is>
-          <t>BU01-02</t>
+          <t>BU01-05</t>
         </is>
       </c>
       <c r="C251" s="22" t="n"/>
       <c r="D251" s="23" t="inlineStr">
         <is>
-          <t>Spielküche klein mit Mikrowelle
-Kleine Spielküche aus Birke-Multiplex mit weißen Fronten: Aufsatz mit Mikrowelle und zwei offenen Fächern, Arbeitsplatte mit Kochfeld, Spülbecken und Wasserhahn, darunter Backofen mit Sichtfenster und ein Schrank.</t>
+          <t>IKEA Småstad Kindertisch weiß
+Niedriger Kindertisch von IKEA in Weiß mit Seitenwangen, Etikett an der Unterseite: Småstad, 804.335.42. Die Platte ist stark verkratzt und mit einer Schutzfolie belegt.</t>
         </is>
       </c>
       <c r="E251" s="13" t="n"/>
@@ -22717,11 +22917,11 @@
       </c>
       <c r="G251" s="21" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>stark gebraucht</t>
         </is>
       </c>
       <c r="H251" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I251" s="21" t="inlineStr">
         <is>
@@ -22729,7 +22929,7 @@
         </is>
       </c>
       <c r="J251" s="24" t="n">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="K251" s="25">
         <f>J251*1.19</f>
@@ -22759,14 +22959,14 @@
       </c>
       <c r="B252" s="10" t="inlineStr">
         <is>
-          <t>BU01-04</t>
+          <t>BU01-06</t>
         </is>
       </c>
       <c r="C252" s="11" t="n"/>
       <c r="D252" s="12" t="inlineStr">
         <is>
-          <t>Gestell Kiefer mit sechs Wannen
-Gestell aus Kiefer massiv mit sechs weißen Kunststoffwannen in zwei Reihen, als Spielzeugaufbewahrung genutzt.</t>
+          <t>Wanddeko Lama, Steckwand
+Wandelement in Lamaform aus weiß lackiertem Holz mit grauen Ohren, Gesicht und Füßen, durchgehend gelocht zum Einstecken von Haken oder Stäben.</t>
         </is>
       </c>
       <c r="E252" s="13" t="n"/>
@@ -22781,7 +22981,7 @@
         </is>
       </c>
       <c r="H252" s="10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I252" s="10" t="inlineStr">
         <is>
@@ -22789,7 +22989,7 @@
         </is>
       </c>
       <c r="J252" s="14" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="K252" s="15">
         <f>J252*1.19</f>
@@ -22819,14 +23019,14 @@
       </c>
       <c r="B253" s="21" t="inlineStr">
         <is>
-          <t>BU01-05</t>
+          <t>BU01-07</t>
         </is>
       </c>
       <c r="C253" s="22" t="n"/>
       <c r="D253" s="23" t="inlineStr">
         <is>
-          <t>IKEA Småstad Kindertisch weiß
-Niedriger Kindertisch von IKEA in Weiß mit Seitenwangen, Etikett an der Unterseite: Småstad, 804.335.42. Die Platte ist stark verkratzt und mit einer Schutzfolie belegt.</t>
+          <t>IKEA Grua Wandspiegel, schwarzer Rahmen
+Wandspiegel mit schmalem schwarzem Rahmen und abgerundeten Ecken. Etikett auf der Rückseite: Grua, IKEA.</t>
         </is>
       </c>
       <c r="E253" s="13" t="n"/>
@@ -22837,11 +23037,11 @@
       </c>
       <c r="G253" s="21" t="inlineStr">
         <is>
-          <t>stark gebraucht</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H253" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I253" s="21" t="inlineStr">
         <is>
@@ -22849,7 +23049,7 @@
         </is>
       </c>
       <c r="J253" s="24" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="K253" s="25">
         <f>J253*1.19</f>
@@ -22877,22 +23077,22 @@
       <c r="A254" s="9" t="n">
         <v>247</v>
       </c>
-      <c r="B254" s="10" t="inlineStr">
-        <is>
-          <t>BU01-06</t>
+      <c r="B254" s="35" t="inlineStr">
+        <is>
+          <t>BU02-01</t>
         </is>
       </c>
       <c r="C254" s="11" t="n"/>
       <c r="D254" s="12" t="inlineStr">
         <is>
-          <t>Wanddeko Lama, Steckwand
-Wandelement in Lamaform aus weiß lackiertem Holz mit grauen Ohren, Gesicht und Füßen, durchgehend gelocht zum Einstecken von Haken oder Stäben.</t>
+          <t>Hausbett Holz natur mit Stoffdach
+Bodenbett in Hausform aus hellem Massivholz mit vier Pfosten und aufgelegtem Stoffdach in Creme mit schwarzer Zackenkante und aufgesticktem Wolkenmotiv. Einschließlich Matratze.</t>
         </is>
       </c>
       <c r="E254" s="13" t="n"/>
       <c r="F254" s="12" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur 2</t>
         </is>
       </c>
       <c r="G254" s="10" t="inlineStr">
@@ -22901,7 +23101,7 @@
         </is>
       </c>
       <c r="H254" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I254" s="10" t="inlineStr">
         <is>
@@ -22909,7 +23109,7 @@
         </is>
       </c>
       <c r="J254" s="14" t="n">
-        <v>25</v>
+        <v>180</v>
       </c>
       <c r="K254" s="15">
         <f>J254*1.19</f>
@@ -22939,20 +23139,20 @@
       </c>
       <c r="B255" s="21" t="inlineStr">
         <is>
-          <t>BU01-07</t>
+          <t>BU02-02</t>
         </is>
       </c>
       <c r="C255" s="22" t="n"/>
       <c r="D255" s="23" t="inlineStr">
         <is>
-          <t>IKEA Grua Wandspiegel, schwarzer Rahmen
-Wandspiegel mit schmalem schwarzem Rahmen und abgerundeten Ecken. Etikett auf der Rückseite: Grua, IKEA.</t>
+          <t>Nachtlicht Marienkäfer, schwarz
+Steckdosen-Nachtlicht in Marienkäferform aus schwarzem Kunststoff mit geprägten Punkten und Fühlern.</t>
         </is>
       </c>
       <c r="E255" s="13" t="n"/>
       <c r="F255" s="23" t="inlineStr">
         <is>
-          <t>Flur 1</t>
+          <t>Flur 2</t>
         </is>
       </c>
       <c r="G255" s="21" t="inlineStr">
@@ -22961,7 +23161,7 @@
         </is>
       </c>
       <c r="H255" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I255" s="21" t="inlineStr">
         <is>
@@ -22969,7 +23169,7 @@
         </is>
       </c>
       <c r="J255" s="24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="K255" s="25">
         <f>J255*1.19</f>
@@ -22982,7 +23182,7 @@
       </c>
       <c r="M255" s="23" t="inlineStr">
         <is>
-          <t>nur Abholung</t>
+          <t>Versand möglich</t>
         </is>
       </c>
       <c r="N255" s="16" t="n"/>
@@ -22999,14 +23199,14 @@
       </c>
       <c r="B256" s="35" t="inlineStr">
         <is>
-          <t>BU02-01</t>
+          <t>BU02-03</t>
         </is>
       </c>
       <c r="C256" s="11" t="n"/>
       <c r="D256" s="12" t="inlineStr">
         <is>
-          <t>Hausbett Holz natur mit Stoffdach
-Bodenbett in Hausform aus hellem Massivholz mit vier Pfosten und aufgelegtem Stoffdach in Creme mit schwarzer Zackenkante und aufgesticktem Wolkenmotiv. Einschließlich Matratze.</t>
+          <t>Kindertisch weiß, oval, aus vier Segmenten
+Vier Tischsegmente mit weißer Platte und Multiplex-Kante auf verchromten Rundfüßen in Kinderhöhe: zwei halbrunde Endstücke und zwei Mittelstücke. Zusammengestellt ergeben sie einen großen ovalen Gruppentisch, einzeln sind sie frei kombinierbar.</t>
         </is>
       </c>
       <c r="E256" s="13" t="n"/>
@@ -23025,11 +23225,11 @@
       </c>
       <c r="I256" s="10" t="inlineStr">
         <is>
-          <t>Stück</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="J256" s="14" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="K256" s="15">
         <f>J256*1.19</f>
@@ -23059,14 +23259,14 @@
       </c>
       <c r="B257" s="21" t="inlineStr">
         <is>
-          <t>BU02-02</t>
+          <t>BU02-05</t>
         </is>
       </c>
       <c r="C257" s="22" t="n"/>
       <c r="D257" s="23" t="inlineStr">
         <is>
-          <t>Nachtlicht Marienkäfer, schwarz
-Steckdosen-Nachtlicht in Marienkäferform aus schwarzem Kunststoff mit geprägten Punkten und Fühlern.</t>
+          <t>IKEA Duktig Spielküche mit Mikrowelle
+Spielküche von IKEA aus Birkenholz mit weißen Fronten: Aufsatz mit Mikrowelle und offenen Fächern, Arbeitsplatte mit Kochfeld, Spülbecken und Wasserhahn, darunter Backofen mit Sichtfenster und ein Schrank.</t>
         </is>
       </c>
       <c r="E257" s="13" t="n"/>
@@ -23081,7 +23281,7 @@
         </is>
       </c>
       <c r="H257" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I257" s="21" t="inlineStr">
         <is>
@@ -23089,7 +23289,7 @@
         </is>
       </c>
       <c r="J257" s="24" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="K257" s="25">
         <f>J257*1.19</f>
@@ -23102,7 +23302,7 @@
       </c>
       <c r="M257" s="23" t="inlineStr">
         <is>
-          <t>Versand möglich</t>
+          <t>nur Abholung</t>
         </is>
       </c>
       <c r="N257" s="16" t="n"/>
@@ -23117,16 +23317,16 @@
       <c r="A258" s="9" t="n">
         <v>251</v>
       </c>
-      <c r="B258" s="35" t="inlineStr">
-        <is>
-          <t>BU02-03</t>
+      <c r="B258" s="10" t="inlineStr">
+        <is>
+          <t>BU02-06</t>
         </is>
       </c>
       <c r="C258" s="11" t="n"/>
       <c r="D258" s="12" t="inlineStr">
         <is>
-          <t>Kindertisch weiß, oval, aus vier Segmenten
-Vier Tischsegmente mit weißer Platte und Multiplex-Kante auf verchromten Rundfüßen in Kinderhöhe: zwei halbrunde Endstücke und zwei Mittelstücke. Zusammengestellt ergeben sie einen großen ovalen Gruppentisch, einzeln sind sie frei kombinierbar.</t>
+          <t>Kinder-Putzständer, fünfteilig
+Ständer aus Holz und Metall in Weiß mit Ablagekasten und aufgehängtem Kinder-Reinigungsgerät: Besen, Schrubber, Kehrblech und Staubwedel.</t>
         </is>
       </c>
       <c r="E258" s="13" t="n"/>
@@ -23145,11 +23345,11 @@
       </c>
       <c r="I258" s="10" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Stück</t>
         </is>
       </c>
       <c r="J258" s="14" t="n">
-        <v>160</v>
+        <v>25</v>
       </c>
       <c r="K258" s="15">
         <f>J258*1.19</f>
@@ -23179,14 +23379,14 @@
       </c>
       <c r="B259" s="21" t="inlineStr">
         <is>
-          <t>BU02-05</t>
+          <t>BU02-09</t>
         </is>
       </c>
       <c r="C259" s="22" t="n"/>
       <c r="D259" s="23" t="inlineStr">
         <is>
-          <t>IKEA Duktig Spielküche mit Mikrowelle
-Spielküche von IKEA aus Birkenholz mit weißen Fronten: Aufsatz mit Mikrowelle und offenen Fächern, Arbeitsplatte mit Kochfeld, Spülbecken und Wasserhahn, darunter Backofen mit Sichtfenster und ein Schrank.</t>
+          <t>Acrylbild Herz auf Strahlenkranz
+Acryl auf Leinwand im Hochformat: breite Pinselstriche in Pink, Magenta und Grau strahlenförmig um ein ausgespartes weißes Herz. Eigenarbeit einer Privatperson, nicht signiert.</t>
         </is>
       </c>
       <c r="E259" s="13" t="n"/>
@@ -23197,7 +23397,7 @@
       </c>
       <c r="G259" s="21" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H259" s="21" t="n">
@@ -23209,7 +23409,7 @@
         </is>
       </c>
       <c r="J259" s="24" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="K259" s="25">
         <f>J259*1.19</f>
@@ -23222,7 +23422,7 @@
       </c>
       <c r="M259" s="23" t="inlineStr">
         <is>
-          <t>nur Abholung</t>
+          <t>Versand möglich</t>
         </is>
       </c>
       <c r="N259" s="16" t="n"/>
@@ -23239,14 +23439,14 @@
       </c>
       <c r="B260" s="10" t="inlineStr">
         <is>
-          <t>BU02-06</t>
+          <t>BU02-10</t>
         </is>
       </c>
       <c r="C260" s="11" t="n"/>
       <c r="D260" s="12" t="inlineStr">
         <is>
-          <t>Kinder-Putzständer, fünfteilig
-Ständer aus Holz und Metall in Weiß mit Ablagekasten und aufgehängtem Kinder-Reinigungsgerät: Besen, Schrubber, Kehrblech und Staubwedel.</t>
+          <t>Spieltisch Kiefer mit herausnehmbaren Platten
+Kindertisch aus Kiefer massiv mit zwei herausnehmbaren weißen Platten. Darunter liegen Wannen, sodass der Tisch als Spiel- und Materialtisch genutzt werden kann. Die Platten sind an den Kanten großflächig abgeplatzt.</t>
         </is>
       </c>
       <c r="E260" s="13" t="n"/>
@@ -23257,11 +23457,11 @@
       </c>
       <c r="G260" s="10" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>stark gebraucht</t>
         </is>
       </c>
       <c r="H260" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I260" s="10" t="inlineStr">
         <is>
@@ -23269,7 +23469,7 @@
         </is>
       </c>
       <c r="J260" s="14" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="K260" s="15">
         <f>J260*1.19</f>
@@ -23299,14 +23499,14 @@
       </c>
       <c r="B261" s="21" t="inlineStr">
         <is>
-          <t>BU02-09</t>
+          <t>BU02-12</t>
         </is>
       </c>
       <c r="C261" s="22" t="n"/>
       <c r="D261" s="23" t="inlineStr">
         <is>
-          <t>Acrylbild Herz auf Strahlenkranz
-Acryl auf Leinwand im Hochformat: breite Pinselstriche in Pink, Magenta und Grau strahlenförmig um ein ausgespartes weißes Herz. Eigenarbeit einer Privatperson, nicht signiert.</t>
+          <t>Wandregal weiß mit drei Wannen, geschwungen
+Weißes Wandelement mit geschwungener Front, drei Fächern und drei eingeschobenen Kunststoffwannen.</t>
         </is>
       </c>
       <c r="E261" s="13" t="n"/>
@@ -23317,7 +23517,7 @@
       </c>
       <c r="G261" s="21" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H261" s="21" t="n">
@@ -23329,7 +23529,7 @@
         </is>
       </c>
       <c r="J261" s="24" t="n">
-        <v>80</v>
+        <v>35</v>
       </c>
       <c r="K261" s="25">
         <f>J261*1.19</f>
@@ -23342,7 +23542,7 @@
       </c>
       <c r="M261" s="23" t="inlineStr">
         <is>
-          <t>Versand möglich</t>
+          <t>nur Abholung</t>
         </is>
       </c>
       <c r="N261" s="16" t="n"/>
@@ -23359,14 +23559,14 @@
       </c>
       <c r="B262" s="10" t="inlineStr">
         <is>
-          <t>BU02-10</t>
+          <t>BU02-15</t>
         </is>
       </c>
       <c r="C262" s="11" t="n"/>
       <c r="D262" s="12" t="inlineStr">
         <is>
-          <t>Spieltisch Kiefer mit herausnehmbaren Platten
-Kindertisch aus Kiefer massiv mit zwei herausnehmbaren weißen Platten. Darunter liegen Wannen, sodass der Tisch als Spiel- und Materialtisch genutzt werden kann. Die Platten sind an den Kanten großflächig abgeplatzt.</t>
+          <t>Bodensitzkissen beige, selbststehend
+Selbststehendes Bodensitzkissen aus beigem Leinenstoff mit gesteppten Feldern, Rückenlehne und langer Sitzfläche. Die Lehne lässt sich flach ausklappen.</t>
         </is>
       </c>
       <c r="E262" s="13" t="n"/>
@@ -23377,7 +23577,7 @@
       </c>
       <c r="G262" s="10" t="inlineStr">
         <is>
-          <t>stark gebraucht</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H262" s="10" t="n">
@@ -23389,7 +23589,7 @@
         </is>
       </c>
       <c r="J262" s="14" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="K262" s="15">
         <f>J262*1.19</f>
@@ -23419,14 +23619,14 @@
       </c>
       <c r="B263" s="21" t="inlineStr">
         <is>
-          <t>BU02-12</t>
+          <t>BU02-16</t>
         </is>
       </c>
       <c r="C263" s="22" t="n"/>
       <c r="D263" s="23" t="inlineStr">
         <is>
-          <t>Wandregal weiß mit drei Wannen, geschwungen
-Weißes Wandelement mit geschwungener Front, drei Fächern und drei eingeschobenen Kunststoffwannen.</t>
+          <t>Servierwagen Metall schwarz, drei Ebenen
+Rollwagen aus schwarz lackiertem Metall mit drei Ablageebenen und Lochblechböden, auf vier Rollen.</t>
         </is>
       </c>
       <c r="E263" s="13" t="n"/>
@@ -23449,7 +23649,7 @@
         </is>
       </c>
       <c r="J263" s="24" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K263" s="25">
         <f>J263*1.19</f>
@@ -23479,14 +23679,14 @@
       </c>
       <c r="B264" s="10" t="inlineStr">
         <is>
-          <t>BU02-15</t>
+          <t>BU02-17</t>
         </is>
       </c>
       <c r="C264" s="11" t="n"/>
       <c r="D264" s="12" t="inlineStr">
         <is>
-          <t>Bodensitzkissen beige, selbststehend
-Selbststehendes Bodensitzkissen aus beigem Leinenstoff mit gesteppten Feldern, Rückenlehne und langer Sitzfläche. Die Lehne lässt sich flach ausklappen.</t>
+          <t>Kommode weiß, drei Schubladen
+Kommode in Weiß mit drei breiten Schubladen und mittig ausgeschnittenen Griffmulden, auf umlaufendem Sockel.</t>
         </is>
       </c>
       <c r="E264" s="13" t="n"/>
@@ -23501,7 +23701,7 @@
         </is>
       </c>
       <c r="H264" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I264" s="10" t="inlineStr">
         <is>
@@ -23509,7 +23709,7 @@
         </is>
       </c>
       <c r="J264" s="14" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="K264" s="15">
         <f>J264*1.19</f>
@@ -23539,17 +23739,21 @@
       </c>
       <c r="B265" s="21" t="inlineStr">
         <is>
-          <t>BU02-16</t>
+          <t>BU02-18</t>
         </is>
       </c>
       <c r="C265" s="22" t="n"/>
       <c r="D265" s="23" t="inlineStr">
         <is>
-          <t>Servierwagen Metall schwarz, drei Ebenen
-Rollwagen aus schwarz lackiertem Metall mit drei Ablageebenen und Lochblechböden, auf vier Rollen.</t>
-        </is>
-      </c>
-      <c r="E265" s="13" t="n"/>
+          <t>Hochflorteppich grau
+Hochflorteppich in Grau, rechteckig. Maße laut Etikett auf der Rückseite: 160 × 230 cm.</t>
+        </is>
+      </c>
+      <c r="E265" s="13" t="inlineStr">
+        <is>
+          <t>160 × 230 cm</t>
+        </is>
+      </c>
       <c r="F265" s="23" t="inlineStr">
         <is>
           <t>Flur 2</t>
@@ -23569,7 +23773,7 @@
         </is>
       </c>
       <c r="J265" s="24" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="K265" s="25">
         <f>J265*1.19</f>
@@ -23582,7 +23786,7 @@
       </c>
       <c r="M265" s="23" t="inlineStr">
         <is>
-          <t>nur Abholung</t>
+          <t>Versand möglich</t>
         </is>
       </c>
       <c r="N265" s="16" t="n"/>
@@ -23599,14 +23803,14 @@
       </c>
       <c r="B266" s="10" t="inlineStr">
         <is>
-          <t>BU02-17</t>
+          <t>BU02-19</t>
         </is>
       </c>
       <c r="C266" s="11" t="n"/>
       <c r="D266" s="12" t="inlineStr">
         <is>
-          <t>Kommode weiß, drei Schubladen
-Kommode in Weiß mit drei breiten Schubladen und mittig ausgeschnittenen Griffmulden, auf umlaufendem Sockel.</t>
+          <t>Spielmöbel Kiefer, dreiteilig
+Dreiteilige Kombination aus Kiefer massiv: Wandregal mit zwei Kunststoffwannen, niedrige Werkbank mit offenem Unterbau und zwei Wannen sowie ein hohes Seitenteil mit Wanne.</t>
         </is>
       </c>
       <c r="E266" s="13" t="n"/>
@@ -23621,15 +23825,15 @@
         </is>
       </c>
       <c r="H266" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I266" s="10" t="inlineStr">
         <is>
-          <t>Stück</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="J266" s="14" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="K266" s="15">
         <f>J266*1.19</f>
@@ -23659,24 +23863,20 @@
       </c>
       <c r="B267" s="21" t="inlineStr">
         <is>
-          <t>BU02-18</t>
+          <t>BU03-01</t>
         </is>
       </c>
       <c r="C267" s="22" t="n"/>
       <c r="D267" s="23" t="inlineStr">
         <is>
-          <t>Hochflorteppich grau
-Hochflorteppich in Grau, rechteckig. Maße laut Etikett auf der Rückseite: 160 × 230 cm.</t>
-        </is>
-      </c>
-      <c r="E267" s="13" t="inlineStr">
-        <is>
-          <t>160 × 230 cm</t>
-        </is>
-      </c>
+          <t>Pinnwand Holz mit Klammerleinen
+Großes Wandelement aus hellem Massivholz mit vier waagerechten Bändern und Holzklammern zum Aufhängen von Bildern und Bastelarbeiten. Zwei zusätzliche Querbretter als Ablage.</t>
+        </is>
+      </c>
+      <c r="E267" s="13" t="n"/>
       <c r="F267" s="23" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur 3</t>
         </is>
       </c>
       <c r="G267" s="21" t="inlineStr">
@@ -23693,7 +23893,7 @@
         </is>
       </c>
       <c r="J267" s="24" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="K267" s="25">
         <f>J267*1.19</f>
@@ -23706,7 +23906,7 @@
       </c>
       <c r="M267" s="23" t="inlineStr">
         <is>
-          <t>Versand möglich</t>
+          <t>nur Abholung</t>
         </is>
       </c>
       <c r="N267" s="16" t="n"/>
@@ -23723,20 +23923,20 @@
       </c>
       <c r="B268" s="10" t="inlineStr">
         <is>
-          <t>BU02-19</t>
+          <t>BU03-02</t>
         </is>
       </c>
       <c r="C268" s="11" t="n"/>
       <c r="D268" s="12" t="inlineStr">
         <is>
-          <t>Spielmöbel Kiefer, dreiteilig
-Dreiteilige Kombination aus Kiefer massiv: Wandregal mit zwei Kunststoffwannen, niedrige Werkbank mit offenem Unterbau und zwei Wannen sowie ein hohes Seitenteil mit Wanne.</t>
+          <t>Schwingspiegel, geschwungene Form
+Hoher Wandspiegel mit geschwungener Außenkante ohne Rahmen, zum Anschrauben.</t>
         </is>
       </c>
       <c r="E268" s="13" t="n"/>
       <c r="F268" s="12" t="inlineStr">
         <is>
-          <t>Flur 2</t>
+          <t>Flur 3</t>
         </is>
       </c>
       <c r="G268" s="10" t="inlineStr">
@@ -23749,11 +23949,11 @@
       </c>
       <c r="I268" s="10" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Stück</t>
         </is>
       </c>
       <c r="J268" s="14" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="K268" s="15">
         <f>J268*1.19</f>
@@ -23783,14 +23983,14 @@
       </c>
       <c r="B269" s="21" t="inlineStr">
         <is>
-          <t>BU03-01</t>
+          <t>BU03-03</t>
         </is>
       </c>
       <c r="C269" s="22" t="n"/>
       <c r="D269" s="23" t="inlineStr">
         <is>
-          <t>Pinnwand Holz mit Klammerleinen
-Großes Wandelement aus hellem Massivholz mit vier waagerechten Bändern und Holzklammern zum Aufhängen von Bildern und Bastelarbeiten. Zwei zusätzliche Querbretter als Ablage.</t>
+          <t>Schuhregal schwarz mit Chromstangen
+Niedriges Schuhregal aus schwarz lackiertem Holz mit schwarzer Deckplatte und drei Ebenen aus verchromten Rundstangen, auch als Sitzbank nutzbar.</t>
         </is>
       </c>
       <c r="E269" s="13" t="n"/>
@@ -23805,7 +24005,7 @@
         </is>
       </c>
       <c r="H269" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I269" s="21" t="inlineStr">
         <is>
@@ -23813,7 +24013,7 @@
         </is>
       </c>
       <c r="J269" s="24" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="K269" s="25">
         <f>J269*1.19</f>
@@ -23843,14 +24043,14 @@
       </c>
       <c r="B270" s="10" t="inlineStr">
         <is>
-          <t>BU03-02</t>
+          <t>BU03-04</t>
         </is>
       </c>
       <c r="C270" s="11" t="n"/>
       <c r="D270" s="12" t="inlineStr">
         <is>
-          <t>Schwingspiegel, geschwungene Form
-Hoher Wandspiegel mit geschwungener Außenkante ohne Rahmen, zum Anschrauben.</t>
+          <t>Metallregal weiß, vier Böden
+Offenes Regal mit weißem Metallgestell, Kreuzstrebe auf der Rückseite und vier weißen Böden.</t>
         </is>
       </c>
       <c r="E270" s="13" t="n"/>
@@ -23873,7 +24073,7 @@
         </is>
       </c>
       <c r="J270" s="14" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K270" s="15">
         <f>J270*1.19</f>
@@ -23903,14 +24103,14 @@
       </c>
       <c r="B271" s="21" t="inlineStr">
         <is>
-          <t>BU03-03</t>
+          <t>BU03-05</t>
         </is>
       </c>
       <c r="C271" s="22" t="n"/>
       <c r="D271" s="23" t="inlineStr">
         <is>
-          <t>Schuhregal schwarz mit Chromstangen
-Niedriges Schuhregal aus schwarz lackiertem Holz mit schwarzer Deckplatte und drei Ebenen aus verchromten Rundstangen, auch als Sitzbank nutzbar.</t>
+          <t>Schuhschrank weiß mit Klappfächern
+Schmaler Schuhschrank in Weiß mit zwei Klappfächern und schwarzen Knöpfen. Die Schuhablagen sind innen verschmutzt und an den Kanten abgestoßen.</t>
         </is>
       </c>
       <c r="E271" s="13" t="n"/>
@@ -23925,7 +24125,7 @@
         </is>
       </c>
       <c r="H271" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I271" s="21" t="inlineStr">
         <is>
@@ -23933,7 +24133,7 @@
         </is>
       </c>
       <c r="J271" s="24" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="K271" s="25">
         <f>J271*1.19</f>
@@ -23963,14 +24163,14 @@
       </c>
       <c r="B272" s="10" t="inlineStr">
         <is>
-          <t>BU03-04</t>
+          <t>BU03-06</t>
         </is>
       </c>
       <c r="C272" s="11" t="n"/>
       <c r="D272" s="12" t="inlineStr">
         <is>
-          <t>Metallregal weiß, vier Böden
-Offenes Regal mit weißem Metallgestell, Kreuzstrebe auf der Rückseite und vier weißen Böden.</t>
+          <t>Wäschekorb anthrazit mit Deckel, hoch
+Hoher Wäschekorb aus Kunststoff in Flechtoptik, anthrazit, nach unten verjüngt, mit aufklappbarem Deckel und Griffloch.</t>
         </is>
       </c>
       <c r="E272" s="13" t="n"/>
@@ -23985,7 +24185,7 @@
         </is>
       </c>
       <c r="H272" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I272" s="10" t="inlineStr">
         <is>
@@ -23993,7 +24193,7 @@
         </is>
       </c>
       <c r="J272" s="14" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="K272" s="15">
         <f>J272*1.19</f>
@@ -24006,7 +24206,7 @@
       </c>
       <c r="M272" s="12" t="inlineStr">
         <is>
-          <t>nur Abholung</t>
+          <t>Versand möglich</t>
         </is>
       </c>
       <c r="N272" s="16" t="n"/>
@@ -24023,14 +24223,14 @@
       </c>
       <c r="B273" s="21" t="inlineStr">
         <is>
-          <t>BU03-05</t>
+          <t>BU03-07</t>
         </is>
       </c>
       <c r="C273" s="22" t="n"/>
       <c r="D273" s="23" t="inlineStr">
         <is>
-          <t>Schuhschrank weiß mit Klappfächern
-Schmaler Schuhschrank in Weiß mit zwei Klappfächern und schwarzen Knöpfen. Die Schuhablagen sind innen verschmutzt und an den Kanten abgestoßen.</t>
+          <t>Tischleuchte Holzgestell mit Stoffschirm
+Tischleuchte mit dreieckigem Gestell aus hellem Holz und zylindrischem Stoffschirm in Hellgrau, mit Schnurschalter.</t>
         </is>
       </c>
       <c r="E273" s="13" t="n"/>
@@ -24053,7 +24253,7 @@
         </is>
       </c>
       <c r="J273" s="24" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="K273" s="25">
         <f>J273*1.19</f>
@@ -24066,7 +24266,7 @@
       </c>
       <c r="M273" s="23" t="inlineStr">
         <is>
-          <t>nur Abholung</t>
+          <t>Versand möglich</t>
         </is>
       </c>
       <c r="N273" s="16" t="n"/>
@@ -24083,14 +24283,14 @@
       </c>
       <c r="B274" s="10" t="inlineStr">
         <is>
-          <t>BU03-06</t>
+          <t>BU03-08</t>
         </is>
       </c>
       <c r="C274" s="11" t="n"/>
       <c r="D274" s="12" t="inlineStr">
         <is>
-          <t>Wäschekorb anthrazit mit Deckel, hoch
-Hoher Wäschekorb aus Kunststoff in Flechtoptik, anthrazit, nach unten verjüngt, mit aufklappbarem Deckel und Griffloch.</t>
+          <t>Beistelltisch rund türkis mit Hairpin-Beinen
+Kleiner runder Beistelltisch mit türkis lackierter Holzplatte auf drei schwarzen Hairpin-Beinen aus Rundstahl. Die Platte ist leicht verkratzt.</t>
         </is>
       </c>
       <c r="E274" s="13" t="n"/>
@@ -24113,7 +24313,7 @@
         </is>
       </c>
       <c r="J274" s="14" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="K274" s="15">
         <f>J274*1.19</f>
@@ -24143,20 +24343,20 @@
       </c>
       <c r="B275" s="21" t="inlineStr">
         <is>
-          <t>BU03-07</t>
+          <t>BU04-06</t>
         </is>
       </c>
       <c r="C275" s="22" t="n"/>
       <c r="D275" s="23" t="inlineStr">
         <is>
-          <t>Tischleuchte Holzgestell mit Stoffschirm
-Tischleuchte mit dreieckigem Gestell aus hellem Holz und zylindrischem Stoffschirm in Hellgrau, mit Schnurschalter.</t>
+          <t>Kindertisch weiß, lang, zweiteilig
+Langer Kindertisch aus zwei aneinandergestellten Platten in Weiß mit cremefarbener Kante, auf cremefarbenen Vierkantfüßen aus Metall mit Gleitern. Die Platten sind an den Kanten abgestoßen.</t>
         </is>
       </c>
       <c r="E275" s="13" t="n"/>
       <c r="F275" s="23" t="inlineStr">
         <is>
-          <t>Flur 3</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="G275" s="21" t="inlineStr">
@@ -24169,11 +24369,11 @@
       </c>
       <c r="I275" s="21" t="inlineStr">
         <is>
-          <t>Stück</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="J275" s="24" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="K275" s="25">
         <f>J275*1.19</f>
@@ -24186,7 +24386,7 @@
       </c>
       <c r="M275" s="23" t="inlineStr">
         <is>
-          <t>Versand möglich</t>
+          <t>nur Abholung</t>
         </is>
       </c>
       <c r="N275" s="16" t="n"/>
@@ -24203,25 +24403,25 @@
       </c>
       <c r="B276" s="10" t="inlineStr">
         <is>
-          <t>BU03-08</t>
+          <t>BU04-07</t>
         </is>
       </c>
       <c r="C276" s="11" t="n"/>
       <c r="D276" s="12" t="inlineStr">
         <is>
-          <t>Beistelltisch rund türkis mit Hairpin-Beinen
-Kleiner runder Beistelltisch mit türkis lackierter Holzplatte auf drei schwarzen Hairpin-Beinen aus Rundstahl. Die Platte ist leicht verkratzt.</t>
+          <t>Gemälde Schwarzwaldfrau mit Planeten
+Acryl auf Leinwand im Hochformat: Frau in Schwarzwälder Tracht mit Bollenhut, umgeben von gemalten Planeten und Sternen. Eigenarbeit einer Privatperson, nicht signiert.</t>
         </is>
       </c>
       <c r="E276" s="13" t="n"/>
       <c r="F276" s="12" t="inlineStr">
         <is>
-          <t>Flur 3</t>
+          <t>Gruppenraum</t>
         </is>
       </c>
       <c r="G276" s="10" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H276" s="10" t="n">
@@ -24233,7 +24433,7 @@
         </is>
       </c>
       <c r="J276" s="14" t="n">
-        <v>35</v>
+        <v>250</v>
       </c>
       <c r="K276" s="15">
         <f>J276*1.19</f>
@@ -24246,7 +24446,7 @@
       </c>
       <c r="M276" s="12" t="inlineStr">
         <is>
-          <t>Versand möglich</t>
+          <t>nur Abholung</t>
         </is>
       </c>
       <c r="N276" s="16" t="n"/>
@@ -24263,14 +24463,14 @@
       </c>
       <c r="B277" s="21" t="inlineStr">
         <is>
-          <t>BU04-06</t>
+          <t>BU04-08</t>
         </is>
       </c>
       <c r="C277" s="22" t="n"/>
       <c r="D277" s="23" t="inlineStr">
         <is>
-          <t>Kindertisch weiß, lang, zweiteilig
-Langer Kindertisch aus zwei aneinandergestellten Platten in Weiß mit cremefarbener Kante, auf cremefarbenen Vierkantfüßen aus Metall mit Gleitern. Die Platten sind an den Kanten abgestoßen.</t>
+          <t>Garderobenständer bunt, Stangenform
+Stehender Garderobenständer: weiße Rundstange mit farbig lackierten Ringen in Grün, Blau, Rot, Orange und Gelb und passenden Haken in mehreren Höhen, auf Tellerfuß.</t>
         </is>
       </c>
       <c r="E277" s="13" t="n"/>
@@ -24285,15 +24485,15 @@
         </is>
       </c>
       <c r="H277" s="21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I277" s="21" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Stück</t>
         </is>
       </c>
       <c r="J277" s="24" t="n">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="K277" s="25">
         <f>J277*1.19</f>
@@ -24321,16 +24521,16 @@
       <c r="A278" s="9" t="n">
         <v>271</v>
       </c>
-      <c r="B278" s="10" t="inlineStr">
-        <is>
-          <t>BU04-07</t>
+      <c r="B278" s="35" t="inlineStr">
+        <is>
+          <t>BU04-10</t>
         </is>
       </c>
       <c r="C278" s="11" t="n"/>
       <c r="D278" s="12" t="inlineStr">
         <is>
-          <t>Gemälde Schwarzwaldfrau mit Planeten
-Acryl auf Leinwand im Hochformat: Frau in Schwarzwälder Tracht mit Bollenhut, umgeben von gemalten Planeten und Sternen. Eigenarbeit einer Privatperson, nicht signiert.</t>
+          <t>Kindertisch weiß aus fünf Segmenten
+Fünf Tischsegmente mit weißer Platte, Multiplex-Kante und verchromten Rundfüßen in Kinderhöhe. Zusammengestellt ergeben sie einen großen Gruppentisch, einzeln sind sie frei kombinierbar.</t>
         </is>
       </c>
       <c r="E278" s="13" t="n"/>
@@ -24341,7 +24541,7 @@
       </c>
       <c r="G278" s="10" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H278" s="10" t="n">
@@ -24349,11 +24549,11 @@
       </c>
       <c r="I278" s="10" t="inlineStr">
         <is>
-          <t>Stück</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="J278" s="14" t="n">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="K278" s="15">
         <f>J278*1.19</f>
@@ -24383,14 +24583,14 @@
       </c>
       <c r="B279" s="21" t="inlineStr">
         <is>
-          <t>BU04-08</t>
+          <t>BU04-11</t>
         </is>
       </c>
       <c r="C279" s="22" t="n"/>
       <c r="D279" s="23" t="inlineStr">
         <is>
-          <t>Garderobenständer bunt, Stangenform
-Stehender Garderobenständer: weiße Rundstange mit farbig lackierten Ringen in Grün, Blau, Rot, Orange und Gelb und passenden Haken in mehreren Höhen, auf Tellerfuß.</t>
+          <t>Regal weiß, vier Böden
+Offenes Regal in Weiß mit vier Böden, eines der beiden Regale hat zusätzlich zwei Schubladen. Böden und Kanten sind großflächig verschmutzt und abgestoßen.</t>
         </is>
       </c>
       <c r="E279" s="13" t="n"/>
@@ -24401,7 +24601,7 @@
       </c>
       <c r="G279" s="21" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>stark gebraucht</t>
         </is>
       </c>
       <c r="H279" s="21" t="n">
@@ -24413,7 +24613,7 @@
         </is>
       </c>
       <c r="J279" s="24" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K279" s="25">
         <f>J279*1.19</f>
@@ -24441,16 +24641,16 @@
       <c r="A280" s="9" t="n">
         <v>273</v>
       </c>
-      <c r="B280" s="35" t="inlineStr">
-        <is>
-          <t>BU04-10</t>
+      <c r="B280" s="10" t="inlineStr">
+        <is>
+          <t>BU04-13</t>
         </is>
       </c>
       <c r="C280" s="11" t="n"/>
       <c r="D280" s="12" t="inlineStr">
         <is>
-          <t>Kindertisch weiß aus fünf Segmenten
-Fünf Tischsegmente mit weißer Platte, Multiplex-Kante und verchromten Rundfüßen in Kinderhöhe. Zusammengestellt ergeben sie einen großen Gruppentisch, einzeln sind sie frei kombinierbar.</t>
+          <t>Servierwagen Metall grau, drei Ebenen
+Rollwagen aus dunkelgrau lackiertem Metall mit drei Ablageebenen und Lochblechböden, auf vier Rollen.</t>
         </is>
       </c>
       <c r="E280" s="13" t="n"/>
@@ -24469,11 +24669,11 @@
       </c>
       <c r="I280" s="10" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Stück</t>
         </is>
       </c>
       <c r="J280" s="14" t="n">
-        <v>190</v>
+        <v>30</v>
       </c>
       <c r="K280" s="15">
         <f>J280*1.19</f>
@@ -24503,14 +24703,14 @@
       </c>
       <c r="B281" s="21" t="inlineStr">
         <is>
-          <t>BU04-11</t>
+          <t>BU04-14</t>
         </is>
       </c>
       <c r="C281" s="22" t="n"/>
       <c r="D281" s="23" t="inlineStr">
         <is>
-          <t>Regal weiß, vier Böden
-Offenes Regal in Weiß mit vier Böden, eines der beiden Regale hat zusätzlich zwei Schubladen. Böden und Kanten sind großflächig verschmutzt und abgestoßen.</t>
+          <t>Bücherregal creme mit Wolkenaufsatz
+Stehendes Bücherregal aus Holz, creme lackiert, mit geschwungenem Wolkenaufsatz und drei Ablagen mit vorderer Haltelatte für nach vorn zeigende Bilderbücher.</t>
         </is>
       </c>
       <c r="E281" s="13" t="n"/>
@@ -24521,11 +24721,11 @@
       </c>
       <c r="G281" s="21" t="inlineStr">
         <is>
-          <t>stark gebraucht</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H281" s="21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I281" s="21" t="inlineStr">
         <is>
@@ -24533,7 +24733,7 @@
         </is>
       </c>
       <c r="J281" s="24" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K281" s="25">
         <f>J281*1.19</f>
@@ -24563,14 +24763,14 @@
       </c>
       <c r="B282" s="10" t="inlineStr">
         <is>
-          <t>BU04-13</t>
+          <t>BU04-15</t>
         </is>
       </c>
       <c r="C282" s="11" t="n"/>
       <c r="D282" s="12" t="inlineStr">
         <is>
-          <t>Servierwagen Metall grau, drei Ebenen
-Rollwagen aus dunkelgrau lackiertem Metall mit drei Ablageebenen und Lochblechböden, auf vier Rollen.</t>
+          <t>Acrylbilder Roboter, schwarz-weiß
+Zwei Bilder auf Leinwand im Quadrat: Roboterfiguren mit breitem Pinsel in Schwarz auf weißem Grund. Eigenarbeit einer Privatperson, nicht signiert.</t>
         </is>
       </c>
       <c r="E282" s="13" t="n"/>
@@ -24581,11 +24781,11 @@
       </c>
       <c r="G282" s="10" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H282" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I282" s="10" t="inlineStr">
         <is>
@@ -24593,7 +24793,7 @@
         </is>
       </c>
       <c r="J282" s="14" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K282" s="15">
         <f>J282*1.19</f>
@@ -24606,7 +24806,7 @@
       </c>
       <c r="M282" s="12" t="inlineStr">
         <is>
-          <t>nur Abholung</t>
+          <t>Versand möglich</t>
         </is>
       </c>
       <c r="N282" s="16" t="n"/>
@@ -24621,22 +24821,22 @@
       <c r="A283" s="20" t="n">
         <v>276</v>
       </c>
-      <c r="B283" s="21" t="inlineStr">
-        <is>
-          <t>BU04-14</t>
+      <c r="B283" s="35" t="inlineStr">
+        <is>
+          <t>BU05-01</t>
         </is>
       </c>
       <c r="C283" s="22" t="n"/>
       <c r="D283" s="23" t="inlineStr">
         <is>
-          <t>Bücherregal creme mit Wolkenaufsatz
-Stehendes Bücherregal aus Holz, creme lackiert, mit geschwungenem Wolkenaufsatz und drei Ablagen mit vorderer Haltelatte für nach vorn zeigende Bilderbücher.</t>
+          <t>Spielhaus weiß mit Hochebene und Bett
+Große Spielhaus-Konstruktion in Weiß: obere Spielebene mit Brüstung, grüner Tafel und Ablagefach, darunter eine Liegefläche mit Matratze. Eine Seitenwand trägt eine goldene Krone als Aufkleber.</t>
         </is>
       </c>
       <c r="E283" s="13" t="n"/>
       <c r="F283" s="23" t="inlineStr">
         <is>
-          <t>Gruppenraum</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="G283" s="21" t="inlineStr">
@@ -24653,7 +24853,7 @@
         </is>
       </c>
       <c r="J283" s="24" t="n">
-        <v>45</v>
+        <v>450</v>
       </c>
       <c r="K283" s="25">
         <f>J283*1.19</f>
@@ -24681,39 +24881,39 @@
       <c r="A284" s="9" t="n">
         <v>277</v>
       </c>
-      <c r="B284" s="10" t="inlineStr">
-        <is>
-          <t>BU04-15</t>
+      <c r="B284" s="35" t="inlineStr">
+        <is>
+          <t>BU05-02</t>
         </is>
       </c>
       <c r="C284" s="11" t="n"/>
       <c r="D284" s="12" t="inlineStr">
         <is>
-          <t>Acrylbilder Roboter, schwarz-weiß
-Zwei Bilder auf Leinwand im Quadrat: Roboterfiguren mit breitem Pinsel in Schwarz auf weißem Grund. Eigenarbeit einer Privatperson, nicht signiert.</t>
+          <t>Wesco Spielküche, vier Module mit Mikrowelle
+Spielküche von Wesco aus Birke-Multiplex: offenes Regalmodul, Backofenmodul mit Klappe, Spülenmodul mit Becken und Kochfeldmodul, dazu eine aufgesetzte Spielmikrowelle. Fronten mit aufgedruckten Bedienfeldern, Rückwände mit Fliesenmuster.</t>
         </is>
       </c>
       <c r="E284" s="13" t="n"/>
       <c r="F284" s="12" t="inlineStr">
         <is>
-          <t>Gruppenraum</t>
+          <t>Schlafraum</t>
         </is>
       </c>
       <c r="G284" s="10" t="inlineStr">
         <is>
-          <t>gut</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H284" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I284" s="10" t="inlineStr">
         <is>
-          <t>Stück</t>
+          <t>Set</t>
         </is>
       </c>
       <c r="J284" s="14" t="n">
-        <v>60</v>
+        <v>550</v>
       </c>
       <c r="K284" s="15">
         <f>J284*1.19</f>
@@ -24726,7 +24926,7 @@
       </c>
       <c r="M284" s="12" t="inlineStr">
         <is>
-          <t>Versand möglich</t>
+          <t>nur Abholung</t>
         </is>
       </c>
       <c r="N284" s="16" t="n"/>
@@ -24741,16 +24941,16 @@
       <c r="A285" s="20" t="n">
         <v>278</v>
       </c>
-      <c r="B285" s="35" t="inlineStr">
-        <is>
-          <t>BU05-01</t>
+      <c r="B285" s="21" t="inlineStr">
+        <is>
+          <t>BU05-03</t>
         </is>
       </c>
       <c r="C285" s="22" t="n"/>
       <c r="D285" s="23" t="inlineStr">
         <is>
-          <t>Spielhaus weiß mit Hochebene und Bett
-Große Spielhaus-Konstruktion in Weiß: obere Spielebene mit Brüstung, grüner Tafel und Ablagefach, darunter eine Liegefläche mit Matratze. Eine Seitenwand trägt eine goldene Krone als Aufkleber.</t>
+          <t>Treppenregal weiß mit Wannen
+Weißes Regal in Treppenform: zwei hohe Fächer mit eingeschobenen Kunststoffwannen, dazu eine niedrigere Stufe mit Ablage und Wanne, die als Sitzfläche dient.</t>
         </is>
       </c>
       <c r="E285" s="13" t="n"/>
@@ -24773,7 +24973,7 @@
         </is>
       </c>
       <c r="J285" s="24" t="n">
-        <v>450</v>
+        <v>60</v>
       </c>
       <c r="K285" s="25">
         <f>J285*1.19</f>
@@ -24801,16 +25001,16 @@
       <c r="A286" s="9" t="n">
         <v>279</v>
       </c>
-      <c r="B286" s="35" t="inlineStr">
-        <is>
-          <t>BU05-02</t>
+      <c r="B286" s="10" t="inlineStr">
+        <is>
+          <t>BU05-04</t>
         </is>
       </c>
       <c r="C286" s="11" t="n"/>
       <c r="D286" s="12" t="inlineStr">
         <is>
-          <t>Wesco Spielküche, vier Module mit Mikrowelle
-Spielküche von Wesco aus Birke-Multiplex: offenes Regalmodul, Backofenmodul mit Klappe, Spülenmodul mit Becken und Kochfeldmodul, dazu eine aufgesetzte Spielmikrowelle. Fronten mit aufgedruckten Bedienfeldern, Rückwände mit Fliesenmuster.</t>
+          <t>Schaukeltier Storch
+Plüsch-Schaukeltier in Storchenform: weißer Körper mit rotem Schnabel, gelber Zipfelmütze mit Bommeln und rot-weiß gepunktetem Sattel mit Haltegriff, auf hellen Holzkufen.</t>
         </is>
       </c>
       <c r="E286" s="13" t="n"/>
@@ -24829,11 +25029,11 @@
       </c>
       <c r="I286" s="10" t="inlineStr">
         <is>
-          <t>Set</t>
+          <t>Stück</t>
         </is>
       </c>
       <c r="J286" s="14" t="n">
-        <v>550</v>
+        <v>45</v>
       </c>
       <c r="K286" s="15">
         <f>J286*1.19</f>
@@ -24863,14 +25063,14 @@
       </c>
       <c r="B287" s="21" t="inlineStr">
         <is>
-          <t>BU05-03</t>
+          <t>BU05-05</t>
         </is>
       </c>
       <c r="C287" s="22" t="n"/>
       <c r="D287" s="23" t="inlineStr">
         <is>
-          <t>Treppenregal weiß mit Wannen
-Weißes Regal in Treppenform: zwei hohe Fächer mit eingeschobenen Kunststoffwannen, dazu eine niedrigere Stufe mit Ablage und Wanne, die als Sitzfläche dient.</t>
+          <t>Kindersessel Teddyfell beige
+Kindersessel aus beigem Teddyfell mit runder Lehne, zwei aufgesetzten Ohren und breiten Armlehnen. Am Rücken ein Tragegriff; das Band am Griff ist eingerissen.</t>
         </is>
       </c>
       <c r="E287" s="13" t="n"/>
@@ -24893,7 +25093,7 @@
         </is>
       </c>
       <c r="J287" s="24" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="K287" s="25">
         <f>J287*1.19</f>
@@ -24923,14 +25123,14 @@
       </c>
       <c r="B288" s="10" t="inlineStr">
         <is>
-          <t>BU05-04</t>
+          <t>BU05-06</t>
         </is>
       </c>
       <c r="C288" s="11" t="n"/>
       <c r="D288" s="12" t="inlineStr">
         <is>
-          <t>Schaukeltier Storch
-Plüsch-Schaukeltier in Storchenform: weißer Körper mit rotem Schnabel, gelber Zipfelmütze mit Bommeln und rot-weiß gepunktetem Sattel mit Haltegriff, auf hellen Holzkufen.</t>
+          <t>Sitzbank gepolstert, hellgrau
+Niedrige gepolsterte Sitzbank in Kinderhöhe mit hellgrauem Chenillebezug und flacher Rückenlehne, ohne Armlehnen. Der Bezug ist an mehreren Stellen fleckig.</t>
         </is>
       </c>
       <c r="E288" s="13" t="n"/>
@@ -24945,7 +25145,7 @@
         </is>
       </c>
       <c r="H288" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I288" s="10" t="inlineStr">
         <is>
@@ -24953,7 +25153,7 @@
         </is>
       </c>
       <c r="J288" s="14" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="K288" s="15">
         <f>J288*1.19</f>
@@ -24983,14 +25183,14 @@
       </c>
       <c r="B289" s="21" t="inlineStr">
         <is>
-          <t>BU05-05</t>
+          <t>BU05-07</t>
         </is>
       </c>
       <c r="C289" s="22" t="n"/>
       <c r="D289" s="23" t="inlineStr">
         <is>
-          <t>Kindersessel Teddyfell beige
-Kindersessel aus beigem Teddyfell mit runder Lehne, zwei aufgesetzten Ohren und breiten Armlehnen. Am Rücken ein Tragegriff; das Band am Griff ist eingerissen.</t>
+          <t>Puppenwagen rosa mit Tragetasche
+Puppen-Sportwagen mit rosa-weiß gestreiftem Bezug, blauem Verdeck und höhenverstellbarem Schiebegriff, dazu eine passende Tragetasche. Der Griff ist an mehreren Stellen aufgerissen.</t>
         </is>
       </c>
       <c r="E289" s="13" t="n"/>
@@ -25001,7 +25201,7 @@
       </c>
       <c r="G289" s="21" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>stark gebraucht</t>
         </is>
       </c>
       <c r="H289" s="21" t="n">
@@ -25013,7 +25213,7 @@
         </is>
       </c>
       <c r="J289" s="24" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="K289" s="25">
         <f>J289*1.19</f>
@@ -25043,14 +25243,14 @@
       </c>
       <c r="B290" s="10" t="inlineStr">
         <is>
-          <t>BU05-06</t>
+          <t>BU05-09</t>
         </is>
       </c>
       <c r="C290" s="11" t="n"/>
       <c r="D290" s="12" t="inlineStr">
         <is>
-          <t>Sitzbank gepolstert, hellgrau
-Niedrige gepolsterte Sitzbank in Kinderhöhe mit hellgrauem Chenillebezug und flacher Rückenlehne, ohne Armlehnen. Der Bezug ist an mehreren Stellen fleckig.</t>
+          <t>Puppenwagen Holz mit Gummirädern
+Puppen- und Lauflernwagen von Wesco aus Birke-Multiplex mit hohem Schiebebügel und vier schwarzen Gummirädern.</t>
         </is>
       </c>
       <c r="E290" s="13" t="n"/>
@@ -25065,7 +25265,7 @@
         </is>
       </c>
       <c r="H290" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I290" s="10" t="inlineStr">
         <is>
@@ -25073,7 +25273,7 @@
         </is>
       </c>
       <c r="J290" s="14" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="K290" s="15">
         <f>J290*1.19</f>
@@ -25103,14 +25303,14 @@
       </c>
       <c r="B291" s="21" t="inlineStr">
         <is>
-          <t>BU05-07</t>
+          <t>BU05-10</t>
         </is>
       </c>
       <c r="C291" s="22" t="n"/>
       <c r="D291" s="23" t="inlineStr">
         <is>
-          <t>Puppenwagen rosa mit Tragetasche
-Puppen-Sportwagen mit rosa-weiß gestreiftem Bezug, blauem Verdeck und höhenverstellbarem Schiebegriff, dazu eine passende Tragetasche. Der Griff ist an mehreren Stellen aufgerissen.</t>
+          <t>Wesco Rutschfahrzeug mit Spielelementen
+Rutschfahrzeug aus Birke-Multiplex mit gepolsterter Sitzfläche, Steckformen im Sitz, Rückenlehne mit rundem Spiegel und seitlichen Zahnrädern zum Drehen, auf vier Gummirädern. Logo auf der Frontblende: wesco.</t>
         </is>
       </c>
       <c r="E291" s="13" t="n"/>
@@ -25121,7 +25321,7 @@
       </c>
       <c r="G291" s="21" t="inlineStr">
         <is>
-          <t>stark gebraucht</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H291" s="21" t="n">
@@ -25133,7 +25333,7 @@
         </is>
       </c>
       <c r="J291" s="24" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="K291" s="25">
         <f>J291*1.19</f>
@@ -25163,20 +25363,20 @@
       </c>
       <c r="B292" s="10" t="inlineStr">
         <is>
-          <t>BU05-09</t>
+          <t>BU06-05</t>
         </is>
       </c>
       <c r="C292" s="11" t="n"/>
       <c r="D292" s="12" t="inlineStr">
         <is>
-          <t>Puppenwagen Holz mit Gummirädern
-Puppen- und Lauflernwagen aus Birke-Multiplex mit hohem Schiebebügel und vier schwarzen Gummirädern. Herstellerangabe laut Erfassungsblatt der Einrichtung: Wesco.</t>
+          <t>Lernturm Holz natur
+Küchen-Lernturm aus hellem Multiplex: Standfläche in Arbeitshöhe, umlaufende Brüstung mit Griffausschnitten und eine tiefer liegende Aufstiegsstufe. Kanten an mehreren Stellen abgestoßen.</t>
         </is>
       </c>
       <c r="E292" s="13" t="n"/>
       <c r="F292" s="12" t="inlineStr">
         <is>
-          <t>Schlafraum</t>
+          <t>Küche / Essen</t>
         </is>
       </c>
       <c r="G292" s="10" t="inlineStr">
@@ -25193,7 +25393,7 @@
         </is>
       </c>
       <c r="J292" s="14" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K292" s="15">
         <f>J292*1.19</f>
@@ -25223,20 +25423,20 @@
       </c>
       <c r="B293" s="21" t="inlineStr">
         <is>
-          <t>BU05-10</t>
+          <t>BU06-06</t>
         </is>
       </c>
       <c r="C293" s="22" t="n"/>
       <c r="D293" s="23" t="inlineStr">
         <is>
-          <t>Wesco Rutschfahrzeug mit Spielelementen
-Rutschfahrzeug aus Birke-Multiplex mit gepolsterter Sitzfläche, Steckformen im Sitz, Rückenlehne mit rundem Spiegel und seitlichen Zahnrädern zum Drehen, auf vier Gummirädern. Logo auf der Frontblende: wesco.</t>
+          <t>Lernturm Holz weiß
+Küchen-Lernturm aus weiß lackiertem Multiplex: Standfläche in Arbeitshöhe, hohe Rückwand, Haltestange vorne und eine tiefer liegende Aufstiegsstufe.</t>
         </is>
       </c>
       <c r="E293" s="13" t="n"/>
       <c r="F293" s="23" t="inlineStr">
         <is>
-          <t>Schlafraum</t>
+          <t>Küche / Essen</t>
         </is>
       </c>
       <c r="G293" s="21" t="inlineStr">
@@ -25253,7 +25453,7 @@
         </is>
       </c>
       <c r="J293" s="24" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="K293" s="25">
         <f>J293*1.19</f>
@@ -25277,261 +25477,741 @@
         <v/>
       </c>
     </row>
-    <row r="295" ht="24" customHeight="1">
-      <c r="A295" s="36" t="inlineStr">
+    <row r="294" ht="78" customHeight="1">
+      <c r="A294" s="9" t="n">
+        <v>287</v>
+      </c>
+      <c r="B294" s="10" t="inlineStr">
+        <is>
+          <t>BU06-07</t>
+        </is>
+      </c>
+      <c r="C294" s="11" t="n"/>
+      <c r="D294" s="12" t="inlineStr">
+        <is>
+          <t>Rollschrank dunkelgrau, acht Fächer
+Regal in Dunkelgrau mit acht Fächern in zwei Reihen, drei Fächer mit Türen und Metallgriffen, auf Rollen.</t>
+        </is>
+      </c>
+      <c r="E294" s="13" t="n"/>
+      <c r="F294" s="12" t="inlineStr">
+        <is>
+          <t>Küche / Essen</t>
+        </is>
+      </c>
+      <c r="G294" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H294" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I294" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J294" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="K294" s="15">
+        <f>J294*1.19</f>
+        <v/>
+      </c>
+      <c r="L294" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M294" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N294" s="16" t="n"/>
+      <c r="O294" s="17" t="n"/>
+      <c r="P294" s="18" t="n"/>
+      <c r="Q294" s="19">
+        <f>IF(N294&lt;&gt;"ja","",IF(O294="",H294,O294)*J294)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="295" ht="78" customHeight="1">
+      <c r="A295" s="20" t="n">
+        <v>288</v>
+      </c>
+      <c r="B295" s="21" t="inlineStr">
+        <is>
+          <t>BU06-08</t>
+        </is>
+      </c>
+      <c r="C295" s="22" t="n"/>
+      <c r="D295" s="23" t="inlineStr">
+        <is>
+          <t>Abfallbehälter Metall schwarz
+Hoher runder Abfallbehälter aus schwarz lackiertem Metall mit Inneneimer.</t>
+        </is>
+      </c>
+      <c r="E295" s="13" t="n"/>
+      <c r="F295" s="23" t="inlineStr">
+        <is>
+          <t>Küche / Essen</t>
+        </is>
+      </c>
+      <c r="G295" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H295" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I295" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J295" s="24" t="n">
+        <v>45</v>
+      </c>
+      <c r="K295" s="25">
+        <f>J295*1.19</f>
+        <v/>
+      </c>
+      <c r="L295" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M295" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N295" s="16" t="n"/>
+      <c r="O295" s="17" t="n"/>
+      <c r="P295" s="18" t="n"/>
+      <c r="Q295" s="26">
+        <f>IF(N295&lt;&gt;"ja","",IF(O295="",H295,O295)*J295)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="296" ht="78" customHeight="1">
+      <c r="A296" s="9" t="n">
+        <v>289</v>
+      </c>
+      <c r="B296" s="10" t="inlineStr">
+        <is>
+          <t>BU06-09</t>
+        </is>
+      </c>
+      <c r="C296" s="11" t="n"/>
+      <c r="D296" s="12" t="inlineStr">
+        <is>
+          <t>Abfallbehälter Metall weiß mit Push-Deckel
+Hoher runder Abfallbehälter aus weiß lackiertem Metall mit verchromtem Push-Deckel.</t>
+        </is>
+      </c>
+      <c r="E296" s="13" t="n"/>
+      <c r="F296" s="12" t="inlineStr">
+        <is>
+          <t>Küche / Essen</t>
+        </is>
+      </c>
+      <c r="G296" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H296" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I296" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J296" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="K296" s="15">
+        <f>J296*1.19</f>
+        <v/>
+      </c>
+      <c r="L296" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M296" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N296" s="16" t="n"/>
+      <c r="O296" s="17" t="n"/>
+      <c r="P296" s="18" t="n"/>
+      <c r="Q296" s="19">
+        <f>IF(N296&lt;&gt;"ja","",IF(O296="",H296,O296)*J296)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="297" ht="78" customHeight="1">
+      <c r="A297" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="B297" s="21" t="inlineStr">
+        <is>
+          <t>BU06-10</t>
+        </is>
+      </c>
+      <c r="C297" s="22" t="n"/>
+      <c r="D297" s="23" t="inlineStr">
+        <is>
+          <t>Servierwagen Edelstahl, drei Ebenen
+Servierwagen aus Edelstahl mit drei geschlossenen Ablageböden, umlaufenden Schiebegriffen und vier Lenkrollen, zwei davon feststellbar.</t>
+        </is>
+      </c>
+      <c r="E297" s="13" t="n"/>
+      <c r="F297" s="23" t="inlineStr">
+        <is>
+          <t>Küche / Essen</t>
+        </is>
+      </c>
+      <c r="G297" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H297" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I297" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J297" s="24" t="n">
+        <v>90</v>
+      </c>
+      <c r="K297" s="25">
+        <f>J297*1.19</f>
+        <v/>
+      </c>
+      <c r="L297" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M297" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N297" s="16" t="n"/>
+      <c r="O297" s="17" t="n"/>
+      <c r="P297" s="18" t="n"/>
+      <c r="Q297" s="26">
+        <f>IF(N297&lt;&gt;"ja","",IF(O297="",H297,O297)*J297)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="298" ht="78" customHeight="1">
+      <c r="A298" s="9" t="n">
+        <v>291</v>
+      </c>
+      <c r="B298" s="10" t="inlineStr">
+        <is>
+          <t>BU06-11</t>
+        </is>
+      </c>
+      <c r="C298" s="11" t="n"/>
+      <c r="D298" s="12" t="inlineStr">
+        <is>
+          <t>Schreibtisch schwarzbraun mit Schublade
+Schmaler Schreibtisch in Schwarzbraun mit einer breiten Schublade und seitlichem Unterbau.</t>
+        </is>
+      </c>
+      <c r="E298" s="13" t="n"/>
+      <c r="F298" s="12" t="inlineStr">
+        <is>
+          <t>Küche / Essen</t>
+        </is>
+      </c>
+      <c r="G298" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H298" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I298" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J298" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="K298" s="15">
+        <f>J298*1.19</f>
+        <v/>
+      </c>
+      <c r="L298" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M298" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N298" s="16" t="n"/>
+      <c r="O298" s="17" t="n"/>
+      <c r="P298" s="18" t="n"/>
+      <c r="Q298" s="19">
+        <f>IF(N298&lt;&gt;"ja","",IF(O298="",H298,O298)*J298)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="299" ht="78" customHeight="1">
+      <c r="A299" s="20" t="n">
+        <v>292</v>
+      </c>
+      <c r="B299" s="21" t="inlineStr">
+        <is>
+          <t>BU06-12</t>
+        </is>
+      </c>
+      <c r="C299" s="22" t="n"/>
+      <c r="D299" s="23" t="inlineStr">
+        <is>
+          <t>Schalensessel grau mit Holzbeinen
+Sessel in Erwachsenengröße: graue Kunststoffschale mit Armlehnen auf konischen Beinen aus hellem Massivholz, dazu ein rundes Sitzkissen aus cognacfarbenem Kunstleder.</t>
+        </is>
+      </c>
+      <c r="E299" s="13" t="n"/>
+      <c r="F299" s="23" t="inlineStr">
+        <is>
+          <t>Küche / Essen</t>
+        </is>
+      </c>
+      <c r="G299" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H299" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I299" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J299" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="K299" s="25">
+        <f>J299*1.19</f>
+        <v/>
+      </c>
+      <c r="L299" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M299" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N299" s="16" t="n"/>
+      <c r="O299" s="17" t="n"/>
+      <c r="P299" s="18" t="n"/>
+      <c r="Q299" s="26">
+        <f>IF(N299&lt;&gt;"ja","",IF(O299="",H299,O299)*J299)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="300" ht="78" customHeight="1">
+      <c r="A300" s="9" t="n">
+        <v>293</v>
+      </c>
+      <c r="B300" s="10" t="inlineStr">
+        <is>
+          <t>BU06-13</t>
+        </is>
+      </c>
+      <c r="C300" s="11" t="n"/>
+      <c r="D300" s="12" t="inlineStr">
+        <is>
+          <t>Regal weiß, schmal und hoch
+Schmales hohes Regal in Weiß mit verstellbaren Böden.</t>
+        </is>
+      </c>
+      <c r="E300" s="13" t="n"/>
+      <c r="F300" s="12" t="inlineStr">
+        <is>
+          <t>Küche / Essen</t>
+        </is>
+      </c>
+      <c r="G300" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H300" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I300" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J300" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="K300" s="15">
+        <f>J300*1.19</f>
+        <v/>
+      </c>
+      <c r="L300" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M300" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N300" s="16" t="n"/>
+      <c r="O300" s="17" t="n"/>
+      <c r="P300" s="18" t="n"/>
+      <c r="Q300" s="19">
+        <f>IF(N300&lt;&gt;"ja","",IF(O300="",H300,O300)*J300)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="301" ht="78" customHeight="1">
+      <c r="A301" s="20" t="n">
+        <v>294</v>
+      </c>
+      <c r="B301" s="21" t="inlineStr">
+        <is>
+          <t>BU06-14</t>
+        </is>
+      </c>
+      <c r="C301" s="22" t="n"/>
+      <c r="D301" s="23" t="inlineStr">
+        <is>
+          <t>Fächerregal grau, 24 Fächer
+Langes niedriges Regal in Grau mit vierundzwanzig Fächern in vier Reihen, durchgehende Deckplatte. Als Postfach- und Ablageregal genutzt.</t>
+        </is>
+      </c>
+      <c r="E301" s="13" t="n"/>
+      <c r="F301" s="23" t="inlineStr">
+        <is>
+          <t>Küche / Essen</t>
+        </is>
+      </c>
+      <c r="G301" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H301" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I301" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J301" s="24" t="n">
+        <v>120</v>
+      </c>
+      <c r="K301" s="25">
+        <f>J301*1.19</f>
+        <v/>
+      </c>
+      <c r="L301" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M301" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N301" s="16" t="n"/>
+      <c r="O301" s="17" t="n"/>
+      <c r="P301" s="18" t="n"/>
+      <c r="Q301" s="26">
+        <f>IF(N301&lt;&gt;"ja","",IF(O301="",H301,O301)*J301)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="303" ht="24" customHeight="1">
+      <c r="A303" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B295" s="1" t="n"/>
-      <c r="C295" s="1" t="n"/>
-      <c r="D295" s="1" t="n"/>
-      <c r="E295" s="1" t="n"/>
-      <c r="F295" s="1" t="n"/>
-      <c r="G295" s="1" t="n"/>
-      <c r="H295" s="1" t="n"/>
-      <c r="I295" s="1" t="n"/>
-      <c r="J295" s="1" t="n"/>
-      <c r="K295" s="1" t="n"/>
-      <c r="L295" s="1" t="n"/>
-      <c r="M295" s="1" t="n"/>
-      <c r="N295" s="1" t="n"/>
-      <c r="O295" s="1" t="n"/>
-      <c r="P295" s="1" t="n"/>
-      <c r="Q295" s="1" t="n"/>
-    </row>
-    <row r="296" ht="22" customHeight="1">
-      <c r="A296" s="37" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl netto</t>
-        </is>
-      </c>
-      <c r="Q296" s="38">
-        <f>SUM(Q8:Q293)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="297" ht="22" customHeight="1">
-      <c r="A297" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q297" s="38">
-        <f>Q296*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="298" ht="26" customHeight="1">
-      <c r="A298" s="39" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl brutto</t>
-        </is>
-      </c>
-      <c r="Q298" s="40">
-        <f>Q296+Q297</f>
-        <v/>
-      </c>
-    </row>
-    <row r="299" ht="22" customHeight="1">
-      <c r="A299" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q299" s="41">
-        <f>COUNTIF(N8:N293,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="302" ht="24" customHeight="1">
-      <c r="A302" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B302" s="44" t="n"/>
-      <c r="C302" s="44" t="n"/>
-      <c r="D302" s="44" t="n"/>
-      <c r="E302" s="44" t="n"/>
-      <c r="F302" s="44" t="n"/>
-      <c r="G302" s="44" t="n"/>
-      <c r="H302" s="44" t="n"/>
-      <c r="I302" s="44" t="n"/>
-      <c r="J302" s="44" t="n"/>
-      <c r="K302" s="44" t="n"/>
-      <c r="L302" s="44" t="n"/>
-      <c r="M302" s="44" t="n"/>
-      <c r="N302" s="44" t="n"/>
-      <c r="O302" s="44" t="n"/>
-      <c r="P302" s="44" t="n"/>
-      <c r="Q302" s="44" t="n"/>
-    </row>
-    <row r="303" ht="22" customHeight="1">
-      <c r="A303" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
-        </is>
-      </c>
-      <c r="Q303" s="38">
-        <f>SUMPRODUCT(H8:H293,J8:J293)</f>
-        <v/>
-      </c>
+      <c r="B303" s="1" t="n"/>
+      <c r="C303" s="1" t="n"/>
+      <c r="D303" s="1" t="n"/>
+      <c r="E303" s="1" t="n"/>
+      <c r="F303" s="1" t="n"/>
+      <c r="G303" s="1" t="n"/>
+      <c r="H303" s="1" t="n"/>
+      <c r="I303" s="1" t="n"/>
+      <c r="J303" s="1" t="n"/>
+      <c r="K303" s="1" t="n"/>
+      <c r="L303" s="1" t="n"/>
+      <c r="M303" s="1" t="n"/>
+      <c r="N303" s="1" t="n"/>
+      <c r="O303" s="1" t="n"/>
+      <c r="P303" s="1" t="n"/>
+      <c r="Q303" s="1" t="n"/>
     </row>
     <row r="304" ht="22" customHeight="1">
       <c r="A304" s="37" t="inlineStr">
         <is>
+          <t>Wert Ihrer Auswahl netto</t>
+        </is>
+      </c>
+      <c r="Q304" s="38">
+        <f>SUM(Q8:Q301)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="305" ht="22" customHeight="1">
+      <c r="A305" s="37" t="inlineStr">
+        <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q304" s="38">
-        <f>Q303*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="305" ht="22" customHeight="1">
-      <c r="A305" s="45" t="inlineStr">
+      <c r="Q305" s="38">
+        <f>Q304*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="306" ht="26" customHeight="1">
+      <c r="A306" s="39" t="inlineStr">
+        <is>
+          <t>Wert Ihrer Auswahl brutto</t>
+        </is>
+      </c>
+      <c r="Q306" s="40">
+        <f>Q304+Q305</f>
+        <v/>
+      </c>
+    </row>
+    <row r="307" ht="22" customHeight="1">
+      <c r="A307" s="37" t="inlineStr">
+        <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q307" s="41">
+        <f>COUNTIF(N8:N301,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="24" customHeight="1">
+      <c r="A310" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B310" s="44" t="n"/>
+      <c r="C310" s="44" t="n"/>
+      <c r="D310" s="44" t="n"/>
+      <c r="E310" s="44" t="n"/>
+      <c r="F310" s="44" t="n"/>
+      <c r="G310" s="44" t="n"/>
+      <c r="H310" s="44" t="n"/>
+      <c r="I310" s="44" t="n"/>
+      <c r="J310" s="44" t="n"/>
+      <c r="K310" s="44" t="n"/>
+      <c r="L310" s="44" t="n"/>
+      <c r="M310" s="44" t="n"/>
+      <c r="N310" s="44" t="n"/>
+      <c r="O310" s="44" t="n"/>
+      <c r="P310" s="44" t="n"/>
+      <c r="Q310" s="44" t="n"/>
+    </row>
+    <row r="311" ht="22" customHeight="1">
+      <c r="A311" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q311" s="38">
+        <f>SUMPRODUCT(H8:H301,J8:J301)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="312" ht="22" customHeight="1">
+      <c r="A312" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q312" s="38">
+        <f>Q311*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="313" ht="22" customHeight="1">
+      <c r="A313" s="45" t="inlineStr">
         <is>
           <t>Gesamtwert brutto</t>
         </is>
       </c>
-      <c r="Q305" s="46">
-        <f>Q303+Q304</f>
-        <v/>
-      </c>
-    </row>
-    <row r="307" ht="24" customHeight="1">
-      <c r="A307" s="47" t="inlineStr">
+      <c r="Q313" s="46">
+        <f>Q311+Q312</f>
+        <v/>
+      </c>
+    </row>
+    <row r="315" ht="24" customHeight="1">
+      <c r="A315" s="47" t="inlineStr">
         <is>
           <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
         </is>
       </c>
-      <c r="B307" s="48" t="n"/>
-      <c r="C307" s="48" t="n"/>
-      <c r="D307" s="48" t="n"/>
-      <c r="E307" s="48" t="n"/>
-      <c r="F307" s="48" t="n"/>
-      <c r="G307" s="48" t="n"/>
-      <c r="H307" s="48" t="n"/>
-      <c r="I307" s="48" t="n"/>
-      <c r="J307" s="48" t="n"/>
-      <c r="K307" s="48" t="n"/>
-      <c r="L307" s="48" t="n"/>
-      <c r="M307" s="48" t="n"/>
-      <c r="N307" s="48" t="n"/>
-      <c r="O307" s="48" t="n"/>
-      <c r="P307" s="48" t="n"/>
-      <c r="Q307" s="48" t="n"/>
-    </row>
-    <row r="308" ht="22" customHeight="1">
-      <c r="A308" s="37" t="inlineStr">
+      <c r="B315" s="48" t="n"/>
+      <c r="C315" s="48" t="n"/>
+      <c r="D315" s="48" t="n"/>
+      <c r="E315" s="48" t="n"/>
+      <c r="F315" s="48" t="n"/>
+      <c r="G315" s="48" t="n"/>
+      <c r="H315" s="48" t="n"/>
+      <c r="I315" s="48" t="n"/>
+      <c r="J315" s="48" t="n"/>
+      <c r="K315" s="48" t="n"/>
+      <c r="L315" s="48" t="n"/>
+      <c r="M315" s="48" t="n"/>
+      <c r="N315" s="48" t="n"/>
+      <c r="O315" s="48" t="n"/>
+      <c r="P315" s="48" t="n"/>
+      <c r="Q315" s="48" t="n"/>
+    </row>
+    <row r="316" ht="22" customHeight="1">
+      <c r="A316" s="37" t="inlineStr">
         <is>
           <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
         </is>
       </c>
-      <c r="Q308" s="38">
-        <f>-Q303*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="309" ht="22" customHeight="1">
-      <c r="A309" s="45" t="inlineStr">
+      <c r="Q316" s="38">
+        <f>-Q311*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="317" ht="22" customHeight="1">
+      <c r="A317" s="45" t="inlineStr">
         <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="Q309" s="46">
-        <f>Q303+Q308</f>
-        <v/>
-      </c>
-    </row>
-    <row r="310" ht="22" customHeight="1">
-      <c r="A310" s="37" t="inlineStr">
+      <c r="Q317" s="46">
+        <f>Q311+Q316</f>
+        <v/>
+      </c>
+    </row>
+    <row r="318" ht="22" customHeight="1">
+      <c r="A318" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q310" s="38">
-        <f>Q309*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="311" ht="26" customHeight="1">
-      <c r="A311" s="39" t="inlineStr">
+      <c r="Q318" s="38">
+        <f>Q317*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="319" ht="26" customHeight="1">
+      <c r="A319" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q311" s="40">
-        <f>Q309+Q310</f>
-        <v/>
-      </c>
-    </row>
-    <row r="312">
-      <c r="A312" s="42" t="inlineStr">
+      <c r="Q319" s="40">
+        <f>Q317+Q318</f>
+        <v/>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="314">
-      <c r="A314" s="49" t="inlineStr">
+    <row r="322">
+      <c r="A322" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="315"/>
-    <row r="316"/>
-    <row r="317"/>
+    <row r="323"/>
+    <row r="324"/>
+    <row r="325"/>
   </sheetData>
-  <autoFilter ref="A7:Q293"/>
+  <autoFilter ref="A7:Q301"/>
   <mergeCells count="26">
-    <mergeCell ref="A295:Q295"/>
+    <mergeCell ref="A313:P313"/>
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A309:P309"/>
-    <mergeCell ref="A298:P298"/>
-    <mergeCell ref="A303:P303"/>
+    <mergeCell ref="A307:P307"/>
+    <mergeCell ref="A320:Q320"/>
+    <mergeCell ref="A312:P312"/>
+    <mergeCell ref="A310:Q310"/>
     <mergeCell ref="A311:P311"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A300:Q300"/>
+    <mergeCell ref="A318:P318"/>
     <mergeCell ref="L4:Q4"/>
-    <mergeCell ref="A299:P299"/>
-    <mergeCell ref="A308:P308"/>
+    <mergeCell ref="A322:Q325"/>
+    <mergeCell ref="A315:Q315"/>
     <mergeCell ref="C3:I3"/>
+    <mergeCell ref="A319:P319"/>
     <mergeCell ref="A304:P304"/>
-    <mergeCell ref="A310:P310"/>
-    <mergeCell ref="A296:P296"/>
     <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A314:Q317"/>
-    <mergeCell ref="A302:Q302"/>
+    <mergeCell ref="A308:Q308"/>
+    <mergeCell ref="A316:P316"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
     <mergeCell ref="A305:P305"/>
-    <mergeCell ref="A307:Q307"/>
-    <mergeCell ref="A312:Q312"/>
+    <mergeCell ref="A303:Q303"/>
+    <mergeCell ref="A317:P317"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A297:P297"/>
+    <mergeCell ref="A306:P306"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q293">
+  <conditionalFormatting sqref="A8:Q301">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N293" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N301" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O293" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O301" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$301</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$310</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -7793,6 +7793,231 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>301</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="296" name="Image 296" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId296"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>302</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="297" name="Image 297" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId297"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>303</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="298" name="Image 298" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId298"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>304</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="299" name="Image 299" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId299"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>305</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="300" name="Image 300" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId300"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>306</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="301" name="Image 301" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId301"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>307</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="302" name="Image 302" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId302"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>308</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="303" name="Image 303" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId303"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>309</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="304" name="Image 304" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId304"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -8085,7 +8310,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q325"/>
+  <dimension ref="A1:Q334"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -15417,7 +15642,7 @@
         </is>
       </c>
       <c r="H126" s="10" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I126" s="10" t="inlineStr">
         <is>
@@ -16617,7 +16842,7 @@
         </is>
       </c>
       <c r="H146" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I146" s="10" t="inlineStr">
         <is>
@@ -25957,261 +26182,801 @@
         <v/>
       </c>
     </row>
-    <row r="303" ht="24" customHeight="1">
-      <c r="A303" s="36" t="inlineStr">
+    <row r="302" ht="78" customHeight="1">
+      <c r="A302" s="9" t="n">
+        <v>295</v>
+      </c>
+      <c r="B302" s="10" t="inlineStr">
+        <is>
+          <t>NE03-01</t>
+        </is>
+      </c>
+      <c r="C302" s="11" t="n"/>
+      <c r="D302" s="12" t="inlineStr">
+        <is>
+          <t>Wandregale in Wolkenform
+Wandregale in Wolkenform aus lackiertem Holz, ohne Zwischenböden: ein großes und ein kleineres in Weiß, zwei in Schwarz.</t>
+        </is>
+      </c>
+      <c r="E302" s="13" t="n"/>
+      <c r="F302" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 2</t>
+        </is>
+      </c>
+      <c r="G302" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H302" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I302" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J302" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K302" s="15">
+        <f>J302*1.19</f>
+        <v/>
+      </c>
+      <c r="L302" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M302" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N302" s="16" t="n"/>
+      <c r="O302" s="17" t="n"/>
+      <c r="P302" s="18" t="n"/>
+      <c r="Q302" s="19">
+        <f>IF(N302&lt;&gt;"ja","",IF(O302="",H302,O302)*J302)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="303" ht="78" customHeight="1">
+      <c r="A303" s="20" t="n">
+        <v>296</v>
+      </c>
+      <c r="B303" s="21" t="inlineStr">
+        <is>
+          <t>NE03-03</t>
+        </is>
+      </c>
+      <c r="C303" s="22" t="n"/>
+      <c r="D303" s="23" t="inlineStr">
+        <is>
+          <t>Wesco Gitterbett Kunststoff, grau
+Krippenbett von Wesco aus grauem Kunststoff mit geschlossenem Sockel, belüfteten Seitenwänden und Griffausschnitten zum Verschieben. Logo an der Längsseite: wesco.</t>
+        </is>
+      </c>
+      <c r="E303" s="13" t="n"/>
+      <c r="F303" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 2</t>
+        </is>
+      </c>
+      <c r="G303" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H303" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I303" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J303" s="24" t="n">
+        <v>180</v>
+      </c>
+      <c r="K303" s="25">
+        <f>J303*1.19</f>
+        <v/>
+      </c>
+      <c r="L303" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M303" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N303" s="16" t="n"/>
+      <c r="O303" s="17" t="n"/>
+      <c r="P303" s="18" t="n"/>
+      <c r="Q303" s="26">
+        <f>IF(N303&lt;&gt;"ja","",IF(O303="",H303,O303)*J303)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="304" ht="78" customHeight="1">
+      <c r="A304" s="9" t="n">
+        <v>297</v>
+      </c>
+      <c r="B304" s="10" t="inlineStr">
+        <is>
+          <t>NE03-04</t>
+        </is>
+      </c>
+      <c r="C304" s="11" t="n"/>
+      <c r="D304" s="12" t="inlineStr">
+        <is>
+          <t>Gitterbett Holz weiß
+Kinderbett aus weiß lackiertem Holz mit Sprossen an allen vier Seiten und geschwungenen Kopf- und Fußteilen, einschließlich Matratze.</t>
+        </is>
+      </c>
+      <c r="E304" s="13" t="n"/>
+      <c r="F304" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 2</t>
+        </is>
+      </c>
+      <c r="G304" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H304" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I304" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J304" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="K304" s="15">
+        <f>J304*1.19</f>
+        <v/>
+      </c>
+      <c r="L304" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M304" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N304" s="16" t="n"/>
+      <c r="O304" s="17" t="n"/>
+      <c r="P304" s="18" t="n"/>
+      <c r="Q304" s="19">
+        <f>IF(N304&lt;&gt;"ja","",IF(O304="",H304,O304)*J304)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="305" ht="78" customHeight="1">
+      <c r="A305" s="20" t="n">
+        <v>298</v>
+      </c>
+      <c r="B305" s="21" t="inlineStr">
+        <is>
+          <t>NE03-05</t>
+        </is>
+      </c>
+      <c r="C305" s="22" t="n"/>
+      <c r="D305" s="23" t="inlineStr">
+        <is>
+          <t>Hauck Kinderwagen schwarz
+Sportwagen von Hauck in Schwarz mit Verdeck, Fünfpunktgurt und Faltmechanik. Aufdruck am Sitz: Rapid Fold. Der Stoff ist an mehreren Stellen verschmutzt.</t>
+        </is>
+      </c>
+      <c r="E305" s="13" t="n"/>
+      <c r="F305" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 2</t>
+        </is>
+      </c>
+      <c r="G305" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H305" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I305" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J305" s="24" t="n">
+        <v>45</v>
+      </c>
+      <c r="K305" s="25">
+        <f>J305*1.19</f>
+        <v/>
+      </c>
+      <c r="L305" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M305" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N305" s="16" t="n"/>
+      <c r="O305" s="17" t="n"/>
+      <c r="P305" s="18" t="n"/>
+      <c r="Q305" s="26">
+        <f>IF(N305&lt;&gt;"ja","",IF(O305="",H305,O305)*J305)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="306" ht="78" customHeight="1">
+      <c r="A306" s="9" t="n">
+        <v>299</v>
+      </c>
+      <c r="B306" s="10" t="inlineStr">
+        <is>
+          <t>NE03-06</t>
+        </is>
+      </c>
+      <c r="C306" s="11" t="n"/>
+      <c r="D306" s="12" t="inlineStr">
+        <is>
+          <t>Leuchtobjekt Elefant, Metall
+Dekoleuchte in Elefantenform aus taupefarbenem Metall mit elf Fassungen für Glühlampen auf der Vorderseite, zum Stellen.</t>
+        </is>
+      </c>
+      <c r="E306" s="13" t="n"/>
+      <c r="F306" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 2</t>
+        </is>
+      </c>
+      <c r="G306" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H306" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I306" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J306" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="K306" s="15">
+        <f>J306*1.19</f>
+        <v/>
+      </c>
+      <c r="L306" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M306" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N306" s="16" t="n"/>
+      <c r="O306" s="17" t="n"/>
+      <c r="P306" s="18" t="n"/>
+      <c r="Q306" s="19">
+        <f>IF(N306&lt;&gt;"ja","",IF(O306="",H306,O306)*J306)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="307" ht="78" customHeight="1">
+      <c r="A307" s="20" t="n">
+        <v>300</v>
+      </c>
+      <c r="B307" s="21" t="inlineStr">
+        <is>
+          <t>NE03-07</t>
+        </is>
+      </c>
+      <c r="C307" s="22" t="n"/>
+      <c r="D307" s="23" t="inlineStr">
+        <is>
+          <t>IKEA Kleiderschrank anthrazit mit drei Böden
+Hoher Schrank von IKEA in Anthrazit mit zwei Türen, weißen ovalen Griffmulden und drei Einlegeböden.</t>
+        </is>
+      </c>
+      <c r="E307" s="13" t="n"/>
+      <c r="F307" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 2</t>
+        </is>
+      </c>
+      <c r="G307" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H307" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I307" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J307" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="K307" s="25">
+        <f>J307*1.19</f>
+        <v/>
+      </c>
+      <c r="L307" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M307" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N307" s="16" t="n"/>
+      <c r="O307" s="17" t="n"/>
+      <c r="P307" s="18" t="n"/>
+      <c r="Q307" s="26">
+        <f>IF(N307&lt;&gt;"ja","",IF(O307="",H307,O307)*J307)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="308" ht="78" customHeight="1">
+      <c r="A308" s="9" t="n">
+        <v>301</v>
+      </c>
+      <c r="B308" s="10" t="inlineStr">
+        <is>
+          <t>NE03-09</t>
+        </is>
+      </c>
+      <c r="C308" s="11" t="n"/>
+      <c r="D308" s="12" t="inlineStr">
+        <is>
+          <t>IKEA Schrank weiß mit Drahtkörben
+Hoher Schrank von IKEA in Weiß mit zwei Türen, weißen ovalen Griffmulden und innen sechs herausziehbaren Drahtkörben.</t>
+        </is>
+      </c>
+      <c r="E308" s="13" t="n"/>
+      <c r="F308" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 2</t>
+        </is>
+      </c>
+      <c r="G308" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H308" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I308" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J308" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="K308" s="15">
+        <f>J308*1.19</f>
+        <v/>
+      </c>
+      <c r="L308" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M308" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N308" s="16" t="n"/>
+      <c r="O308" s="17" t="n"/>
+      <c r="P308" s="18" t="n"/>
+      <c r="Q308" s="19">
+        <f>IF(N308&lt;&gt;"ja","",IF(O308="",H308,O308)*J308)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="309" ht="78" customHeight="1">
+      <c r="A309" s="20" t="n">
+        <v>302</v>
+      </c>
+      <c r="B309" s="21" t="inlineStr">
+        <is>
+          <t>NE03-10</t>
+        </is>
+      </c>
+      <c r="C309" s="22" t="n"/>
+      <c r="D309" s="23" t="inlineStr">
+        <is>
+          <t>Plüsch-Elefanten, zwei Stück
+Zwei große Plüsch-Elefanten zum Stellen: einer aus cremefarbenem Breitcord, einer aus grau-cremefarben gestreiftem Stoff mit aufgestickten Augen. Am gestreiften Elefanten ein Etikett: done by deer.</t>
+        </is>
+      </c>
+      <c r="E309" s="13" t="n"/>
+      <c r="F309" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 2</t>
+        </is>
+      </c>
+      <c r="G309" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H309" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I309" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J309" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="K309" s="25">
+        <f>J309*1.19</f>
+        <v/>
+      </c>
+      <c r="L309" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M309" s="23" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N309" s="16" t="n"/>
+      <c r="O309" s="17" t="n"/>
+      <c r="P309" s="18" t="n"/>
+      <c r="Q309" s="26">
+        <f>IF(N309&lt;&gt;"ja","",IF(O309="",H309,O309)*J309)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="310" ht="78" customHeight="1">
+      <c r="A310" s="9" t="n">
+        <v>303</v>
+      </c>
+      <c r="B310" s="10" t="inlineStr">
+        <is>
+          <t>NE03-11</t>
+        </is>
+      </c>
+      <c r="C310" s="11" t="n"/>
+      <c r="D310" s="12" t="inlineStr">
+        <is>
+          <t>Wolken-Mobile Stoff, weiß
+Mobile aus drei weißen Stoffwolken in unterschiedlicher Größe, zum Aufhängen.</t>
+        </is>
+      </c>
+      <c r="E310" s="13" t="n"/>
+      <c r="F310" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 2</t>
+        </is>
+      </c>
+      <c r="G310" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H310" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I310" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J310" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="K310" s="15">
+        <f>J310*1.19</f>
+        <v/>
+      </c>
+      <c r="L310" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M310" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N310" s="16" t="n"/>
+      <c r="O310" s="17" t="n"/>
+      <c r="P310" s="18" t="n"/>
+      <c r="Q310" s="19">
+        <f>IF(N310&lt;&gt;"ja","",IF(O310="",H310,O310)*J310)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="312" ht="24" customHeight="1">
+      <c r="A312" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B303" s="1" t="n"/>
-      <c r="C303" s="1" t="n"/>
-      <c r="D303" s="1" t="n"/>
-      <c r="E303" s="1" t="n"/>
-      <c r="F303" s="1" t="n"/>
-      <c r="G303" s="1" t="n"/>
-      <c r="H303" s="1" t="n"/>
-      <c r="I303" s="1" t="n"/>
-      <c r="J303" s="1" t="n"/>
-      <c r="K303" s="1" t="n"/>
-      <c r="L303" s="1" t="n"/>
-      <c r="M303" s="1" t="n"/>
-      <c r="N303" s="1" t="n"/>
-      <c r="O303" s="1" t="n"/>
-      <c r="P303" s="1" t="n"/>
-      <c r="Q303" s="1" t="n"/>
-    </row>
-    <row r="304" ht="22" customHeight="1">
-      <c r="A304" s="37" t="inlineStr">
+      <c r="B312" s="1" t="n"/>
+      <c r="C312" s="1" t="n"/>
+      <c r="D312" s="1" t="n"/>
+      <c r="E312" s="1" t="n"/>
+      <c r="F312" s="1" t="n"/>
+      <c r="G312" s="1" t="n"/>
+      <c r="H312" s="1" t="n"/>
+      <c r="I312" s="1" t="n"/>
+      <c r="J312" s="1" t="n"/>
+      <c r="K312" s="1" t="n"/>
+      <c r="L312" s="1" t="n"/>
+      <c r="M312" s="1" t="n"/>
+      <c r="N312" s="1" t="n"/>
+      <c r="O312" s="1" t="n"/>
+      <c r="P312" s="1" t="n"/>
+      <c r="Q312" s="1" t="n"/>
+    </row>
+    <row r="313" ht="22" customHeight="1">
+      <c r="A313" s="37" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl netto</t>
         </is>
       </c>
-      <c r="Q304" s="38">
-        <f>SUM(Q8:Q301)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="305" ht="22" customHeight="1">
-      <c r="A305" s="37" t="inlineStr">
+      <c r="Q313" s="38">
+        <f>SUM(Q8:Q310)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="314" ht="22" customHeight="1">
+      <c r="A314" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q305" s="38">
-        <f>Q304*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="306" ht="26" customHeight="1">
-      <c r="A306" s="39" t="inlineStr">
+      <c r="Q314" s="38">
+        <f>Q313*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="315" ht="26" customHeight="1">
+      <c r="A315" s="39" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl brutto</t>
         </is>
       </c>
-      <c r="Q306" s="40">
-        <f>Q304+Q305</f>
-        <v/>
-      </c>
-    </row>
-    <row r="307" ht="22" customHeight="1">
-      <c r="A307" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q307" s="41">
-        <f>COUNTIF(N8:N301,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="308">
-      <c r="A308" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="310" ht="24" customHeight="1">
-      <c r="A310" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B310" s="44" t="n"/>
-      <c r="C310" s="44" t="n"/>
-      <c r="D310" s="44" t="n"/>
-      <c r="E310" s="44" t="n"/>
-      <c r="F310" s="44" t="n"/>
-      <c r="G310" s="44" t="n"/>
-      <c r="H310" s="44" t="n"/>
-      <c r="I310" s="44" t="n"/>
-      <c r="J310" s="44" t="n"/>
-      <c r="K310" s="44" t="n"/>
-      <c r="L310" s="44" t="n"/>
-      <c r="M310" s="44" t="n"/>
-      <c r="N310" s="44" t="n"/>
-      <c r="O310" s="44" t="n"/>
-      <c r="P310" s="44" t="n"/>
-      <c r="Q310" s="44" t="n"/>
-    </row>
-    <row r="311" ht="22" customHeight="1">
-      <c r="A311" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
-        </is>
-      </c>
-      <c r="Q311" s="38">
-        <f>SUMPRODUCT(H8:H301,J8:J301)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="312" ht="22" customHeight="1">
-      <c r="A312" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q312" s="38">
-        <f>Q311*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="313" ht="22" customHeight="1">
-      <c r="A313" s="45" t="inlineStr">
-        <is>
-          <t>Gesamtwert brutto</t>
-        </is>
-      </c>
-      <c r="Q313" s="46">
-        <f>Q311+Q312</f>
-        <v/>
-      </c>
-    </row>
-    <row r="315" ht="24" customHeight="1">
-      <c r="A315" s="47" t="inlineStr">
-        <is>
-          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B315" s="48" t="n"/>
-      <c r="C315" s="48" t="n"/>
-      <c r="D315" s="48" t="n"/>
-      <c r="E315" s="48" t="n"/>
-      <c r="F315" s="48" t="n"/>
-      <c r="G315" s="48" t="n"/>
-      <c r="H315" s="48" t="n"/>
-      <c r="I315" s="48" t="n"/>
-      <c r="J315" s="48" t="n"/>
-      <c r="K315" s="48" t="n"/>
-      <c r="L315" s="48" t="n"/>
-      <c r="M315" s="48" t="n"/>
-      <c r="N315" s="48" t="n"/>
-      <c r="O315" s="48" t="n"/>
-      <c r="P315" s="48" t="n"/>
-      <c r="Q315" s="48" t="n"/>
+      <c r="Q315" s="40">
+        <f>Q313+Q314</f>
+        <v/>
+      </c>
     </row>
     <row r="316" ht="22" customHeight="1">
       <c r="A316" s="37" t="inlineStr">
         <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q316" s="41">
+        <f>COUNTIF(N8:N310,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="319" ht="24" customHeight="1">
+      <c r="A319" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B319" s="44" t="n"/>
+      <c r="C319" s="44" t="n"/>
+      <c r="D319" s="44" t="n"/>
+      <c r="E319" s="44" t="n"/>
+      <c r="F319" s="44" t="n"/>
+      <c r="G319" s="44" t="n"/>
+      <c r="H319" s="44" t="n"/>
+      <c r="I319" s="44" t="n"/>
+      <c r="J319" s="44" t="n"/>
+      <c r="K319" s="44" t="n"/>
+      <c r="L319" s="44" t="n"/>
+      <c r="M319" s="44" t="n"/>
+      <c r="N319" s="44" t="n"/>
+      <c r="O319" s="44" t="n"/>
+      <c r="P319" s="44" t="n"/>
+      <c r="Q319" s="44" t="n"/>
+    </row>
+    <row r="320" ht="22" customHeight="1">
+      <c r="A320" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q320" s="38">
+        <f>SUMPRODUCT(H8:H310,J8:J310)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="321" ht="22" customHeight="1">
+      <c r="A321" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q321" s="38">
+        <f>Q320*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="322" ht="22" customHeight="1">
+      <c r="A322" s="45" t="inlineStr">
+        <is>
+          <t>Gesamtwert brutto</t>
+        </is>
+      </c>
+      <c r="Q322" s="46">
+        <f>Q320+Q321</f>
+        <v/>
+      </c>
+    </row>
+    <row r="324" ht="24" customHeight="1">
+      <c r="A324" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B324" s="48" t="n"/>
+      <c r="C324" s="48" t="n"/>
+      <c r="D324" s="48" t="n"/>
+      <c r="E324" s="48" t="n"/>
+      <c r="F324" s="48" t="n"/>
+      <c r="G324" s="48" t="n"/>
+      <c r="H324" s="48" t="n"/>
+      <c r="I324" s="48" t="n"/>
+      <c r="J324" s="48" t="n"/>
+      <c r="K324" s="48" t="n"/>
+      <c r="L324" s="48" t="n"/>
+      <c r="M324" s="48" t="n"/>
+      <c r="N324" s="48" t="n"/>
+      <c r="O324" s="48" t="n"/>
+      <c r="P324" s="48" t="n"/>
+      <c r="Q324" s="48" t="n"/>
+    </row>
+    <row r="325" ht="22" customHeight="1">
+      <c r="A325" s="37" t="inlineStr">
+        <is>
           <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
         </is>
       </c>
-      <c r="Q316" s="38">
-        <f>-Q311*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="317" ht="22" customHeight="1">
-      <c r="A317" s="45" t="inlineStr">
+      <c r="Q325" s="38">
+        <f>-Q320*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="326" ht="22" customHeight="1">
+      <c r="A326" s="45" t="inlineStr">
         <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="Q317" s="46">
-        <f>Q311+Q316</f>
-        <v/>
-      </c>
-    </row>
-    <row r="318" ht="22" customHeight="1">
-      <c r="A318" s="37" t="inlineStr">
+      <c r="Q326" s="46">
+        <f>Q320+Q325</f>
+        <v/>
+      </c>
+    </row>
+    <row r="327" ht="22" customHeight="1">
+      <c r="A327" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q318" s="38">
-        <f>Q317*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="319" ht="26" customHeight="1">
-      <c r="A319" s="39" t="inlineStr">
+      <c r="Q327" s="38">
+        <f>Q326*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="328" ht="26" customHeight="1">
+      <c r="A328" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q319" s="40">
-        <f>Q317+Q318</f>
-        <v/>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" s="42" t="inlineStr">
+      <c r="Q328" s="40">
+        <f>Q326+Q327</f>
+        <v/>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="322">
-      <c r="A322" s="49" t="inlineStr">
+    <row r="331">
+      <c r="A331" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="323"/>
-    <row r="324"/>
-    <row r="325"/>
+    <row r="332"/>
+    <row r="333"/>
+    <row r="334"/>
   </sheetData>
-  <autoFilter ref="A7:Q301"/>
+  <autoFilter ref="A7:Q310"/>
   <mergeCells count="26">
     <mergeCell ref="A313:P313"/>
+    <mergeCell ref="A329:Q329"/>
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A307:P307"/>
-    <mergeCell ref="A320:Q320"/>
-    <mergeCell ref="A312:P312"/>
-    <mergeCell ref="A310:Q310"/>
-    <mergeCell ref="A311:P311"/>
+    <mergeCell ref="A322:P322"/>
+    <mergeCell ref="A321:P321"/>
+    <mergeCell ref="A319:Q319"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A318:P318"/>
+    <mergeCell ref="A327:P327"/>
     <mergeCell ref="L4:Q4"/>
-    <mergeCell ref="A322:Q325"/>
-    <mergeCell ref="A315:Q315"/>
+    <mergeCell ref="A331:Q334"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A319:P319"/>
-    <mergeCell ref="A304:P304"/>
+    <mergeCell ref="A320:P320"/>
+    <mergeCell ref="A314:P314"/>
+    <mergeCell ref="A328:P328"/>
+    <mergeCell ref="A317:Q317"/>
+    <mergeCell ref="A325:P325"/>
     <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A308:Q308"/>
+    <mergeCell ref="A315:P315"/>
     <mergeCell ref="A316:P316"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A305:P305"/>
-    <mergeCell ref="A303:Q303"/>
-    <mergeCell ref="A317:P317"/>
+    <mergeCell ref="A312:Q312"/>
+    <mergeCell ref="A326:P326"/>
+    <mergeCell ref="A324:Q324"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A306:P306"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q301">
+  <conditionalFormatting sqref="A8:Q310">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N301" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N310" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O301" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O310" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$310</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$322</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8018,6 +8018,306 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>310</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="305" name="Image 305" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId305"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>311</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="306" name="Image 306" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId306"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>312</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="307" name="Image 307" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId307"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>313</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="308" name="Image 308" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId308"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>314</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="309" name="Image 309" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId309"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>315</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="310" name="Image 310" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId310"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>316</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="311" name="Image 311" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId311"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>317</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="312" name="Image 312" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId312"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>318</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="313" name="Image 313" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId313"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>319</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="314" name="Image 314" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId314"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>320</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="315" name="Image 315" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId315"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>321</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="316" name="Image 316" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId316"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -8310,7 +8610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q334"/>
+  <dimension ref="A1:Q346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -15638,11 +15938,11 @@
       </c>
       <c r="G126" s="10" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H126" s="10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I126" s="10" t="inlineStr">
         <is>
@@ -17918,7 +18218,7 @@
       </c>
       <c r="G164" s="10" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H164" s="10" t="n">
@@ -22962,7 +23262,7 @@
       </c>
       <c r="G248" s="10" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H248" s="10" t="n">
@@ -23322,7 +23622,7 @@
       </c>
       <c r="G254" s="10" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H254" s="10" t="n">
@@ -26266,7 +26566,7 @@
       </c>
       <c r="G303" s="21" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H303" s="21" t="n">
@@ -26326,11 +26626,11 @@
       </c>
       <c r="G304" s="10" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H304" s="10" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I304" s="10" t="inlineStr">
         <is>
@@ -26435,7 +26735,7 @@
       <c r="D306" s="12" t="inlineStr">
         <is>
           <t>Leuchtobjekt Elefant, Metall
-Dekoleuchte in Elefantenform aus taupefarbenem Metall mit elf Fassungen für Glühlampen auf der Vorderseite, zum Stellen.</t>
+Dekoleuchte in Elefantenform aus taupefarbenem Metall mit elf Fassungen für Glühlampen auf der Vorderseite, zum Stellen. Hersteller: Zara Home.</t>
         </is>
       </c>
       <c r="E306" s="13" t="n"/>
@@ -26690,7 +26990,7 @@
         </is>
       </c>
       <c r="H310" s="10" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I310" s="10" t="inlineStr">
         <is>
@@ -26722,261 +27022,985 @@
         <v/>
       </c>
     </row>
-    <row r="312" ht="24" customHeight="1">
-      <c r="A312" s="36" t="inlineStr">
+    <row r="311" ht="78" customHeight="1">
+      <c r="A311" s="20" t="n">
+        <v>304</v>
+      </c>
+      <c r="B311" s="21" t="inlineStr">
+        <is>
+          <t>NE04-03</t>
+        </is>
+      </c>
+      <c r="C311" s="22" t="n"/>
+      <c r="D311" s="23" t="inlineStr">
+        <is>
+          <t>Wanddekoration Wolken schwarz
+Flache Wandelemente in Wolkenform aus schwarz lackiertem Holz, zum Aufhängen.</t>
+        </is>
+      </c>
+      <c r="E311" s="13" t="n"/>
+      <c r="F311" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 3</t>
+        </is>
+      </c>
+      <c r="G311" s="21" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H311" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I311" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J311" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="K311" s="25">
+        <f>J311*1.19</f>
+        <v/>
+      </c>
+      <c r="L311" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M311" s="23" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N311" s="16" t="n"/>
+      <c r="O311" s="17" t="n"/>
+      <c r="P311" s="18" t="n"/>
+      <c r="Q311" s="26">
+        <f>IF(N311&lt;&gt;"ja","",IF(O311="",H311,O311)*J311)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="312" ht="78" customHeight="1">
+      <c r="A312" s="9" t="n">
+        <v>305</v>
+      </c>
+      <c r="B312" s="10" t="inlineStr">
+        <is>
+          <t>NE04-04</t>
+        </is>
+      </c>
+      <c r="C312" s="11" t="n"/>
+      <c r="D312" s="12" t="inlineStr">
+        <is>
+          <t>Schrank weiß mit zwei Türen und zwei Schubladen
+Weißer Schrank mit zwei oberen Türen und zwei breiten Schubladen darunter, Griffmulden ausgeschnitten.</t>
+        </is>
+      </c>
+      <c r="E312" s="13" t="n"/>
+      <c r="F312" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 3</t>
+        </is>
+      </c>
+      <c r="G312" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H312" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I312" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J312" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="K312" s="15">
+        <f>J312*1.19</f>
+        <v/>
+      </c>
+      <c r="L312" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M312" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N312" s="16" t="n"/>
+      <c r="O312" s="17" t="n"/>
+      <c r="P312" s="18" t="n"/>
+      <c r="Q312" s="19">
+        <f>IF(N312&lt;&gt;"ja","",IF(O312="",H312,O312)*J312)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="313" ht="78" customHeight="1">
+      <c r="A313" s="20" t="n">
+        <v>306</v>
+      </c>
+      <c r="B313" s="21" t="inlineStr">
+        <is>
+          <t>NE04-06</t>
+        </is>
+      </c>
+      <c r="C313" s="22" t="n"/>
+      <c r="D313" s="23" t="inlineStr">
+        <is>
+          <t>Wandspiegel in Wolkenform, weiß
+Wandspiegel in Wolkenform mit breitem weiß lackiertem Holzrahmen.</t>
+        </is>
+      </c>
+      <c r="E313" s="13" t="n"/>
+      <c r="F313" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 3</t>
+        </is>
+      </c>
+      <c r="G313" s="21" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H313" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I313" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J313" s="24" t="n">
+        <v>45</v>
+      </c>
+      <c r="K313" s="25">
+        <f>J313*1.19</f>
+        <v/>
+      </c>
+      <c r="L313" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M313" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N313" s="16" t="n"/>
+      <c r="O313" s="17" t="n"/>
+      <c r="P313" s="18" t="n"/>
+      <c r="Q313" s="26">
+        <f>IF(N313&lt;&gt;"ja","",IF(O313="",H313,O313)*J313)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="314" ht="78" customHeight="1">
+      <c r="A314" s="9" t="n">
+        <v>307</v>
+      </c>
+      <c r="B314" s="10" t="inlineStr">
+        <is>
+          <t>NE04-07</t>
+        </is>
+      </c>
+      <c r="C314" s="11" t="n"/>
+      <c r="D314" s="12" t="inlineStr">
+        <is>
+          <t>Wesco Wickelauflage beige
+Große Wickelauflage von Wesco mit beigem Kunstlederbezug und umlaufendem Rand.</t>
+        </is>
+      </c>
+      <c r="E314" s="13" t="n"/>
+      <c r="F314" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 3</t>
+        </is>
+      </c>
+      <c r="G314" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H314" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I314" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J314" s="14" t="n">
+        <v>45</v>
+      </c>
+      <c r="K314" s="15">
+        <f>J314*1.19</f>
+        <v/>
+      </c>
+      <c r="L314" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M314" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N314" s="16" t="n"/>
+      <c r="O314" s="17" t="n"/>
+      <c r="P314" s="18" t="n"/>
+      <c r="Q314" s="19">
+        <f>IF(N314&lt;&gt;"ja","",IF(O314="",H314,O314)*J314)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="315" ht="78" customHeight="1">
+      <c r="A315" s="20" t="n">
+        <v>308</v>
+      </c>
+      <c r="B315" s="21" t="inlineStr">
+        <is>
+          <t>NE04-08</t>
+        </is>
+      </c>
+      <c r="C315" s="22" t="n"/>
+      <c r="D315" s="23" t="inlineStr">
+        <is>
+          <t>Wickelkommode Buche mit zehn Wannen
+Wickelkommode aus Buche-Dekor mit weißer Wickelfläche und umlaufender Aufkantung, darunter zehn herausziehbare Kunststoffwannen in zwei Reihen.</t>
+        </is>
+      </c>
+      <c r="E315" s="13" t="n"/>
+      <c r="F315" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 3</t>
+        </is>
+      </c>
+      <c r="G315" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H315" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I315" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J315" s="24" t="n">
+        <v>180</v>
+      </c>
+      <c r="K315" s="25">
+        <f>J315*1.19</f>
+        <v/>
+      </c>
+      <c r="L315" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M315" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N315" s="16" t="n"/>
+      <c r="O315" s="17" t="n"/>
+      <c r="P315" s="18" t="n"/>
+      <c r="Q315" s="26">
+        <f>IF(N315&lt;&gt;"ja","",IF(O315="",H315,O315)*J315)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="316" ht="78" customHeight="1">
+      <c r="A316" s="9" t="n">
+        <v>309</v>
+      </c>
+      <c r="B316" s="35" t="inlineStr">
+        <is>
+          <t>NE04-09</t>
+        </is>
+      </c>
+      <c r="C316" s="11" t="n"/>
+      <c r="D316" s="12" t="inlineStr">
+        <is>
+          <t>Wickelkommode Buche groß mit Treppe
+Große Wickelkommode aus Buche-Dekor mit weißer Wickelfläche und Aufkantung: in der Mitte eine herausrollbare Treppe für den Aufstieg, links und rechts je fünf herausziehbare Kunststoffwannen.</t>
+        </is>
+      </c>
+      <c r="E316" s="13" t="n"/>
+      <c r="F316" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 3</t>
+        </is>
+      </c>
+      <c r="G316" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H316" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I316" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J316" s="14" t="n">
+        <v>250</v>
+      </c>
+      <c r="K316" s="15">
+        <f>J316*1.19</f>
+        <v/>
+      </c>
+      <c r="L316" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M316" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N316" s="16" t="n"/>
+      <c r="O316" s="17" t="n"/>
+      <c r="P316" s="18" t="n"/>
+      <c r="Q316" s="19">
+        <f>IF(N316&lt;&gt;"ja","",IF(O316="",H316,O316)*J316)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="317" ht="78" customHeight="1">
+      <c r="A317" s="20" t="n">
+        <v>310</v>
+      </c>
+      <c r="B317" s="21" t="inlineStr">
+        <is>
+          <t>NE04-10</t>
+        </is>
+      </c>
+      <c r="C317" s="22" t="n"/>
+      <c r="D317" s="23" t="inlineStr">
+        <is>
+          <t>Wickelkommode mit Türen und Fachböden
+Wickelkommode aus Buche-Dekor mit weißer Wickelfläche und Aufkantung, geschlossener Unterbau mit zwei Türen und drei Fachböden.</t>
+        </is>
+      </c>
+      <c r="E317" s="13" t="n"/>
+      <c r="F317" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 3</t>
+        </is>
+      </c>
+      <c r="G317" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H317" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I317" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J317" s="24" t="n">
+        <v>180</v>
+      </c>
+      <c r="K317" s="25">
+        <f>J317*1.19</f>
+        <v/>
+      </c>
+      <c r="L317" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M317" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N317" s="16" t="n"/>
+      <c r="O317" s="17" t="n"/>
+      <c r="P317" s="18" t="n"/>
+      <c r="Q317" s="26">
+        <f>IF(N317&lt;&gt;"ja","",IF(O317="",H317,O317)*J317)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="318" ht="78" customHeight="1">
+      <c r="A318" s="9" t="n">
+        <v>311</v>
+      </c>
+      <c r="B318" s="10" t="inlineStr">
+        <is>
+          <t>NE04-11</t>
+        </is>
+      </c>
+      <c r="C318" s="11" t="n"/>
+      <c r="D318" s="12" t="inlineStr">
+        <is>
+          <t>Baby Jogger City Select Kinderwagen, rot
+Kinderwagen Baby Jogger City Select in Rot mit Verdeck, Fünfpunktgurt, Einkaufskorb und luftbereiften Rädern. Aufdruck am Rahmen: city select by baby jogger. Der Rahmen ist an mehreren Stellen abgeschabt.</t>
+        </is>
+      </c>
+      <c r="E318" s="13" t="n"/>
+      <c r="F318" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 3</t>
+        </is>
+      </c>
+      <c r="G318" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H318" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I318" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J318" s="14" t="n">
+        <v>180</v>
+      </c>
+      <c r="K318" s="15">
+        <f>J318*1.19</f>
+        <v/>
+      </c>
+      <c r="L318" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M318" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N318" s="16" t="n"/>
+      <c r="O318" s="17" t="n"/>
+      <c r="P318" s="18" t="n"/>
+      <c r="Q318" s="19">
+        <f>IF(N318&lt;&gt;"ja","",IF(O318="",H318,O318)*J318)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="319" ht="78" customHeight="1">
+      <c r="A319" s="20" t="n">
+        <v>312</v>
+      </c>
+      <c r="B319" s="21" t="inlineStr">
+        <is>
+          <t>NE04-12</t>
+        </is>
+      </c>
+      <c r="C319" s="22" t="n"/>
+      <c r="D319" s="23" t="inlineStr">
+        <is>
+          <t>Hochflorteppich rund, rot-orange
+Runder Hochflorteppich in melierten Rot-, Orange- und Violetttönen.</t>
+        </is>
+      </c>
+      <c r="E319" s="13" t="inlineStr">
+        <is>
+          <t>Ø ca. 200 cm</t>
+        </is>
+      </c>
+      <c r="F319" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 3</t>
+        </is>
+      </c>
+      <c r="G319" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H319" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I319" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J319" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="K319" s="25">
+        <f>J319*1.19</f>
+        <v/>
+      </c>
+      <c r="L319" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M319" s="23" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N319" s="16" t="n"/>
+      <c r="O319" s="17" t="n"/>
+      <c r="P319" s="18" t="n"/>
+      <c r="Q319" s="26">
+        <f>IF(N319&lt;&gt;"ja","",IF(O319="",H319,O319)*J319)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="320" ht="78" customHeight="1">
+      <c r="A320" s="9" t="n">
+        <v>313</v>
+      </c>
+      <c r="B320" s="10" t="inlineStr">
+        <is>
+          <t>NE04-13</t>
+        </is>
+      </c>
+      <c r="C320" s="11" t="n"/>
+      <c r="D320" s="12" t="inlineStr">
+        <is>
+          <t>Windeleimer weiß mit Deckel
+Hoher Windeleimer aus weißem Kunststoff mit aufklappbarem Deckel, Dichtring und Fußpedal.</t>
+        </is>
+      </c>
+      <c r="E320" s="13" t="n"/>
+      <c r="F320" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 3</t>
+        </is>
+      </c>
+      <c r="G320" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H320" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I320" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J320" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K320" s="15">
+        <f>J320*1.19</f>
+        <v/>
+      </c>
+      <c r="L320" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M320" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N320" s="16" t="n"/>
+      <c r="O320" s="17" t="n"/>
+      <c r="P320" s="18" t="n"/>
+      <c r="Q320" s="19">
+        <f>IF(N320&lt;&gt;"ja","",IF(O320="",H320,O320)*J320)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="321" ht="78" customHeight="1">
+      <c r="A321" s="20" t="n">
+        <v>314</v>
+      </c>
+      <c r="B321" s="21" t="inlineStr">
+        <is>
+          <t>NE04-14</t>
+        </is>
+      </c>
+      <c r="C321" s="22" t="n"/>
+      <c r="D321" s="23" t="inlineStr">
+        <is>
+          <t>Wandregal in Bergform, Holz
+Wandregal in Form einer Bergkette aus hellem Holz mit weiß lackierten Gipfeln, durchgehender Ablageboden.</t>
+        </is>
+      </c>
+      <c r="E321" s="13" t="n"/>
+      <c r="F321" s="23" t="inlineStr">
+        <is>
+          <t>Schlafraum 3</t>
+        </is>
+      </c>
+      <c r="G321" s="21" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H321" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I321" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J321" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="K321" s="25">
+        <f>J321*1.19</f>
+        <v/>
+      </c>
+      <c r="L321" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M321" s="23" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N321" s="16" t="n"/>
+      <c r="O321" s="17" t="n"/>
+      <c r="P321" s="18" t="n"/>
+      <c r="Q321" s="26">
+        <f>IF(N321&lt;&gt;"ja","",IF(O321="",H321,O321)*J321)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="322" ht="78" customHeight="1">
+      <c r="A322" s="9" t="n">
+        <v>315</v>
+      </c>
+      <c r="B322" s="10" t="inlineStr">
+        <is>
+          <t>NE04-15</t>
+        </is>
+      </c>
+      <c r="C322" s="11" t="n"/>
+      <c r="D322" s="12" t="inlineStr">
+        <is>
+          <t>Mobile Holzbogen mit Filzkugeln
+Mobile mit geschwungenem Bogen aus Birkenholz, daran Filzkugeln in Rot, Grau und Weiß sowie Sterne und Häuschen aus Holz und Filz in Schwarz, Grau und Natur.</t>
+        </is>
+      </c>
+      <c r="E322" s="13" t="n"/>
+      <c r="F322" s="12" t="inlineStr">
+        <is>
+          <t>Schlafraum 3</t>
+        </is>
+      </c>
+      <c r="G322" s="10" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H322" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="I322" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J322" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="K322" s="15">
+        <f>J322*1.19</f>
+        <v/>
+      </c>
+      <c r="L322" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M322" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N322" s="16" t="n"/>
+      <c r="O322" s="17" t="n"/>
+      <c r="P322" s="18" t="n"/>
+      <c r="Q322" s="19">
+        <f>IF(N322&lt;&gt;"ja","",IF(O322="",H322,O322)*J322)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="324" ht="24" customHeight="1">
+      <c r="A324" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B312" s="1" t="n"/>
-      <c r="C312" s="1" t="n"/>
-      <c r="D312" s="1" t="n"/>
-      <c r="E312" s="1" t="n"/>
-      <c r="F312" s="1" t="n"/>
-      <c r="G312" s="1" t="n"/>
-      <c r="H312" s="1" t="n"/>
-      <c r="I312" s="1" t="n"/>
-      <c r="J312" s="1" t="n"/>
-      <c r="K312" s="1" t="n"/>
-      <c r="L312" s="1" t="n"/>
-      <c r="M312" s="1" t="n"/>
-      <c r="N312" s="1" t="n"/>
-      <c r="O312" s="1" t="n"/>
-      <c r="P312" s="1" t="n"/>
-      <c r="Q312" s="1" t="n"/>
-    </row>
-    <row r="313" ht="22" customHeight="1">
-      <c r="A313" s="37" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl netto</t>
-        </is>
-      </c>
-      <c r="Q313" s="38">
-        <f>SUM(Q8:Q310)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="314" ht="22" customHeight="1">
-      <c r="A314" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q314" s="38">
-        <f>Q313*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="315" ht="26" customHeight="1">
-      <c r="A315" s="39" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl brutto</t>
-        </is>
-      </c>
-      <c r="Q315" s="40">
-        <f>Q313+Q314</f>
-        <v/>
-      </c>
-    </row>
-    <row r="316" ht="22" customHeight="1">
-      <c r="A316" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q316" s="41">
-        <f>COUNTIF(N8:N310,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="319" ht="24" customHeight="1">
-      <c r="A319" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B319" s="44" t="n"/>
-      <c r="C319" s="44" t="n"/>
-      <c r="D319" s="44" t="n"/>
-      <c r="E319" s="44" t="n"/>
-      <c r="F319" s="44" t="n"/>
-      <c r="G319" s="44" t="n"/>
-      <c r="H319" s="44" t="n"/>
-      <c r="I319" s="44" t="n"/>
-      <c r="J319" s="44" t="n"/>
-      <c r="K319" s="44" t="n"/>
-      <c r="L319" s="44" t="n"/>
-      <c r="M319" s="44" t="n"/>
-      <c r="N319" s="44" t="n"/>
-      <c r="O319" s="44" t="n"/>
-      <c r="P319" s="44" t="n"/>
-      <c r="Q319" s="44" t="n"/>
-    </row>
-    <row r="320" ht="22" customHeight="1">
-      <c r="A320" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
-        </is>
-      </c>
-      <c r="Q320" s="38">
-        <f>SUMPRODUCT(H8:H310,J8:J310)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="321" ht="22" customHeight="1">
-      <c r="A321" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q321" s="38">
-        <f>Q320*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="322" ht="22" customHeight="1">
-      <c r="A322" s="45" t="inlineStr">
-        <is>
-          <t>Gesamtwert brutto</t>
-        </is>
-      </c>
-      <c r="Q322" s="46">
-        <f>Q320+Q321</f>
-        <v/>
-      </c>
-    </row>
-    <row r="324" ht="24" customHeight="1">
-      <c r="A324" s="47" t="inlineStr">
-        <is>
-          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B324" s="48" t="n"/>
-      <c r="C324" s="48" t="n"/>
-      <c r="D324" s="48" t="n"/>
-      <c r="E324" s="48" t="n"/>
-      <c r="F324" s="48" t="n"/>
-      <c r="G324" s="48" t="n"/>
-      <c r="H324" s="48" t="n"/>
-      <c r="I324" s="48" t="n"/>
-      <c r="J324" s="48" t="n"/>
-      <c r="K324" s="48" t="n"/>
-      <c r="L324" s="48" t="n"/>
-      <c r="M324" s="48" t="n"/>
-      <c r="N324" s="48" t="n"/>
-      <c r="O324" s="48" t="n"/>
-      <c r="P324" s="48" t="n"/>
-      <c r="Q324" s="48" t="n"/>
+      <c r="B324" s="1" t="n"/>
+      <c r="C324" s="1" t="n"/>
+      <c r="D324" s="1" t="n"/>
+      <c r="E324" s="1" t="n"/>
+      <c r="F324" s="1" t="n"/>
+      <c r="G324" s="1" t="n"/>
+      <c r="H324" s="1" t="n"/>
+      <c r="I324" s="1" t="n"/>
+      <c r="J324" s="1" t="n"/>
+      <c r="K324" s="1" t="n"/>
+      <c r="L324" s="1" t="n"/>
+      <c r="M324" s="1" t="n"/>
+      <c r="N324" s="1" t="n"/>
+      <c r="O324" s="1" t="n"/>
+      <c r="P324" s="1" t="n"/>
+      <c r="Q324" s="1" t="n"/>
     </row>
     <row r="325" ht="22" customHeight="1">
       <c r="A325" s="37" t="inlineStr">
         <is>
-          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
+          <t>Wert Ihrer Auswahl netto</t>
         </is>
       </c>
       <c r="Q325" s="38">
-        <f>-Q320*0.15</f>
+        <f>SUM(Q8:Q322)</f>
         <v/>
       </c>
     </row>
     <row r="326" ht="22" customHeight="1">
-      <c r="A326" s="45" t="inlineStr">
-        <is>
-          <t>Paketpreis netto</t>
-        </is>
-      </c>
-      <c r="Q326" s="46">
-        <f>Q320+Q325</f>
-        <v/>
-      </c>
-    </row>
-    <row r="327" ht="22" customHeight="1">
-      <c r="A327" s="37" t="inlineStr">
+      <c r="A326" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q327" s="38">
-        <f>Q326*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="328" ht="26" customHeight="1">
-      <c r="A328" s="39" t="inlineStr">
-        <is>
-          <t>Paketpreis brutto</t>
-        </is>
-      </c>
-      <c r="Q328" s="40">
-        <f>Q326+Q327</f>
+      <c r="Q326" s="38">
+        <f>Q325*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="327" ht="26" customHeight="1">
+      <c r="A327" s="39" t="inlineStr">
+        <is>
+          <t>Wert Ihrer Auswahl brutto</t>
+        </is>
+      </c>
+      <c r="Q327" s="40">
+        <f>Q325+Q326</f>
+        <v/>
+      </c>
+    </row>
+    <row r="328" ht="22" customHeight="1">
+      <c r="A328" s="37" t="inlineStr">
+        <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q328" s="41">
+        <f>COUNTIF(N8:N322,"ja")</f>
         <v/>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="42" t="inlineStr">
         <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="24" customHeight="1">
+      <c r="A331" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B331" s="44" t="n"/>
+      <c r="C331" s="44" t="n"/>
+      <c r="D331" s="44" t="n"/>
+      <c r="E331" s="44" t="n"/>
+      <c r="F331" s="44" t="n"/>
+      <c r="G331" s="44" t="n"/>
+      <c r="H331" s="44" t="n"/>
+      <c r="I331" s="44" t="n"/>
+      <c r="J331" s="44" t="n"/>
+      <c r="K331" s="44" t="n"/>
+      <c r="L331" s="44" t="n"/>
+      <c r="M331" s="44" t="n"/>
+      <c r="N331" s="44" t="n"/>
+      <c r="O331" s="44" t="n"/>
+      <c r="P331" s="44" t="n"/>
+      <c r="Q331" s="44" t="n"/>
+    </row>
+    <row r="332" ht="22" customHeight="1">
+      <c r="A332" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q332" s="38">
+        <f>SUMPRODUCT(H8:H322,J8:J322)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="333" ht="22" customHeight="1">
+      <c r="A333" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q333" s="38">
+        <f>Q332*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="334" ht="22" customHeight="1">
+      <c r="A334" s="45" t="inlineStr">
+        <is>
+          <t>Gesamtwert brutto</t>
+        </is>
+      </c>
+      <c r="Q334" s="46">
+        <f>Q332+Q333</f>
+        <v/>
+      </c>
+    </row>
+    <row r="336" ht="24" customHeight="1">
+      <c r="A336" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B336" s="48" t="n"/>
+      <c r="C336" s="48" t="n"/>
+      <c r="D336" s="48" t="n"/>
+      <c r="E336" s="48" t="n"/>
+      <c r="F336" s="48" t="n"/>
+      <c r="G336" s="48" t="n"/>
+      <c r="H336" s="48" t="n"/>
+      <c r="I336" s="48" t="n"/>
+      <c r="J336" s="48" t="n"/>
+      <c r="K336" s="48" t="n"/>
+      <c r="L336" s="48" t="n"/>
+      <c r="M336" s="48" t="n"/>
+      <c r="N336" s="48" t="n"/>
+      <c r="O336" s="48" t="n"/>
+      <c r="P336" s="48" t="n"/>
+      <c r="Q336" s="48" t="n"/>
+    </row>
+    <row r="337" ht="22" customHeight="1">
+      <c r="A337" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
+        </is>
+      </c>
+      <c r="Q337" s="38">
+        <f>-Q332*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="338" ht="22" customHeight="1">
+      <c r="A338" s="45" t="inlineStr">
+        <is>
+          <t>Paketpreis netto</t>
+        </is>
+      </c>
+      <c r="Q338" s="46">
+        <f>Q332+Q337</f>
+        <v/>
+      </c>
+    </row>
+    <row r="339" ht="22" customHeight="1">
+      <c r="A339" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q339" s="38">
+        <f>Q338*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="340" ht="26" customHeight="1">
+      <c r="A340" s="39" t="inlineStr">
+        <is>
+          <t>Paketpreis brutto</t>
+        </is>
+      </c>
+      <c r="Q340" s="40">
+        <f>Q338+Q339</f>
+        <v/>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="42" t="inlineStr">
+        <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="331">
-      <c r="A331" s="49" t="inlineStr">
+    <row r="343">
+      <c r="A343" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="332"/>
-    <row r="333"/>
-    <row r="334"/>
+    <row r="344"/>
+    <row r="345"/>
+    <row r="346"/>
   </sheetData>
-  <autoFilter ref="A7:Q310"/>
+  <autoFilter ref="A7:Q322"/>
   <mergeCells count="26">
-    <mergeCell ref="A313:P313"/>
     <mergeCell ref="A329:Q329"/>
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A322:P322"/>
-    <mergeCell ref="A321:P321"/>
-    <mergeCell ref="A319:Q319"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A327:P327"/>
+    <mergeCell ref="A333:P333"/>
+    <mergeCell ref="A332:P332"/>
     <mergeCell ref="L4:Q4"/>
-    <mergeCell ref="A331:Q334"/>
     <mergeCell ref="C3:I3"/>
-    <mergeCell ref="A320:P320"/>
-    <mergeCell ref="A314:P314"/>
+    <mergeCell ref="A338:P338"/>
     <mergeCell ref="A328:P328"/>
-    <mergeCell ref="A317:Q317"/>
+    <mergeCell ref="A337:P337"/>
+    <mergeCell ref="A340:P340"/>
     <mergeCell ref="A325:P325"/>
+    <mergeCell ref="A339:P339"/>
+    <mergeCell ref="A334:P334"/>
     <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A315:P315"/>
-    <mergeCell ref="A316:P316"/>
+    <mergeCell ref="A341:Q341"/>
+    <mergeCell ref="A331:Q331"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A312:Q312"/>
     <mergeCell ref="A326:P326"/>
     <mergeCell ref="A324:Q324"/>
+    <mergeCell ref="A336:Q336"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
+    <mergeCell ref="A343:Q346"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q310">
+  <conditionalFormatting sqref="A8:Q322">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N310" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N322" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O310" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O322" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$322</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$333</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8318,6 +8318,281 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>322</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="317" name="Image 317" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId317"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>323</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="318" name="Image 318" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId318"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>324</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="319" name="Image 319" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId319"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>325</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="320" name="Image 320" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId320"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>326</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="321" name="Image 321" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId321"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>327</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="322" name="Image 322" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId322"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>328</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="323" name="Image 323" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId323"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>329</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="324" name="Image 324" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId324"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>330</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="325" name="Image 325" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId325"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>331</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="326" name="Image 326" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId326"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>332</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="327" name="Image 327" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId327"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -8610,7 +8885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q346"/>
+  <dimension ref="A1:Q357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -12029,7 +12304,7 @@
         </is>
       </c>
       <c r="H61" s="21" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I61" s="21" t="inlineStr">
         <is>
@@ -12089,7 +12364,7 @@
         </is>
       </c>
       <c r="H62" s="10" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I62" s="10" t="inlineStr">
         <is>
@@ -14682,7 +14957,7 @@
         </is>
       </c>
       <c r="H105" s="21" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="I105" s="21" t="inlineStr">
         <is>
@@ -16767,7 +17042,7 @@
       <c r="D140" s="12" t="inlineStr">
         <is>
           <t>Kindertisch rund weiß mit Holzbeinen
-Runder Kindertisch, weiße Platte auf konischen Beinen aus massivem Holz. Die Plattenkante ist an einer Stelle beschädigt und dunkel abgestoßen.</t>
+Runder Kindertisch, weiße Platte auf konischen Beinen aus massivem Holz.</t>
         </is>
       </c>
       <c r="E140" s="13" t="n"/>
@@ -16778,11 +17053,11 @@
       </c>
       <c r="G140" s="10" t="inlineStr">
         <is>
-          <t>stark gebraucht</t>
+          <t>gebraucht</t>
         </is>
       </c>
       <c r="H140" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I140" s="10" t="inlineStr">
         <is>
@@ -27286,7 +27561,7 @@
       </c>
       <c r="G315" s="21" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H315" s="21" t="n">
@@ -27346,7 +27621,7 @@
       </c>
       <c r="G316" s="10" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H316" s="10" t="n">
@@ -27406,7 +27681,7 @@
       </c>
       <c r="G317" s="21" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H317" s="21" t="n">
@@ -27590,7 +27865,7 @@
       </c>
       <c r="G320" s="10" t="inlineStr">
         <is>
-          <t>gebraucht</t>
+          <t>gut</t>
         </is>
       </c>
       <c r="H320" s="10" t="n">
@@ -27746,261 +28021,921 @@
         <v/>
       </c>
     </row>
-    <row r="324" ht="24" customHeight="1">
-      <c r="A324" s="36" t="inlineStr">
+    <row r="323" ht="78" customHeight="1">
+      <c r="A323" s="20" t="n">
+        <v>316</v>
+      </c>
+      <c r="B323" s="35" t="inlineStr">
+        <is>
+          <t>NE05-04</t>
+        </is>
+      </c>
+      <c r="C323" s="22" t="n"/>
+      <c r="D323" s="23" t="inlineStr">
+        <is>
+          <t>Freischwinger rot, Erwachsenengröße
+Freischwinger aus einem Stück Kunststoff, rot matt, S-förmig geschwungen. Erwachsenengröße.</t>
+        </is>
+      </c>
+      <c r="E323" s="13" t="n"/>
+      <c r="F323" s="23" t="inlineStr">
+        <is>
+          <t>Speisesaal</t>
+        </is>
+      </c>
+      <c r="G323" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H323" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I323" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J323" s="24" t="n">
+        <v>180</v>
+      </c>
+      <c r="K323" s="25">
+        <f>J323*1.19</f>
+        <v/>
+      </c>
+      <c r="L323" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M323" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N323" s="16" t="n"/>
+      <c r="O323" s="17" t="n"/>
+      <c r="P323" s="18" t="n"/>
+      <c r="Q323" s="26">
+        <f>IF(N323&lt;&gt;"ja","",IF(O323="",H323,O323)*J323)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="324" ht="78" customHeight="1">
+      <c r="A324" s="9" t="n">
+        <v>317</v>
+      </c>
+      <c r="B324" s="35" t="inlineStr">
+        <is>
+          <t>NE05-05</t>
+        </is>
+      </c>
+      <c r="C324" s="11" t="n"/>
+      <c r="D324" s="12" t="inlineStr">
+        <is>
+          <t>Freischwinger rot, Kindergröße
+Freischwinger aus einem Stück Kunststoff, rot matt, S-förmig geschwungen. Kindergröße.</t>
+        </is>
+      </c>
+      <c r="E324" s="13" t="n"/>
+      <c r="F324" s="12" t="inlineStr">
+        <is>
+          <t>Speisesaal</t>
+        </is>
+      </c>
+      <c r="G324" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H324" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I324" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J324" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="K324" s="15">
+        <f>J324*1.19</f>
+        <v/>
+      </c>
+      <c r="L324" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M324" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N324" s="16" t="n"/>
+      <c r="O324" s="17" t="n"/>
+      <c r="P324" s="18" t="n"/>
+      <c r="Q324" s="19">
+        <f>IF(N324&lt;&gt;"ja","",IF(O324="",H324,O324)*J324)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="325" ht="78" customHeight="1">
+      <c r="A325" s="20" t="n">
+        <v>318</v>
+      </c>
+      <c r="B325" s="21" t="inlineStr">
+        <is>
+          <t>NE05-06</t>
+        </is>
+      </c>
+      <c r="C325" s="22" t="n"/>
+      <c r="D325" s="23" t="inlineStr">
+        <is>
+          <t>Treppenhochstuhl schwarz
+Mitwachsender Treppenhochstuhl: Seitenwangen und Platten schwarz lackiert, Sitz- und Fußbrett in der Höhe verstellbar, umlaufender Bügel mit Rückenlehne. Die Seitenwangen tragen Lochreihen für die Verstellung.</t>
+        </is>
+      </c>
+      <c r="E325" s="13" t="n"/>
+      <c r="F325" s="23" t="inlineStr">
+        <is>
+          <t>Speisesaal</t>
+        </is>
+      </c>
+      <c r="G325" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H325" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I325" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J325" s="24" t="n">
+        <v>90</v>
+      </c>
+      <c r="K325" s="25">
+        <f>J325*1.19</f>
+        <v/>
+      </c>
+      <c r="L325" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M325" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N325" s="16" t="n"/>
+      <c r="O325" s="17" t="n"/>
+      <c r="P325" s="18" t="n"/>
+      <c r="Q325" s="26">
+        <f>IF(N325&lt;&gt;"ja","",IF(O325="",H325,O325)*J325)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="326" ht="78" customHeight="1">
+      <c r="A326" s="9" t="n">
+        <v>319</v>
+      </c>
+      <c r="B326" s="10" t="inlineStr">
+        <is>
+          <t>NE05-07</t>
+        </is>
+      </c>
+      <c r="C326" s="11" t="n"/>
+      <c r="D326" s="12" t="inlineStr">
+        <is>
+          <t>Treppenhochstuhl schwarz-weiß
+Mitwachsender Treppenhochstuhl: Seitenwangen schwarz lackiert, Sitz- und Fußbrett sowie Bügel mit Rückenlehne in Weiß, in der Höhe verstellbar. Die Seitenwangen tragen Lochreihen für die Verstellung.</t>
+        </is>
+      </c>
+      <c r="E326" s="13" t="n"/>
+      <c r="F326" s="12" t="inlineStr">
+        <is>
+          <t>Speisesaal</t>
+        </is>
+      </c>
+      <c r="G326" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H326" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="I326" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J326" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="K326" s="15">
+        <f>J326*1.19</f>
+        <v/>
+      </c>
+      <c r="L326" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M326" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N326" s="16" t="n"/>
+      <c r="O326" s="17" t="n"/>
+      <c r="P326" s="18" t="n"/>
+      <c r="Q326" s="19">
+        <f>IF(N326&lt;&gt;"ja","",IF(O326="",H326,O326)*J326)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="327" ht="78" customHeight="1">
+      <c r="A327" s="20" t="n">
+        <v>320</v>
+      </c>
+      <c r="B327" s="21" t="inlineStr">
+        <is>
+          <t>NE05-08</t>
+        </is>
+      </c>
+      <c r="C327" s="22" t="n"/>
+      <c r="D327" s="23" t="inlineStr">
+        <is>
+          <t>Treppenhochstuhl grau mit Buchengestell
+Mitwachsender Treppenhochstuhl: Seitenwangen aus Buche natur, Sitz- und Fußbrett sowie Bügel mit Rückenlehne in Grau, in der Höhe verstellbar. Die Seitenwangen tragen Lochreihen für die Verstellung.</t>
+        </is>
+      </c>
+      <c r="E327" s="13" t="n"/>
+      <c r="F327" s="23" t="inlineStr">
+        <is>
+          <t>Speisesaal</t>
+        </is>
+      </c>
+      <c r="G327" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H327" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I327" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J327" s="24" t="n">
+        <v>90</v>
+      </c>
+      <c r="K327" s="25">
+        <f>J327*1.19</f>
+        <v/>
+      </c>
+      <c r="L327" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M327" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N327" s="16" t="n"/>
+      <c r="O327" s="17" t="n"/>
+      <c r="P327" s="18" t="n"/>
+      <c r="Q327" s="26">
+        <f>IF(N327&lt;&gt;"ja","",IF(O327="",H327,O327)*J327)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="328" ht="78" customHeight="1">
+      <c r="A328" s="9" t="n">
+        <v>321</v>
+      </c>
+      <c r="B328" s="10" t="inlineStr">
+        <is>
+          <t>NE05-09</t>
+        </is>
+      </c>
+      <c r="C328" s="11" t="n"/>
+      <c r="D328" s="12" t="inlineStr">
+        <is>
+          <t>IKEA Ingolf Kinderhochstuhl weiß
+Hoher Kinderstuhl von IKEA aus Massivholz, weiß lackiert, mit Kreuzstrebe in der Lehne und Fußstütze. Etikett an der Unterseite: Ingolf, 20948, IKEA of Sweden. Die Sitzfläche ist stark verkratzt und die Farbe an den Kanten abgeplatzt.</t>
+        </is>
+      </c>
+      <c r="E328" s="13" t="n"/>
+      <c r="F328" s="12" t="inlineStr">
+        <is>
+          <t>Speisesaal</t>
+        </is>
+      </c>
+      <c r="G328" s="10" t="inlineStr">
+        <is>
+          <t>stark gebraucht</t>
+        </is>
+      </c>
+      <c r="H328" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="I328" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J328" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="K328" s="15">
+        <f>J328*1.19</f>
+        <v/>
+      </c>
+      <c r="L328" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M328" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N328" s="16" t="n"/>
+      <c r="O328" s="17" t="n"/>
+      <c r="P328" s="18" t="n"/>
+      <c r="Q328" s="19">
+        <f>IF(N328&lt;&gt;"ja","",IF(O328="",H328,O328)*J328)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="329" ht="78" customHeight="1">
+      <c r="A329" s="20" t="n">
+        <v>322</v>
+      </c>
+      <c r="B329" s="21" t="inlineStr">
+        <is>
+          <t>NE05-13</t>
+        </is>
+      </c>
+      <c r="C329" s="22" t="n"/>
+      <c r="D329" s="23" t="inlineStr">
+        <is>
+          <t>Rollwagen schwarz mit Holzplatte
+Rollwagen mit schwarzem Metallgestell, oberer Platte aus Multiplex und zwei schwarzen Ablageböden, auf vier Lenkrollen.</t>
+        </is>
+      </c>
+      <c r="E329" s="13" t="n"/>
+      <c r="F329" s="23" t="inlineStr">
+        <is>
+          <t>Speisesaal</t>
+        </is>
+      </c>
+      <c r="G329" s="21" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H329" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I329" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J329" s="24" t="n">
+        <v>70</v>
+      </c>
+      <c r="K329" s="25">
+        <f>J329*1.19</f>
+        <v/>
+      </c>
+      <c r="L329" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M329" s="23" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N329" s="16" t="n"/>
+      <c r="O329" s="17" t="n"/>
+      <c r="P329" s="18" t="n"/>
+      <c r="Q329" s="26">
+        <f>IF(N329&lt;&gt;"ja","",IF(O329="",H329,O329)*J329)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="330" ht="78" customHeight="1">
+      <c r="A330" s="9" t="n">
+        <v>323</v>
+      </c>
+      <c r="B330" s="10" t="inlineStr">
+        <is>
+          <t>NE05-14</t>
+        </is>
+      </c>
+      <c r="C330" s="11" t="n"/>
+      <c r="D330" s="12" t="inlineStr">
+        <is>
+          <t>Glas-Magnettafel weiß, großformatig
+Große Schreib- und Magnettafel aus weiß lackiertem Glas, beschreibbar mit Whiteboard-Markern, einschließlich Magneten.</t>
+        </is>
+      </c>
+      <c r="E330" s="13" t="n"/>
+      <c r="F330" s="12" t="inlineStr">
+        <is>
+          <t>Speisesaal</t>
+        </is>
+      </c>
+      <c r="G330" s="10" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H330" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I330" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J330" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="K330" s="15">
+        <f>J330*1.19</f>
+        <v/>
+      </c>
+      <c r="L330" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M330" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N330" s="16" t="n"/>
+      <c r="O330" s="17" t="n"/>
+      <c r="P330" s="18" t="n"/>
+      <c r="Q330" s="19">
+        <f>IF(N330&lt;&gt;"ja","",IF(O330="",H330,O330)*J330)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="331" ht="78" customHeight="1">
+      <c r="A331" s="20" t="n">
+        <v>324</v>
+      </c>
+      <c r="B331" s="21" t="inlineStr">
+        <is>
+          <t>NE05-15</t>
+        </is>
+      </c>
+      <c r="C331" s="22" t="n"/>
+      <c r="D331" s="23" t="inlineStr">
+        <is>
+          <t>Wandleuchte Rehkitz schwarz
+Wandleuchte in Form eines Rehkitzes aus schwarz lackiertem Holz, mit Kabel und Schnurschalter.</t>
+        </is>
+      </c>
+      <c r="E331" s="13" t="n"/>
+      <c r="F331" s="23" t="inlineStr">
+        <is>
+          <t>Speisesaal</t>
+        </is>
+      </c>
+      <c r="G331" s="21" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H331" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="I331" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J331" s="24" t="n">
+        <v>35</v>
+      </c>
+      <c r="K331" s="25">
+        <f>J331*1.19</f>
+        <v/>
+      </c>
+      <c r="L331" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M331" s="23" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N331" s="16" t="n"/>
+      <c r="O331" s="17" t="n"/>
+      <c r="P331" s="18" t="n"/>
+      <c r="Q331" s="26">
+        <f>IF(N331&lt;&gt;"ja","",IF(O331="",H331,O331)*J331)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="332" ht="78" customHeight="1">
+      <c r="A332" s="9" t="n">
+        <v>325</v>
+      </c>
+      <c r="B332" s="10" t="inlineStr">
+        <is>
+          <t>NE05-16</t>
+        </is>
+      </c>
+      <c r="C332" s="11" t="n"/>
+      <c r="D332" s="12" t="inlineStr">
+        <is>
+          <t>Deko-Stern Holz
+Fünfzackiger Stern aus massivem Holz, natur, zum Stellen oder Aufhängen.</t>
+        </is>
+      </c>
+      <c r="E332" s="13" t="n"/>
+      <c r="F332" s="12" t="inlineStr">
+        <is>
+          <t>Speisesaal</t>
+        </is>
+      </c>
+      <c r="G332" s="10" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H332" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="I332" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J332" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="K332" s="15">
+        <f>J332*1.19</f>
+        <v/>
+      </c>
+      <c r="L332" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M332" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N332" s="16" t="n"/>
+      <c r="O332" s="17" t="n"/>
+      <c r="P332" s="18" t="n"/>
+      <c r="Q332" s="19">
+        <f>IF(N332&lt;&gt;"ja","",IF(O332="",H332,O332)*J332)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="333" ht="78" customHeight="1">
+      <c r="A333" s="20" t="n">
+        <v>326</v>
+      </c>
+      <c r="B333" s="21" t="inlineStr">
+        <is>
+          <t>NE05-17</t>
+        </is>
+      </c>
+      <c r="C333" s="22" t="n"/>
+      <c r="D333" s="23" t="inlineStr">
+        <is>
+          <t>Wandhaken in Stuhlform, schwarz
+Kleine Wandhaken in Form von Stühlen aus schwarz lackiertem Holz, in zwei verschiedenen Ausführungen.</t>
+        </is>
+      </c>
+      <c r="E333" s="13" t="n"/>
+      <c r="F333" s="23" t="inlineStr">
+        <is>
+          <t>Speisesaal</t>
+        </is>
+      </c>
+      <c r="G333" s="21" t="inlineStr">
+        <is>
+          <t>gut</t>
+        </is>
+      </c>
+      <c r="H333" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="I333" s="21" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J333" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="K333" s="25">
+        <f>J333*1.19</f>
+        <v/>
+      </c>
+      <c r="L333" s="21" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M333" s="23" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N333" s="16" t="n"/>
+      <c r="O333" s="17" t="n"/>
+      <c r="P333" s="18" t="n"/>
+      <c r="Q333" s="26">
+        <f>IF(N333&lt;&gt;"ja","",IF(O333="",H333,O333)*J333)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="335" ht="24" customHeight="1">
+      <c r="A335" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B324" s="1" t="n"/>
-      <c r="C324" s="1" t="n"/>
-      <c r="D324" s="1" t="n"/>
-      <c r="E324" s="1" t="n"/>
-      <c r="F324" s="1" t="n"/>
-      <c r="G324" s="1" t="n"/>
-      <c r="H324" s="1" t="n"/>
-      <c r="I324" s="1" t="n"/>
-      <c r="J324" s="1" t="n"/>
-      <c r="K324" s="1" t="n"/>
-      <c r="L324" s="1" t="n"/>
-      <c r="M324" s="1" t="n"/>
-      <c r="N324" s="1" t="n"/>
-      <c r="O324" s="1" t="n"/>
-      <c r="P324" s="1" t="n"/>
-      <c r="Q324" s="1" t="n"/>
-    </row>
-    <row r="325" ht="22" customHeight="1">
-      <c r="A325" s="37" t="inlineStr">
+      <c r="B335" s="1" t="n"/>
+      <c r="C335" s="1" t="n"/>
+      <c r="D335" s="1" t="n"/>
+      <c r="E335" s="1" t="n"/>
+      <c r="F335" s="1" t="n"/>
+      <c r="G335" s="1" t="n"/>
+      <c r="H335" s="1" t="n"/>
+      <c r="I335" s="1" t="n"/>
+      <c r="J335" s="1" t="n"/>
+      <c r="K335" s="1" t="n"/>
+      <c r="L335" s="1" t="n"/>
+      <c r="M335" s="1" t="n"/>
+      <c r="N335" s="1" t="n"/>
+      <c r="O335" s="1" t="n"/>
+      <c r="P335" s="1" t="n"/>
+      <c r="Q335" s="1" t="n"/>
+    </row>
+    <row r="336" ht="22" customHeight="1">
+      <c r="A336" s="37" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl netto</t>
         </is>
       </c>
-      <c r="Q325" s="38">
-        <f>SUM(Q8:Q322)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="326" ht="22" customHeight="1">
-      <c r="A326" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q326" s="38">
-        <f>Q325*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="327" ht="26" customHeight="1">
-      <c r="A327" s="39" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl brutto</t>
-        </is>
-      </c>
-      <c r="Q327" s="40">
-        <f>Q325+Q326</f>
-        <v/>
-      </c>
-    </row>
-    <row r="328" ht="22" customHeight="1">
-      <c r="A328" s="37" t="inlineStr">
-        <is>
-          <t>gewählte Positionen</t>
-        </is>
-      </c>
-      <c r="Q328" s="41">
-        <f>COUNTIF(N8:N322,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" s="42" t="inlineStr">
-        <is>
-          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="331" ht="24" customHeight="1">
-      <c r="A331" s="43" t="inlineStr">
-        <is>
-          <t>B · GESAMTBESTAND</t>
-        </is>
-      </c>
-      <c r="B331" s="44" t="n"/>
-      <c r="C331" s="44" t="n"/>
-      <c r="D331" s="44" t="n"/>
-      <c r="E331" s="44" t="n"/>
-      <c r="F331" s="44" t="n"/>
-      <c r="G331" s="44" t="n"/>
-      <c r="H331" s="44" t="n"/>
-      <c r="I331" s="44" t="n"/>
-      <c r="J331" s="44" t="n"/>
-      <c r="K331" s="44" t="n"/>
-      <c r="L331" s="44" t="n"/>
-      <c r="M331" s="44" t="n"/>
-      <c r="N331" s="44" t="n"/>
-      <c r="O331" s="44" t="n"/>
-      <c r="P331" s="44" t="n"/>
-      <c r="Q331" s="44" t="n"/>
-    </row>
-    <row r="332" ht="22" customHeight="1">
-      <c r="A332" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
-        </is>
-      </c>
-      <c r="Q332" s="38">
-        <f>SUMPRODUCT(H8:H322,J8:J322)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="333" ht="22" customHeight="1">
-      <c r="A333" s="37" t="inlineStr">
-        <is>
-          <t>zzgl. 19 % Umsatzsteuer</t>
-        </is>
-      </c>
-      <c r="Q333" s="38">
-        <f>Q332*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="334" ht="22" customHeight="1">
-      <c r="A334" s="45" t="inlineStr">
-        <is>
-          <t>Gesamtwert brutto</t>
-        </is>
-      </c>
-      <c r="Q334" s="46">
-        <f>Q332+Q333</f>
-        <v/>
-      </c>
-    </row>
-    <row r="336" ht="24" customHeight="1">
-      <c r="A336" s="47" t="inlineStr">
-        <is>
-          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
-        </is>
-      </c>
-      <c r="B336" s="48" t="n"/>
-      <c r="C336" s="48" t="n"/>
-      <c r="D336" s="48" t="n"/>
-      <c r="E336" s="48" t="n"/>
-      <c r="F336" s="48" t="n"/>
-      <c r="G336" s="48" t="n"/>
-      <c r="H336" s="48" t="n"/>
-      <c r="I336" s="48" t="n"/>
-      <c r="J336" s="48" t="n"/>
-      <c r="K336" s="48" t="n"/>
-      <c r="L336" s="48" t="n"/>
-      <c r="M336" s="48" t="n"/>
-      <c r="N336" s="48" t="n"/>
-      <c r="O336" s="48" t="n"/>
-      <c r="P336" s="48" t="n"/>
-      <c r="Q336" s="48" t="n"/>
+      <c r="Q336" s="38">
+        <f>SUM(Q8:Q333)</f>
+        <v/>
+      </c>
     </row>
     <row r="337" ht="22" customHeight="1">
       <c r="A337" s="37" t="inlineStr">
         <is>
-          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
+          <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
       <c r="Q337" s="38">
-        <f>-Q332*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="338" ht="22" customHeight="1">
-      <c r="A338" s="45" t="inlineStr">
-        <is>
-          <t>Paketpreis netto</t>
-        </is>
-      </c>
-      <c r="Q338" s="46">
-        <f>Q332+Q337</f>
+        <f>Q336*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="338" ht="26" customHeight="1">
+      <c r="A338" s="39" t="inlineStr">
+        <is>
+          <t>Wert Ihrer Auswahl brutto</t>
+        </is>
+      </c>
+      <c r="Q338" s="40">
+        <f>Q336+Q337</f>
         <v/>
       </c>
     </row>
     <row r="339" ht="22" customHeight="1">
       <c r="A339" s="37" t="inlineStr">
         <is>
+          <t>gewählte Positionen</t>
+        </is>
+      </c>
+      <c r="Q339" s="41">
+        <f>COUNTIF(N8:N333,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="42" t="inlineStr">
+        <is>
+          <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="24" customHeight="1">
+      <c r="A342" s="43" t="inlineStr">
+        <is>
+          <t>B · GESAMTBESTAND</t>
+        </is>
+      </c>
+      <c r="B342" s="44" t="n"/>
+      <c r="C342" s="44" t="n"/>
+      <c r="D342" s="44" t="n"/>
+      <c r="E342" s="44" t="n"/>
+      <c r="F342" s="44" t="n"/>
+      <c r="G342" s="44" t="n"/>
+      <c r="H342" s="44" t="n"/>
+      <c r="I342" s="44" t="n"/>
+      <c r="J342" s="44" t="n"/>
+      <c r="K342" s="44" t="n"/>
+      <c r="L342" s="44" t="n"/>
+      <c r="M342" s="44" t="n"/>
+      <c r="N342" s="44" t="n"/>
+      <c r="O342" s="44" t="n"/>
+      <c r="P342" s="44" t="n"/>
+      <c r="Q342" s="44" t="n"/>
+    </row>
+    <row r="343" ht="22" customHeight="1">
+      <c r="A343" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q343" s="38">
+        <f>SUMPRODUCT(H8:H333,J8:J333)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="344" ht="22" customHeight="1">
+      <c r="A344" s="37" t="inlineStr">
+        <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q339" s="38">
-        <f>Q338*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="340" ht="26" customHeight="1">
-      <c r="A340" s="39" t="inlineStr">
+      <c r="Q344" s="38">
+        <f>Q343*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="345" ht="22" customHeight="1">
+      <c r="A345" s="45" t="inlineStr">
+        <is>
+          <t>Gesamtwert brutto</t>
+        </is>
+      </c>
+      <c r="Q345" s="46">
+        <f>Q343+Q344</f>
+        <v/>
+      </c>
+    </row>
+    <row r="347" ht="24" customHeight="1">
+      <c r="A347" s="47" t="inlineStr">
+        <is>
+          <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
+        </is>
+      </c>
+      <c r="B347" s="48" t="n"/>
+      <c r="C347" s="48" t="n"/>
+      <c r="D347" s="48" t="n"/>
+      <c r="E347" s="48" t="n"/>
+      <c r="F347" s="48" t="n"/>
+      <c r="G347" s="48" t="n"/>
+      <c r="H347" s="48" t="n"/>
+      <c r="I347" s="48" t="n"/>
+      <c r="J347" s="48" t="n"/>
+      <c r="K347" s="48" t="n"/>
+      <c r="L347" s="48" t="n"/>
+      <c r="M347" s="48" t="n"/>
+      <c r="N347" s="48" t="n"/>
+      <c r="O347" s="48" t="n"/>
+      <c r="P347" s="48" t="n"/>
+      <c r="Q347" s="48" t="n"/>
+    </row>
+    <row r="348" ht="22" customHeight="1">
+      <c r="A348" s="37" t="inlineStr">
+        <is>
+          <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
+        </is>
+      </c>
+      <c r="Q348" s="38">
+        <f>-Q343*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="349" ht="22" customHeight="1">
+      <c r="A349" s="45" t="inlineStr">
+        <is>
+          <t>Paketpreis netto</t>
+        </is>
+      </c>
+      <c r="Q349" s="46">
+        <f>Q343+Q348</f>
+        <v/>
+      </c>
+    </row>
+    <row r="350" ht="22" customHeight="1">
+      <c r="A350" s="37" t="inlineStr">
+        <is>
+          <t>zzgl. 19 % Umsatzsteuer</t>
+        </is>
+      </c>
+      <c r="Q350" s="38">
+        <f>Q349*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="351" ht="26" customHeight="1">
+      <c r="A351" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q340" s="40">
-        <f>Q338+Q339</f>
-        <v/>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" s="42" t="inlineStr">
+      <c r="Q351" s="40">
+        <f>Q349+Q350</f>
+        <v/>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="343">
-      <c r="A343" s="49" t="inlineStr">
+    <row r="354">
+      <c r="A354" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="344"/>
-    <row r="345"/>
-    <row r="346"/>
+    <row r="355"/>
+    <row r="356"/>
+    <row r="357"/>
   </sheetData>
-  <autoFilter ref="A7:Q322"/>
+  <autoFilter ref="A7:Q333"/>
   <mergeCells count="26">
-    <mergeCell ref="A329:Q329"/>
     <mergeCell ref="C1:Q1"/>
+    <mergeCell ref="A347:Q347"/>
+    <mergeCell ref="A352:Q352"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A327:P327"/>
-    <mergeCell ref="A333:P333"/>
-    <mergeCell ref="A332:P332"/>
+    <mergeCell ref="A336:P336"/>
+    <mergeCell ref="A340:Q340"/>
     <mergeCell ref="L4:Q4"/>
+    <mergeCell ref="A348:P348"/>
     <mergeCell ref="C3:I3"/>
+    <mergeCell ref="A344:P344"/>
     <mergeCell ref="A338:P338"/>
-    <mergeCell ref="A328:P328"/>
     <mergeCell ref="A337:P337"/>
-    <mergeCell ref="A340:P340"/>
-    <mergeCell ref="A325:P325"/>
+    <mergeCell ref="A335:Q335"/>
+    <mergeCell ref="A350:P350"/>
+    <mergeCell ref="A349:P349"/>
     <mergeCell ref="A339:P339"/>
-    <mergeCell ref="A334:P334"/>
+    <mergeCell ref="A343:P343"/>
     <mergeCell ref="C4:I4"/>
-    <mergeCell ref="A341:Q341"/>
-    <mergeCell ref="A331:Q331"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
-    <mergeCell ref="A326:P326"/>
-    <mergeCell ref="A324:Q324"/>
-    <mergeCell ref="A336:Q336"/>
+    <mergeCell ref="A345:P345"/>
+    <mergeCell ref="A342:Q342"/>
+    <mergeCell ref="A351:P351"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A343:Q346"/>
+    <mergeCell ref="A354:Q357"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q322">
+  <conditionalFormatting sqref="A8:Q333">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N322" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N333" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O322" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O333" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$333</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$334</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8593,6 +8593,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>333</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="704850" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="328" name="Image 328" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId328"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -8885,7 +8910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q357"/>
+  <dimension ref="A1:Q358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -28681,261 +28706,321 @@
         <v/>
       </c>
     </row>
-    <row r="335" ht="24" customHeight="1">
-      <c r="A335" s="36" t="inlineStr">
+    <row r="334" ht="78" customHeight="1">
+      <c r="A334" s="9" t="n">
+        <v>327</v>
+      </c>
+      <c r="B334" s="35" t="inlineStr">
+        <is>
+          <t>NE05-12</t>
+        </is>
+      </c>
+      <c r="C334" s="11" t="n"/>
+      <c r="D334" s="12" t="inlineStr">
+        <is>
+          <t>Freischwinger weiß, Kindergröße
+Freischwinger aus einem Stück Kunststoff, weiß matt, S-förmig geschwungen. Kindergröße.</t>
+        </is>
+      </c>
+      <c r="E334" s="13" t="n"/>
+      <c r="F334" s="12" t="inlineStr">
+        <is>
+          <t>Speisesaal</t>
+        </is>
+      </c>
+      <c r="G334" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H334" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I334" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J334" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="K334" s="15">
+        <f>J334*1.19</f>
+        <v/>
+      </c>
+      <c r="L334" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M334" s="12" t="inlineStr">
+        <is>
+          <t>nur Abholung</t>
+        </is>
+      </c>
+      <c r="N334" s="16" t="n"/>
+      <c r="O334" s="17" t="n"/>
+      <c r="P334" s="18" t="n"/>
+      <c r="Q334" s="19">
+        <f>IF(N334&lt;&gt;"ja","",IF(O334="",H334,O334)*J334)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="336" ht="24" customHeight="1">
+      <c r="A336" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B335" s="1" t="n"/>
-      <c r="C335" s="1" t="n"/>
-      <c r="D335" s="1" t="n"/>
-      <c r="E335" s="1" t="n"/>
-      <c r="F335" s="1" t="n"/>
-      <c r="G335" s="1" t="n"/>
-      <c r="H335" s="1" t="n"/>
-      <c r="I335" s="1" t="n"/>
-      <c r="J335" s="1" t="n"/>
-      <c r="K335" s="1" t="n"/>
-      <c r="L335" s="1" t="n"/>
-      <c r="M335" s="1" t="n"/>
-      <c r="N335" s="1" t="n"/>
-      <c r="O335" s="1" t="n"/>
-      <c r="P335" s="1" t="n"/>
-      <c r="Q335" s="1" t="n"/>
-    </row>
-    <row r="336" ht="22" customHeight="1">
-      <c r="A336" s="37" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl netto</t>
-        </is>
-      </c>
-      <c r="Q336" s="38">
-        <f>SUM(Q8:Q333)</f>
-        <v/>
-      </c>
+      <c r="B336" s="1" t="n"/>
+      <c r="C336" s="1" t="n"/>
+      <c r="D336" s="1" t="n"/>
+      <c r="E336" s="1" t="n"/>
+      <c r="F336" s="1" t="n"/>
+      <c r="G336" s="1" t="n"/>
+      <c r="H336" s="1" t="n"/>
+      <c r="I336" s="1" t="n"/>
+      <c r="J336" s="1" t="n"/>
+      <c r="K336" s="1" t="n"/>
+      <c r="L336" s="1" t="n"/>
+      <c r="M336" s="1" t="n"/>
+      <c r="N336" s="1" t="n"/>
+      <c r="O336" s="1" t="n"/>
+      <c r="P336" s="1" t="n"/>
+      <c r="Q336" s="1" t="n"/>
     </row>
     <row r="337" ht="22" customHeight="1">
       <c r="A337" s="37" t="inlineStr">
         <is>
+          <t>Wert Ihrer Auswahl netto</t>
+        </is>
+      </c>
+      <c r="Q337" s="38">
+        <f>SUM(Q8:Q334)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="338" ht="22" customHeight="1">
+      <c r="A338" s="37" t="inlineStr">
+        <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q337" s="38">
-        <f>Q336*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="338" ht="26" customHeight="1">
-      <c r="A338" s="39" t="inlineStr">
+      <c r="Q338" s="38">
+        <f>Q337*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="339" ht="26" customHeight="1">
+      <c r="A339" s="39" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl brutto</t>
         </is>
       </c>
-      <c r="Q338" s="40">
-        <f>Q336+Q337</f>
-        <v/>
-      </c>
-    </row>
-    <row r="339" ht="22" customHeight="1">
-      <c r="A339" s="37" t="inlineStr">
+      <c r="Q339" s="40">
+        <f>Q337+Q338</f>
+        <v/>
+      </c>
+    </row>
+    <row r="340" ht="22" customHeight="1">
+      <c r="A340" s="37" t="inlineStr">
         <is>
           <t>gewählte Positionen</t>
         </is>
       </c>
-      <c r="Q339" s="41">
-        <f>COUNTIF(N8:N333,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="42" t="inlineStr">
+      <c r="Q340" s="41">
+        <f>COUNTIF(N8:N334,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="42" t="inlineStr">
         <is>
           <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
         </is>
       </c>
     </row>
-    <row r="342" ht="24" customHeight="1">
-      <c r="A342" s="43" t="inlineStr">
+    <row r="343" ht="24" customHeight="1">
+      <c r="A343" s="43" t="inlineStr">
         <is>
           <t>B · GESAMTBESTAND</t>
         </is>
       </c>
-      <c r="B342" s="44" t="n"/>
-      <c r="C342" s="44" t="n"/>
-      <c r="D342" s="44" t="n"/>
-      <c r="E342" s="44" t="n"/>
-      <c r="F342" s="44" t="n"/>
-      <c r="G342" s="44" t="n"/>
-      <c r="H342" s="44" t="n"/>
-      <c r="I342" s="44" t="n"/>
-      <c r="J342" s="44" t="n"/>
-      <c r="K342" s="44" t="n"/>
-      <c r="L342" s="44" t="n"/>
-      <c r="M342" s="44" t="n"/>
-      <c r="N342" s="44" t="n"/>
-      <c r="O342" s="44" t="n"/>
-      <c r="P342" s="44" t="n"/>
-      <c r="Q342" s="44" t="n"/>
-    </row>
-    <row r="343" ht="22" customHeight="1">
-      <c r="A343" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
-        </is>
-      </c>
-      <c r="Q343" s="38">
-        <f>SUMPRODUCT(H8:H333,J8:J333)</f>
-        <v/>
-      </c>
+      <c r="B343" s="44" t="n"/>
+      <c r="C343" s="44" t="n"/>
+      <c r="D343" s="44" t="n"/>
+      <c r="E343" s="44" t="n"/>
+      <c r="F343" s="44" t="n"/>
+      <c r="G343" s="44" t="n"/>
+      <c r="H343" s="44" t="n"/>
+      <c r="I343" s="44" t="n"/>
+      <c r="J343" s="44" t="n"/>
+      <c r="K343" s="44" t="n"/>
+      <c r="L343" s="44" t="n"/>
+      <c r="M343" s="44" t="n"/>
+      <c r="N343" s="44" t="n"/>
+      <c r="O343" s="44" t="n"/>
+      <c r="P343" s="44" t="n"/>
+      <c r="Q343" s="44" t="n"/>
     </row>
     <row r="344" ht="22" customHeight="1">
       <c r="A344" s="37" t="inlineStr">
         <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q344" s="38">
+        <f>SUMPRODUCT(H8:H334,J8:J334)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="345" ht="22" customHeight="1">
+      <c r="A345" s="37" t="inlineStr">
+        <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q344" s="38">
-        <f>Q343*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="345" ht="22" customHeight="1">
-      <c r="A345" s="45" t="inlineStr">
+      <c r="Q345" s="38">
+        <f>Q344*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="346" ht="22" customHeight="1">
+      <c r="A346" s="45" t="inlineStr">
         <is>
           <t>Gesamtwert brutto</t>
         </is>
       </c>
-      <c r="Q345" s="46">
-        <f>Q343+Q344</f>
-        <v/>
-      </c>
-    </row>
-    <row r="347" ht="24" customHeight="1">
-      <c r="A347" s="47" t="inlineStr">
+      <c r="Q346" s="46">
+        <f>Q344+Q345</f>
+        <v/>
+      </c>
+    </row>
+    <row r="348" ht="24" customHeight="1">
+      <c r="A348" s="47" t="inlineStr">
         <is>
           <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
         </is>
       </c>
-      <c r="B347" s="48" t="n"/>
-      <c r="C347" s="48" t="n"/>
-      <c r="D347" s="48" t="n"/>
-      <c r="E347" s="48" t="n"/>
-      <c r="F347" s="48" t="n"/>
-      <c r="G347" s="48" t="n"/>
-      <c r="H347" s="48" t="n"/>
-      <c r="I347" s="48" t="n"/>
-      <c r="J347" s="48" t="n"/>
-      <c r="K347" s="48" t="n"/>
-      <c r="L347" s="48" t="n"/>
-      <c r="M347" s="48" t="n"/>
-      <c r="N347" s="48" t="n"/>
-      <c r="O347" s="48" t="n"/>
-      <c r="P347" s="48" t="n"/>
-      <c r="Q347" s="48" t="n"/>
-    </row>
-    <row r="348" ht="22" customHeight="1">
-      <c r="A348" s="37" t="inlineStr">
+      <c r="B348" s="48" t="n"/>
+      <c r="C348" s="48" t="n"/>
+      <c r="D348" s="48" t="n"/>
+      <c r="E348" s="48" t="n"/>
+      <c r="F348" s="48" t="n"/>
+      <c r="G348" s="48" t="n"/>
+      <c r="H348" s="48" t="n"/>
+      <c r="I348" s="48" t="n"/>
+      <c r="J348" s="48" t="n"/>
+      <c r="K348" s="48" t="n"/>
+      <c r="L348" s="48" t="n"/>
+      <c r="M348" s="48" t="n"/>
+      <c r="N348" s="48" t="n"/>
+      <c r="O348" s="48" t="n"/>
+      <c r="P348" s="48" t="n"/>
+      <c r="Q348" s="48" t="n"/>
+    </row>
+    <row r="349" ht="22" customHeight="1">
+      <c r="A349" s="37" t="inlineStr">
         <is>
           <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
         </is>
       </c>
-      <c r="Q348" s="38">
-        <f>-Q343*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="349" ht="22" customHeight="1">
-      <c r="A349" s="45" t="inlineStr">
+      <c r="Q349" s="38">
+        <f>-Q344*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="350" ht="22" customHeight="1">
+      <c r="A350" s="45" t="inlineStr">
         <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="Q349" s="46">
-        <f>Q343+Q348</f>
-        <v/>
-      </c>
-    </row>
-    <row r="350" ht="22" customHeight="1">
-      <c r="A350" s="37" t="inlineStr">
+      <c r="Q350" s="46">
+        <f>Q344+Q349</f>
+        <v/>
+      </c>
+    </row>
+    <row r="351" ht="22" customHeight="1">
+      <c r="A351" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q350" s="38">
-        <f>Q349*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="351" ht="26" customHeight="1">
-      <c r="A351" s="39" t="inlineStr">
+      <c r="Q351" s="38">
+        <f>Q350*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="352" ht="26" customHeight="1">
+      <c r="A352" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q351" s="40">
-        <f>Q349+Q350</f>
-        <v/>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" s="42" t="inlineStr">
+      <c r="Q352" s="40">
+        <f>Q350+Q351</f>
+        <v/>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="354">
-      <c r="A354" s="49" t="inlineStr">
+    <row r="355">
+      <c r="A355" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="355"/>
     <row r="356"/>
     <row r="357"/>
+    <row r="358"/>
   </sheetData>
-  <autoFilter ref="A7:Q333"/>
+  <autoFilter ref="A7:Q334"/>
   <mergeCells count="26">
+    <mergeCell ref="A353:Q353"/>
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A347:Q347"/>
-    <mergeCell ref="A352:Q352"/>
+    <mergeCell ref="A355:Q358"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A336:P336"/>
-    <mergeCell ref="A340:Q340"/>
     <mergeCell ref="L4:Q4"/>
-    <mergeCell ref="A348:P348"/>
+    <mergeCell ref="A343:Q343"/>
     <mergeCell ref="C3:I3"/>
     <mergeCell ref="A344:P344"/>
     <mergeCell ref="A338:P338"/>
+    <mergeCell ref="A352:P352"/>
     <mergeCell ref="A337:P337"/>
-    <mergeCell ref="A335:Q335"/>
     <mergeCell ref="A350:P350"/>
+    <mergeCell ref="A340:P340"/>
     <mergeCell ref="A349:P349"/>
     <mergeCell ref="A339:P339"/>
-    <mergeCell ref="A343:P343"/>
     <mergeCell ref="C4:I4"/>
+    <mergeCell ref="A341:Q341"/>
+    <mergeCell ref="A346:P346"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
     <mergeCell ref="A345:P345"/>
-    <mergeCell ref="A342:Q342"/>
+    <mergeCell ref="A336:Q336"/>
     <mergeCell ref="A351:P351"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A354:Q357"/>
+    <mergeCell ref="A348:Q348"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q333">
+  <conditionalFormatting sqref="A8:Q334">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N333" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N334" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O333" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O334" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>

--- a/ausgabe/02_Angebot_Klinik.xlsx
+++ b/ausgabe/02_Angebot_Klinik.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Angebot" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$333</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Angebot'!$A$7:$Q$334</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -8593,6 +8593,31 @@
     </pic>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>333</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1257300" cy="942975"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="328" name="Image 328" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId328"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -8885,7 +8910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q357"/>
+  <dimension ref="A1:Q358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -15721,8 +15746,8 @@
       <c r="C118" s="11" t="n"/>
       <c r="D118" s="12" t="inlineStr">
         <is>
-          <t>Sitztier Elefant, weiß und schwarz
-Sitztier in Elefantenform aus Kunststoff, ein weißes und ein schwarzes Exemplar in gleicher Größe. Am Ohr ein ovales Metallplättchen mit eingravierter Signatur.</t>
+          <t>Vitra Eames Elephant, große Ausführung
+Eames Elephant von Vitra, Entwurf Charles und Ray Eames 1945: Sitz- und Spieltier in Elefantenform aus Kunststoff, große Ausführung. An der Flanke ein rundes Metallplättchen mit der Prägung "Design: Charles &amp; Ray Eames, 1945 – © Eames Office – www.vitra.com – Elephant". Ein weißes und zwei schwarze Exemplare, alle mit Gebrauchsspuren und Kratzern.</t>
         </is>
       </c>
       <c r="E118" s="13" t="n"/>
@@ -15737,7 +15762,7 @@
         </is>
       </c>
       <c r="H118" s="10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I118" s="10" t="inlineStr">
         <is>
@@ -15745,7 +15770,7 @@
         </is>
       </c>
       <c r="J118" s="14" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="K118" s="15">
         <f>J118*1.19</f>
@@ -17581,8 +17606,8 @@
       <c r="C149" s="22" t="n"/>
       <c r="D149" s="23" t="inlineStr">
         <is>
-          <t>Mitwachsender Treppenhochstuhl, weiß
-Treppenhochstuhl aus Buche mit weißen Sitz- und Rückenplatten, Sitz und Fußbrett in der Höhe verstellbar. Die Seitenwangen tragen Lochreihen für die Verstellung.</t>
+          <t>Stokke Steps Treppenhochstuhl, weiß mit Buchengestell
+Stokke Steps: mitwachsender Treppenhochstuhl, Seitenwangen aus Buche natur, Sitz- und Fußbrett sowie Rückenlehne mit Bügel in Weiß, in der Höhe verstellbar.</t>
         </is>
       </c>
       <c r="E149" s="13" t="n"/>
@@ -17605,7 +17630,7 @@
         </is>
       </c>
       <c r="J149" s="24" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="K149" s="25">
         <f>J149*1.19</f>
@@ -27973,8 +27998,8 @@
       <c r="C322" s="11" t="n"/>
       <c r="D322" s="12" t="inlineStr">
         <is>
-          <t>Freischwinger rot, Erwachsenengröße
-Freischwinger aus einem Stück Kunststoff, rot matt, S-förmig geschwungen. Erwachsenengröße.</t>
+          <t>Vitra Panton Chair rot, Erwachsenengröße
+Panton Chair von Vitra, Entwurf Verner Panton: Freischwinger aus einem Stück Kunststoff, rot matt, S-förmig geschwungen. Erwachsenengröße. Aufkleber an der Unterseite: 44003000, 26.03.2019.</t>
         </is>
       </c>
       <c r="E322" s="13" t="n"/>
@@ -27997,7 +28022,7 @@
         </is>
       </c>
       <c r="J322" s="14" t="n">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="K322" s="15">
         <f>J322*1.19</f>
@@ -28033,8 +28058,8 @@
       <c r="C323" s="22" t="n"/>
       <c r="D323" s="23" t="inlineStr">
         <is>
-          <t>Freischwinger rot, Kindergröße
-Freischwinger aus einem Stück Kunststoff, rot matt, S-förmig geschwungen. Kindergröße.</t>
+          <t>Vitra Panton Chair Junior rot, Kindergröße
+Panton Chair Junior von Vitra, Entwurf Verner Panton: Freischwinger aus einem Stück Kunststoff, rot matt, S-förmig geschwungen, in Kindergröße. Die Aufkleber an der Unterseite sind nicht mehr lesbar; der Stuhl in Erwachsenengröße aus demselben Raum (NE05-04) trägt den Vitra-Aufkleber.</t>
         </is>
       </c>
       <c r="E323" s="13" t="n"/>
@@ -28057,7 +28082,7 @@
         </is>
       </c>
       <c r="J323" s="24" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="K323" s="25">
         <f>J323*1.19</f>
@@ -28093,8 +28118,8 @@
       <c r="C324" s="11" t="n"/>
       <c r="D324" s="12" t="inlineStr">
         <is>
-          <t>Treppenhochstuhl schwarz
-Mitwachsender Treppenhochstuhl: Seitenwangen und Platten schwarz lackiert, Sitz- und Fußbrett in der Höhe verstellbar, umlaufender Bügel mit Rückenlehne. Die Seitenwangen tragen Lochreihen für die Verstellung.</t>
+          <t>Stokke Steps Treppenhochstuhl, schwarz
+Stokke Steps: mitwachsender Treppenhochstuhl, Seitenwangen und Platten schwarz, Sitz- und Fußbrett in der Höhe verstellbar, Rückenlehne mit umlaufendem Bügel. Artikelnummer 460002.</t>
         </is>
       </c>
       <c r="E324" s="13" t="n"/>
@@ -28117,7 +28142,7 @@
         </is>
       </c>
       <c r="J324" s="14" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="K324" s="15">
         <f>J324*1.19</f>
@@ -28153,8 +28178,8 @@
       <c r="C325" s="22" t="n"/>
       <c r="D325" s="23" t="inlineStr">
         <is>
-          <t>Treppenhochstuhl schwarz-weiß
-Mitwachsender Treppenhochstuhl: Seitenwangen schwarz lackiert, Sitz- und Fußbrett sowie Bügel mit Rückenlehne in Weiß, in der Höhe verstellbar. Die Seitenwangen tragen Lochreihen für die Verstellung.</t>
+          <t>Stokke Steps Treppenhochstuhl, weiß mit schwarzem Gestell
+Stokke Steps: mitwachsender Treppenhochstuhl, Seitenwangen schwarz, Sitz- und Fußbrett sowie Rückenlehne mit Bügel in Weiß, in der Höhe verstellbar. Artikelnummer 460001.</t>
         </is>
       </c>
       <c r="E325" s="13" t="n"/>
@@ -28177,7 +28202,7 @@
         </is>
       </c>
       <c r="J325" s="24" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="K325" s="25">
         <f>J325*1.19</f>
@@ -28213,8 +28238,8 @@
       <c r="C326" s="11" t="n"/>
       <c r="D326" s="12" t="inlineStr">
         <is>
-          <t>Treppenhochstuhl grau mit Buchengestell
-Mitwachsender Treppenhochstuhl: Seitenwangen aus Buche natur, Sitz- und Fußbrett sowie Bügel mit Rückenlehne in Grau, in der Höhe verstellbar. Die Seitenwangen tragen Lochreihen für die Verstellung.</t>
+          <t>Stokke Steps Treppenhochstuhl, grau mit Buchengestell
+Stokke Steps: mitwachsender Treppenhochstuhl, Seitenwangen aus Buche natur, Sitz- und Fußbrett sowie Rückenlehne mit Bügel in Grau, in der Höhe verstellbar. Artikelnummer 460003.</t>
         </is>
       </c>
       <c r="E326" s="13" t="n"/>
@@ -28237,7 +28262,7 @@
         </is>
       </c>
       <c r="J326" s="14" t="n">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="K326" s="15">
         <f>J326*1.19</f>
@@ -28633,8 +28658,8 @@
       <c r="C333" s="22" t="n"/>
       <c r="D333" s="23" t="inlineStr">
         <is>
-          <t>Freischwinger weiß, Kindergröße
-Freischwinger aus einem Stück Kunststoff, weiß matt, S-förmig geschwungen. Kindergröße.</t>
+          <t>Vitra Panton Chair Junior weiß, Kindergröße
+Panton Chair Junior von Vitra, Entwurf Verner Panton: Freischwinger aus einem Stück Kunststoff, weiß matt, S-förmig geschwungen, in Kindergröße. Die Aufkleber an der Unterseite sind nicht mehr lesbar; der Stuhl in Erwachsenengröße aus demselben Raum (NE05-04) trägt den Vitra-Aufkleber.</t>
         </is>
       </c>
       <c r="E333" s="13" t="n"/>
@@ -28657,7 +28682,7 @@
         </is>
       </c>
       <c r="J333" s="24" t="n">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="K333" s="25">
         <f>J333*1.19</f>
@@ -28681,261 +28706,321 @@
         <v/>
       </c>
     </row>
-    <row r="335" ht="24" customHeight="1">
-      <c r="A335" s="36" t="inlineStr">
+    <row r="334" ht="78" customHeight="1">
+      <c r="A334" s="9" t="n">
+        <v>327</v>
+      </c>
+      <c r="B334" s="35" t="inlineStr">
+        <is>
+          <t>NU02-25</t>
+        </is>
+      </c>
+      <c r="C334" s="11" t="n"/>
+      <c r="D334" s="12" t="inlineStr">
+        <is>
+          <t>Vitra Eames Elephant, kleine Ausführung, schwarz
+Eames Elephant Small von Vitra, Entwurf Charles und Ray Eames 1945: Sitz- und Spieltier in Elefantenform aus Kunststoff, kleine Ausführung, schwarz. An der Flanke das runde Vitra-Metallplättchen.</t>
+        </is>
+      </c>
+      <c r="E334" s="13" t="n"/>
+      <c r="F334" s="12" t="inlineStr">
+        <is>
+          <t>Gruppenraum 5</t>
+        </is>
+      </c>
+      <c r="G334" s="10" t="inlineStr">
+        <is>
+          <t>gebraucht</t>
+        </is>
+      </c>
+      <c r="H334" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="I334" s="10" t="inlineStr">
+        <is>
+          <t>Stück</t>
+        </is>
+      </c>
+      <c r="J334" s="14" t="n">
+        <v>110</v>
+      </c>
+      <c r="K334" s="15">
+        <f>J334*1.19</f>
+        <v/>
+      </c>
+      <c r="L334" s="10" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="M334" s="12" t="inlineStr">
+        <is>
+          <t>Versand möglich</t>
+        </is>
+      </c>
+      <c r="N334" s="16" t="n"/>
+      <c r="O334" s="17" t="n"/>
+      <c r="P334" s="18" t="n"/>
+      <c r="Q334" s="19">
+        <f>IF(N334&lt;&gt;"ja","",IF(O334="",H334,O334)*J334)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="336" ht="24" customHeight="1">
+      <c r="A336" s="36" t="inlineStr">
         <is>
           <t>A · IHRE AUSWAHL</t>
         </is>
       </c>
-      <c r="B335" s="1" t="n"/>
-      <c r="C335" s="1" t="n"/>
-      <c r="D335" s="1" t="n"/>
-      <c r="E335" s="1" t="n"/>
-      <c r="F335" s="1" t="n"/>
-      <c r="G335" s="1" t="n"/>
-      <c r="H335" s="1" t="n"/>
-      <c r="I335" s="1" t="n"/>
-      <c r="J335" s="1" t="n"/>
-      <c r="K335" s="1" t="n"/>
-      <c r="L335" s="1" t="n"/>
-      <c r="M335" s="1" t="n"/>
-      <c r="N335" s="1" t="n"/>
-      <c r="O335" s="1" t="n"/>
-      <c r="P335" s="1" t="n"/>
-      <c r="Q335" s="1" t="n"/>
-    </row>
-    <row r="336" ht="22" customHeight="1">
-      <c r="A336" s="37" t="inlineStr">
-        <is>
-          <t>Wert Ihrer Auswahl netto</t>
-        </is>
-      </c>
-      <c r="Q336" s="38">
-        <f>SUM(Q8:Q333)</f>
-        <v/>
-      </c>
+      <c r="B336" s="1" t="n"/>
+      <c r="C336" s="1" t="n"/>
+      <c r="D336" s="1" t="n"/>
+      <c r="E336" s="1" t="n"/>
+      <c r="F336" s="1" t="n"/>
+      <c r="G336" s="1" t="n"/>
+      <c r="H336" s="1" t="n"/>
+      <c r="I336" s="1" t="n"/>
+      <c r="J336" s="1" t="n"/>
+      <c r="K336" s="1" t="n"/>
+      <c r="L336" s="1" t="n"/>
+      <c r="M336" s="1" t="n"/>
+      <c r="N336" s="1" t="n"/>
+      <c r="O336" s="1" t="n"/>
+      <c r="P336" s="1" t="n"/>
+      <c r="Q336" s="1" t="n"/>
     </row>
     <row r="337" ht="22" customHeight="1">
       <c r="A337" s="37" t="inlineStr">
         <is>
+          <t>Wert Ihrer Auswahl netto</t>
+        </is>
+      </c>
+      <c r="Q337" s="38">
+        <f>SUM(Q8:Q334)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="338" ht="22" customHeight="1">
+      <c r="A338" s="37" t="inlineStr">
+        <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q337" s="38">
-        <f>Q336*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="338" ht="26" customHeight="1">
-      <c r="A338" s="39" t="inlineStr">
+      <c r="Q338" s="38">
+        <f>Q337*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="339" ht="26" customHeight="1">
+      <c r="A339" s="39" t="inlineStr">
         <is>
           <t>Wert Ihrer Auswahl brutto</t>
         </is>
       </c>
-      <c r="Q338" s="40">
-        <f>Q336+Q337</f>
-        <v/>
-      </c>
-    </row>
-    <row r="339" ht="22" customHeight="1">
-      <c r="A339" s="37" t="inlineStr">
+      <c r="Q339" s="40">
+        <f>Q337+Q338</f>
+        <v/>
+      </c>
+    </row>
+    <row r="340" ht="22" customHeight="1">
+      <c r="A340" s="37" t="inlineStr">
         <is>
           <t>gewählte Positionen</t>
         </is>
       </c>
-      <c r="Q339" s="41">
-        <f>COUNTIF(N8:N333,"ja")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" s="42" t="inlineStr">
+      <c r="Q340" s="41">
+        <f>COUNTIF(N8:N334,"ja")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="42" t="inlineStr">
         <is>
           <t>Solange Sie nichts eintragen, bleiben diese Summen leer. Ihre Eintragungen sind eine Interessenbekundung und keine Reservierung.</t>
         </is>
       </c>
     </row>
-    <row r="342" ht="24" customHeight="1">
-      <c r="A342" s="43" t="inlineStr">
+    <row r="343" ht="24" customHeight="1">
+      <c r="A343" s="43" t="inlineStr">
         <is>
           <t>B · GESAMTBESTAND</t>
         </is>
       </c>
-      <c r="B342" s="44" t="n"/>
-      <c r="C342" s="44" t="n"/>
-      <c r="D342" s="44" t="n"/>
-      <c r="E342" s="44" t="n"/>
-      <c r="F342" s="44" t="n"/>
-      <c r="G342" s="44" t="n"/>
-      <c r="H342" s="44" t="n"/>
-      <c r="I342" s="44" t="n"/>
-      <c r="J342" s="44" t="n"/>
-      <c r="K342" s="44" t="n"/>
-      <c r="L342" s="44" t="n"/>
-      <c r="M342" s="44" t="n"/>
-      <c r="N342" s="44" t="n"/>
-      <c r="O342" s="44" t="n"/>
-      <c r="P342" s="44" t="n"/>
-      <c r="Q342" s="44" t="n"/>
-    </row>
-    <row r="343" ht="22" customHeight="1">
-      <c r="A343" s="37" t="inlineStr">
-        <is>
-          <t>Gesamtwert aller gelisteten Positionen netto</t>
-        </is>
-      </c>
-      <c r="Q343" s="38">
-        <f>SUMPRODUCT(H8:H333,J8:J333)</f>
-        <v/>
-      </c>
+      <c r="B343" s="44" t="n"/>
+      <c r="C343" s="44" t="n"/>
+      <c r="D343" s="44" t="n"/>
+      <c r="E343" s="44" t="n"/>
+      <c r="F343" s="44" t="n"/>
+      <c r="G343" s="44" t="n"/>
+      <c r="H343" s="44" t="n"/>
+      <c r="I343" s="44" t="n"/>
+      <c r="J343" s="44" t="n"/>
+      <c r="K343" s="44" t="n"/>
+      <c r="L343" s="44" t="n"/>
+      <c r="M343" s="44" t="n"/>
+      <c r="N343" s="44" t="n"/>
+      <c r="O343" s="44" t="n"/>
+      <c r="P343" s="44" t="n"/>
+      <c r="Q343" s="44" t="n"/>
     </row>
     <row r="344" ht="22" customHeight="1">
       <c r="A344" s="37" t="inlineStr">
         <is>
+          <t>Gesamtwert aller gelisteten Positionen netto</t>
+        </is>
+      </c>
+      <c r="Q344" s="38">
+        <f>SUMPRODUCT(H8:H334,J8:J334)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="345" ht="22" customHeight="1">
+      <c r="A345" s="37" t="inlineStr">
+        <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q344" s="38">
-        <f>Q343*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="345" ht="22" customHeight="1">
-      <c r="A345" s="45" t="inlineStr">
+      <c r="Q345" s="38">
+        <f>Q344*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="346" ht="22" customHeight="1">
+      <c r="A346" s="45" t="inlineStr">
         <is>
           <t>Gesamtwert brutto</t>
         </is>
       </c>
-      <c r="Q345" s="46">
-        <f>Q343+Q344</f>
-        <v/>
-      </c>
-    </row>
-    <row r="347" ht="24" customHeight="1">
-      <c r="A347" s="47" t="inlineStr">
+      <c r="Q346" s="46">
+        <f>Q344+Q345</f>
+        <v/>
+      </c>
+    </row>
+    <row r="348" ht="24" customHeight="1">
+      <c r="A348" s="47" t="inlineStr">
         <is>
           <t>C · PAKETANGEBOT  (Übernahme des gesamten Bestands)</t>
         </is>
       </c>
-      <c r="B347" s="48" t="n"/>
-      <c r="C347" s="48" t="n"/>
-      <c r="D347" s="48" t="n"/>
-      <c r="E347" s="48" t="n"/>
-      <c r="F347" s="48" t="n"/>
-      <c r="G347" s="48" t="n"/>
-      <c r="H347" s="48" t="n"/>
-      <c r="I347" s="48" t="n"/>
-      <c r="J347" s="48" t="n"/>
-      <c r="K347" s="48" t="n"/>
-      <c r="L347" s="48" t="n"/>
-      <c r="M347" s="48" t="n"/>
-      <c r="N347" s="48" t="n"/>
-      <c r="O347" s="48" t="n"/>
-      <c r="P347" s="48" t="n"/>
-      <c r="Q347" s="48" t="n"/>
-    </row>
-    <row r="348" ht="22" customHeight="1">
-      <c r="A348" s="37" t="inlineStr">
+      <c r="B348" s="48" t="n"/>
+      <c r="C348" s="48" t="n"/>
+      <c r="D348" s="48" t="n"/>
+      <c r="E348" s="48" t="n"/>
+      <c r="F348" s="48" t="n"/>
+      <c r="G348" s="48" t="n"/>
+      <c r="H348" s="48" t="n"/>
+      <c r="I348" s="48" t="n"/>
+      <c r="J348" s="48" t="n"/>
+      <c r="K348" s="48" t="n"/>
+      <c r="L348" s="48" t="n"/>
+      <c r="M348" s="48" t="n"/>
+      <c r="N348" s="48" t="n"/>
+      <c r="O348" s="48" t="n"/>
+      <c r="P348" s="48" t="n"/>
+      <c r="Q348" s="48" t="n"/>
+    </row>
+    <row r="349" ht="22" customHeight="1">
+      <c r="A349" s="37" t="inlineStr">
         <is>
           <t>Gesamtwert netto abzüglich Paketnachlass 15 %</t>
         </is>
       </c>
-      <c r="Q348" s="38">
-        <f>-Q343*0.15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="349" ht="22" customHeight="1">
-      <c r="A349" s="45" t="inlineStr">
+      <c r="Q349" s="38">
+        <f>-Q344*0.15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="350" ht="22" customHeight="1">
+      <c r="A350" s="45" t="inlineStr">
         <is>
           <t>Paketpreis netto</t>
         </is>
       </c>
-      <c r="Q349" s="46">
-        <f>Q343+Q348</f>
-        <v/>
-      </c>
-    </row>
-    <row r="350" ht="22" customHeight="1">
-      <c r="A350" s="37" t="inlineStr">
+      <c r="Q350" s="46">
+        <f>Q344+Q349</f>
+        <v/>
+      </c>
+    </row>
+    <row r="351" ht="22" customHeight="1">
+      <c r="A351" s="37" t="inlineStr">
         <is>
           <t>zzgl. 19 % Umsatzsteuer</t>
         </is>
       </c>
-      <c r="Q350" s="38">
-        <f>Q349*0.19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="351" ht="26" customHeight="1">
-      <c r="A351" s="39" t="inlineStr">
+      <c r="Q351" s="38">
+        <f>Q350*0.19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="352" ht="26" customHeight="1">
+      <c r="A352" s="39" t="inlineStr">
         <is>
           <t>Paketpreis brutto</t>
         </is>
       </c>
-      <c r="Q351" s="40">
-        <f>Q349+Q350</f>
-        <v/>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" s="42" t="inlineStr">
+      <c r="Q352" s="40">
+        <f>Q350+Q351</f>
+        <v/>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="42" t="inlineStr">
         <is>
           <t>Das Paketangebot gilt für die Übernahme sämtlicher oben gelisteter Positionen in einem Zug, inklusive Abholung innerhalb von zwei Wochen nach Zuschlag. Sprechen Sie uns dafür bitte direkt an – eine Reservierung im Onlinekatalog ist dann nicht nötig.</t>
         </is>
       </c>
     </row>
-    <row r="354">
-      <c r="A354" s="49" t="inlineStr">
+    <row r="355">
+      <c r="A355" s="49" t="inlineStr">
         <is>
           <t>Verkaufsbedingungen: Der Verkauf erfolgt aus einer Betriebsauflösung unter Ausschluss jeglicher Gewährleistung; es handelt sich durchweg um gebrauchte Gegenstände, die in dem Zustand verkauft werden, in dem sie sich befinden. Angebot freibleibend, Zwischenverkauf vorbehalten. Ihre Eintragungen in dieser Liste sind eine Interessenbekundung; verbindlich wird die Zuteilung erst mit unserer schriftlichen Bestätigung. Abholung nach Terminvereinbarung; Demontage, Verladung und Transport erfolgen durch den Käufer auf eigene Kosten und Gefahr. Elektrogeräte werden ohne Prüfnachweis nach DGUV V3 übergeben. Die Rechnung wird nach Abholung gestellt, zahlbar innerhalb von 14 Tagen ohne Abzug. Das Eigentum geht erst mit vollständiger Bezahlung über.
 Kikripp GmbH · Hermann-Schwer-Str. 1 · 78048 Villingen-Schwenningen · Jenny Preisigke · 07725 5179702 · jennyp@kikripp.de</t>
         </is>
       </c>
     </row>
-    <row r="355"/>
     <row r="356"/>
     <row r="357"/>
+    <row r="358"/>
   </sheetData>
-  <autoFilter ref="A7:Q333"/>
+  <autoFilter ref="A7:Q334"/>
   <mergeCells count="26">
+    <mergeCell ref="A353:Q353"/>
     <mergeCell ref="C1:Q1"/>
-    <mergeCell ref="A347:Q347"/>
-    <mergeCell ref="A352:Q352"/>
+    <mergeCell ref="A355:Q358"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="A336:P336"/>
-    <mergeCell ref="A340:Q340"/>
     <mergeCell ref="L4:Q4"/>
-    <mergeCell ref="A348:P348"/>
+    <mergeCell ref="A343:Q343"/>
     <mergeCell ref="C3:I3"/>
     <mergeCell ref="A344:P344"/>
     <mergeCell ref="A338:P338"/>
+    <mergeCell ref="A352:P352"/>
     <mergeCell ref="A337:P337"/>
-    <mergeCell ref="A335:Q335"/>
     <mergeCell ref="A350:P350"/>
+    <mergeCell ref="A340:P340"/>
     <mergeCell ref="A349:P349"/>
     <mergeCell ref="A339:P339"/>
-    <mergeCell ref="A343:P343"/>
     <mergeCell ref="C4:I4"/>
+    <mergeCell ref="A341:Q341"/>
+    <mergeCell ref="A346:P346"/>
     <mergeCell ref="A5:Q5"/>
     <mergeCell ref="L2:Q2"/>
     <mergeCell ref="A345:P345"/>
-    <mergeCell ref="A342:Q342"/>
+    <mergeCell ref="A336:Q336"/>
     <mergeCell ref="A351:P351"/>
     <mergeCell ref="C2:I2"/>
     <mergeCell ref="L3:Q3"/>
-    <mergeCell ref="A354:Q357"/>
+    <mergeCell ref="A348:Q348"/>
   </mergeCells>
-  <conditionalFormatting sqref="A8:Q333">
+  <conditionalFormatting sqref="A8:Q334">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="0">
       <formula>$N8="ja"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="N8:N333" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
+    <dataValidation sqref="N8:N334" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Interesse" error="Bitte „ja&quot; oder „nein&quot; wählen." type="list">
       <formula1>"ja,nein"</formula1>
     </dataValidation>
-    <dataValidation sqref="O8:O333" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
+    <dataValidation sqref="O8:O334" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Stückzahl" error="Bitte eine ganze Zahl größer 0 eintragen oder das Feld leer lassen – dann gilt die volle verfügbare Menge." type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
